--- a/data/topic_feeds.xlsx
+++ b/data/topic_feeds.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G121"/>
+  <dimension ref="A1:G197"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4429,6 +4429,2514 @@
         <v>46013.61065972222</v>
       </c>
     </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>Current_Affairs</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>(geopolitics OR migration OR economy OR conflict OR legislation OR terrorism OR disinformation OR misinformation OR government OR policy OR regulation) AND (briefing OR analysis OR update OR report)</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>US economy grew strongly in third quarter, GDP report says - The Guardian</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>Tue, 23 Dec 2025 13:41:00 GMT</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMigwFBVV95cUxPYXBVUXdiVWd3X3hOZk15a1F5MEowd2hkdFJGanYtQ0ZVMERfYVJwMEdPSjJyQXhVMXhWSnFkNGxxTnA2VUxhdzYyQnE1MXZfWmZIMHUzSi15VDZLaXEyemtiM25tQVRXV1dJZklHYW1ENkM5em5ITnRISzBTUS1TZy1ENA?oc=5</t>
+        </is>
+      </c>
+      <c r="F122" t="n">
+        <v>7</v>
+      </c>
+      <c r="G122" s="2" t="n">
+        <v>46014.57013888889</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>Current_Affairs</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>(geopolitics OR migration OR economy OR conflict OR legislation OR terrorism OR disinformation OR misinformation OR government OR policy OR regulation) AND (briefing OR analysis OR update OR report)</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>UK Government Urged to Review Palantir Contracts After Swiss Security Report - TechRepublic</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>Tue, 23 Dec 2025 15:59:34 GMT</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxNTHlMeWFVcUNqVUVqSVhOTzlsT1EzSzJMQ2JKbDdERi0wWUtCTFZxN2FzUXotN0I1ZmdoeDNObTVZZWRaWVFmQ0ZlTnl1RVlERWhxWmt1bHFOLXpUQnppeEt6YkxLT2NPd01VcXFCbGtQZjJoYUJublNwNXRjcUxJNQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F123" t="n">
+        <v>7</v>
+      </c>
+      <c r="G123" s="2" t="n">
+        <v>46014.66636574074</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>Current_Affairs</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>(geopolitics OR migration OR economy OR conflict OR legislation OR terrorism OR disinformation OR misinformation OR government OR policy OR regulation) AND (briefing OR analysis OR update OR report)</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>CM says Inquiry Report "completely exonerates" the Government - Gibraltar Broadcasting Corporation</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>Tue, 23 Dec 2025 20:37:30 GMT</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiiwFBVV95cUxPdC1HV3hmRVNxZkVYRUJZaGFpbUxvcTMyMTlEMlJqT2dDc0NXTHNMZ1RpUlktR3plZ2JSWk1uQnRhZ053UGpVNUs4cXFYZ25IT1ZhVG4zS2dTT2VtQnZocXhPOXp1cW5NZmVnR25xcUhYR2owNTlWLV9sMjBqaW02TnZUeXhkSnhoZ3lR?oc=5</t>
+        </is>
+      </c>
+      <c r="F124" t="n">
+        <v>7</v>
+      </c>
+      <c r="G124" s="2" t="n">
+        <v>46014.859375</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>Current_Affairs</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>(geopolitics OR migration OR economy OR conflict OR legislation OR terrorism OR disinformation OR misinformation OR government OR policy OR regulation) AND (briefing OR analysis OR update OR report)</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>iOS 26.3: EU Regulation Forces Apple's Biggest Update - Gadget Hacks</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>Tue, 23 Dec 2025 14:34:15 GMT</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMijwFBVV95cUxQdnlhQmpUSDdGZGZGZXFpazV1OGNTSkhSV011VzFRRndEYzlmUnRaa2VPVU9YRTdabGtZNWxBUDlKU25GTFZHYTBBcGNYNGQ3YXlUQ2RVWTNDN3lGLUdGdlY0bTN0eWN5SzF4TTVmZG9XVklDTFdYYUZpYVEwblJlXzluQzZkNUppOGhhMDExMA?oc=5</t>
+        </is>
+      </c>
+      <c r="F125" t="n">
+        <v>7</v>
+      </c>
+      <c r="G125" s="2" t="n">
+        <v>46014.60711805556</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>Current_Affairs</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>(geopolitics OR migration OR economy OR conflict OR legislation OR terrorism OR disinformation OR misinformation OR government OR policy OR regulation) AND (briefing OR analysis OR update OR report)</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>Ministry of Labour Sets Policy for Public Holidays - Syria Report</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>Tue, 23 Dec 2025 16:26:26 GMT</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiggFBVV95cUxPZG1jTUV0OVVHWVR2Q09kcXBGQ2ZqSVlIY0VRcXlCYjFGTkwxWlpGcml2b0k3aHc2enNDc19uOVBHVU9vWURNcTFhWVhtT0lSWHVQVGw2MldTbXlPZW5odDl1LWh4X1FyUVAtYlJ2TEI1VnUzbG9yWHpOaEtFclp3ZFdB?oc=5</t>
+        </is>
+      </c>
+      <c r="F126" t="n">
+        <v>7</v>
+      </c>
+      <c r="G126" s="2" t="n">
+        <v>46014.68502314815</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>Current_Affairs</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>(geopolitics OR migration OR economy OR conflict OR legislation OR terrorism OR disinformation OR misinformation OR government OR policy OR regulation) AND (briefing OR analysis OR update OR report)</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>Government provides update on 5% Deposit Scheme - Broker Daily</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>Tue, 23 Dec 2025 19:25:00 GMT</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMikgFBVV95cUxQeWU5YTl6c3F5cW9TWjN2V21HNlRRanBhbHh0YWlJMUdEaXMxWVBEXzAyVmQ2UlJUSWxSVHJGcXBLRUlIRGV4cGtEMjhDSUUwVFBjd0ZPRGFGU3NEcThYbDlyZ2duYzZYZG5idE5EUjRFQWhHQ2hORDZIWHNwOU5Da2EtR3d2SkhKZHBDWUQ3MlEwdw?oc=5</t>
+        </is>
+      </c>
+      <c r="F127" t="n">
+        <v>7</v>
+      </c>
+      <c r="G127" s="2" t="n">
+        <v>46014.80902777778</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>Current_Affairs</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>(geopolitics OR migration OR economy OR conflict OR legislation OR terrorism OR disinformation OR misinformation OR government OR policy OR regulation) AND (briefing OR analysis OR update OR report)</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>GDP report is a much-needed vote of confidence for the economy - Axios</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>Tue, 23 Dec 2025 17:39:57 GMT</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMibEFVX3lxTFBYRmtwRmNYMmpPdVY4bUJKMzJpSXZtYWJRRUNkU1FjWlJsemlKdFJmeHFmM0hIcjJlS2NQVTI2dFNvTTA3RWFlVUJtYm02Tl84WlZBcEM4N2NtVlkxYlhVMW1BVTc2X1dSNnVKSw?oc=5</t>
+        </is>
+      </c>
+      <c r="F128" t="n">
+        <v>7</v>
+      </c>
+      <c r="G128" s="2" t="n">
+        <v>46014.73607638889</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>Current_Affairs</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>(geopolitics OR migration OR economy OR conflict OR legislation OR terrorism OR disinformation OR misinformation OR government OR policy OR regulation) AND (briefing OR analysis OR update OR report)</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>Crime Report: December 23, 2025 - Arlington County Government</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>Tue, 23 Dec 2025 15:42:20 GMT</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxQVGhZM3JpTjFfQUhzMHdOWDZyMkpLNF9NVWhjeVNLSXRzX3FMc3JyLWpycHZRWGtVSFdrWkxENlIwV1lDNlF4QmcwTDY1VXFXd3cybzV0c1J5NnZCaEk4dmlvMWMxTElQSDZNXzloMGltSVB6RTFDSUl1dHZHaDJ5VTJGMndYNkpya2JadmNpcTQ1UnBzM3RYdndXMA?oc=5</t>
+        </is>
+      </c>
+      <c r="F129" t="n">
+        <v>7</v>
+      </c>
+      <c r="G129" s="2" t="n">
+        <v>46014.65439814814</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>Current_Affairs</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>(geopolitics OR migration OR economy OR conflict OR legislation OR terrorism OR disinformation OR misinformation OR government OR policy OR regulation) AND (briefing OR analysis OR update OR report)</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>How Did DOGE Disrupt So Much While Saving So Little? - The New York Times</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>Wed, 24 Dec 2025 00:27:30 GMT</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiggFBVV95cUxNbzB4WVdjVFBJMlREQXVOR3JYampuaFVmbENySG9kMGFTV0dOUU5JVmNhVFptcnc0Z1YwNTkwMy04MHN5Mk5SVEtBTkxJSkFXLUZyd3VJcVFsUDJmcklPQ0VBblNHUnhLTUYzeGVRbHNxeWVveTdtNUxzSnM0OUJJNWJn?oc=5</t>
+        </is>
+      </c>
+      <c r="F130" t="n">
+        <v>7</v>
+      </c>
+      <c r="G130" s="2" t="n">
+        <v>46015.01909722222</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>Current_Affairs</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>(geopolitics OR migration OR economy OR conflict OR legislation OR terrorism OR disinformation OR misinformation OR government OR policy OR regulation) AND (briefing OR analysis OR update OR report)</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>Consumers Power Strongest U.S. Economic Growth in Two Years - The Wall Street Journal</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>Tue, 23 Dec 2025 19:54:00 GMT</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi7AJBVV95cUxPdFpCNExtbW8wX1g1aGQtcUNfUUZwZGlWM2ExTERyMzR5N0daTEQ2cjN4eWVCX3lQQ1NKZnk3YUptLUhlWlZMOUxGbFZjcDBKTi1TdkJwZG56ckplcW5PZ1dMdHNkR24tUER3eHN0akxSZE1Fc1dBZzR6OUNNTk0tUWdaRmNLZ0pxLVpNLUh5cDRLNFFXcW52TG4xcVpmNWliaHVsbzMxLTFKRXNXaDZqRW9VRFA3TERZdmMtanQ2WmREQ2pjMVlYTURRVXpsbWdUTUhZLXpyYXRTekZueXZtcmFuT2dTeFpDVEdBbWxDX0lJTXhSV1B1VnI5c1lRQi0tLWd2YUFBZWlpaTV2SGtXZ3NXcER2dlRmOTdMWHBtU3hXd0E0VFR1eHRXb0RBN01tTUtTMWNrSlVIUTZDakltOFNEaWV5T0FKWXVKZlBQYXE1RndiWlZyM05zMHgxamw1cFlOOXpiTThRVXQ0?oc=5</t>
+        </is>
+      </c>
+      <c r="F131" t="n">
+        <v>7</v>
+      </c>
+      <c r="G131" s="2" t="n">
+        <v>46014.82916666667</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>Supply_Chain</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>Scottish whisky market slides into supply glut amid falling sales and US tariffs - The Guardian</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>Tue, 23 Dec 2025 18:56:00 GMT</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxPcFhaNi1FNk9JekFOc2p0bzhmb2pnb0V2RFAta1pSeVNwQ2RtbWRRdEw1X3JDdGl2SnBaSDlhZVJ5cXhaMFdYU256OGROcU9xU0hyeWRuTmMtZkllQUEyVDBFYUdXSEFuUmZ3OXg3NEU0N2NXblJKcW1fc3FyLXd0OVJ4NmM5Q0Exa1Y4MEp2RkVhemp6WmRCSnhwOWR4UzFqSmdKanZTNXNaY25Qd01UWllQbXE?oc=5</t>
+        </is>
+      </c>
+      <c r="F132" t="n">
+        <v>7</v>
+      </c>
+      <c r="G132" s="2" t="n">
+        <v>46014.78888888889</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>Supply_Chain</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>Security Council remains divided over Iran nuclear programme, sanctions stay in place - UN News</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>Tue, 23 Dec 2025 19:09:40 GMT</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiV0FVX3lxTFBmMV9NZXNEaE02NWc5cXdac1g5NEtMZGVmMlB3dHkwbTJWanl1OFppWkZpNE8tVmJBM0VSX095ZHg1NTU3WkV0YVdNeEw5dnhzdGw0NlpMMA?oc=5</t>
+        </is>
+      </c>
+      <c r="F133" t="n">
+        <v>7</v>
+      </c>
+      <c r="G133" s="2" t="n">
+        <v>46014.79837962963</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>Supply_Chain</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>Port Talbot pollution drops after Tata blast furnaces shut - BBC</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>Tue, 23 Dec 2025 22:55:59 GMT</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiXEFVX3lxTE1IQ0t6YWwwT2MzNjFSMExFMzVrcWk0MjFLNGNoTXU4TDcwY21XSmc4ekRxZGEweDgzOXNwcmJsLUF2Q0xpRmdTY1lpQUcwSDNxR0F6VHRJVVg2SjJa0gFiQVVfeXFMTnpzSkR2cTZtTS1JcHBCTkFrNk92TTRJdTRTR3RWT0M3YThiNmhrUVFHcHI2c3JpYlhnUi1iWkRVeU1Db2VJU2lBeXdTU2ZINTJCdGxRLWRmT3MzazFFNlVZZHc?oc=5</t>
+        </is>
+      </c>
+      <c r="F134" t="n">
+        <v>7</v>
+      </c>
+      <c r="G134" s="2" t="n">
+        <v>46014.95554398148</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>Supply_Chain</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>US delays announcement of China chip tariffs until 2027 - Reuters</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>Tue, 23 Dec 2025 21:17:14 GMT</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMigwFBVV95cUxPNzVpN1lfdXBzckgxNWVtUVQ5RWFrSmV5UmltVEZmZThPSWFCWWFpYmtORUxBSlN2N0kwOURxcWNfQnJtWWp1S2I1MmFMYmdlTXhudFRydXpaMWtJbDdLa0dILTZUNVVEZ0UtdFpZTzZzWHJ6UDJESmFaTjE4b1AxVGdxaw?oc=5</t>
+        </is>
+      </c>
+      <c r="F135" t="n">
+        <v>7</v>
+      </c>
+      <c r="G135" s="2" t="n">
+        <v>46014.8869675926</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>Supply_Chain</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>Navigating Africa’s Container Shipping: Challenges and Prospects - Maritime Fairtrade</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>Wed, 24 Dec 2025 00:07:44 GMT</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxOVGdGQVptcHZlbVZJQTVaMVN2NEQ1VlBRZ2kydlN3bEo1eWx0THAtQjlsMktDSVVPU3BpZzMybEl2UlNBdW5SVXQxUWtuaHBQYy1ZX2IyWWh2ajBIYklQNnV5cHNxU2V1YUU3ZmdpZ1JqLUVVVE5EbEtZWUpqNVlyZ3VIenNBU1EyNm44aEM4cTZnUVl4Z3R3LQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F136" t="n">
+        <v>7</v>
+      </c>
+      <c r="G136" s="2" t="n">
+        <v>46015.00537037037</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>Supply_Chain</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>State Department imposes sanctions on former EU official, disinformation group leaders for ‘censorship’ - CNN</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>Tue, 23 Dec 2025 23:38:20 GMT</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMifEFVX3lxTE1qVk5oRkdqOEo0QlFwSmx0SXZUVmktS2ljTGNsbEg2OGltRUo5a2o3SE5mXzZWT2tCMlJNUnpOTk40d08yeDBIMXZrZWlyaFFMc25SZWNLNklSVjUtZ0FYcVFtUm1VVHNHUDdpN09fY2NCQWZ6MHNwT2xrUGY?oc=5</t>
+        </is>
+      </c>
+      <c r="F137" t="n">
+        <v>7</v>
+      </c>
+      <c r="G137" s="2" t="n">
+        <v>46014.9849537037</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>Supply_Chain</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>Living, logistics and data centres: the CRE sectors set to shine in 2026 - Green Street News</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>Tue, 23 Dec 2025 22:06:41 GMT</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxOTDgzWFk4Wk9fX1JrY1VKdGJXVnZHSEg1U0hEamRrMUs0SjR2dWp1YkdrMF84SHVza2RSS3NkWE5EaVdfZEg5U2hNeEZac1JiUU5CV1R0S3RJWVpQWXVWc1IwbFJxa1p2Z2Fmdy1UbXI5MGNsS1JqampOYkNMSlJuUF9RVDN4LWtHM25WaFRDVHA3Y190S2pwTVFNSzhaVW1hLXF2M0tqOEVTSE0?oc=5</t>
+        </is>
+      </c>
+      <c r="F138" t="n">
+        <v>7</v>
+      </c>
+      <c r="G138" s="2" t="n">
+        <v>46014.92130787037</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>Supply_Chain</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>Linear Faraday instability of a viscous liquid film on a vibrating substrate - Cambridge University Press &amp; Assessment</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>Tue, 23 Dec 2025 20:45:45 GMT</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMikgJBVV95cUxNODc4TWs0SnhzWjJMSVpXNnlYVWF5SWNTMDFWRWdwQ3dFWXNaYnc3enZmaFJsZHdGWGM0WW9UYUFUdEExMWhNemhFSUR3RDEySE1RaWpRX0VqNTdETHBQcWVjUFEyMHpxb0J2a01LcTNqSjhoZkdha280MXl4RmJER1NtNG82bFhReFlZRGNUWnFPTmxRSEdsNXNwWXpwZWtNSllOemV5eUtxejloa005UWMyZlRObGFrS05zd05aUnNGY0xjUHdWTHI1MVBtY0dpNTdrTjhCTjF0azZRUUU3dEpLZFNiczJLeGlGYjZpZUlXQjNaak40UWJqNUE2QndWNktVckRfc09vR21jcnFrdThB?oc=5</t>
+        </is>
+      </c>
+      <c r="F139" t="n">
+        <v>7</v>
+      </c>
+      <c r="G139" s="2" t="n">
+        <v>46014.86510416667</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>Supply_Chain</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>Historic Kentucky bourbon distillery goes dark after Canada takes revenge over US tariffs - Daily Mail</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>Tue, 23 Dec 2025 19:09:07 GMT</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxOdFdwSThhY1ZTdE9ZYTdlbDhCNnROX2hEVnVwX3B4aUptV2ZUSEF2X3RqaXZ2LVloR0ZvYldSZW11M25icVZ4OUktNVVDVjYyZVRkdUVZbUdzUlJ2cGgyZ2c3NmgyXy14dDNuQzZxZ2NSOGg4azMtWmJkaUpyTjZreWF6WUdCOEI4b3F4anl5T21JcF90NVRicjdzd1VFUdIBowFBVV95cUxNSEVua2pRVE9TNnVNanNjZ2RwMThtWGhFbzYzWWdyMV9GTk1aZTVqWUhRX01WR0xSbzdmR3k1UkJfajlVcWZ4SUc2QTh3OTFia0tpaW5sSWNqZjhEY2NsQlVFRHN3aC1uUTZiOGI4VUU0MTlFb1RrZFJ3WGxJeEVYcmFlTm8tMC14ekVjZmN5M0tyS0xHQVJnUFFQMFdaejQ0MG9F?oc=5</t>
+        </is>
+      </c>
+      <c r="F140" t="n">
+        <v>7</v>
+      </c>
+      <c r="G140" s="2" t="n">
+        <v>46014.79799768519</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>Supply_Chain</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>Copper price hits record high on concerns over tariffs and shortages - Financial Times</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>Tue, 23 Dec 2025 11:44:31 GMT</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMicEFVX3lxTE1qM3pXWURJZlU0eUZ1My10MGJYdU1iMW9iUzNyNWJETFYtUjNsaGNDNUN2MHg0dEIwamRueVlaSXZISVpFR3V4TEVUYldrV0RPS1h4d2R1dlpmWlRvUF9nMlA4YU5OTWRoQjUzUmN1NnQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F141" t="n">
+        <v>7</v>
+      </c>
+      <c r="G141" s="2" t="n">
+        <v>46014.48924768518</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>Supply_Chain</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>Panama Canal ports deal at risk after China’s Cosco demands majority stake - Financial Times</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>Tue, 23 Dec 2025 12:26:32 GMT</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMicEFVX3lxTFB1TDZSVWhZcVgxY0NnUE84MERKWnRXeERaVGhlMFJ6dC1takw1UlA3TmNYQ3dqWDY4T0NBWUE2ZHVCRG14WVRBQk5RX3VTQU16SjNITjRtUkZlcXphd3hFZlJDLTQyUk1YTFFRQ1JpalU?oc=5</t>
+        </is>
+      </c>
+      <c r="F142" t="n">
+        <v>7</v>
+      </c>
+      <c r="G142" s="2" t="n">
+        <v>46014.51842592593</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>Supply_Chain</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>Trump news at a glance: President claims tariffs behind unexpected growth, but consumer confidence falls - The Guardian</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>Wed, 24 Dec 2025 01:27:56 GMT</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxOQThXc01mRENsSlF3MWlOeVJPcEtReVNFTGV6LWdhUU5kYWpPVnNUWUVJQnJxaDVKZFJISXFRTGY3eV9TdndTUGNfR0d2a0oxTnVnMGhUVmloTmh1UTBDb1NnODE4M0pHend6ZmUxQVVPd0JXRFZ0amh2TGUtNlpwbVY5STUzM2NRTWNKUmVFYUxOam5jd1NqNWNB?oc=5</t>
+        </is>
+      </c>
+      <c r="F143" t="n">
+        <v>7</v>
+      </c>
+      <c r="G143" s="2" t="n">
+        <v>46015.06106481481</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>Supply_Chain</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>Beyond compliance: Forging a proactive safety culture for 2026 - Fleet World</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>Tue, 23 Dec 2025 22:05:36 GMT</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxQYXpOdWVLYkN4OG9CdUd4bGxhckZGWEFwWEpQRkliWHM3Vi0zWmVaZ0NpMzRyUkU5azRoN0xPRFZMTEp6dUtObGRwTlRxY0hGNDlPNmZQU2xDbWxvQXdqdlRvM1JUMk9CM2UyLWdGelphYldBaDRXRDl0ZUtBM0pMMWNNaEJKdW9yX2RDak5Fcnc?oc=5</t>
+        </is>
+      </c>
+      <c r="F144" t="n">
+        <v>7</v>
+      </c>
+      <c r="G144" s="2" t="n">
+        <v>46014.92055555555</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>Supply_Chain</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>IIT-M Introduces Groundbreaking MBA in Digital Maritime &amp; Supply Chain - Maritime Fairtrade</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>Wed, 24 Dec 2025 00:35:16 GMT</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxNZTNncTRxWndMSm1ZWlJvSHlQb0Z1Tzk3U1lwSS0xVUVoSkRGTDBnOHVTemR6QVFkdG5JTkIzZWw1VXRjVDg0clBxMXNCbXc0V2hfMEN0NllLQUZzWVB1OHJNSFlFMjBNdGdYblgyRUxsVXA5dGkxa2xWNWx6cV8zRHJNOExybXYwa0tsWVlvZV82aW8xaG5zYU0yRU5hMVlk?oc=5</t>
+        </is>
+      </c>
+      <c r="F145" t="n">
+        <v>7</v>
+      </c>
+      <c r="G145" s="2" t="n">
+        <v>46015.02449074074</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>Supply_Chain</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>China to Develop New Port in Kuwait for Regional and Global Trade - The Maritime Executive</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>Tue, 23 Dec 2025 23:21:06 GMT</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxQMDBiQ1k2clhYNTVpRm1xbTZmRlhMV1ZqdGxKdVo1eDM0T0VfWW9KUjR4Tkd6X3ZWZy02emNNa2Rkd1RiMlBNUjcwcHp4QjlFbVBDNklpYWltd3A3dEx0T0ctWXU3cC1meVRxVjZnWkdiZ0Z3dFA3eGVpNXh4N3JZVWFaS3lQOUJidGEteEhnYXpnNW9BdnRna2tKNHVCVUQtQTRsQTJCcw?oc=5</t>
+        </is>
+      </c>
+      <c r="F146" t="n">
+        <v>7</v>
+      </c>
+      <c r="G146" s="2" t="n">
+        <v>46014.97298611111</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>Supply_Chain</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>Man arrested after €3.7m cocaine seizure at Rosslare port - BBC</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>Tue, 23 Dec 2025 12:07:11 GMT</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTFBzNHRQaHZILXNKMl96OUp0NlNZVmtKbUNEUUYyS2E4LUpBRmtpSGdXbjROdG9qV2ZKeTA2VGxucURaUmt5NW9hU0J3NGh1RVpQcWlqTWtjeFJGd9IBX0FVX3lxTE9PV1BXd2VJeENoZGR0eVBVZ3F0UmktU3V2dUxKTGJDQWwxN3Rld0RBY0Rib0pydzBRUUlOb09PbloySlluQmpWN09PRTI1Y0RxdVlhdFlnRzZXV283ZjZJ?oc=5</t>
+        </is>
+      </c>
+      <c r="F147" t="n">
+        <v>7</v>
+      </c>
+      <c r="G147" s="2" t="n">
+        <v>46014.50498842593</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>Supply_Chain</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>AI, Tariffs Fuel Big Tech Layoffs - Global Finance Magazine</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>Tue, 23 Dec 2025 21:33:06 GMT</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiZ0FVX3lxTE1HTHJJZFNOVlRod2t3OVNkWjQ0MXdfWmVRU3ZrYXh0OWY4T0FSd0VydG1JLUZJcWYtcmY0NkRfazFZZEh6dWtKNU9WaXJhdFl1VWV4dzQ2SjdqdHJBcHVNV2RrTVpGTnc?oc=5</t>
+        </is>
+      </c>
+      <c r="F148" t="n">
+        <v>7</v>
+      </c>
+      <c r="G148" s="2" t="n">
+        <v>46014.89798611111</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>Supply_Chain</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>Strengthening supply chain security: Preparing for the next malware campaign - The GitHub Blog</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>Wed, 24 Dec 2025 00:01:15 GMT</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxQb1NNOW03OWs4N29yNEhnR3YtTzY3Y0pac1BIcjY1T0FJRmdUNVJ5Uk1hWkFjeTlYdTFTYUlRUmFjeEdpR3hiQ0E2WkFqTGM2Y1FnMVU3allYSUhpQ2J2ZUZKTzloeVpnMUxxYVgyRTZNUWFpQVdING1rMWV1c0xPVG1VaW10cnhQd3NiT1NsbzNMX1NPRnN1NjJyQURQNDRRbUNlQ0dWbWZWeTVMMU1nV2FpMmx3OVpVbktOSk8yRzZnRXFGdVE?oc=5</t>
+        </is>
+      </c>
+      <c r="F149" t="n">
+        <v>7</v>
+      </c>
+      <c r="G149" s="2" t="n">
+        <v>46015.00086805555</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>Supply_Chain</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>How brands shifted marketing and media strategies through year of tariffs - Digiday</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>Tue, 23 Dec 2025 05:02:38 GMT</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxQUW5JMlVDbUk1ZFpTWTM5S19Rd1piMXgxRk1RT0twZVk1Nk5LZ1NNVEN1QXd0NmpxMlZSVFZhT0pDZ2xrOEhLTHhtdElycXBJeWxXMnZOaERGMGFqNXVXZGRzTER6dnNYZzR4WmJNb0E3WWJIeVB5UExVMFVMaVhsVUx4RGdGX21UVVVlRmxDaHVSb0dTdUk5eFgybkZPVUxOUDlCNUM0NA?oc=5</t>
+        </is>
+      </c>
+      <c r="F150" t="n">
+        <v>7</v>
+      </c>
+      <c r="G150" s="2" t="n">
+        <v>46014.21016203704</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>Supply_Chain</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>Shipping Giants and Insurers Unite to Combat Corruption through MACN - Maritime Fairtrade</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>Wed, 24 Dec 2025 00:29:54 GMT</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxNRWU0dkEtSnVKU3dWTDZTcHdxUzdoTHFjelE1UFdPNktRRXVZSV8wbVhydldHTFZLLTN6aUphZ0lTXzhVcV9qajJUX2tXSnkxdU96dkVrZmhMd2RRSkVUVjc1b1ZzckN0R19IaTV0bko4aEZVRUxBd3QyRzRXWU1RMWRUaFdiOTBQT2lQWF94LUdhMWxzUm9DRGpjaEY4RmhO?oc=5</t>
+        </is>
+      </c>
+      <c r="F151" t="n">
+        <v>7</v>
+      </c>
+      <c r="G151" s="2" t="n">
+        <v>46015.02076388889</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>Supply_Chain</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>Huddersfield Town press conference: Lee Grant and Bojan Radulovic ahead of Port Vale clash - We Are Terriers</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>Tue, 23 Dec 2025 11:53:59 GMT</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxPWWtKQ2pEX1FtemM0NHNlQ2lQNVJQczZzTUtjYVl4RHhyRGlxb2UwODhtRW1ld2dJLW8tTG5xQzNlYWpzMU1HQzV5YkJCeEdXbnpIUnliLVV3QjI3R0ozWjlpWFJ2OElBY0dpRVVKSG5sM2RNdU5ZQnV5WjRBUWdISTY2eml4ZmJlNWRHTFhlbzA4NEh5Y2xkM3RQX1NNT3dYd0VYbQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F152" t="n">
+        <v>7</v>
+      </c>
+      <c r="G152" s="2" t="n">
+        <v>46014.49582175926</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>Supply_Chain</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>Malicious AI Models: Risks Across the AI Supply Chain - wiz.io</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>Tue, 23 Dec 2025 21:18:36 GMT</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiakFVX3lxTE5lSkEyeHlCMURVQS1EOVJ3Nm53Sm1SMUpqSl9OV3dRdm5aSjVFNzNvYndrTmZoanlWdFo4UXd2OFFfQkdGZmZfNkRjbDNXTndTUXZsRHB1a0o0N2FDZHJFUmNiMUktZWItYkE?oc=5</t>
+        </is>
+      </c>
+      <c r="F153" t="n">
+        <v>7</v>
+      </c>
+      <c r="G153" s="2" t="n">
+        <v>46014.88791666667</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>Supply_Chain</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>Pacific Basin Shipping orders its first bulkers in China in over a decade - Tradewinds News</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>Tue, 23 Dec 2025 12:55:25 GMT</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxNdGlBRm8tNVBJUFMybzhCYUNGclFYWHN0QmQ3c0tPbW5zd1RrZ3lFU3MxbGlwODdQQ2JmeXY1bXNyS1dyLWphY2phTTRWVC1FMkgtTzBLUEZCT0JLQklBWlh4eXhRR05VTHhkaWtFTmo0S3BBWEZ0eXNxc0MzeUV0b3JjTnh4cTBLY0d4ZVRDRm81UFd6Yk4zU2twUUdibHB5S00zcEl5eC1QU1A0dENlYlpjbHpzRE56U0xJNDZ1NTVsUQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F154" t="n">
+        <v>7</v>
+      </c>
+      <c r="G154" s="2" t="n">
+        <v>46014.5384837963</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>Supply_Chain</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>Sumec Marine Inks Contract with Shanghai Jinjiang Shipping for Two 1,100-TEU Container Vessels - imarinenews.com</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>Wed, 24 Dec 2025 01:36:04 GMT</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiT0FVX3lxTFB2MlpLdHVUY3RsbHpPVDNwcE9kT0RrRVJUZ2RSdHAtRjF0ZVF2WHlmSlplWURkVXhEMTZTRXRmbVdrVV9hem5nMzBNaFVnTlk?oc=5</t>
+        </is>
+      </c>
+      <c r="F155" t="n">
+        <v>7</v>
+      </c>
+      <c r="G155" s="2" t="n">
+        <v>46015.06671296297</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>Supply_Chain</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>Might We See a Streamlining of EU Digital Compliance? - JD Supra</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>Tue, 23 Dec 2025 22:33:36 GMT</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiggFBVV95cUxPdWVlWEtyeGYwOHNHVXk1UVFrd3p3dTBGY1JxM1NLNTZIaWNqOUpwR3pYVlZpU3RncGhlSWtJdUtOT3BYeUl5ejRhQTIxSG9qWTFHbGxYRHpNN1lHVFN0SW5RRFJQb3JfVHdhYnJlbC1sSHUtbzFHSS1SenFMbmtNcEh3?oc=5</t>
+        </is>
+      </c>
+      <c r="F156" t="n">
+        <v>7</v>
+      </c>
+      <c r="G156" s="2" t="n">
+        <v>46014.94</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>Supply_Chain</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>Russia Risks Logistics Crisis With Winter Troop Surge In Ukraine - Forbes</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>Tue, 23 Dec 2025 11:40:03 GMT</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxOei1hdFFrTV84d2UtYXlaMTN3Y1ZrdjJlV05GajViVmFwWTg3TFhtS2VVNTVidXpLOW5ZNFdoZ3VocnZTcWpsY2t3WDYzSGcwV296bVdOTG1HeUU4ZVZTVG1fd0t0NEtGLW1ySlpITnk2ZWllTkZRS0FtWHI4SDU3bGJ1dmtPNzhVWU9QWUlHTUdjUFR1Zk5KUF8zWDEtd1lMZU1QS3cxcmlfNW93ZkdNaXB5Nkd0VllBa0E?oc=5</t>
+        </is>
+      </c>
+      <c r="F157" t="n">
+        <v>7</v>
+      </c>
+      <c r="G157" s="2" t="n">
+        <v>46014.48614583333</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>Supply_Chain</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>Peter G's busy Christmas: United Overseas snaps up dry bulk arm of Norvic Shipping - Tradewinds News</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>Tue, 23 Dec 2025 18:35:45 GMT</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxPSUVMdXk2UmpCMGNfbG04M1J0eU5COGJ4ZzR6RjhweDRuRDZTOTVqRzBJc1Z2THFyWnBDSU1yUE90T1Zjdkt3djBLOHFfREdSaFRxTW41RV9CYmg1UVRLWTVFVDNmRlpjUzZwQ2FDWFM4OTY1MDBIekExNEJBaTBUbE5GWlk5VmNIbW9OUXcyMTl6TUN0VFIxUkdpeGd1bGQ4RjNsa3RUZjhraEhHV0xycHBUbE1zRGRPWkw0NjBBLWVNREQtVzJ2Uk1BQQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F158" t="n">
+        <v>7</v>
+      </c>
+      <c r="G158" s="2" t="n">
+        <v>46014.77482638889</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>Supply_Chain</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>UN Reaches Shipping Emissions Agreement Amid US Opposition - Maritime Fairtrade</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>Wed, 24 Dec 2025 00:34:56 GMT</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxQc1l4ZzVWUnFGOFlMSC03N3BnTDBIWldpZmRXRVNxSHVfM1ZUNmZxTW12NEVodWsxYl9XVHFmMlB5REZlcWtHVkp3bktmSnBWUWJYaU1zdkZKQnpVQjRlZlN5THhPa0I5YXcyaFRLTGdZTWRjVXhwMFU5dXZMOXhRUWdUVFpnUk5CU2pHVXdoRWk4LTg?oc=5</t>
+        </is>
+      </c>
+      <c r="F159" t="n">
+        <v>7</v>
+      </c>
+      <c r="G159" s="2" t="n">
+        <v>46015.02425925926</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>Supply_Chain</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>JINGDONG Property Announces Acquisition of Grade-A Logistics Asset in Leicester, the UK's Logistics Golden Triangle - JD Corporate Blog</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>Mon, 22 Dec 2025 11:15:24 GMT</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi2gFBVV95cUxQT3M4S1p0eEc5WEIxYWdFa0RGX1F1Q3hVcF9NUFdKQXFadFpfYUYyeGpTY2RUSVU0QVlHREU2azFrbWZ0T2MwaUZLUVFpM0Flc2VLNjZwZmNobDc1LVdRNHFUZlE0UGlJWlFpSUlNaHRWYlBGb3pnOFhoc2hvXzY0U2xoaXVNaTNBSGhqYWlTMFJEenFZTWpMa2ZnMU1VWUk1dWl2RnBjWXFtRFpnUzQ3a2drVWprclFndXdHVlBwbVYyNlpvZnQwdUlaN201MG1KTy1GVDNaT3VqQQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F160" t="n">
+        <v>7</v>
+      </c>
+      <c r="G160" s="2" t="n">
+        <v>46013.46902777778</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>Supply_Chain</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>Dry Bulk Shipping: Global Iron Ore Volumes Post Slight Increase, Despite China’s Imports Decrease - Hellenic Shipping News</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>Tue, 23 Dec 2025 22:05:31 GMT</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMizAFBVV95cUxOWFdIRXpWX3l0Q2UtSUNtQ2ZKdUdEdmpzS2xxbVl2Yk1Pd0RpMzZxU1VIcVFHdU90YVJHbmoyeGFQUDJRem1lMklOaGtfSHJLeWxaNFdkTXhSRG5NaG5yYjBoM3NacWZPakFvczJFS0xCRjZqVVdaSldOb3g3bVdGYVV3eVh3b2owcmExUU9jTFhBbjRfMk1KeFlGU3preTJXWU5FeHZBblJMV1Y2dEdubDdMalBiRl9jNFBwUHhxMFhoRzgtYTAtQzRBTmQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F161" t="n">
+        <v>7</v>
+      </c>
+      <c r="G161" s="2" t="n">
+        <v>46014.92049768518</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>Protest</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally)</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>British police detain Greta Thunberg at pro-Palestinian protest in London - Al Jazeera</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>Tue, 23 Dec 2025 14:12:17 GMT</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxPTUhjNXV4a3ZmajU1N1p4ZXRRNlZYdDR6S29OZDRCTE5GSWNrOV9uT2RXNUwtOUlMLVZkVUYwaWZOUjQtMlRka2phTUQ0aGJ0UDBZSWN6UWk2aV81RU50OEVzUHVvcmwxYWVFX2k4R2xLNUVuZlVKQkVFWk40VlhxZEVtY1d3cWxfUHY3ZkZONEdyOUt5ckZsVkViVkVtemxQeVE4SG5uSDNmNm440gGyAUFVX3lxTE9rRnVkLVVIajB5WDNqN0JYcmN2amxiMDFYMkdOZDhvWlFyN2lrUS1HRUMtaXdZdGI2MEpkX1ZhOWotMGpMbmoyLUpZOEx1XzItaTE4R1FBOWRhZWF0U0dOWjF1VHR2c2twQ1JxT3MxemNHRUtPQkFUWjZDQkppR3VORmxYMHdlQkk3Vnl1c0pxRnB1WFNDMlVLUjc3dHl0aTU4Zy1zSEpIOFdyS3c1Rmw3SWc?oc=5</t>
+        </is>
+      </c>
+      <c r="F162" t="n">
+        <v>7</v>
+      </c>
+      <c r="G162" s="2" t="n">
+        <v>46014.59186342593</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>Protest</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally)</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>Amova Asset Management strikes deal for Malaysia’s AHAM Capital - Pensions &amp; Investments</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>Tue, 23 Dec 2025 20:45:00 GMT</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMieEFVX3lxTE9BUnJzSk5pSjBzMFJuMFptUFNHcURYN1J5ckszVE5hV01Fc2FOSG1fc0NoSzJzU0N1cU1naERvc2p4Z0xSYTVsaVFBUERNTkNoSm1ORHFDZl9aRnl6TmV0SVhkbmQ5V24yMDRDczhDQm50Qk1yTjB1Xw?oc=5</t>
+        </is>
+      </c>
+      <c r="F163" t="n">
+        <v>7</v>
+      </c>
+      <c r="G163" s="2" t="n">
+        <v>46014.86458333334</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>Protest</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally)</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>Massive protest outside Bangladesh High Commission in Delhi; protestors clash with police, detained - Asia News Network</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>Wed, 24 Dec 2025 00:36:38 GMT</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxPRmd3T0ZBRGhFakNJa0tzcVJ6ZmstRmF3QzVjQWp4ajhkOW5COS1XTk1FZVJCV0hyV3JUWmFNRjlFRFczRGJCRFJ1a3h6bmxDUVZRTFFxTmcwemp3bGRyOTJ2SmRwVjd5eW9SY2RtY1F0ekdYSnczcGxleUNCQklTUjdVVGhqbzFLRTJOQmh1UzNZcEQ2NWtOUmRVZlpfLWZZN0c0eFlwU3pkVExtNzZJZExyYjNnN2J1QVpxdVBRa1c?oc=5</t>
+        </is>
+      </c>
+      <c r="F164" t="n">
+        <v>7</v>
+      </c>
+      <c r="G164" s="2" t="n">
+        <v>46015.02543981482</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>Protest</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally)</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>Protests over fuel subsidy cut leave police injured in Bolivia - upi.com</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>Tue, 23 Dec 2025 20:07:36 GMT</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxOS0VsMWpIemtWY2M2RGZIV0FXZkNTNG5CN3JQT3psWDJxejQ2c0NkR2x6d1FveUpUNHIwMzcxaGpqdk1ZcFpzeVZpWnNTcUNfMEZWMW5DbENZbGpQSGNBTklTOHIzQXN5MnZubTNhbTlpVlpjV1lhMzF4T2l0NVM3ZHhqaXNzaUc4OG53V3BTSkRLQ2Rzd2VMOW90QWw2cXNrbnNZZV930gGrAUFVX3lxTE55dzJ2QUc1TWpnWUlFcHNYYlZXaFZlVC1JaUZaZUhiSGFQZXdFVGxtMEFxMC1IeVdMQzN2X0lySzg0UFM2MzZxNzNoX1RVdTRXRWVCLVpVSFpSNWlBZ0pwQkZ0ODFucHpDRGJfbzlMR1JQTklqRUZYYjQ3cUtCc3lNa0dxcG9pN0VqbFMxcUpIdTR2bEwyWXE5andiSjRNMFM3R3BjUnNmZkczNA?oc=5</t>
+        </is>
+      </c>
+      <c r="F165" t="n">
+        <v>7</v>
+      </c>
+      <c r="G165" s="2" t="n">
+        <v>46014.83861111111</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>Protest</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally)</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>Minns defends new guns and protest laws after marathon debate - Capital Brief</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>Wed, 24 Dec 2025 01:01:00 GMT</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi0wFBVV95cUxQWXFlOU91YVZpRUFyakxOdS1WZDlyQlo0ei1FQkMyRFd3RnY2MGVwV2JPUjdiYTZVbE9jZV9nb0FYeGV3bWpaN0xKVzVSZm9abHhyV21GVXl4MnRsTDdqMmJfTHljSktqV3dNZDd3aEhMZlp0ODNXdXE4Ykx5WndjSXA4YUNZUmFQbmFGMHdGeTRWbmJEVEdYeDhKaE12ZHB5aUFQY2VLNi12OTl2YTRmU1FmTzVoc3hRZW1STnlram5sZEVnOGQycHJyMl9nRG5HaXNj?oc=5</t>
+        </is>
+      </c>
+      <c r="F166" t="n">
+        <v>7</v>
+      </c>
+      <c r="G166" s="2" t="n">
+        <v>46015.04236111111</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>Protest</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally)</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>24 Wounded in East Jerusalem Amid Police, IDF Raid, Red Crescent Says - Haaretz</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>Tue, 23 Dec 2025 23:08:00 GMT</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMilwJBVV95cUxNOEU0WVNTSF9kNWU4dVp6U0RUYmwtT0NNeVlobDBGenVfSDdTU2hGMExJekM2YXgxYnpUWWR4N0VjRXM1ek5fcExwcnpuamppRGpuMUVKNzU0M2Z3OEY1ZXVXLV85S20wWnhuWmFJbDdzVkpNMndleE1FbFljSEtyZXlKUk9RSUt3TjlFNXNvQWpfZXllb1ZjUF8tR3ZualJROEo0bWVLN0xUdkQ2QkhLZjZzaVlUS0JYLWU5ZzdVV1d1WkQzQnpScGw0SVI1WF9wSG1SMlV6NE5UcGF4WWZRbzdlSWNUczZlQkJIZG1QSFI5LVd6QXdIb25rVVV0SEZMTzRocGYtTWxXRzV1bUxxRHYxMWx6VGc?oc=5</t>
+        </is>
+      </c>
+      <c r="F167" t="n">
+        <v>7</v>
+      </c>
+      <c r="G167" s="2" t="n">
+        <v>46014.96388888889</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>Protest</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally)</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>Ainslie strikes Oakley Capital deal to fund British America's Cup bid - The Straits Times</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>Tue, 23 Dec 2025 07:13:00 GMT</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxPZVVsQ3BoaEgta19weWl1ZVlvUjlmUUl4RF9WWHJrRmNUcm9hc3JzUWY3bExMd0hmM2UxWFNVcVVOOUphSkNmVjcwOXJSUXg0N3dTTkJkR0t2OXZ2SF9TdlYySWRHSEMzRi1MSVcwRzVjZnJXOTVtS2oxYjl5NUc5WFdsSDZGR2IwNVQxQ0xYVDQ5MWhnbFFnUUo5cWlhMjFtZGhKeVNn?oc=5</t>
+        </is>
+      </c>
+      <c r="F168" t="n">
+        <v>7</v>
+      </c>
+      <c r="G168" s="2" t="n">
+        <v>46014.30069444444</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>Protest</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally)</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>Reps approve Tinubu’s request to extend 2025 capital budget to March 2026 - Premium Times Nigeria</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>Tue, 23 Dec 2025 17:04:02 GMT</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiyAFBVV95cUxNajdFakpnYV9XZ2pCdHBZblJwd2hmb21TekNYaXE3Wk55Wm9MdThpU2VmY19oUTBzbEtCNkwwWlAzN3V1cWdlbVdCQTItRUxCcjNZbE81aWJ3ZG5UMEFic1BqX3NpVGxldUp6dTR0WkhMclM3a0wtcEF1MUg0dzg4a3c5c2lNT3pFWmdxLVp1RmNxdlNmMUZPSHkxYVZ1RW5SdE5XNHl0dE9ZbVg0MjF5amJaazdINjI2aDN2d2ZzWnViRDFNaGpHVg?oc=5</t>
+        </is>
+      </c>
+      <c r="F169" t="n">
+        <v>7</v>
+      </c>
+      <c r="G169" s="2" t="n">
+        <v>46014.71113425926</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>Protest</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally)</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>Bondi Beach attack: Father-son duo planned terror strike, say police - newskarnataka.com</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>Wed, 24 Dec 2025 02:07:14 GMT</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxOTkNRcnRZTFJwaHNjNi0teXBfZVRmQTljYTY5cEF5WWY3eHE2cTBFYUdkY0pVZlVHSE9Tanh1UWdTM25GU3ljd1FmMHNBdGRPVnJBcUxHVmVrOEtYOUlSblkxQzBDR3ZOZmRlS09tOGRyWWJrdWdXdnpJR1hZM3YtVUVmdFZxZGMycXZJSU5GR2F1WEQ1bm5JLTN2aDhmV1I2eHhvZGpscXIwb00?oc=5</t>
+        </is>
+      </c>
+      <c r="F170" t="n">
+        <v>7</v>
+      </c>
+      <c r="G170" s="2" t="n">
+        <v>46015.08835648148</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>Elon Musk, AI and the antichrist: the biggest tech stories of 2025 - The Guardian</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>Tue, 23 Dec 2025 19:22:00 GMT</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiggFBVV95cUxOTnhaUURYZ2laU3hMYXl6a3Y0N2pXSm80UGs4dmEzVVd2RzJVWnBoRkhvdnUxUjZTMWpSemE2R2R0M0pvMGNLOVJDOXFBUUpkWjZDdWtKdURBMHplbndSQ3E1LVREdXYyMGRkdV9WSVFFbE02OVVBWjZNd3pxdXN4VFF3?oc=5</t>
+        </is>
+      </c>
+      <c r="F171" t="n">
+        <v>7</v>
+      </c>
+      <c r="G171" s="2" t="n">
+        <v>46014.80694444444</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>AI and digital tools can empower civil engineers, not replace them - New Civil Engineer</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>Tue, 23 Dec 2025 12:25:43 GMT</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxNbGM5SEVHUUdFaWxqVEc2bi1fZW55ZkxxUVJmRzExRzhlMzZkbzV0VTFIWUZ5Y0h1MmExRVdZVWZEUVNiYjRlbkttWFRxSElzUkdWU0dLMlp3RFBidm0yRTNHakV2cEtQcWlNdjRvdEhEUDQ4VF9McHA5TWdvQUZMMGZnbjNmZS11UWNIN2JqeGZhZWNoRmI1ekVMMG90cjByVUxkNXljM2lsSlpRYXI0dm54VTFrWEJsR2c?oc=5</t>
+        </is>
+      </c>
+      <c r="F172" t="n">
+        <v>7</v>
+      </c>
+      <c r="G172" s="2" t="n">
+        <v>46014.51785879629</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>AI View: December 2025 - Simmons &amp; Simmons</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>Tue, 23 Dec 2025 16:18:45 GMT</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxPZWxsa3JwX25DZm9tMDFmWkMxcUhqT3V2a19JcTY5QzJwQi1ZTkI4SUFMQ1RvT0ZVM1cxSWlHdGhlVG4wTG5vVkJxamlPNVdpbmdOVTZFMWlyWkc4RTVpb0JLZGZlT0Y4T1RxMFA0MENJbjR2WVVXZlptOUlLd1gwenlNVk40VDg3cVVWLVg3aERvSDBlUnU0eDZNZw?oc=5</t>
+        </is>
+      </c>
+      <c r="F173" t="n">
+        <v>7</v>
+      </c>
+      <c r="G173" s="2" t="n">
+        <v>46014.6796875</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>Hyundai Motor Group Strengthens Software and IT Leadership with Key Executive Appointments - hyundai.com</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>Wed, 24 Dec 2025 01:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMicEFVX3lxTE9ON3RCNjdNYXJFRUllM2trVzB0SmsxaW8zVy1BeTNxZE9mOGR2ekxTNXRMRTZZSzBVYlBveWpSSV9RWnlIQnl6aUNJaTM2TXM3dFlBQ1NldGlUdmJmZlRqZVViSXdNYm51M1F1QlhJUVM?oc=5</t>
+        </is>
+      </c>
+      <c r="F174" t="n">
+        <v>7</v>
+      </c>
+      <c r="G174" s="2" t="n">
+        <v>46015.04166666666</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>Dreamlines-Cruise1st targets ‘significant growth’ by developing AI and packages - Travel Weekly - Home</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>Tue, 23 Dec 2025 08:55:00 GMT</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxOb0loVVprNFBHUmFlQ0h6cUhTSWhBcmNfQ2xKUzZDZWZ3ajQxbG14X25GVmVYa3c4dEVNcmhXT09JU0lhY0ZBczFfcjdacWlySENMNWFVVEFoLVBnZDRLaTNidlpmR1R6aS1Vd0I2cU42UUxiWG15Y3RuTmE3WHNSN2tQUjdDd0JJZEU5Wk50VjBuZk9jT2hyUm9xalZRVGVwemVwRFBlNzB2RzdxR1RFLW9iT2FtUQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F175" t="n">
+        <v>7</v>
+      </c>
+      <c r="G175" s="2" t="n">
+        <v>46014.37152777778</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>Researchers use robotics to find potential new antibiotic among hundreds of metal complexes - University of York</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>Tue, 23 Dec 2025 14:35:34 GMT</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxPRUNqWnVkWVZrOWh5NGtTTHlZa19ubzRwNFB4eFF6TElmRFFBUFJZeWo5UW15N2tMNXRlUkdPOHV4Vkt6dVBQSWxqMlZvcnVBLXkwWUpfSERBZ2tPdXp4RmlKN0YxSHRvTXVvSlFrczA4NVdUZkIyUlc2WG91OFd5RnZSNjR6UUpxVTNwS1ZEdTR3d1E?oc=5</t>
+        </is>
+      </c>
+      <c r="F176" t="n">
+        <v>7</v>
+      </c>
+      <c r="G176" s="2" t="n">
+        <v>46014.60803240741</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>What Is AI Threat Intelligence? Real Risks to AI Systems Explained - wiz.io</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>Tue, 23 Dec 2025 19:32:27 GMT</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMib0FVX3lxTE1NcjZmWFF1YXhxaWhvMnFUbDFVWmRYdVdXeEdSZnp0SXgyZndNMVk4VzJxc2pNNG9PQlY4TGQ4UllFcHRxZlJnd2YxMDNnek1rako4dFJzUTFnZUd2U25YRHlYUmF5TUoxVWpvcmpzZw?oc=5</t>
+        </is>
+      </c>
+      <c r="F177" t="n">
+        <v>7</v>
+      </c>
+      <c r="G177" s="2" t="n">
+        <v>46014.81420138889</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>2025 Cybersecurity and AI Year in Review - Holland &amp; Knight</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>Tue, 23 Dec 2025 15:13:21 GMT</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxQN2Q3SWc1X20xVUd6eHUwdkYwWFZ6MEhMdlhFZTVrUEU5Z3pBUTQ5alhheS1LbFZ5SFF2RGM5RWIxTEprb1ZSaXpfQjlKbFdOLWg0c0ZGZHBGTnk0U2JvYlg2b29Xd1JFbkxTbmxVUXJFSHpEZUtLeG9lODNiVEh4R1Z0aFAxcF8wMVIwNHItYll6VVFJbzkyOGNjTQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F178" t="n">
+        <v>7</v>
+      </c>
+      <c r="G178" s="2" t="n">
+        <v>46014.63427083333</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>CISA Releases Cybersecurity Performance Goals 2.0 for Critical Infrastructure - Inside Privacy</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>Tue, 23 Dec 2025 12:17:07 GMT</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxPSmFjNEJUaHRwRUlMOTU0Mm51UXhpX0hIQkNkdkFHX1hLTWpYTThLdDl5cUh0SldBOXllZnk4dGYyYXFlaHE2UzdxanZtQXVlZzZlMFlLVVladTlLcWFKYWZvUlM4aHY5MnRzOGpvMjNiTlM0WWMtZnZtRllISUJSdVZRZ2pTMUhDZ3N2QVNGVklsUU1ybldSN3JzdHRYd2Q1TnptVjQ0S2RUWkVRNmpTT2M1NTNYN1hpajEzbTFLbw?oc=5</t>
+        </is>
+      </c>
+      <c r="F179" t="n">
+        <v>7</v>
+      </c>
+      <c r="G179" s="2" t="n">
+        <v>46014.51188657407</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>The Convergence of AI and Cryptocurrency: From Digital Transactions to Agentic Payments - Chainalysis</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>Tue, 23 Dec 2025 12:02:37 GMT</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMickFVX3lxTE5aVm1uTFZCY0kxdjFLVDRiV0ZKSFBYM3BKdHNMdm5UNDhIeTUwRUhIbVR4R0VvZ2JEQUZuODRZYzRrcEpQYXZFdUQ3YmtEb2VUNGVPS1ZaWlBPblB2TzBoNHAyOEYwYk9uZDlWSnNUdTcyQQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F180" t="n">
+        <v>7</v>
+      </c>
+      <c r="G180" s="2" t="n">
+        <v>46014.50181712963</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>NIST and MITRE partner to test AI defense technology for critical infrastructure - Cybersecurity Dive</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>Tue, 23 Dec 2025 19:50:46 GMT</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxQMEVNTmF5OUlKQlZFX3VkWWxzcG5qOTE3LXRSNmpVU0I0SDJrRThNQngzUDdrdzZuSVpJOUJ3dGhNdmF0OW51Z1ZfWnZOZklXQjVNNWNNTkZ0MjU1QmpiMkpjRzZBMngyYVVZQnM0NGFJekJNcjZKOFhYZkZrVkZTajltbVZvdERMUnIzZWdjRWstMkUzXy1YZEhrUG83djNOVVE?oc=5</t>
+        </is>
+      </c>
+      <c r="F181" t="n">
+        <v>7</v>
+      </c>
+      <c r="G181" s="2" t="n">
+        <v>46014.8269212963</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>The top technology trends to expect in 2026 - National Technology News</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>Tue, 23 Dec 2025 09:32:52 GMT</t>
+        </is>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMifEFVX3lxTE1MdmhrUzNpT3NZOUd3bzVhY2ZHOGo2QWFNV2pSSmJhWWd4bUtXY3FjWmZ0YUtVX3EzWmFuMFhYNjExQXlCYlhxV1BVVE9pU1d1dVpERFkxX0ZOTFpDT1lOaU9jOVE3dm1QUWxfS2JqaHNyQllheGZBbDhpZFM?oc=5</t>
+        </is>
+      </c>
+      <c r="F182" t="n">
+        <v>7</v>
+      </c>
+      <c r="G182" s="2" t="n">
+        <v>46014.39782407408</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>Motive appoints AI innovator to board of directors - Fleet World</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>Wed, 24 Dec 2025 00:05:23 GMT</t>
+        </is>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiggFBVV95cUxNTXZoemZGWFZoTU9PYlp6eTFjZWJ2NkNTQmZaMnA2OGlidjhKSGFkam92NVJRV1FMUGpNcmRZS2daR2ZlUEhCSVpROUMwVW9ORFhJZGNnRm5qZGRBb25EZW83NUEyNTBzVmdnZU9VV0g0REthaG94azFHRzAzMWZGbU9n?oc=5</t>
+        </is>
+      </c>
+      <c r="F183" t="n">
+        <v>7</v>
+      </c>
+      <c r="G183" s="2" t="n">
+        <v>46015.00373842593</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>NHS boss warns against asking AI tools like ChatGPT for mental health advice - The Mirror</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>Wed, 24 Dec 2025 00:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxNX3BpVGF1ZmVQWDI3Z25haTlyRzBVQXU2bGpNYzZkVXduWEV4T2pRVDlKOEI1YTJxaF9ETnJIZy02RGlnS3A1MDBWRzBmdmpvd0lqQldTMlRIbld5Q1BwWVN2anl5NHFaVEdFLURSUTR6bDhuMS15UjZFVG1KTGMwNdIBhgFBVV95cUxOWHRUMnNjSG1kZDZlcVJTN2M1SE5hX015R3ctSVpHVmdMTGp6V2h0WDM2bEpzRWUzcVZfUWZUWDVmalRyMjM4V0gyQWZjSDBoVFBxMEtMdnpDa2xtNU5saFNxakVPZEduUzZhSWNZMEdid053bEUwSUJnVEZpYzVaUVdXbFBFQQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F184" t="n">
+        <v>7</v>
+      </c>
+      <c r="G184" s="2" t="n">
+        <v>46015</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>RPS appoints director of finance and technology - thepharmacist.co.uk</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>Tue, 23 Dec 2025 10:28:05 GMT</t>
+        </is>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMijgFBVV95cUxQdGdQS29RTm9HZUNpeUZZUnMwRFY2MEh1SnlJR29xN0xQM3ZGQ3lqMjFjREQxRW5WYXhkTUp5ekdKbng2WUtmZVNvN3VEZWRhUGE1ZmhWWFZneE9TYTVFUEZNWGxJWUVqOTc2MlV4M0JYOTdEbnhnQ0RBUFhYU3E2ZXp6M0c5bW91c1EzS1Z3?oc=5</t>
+        </is>
+      </c>
+      <c r="F185" t="n">
+        <v>7</v>
+      </c>
+      <c r="G185" s="2" t="n">
+        <v>46014.43616898148</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>2025/26 Reflections &amp; Predictions: Paul Greenwood, Clifford Chance – AI adoption is at 90% - Legal IT Insider</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>Tue, 23 Dec 2025 13:20:31 GMT</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxQZ3ZlMkRWQkJYSEt6WlZyMWFXQ3pLQUd6UkRuTldVVTd6ODgxYzVjQlFGdWd3QXdOSlR1M3ZJM1FTWUo5TzdZSGdVUWJTRmtIaVNsbTRSNnVidXZONDVfTmYybk9HaGNzTTg0eUdzS0JvYTFURDVndDZmWGh4bkJiOWpISHU5OUZYMFBaZFpOc0piY0t0M0JZa1JVNEZUQVBPd212R2JfWXJCYk5uTlF3clY0d216ZmREYW5zaG1lSGk?oc=5</t>
+        </is>
+      </c>
+      <c r="F186" t="n">
+        <v>7</v>
+      </c>
+      <c r="G186" s="2" t="n">
+        <v>46014.55591435185</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>What is California’s AI safety law? - Brookings</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>Tue, 23 Dec 2025 15:10:57 GMT</t>
+        </is>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMieEFVX3lxTFBrWnM1OXlQRFRkYWQ3c013RkhGTlR0ZjY0UXJOTVgzVUVOOC1aS2VEQndxQi02X0NNOURTOFlUNzBVeHpqeGZWM2k5Qm9pS2N4WE1haUtaZWdYQkc2M3pONWFRdXlEbHVmdEJEOS1fOFAxOFkwT1ZSbA?oc=5</t>
+        </is>
+      </c>
+      <c r="F187" t="n">
+        <v>7</v>
+      </c>
+      <c r="G187" s="2" t="n">
+        <v>46014.63260416667</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>Why most AI adoption strategies are failing and how Wrike's research reveals the path forward - The Manufacturer</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>Tue, 23 Dec 2025 11:45:35 GMT</t>
+        </is>
+      </c>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMizwFBVV95cUxNRm5rc3FZLTZiQTdKYkFpY3BYdEg3bWtXdHdHYzFTcXUtVU9UMUcyeUZEWFM2UDhidGZwczJvc1dJc3pSTVNVcTBHM2ZjZ3FMUHBvY1ExOWQ0a05JZ0tVMG5ZeXUxQ2w1SGxrQWxMX3ZaTlBJNjBsQ1dTZTZQQ1M2dlJnVTU1eG9GNzk3V0VOeUV4SmJ0Uk5nRWdOemt0dlNNS0o4bWhSVGYzcVZBWVRlUG5IeFRwb0MtNzJSLW9ub2FhY0xRNC1ETktwbnhPLXc?oc=5</t>
+        </is>
+      </c>
+      <c r="F188" t="n">
+        <v>7</v>
+      </c>
+      <c r="G188" s="2" t="n">
+        <v>46014.48998842593</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>Cybersecurity Predictions 2026: Preparing for an era of relentless and intelligent cyberthreats - Intelligent CISO</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>Tue, 23 Dec 2025 13:34:46 GMT</t>
+        </is>
+      </c>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi1AFBVV95cUxONFVuRHFMQWE1ZHRYYkhfMjRvTElKWmc2dzREUkJLWTFBeVlaNndHSTA3TDRZTVlLcnhxdzdSQ2xwLTJsZU5BcjQ2X2RXUUNRbUJjTk94ZmVBSm5VcFZwNFBaaUhCc1gwRzJWV1dldHNEcUNpRU5SejBEeF92TUZMYk10XzltSEhQX3ppZDNDeTBLczNyNkYwUElvYnA5QktaN0szSlJvcFB1S1BvMDNxbzA1X19zakFreW1ub0VUM2pxNVdMNnQ0WGl4NmhneUFWcWNlUA?oc=5</t>
+        </is>
+      </c>
+      <c r="F189" t="n">
+        <v>7</v>
+      </c>
+      <c r="G189" s="2" t="n">
+        <v>46014.56581018519</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>How can Canada become a global AI powerhouse? By investing in mathematics - The Conversation</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>Tue, 23 Dec 2025 14:06:08 GMT</t>
+        </is>
+      </c>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxNYTRoTWEwMGdpZVd4azhwT2dhd0ctNHRPSWs4V3VoZU1BSzRwTEZ2QWhyWW04b0Job1REbVdXcXFzenZ6d3VTZHE2YUNhX242dlN3RmYtUDhaRHVrcTE1eW1ZYjYwTnFBdWRMZG50eXU1VE1INUJ5RU9WSl9uTjktVFNVM0Q0Y1IzWkVjQXIxdURabW93ajV0dDB5bTRjU3FaTkFiUWhHNEpNU0E?oc=5</t>
+        </is>
+      </c>
+      <c r="F190" t="n">
+        <v>7</v>
+      </c>
+      <c r="G190" s="2" t="n">
+        <v>46014.58759259259</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>How Automation and AI are powering the Gulf’s digital future - Intelligent CIO</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>Tue, 23 Dec 2025 14:47:54 GMT</t>
+        </is>
+      </c>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxNX3IxMGJsWVhtX2c3QkhOYmt0WG9jOUlkSEhOcHhubzhXY0QwUEZJdDVZdjBpNmlGOXJ1X1ZwSzBUSFhodHJiOGtPS3RISzNVQXpWcWtNdERIOG9tNXZZSi1hSV9lRE43bHpwNWVCcmxRQWNINDFvYWJIY2FHclVCLXBZQi1uRkpIa29TU1lKZG9wajAwckFGcVFrS1RuUzNWOGV3R21XbjY?oc=5</t>
+        </is>
+      </c>
+      <c r="F191" t="n">
+        <v>7</v>
+      </c>
+      <c r="G191" s="2" t="n">
+        <v>46014.61659722222</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>Kamlesh Jobanputra Joins Edelweiss Life Insurance as Chief Technology and Data Officer - CDO Magazine</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>Tue, 23 Dec 2025 13:30:00 GMT</t>
+        </is>
+      </c>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMizAFBVV95cUxOU2ZmZG1odUxobGY4ZURqY0JiV1llR00wY081akNTZTEyR080aXd1UEZKTDBUSkZHQkNkdTRuYWVFVWNOYkZYZm0tcW01WVN5YWh0T19uOGRIclUtTVhuRHZnSmRlOTNZV3A5NmlXci1XYk5pd3huOUlGb1ZuNmxJZG9sWkwxM21OSlFzVzhWZmdITEJPM3BlVkVfTTlkbjFiQWJoWU9Zd2dFV0tlcnRGTlJydjVfcE9sbnlVWTVGVlNUTzVta0QwWWZtQzc?oc=5</t>
+        </is>
+      </c>
+      <c r="F192" t="n">
+        <v>7</v>
+      </c>
+      <c r="G192" s="2" t="n">
+        <v>46014.5625</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>The Continuing Expansion of Algorithmic Software Laws – Best Practices for Companies in an Evolving Landscape - Winston &amp; Strawn</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>Tue, 23 Dec 2025 21:45:00 GMT</t>
+        </is>
+      </c>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiggJBVV95cUxOYURtZTBiNllCVTdnZ3Q5ME9IMVppNE5hUXJPcFJWdFo1SjlVZElObHBOeWZ0Q2lic2lSSlNMSlNwQ0wtTVlxTE1wMVNlMjlIRmZNS2hSSmRjczRYdVhVci1JaUd6Sm9zTnVTdW5XTjlOYU0tMUpkVW9VTE1qRHJWUGlJdDBkWkpibTQ2bHY5RmFRZVliNk54U18xdWlRSVdmUFVCc2FvOHV2TE9YMFJuOU5WaW5vN3Fma2h2MWZ6MFlnVUwzQVk1SVBiM2tOOUtYOGVITDg2S000OElFN192Z2dFSlZvb05jN0hXeEt0dXpTZWpOZ3BhLVdqOUx2M3NFX3c?oc=5</t>
+        </is>
+      </c>
+      <c r="F193" t="n">
+        <v>7</v>
+      </c>
+      <c r="G193" s="2" t="n">
+        <v>46014.90625</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>Revolution at sea: How AI, electrification, and autonomy are transforming shipping - safety4sea</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>Tue, 23 Dec 2025 12:39:29 GMT</t>
+        </is>
+      </c>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxNMWUxZkNQOFQ2MmxKNVQ5YWhRWGNHWGV3YUNyXzE0djd1blBOTVY3bjVhLVVfblo0c2ZQbjBIZk1KcncySWFDU09iQl9HcDFpakh4bHA3VXdsNzdxaFIzUmJsbG1xTnlEbjdQdW13UGozLVF5MlpyamZuODk3VzhxbkpNRG5UWm1wSTBENGE3TGdXSHJVQ05HaUtzN0NHRjNUUC0zbG1zNFdkZw?oc=5</t>
+        </is>
+      </c>
+      <c r="F194" t="n">
+        <v>7</v>
+      </c>
+      <c r="G194" s="2" t="n">
+        <v>46014.52741898148</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>Google's year in review: 8 areas with research breakthroughs in 2025 - blog.google</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>Tue, 23 Dec 2025 17:18:57 GMT</t>
+        </is>
+      </c>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMib0FVX3lxTE9HUHhmaWlhdHZXZU1JanR6TUpZNEE2dV9KQ0ZCSl8xTXhESmt0YnlISUstWVVGWEE5bEN2ZXFIckNHcVNfbzFrTlFWdVEwWDNGVEhHYzdzUUZMMjFwUkJ1dE9HNHFvR1JaRTlPZXBHZw?oc=5</t>
+        </is>
+      </c>
+      <c r="F195" t="n">
+        <v>7</v>
+      </c>
+      <c r="G195" s="2" t="n">
+        <v>46014.72149305556</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>CISA loses key employee behind early ransomware warnings - Cybersecurity Dive</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>Tue, 23 Dec 2025 15:50:46 GMT</t>
+        </is>
+      </c>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxOUmZpbFF6QUpRMHFMU2pQMXJ6U2hweG4yTEhVNlRBME1Pb2EySldCX2NPSDNFTG1JOTM4QkVqRE9JdDBPNmlSZGxqWWN4SkRxNmx5dUZEdDFzTV91WDZnbmJSN0VERllHNjNwZ3JaVDBYVVdIWGxjM0Z1QUpmYi1wakJwQXpjZVF3eXdVZUZwMzZJTnhLdDBlRXI1N1k?oc=5</t>
+        </is>
+      </c>
+      <c r="F196" t="n">
+        <v>7</v>
+      </c>
+      <c r="G196" s="2" t="n">
+        <v>46014.66025462963</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>Memory Chip Makers Say AI Alters Boom-and-Bust Cycle - Bloomberg.com</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>Wed, 24 Dec 2025 01:34:56 GMT</t>
+        </is>
+      </c>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxPTzNpWk1Ub0NEV3VKTnkwTXFTeEdLTlRkbnprTEFNUTNEXzh3MXZtcUZ1bnNyVkQ1eXJMRTc3Qm1nMXFHUUJ5TWhzRm95dFZ3Wkt3dU05eHc2a0NabnF5eUkyUWJnS0VaNDJRS2JhNHVQZWh3NXg3ZVlzVDdWcmhBc0Q0M2JKTmZQR0FjLV9meDRKMU1Db0lqNDJnMDhTUGxoUzh2TGxTc0d4Zw?oc=5</t>
+        </is>
+      </c>
+      <c r="F197" t="n">
+        <v>7</v>
+      </c>
+      <c r="G197" s="2" t="n">
+        <v>46015.06592592593</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/topic_feeds.xlsx
+++ b/data/topic_feeds.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G197"/>
+  <dimension ref="A1:G296"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6937,6 +6937,3273 @@
         <v>46015.06592592593</v>
       </c>
     </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>Current_Affairs</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>(geopolitics OR migration OR economy OR conflict OR legislation OR terrorism OR disinformation OR misinformation OR government OR policy OR regulation) AND (briefing OR analysis OR update OR report)</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>New analysis shows Britain’s innovators are boosted by Horizon - GOV.UK</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>Mon, 29 Dec 2025 09:06:31 GMT</t>
+        </is>
+      </c>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxOT256ZmtoQ050NExVOExMVnlmdGtQMTg1OTQ2WXB2eHR2dFAyQzV0TjF6TktZLWRraWFkWjZtRTVULTBfQjQ0ZHhkdEJkREpmbm1zeU1CMEJhMEdXUlhlR2JGcGRjZE45TjFvNU9OMko1TFBhZzkzbnNMRjhxNzJmUWsxYklaMUZ3dkw1Z3gtZmlKTDZGSW9HVEpnNkc?oc=5</t>
+        </is>
+      </c>
+      <c r="F198" t="n">
+        <v>7</v>
+      </c>
+      <c r="G198" s="2" t="n">
+        <v>46020.37952546297</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>Current_Affairs</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>(geopolitics OR migration OR economy OR conflict OR legislation OR terrorism OR disinformation OR misinformation OR government OR policy OR regulation) AND (briefing OR analysis OR update OR report)</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>Chinese Tax Regulation Update – November &amp; December 2025 - CMS LawNow</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>Tue, 30 Dec 2025 04:18:36 GMT</t>
+        </is>
+      </c>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxPWURWQk96VWNndTM5aUs5RmhKUDVyT01tSGpLM3BnaVlJTTkwMzZjSFhVaUNMWE1Hby1FcFF2OUJDZWVBUVFEVXhHWHI3ZXA3QTdXelBGY3lwQ0JKRFpsVkhCLTJ1Sm5Ia1dCTzFuY2tUd29yMzZKMEJJbm1zSXRibFVZSmFiMjliaXM0Rko3OXNtTllYeUZlTEZ3?oc=5</t>
+        </is>
+      </c>
+      <c r="F199" t="n">
+        <v>7</v>
+      </c>
+      <c r="G199" s="2" t="n">
+        <v>46021.17958333333</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>Current_Affairs</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>(geopolitics OR migration OR economy OR conflict OR legislation OR terrorism OR disinformation OR misinformation OR government OR policy OR regulation) AND (briefing OR analysis OR update OR report)</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>India overtakes Japan as 4th-largest economy, report says - DW</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>Tue, 30 Dec 2025 12:21:54 GMT</t>
+        </is>
+      </c>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxQaDBsVmpiZHJNTXVGUzQtVm1SSW83Rkt4RFd5cU1SdzZJZkxtU1c3UXRkNmx6ODMzMGZ4YWFyQ09XclFKUFpseVpnaDAzeEVsVGdNZHNaaHJnNHJTNWU4Q1hqUk9rNC1rbFBKY1JPbFc3M0I5TThGdk5GbjN6Yko2STRjWHhMYURvN2tzREo5R2Y2bU3SAZMBQVVfeXFMTUh6X1ZPNV9DQmZBdl9jRDU3WVJ3a3BwdUZOaGNBZ0h0ZkF3engzd25FSkxweFB6LXRjQ3psbVJEVHF2N1A1dlZJc3FydHV2NThzRzJnMkJUeDRUMUNCMG1nWlY4X1NNNUZGMFZsOThtdnIyenhRWllZemZUQ1hydENVVk1mdm55cUJDS0RBMWtXbjY4?oc=5</t>
+        </is>
+      </c>
+      <c r="F200" t="n">
+        <v>7</v>
+      </c>
+      <c r="G200" s="2" t="n">
+        <v>46021.51520833333</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>Current_Affairs</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>(geopolitics OR migration OR economy OR conflict OR legislation OR terrorism OR disinformation OR misinformation OR government OR policy OR regulation) AND (briefing OR analysis OR update OR report)</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>ANALYSIS: An unexpected end-of-year fiasco for the government - Jewish News</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>Tue, 30 Dec 2025 13:42:00 GMT</t>
+        </is>
+      </c>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMilAFBVV95cUxNUmNlam9YUDRNWmRxQ1B0VVhHRTdhdnBSWi0wbHdvMDdaaUM4aFM4clJNcWR2NVFXS0JUYXJmcDh6NGQwYXFMeWFpYmRLY1c2SVJ3ZTB0eTZRLVNXSVVMRjhWbFh2V2YzNlROVHVoczVKTVotdTBqUkdqMlpoMlQybExBblQtOEwyMDkwYXNTT0xMaUMw0gGaAUFVX3lxTFBELTlUOURYUWRKSmluY1VFMmFYWFQzaEF2RzFlZWlTN1VpeHN5QW1fYkVfaDBqV3RiRkpvUlJWZnljb1lKSEpuQUlGUld1Ykc1Z0JHa3ZJUkFtZXViSjFxQzhzOGNZYjB5b0oweFF5WGItQ2Y0SDF0d2h3eEhsd0Y0ZU90YXgxSkhmdjF2eGVmWHctd2tWWlNPX2c?oc=5</t>
+        </is>
+      </c>
+      <c r="F201" t="n">
+        <v>7</v>
+      </c>
+      <c r="G201" s="2" t="n">
+        <v>46021.57083333333</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>Current_Affairs</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>(geopolitics OR migration OR economy OR conflict OR legislation OR terrorism OR disinformation OR misinformation OR government OR policy OR regulation) AND (briefing OR analysis OR update OR report)</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>Reliance denies report of $30 billion Indian government claim over BP-partnered deepwater field - Upstream Online</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>Tue, 30 Dec 2025 08:37:37 GMT</t>
+        </is>
+      </c>
+      <c r="E202" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi4gFBVV95cUxNYkxvYUN5V21KU3lPbEtMS0VXdDdjZGsteVVhRlA5aGp3azdISEdvOUUzME9FMDJsWVc3di13ejNIdl8xY1VBYlF0VzhEMnZKdE1hS3U2anZIelFQWHNHSkc1cTV0V0tmRkF5N3pJbzM3eHZiZmFOQmpQSzJteVhCWklGSmZVUkV2MmJ2ckdiVG9iM2ItT2V2SloxX3hocFpHLVZrcjhLY0Z2REJWb043UHlXalJsSkpiTUFhLTJuLXhtWFp4V0RRSGR4YTE5NkRKeTBjMW95bTR1WEZudGdla2pR?oc=5</t>
+        </is>
+      </c>
+      <c r="F202" t="n">
+        <v>7</v>
+      </c>
+      <c r="G202" s="2" t="n">
+        <v>46021.35945601852</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>Current_Affairs</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>(geopolitics OR migration OR economy OR conflict OR legislation OR terrorism OR disinformation OR misinformation OR government OR policy OR regulation) AND (briefing OR analysis OR update OR report)</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>Nepal: Labour Migration Report 2024 criticised for erasing caste from migration policy and analysis - Business and Human Rights Centre</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>Fri, 26 Dec 2025 10:38:27 GMT</t>
+        </is>
+      </c>
+      <c r="E203" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi5gFBVV95cUxPQW5HVU1BSF9uQWpoZzNpWEh1aklRazN1d1QzSE4wMklzUG9NOFQxRkRTWGZ5T2Z3bVpESW1DbHE2Q1R4ekNPZkZLTDBNeGY4RVdjRXQxQXNWby1PSzlOUWNFNTVYRk50dlBlWlpsaF9TMXRZTE1mS29USWl5Q0FuRm9mQ2JqQXZLNDNfY3VEUDNHUi1lUzJKTjk4aHZxS3ZPVkpFeUN0RkdvY3I2NHNDZ3FKaVRacEstYTlLZF9GbWM5RWpNSzhyVF8yU2s1NDhBbHhCR2JvNXlDeUROdlQ5eHdXVU5DZw?oc=5</t>
+        </is>
+      </c>
+      <c r="F203" t="n">
+        <v>7</v>
+      </c>
+      <c r="G203" s="2" t="n">
+        <v>46017.44336805555</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>Current_Affairs</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>(geopolitics OR migration OR economy OR conflict OR legislation OR terrorism OR disinformation OR misinformation OR government OR policy OR regulation) AND (briefing OR analysis OR update OR report)</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>The hidden scars of conflict and silence: sexual violence against children in the Democratic Republic of the Congo (2022 - 2025) [EN/AR] - ReliefWeb</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>Tue, 30 Dec 2025 00:33:06 GMT</t>
+        </is>
+      </c>
+      <c r="E204" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi9AFBVV95cUxQbVVUdFVTZnBjb244UU9aTmVST2lQWmVOOF81THhDczhvel9nYU1tczRtbUhZbmdkOXA2WW1zcHNCcngxb3AybmtKREYyRUctdXZQZDJDN2hWMVZXRTNjTTJMeFhmZnZWc1hqalJKQUl0WlNsQjRBM3JVUHVURnlwQXhjSmx1LW1oQkxqREJzdjJwbERhUEdQd0hHYzEtY3JDNGxBYnI4YVBYUGxUQmpLcTV5R0YtTnpOaDREWXdabGtBSC1pdE1fLS00U09BWV9fc3BaLUdDVnVaZkw3S3d5RUJaMmFjX2NDRC1SS2k3em9tajNB?oc=5</t>
+        </is>
+      </c>
+      <c r="F204" t="n">
+        <v>7</v>
+      </c>
+      <c r="G204" s="2" t="n">
+        <v>46021.02298611111</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>Current_Affairs</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>(geopolitics OR migration OR economy OR conflict OR legislation OR terrorism OR disinformation OR misinformation OR government OR policy OR regulation) AND (briefing OR analysis OR update OR report)</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>Africa: The Emerging Global Epicenter Of Terrorism – Analysis - Eurasia Review</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>Tue, 30 Dec 2025 17:58:02 GMT</t>
+        </is>
+      </c>
+      <c r="E205" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxNTTJOb3VldGxBRzNUNEUtRXNvTW1sbnRMampqQTl4YnhURWZnMlM1aTB4MGJXaUs1eGpkbnZBSklXUC1wX2xxeDhpT05NTndlOGkwQnNfUkRjMzdrb1k4b2V4empKSVBhZ1BQSThFTVJXWEpFV0tmLVM3elpSTm9iVS1ndkRMZzZhemJZR29lR2VydnBEUmxsNlY0VjBPYmc?oc=5</t>
+        </is>
+      </c>
+      <c r="F205" t="n">
+        <v>7</v>
+      </c>
+      <c r="G205" s="2" t="n">
+        <v>46021.74863425926</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>Current_Affairs</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>(geopolitics OR migration OR economy OR conflict OR legislation OR terrorism OR disinformation OR misinformation OR government OR policy OR regulation) AND (briefing OR analysis OR update OR report)</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>The Death Of Sharif Osman Hadi: Rethinking New Delhi’s Bangladesh Policy – Analysis - Eurasia Review</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>Wed, 31 Dec 2025 00:58:44 GMT</t>
+        </is>
+      </c>
+      <c r="E206" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxNZ0ZDS1FUY2Fob1lnMzEzcUZCeUtPMTNjUG9xeHhTWnVtd3FPVFJ1VTFua3BGaTZqQXN2VDdTOG5EUERjbjBnX2hvU0hFcEpLNVNKNGhHelRXNFFaVjJRS2tTVVVwRWtPcElmSHhPM1dSNzdkYXlfQjZqYnYtVEltWWg3U0R4bW0wNFBJbzluWURPSDdabmZlaHhEZ0F5azJFQTFNMDN6UUZQd2hrS2h6Zk5Xdi1ZQWM0amJF?oc=5</t>
+        </is>
+      </c>
+      <c r="F206" t="n">
+        <v>7</v>
+      </c>
+      <c r="G206" s="2" t="n">
+        <v>46022.04078703704</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>Current_Affairs</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>(geopolitics OR migration OR economy OR conflict OR legislation OR terrorism OR disinformation OR misinformation OR government OR policy OR regulation) AND (briefing OR analysis OR update OR report)</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>South Korea releases policy report on data issues in competition - MLex</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>Tue, 30 Dec 2025 06:11:00 GMT</t>
+        </is>
+      </c>
+      <c r="E207" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxPWWN4Tkx6QkMwQW1RN0Q0aTJqZnhDQ2Z0ZENxU1dmc2hnbGlVeHp1eVRnSHp5dW1WSno4VFZXQVo2UzR3clY1d1dTeUFYUjJFRFQyWkcxamRaakVMclh5eVprM1otNEdxeklWMU1BeHhoWjQ5T3hTQ21ZbDI4Qy1GZUhyejk1R3VQZXFXbW9LdDdVNnh3bmtfZ0VyWmFTTm0zT1h3dUNVc1dwZUnSAVpBVV95cUxQMXlfc1BlMWtSU2EwSGNtTU9QckVyQlRwSzNCeG1NYm5YYm9pSEZKQkNBamU4R2gwbUJvSExwYkt3MGhUU1hValhQTml4azZLSGJNT0lMdDhXR2c?oc=5</t>
+        </is>
+      </c>
+      <c r="F207" t="n">
+        <v>7</v>
+      </c>
+      <c r="G207" s="2" t="n">
+        <v>46021.25763888889</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>Current_Affairs</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>(geopolitics OR migration OR economy OR conflict OR legislation OR terrorism OR disinformation OR misinformation OR government OR policy OR regulation) AND (briefing OR analysis OR update OR report)</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>Middle East space economy enters execution phase in 2025, report finds - SatellitePro ME</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>Tue, 30 Dec 2025 08:21:28 GMT</t>
+        </is>
+      </c>
+      <c r="E208" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxNUjJNaGFkUk01OTlRYWk3dlNsVFZUTHBzWjlNd2xHNTFTTDV2eXpWeGtnNTZRMGIyOEkyaE0zeWRHUmJiZXVJTTZncW9mR1ZDTzNvRzhHMEU1eUFBZHlqTGdvMnhLSjkzSUxldW1SeVRYOTFUc2I0S0xMbm5kN0lFUVJpc1dRYVhORk1ma2diWFFXMFg2RFF6NWhySEMxWnUyeWtCbQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F208" t="n">
+        <v>7</v>
+      </c>
+      <c r="G208" s="2" t="n">
+        <v>46021.34824074074</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>Current_Affairs</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>(geopolitics OR migration OR economy OR conflict OR legislation OR terrorism OR disinformation OR misinformation OR government OR policy OR regulation) AND (briefing OR analysis OR update OR report)</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>Nationwide issues update over Scottish banknotes policy - Daily Record</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>Tue, 30 Dec 2025 10:32:00 GMT</t>
+        </is>
+      </c>
+      <c r="E209" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxOYUJRQVJXVlhJc0ZLZ0MwSnBqZGdmVkZwQ01QT2tMY3p3RHAwTnllaFRIWC1WRkVOWnJnVHJLXzZPaWtwYVJpcEVFLWFkMWQ1SEkxS2pMT3JFVmh4bVpDUVZtcVM4RjdlcmN0UkUyQ1E1VTV4U01yREVDNjZCSE5BSXQ0UENOQkZ3MTE4M0pWc1fSAZYBQVVfeXFMTnJxYWVhaUV2S0hEYkdneF9xOHdiN3RUVkJMeFVIUnR3c3BzalNCM09FM0RlS3llWHJnc0FwaE1JbDNOY1FleFhIcmRsOER5Tm94aENjbUFtNklsdTBWb3YyOE5udTNUMmRNQ2FrRzREb2hIVFYwRGtMUE5tMHgyamViOUpRT3RFTkNSWjQ3Z3FFa09JcHNn?oc=5</t>
+        </is>
+      </c>
+      <c r="F209" t="n">
+        <v>7</v>
+      </c>
+      <c r="G209" s="2" t="n">
+        <v>46021.43888888889</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>Current_Affairs</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>(geopolitics OR migration OR economy OR conflict OR legislation OR terrorism OR disinformation OR misinformation OR government OR policy OR regulation) AND (briefing OR analysis OR update OR report)</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>US Embassies to Track Migration ‘Crimes’ in Western Hemisphere - Bloomberg.com</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>Tue, 30 Dec 2025 16:21:20 GMT</t>
+        </is>
+      </c>
+      <c r="E210" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxNUTlMOHFIdjdtbzlTS3RBdHNsOENwRHY3UC1vOWtGZXhmT012SmZ4SmczeU1jVVNPYlIyLTNUSFpmU2EtbmlCaDZWU0JfcWZNVWM5VnhScE96ckZtYnBXUVhLT0c5VjBIRV9MZUt6eGRDV01sWlI2ZzBPN3VkVE9sTThTWTlFVWdiWVF4amNMQ1V1VzNQR3dHXzl5Skw5eFFuTFhsdmtYYTk4M00yRTB0ZA?oc=5</t>
+        </is>
+      </c>
+      <c r="F210" t="n">
+        <v>7</v>
+      </c>
+      <c r="G210" s="2" t="n">
+        <v>46021.68148148148</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>Current_Affairs</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>(geopolitics OR migration OR economy OR conflict OR legislation OR terrorism OR disinformation OR misinformation OR government OR policy OR regulation) AND (briefing OR analysis OR update OR report)</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>Nigerian government give update on Anthony Joshua's condition following car crash that left two people dead - UNILAD</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>Tue, 30 Dec 2025 09:54:27 GMT</t>
+        </is>
+      </c>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxNcHMtQk53VzVkZE1fQnBONUtWd2pOY2tuRkg0TC1mbVhiRHlNZ1M1MzBkaUN5VWxSYmotRXpHRDVUUXpMZXJDYUFuZTA1X3ZZX1AtNS1EUHBoSGgyOVpoNU5jTDJmSWEzb3FXUm5fRVh3UWkzLXhpT2Ytd0hHd3RQZERIeGw1clBJZFo4aW5QSjlMWGdweHBEdA?oc=5</t>
+        </is>
+      </c>
+      <c r="F211" t="n">
+        <v>7</v>
+      </c>
+      <c r="G211" s="2" t="n">
+        <v>46021.4128125</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>Current_Affairs</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>(geopolitics OR migration OR economy OR conflict OR legislation OR terrorism OR disinformation OR misinformation OR government OR policy OR regulation) AND (briefing OR analysis OR update OR report)</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>Contesting West, Aligning with Rest: Georgian Dream’s Foreign Policy in 2025 and Beyond - Civil Georgia</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>Tue, 30 Dec 2025 13:29:58 GMT</t>
+        </is>
+      </c>
+      <c r="E212" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiR0FVX3lxTE5IMEwxelkzSS1yZDAtVVdfZUY5TmRGR2sxNU1XQTVOWFJqOFl4UnByY2d2UVU3dkJmUHVqVnZXVEhnNmxSQmdV0gFMQVVfeXFMT3RpcHc5ajFITXhPQkZXMEhKaTYxR2EtUGM1UWMtV1JKS3g0X19teHNFNEcwNk9Ga0k3WnVPV2FvOVJQMGNCdGlhOG5JSQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F212" t="n">
+        <v>7</v>
+      </c>
+      <c r="G212" s="2" t="n">
+        <v>46021.56247685185</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>Current_Affairs</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>(geopolitics OR migration OR economy OR conflict OR legislation OR terrorism OR disinformation OR misinformation OR government OR policy OR regulation) AND (briefing OR analysis OR update OR report)</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>Delay to post-Brexit deal costs UK £100m a week, analysis shows - The Independent</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>Mon, 29 Dec 2025 16:55:00 GMT</t>
+        </is>
+      </c>
+      <c r="E213" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxOajkzUGR3ZG51OGoxMWhrNFBpNVJpaGpGeV9hQmNscmlKSElYd1A4aFFQSnFSWEhMQ2V5WmlSbnZQN1lnZXU4X0ptV2RtZURUcmp1TFhXamJqemIzUExhMUNZRmZzWlFEbHRIY1FuTkNxYVZ3ckJHdmkzd2JjcUlTakVGdVllV0dpOWlqYkhKYjVZckJuNEZnRUV3cw?oc=5</t>
+        </is>
+      </c>
+      <c r="F213" t="n">
+        <v>7</v>
+      </c>
+      <c r="G213" s="2" t="n">
+        <v>46020.70486111111</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>Supply_Chain</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>Donald Trump expected to impose new levies if Supreme Court strikes down tariffs - Financial Times</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>Tue, 30 Dec 2025 11:00:09 GMT</t>
+        </is>
+      </c>
+      <c r="E214" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMicEFVX3lxTFBpTVdieWM3VTJQZnR0dGNtWUlBcnh0NXlmWi04MzJLc25ISk9QSVh5YmpYcHpwNVR4b2x4MnZRMkpxRjJycDJLZDVIU0RpbVdLYWUtZjUzbGhzd21EWnNCMGlHNFRTczNob0VWYjBtQ04?oc=5</t>
+        </is>
+      </c>
+      <c r="F214" t="n">
+        <v>7</v>
+      </c>
+      <c r="G214" s="2" t="n">
+        <v>46021.4584375</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>Supply_Chain</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>Exclusive: CIA carried out drone strike on port facility on Venezuelan coast - CNN</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>Tue, 30 Dec 2025 03:10:00 GMT</t>
+        </is>
+      </c>
+      <c r="E215" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMidEFVX3lxTE5qS0NDWmZ4a3JNSl84dVBEYmp6T2N3ZWpzZWVWVVNMalNJVlFCMlpfSGpraTMzSmhzcUZCcDZLNXNVb0Rya1FzVTdoV1dfRy1kWE1NdXd4YzE2bERoLU41dXdaa0F4SWRWVzA2bU5NMFFnQUE5?oc=5</t>
+        </is>
+      </c>
+      <c r="F215" t="n">
+        <v>7</v>
+      </c>
+      <c r="G215" s="2" t="n">
+        <v>46021.13194444445</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>Supply_Chain</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>Horton Port Eynon Lifeboat Crew Rescue man cut off by Tide at Three Cliffs - RNLI</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>Tue, 30 Dec 2025 21:23:51 GMT</t>
+        </is>
+      </c>
+      <c r="E216" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxPVGl2V1FLakxZYXduTXRhQXBGZnVMamIxc05LWHlSMXZkVkphc21rbklnZjQ4VGVFbUdzdGlBX3lOY2lHbklqY3BoSXdqUGwyTEh1UldwME1RRWJ6UVRvTTBOMkxTRHdkY2Jkd3hFdkxocDYxUlFKcFhtZDhDcTVuYktGbzgwa280Y0ZLY1htRXhNd1FhOFRyNHBPUFhlbUZ3aFU3dmZsT2pmWk9hZFNlWVB0SUdMVGV0RUhLREc0NVc?oc=5</t>
+        </is>
+      </c>
+      <c r="F216" t="n">
+        <v>7</v>
+      </c>
+      <c r="G216" s="2" t="n">
+        <v>46021.8915625</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>Supply_Chain</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>Why haven’t Trump’s tariffs crashed the US economy? | Jeffrey Frankel - The Guardian</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>Tue, 30 Dec 2025 04:50:00 GMT</t>
+        </is>
+      </c>
+      <c r="E217" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxPUFlBbGp3cTA1aTI2U2dWXzVGNDBMNlllRF9tV0xDSHpFS0ZreWRmazNLaXQ1V3d1QkxsVWtQRW12b29oUE9zdUFiV3laZlRMZm05TEEzVFA2VGNRZEViOXJVcVgzTDM1NkdfYnM0NnB5MTVMLTZqb05TTWxTR3ZQRXZoc3hqaVNCOFhRYUREdUhNWDFlMDZFYzZKalIwcDZBWWF5TmszWmR5UQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F217" t="n">
+        <v>7</v>
+      </c>
+      <c r="G217" s="2" t="n">
+        <v>46021.20138888889</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>Supply_Chain</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>US issues Iran-Venezuela sanctions over alleged drone trade - Al Jazeera</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>Tue, 30 Dec 2025 17:48:45 GMT</t>
+        </is>
+      </c>
+      <c r="E218" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxQb1FUTU9wQ1dTeks2aHhtT0JHRjJ0U0dpMUZGZ2VQeXBiQXBZUkdKOGVUUFBCS0s3V1JWRmFrUVlXUFIxdlRQYkVKeGFFYzZUZHM1d1B1eFVGWTVoN2thR0R5c1dXSWFTNXBWV1NWRVNkRkxSNW1udGZFMnRqcEp5NUZMb0JyUTM1bG9SM1NuQmF2R1ZUaG1kdEZxT284cWlPeFZJ0gGoAUFVX3lxTE80NXBfQXZxTkpad3Q5dWhoaXRlWkhpbHR5ZGprT2RlajVVTURJSVBneUFqT1pfZjhnSHNzRU5PVGEzYlBzcWp5MHJ3eXR1cE5SaDFONG5Jek9TcUhCalNuZVd6bDhuazlLT3pqQnNpS0sxcU95M2FncDJDSExodDBxdW9uWmREQmZfaFJJMGdORFJFZlZTMV9OREoyb3hPbGNBREFIXzNzNw?oc=5</t>
+        </is>
+      </c>
+      <c r="F218" t="n">
+        <v>7</v>
+      </c>
+      <c r="G218" s="2" t="n">
+        <v>46021.7421875</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>Supply_Chain</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>UAE says it will withdraw from Yemen after Saudi strike on separatist-held port - BBC</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>Tue, 30 Dec 2025 18:22:57 GMT</t>
+        </is>
+      </c>
+      <c r="E219" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTE5RSEdiSURoYmlhcXpQSUpRTFdzcFRTdkliMDRzYlQyakxtVVl2LVRiRzdmSzI5Z2NTajc1OHVPTmtQQnJUNW95WHE2WVQxaVp2SERUcWg1VlVZUdIBX0FVX3lxTE5NN01HNWN0Tl8zZjB3bmtLOUtBdW95ZldoRl9yQmJUQVJ1aUVoOHZiRVFXcllISWtTZk9wMFZfY3FUU1FoVmRXYUpPY1lPU1dpMjFpYWluQ1BVUE9tUWdr?oc=5</t>
+        </is>
+      </c>
+      <c r="F219" t="n">
+        <v>7</v>
+      </c>
+      <c r="G219" s="2" t="n">
+        <v>46021.7659375</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>Supply_Chain</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>Napier Port Holdings Limited's (NZSE:NPH) largest shareholders are private companies with 57% ownership, individual investors own 25% - Yahoo Finance UK</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>Wed, 31 Dec 2025 01:55:00 GMT</t>
+        </is>
+      </c>
+      <c r="E220" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiiwFBVV95cUxNQUwzR1cxRUtyR2UybDlYLXlXQzVvMDNTS1liVjNESFdjbXBxRzc2SzUxZEJSazBSWG4tcm52bFVNQ2FXTGhRUV9sNUFyb1drWnd4WjhSdmFvVVZQUFl5T0dOejdrSDhiQWRSN2FHNzhrXzUxeGN0c3dqNVRIeUwxOXFKUEp2c1FtWVp3?oc=5</t>
+        </is>
+      </c>
+      <c r="F220" t="n">
+        <v>7</v>
+      </c>
+      <c r="G220" s="2" t="n">
+        <v>46022.07986111111</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>Supply_Chain</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>Navigating Tariff Turmoil: Ports and Shipping Face Unprecedented Challenges - Maritime Fairtrade</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>Wed, 31 Dec 2025 00:24:16 GMT</t>
+        </is>
+      </c>
+      <c r="E221" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxNYWNtdWU1S3l1NmhCOVFucWFCRG5KZDJ4UExvSS1YVkkxTVNSalZyV3Y0bjl0TjFJeW03QkE2OGU5QnctaEpYZEdwTkQxek5jVk9XdnF1QkRGaW9ibnJyeEhRQWtLWE1KMWRWSzFscFdtc29DLW02a1EtTVFzTnhkMVRLMUpFWm0tOXgtZ0tUdS1pd1RkZ1hrcks4ZTJKbmQ1Z09fSkRfSE8?oc=5</t>
+        </is>
+      </c>
+      <c r="F221" t="n">
+        <v>7</v>
+      </c>
+      <c r="G221" s="2" t="n">
+        <v>46022.01685185185</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>Supply_Chain</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>Ukraine drone strike damages port, gas pipeline in Russia's Tuapse - TRT World</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>Wed, 31 Dec 2025 01:12:39 GMT</t>
+        </is>
+      </c>
+      <c r="E222" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiWEFVX3lxTE5raXk4anFPTGxyVVl1WExyZmdzNnBMVjFDcVJDVVJQWno4VU9maDZGcndvTVhXXzJtUHByWHRlamFHZ0JUZi1VLXROck5hd2x4NHdyYmx3bHHSAV5BVV95cUxPVVJSeHRxNmU2VXFieFd5VXJ2SUtSaUlVdTNkTFBTMVYwQnJYRzZqdGoxTWZzZy1lZ3FhTHJvc19FZlNyUUNyVHMyQ3p3OFNPZzBSQnVyQ0xkSDR5TWVn?oc=5</t>
+        </is>
+      </c>
+      <c r="F222" t="n">
+        <v>7</v>
+      </c>
+      <c r="G222" s="2" t="n">
+        <v>46022.05045138889</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>Supply_Chain</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>Former EU tech czar says US sanctions against him put Brussels on ‘dangerous path’ - politico.eu</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>Tue, 30 Dec 2025 12:38:00 GMT</t>
+        </is>
+      </c>
+      <c r="E223" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxON282WjJydVVNQTlWQWxuYXhZbG1nR2lRZEVJaEJ0LW1FTUxNczNkeF9hajcyOTJuN0V0VTFHdkhESGdXV0MtdVNqMDg2cFJKQUczNEQyLVAxUU1GamFpWkc2THZBZTM5OEJ1Y05YakJiWmd3VVpTVEJCZ1dwOTF0c3daTkd4S2I3blc1Y2duU2VLc0E2YUdySHRoSldtRUJNcnNyeFlZVVVkcHdDVzVjTHFXVDlPdk5E?oc=5</t>
+        </is>
+      </c>
+      <c r="F223" t="n">
+        <v>7</v>
+      </c>
+      <c r="G223" s="2" t="n">
+        <v>46021.52638888889</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>Supply_Chain</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>In Defense of Instability in Mental Health Recovery - Mad In America</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>Tue, 30 Dec 2025 18:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="E224" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxOUng5NXY3MnZySUZ5cnNSY2N1NzREdnJRc090OUVoalVfaWpIRkVQaUhkb25Ha0d3ZE5CVDh4bDVjMTB5YUIwdVNiSlM2bEVrajdlck54VnI1Q2c0WEYwTXZvVVJET0dnZGlUYzlCUDdTbWdCRXM0b2l1SUdMNENNZWpxTnlvTThtaHVZSDJUOXJCcDg?oc=5</t>
+        </is>
+      </c>
+      <c r="F224" t="n">
+        <v>7</v>
+      </c>
+      <c r="G224" s="2" t="n">
+        <v>46021.75</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>Supply_Chain</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>Busy year ahead for FMC amid trio of shipping probes - Lloyd's List</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>Wed, 31 Dec 2025 02:04:38 GMT</t>
+        </is>
+      </c>
+      <c r="E225" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxPUnU4MXRyMVBOUlE5REZFTWJfbTRyNWRiVktNR0Z6dG1zWWMtVlBQUW9HZXBzY2VFZlNvOVo3M2NMenhBdGEtcVZyV3RhcGpqMnlSUUNTQThWRUhBMWFpRTdyOG0xSDhhRURBeElyeFZzRDJTU2tPaWxKNUo3MFYzd1gtc3lqUUF0S2tjeWJoTHNHSVE?oc=5</t>
+        </is>
+      </c>
+      <c r="F225" t="n">
+        <v>7</v>
+      </c>
+      <c r="G225" s="2" t="n">
+        <v>46022.08655092592</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>Supply_Chain</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>US removes sanctions on former Sberbank executive Alexandra Buriko - Reuters</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>Tue, 30 Dec 2025 22:31:21 GMT</t>
+        </is>
+      </c>
+      <c r="E226" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMivgFBVV95cUxQbTMtekpDRUdYN0RjUU5lVWg2QWhfTngxNzRvLVg0eEdOSWdwSnNmVjZDWHlEZmVJOGRlckpkTHFIS05zNGlKTVF1QWlCd19aTy00QWEzQWhWYmtNanRmRmdLQW05TWktQmstRVBhNXZqOFVUU293ZU12eFhiNDZQcFg5d2U4T1hXYTRjWWlUbTM1ZEdqN2dHdmFpWEtQeUpZUFhhZWs1cGlkSUxyVzdNNXBPM2JwOF9CSkhPQ1BR?oc=5</t>
+        </is>
+      </c>
+      <c r="F226" t="n">
+        <v>7</v>
+      </c>
+      <c r="G226" s="2" t="n">
+        <v>46021.9384375</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>Supply_Chain</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>In 2025, global trade cracked as Europe hurt by US tariffs and new China shock - Euronews.com</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>Mon, 29 Dec 2025 13:12:29 GMT</t>
+        </is>
+      </c>
+      <c r="E227" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxOblNIRkJ5ODRUbS1WRk5lTTFGNHo0a0FMUEE2V1FZZ0V1ODVLTXdTbHZmaFdwVEh4emhhRllWRHM4UnFZbEpVN0huNUcxWUo5UllWWFczXzB3Zi02NFE3VUlHcjJDQldwSEhsS09kbHlWWW5naEREUlMyci1oUlpjRjRLVVNqRjM5Tkl5UzBwRDlBR21heU1hUTViNmJlTmJvYkZQMl9FaVpFdzNPRTRmQmxna1pWQ2FUZ3BKTGhWMzA?oc=5</t>
+        </is>
+      </c>
+      <c r="F227" t="n">
+        <v>7</v>
+      </c>
+      <c r="G227" s="2" t="n">
+        <v>46020.55033564815</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>Supply_Chain</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>Kosovo ruling party wins fresh mandate and EU sanctions relief - Financial Times</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>Tue, 30 Dec 2025 12:52:49 GMT</t>
+        </is>
+      </c>
+      <c r="E228" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMicEFVX3lxTE8yMjNfcjlEcXdlc21paVZsaVgtVEs3c3VSRDNid2dRbVNWWmsyTnYyZDUzdzkwbWtMWUNpT3M4VmZyLUc1TlJaV0N5QUM1RUl2U3JGQ2w4LTRrOEVlbjU2NVY4OWhmUHNPTzBIWkkzNko?oc=5</t>
+        </is>
+      </c>
+      <c r="F228" t="n">
+        <v>7</v>
+      </c>
+      <c r="G228" s="2" t="n">
+        <v>46021.53667824074</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>Supply_Chain</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>Delays at Folkestone and Port of Dover to cross English Channel - BBC</t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>Tue, 30 Dec 2025 21:17:58 GMT</t>
+        </is>
+      </c>
+      <c r="E229" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTE95dWJ1OV85dUl2WENaNWEwejhraGI1Nzdyc2dLS2daMVVSR3ZTRUxGV0R6S3VVU05jd0t3WHdRaFROTU0wMnBVRmZ6N0tCNnZWVk0tTi1lZHFwd9IBX0FVX3lxTE1QYWtRYkRWR0FQTGpnY29FS08ybG1xdnljSEEzcDJlMEJLMHNOdTFtRlBWWEhTWXV1NHltNnE0d3BuZy03TEZZaS0zUWQ5clMtVi1sZHEySFVnMFNCRDlB?oc=5</t>
+        </is>
+      </c>
+      <c r="F229" t="n">
+        <v>7</v>
+      </c>
+      <c r="G229" s="2" t="n">
+        <v>46021.88747685185</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>Supply_Chain</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>Influx of cheap Chinese imports could drive down UK inflation, economists say - The Guardian</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>Tue, 30 Dec 2025 02:31:00 GMT</t>
+        </is>
+      </c>
+      <c r="E230" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMilgFBVV95cUxNYV81OGNacG9Ub0QtWXJPVEFGWFRGdF9VMHZwVDhqcGhVNGkxTklaLXVmZXloc2k1bHZvd2FicVBfY0dxMHR1UmMxTkNtV0RkN0MyTzR0blo0eFh0MGh6VXRHOUZHeHNGZHVIQlJITDJNMy1scnlrUVFaVG5mdFhRUF9GMGw5TW9fSlM2Ql85dWlpeVFGT0E?oc=5</t>
+        </is>
+      </c>
+      <c r="F230" t="n">
+        <v>7</v>
+      </c>
+      <c r="G230" s="2" t="n">
+        <v>46021.10486111111</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>Supply_Chain</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>Darren Moore: Port Vale sack manager with club bottom of League One - BBC</t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>Sun, 28 Dec 2025 17:38:42 GMT</t>
+        </is>
+      </c>
+      <c r="E231" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiZ0FVX3lxTE9tWWpHWjRrM2dJdmVvdTVBbVVaakNLbXVobHdWS1JtUnllNlNranF5VUpEVlQycngzYVk2T2tTQTVCUzNfSG5pOE4xdEdUTTJmTW1HaDdLNVpnRUJpLWlTRkhKTGlZMkU?oc=5</t>
+        </is>
+      </c>
+      <c r="F231" t="n">
+        <v>7</v>
+      </c>
+      <c r="G231" s="2" t="n">
+        <v>46019.73520833333</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>Supply_Chain</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>Treasury removes sanctions for three executives tied to spyware maker Intellexa - The Record from Recorded Future News</t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>Tue, 30 Dec 2025 20:41:06 GMT</t>
+        </is>
+      </c>
+      <c r="E232" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMibEFVX3lxTE9uWjNKb09yMlJzVUZMY053VjN6M21IWHhRYU93N1VkczlEODRXSWw3SHNEVEVNVEx3MkJjSm14VlJaS0drV2wzY3NIZW5fRFJBMGZBUDNfTklPYTF3OE1EMnc3WE9hN19LOTA1Sg?oc=5</t>
+        </is>
+      </c>
+      <c r="F232" t="n">
+        <v>7</v>
+      </c>
+      <c r="G232" s="2" t="n">
+        <v>46021.861875</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>Supply_Chain</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>Mouser shipping PSOC Edge ML MCUs - Electronics Weekly</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>Wed, 31 Dec 2025 01:30:50 GMT</t>
+        </is>
+      </c>
+      <c r="E233" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMilAFBVV95cUxNNlVieGxPLV9CbDM0M1lWeXl2ejJvR2VkR0xqbTNNM1FKNFI1TERObVBwQ2VObkZmNUYzUlVkTi1TcnRjNlptSkhCcUJ2a3dseTZUekJYUXNFWTVjLWZPeGQxTmQ0aXRybV9CRXpWQklpRjUyOWc5d3A3cXF4WEZ1VE9xcU5OQmdXbUc3UVNDaVh1UFBs?oc=5</t>
+        </is>
+      </c>
+      <c r="F233" t="n">
+        <v>7</v>
+      </c>
+      <c r="G233" s="2" t="n">
+        <v>46022.0630787037</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>Supply_Chain</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>Watch Tariffs Functioning as a Sort of ‘Deterrent’: Lucier - Bloomberg.com</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>Tue, 30 Dec 2025 22:17:33 GMT</t>
+        </is>
+      </c>
+      <c r="E234" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxPa2lub1JFMmxFM0gwUHpCU01HcklyRVdNU1lWX3JvLUhqM2YwZlVGV29VcVRtcFB3MFEzekxnNndzWFU1dU1ndVZFY1JJVnJ5TmVMZUhCNDhIbjNkNW1pWnE0X3Q4eTQ2MVc1SklacVQ5VG1ha2tHMTBTSVVxb004WDlCOTVweFFDZXl5UFdwVWJNN1JVM3JWdTAwRTE3cmNDZ3A3SnpLVQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F234" t="n">
+        <v>7</v>
+      </c>
+      <c r="G234" s="2" t="n">
+        <v>46021.92885416667</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>Supply_Chain</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>What caused the Audenshaw freight train derailment? - BBC</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>Tue, 30 Dec 2025 06:22:24 GMT</t>
+        </is>
+      </c>
+      <c r="E235" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTFA4MkNCdjEySERqaEl4NmU1eDVhSldTUUl0ZGNXMmJQUF9xcDB3NjZJMEFuYXhQTW0wWEZYMmVjUDJ2QjZpd1FvZTU5OHVla3dGRklyMjBEUmtjQdIBX0FVX3lxTFAwWUlCY0o4c3RhYklKUWJoeWxiTzhSd1IwNE9SOVBoZEpWenhyUUFLdEN6U0ZpSm5SSUh1WGNWcTdxcFlRUjJXZ1lJTzZfQjJiQUhTX0hlWDlLak9Xb2Y4?oc=5</t>
+        </is>
+      </c>
+      <c r="F235" t="n">
+        <v>7</v>
+      </c>
+      <c r="G235" s="2" t="n">
+        <v>46021.26555555555</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>Supply_Chain</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>Bantams 1 Port Vale 0: Match stats and player ratings - Telegraph and Argus</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>Tue, 30 Dec 2025 06:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="E236" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxQU3NMMHZMV09maFlQZkw2Rkd4ZklNY0UzNmZDcDR5ejVpcnBsdGxsLVRPR2c1dm9wcElvMHFZU0hfQUsydW9XdlZjd25nWkhORWF6cUJtTl9RUzZNTXN4S0dZZ0g4bjJCNEs0eHpMdHBTbGlHbXpsSjBrXzNsSlN5cjAyc3RSQUk3Z0dXejhUMGtZTU9xd0VnbGJNU2tfVkd6MkpmaERjZEVsZHVIU0E?oc=5</t>
+        </is>
+      </c>
+      <c r="F236" t="n">
+        <v>7</v>
+      </c>
+      <c r="G236" s="2" t="n">
+        <v>46021.25</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>Supply_Chain</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>Spetses, Zakynthos port projects approved - eKathimerini.com</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>Wed, 31 Dec 2025 01:17:19 GMT</t>
+        </is>
+      </c>
+      <c r="E237" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMijwFBVV95cUxNdnZoekc2TW54OUk1TnRjZXRObzNzd1BYck8wX1JFcGVjZ2JzMHNDX2hiZVFXRWlCY1c4WnFWd0xNY3h1anVpQlpMV3NXYXFnT2ZtSFFYZDdNd2sxandLbThXRk9PX1RtYTBNV3RBQWJRdXM2WHl4ZGEzVWVVT2xUZGJ2STJtY2tSUmItajAzdw?oc=5</t>
+        </is>
+      </c>
+      <c r="F237" t="n">
+        <v>7</v>
+      </c>
+      <c r="G237" s="2" t="n">
+        <v>46022.05369212963</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>Supply_Chain</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>^GSPC Today, December 30: Venezuela Strike Lifts Oil and Shipping Risk - Meyka</t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>Wed, 31 Dec 2025 02:10:08 GMT</t>
+        </is>
+      </c>
+      <c r="E238" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxPVjBBRVhBUThaMmU2Wk9PeHNjWUZ4cnpOMTkyTV9NZldDNHNMZ3Fvamp2dFBQaENUdHJTQWVDNUJJRHQ4SnBvbEt1Uy01MjJoQWRxNHQxeVVaYm5ycmN4WEJJUFBCa19VdVZqUmt4ZlAzN3kzRXlOTng5ZmVEVUc4ejVvd1ZxQTlfV0lMak5vMGhNV1ozUktlUGZENmQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F238" t="n">
+        <v>7</v>
+      </c>
+      <c r="G238" s="2" t="n">
+        <v>46022.09037037037</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>Supply_Chain</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>5 Supply Chain Lessons Learned in 2025 - Inbound Logistics</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>Tue, 30 Dec 2025 19:20:24 GMT</t>
+        </is>
+      </c>
+      <c r="E239" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiiAFBVV95cUxNenRoekJxUk1VSTJ4MzJXTGUwQmhrXzVYVlYwWG9yX2JSNEpURXIzQy1NUlNlR0R0VE5Bbm02Z3JEbzJMY181V1lxLVJDVWw5RnVNdkhfS0tzVm1LQk9lRmdOOHZ0N1FzRk5pNlVOZkR2bXNVQ0g4T3k2WjVDcDJST3FtOURlbnNL?oc=5</t>
+        </is>
+      </c>
+      <c r="F239" t="n">
+        <v>7</v>
+      </c>
+      <c r="G239" s="2" t="n">
+        <v>46021.80583333333</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>Supply_Chain</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>Kellie Finlayson reveals what her AFL star husband is doing now since leaving Port Adelaide - Daily Mail</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>Tue, 30 Dec 2025 08:45:18 GMT</t>
+        </is>
+      </c>
+      <c r="E240" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi3AFBVV95cUxOUXRoWEpiRW9GVEFoRWhrc3V4bk9kMmU5TWJwM3pGeW1tR1NYeEc1ei1fWGozcmh5VGdMeEhrajBmVE9kWVhxdG5iSmU1Skh1cjktbTllNzl3OHk2aENHZ3V3T1JNODY2TUdDTlZ3bVVVcmxlZ2htdm5kLTUzVkh5ZHpwRkdXRkFyMjRNNm5rNWc3Y3ZIVWNSbVpzRngtTC1hN3RnUENxeGYyVU9yMUdQMURTZFdRY1FUREdpdkM2aGdxRDdidXdEZEhOdW95ODk0bjlEb3RjdzZrZnVv0gHiAUFVX3lxTE43Y0RUVnNVWmFFNVJ2OVZOWnBVSTdjTDVzZnUyTVMyUTRNcFlsRHVQMWpQSktyTFlndzZ4NEl3bUl3MGI2bVV5emVtVjFCY3RjcUViY2RlaExPR2dPclAyaGpOam9tLXRnbm5VV2Jkd2xyU25XTDZXbVRMclV0RDR1LUNqZ3h0WUc0UnpzcXlmQlpaejFnbGFjRVl5aXBtemdkRVIxbGRRNWozeE9MRllkaTZMcTNRQWZhU1QzMEFjV0pfcXRMR2xpMjFwcTJUaGlvTi1ZVU5xdXlGT3p1UU43alE?oc=5</t>
+        </is>
+      </c>
+      <c r="F240" t="n">
+        <v>7</v>
+      </c>
+      <c r="G240" s="2" t="n">
+        <v>46021.36479166667</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>Supply_Chain</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>Ship4wd Platform Review: The Simple Truth About Digital Freight Management - BBN Times</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>Tue, 30 Dec 2025 19:23:43 GMT</t>
+        </is>
+      </c>
+      <c r="E241" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxQNnkzU1JrcEQ5X2tHbGtzcEllbGpnR0trNU95WEhzdGNlRU82UXhSYVQ0V3pjSVFyV1BMbjhMMENPT29peThMNkdsT2duTWlLdDhUdzR0VWRYdEI4bzZ5aFdxSEdqbS01d1BPXzJnSEw2THNSWFh0WEJ6d3llcFB6MXZLZVAweTNVclg2NVo4V2pjTlFtUTZCcGJSVXRqcHpSb0hfSjk4OHc0WDFPdXc?oc=5</t>
+        </is>
+      </c>
+      <c r="F241" t="n">
+        <v>7</v>
+      </c>
+      <c r="G241" s="2" t="n">
+        <v>46021.80813657407</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>Supply_Chain</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>Women Pioneering Change in Greece’s Shipping Industry - Maritime Fairtrade</t>
+        </is>
+      </c>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>Wed, 31 Dec 2025 00:13:58 GMT</t>
+        </is>
+      </c>
+      <c r="E242" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiiwFBVV95cUxNc184VE1Jb0NmcWNXaE8wMDZCdmIzX3AxS2dUd3paMUxsSHE2M1dDcjJEeE9fWXhDTllFcGpucXdackdONGYtSUF6SHNDby0xdFJPR3VSd2FJMExsNEY1YXh4SWRESG9PdkpQRkdZZEUtbTZVMTVFQ1pWRW54bW5lWTBDTlgxb2NSNWRZ?oc=5</t>
+        </is>
+      </c>
+      <c r="F242" t="n">
+        <v>7</v>
+      </c>
+      <c r="G242" s="2" t="n">
+        <v>46022.00969907407</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>Supply_Chain</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>Maersk leans into logistics with new North American chief - FreightWaves</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>Tue, 30 Dec 2025 13:02:00 GMT</t>
+        </is>
+      </c>
+      <c r="E243" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMilgFBVV95cUxQRmNqZmYzTEN2dUZXX1dfWmwtdzhlQnZsNTV1QTNVSzF4ellpWHN1SGd3Wm9PU3RyWjQ1djN0VHJaa0ZWb2xYY0o0cjBYTGdXLUN3bUhYNDZ3a1pYYnFXcGpxSC1KcXp5cS1ZUi11V3hmOFVtdjV5N3VQM0xVc1h0VjNtcVlveU54eE8xeDlKSFV6NmNBMnc?oc=5</t>
+        </is>
+      </c>
+      <c r="F243" t="n">
+        <v>7</v>
+      </c>
+      <c r="G243" s="2" t="n">
+        <v>46021.54305555556</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>Supply_Chain</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>Building and Sustaining Laboratory Compliance - Lab Manager</t>
+        </is>
+      </c>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>Tue, 30 Dec 2025 20:45:02 GMT</t>
+        </is>
+      </c>
+      <c r="E244" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMihAFBVV95cUxOVDMyeFlRYjZCNFpEbjF5SWp0VThRSmxPSnpuNFNCQXJVRkdpa2tXRjVFbC1LLXJta2hGamlfNjBtWTNNLXQzeXNUbEpUeC1YM1B2NThBRkRaMG5kZjZIYVVqaGl3Z2JhNGU4VU54VEdORk82U0FIajRZalU3S1NpSUNKWWs?oc=5</t>
+        </is>
+      </c>
+      <c r="F244" t="n">
+        <v>7</v>
+      </c>
+      <c r="G244" s="2" t="n">
+        <v>46021.86460648148</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>Supply_Chain</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>Port Heraklion (Greece) reports moderate growth in cruise traffic for 2025 - CruiseMapper</t>
+        </is>
+      </c>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>Tue, 30 Dec 2025 18:38:00 GMT</t>
+        </is>
+      </c>
+      <c r="E245" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxQUUxUREgySjJmX1RJaXQ5Mjk0MWRFYWhXNEJ0Y0xUY2ItVjUwcnh5dUxFQTNzNkh6SXJpZG5Ia05XQ2JVUlhHM0Z1TFY0a3NURmt2M2plOS1VMUM0UzZSSDN6M05XNl9SYmZNLTZXem9IME1FTTRoSWZNU1F1TWdEWGJ4akxUTjVTQ3VqSl9saWxXNDNDODZObg?oc=5</t>
+        </is>
+      </c>
+      <c r="F245" t="n">
+        <v>7</v>
+      </c>
+      <c r="G245" s="2" t="n">
+        <v>46021.77638888889</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>Supply_Chain</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>India imposes three-year tariff on some steel products to curb cheap imports - Reuters</t>
+        </is>
+      </c>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t>Tue, 30 Dec 2025 18:42:36 GMT</t>
+        </is>
+      </c>
+      <c r="E246" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxPS3NUZ2VsX1VZclZhbE9Temk5dmxNXzZHX3hIWWFiSUM2VWF3cXJKTzJIWElwbEoweUZ2eGZGRllSbjJ3RnJ4OUo3UHhwSUpLTXZ1NmZkZTJoek9rUjhLVUdTZGdEaW96ZkFrY0g2MEU0TlZVS3hFeTRDRG5QRF84SWRvbThKVF9LSmZVeFg3NlYwc2tFRXBWaXRZYm5kd2ZqZ3YtSHhqMmgxZXNPUVczYUhyeG80WjB2VElJ?oc=5</t>
+        </is>
+      </c>
+      <c r="F246" t="n">
+        <v>7</v>
+      </c>
+      <c r="G246" s="2" t="n">
+        <v>46021.77958333334</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>Supply_Chain</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>FirstFT: Private equity firms sell assets to themselves at record rate - Financial Times</t>
+        </is>
+      </c>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>Tue, 30 Dec 2025 10:52:03 GMT</t>
+        </is>
+      </c>
+      <c r="E247" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMicEFVX3lxTE96SUpJWWtpRV9TLTFoNXZoSEw1TkFqQ2p5UGxFcU9KZktMaVFmd3RyM1doU1hMSTBwVWIyVlF4VGRwdy1Xc1YwSEZxVHRsU1d6UW1UbmJhcnhZMXdQalVkdlVOV2ozLVYxR1JRd3FIYjU?oc=5</t>
+        </is>
+      </c>
+      <c r="F247" t="n">
+        <v>7</v>
+      </c>
+      <c r="G247" s="2" t="n">
+        <v>46021.4528125</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>Supply_Chain</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+        </is>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>Ship Recycling Market Ends 2025 Lacking Forward Momentum - Hellenic Shipping News</t>
+        </is>
+      </c>
+      <c r="D248" t="inlineStr">
+        <is>
+          <t>Tue, 30 Dec 2025 22:01:28 GMT</t>
+        </is>
+      </c>
+      <c r="E248" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxNWm9aUW1mN3RWd2x2WEpmcVQ3WXR5TXQ2WHVWUHhlTGJXMGt2SnJsTko0Mzk5bEJVMWpkU2UzNWJCbHFVSkdTd0xCSzdMMEpISk9TZnZjUmpqMmxNUzQybU1uNjZ5ZFc0dkdOMmhnSks4Z29NeXFseFlNMm9MQkxCZmUzNVFmNk1pNUo4emRpeWRIWXJwN0htX1N3?oc=5</t>
+        </is>
+      </c>
+      <c r="F248" t="n">
+        <v>7</v>
+      </c>
+      <c r="G248" s="2" t="n">
+        <v>46021.91768518519</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>Supply_Chain</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>Trump Says U.S. Struck a Port Facility in Venezuela in Escalating Pressure Campaign: What to Know - Time Magazine</t>
+        </is>
+      </c>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>Tue, 30 Dec 2025 17:42:24 GMT</t>
+        </is>
+      </c>
+      <c r="E249" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMic0FVX3lxTE5kOVRUQ1lmNnQyOGIxZjNKVmJ4U2F4ak9JODA2OXoyakszZlN2NWx3U09fdWluMjdSbUswNzUxT0dSbHFoM0xNMmRYQk5BZDBzQ3RUcHRCSVBmNmRTS2J4V3U0bV9rdGtGbWt4b2lkT3BmOEE?oc=5</t>
+        </is>
+      </c>
+      <c r="F249" t="n">
+        <v>7</v>
+      </c>
+      <c r="G249" s="2" t="n">
+        <v>46021.73777777778</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>Supply_Chain</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>Turkey’s KAAN Fighter Moves Forward With US Engines Despite Sanctions - GreekReporter.com</t>
+        </is>
+      </c>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>Tue, 30 Dec 2025 14:47:34 GMT</t>
+        </is>
+      </c>
+      <c r="E250" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMihAFBVV95cUxPbi1YNmJfd2NMRXdwX2VUY2I4ZTZqZ2xsbFNIbWc5OGUtemxsWVU3alBCWnpzdklyQTFOaU9FY1QtY0FoOGFhR0dONkdBdnY5emJXc3dkMGZyZ1Q3a0ZqeUZKMUgwZVRFVmpaX0IzZjdxNXFBZ0otZ2dPeGh2anlwOWlTUnQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F250" t="n">
+        <v>7</v>
+      </c>
+      <c r="G250" s="2" t="n">
+        <v>46021.61636574074</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>Protest</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally)</t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>Miners clash with police in Bolivia as protests over fuel subsidies enter second week - ABC News</t>
+        </is>
+      </c>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>Tue, 30 Dec 2025 23:29:47 GMT</t>
+        </is>
+      </c>
+      <c r="E251" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxNQUJOdlY5M1pZdFZpc2duMnNLQU9BQ29pQUNtWk5YbEpKMjl6RUxtMnRLSGFtS1hmaFR2M29wTjV6UVFZb1dMSV9LUzV6eWV4cHBYdE5ucGd5Ujh6NXBuTXJlanhXODVsaTdna2tMbzRXY05IQVhKVDREN1ZkWUYtcG9aU21jSDFtWnFqUWc1UmNTQm8zM2s1dEppWnFNNEtoVTM2RnVJRE9WdTg0NmFYQ0lqNE_SAboBQVVfeXFMUGgxdlRUWTROcDFsMkI2UmtRTU9CcjRkYTE4S0dlRWMwUEp2YkV6cjRZbWQ0cHhXVTNRQlBPS2Z5MjVmdTVyZEp0RlJqT0ZWVnRVS1BXRjdaTmVVMmJiQmRRaVdfSTNObWVUOG1mZl9lVUt3bU9lRC1kbTlxZUhCRmJhaDVGa3FSMFpUeS0yRDhCZGV6cHVnYnMxR1V1OHNyMkRMQ0hjb2Q4azk2a0VsVUkxcDdnSURLMVdR?oc=5</t>
+        </is>
+      </c>
+      <c r="F251" t="n">
+        <v>7</v>
+      </c>
+      <c r="G251" s="2" t="n">
+        <v>46021.9790162037</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>Protest</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally)</t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>Iran In 'New Phase Of Turmoil’ As Protests Spread Beyond Capital - Radio Free Europe/Radio Liberty</t>
+        </is>
+      </c>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t>Tue, 30 Dec 2025 11:14:18 GMT</t>
+        </is>
+      </c>
+      <c r="E252" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiiwFBVV95cUxQQmF5bWwyYzFYbFh5QXZ2UzQtaVhDOGVCcjNFQ19EbUhpZFlRdkRSQUVIQTRYWmZ5MlZtVU1yWDVWN2pCM0V6V1FLQnNINmQ3cmZEX0xCRzdGVXF1S0ZfNVpBckNpS3BGSk03dy1fT1JaM05hRmpBSmZiU3FsbmlmYUlEdXY1QlBmZ0Rr0gGOAUFVX3lxTFAwYndLQmhYNXNzVGM1b001TFNjOVRhR2hSRmgxOEtKVEVOQmQ2ZGJrYWFlVk1UamNQRnhyZldhcWc0NzRkM0o5bXVwdE1vYWgyaFFPZ0hGcHp5eGJ6Z0QwQjZ6TFNtOUo5Vk15cnBMbmV5a0l5Z1J1WDBOdXM3bEI3c3BrZmx6Vm9CaW51ZEE?oc=5</t>
+        </is>
+      </c>
+      <c r="F252" t="n">
+        <v>7</v>
+      </c>
+      <c r="G252" s="2" t="n">
+        <v>46021.46826388889</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>Protest</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally)</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>Police chiefs reflect on ‘worrying’ unrest linked to anti-asylum protests - Press and Journal</t>
+        </is>
+      </c>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t>Tue, 30 Dec 2025 06:00:42 GMT</t>
+        </is>
+      </c>
+      <c r="E253" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxNWExtTUotaXMtdkhxaDgwTGtkaE4xZy1MNWJGSVFCNDRibzU0NWFvS3JEaWpQZ1VRaFlxNnBxZG9UTWR0bTBOamozbjJYMTJST3RockgwZFpZRFZuRlhqUHdTWDRUR1JNQUxURXNGdHVqZjhlT1VXYnFVS3YyTkhOaHhUMjhkYVNTb1F0M0dCZDZQSmJnaWVMZE5zYmlLRm0tSUwyeml0ZTVXcEo0aUdtWXlDWjU?oc=5</t>
+        </is>
+      </c>
+      <c r="F253" t="n">
+        <v>7</v>
+      </c>
+      <c r="G253" s="2" t="n">
+        <v>46021.25048611111</v>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>Protest</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally)</t>
+        </is>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>Thieves strike cars in the early hours of the morning as police appeal for witnesses - portsmouth.co.uk</t>
+        </is>
+      </c>
+      <c r="D254" t="inlineStr">
+        <is>
+          <t>Mon, 29 Dec 2025 15:31:00 GMT</t>
+        </is>
+      </c>
+      <c r="E254" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxPN08yYmJjSWw5dGxxZW5uSW9oN3JwSTZwSEhiOVlVQlRYSjVwWE1wQURSdjdmZ0NCbFdRWE12ZlF5WHo0VXZqRXVjT1hVUF9Eblh4a20zR2ZTTVRaX01MRVBLSW0tNE5Rd2dNM292WV9xM1dvSmRnb3Y0Mm1adUVLODdwdW5vSGZtOVE4aVU5ZklpLUNrVWl3VXV0NEU4QTByRjgxT0ROY1hXWG5ocmNFamVFVXRORHROYTh6UjNPOHY4WWZNN0pEUTFmUQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F254" t="n">
+        <v>7</v>
+      </c>
+      <c r="G254" s="2" t="n">
+        <v>46020.64652777778</v>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>Protest</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally)</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>Derry Journal Review Of The Year 2025: March - HMO concerns and police chief details priorities - Derry Journal</t>
+        </is>
+      </c>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>Tue, 30 Dec 2025 00:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="E255" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi2AFBVV95cUxOcmJ1ZENiVkdPQXBDN0NOQ0RSYURDMzZ2cHZ3czUya0p5ZEJFVS1LTGlLcmNjVk1EYnFKTmg5UHlpYkY2b1ZFYjVEOUcwQ3l3NDMwMmRzMU1Sc1B4dDgtaUw5Vjd6UFBsSXN3T1U3emVwWHl2ME5KY1dvbnNhZWxOZHZKYUs3cU1TZEp4bU1ma1ZaVzBEZ2lDZ0p2SENyMVVHOTNhVy1OMWg4dU0wYVUyN3A5REZwWnlxLThwOG45dEIzNGZKVi1KU01TaWV3RHRTdHFadC1IREM?oc=5</t>
+        </is>
+      </c>
+      <c r="F255" t="n">
+        <v>7</v>
+      </c>
+      <c r="G255" s="2" t="n">
+        <v>46021</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>Protest</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally)</t>
+        </is>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>Tehran Bazaar Uprising Continues for Second Day, Spreading Across the Capital - National Council of Resistance of Iran - NCRI</t>
+        </is>
+      </c>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t>Mon, 29 Dec 2025 16:30:16 GMT</t>
+        </is>
+      </c>
+      <c r="E256" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi3AFBVV95cUxNR0JvTzdCOVV1ZmlyM3k5VUU4OTlfM3paNmxpS3ZSdzVMbEVpcHVidzU2OWRVS2plZnpadlNNUU92ODEtRG1ySmNWOEE5bGFyNlFRM3BXQi1RQTIxODdEQ1JUejZIbS1pM0JXRjJSUkZzd1NXUk9Ub3RyWVV4am5IcGg2VnlzWlBsdmkyYWFuSEU2dFdpZUZ1OWsxVTBZTXVrcWJrWEhacjJRMjhOLXNTRG5sMkxJOXF0QkdfMVBFUlRiTWpEUmRWSjIzS2RacFdjbllmSVpIVkJSalVj?oc=5</t>
+        </is>
+      </c>
+      <c r="F256" t="n">
+        <v>7</v>
+      </c>
+      <c r="G256" s="2" t="n">
+        <v>46020.68768518518</v>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>Protest</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally)</t>
+        </is>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>Protests and police present at Boxing Day hunt - South Wales Argus</t>
+        </is>
+      </c>
+      <c r="D257" t="inlineStr">
+        <is>
+          <t>Fri, 26 Dec 2025 16:35:00 GMT</t>
+        </is>
+      </c>
+      <c r="E257" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxPOS12a2gtQU1aeUZ0bWpJRUc1NzBILU1jM1lqYTlJUEJlOER5N3huNUU4bF9xZzlKdDB0ZmNraWFXb0lrTEhmUlZsWTFBREx5YTNqTk9ld3Blbk1nM3huekVBUnZ3aFY4MndRMVdCWkpGMGJSZnhxSjZ6NjBYWFNMZ3FDYmJWMHQycU0tS3oxaXhxQ0p0RW1B?oc=5</t>
+        </is>
+      </c>
+      <c r="F257" t="n">
+        <v>7</v>
+      </c>
+      <c r="G257" s="2" t="n">
+        <v>46017.69097222222</v>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>Protest</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally)</t>
+        </is>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>After an anti-Muslim protest, Austin police are changing how they handle hateful demonstrations - KUT</t>
+        </is>
+      </c>
+      <c r="D258" t="inlineStr">
+        <is>
+          <t>Tue, 30 Dec 2025 19:47:55 GMT</t>
+        </is>
+      </c>
+      <c r="E258" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxOemhLV2lUREJUeGUxT0llTGM5LXd5ejBROTdaWll6ZFBubDZFM3dTc3lMeFNUenlRaGVscEtJOEg0WjNYX2dFRVMteEhDUGhOTlJxaV9JYUUyU3JDc2dWSi1Cd3AteUZBMjBYbkZ3ZDRoMm1aTjhmMUtpNFN1cTBvOVRSbThmVmVSQU05ejBqRkZwd056SnZpdENuZ0VmUQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F258" t="n">
+        <v>7</v>
+      </c>
+      <c r="G258" s="2" t="n">
+        <v>46021.82494212963</v>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>Protest</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally)</t>
+        </is>
+      </c>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t>Russia strikes Kyiv, Ukraine, kills at least 1 person day before presidents Volodymyr Zelenskyy, Donald Trump meet in Florida - ABC7 Los Angeles</t>
+        </is>
+      </c>
+      <c r="D259" t="inlineStr">
+        <is>
+          <t>Sat, 27 Dec 2025 23:29:04 GMT</t>
+        </is>
+      </c>
+      <c r="E259" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi4gFBVV95cUxPR1lTcVJKaE5qSy1VYWQ3NmtSNGR6bzdTYk5WVENjcWVJeS1VaEdHU1dWclJkSHhsdU5vSzBxNUFfMkllUHFDSGh0dld1c3ctNTlBcEZJcF85QVVOZGNjSVd6T1BhbzNvbnlIR0xvcWN0SEdJRlhSX2FqTldhLTdHZzAyYTdfREI5OGI2TFpUUmJ6SXZDdkJVQkprejRxLWlsNXFnemQyTW9jVWJCRW5pb3N1X3lTRkRwZ21zdS1OTlNGZ2ZwYzEwQ01CYTZ6Rk5uRFJXOVA5R2l0YktQQVpWQnZB0gHnAUFVX3lxTE9JTzJuMXRJZ1FpSUt3NmNGQi1JQmxBX01VV2szTWFmcjZwa2o3eG1fcTAxUGJHb0UyODVVU1V3ZkV0RkpJQlltMHpReUx1eUZWNTl3bVJsYmRQbDJkQ3B5SFM2N2s1Smt3T0NwM1JmV1ViU3FxWk50X05FUkFIZWgyYzFnYWJGSjJBdVprTlZETE1zaGdFZDA4M3F3WFdJeXFDLV9BU1lyX3NZS2hodExfWU5teEh4Y2VTVWU5VFcydmh4MHRHMXFYMUsybG52U0ZlVmRjZTVnRGl3emVweEdFdEE0Rzcydw?oc=5</t>
+        </is>
+      </c>
+      <c r="F259" t="n">
+        <v>7</v>
+      </c>
+      <c r="G259" s="2" t="n">
+        <v>46018.97851851852</v>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>Protest</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally)</t>
+        </is>
+      </c>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t>A priest, protests &amp; police: Why parishioners at a Parma church want answers from their Bishop - News 5 Cleveland WEWS</t>
+        </is>
+      </c>
+      <c r="D260" t="inlineStr">
+        <is>
+          <t>Tue, 30 Dec 2025 23:53:07 GMT</t>
+        </is>
+      </c>
+      <c r="E260" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi0wFBVV95cUxObFh2bFZUdm1NRUx6d2hCazdXTUxNQVF1ZDRiZ2JKbmRPZFJGV3V4amVSdWYzR1FwMzZRZmtnOGY1ZFVha0F3dHJXTkF4Z0gwZGh0aUJwLVI0dGtsbkxlNl9Wc2VfU3J3bXRROXBPRFl4N19uWGVORy12U1pkc3V5elJoU0NQVzdGMWE3X0FJRWUxeXlMVVI2SlpLVkFvdG5ZMXhGeC1rNk5GV0dlSEZEaHhXMTdmLTE1b2F1a3VrYTM1QXBTeEZKWWdwTWhRN0Z1blFr?oc=5</t>
+        </is>
+      </c>
+      <c r="F260" t="n">
+        <v>7</v>
+      </c>
+      <c r="G260" s="2" t="n">
+        <v>46021.99521990741</v>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+        </is>
+      </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>Property experts foresee more AI growth in 2026 - Estate Agent Today</t>
+        </is>
+      </c>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t>Wed, 31 Dec 2025 00:06:39 GMT</t>
+        </is>
+      </c>
+      <c r="E261" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxQTDhqRVRqRVRnMElsMHBiWk0wTXZodGpreUVUYTBXQk83bmZpa3JBWDFSeHZkMHpReFRVRzJNTThtVWlpVkZNemFWWW5NeDVQWE1MSWwyUHF1cHR4bWQtWGFfM01UbVRHc0poM0dybXhJSTRkdXBKU1FNOVZnZnd6dFNoaFB0X3F6Z0ZMNDJvcFRrLXpGalFxVzNTcmttT1J5YlN5Sjc3aEk?oc=5</t>
+        </is>
+      </c>
+      <c r="F261" t="n">
+        <v>7</v>
+      </c>
+      <c r="G261" s="2" t="n">
+        <v>46022.00461805556</v>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+        </is>
+      </c>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t>Tech wave for power firms amid the AI revolution: ALEX BRUMMER - This is Money</t>
+        </is>
+      </c>
+      <c r="D262" t="inlineStr">
+        <is>
+          <t>Tue, 30 Dec 2025 22:01:05 GMT</t>
+        </is>
+      </c>
+      <c r="E262" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi8wFBVV95cUxPOWV2U2NQT2tROGdmcTl2amsyWVVPNGE5UUZuTU51R19QRnR4cHVRODRZdVNDTkhKSzA5cEVKSWFEMzQydHFxV213U0V0OThfVzljUld4Z0U0T0pKNHJTNW1ZS0tHbjhVRjBOUUg3U1M5V3M4bkxvSm5qWmFwSll1OW9DSDAzNFJUMENKOEh2a0p5SENVU25FczF4Z2NrNDFTSU1vS2pLc0paUzRjT0wwanBEWkhORXlhZjZ6cHN5MlhJVlF1SXFLdEhzR0hEQmVNTFBDQTNhSGtsX1hYXzhXWEZMU0FkMzItRTN3ZE5QQmNidFk?oc=5</t>
+        </is>
+      </c>
+      <c r="F262" t="n">
+        <v>7</v>
+      </c>
+      <c r="G262" s="2" t="n">
+        <v>46021.91741898148</v>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+        </is>
+      </c>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t>Exclusive | Meta Buys AI Startup Manus for More Than $2 Billion - The Wall Street Journal</t>
+        </is>
+      </c>
+      <c r="D263" t="inlineStr">
+        <is>
+          <t>Tue, 30 Dec 2025 16:18:00 GMT</t>
+        </is>
+      </c>
+      <c r="E263" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMioANBVV95cUxNb05GVHl3aEtkVXEybnFGOFBnd2tlS1IxeTJqczFLTW42bXplT1MxbWZZa3NwZ245RGdmNENNWEFMOHNzaVBWbjJ2NUhXa0R0Y1BoVzVpbnJTTlpMNUEzaTU4czJOekxYQnoweUUxVHJZR0tNcTc5NmhSTERGWC1JSk9wTzhhRl95VlRlZFhWek03RGE5WGRBNU5VaEc0U0VDaW9rUlNEOFRaOXlMR2lwOWw0TE51aWZpejlBNnRkbEY0dXN4R1VqSU1wWnFPekR1VnhTdXIzWjN3NVNHLTl2clZJU0JlRzlsbXJ1cy1YVGZSQlpRWkw0Rml3REk0RkZ0amR1aFlhYko4V1FIUGsybHBSNFFUdjNNejVJUTAxYktSWEtndUFlSThGYzBzckxaWDFBbndGSHloRzZEbzRsQW04XzlNM1BEdDdicmlYLXBxQm1PRnc3ekl6XzVPSU95a1Itd2taVHJMNG9QbUllX1EyQ2VvWmVSNTJranRLakJWNzFNT2FEZjFEX0UwUlB5NGdySzU1R08xZ0lGY2xtbA?oc=5</t>
+        </is>
+      </c>
+      <c r="F263" t="n">
+        <v>7</v>
+      </c>
+      <c r="G263" s="2" t="n">
+        <v>46021.67916666667</v>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+        </is>
+      </c>
+      <c r="C264" t="inlineStr">
+        <is>
+          <t>PwC: AI, cloud and next-generation networks redefine the Middle East’s TMT future - Computer Weekly</t>
+        </is>
+      </c>
+      <c r="D264" t="inlineStr">
+        <is>
+          <t>Tue, 30 Dec 2025 11:18:26 GMT</t>
+        </is>
+      </c>
+      <c r="E264" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxPcm5nb1htWS1QQ1Y4NE1GUVJ2dW5pZnNTY3FUalpkQ21Selk2VFFXekpPN2l1RmZhZ3dIZkIwbkd2Q3BpM2c0bmRhbE1MV1Jrcmw4NUp6a2RlRkVPeWhLdzQzZ0otTUcwaXpOWlRkUFhfbC05Z3YzQ3RqaWNzVEVtSlU0V0tjcVU4bWVCeThZaXdTdWxLRVdsS1BFS0E0amp5QVJHd05yTk50YnQ4WU5RS2pmSEdfQU9EQ2UwVm1wcWEwUQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F264" t="n">
+        <v>7</v>
+      </c>
+      <c r="G264" s="2" t="n">
+        <v>46021.47113425926</v>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+        </is>
+      </c>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t>Enhancing HR and Employee Experience with Technology and AI: The UAE’s Digital Momentum - Lockton</t>
+        </is>
+      </c>
+      <c r="D265" t="inlineStr">
+        <is>
+          <t>Tue, 30 Dec 2025 09:19:57 GMT</t>
+        </is>
+      </c>
+      <c r="E265" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxPNTMyV1RaWnJrX3J1MEE4UjZhZ0xUXzJ4WDB1aGFTX1BlRlNLLXBKOVVSR2xKVExEZkVUQVpGazl6R0lKOGloZ0JEMWZLeVBWRFk1dm8xZkpXSF9QUjRlLTVzeFdZeFpxRnJNMnFZeGk4YTktV19pZHZkdlZQMlBCZ0xmTG5fcHVHSERVMmNHZzNNd3BwTjBwaFNzUjR6Y1BNZWczX013dy1XN0pvb0RpVlF5Nm43S1htLUFxNUt1VTZjMDA?oc=5</t>
+        </is>
+      </c>
+      <c r="F265" t="n">
+        <v>7</v>
+      </c>
+      <c r="G265" s="2" t="n">
+        <v>46021.38885416667</v>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+        </is>
+      </c>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t>Samsung Welcomes Galaxy A17 5G and Galaxy Tab A11+ to the Galaxy Ecosystem - samsung.com</t>
+        </is>
+      </c>
+      <c r="D266" t="inlineStr">
+        <is>
+          <t>Tue, 30 Dec 2025 13:04:27 GMT</t>
+        </is>
+      </c>
+      <c r="E266" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMilgFBVV95cUxPSDNnT2dpQ3psQnYxZC13ekhDVWxpNnFMUV9TcUlWQ0JzbjRsWTlZZ2ZrODZaVzJkZHRuYkl5a2ExM19nWTkxSl94NmdmZU5DLVJpYnJ6emhhQm5FTFNsWFFMeFAxSnI4SzlsMlNCR2ROU0J4ZXducGNBWFRZenBOaWFZRW16cjVVVGhwVUpXNWRJZFNRNmc?oc=5</t>
+        </is>
+      </c>
+      <c r="F266" t="n">
+        <v>7</v>
+      </c>
+      <c r="G266" s="2" t="n">
+        <v>46021.54475694444</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+        </is>
+      </c>
+      <c r="C267" t="inlineStr">
+        <is>
+          <t>TCL Unveils Note A1 NXTPAPER: AI-Powered E-Note with Paper-Like Display and Smart Productivity Tools - PR Newswire UK</t>
+        </is>
+      </c>
+      <c r="D267" t="inlineStr">
+        <is>
+          <t>Tue, 30 Dec 2025 16:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="E267" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi7gFBVV95cUxQS0VpT3FaMENlRVZwTE5VYmR4MVhCc2ZFSE5JSW9SSnowSFVldk1XUS04ZnRaa09GM2VqWkhsUWhhbkd0R2c3S09KQkpLTTZTVU1fczk5eVhfbzBOYmRuUXg1OURHWXZob1BfYTk2Q0txb3FycEtKZDZtUm94S0ZZTFRaS19WVmtaRmJsN0FWOEJIa25tVk9kcWYzdHhZcFpLUW5iNUthZWRhcXhWbHR6TG0tb3IxTnh1VXRBa1ZBR01RbjdUTG9QVTJ2Rl83dF9LTFZBbG9mVXEydzFHbml6cWZ4WElKdEhxYVZxQmRR?oc=5</t>
+        </is>
+      </c>
+      <c r="F267" t="n">
+        <v>7</v>
+      </c>
+      <c r="G267" s="2" t="n">
+        <v>46021.66666666666</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+        </is>
+      </c>
+      <c r="C268" t="inlineStr">
+        <is>
+          <t>Copilot Studio Feature Enables Silent AI Backdoors - eSecurity Planet</t>
+        </is>
+      </c>
+      <c r="D268" t="inlineStr">
+        <is>
+          <t>Tue, 30 Dec 2025 18:59:09 GMT</t>
+        </is>
+      </c>
+      <c r="E268" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxOY3liZUZDakQ4WWtPdW5oTzlhZ0VQNWJ6WnFUMGV4MDIxa1pLSGt1ZFkyNUl3a2xsME1zV1VCV282d2ZRRjNrUmo4WWxoUlRGOVpZT0lhRjBVZnZrODAwdUNwbTY0ZTU0Rm1QZHJKZWNuR205Smk4Q3JDNXpYa0xkTERUNkxxakJJSlpzMVBYdTB4U2Y5YkV0ZjFrZjR3bWlRNHZhOWtFYkJDRUE?oc=5</t>
+        </is>
+      </c>
+      <c r="F268" t="n">
+        <v>7</v>
+      </c>
+      <c r="G268" s="2" t="n">
+        <v>46021.79107638889</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+        </is>
+      </c>
+      <c r="C269" t="inlineStr">
+        <is>
+          <t>Faster treatments and support for health workers as AI tackles A&amp;E bottlenecks - GOV.UK</t>
+        </is>
+      </c>
+      <c r="D269" t="inlineStr">
+        <is>
+          <t>Sun, 28 Dec 2025 22:33:35 GMT</t>
+        </is>
+      </c>
+      <c r="E269" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxNVjZpTm5rUUY2akVubEFCODJvdHRqN3R4OVF1LVQtMnI0Z3pyam50cXZmN3lXdS0xbEp2cUtnM2VHdmdMRHRHMG5VQ1FnWjEwdkZNWG1CY1hsUTVtd0RDaE1nTlFuM0cya2I0blJuOUl2SVAwQWttX0ROa2FUNnE0ZXJDcDdJODFaSU9meGpseFdxaGlvQkt0RlZEQUliZDl4UVlLS2RMRVA1NC1DV2Y0OXhn?oc=5</t>
+        </is>
+      </c>
+      <c r="F269" t="n">
+        <v>7</v>
+      </c>
+      <c r="G269" s="2" t="n">
+        <v>46019.93998842593</v>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+        </is>
+      </c>
+      <c r="C270" t="inlineStr">
+        <is>
+          <t>2026 Legal Forecast on AI and Regulations - JD Supra</t>
+        </is>
+      </c>
+      <c r="D270" t="inlineStr">
+        <is>
+          <t>Tue, 30 Dec 2025 16:59:41 GMT</t>
+        </is>
+      </c>
+      <c r="E270" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiiAFBVV95cUxNRFhTY2lSdW1tUHRmekg2alFWdFBwbUIwUmZpbDVpeWlxbnBGZlpIajZ1cHdrZGNEMHpyMmt2R19CVzlsMXZTTDcwLXByWVdqZ0JlMmNNVHEtaGtkTk91MUpBM1A1MkxGMzhqWi0zSnFKcmVPaFNQYnVpYzZtX3pnUXBfUFh2bWxx?oc=5</t>
+        </is>
+      </c>
+      <c r="F270" t="n">
+        <v>7</v>
+      </c>
+      <c r="G270" s="2" t="n">
+        <v>46021.70811342593</v>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+        </is>
+      </c>
+      <c r="C271" t="inlineStr">
+        <is>
+          <t>Leveraging insights from neuroscience to build adaptive artificial intelligence - Nature</t>
+        </is>
+      </c>
+      <c r="D271" t="inlineStr">
+        <is>
+          <t>Tue, 30 Dec 2025 10:39:51 GMT</t>
+        </is>
+      </c>
+      <c r="E271" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiX0FVX3lxTFBpZGhzNEhpRUlBZTlldTJvcUVSOTZMRWY2bV9SZHh1bEhiRkEzV1pLVUNTRUJYbGJSb2l2RDJzeHh2cF9mcll2XzVheUpRN1VhS0xSNFAyMnNMelRhVXJV?oc=5</t>
+        </is>
+      </c>
+      <c r="F271" t="n">
+        <v>7</v>
+      </c>
+      <c r="G271" s="2" t="n">
+        <v>46021.44434027778</v>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+        </is>
+      </c>
+      <c r="C272" t="inlineStr">
+        <is>
+          <t>Could AI relationships actually be good for us? - The Guardian</t>
+        </is>
+      </c>
+      <c r="D272" t="inlineStr">
+        <is>
+          <t>Sun, 28 Dec 2025 18:34:00 GMT</t>
+        </is>
+      </c>
+      <c r="E272" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxPRGpOU0E0VGFYQ083RVphZ1dldV9HYndDMFZiTGJnalNTS0F1dVotVFJjakdvaWg1bzVBMy1BWmdPUXNXanpJZkx0OEZfQjV6V0FaRXZSSEl0MFk4eVgtUmRxSGxSM205UjBsQVlmT0p1TDl1a3c4a3drYm11c0NYVDI3OXpJbnZuY3FUZGpMQnE3d2ozcE84?oc=5</t>
+        </is>
+      </c>
+      <c r="F272" t="n">
+        <v>7</v>
+      </c>
+      <c r="G272" s="2" t="n">
+        <v>46019.77361111111</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+        </is>
+      </c>
+      <c r="C273" t="inlineStr">
+        <is>
+          <t>AI gains ground across the footwear industry - World Footwear</t>
+        </is>
+      </c>
+      <c r="D273" t="inlineStr">
+        <is>
+          <t>Tue, 30 Dec 2025 15:12:13 GMT</t>
+        </is>
+      </c>
+      <c r="E273" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMilAFBVV95cUxNM3QwVldVSTFiQnpKZk1yWDI0Q0VJT0JRUUpHaU9COXg3SENzbXBzd0tuQ0otc3JUT2NXQXdhSmtJT0Z4N0VkcG94eTZOOGxwN202OVduS2hxWnNIYjByS0hEWXNGMzRobzVKcVBaeXhScWpYZjlnTkJ0YlFGTWNBeUhENHplcUR1N2JDZzRydVdCRFNZ?oc=5</t>
+        </is>
+      </c>
+      <c r="F273" t="n">
+        <v>7</v>
+      </c>
+      <c r="G273" s="2" t="n">
+        <v>46021.63348379629</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+        </is>
+      </c>
+      <c r="C274" t="inlineStr">
+        <is>
+          <t>Salute &amp; MCIM: Cutting Liquid Cooling Risk In AI DCs - AI Magazine</t>
+        </is>
+      </c>
+      <c r="D274" t="inlineStr">
+        <is>
+          <t>Tue, 30 Dec 2025 08:35:42 GMT</t>
+        </is>
+      </c>
+      <c r="E274" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMikgFBVV95cUxORFF1cHM1TS1nWEh6OVZUdzdKVFB4cnV3cl95S3FMRkJ5WG1KTlJfUlFObC1TblF2NXJYdEd4Q05aYmNhVnFRSkd1VnJ4X1dIVE9va045cUpqX1Jyc0tEM25TQmFkaDdCZ1Z6SGRfMksyNWdmaWtvdFU4ejVEVEhlVmhMQmZqc1lNRjlpNlpRTm1Fdw?oc=5</t>
+        </is>
+      </c>
+      <c r="F274" t="n">
+        <v>7</v>
+      </c>
+      <c r="G274" s="2" t="n">
+        <v>46021.358125</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+        </is>
+      </c>
+      <c r="C275" t="inlineStr">
+        <is>
+          <t>Europe’s MDs’ Top 2025 Reads: Burnout, AI, and…Sperm? - Medscape</t>
+        </is>
+      </c>
+      <c r="D275" t="inlineStr">
+        <is>
+          <t>Mon, 29 Dec 2025 12:05:51 GMT</t>
+        </is>
+      </c>
+      <c r="E275" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxOLV9rMjJyNndSZ3AwcFl0TEpZSFl3NVQzQXN3MjB4N2xXSDA1UlY1RnNqelZ0YWYwUDBZUWd1dHBrejZ6VFVvcHpvM0RKWGRWZDFLRFZHbXBXUFFkWWN5T181SW5TVEFXdThNcjIzVXB0S3V6cGlxSWFJemItVnpBanA3b0p2TjZmRUtweV82YzhLX2NITHhid3o4QWNCUQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F275" t="n">
+        <v>7</v>
+      </c>
+      <c r="G275" s="2" t="n">
+        <v>46020.5040625</v>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+        </is>
+      </c>
+      <c r="C276" t="inlineStr">
+        <is>
+          <t>Octopus Energy to spin out AI utility platform Kraken at €7.3B valuation after €850M funding round - BeBeez International</t>
+        </is>
+      </c>
+      <c r="D276" t="inlineStr">
+        <is>
+          <t>Tue, 30 Dec 2025 12:27:21 GMT</t>
+        </is>
+      </c>
+      <c r="E276" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMixwFBVV95cUxONXhFeGFWUlphQ1hrV3VFWWo2SEpDb3IwNm12TUhaYnZuYkNac2ZmWUZ2RjlzWFBXc29KN1FsZjJIeGRiUml0QmIzM1NYYjM5d0N3akpsWnNFSlRFTTZSMmVEZUVKQjE3dWRQVFNNVmc5VUlOdjFLTmFNaXpZUHVkSGFfNWRnZUpiZkkyVC1sT19MdzlhLU1ZNFVKekJkQUl4Yld6RllhMW93cHUwSkktbmZ6djdSSFBBN3JUQjREMmgzWGFHV0Uw?oc=5</t>
+        </is>
+      </c>
+      <c r="F276" t="n">
+        <v>7</v>
+      </c>
+      <c r="G276" s="2" t="n">
+        <v>46021.51899305556</v>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+        </is>
+      </c>
+      <c r="C277" t="inlineStr">
+        <is>
+          <t>Framework Advances Steerability Analysis Using Machine Learning and Batch Sampling of Measurements - Quantum Zeitgeist</t>
+        </is>
+      </c>
+      <c r="D277" t="inlineStr">
+        <is>
+          <t>Wed, 31 Dec 2025 00:01:44 GMT</t>
+        </is>
+      </c>
+      <c r="E277" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxOOU1QdG96NXMyNktwcVI5Um53a2tuUkJSaER2TFNDOF9TRmZDcDBCRE16YTRmd2ZlM1BUeGh5ZUlKbHoxaTZyVjktUS1kZUV6NFhNenRCdHJqZ3NYRWlnVURRbGV1b1VZRjlGbXBqeDFVM1NpVjJzVWZPWVRjdFp0OHlBZkNtVF9IV29kOEtBUnV0cWtHTjZnUmE1UE41akhCakNCSEItMkpONmVqbmlQVmtSRE4yZw?oc=5</t>
+        </is>
+      </c>
+      <c r="F277" t="n">
+        <v>7</v>
+      </c>
+      <c r="G277" s="2" t="n">
+        <v>46022.0012037037</v>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+        </is>
+      </c>
+      <c r="C278" t="inlineStr">
+        <is>
+          <t>Great Britain's Olympic and Paralympic teams need to harness AI for success - BBC</t>
+        </is>
+      </c>
+      <c r="D278" t="inlineStr">
+        <is>
+          <t>Tue, 30 Dec 2025 10:38:14 GMT</t>
+        </is>
+      </c>
+      <c r="E278" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiZ0FVX3lxTFBhempNLV9kWGdBN2RFWTFkOTlJbUx4STRBN1FNSjhqSkg3eEttcVp4UVJieDNiZnF6YUZmMjhFVlVNdEo5TnFzWWZEVkZZTTNEbHUzWjZwT0FkdWhNTnh2bkYwd3pFdUE?oc=5</t>
+        </is>
+      </c>
+      <c r="F278" t="n">
+        <v>7</v>
+      </c>
+      <c r="G278" s="2" t="n">
+        <v>46021.44321759259</v>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+        </is>
+      </c>
+      <c r="C279" t="inlineStr">
+        <is>
+          <t>Measuring context sensitivity in artificial intelligence content moderation - Nature</t>
+        </is>
+      </c>
+      <c r="D279" t="inlineStr">
+        <is>
+          <t>Tue, 30 Dec 2025 11:17:52 GMT</t>
+        </is>
+      </c>
+      <c r="E279" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiX0FVX3lxTE9EX21GbDJyamc2Zlp6bkxldnB4OExrSTVyM1kwY0JTcUVDSElDMU1RS0NoS0hObFo4RmJfdXJZZjI5bnJFZUNuOFBHeFhtbENaYkFPQ0JMTEh5Y1BCalNB?oc=5</t>
+        </is>
+      </c>
+      <c r="F279" t="n">
+        <v>7</v>
+      </c>
+      <c r="G279" s="2" t="n">
+        <v>46021.47074074074</v>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+        </is>
+      </c>
+      <c r="C280" t="inlineStr">
+        <is>
+          <t>Artificial intelligence: China plans rules to protect children and tackle suicide risks - BBC</t>
+        </is>
+      </c>
+      <c r="D280" t="inlineStr">
+        <is>
+          <t>Tue, 30 Dec 2025 02:32:33 GMT</t>
+        </is>
+      </c>
+      <c r="E280" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTE95QlZPcUlqRk9LdjdtajFLOUVfdVozZ296YmFnb18wTGhnTDZZMGp0MlEySEVEaFJRSmpBX0lNVTNuZXpfZFdEQTgwczhsejJRNEE4ZFUxSE5IUdIBX0FVX3lxTE5aUDVpOHN3SjVnSEhoakhFTEJTS3BzeEt6bkVZbHZRdlBGMnV5OHdSTnZHSUVsYV9YT3BvYzIySEpTeXRka3I3R3JucjdFd0pINUFOWTBFM3gwdGYxcmw4?oc=5</t>
+        </is>
+      </c>
+      <c r="F280" t="n">
+        <v>7</v>
+      </c>
+      <c r="G280" s="2" t="n">
+        <v>46021.1059375</v>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+        </is>
+      </c>
+      <c r="C281" t="inlineStr">
+        <is>
+          <t>Leveraging AI and satellite technologies for autonomous operations - Mining Technology</t>
+        </is>
+      </c>
+      <c r="D281" t="inlineStr">
+        <is>
+          <t>Tue, 30 Dec 2025 07:19:39 GMT</t>
+        </is>
+      </c>
+      <c r="E281" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxOUWVMYmpIWkNINjRkQ093a2hhRmhpbkE1RVNoYkM4UVg5SVJPeS1lWWpETUVPYmVKaEpLU29IYXdjNzR6WVh3RHVBVnZwUHJYMlhkdUhsQS1tQXNONWhoMTZBUlhjRHMxOElEM2VDWW1mUklablA3c2ZqOFhuVVVxNWM4dnVrN3RrdWVSM1Noa3hQdnhWWkdDcWNfbldkYnRUaGc1a3V6UEk0dFgyQlRz?oc=5</t>
+        </is>
+      </c>
+      <c r="F281" t="n">
+        <v>7</v>
+      </c>
+      <c r="G281" s="2" t="n">
+        <v>46021.3053125</v>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+        </is>
+      </c>
+      <c r="C282" t="inlineStr">
+        <is>
+          <t>AI will reshape engineering careers and experience, not jobs, is at risk - Engineering.com</t>
+        </is>
+      </c>
+      <c r="D282" t="inlineStr">
+        <is>
+          <t>Tue, 30 Dec 2025 19:26:42 GMT</t>
+        </is>
+      </c>
+      <c r="E282" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxQaUlDSnlzMnJ1aFJhRk5wTEw1S0p3eXNLQ3hwZ2FVajBJNGZNMHg5b19DSll5MW52WUhnMHpnV0NNNlpIdXBFbFgwZUQ4dEZwa2JieGNrdWs2M1ZFNU9EN0toeEwweVRfd0lRWjFpTHNHQV95dmJGNmM3bXRtNUFiZWFEQnF6VXpTNFEzOVB6THotcS0yOEtMSGI1MVNWOUxG?oc=5</t>
+        </is>
+      </c>
+      <c r="F282" t="n">
+        <v>7</v>
+      </c>
+      <c r="G282" s="2" t="n">
+        <v>46021.81020833334</v>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+        </is>
+      </c>
+      <c r="C283" t="inlineStr">
+        <is>
+          <t>OSS Announces the Sale of Bressner Technology GmbH to Hiper Euro GMBH - Investing News Network</t>
+        </is>
+      </c>
+      <c r="D283" t="inlineStr">
+        <is>
+          <t>Tue, 30 Dec 2025 21:48:16 GMT</t>
+        </is>
+      </c>
+      <c r="E283" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxQMzdmajJEVC10aWVfTkstWnJqdFYtVkhGZVptX0NOQ0k3VlJseldnNHBsdDFUMWlUbF9abXA0cDlmMVd6SEF2REwyc0RVbTlZbVVxR2d3U1AwR3N6MnpFZ3hGQUZqeVBISEhBUk5LRVYxU1JoLXV4aDhMQWk3NkkydThIYWU3d3pOekhxeXNNaV9nRFotUlRteWd3VE8?oc=5</t>
+        </is>
+      </c>
+      <c r="F283" t="n">
+        <v>7</v>
+      </c>
+      <c r="G283" s="2" t="n">
+        <v>46021.90851851852</v>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+        </is>
+      </c>
+      <c r="C284" t="inlineStr">
+        <is>
+          <t>Three New Year’s Resolutions CFOs Are Making About Data and AI - PYMNTS.com</t>
+        </is>
+      </c>
+      <c r="D284" t="inlineStr">
+        <is>
+          <t>Tue, 30 Dec 2025 21:57:28 GMT</t>
+        </is>
+      </c>
+      <c r="E284" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxOS0hoVDVlc2VKYmhLUklUV3UzUWtzc0Iwd053Xy1PZTNmSzFRTkI0TFQxRG5IaURBbUROQVlPNlo1NmNkNWJoSFZkZVowbmZPSnJwLTFmekkwOVFtcmVJLWJ5ZXUtQU9lcWhlRFNhTGxmQ2FlX3h1TjhuOUxNd0lvc1YzVFdDOGtyUW9nZFhHS2luaV9qV3lBcVFjNlpqM082QjNoMFZnSQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F284" t="n">
+        <v>7</v>
+      </c>
+      <c r="G284" s="2" t="n">
+        <v>46021.91490740741</v>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+        </is>
+      </c>
+      <c r="C285" t="inlineStr">
+        <is>
+          <t>Microsoft’s Nadella overhauls leadership as he plots AI strategy beyond OpenAI - Financial Times</t>
+        </is>
+      </c>
+      <c r="D285" t="inlineStr">
+        <is>
+          <t>Tue, 30 Dec 2025 05:00:20 GMT</t>
+        </is>
+      </c>
+      <c r="E285" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMicEFVX3lxTE1kUVQ1dUlFWEQtSlJzNm1rSHRLbVUyN0drLXhBbHVXSGFJdlJqWjFYS3lxa2kwcG1mV0JRYWZCS0ZoMVgxWkZMaGR6LWNFRm9OVXl4ZzNDaVBpVnV4OXZJZ1o0QnlMdGlTX0ROMHo1dTM?oc=5</t>
+        </is>
+      </c>
+      <c r="F285" t="n">
+        <v>7</v>
+      </c>
+      <c r="G285" s="2" t="n">
+        <v>46021.20856481481</v>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+        </is>
+      </c>
+      <c r="C286" t="inlineStr">
+        <is>
+          <t>Zhaohui Su: Pharma’s Shift Toward Personalized Care, AI, and Real-World Evidence in 2026 - Oncodaily</t>
+        </is>
+      </c>
+      <c r="D286" t="inlineStr">
+        <is>
+          <t>Tue, 30 Dec 2025 20:31:22 GMT</t>
+        </is>
+      </c>
+      <c r="E286" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTE1EX0VRVGlpZmkyU3k4Q3BueWl0akdXYVdNNE44NVVmdEdad0dFa1hFWDY1bGswUWN0amJjZnlidEZvZHl1ZmVTQV9pUHdOemVMMkxpT2tlRGNmQQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F286" t="n">
+        <v>7</v>
+      </c>
+      <c r="G286" s="2" t="n">
+        <v>46021.85511574074</v>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+        </is>
+      </c>
+      <c r="C287" t="inlineStr">
+        <is>
+          <t>AI surge fuels dramatic transformation of CIO role - TechTarget</t>
+        </is>
+      </c>
+      <c r="D287" t="inlineStr">
+        <is>
+          <t>Tue, 30 Dec 2025 13:15:58 GMT</t>
+        </is>
+      </c>
+      <c r="E287" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxPQnpqMlZYd3FycnJBWGRONmkzN0xxd19lbzE3dkNvaUh6UWI4ZG5oTFlxeWVfSVFqVGUzRW93LUhBQ3JGMlgtRDNacVVycURsbGRmc3BMOUxwZTlUbVJ5OThOQmREWWxqdGlBYzlYS3ZQZ2RIUlpyTEdBdDlyckpKUnVjVWw4amdoeE1PWmdSMS1Ca093MkctSTYyWQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F287" t="n">
+        <v>7</v>
+      </c>
+      <c r="G287" s="2" t="n">
+        <v>46021.55275462963</v>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B288" t="inlineStr">
+        <is>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+        </is>
+      </c>
+      <c r="C288" t="inlineStr">
+        <is>
+          <t>How AI Is Redefining Accounting by Doing the ‘Boring Stuff’ - PYMNTS.com</t>
+        </is>
+      </c>
+      <c r="D288" t="inlineStr">
+        <is>
+          <t>Tue, 30 Dec 2025 20:15:07 GMT</t>
+        </is>
+      </c>
+      <c r="E288" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxOQU9weThwN3BRamY5Zm5uRFR3TGx2dk5mdTl2LTlxU0pscmFTNlNEZ2c3d0tQNnN1S3lQakhjLTF6dGNqMW1ndTlBVkNTQVpQNjVwUm1xeFRpQkZqTVMyVkI3enF4TjRmS1R4S3V0cnpNRl9SQVlkcHpGSjBIN0ZHLTZXNWM2bWlHVGV4OC0tOGRlMU5vNjRhV1BnbFo5bEhaMWhCRDc0bTh2VnBmelJoZ2R3?oc=5</t>
+        </is>
+      </c>
+      <c r="F288" t="n">
+        <v>7</v>
+      </c>
+      <c r="G288" s="2" t="n">
+        <v>46021.84383101852</v>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+        </is>
+      </c>
+      <c r="C289" t="inlineStr">
+        <is>
+          <t>What the public really thinks about AI - Vox</t>
+        </is>
+      </c>
+      <c r="D289" t="inlineStr">
+        <is>
+          <t>Tue, 30 Dec 2025 16:15:00 GMT</t>
+        </is>
+      </c>
+      <c r="E289" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiggFBVV95cUxNNmZNNjFFMU9KVWxLVjJfSkRwRGM0X0NzWHQwMDN5ajc0WkYyNGpHeGkxNzVCWVdvMk1jSHUxczNNUkNzQUNDbGxTUFZxX2Q4enppX0VmVzRqX1hHX0l4U0FfN3U3M2thR1RKVk10MUJDNzk3bmllaG1CRW9KM29IOEZn?oc=5</t>
+        </is>
+      </c>
+      <c r="F289" t="n">
+        <v>7</v>
+      </c>
+      <c r="G289" s="2" t="n">
+        <v>46021.67708333334</v>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+        </is>
+      </c>
+      <c r="C290" t="inlineStr">
+        <is>
+          <t>AI And The Death of The 2021 Sales Process - SaaStr</t>
+        </is>
+      </c>
+      <c r="D290" t="inlineStr">
+        <is>
+          <t>Sat, 27 Dec 2025 16:33:54 GMT</t>
+        </is>
+      </c>
+      <c r="E290" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMidEFVX3lxTE0zdGVtbENkQ3hrRmxDdkVRS2lPeXBfTG1wVkVpRWhYaEVuZVNiOWxKbnBfeDQ0Y2V0aWh3dUxvRFAtdlNpVllyT0N6N29JSWRBaWo4Q2tIVnZ3VHdOaEpSNTh4MHlOMXJjaDVVVEo3MWJTUmNE?oc=5</t>
+        </is>
+      </c>
+      <c r="F290" t="n">
+        <v>7</v>
+      </c>
+      <c r="G290" s="2" t="n">
+        <v>46018.69020833333</v>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B291" t="inlineStr">
+        <is>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+        </is>
+      </c>
+      <c r="C291" t="inlineStr">
+        <is>
+          <t>Amazon Eyes $3 Trillion Valuation as AI and AWS Drive 2026 Growth - Yahoo Finance</t>
+        </is>
+      </c>
+      <c r="D291" t="inlineStr">
+        <is>
+          <t>Tue, 30 Dec 2025 16:40:40 GMT</t>
+        </is>
+      </c>
+      <c r="E291" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMihAFBVV95cUxPdl9SMXhBMi1rRTJpd3FMaDlzcDRuajlCeDFncHRwbmdUel9jamFfWllobWZCcXVCMTZfUndWb2xIbjZWdGVKUW10UXg3NFY3Q094ajBIeWxLS2xoX3IxeGdmMHZRQ1ZxMlhtanMydmxYTF83SVkzeVhlQUpGVkQ0ZVZkNE4?oc=5</t>
+        </is>
+      </c>
+      <c r="F291" t="n">
+        <v>7</v>
+      </c>
+      <c r="G291" s="2" t="n">
+        <v>46021.69490740741</v>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B292" t="inlineStr">
+        <is>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+        </is>
+      </c>
+      <c r="C292" t="inlineStr">
+        <is>
+          <t>High Fidelity Quantum State Transformation Achieves Optimisation under Locality Constraints - Quantum Zeitgeist</t>
+        </is>
+      </c>
+      <c r="D292" t="inlineStr">
+        <is>
+          <t>Tue, 30 Dec 2025 21:01:05 GMT</t>
+        </is>
+      </c>
+      <c r="E292" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxNcXlrVFdESXdXeDhqVlpqNE9uNWZQbUJVTDRYUkNBZm5WWnp5REFvbVFQWVR3bllSRHdueExoLWpPUk5yREllRmlXMUFTZ3YxRk5FNUxqN3oxSkwwZEVhOGtubEpoSWlDWG1yWlpkT2dBTFNwaXBYZXBpUEp0SzRJMkNfYkx4aVFQQVN0RlZGS0VKVE5aUkVxcXJKTnZOazMyWjVwUWc2S1dlakRzMEV4eGgyay1uZw?oc=5</t>
+        </is>
+      </c>
+      <c r="F292" t="n">
+        <v>7</v>
+      </c>
+      <c r="G292" s="2" t="n">
+        <v>46021.87575231482</v>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B293" t="inlineStr">
+        <is>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+        </is>
+      </c>
+      <c r="C293" t="inlineStr">
+        <is>
+          <t>Prevent Ransomware Attacks From Ruining Your New Year - The National Law Review</t>
+        </is>
+      </c>
+      <c r="D293" t="inlineStr">
+        <is>
+          <t>Tue, 30 Dec 2025 21:58:04 GMT</t>
+        </is>
+      </c>
+      <c r="E293" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiiAFBVV95cUxPU3lRUkx4bmZ3aFJpZU1LSUtuczUtdlptV0N2SmRZX1Vhdm45b0x0SW5zWXFlUGdjaTUtbm01c0t0aE9EMjI1eEpaYVNoamdFbXVyTjdicEU4ME5yQWVOdjVKRFNWMXFrNEhkX21md1dqcFlFRjVzVFdTQjFmem5makJSU3lCWU1u0gGOAUFVX3lxTE9IaFRLU19oeVpxLWxJTDdub09ESWVKaUFadFRBbjRDbTVTQU40Q2dWTmswX202MlNnZFRYVlN3T2JxUUxTdVpOcWNodmpGM2tXTzBSeDhnTG4yRTdfZ2h2TVdRcU5Jay1Ja2JpOGtBanJZVE5fLWlaN1c0MGQ3R2Q1WHU2SU52YTJkR0ZKYmc?oc=5</t>
+        </is>
+      </c>
+      <c r="F293" t="n">
+        <v>7</v>
+      </c>
+      <c r="G293" s="2" t="n">
+        <v>46021.91532407407</v>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B294" t="inlineStr">
+        <is>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+        </is>
+      </c>
+      <c r="C294" t="inlineStr">
+        <is>
+          <t>How AI Is Saving Distressed Real Estate From The ‘Carbon Cliff’ - Forbes</t>
+        </is>
+      </c>
+      <c r="D294" t="inlineStr">
+        <is>
+          <t>Tue, 30 Dec 2025 13:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="E294" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxNU3ZnZmc4Q1haNDI1R1J0RDZ6czJrVUNiekJocV80S2dqLUJFZTNjcC1vVEZ0SHNSZmdfSXBwRHVYX2tyZzRXQlIxeElSak82VFU0emc5TXVoSFhCOVlxUUdMdkt5V1hkYk55VnJTT0lCX01NZnEzRmVjbTJGRHk5ZmVLY2xjOVczZGxQZXl5NFFCUHZCbzVjTHM0WGwxTzBvM2tBUXlIMmt6LTczTHZF?oc=5</t>
+        </is>
+      </c>
+      <c r="F294" t="n">
+        <v>7</v>
+      </c>
+      <c r="G294" s="2" t="n">
+        <v>46021.54166666666</v>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B295" t="inlineStr">
+        <is>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+        </is>
+      </c>
+      <c r="C295" t="inlineStr">
+        <is>
+          <t>8 AI Books Published In 2025 That Every Educator Needs On Their Shelf - Forbes</t>
+        </is>
+      </c>
+      <c r="D295" t="inlineStr">
+        <is>
+          <t>Sun, 28 Dec 2025 12:46:59 GMT</t>
+        </is>
+      </c>
+      <c r="E295" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxPM2EwQmVibmtXTl9hOGFXa2l6NzZZMXRRSWZmSkEyN2NYOVNxa01aVkZiRnFtVy1SbkJMMW5nd1RCWERlZjRwQU1QZFVvUEVPMGZsSmppa3V5bUQ5ekxqcVJ5dzZGc0lhZG9mcTdmdnRUdW5kbnVROFVEbFdMZDNqVEpFeFR2TDFWR3VVLWI3UUVsZ1NENTM4Z2FCRmM2bm5VM0k1bEl2S0dGalFIUnRLWG4zVm9ZbEdDVGJnTQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F295" t="n">
+        <v>7</v>
+      </c>
+      <c r="G295" s="2" t="n">
+        <v>46019.53262731482</v>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B296" t="inlineStr">
+        <is>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+        </is>
+      </c>
+      <c r="C296" t="inlineStr">
+        <is>
+          <t>Ericsson Year in Review 2025: Part Two – July to December - 5G Americas</t>
+        </is>
+      </c>
+      <c r="D296" t="inlineStr">
+        <is>
+          <t>Tue, 30 Dec 2025 17:42:47 GMT</t>
+        </is>
+      </c>
+      <c r="E296" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiigFBVV95cUxPRWRaYVVQdTVaaXBsOERtTjJxYU1YTGJOV0xxZmtfclppN3RjX1dSem5YdG5JbWNJVzFzUTBxaVBZaVVUakp4X0x4MnM2N0R4emx1TVV0MG80cFNhY3h4OUs1eHZrQzVVNS1MMlBLQl95MXhwdkpnYXI4LTZTaEhHbzBOVGlkdF8tT1E?oc=5</t>
+        </is>
+      </c>
+      <c r="F296" t="n">
+        <v>7</v>
+      </c>
+      <c r="G296" s="2" t="n">
+        <v>46021.73804398148</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/topic_feeds.xlsx
+++ b/data/topic_feeds.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G296"/>
+  <dimension ref="A1:G418"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10204,6 +10204,4032 @@
         <v>46021.73804398148</v>
       </c>
     </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>Current_Affairs</t>
+        </is>
+      </c>
+      <c r="B297" t="inlineStr">
+        <is>
+          <t>(geopolitics OR migration OR economy OR conflict OR legislation OR terrorism OR disinformation OR misinformation OR government OR policy OR regulation) AND (briefing OR analysis OR update OR report)</t>
+        </is>
+      </c>
+      <c r="C297" t="inlineStr">
+        <is>
+          <t>Minister for the Middle East statement: Regional update - GOV.UK</t>
+        </is>
+      </c>
+      <c r="D297" t="inlineStr">
+        <is>
+          <t>Tue, 06 Jan 2026 13:46:19 GMT</t>
+        </is>
+      </c>
+      <c r="E297" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxNN2RUUTJQYUNDamRuMkZpY1U4Njc5U1BiQVQtWkNCcFV0cEVscENzSXpTc0hPUlV5UzRvdmUyMjFRYVdiVktqM0I1eWRwMU5OaHBBdjNpWjFMRnZNMHh6Wi1BWTVfQkpEQ1lTSVQ1R080SjRUY1Ytak9Yb2kwWWU3cXc4T3NBQW03RGNtZjF3S3NwcEkyYjdFNw?oc=5</t>
+        </is>
+      </c>
+      <c r="F297" t="n">
+        <v>7</v>
+      </c>
+      <c r="G297" s="2" t="n">
+        <v>46028.57383101852</v>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>Current_Affairs</t>
+        </is>
+      </c>
+      <c r="B298" t="inlineStr">
+        <is>
+          <t>(geopolitics OR migration OR economy OR conflict OR legislation OR terrorism OR disinformation OR misinformation OR government OR policy OR regulation) AND (briefing OR analysis OR update OR report)</t>
+        </is>
+      </c>
+      <c r="C298" t="inlineStr">
+        <is>
+          <t>Media Advisory | United Nations to launch 2026 report on the global economy - Welcome to the United Nations</t>
+        </is>
+      </c>
+      <c r="D298" t="inlineStr">
+        <is>
+          <t>Tue, 06 Jan 2026 20:19:55 GMT</t>
+        </is>
+      </c>
+      <c r="E298" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMihgFBVV95cUxNUEJnRkZZUWtPckJXU0M1dXpLcGdSSW5MV19rY0FtcXpFTkdIaE4yNk1yeV9jY2t0M3NsSFUtNEdyOUFKV1FoOVlDQzZMTkhGMlBDUDEyMGxkT2hjNUxRdWJTSDNjVjNrenpsVVJpV3ZkOVhwSDhFaE51aElzZ2pBOWNKT3pQQQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F298" t="n">
+        <v>7</v>
+      </c>
+      <c r="G298" s="2" t="n">
+        <v>46028.84716435185</v>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>Current_Affairs</t>
+        </is>
+      </c>
+      <c r="B299" t="inlineStr">
+        <is>
+          <t>(geopolitics OR migration OR economy OR conflict OR legislation OR terrorism OR disinformation OR misinformation OR government OR policy OR regulation) AND (briefing OR analysis OR update OR report)</t>
+        </is>
+      </c>
+      <c r="C299" t="inlineStr">
+        <is>
+          <t>Averting an Environmental Catastrophe in the Chagos Archipelago - Policy Exchange</t>
+        </is>
+      </c>
+      <c r="D299" t="inlineStr">
+        <is>
+          <t>Sun, 04 Jan 2026 22:01:26 GMT</t>
+        </is>
+      </c>
+      <c r="E299" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxNZ1dnNURpQWEySjlGLVI0bEQyYk5hNzBPME0wM0tzdlFDUVA4SW5sNnVyN1d4cWtwcURQRHFURTlGemVpOEotSHBlb1M0LV8td21teGZMYlo3UldlOUhIUkhGRUpzejN5UjhJNFFOZEtUUXdfaTlrY1RUNmdyYW5iRWw5bFdNX3cxZzEzTkFpX25TalQyS1pRRDN4d3N0SFhIaGxjUnBldF9oQQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F299" t="n">
+        <v>7</v>
+      </c>
+      <c r="G299" s="2" t="n">
+        <v>46026.91766203703</v>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>Current_Affairs</t>
+        </is>
+      </c>
+      <c r="B300" t="inlineStr">
+        <is>
+          <t>(geopolitics OR migration OR economy OR conflict OR legislation OR terrorism OR disinformation OR misinformation OR government OR policy OR regulation) AND (briefing OR analysis OR update OR report)</t>
+        </is>
+      </c>
+      <c r="C300" t="inlineStr">
+        <is>
+          <t>Government demands Musk's X deals with 'appalling' Grok AI - BBC</t>
+        </is>
+      </c>
+      <c r="D300" t="inlineStr">
+        <is>
+          <t>Tue, 06 Jan 2026 14:15:27 GMT</t>
+        </is>
+      </c>
+      <c r="E300" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiXEFVX3lxTE5aeGw4MHRnV3NhSnVEeElzX3dXRXkxSkVlR0Y0N01rM3RJTFBjZEVhVTFyZEQwMVRqcVNjeG9fc3pfbGFqWWJFbmRsTnp4TDNzVm96U3I5TC16ZThv0gFiQVVfeXFMT3JNTUZlamV6QWo0VWFkUFNUODBLakNYNFhKdlk5ekRTOUh1eXNVazZJUUtaUEloODJrbEM2SjBoS0xULVEyNXQyQ2hiZjM1SHNrbTBOem9waVgtS25TcGV0bVE?oc=5</t>
+        </is>
+      </c>
+      <c r="F300" t="n">
+        <v>7</v>
+      </c>
+      <c r="G300" s="2" t="n">
+        <v>46028.5940625</v>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>Current_Affairs</t>
+        </is>
+      </c>
+      <c r="B301" t="inlineStr">
+        <is>
+          <t>(geopolitics OR migration OR economy OR conflict OR legislation OR terrorism OR disinformation OR misinformation OR government OR policy OR regulation) AND (briefing OR analysis OR update OR report)</t>
+        </is>
+      </c>
+      <c r="C301" t="inlineStr">
+        <is>
+          <t>Council report planned to go to minister says it believes holding elections in May will jeopardise the effectiveness of local government reorganisation - Thurrock Nub News</t>
+        </is>
+      </c>
+      <c r="D301" t="inlineStr">
+        <is>
+          <t>Tue, 06 Jan 2026 11:19:30 GMT</t>
+        </is>
+      </c>
+      <c r="E301" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMipwJBVV95cUxQdmZjelNqejZYSTFybDc4cjU3UURpN0RRRDhHTWJiN1N5cVlqSVg4RkZmYklSRjk1WlByQ2xLb3dkMlU2NFBhMmttcElEMkxtbFpSVFRfYWhySWpzZTVlN0F5NENHLVpucU9zM3AxQ0ozUzdmNjR2OUhjWk1OeEVKU1VNeDlfYTExcnJoSjJ3aW5xcXNCTTRzdFliazkwUmdYMmhZZHhQMFpSM3ZZYUZScVp3aGhZcWJfUWNPR2liUElNMVc3eThRZzkxZk5BQVpMbGljeXlVbDVRMlRvUURSOGRfMlhMckNVMFk3Yy10ZFVXS1BMYW43OHBFWmVTYzExcWVYelhhUFhxVmdCOFJKRl9McXlQa1BnQk1pYXMyVlFvbVVlZU5R?oc=5</t>
+        </is>
+      </c>
+      <c r="F301" t="n">
+        <v>7</v>
+      </c>
+      <c r="G301" s="2" t="n">
+        <v>46028.471875</v>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>Current_Affairs</t>
+        </is>
+      </c>
+      <c r="B302" t="inlineStr">
+        <is>
+          <t>(geopolitics OR migration OR economy OR conflict OR legislation OR terrorism OR disinformation OR misinformation OR government OR policy OR regulation) AND (briefing OR analysis OR update OR report)</t>
+        </is>
+      </c>
+      <c r="C302" t="inlineStr">
+        <is>
+          <t>Ukraine – conflict : ETC Situation Report #54 - Reporting period: December 2025 - ReliefWeb</t>
+        </is>
+      </c>
+      <c r="D302" t="inlineStr">
+        <is>
+          <t>Mon, 05 Jan 2026 10:03:08 GMT</t>
+        </is>
+      </c>
+      <c r="E302" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxQRG85amR2dFVybTNzdVFZUHJRZTNTbk5NdnU4Mk5hS0k3dVN3N2tIXzlDMWRqclFzVTdYaDFfVG1LYVNsRXU3WWRMV0w4aVBNQXdQRjA1Z2NqOF8tWUc0RkNqSVhzbXh4MW1Lb0xrdTN3a3JlcFowOGV3U2NKRUU2WktWeXBQTUFQQl9NOVdjVjIwM2djTGdVQWFKUVZTZEF2WXJvUEJOOTZhUkhI?oc=5</t>
+        </is>
+      </c>
+      <c r="F302" t="n">
+        <v>7</v>
+      </c>
+      <c r="G302" s="2" t="n">
+        <v>46027.41884259259</v>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>Current_Affairs</t>
+        </is>
+      </c>
+      <c r="B303" t="inlineStr">
+        <is>
+          <t>(geopolitics OR migration OR economy OR conflict OR legislation OR terrorism OR disinformation OR misinformation OR government OR policy OR regulation) AND (briefing OR analysis OR update OR report)</t>
+        </is>
+      </c>
+      <c r="C303" t="inlineStr">
+        <is>
+          <t>The Dual Nature Of Inheritance Tax From A Policy Perspective – Analysis - Eurasia Review</t>
+        </is>
+      </c>
+      <c r="D303" t="inlineStr">
+        <is>
+          <t>Wed, 07 Jan 2026 01:56:39 GMT</t>
+        </is>
+      </c>
+      <c r="E303" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxQT0daTDd4N2czOV9DemFvUDQyQ2R0MGtFWVhjR21qZE5mb2xadk45YU9EbzhzVDcxc1BfNDNsOVQ1QVRCR1hfenpzSnVBTU5oQ1JNZjAzb3RWQ2UwVk9FRGNGTnJRM3N1alpUZUFWaFRTN2N3WGIxLXpXb1c1LUlGR2dMZUFYVnVpazJLNWpoUU8tQlpvY0ktQ3ppcUFkZDNDVmU5YkQ0Mm0xc091UXc?oc=5</t>
+        </is>
+      </c>
+      <c r="F303" t="n">
+        <v>7</v>
+      </c>
+      <c r="G303" s="2" t="n">
+        <v>46029.08100694444</v>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>Current_Affairs</t>
+        </is>
+      </c>
+      <c r="B304" t="inlineStr">
+        <is>
+          <t>(geopolitics OR migration OR economy OR conflict OR legislation OR terrorism OR disinformation OR misinformation OR government OR policy OR regulation) AND (briefing OR analysis OR update OR report)</t>
+        </is>
+      </c>
+      <c r="C304" t="inlineStr">
+        <is>
+          <t>Truth Initiative Report Finds Rapidly Evolving Nicotine Market Outpacing Regulation, Putting Youth at Risk - PR Newswire</t>
+        </is>
+      </c>
+      <c r="D304" t="inlineStr">
+        <is>
+          <t>Tue, 06 Jan 2026 14:45:00 GMT</t>
+        </is>
+      </c>
+      <c r="E304" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi8wFBVV95cUxPTTZQSU94bEtMMkIxTkdvek82WEpGX3BlaVF2WEg0ZWNXUHJqU3RCRVF1SXJXejgyNEpreFg2anFGZ18weTVlejE3QzdNcTNiNThheDYxSFlYTmFJQzJhUzZVU0tWbG9CUXZNUG52OGpuUDdmZnJPSlF3UFJSOU9JdmV5RUN0c0sxYTNCVlRYRndYQThqUU9waHc2T2tuQWs3eHg0WUxzc2xtcGRxYUpzUVViYzNaSUdCcEVVQUFYSzRsQ1Vaay12aW5TZWYtUEZNTnhlVlRvTGN1SWJUNGdYb2hYSm9zWng1RGVTb2h0Z1Y4OVk?oc=5</t>
+        </is>
+      </c>
+      <c r="F304" t="n">
+        <v>7</v>
+      </c>
+      <c r="G304" s="2" t="n">
+        <v>46028.61458333334</v>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="inlineStr">
+        <is>
+          <t>Current_Affairs</t>
+        </is>
+      </c>
+      <c r="B305" t="inlineStr">
+        <is>
+          <t>(geopolitics OR migration OR economy OR conflict OR legislation OR terrorism OR disinformation OR misinformation OR government OR policy OR regulation) AND (briefing OR analysis OR update OR report)</t>
+        </is>
+      </c>
+      <c r="C305" t="inlineStr">
+        <is>
+          <t>Taiwan conflict ‘catastrophic’ for China: US report - Taipei Times</t>
+        </is>
+      </c>
+      <c r="D305" t="inlineStr">
+        <is>
+          <t>Tue, 06 Jan 2026 16:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="E305" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMieEFVX3lxTFBxTWRtMWJsNlJ2RDVUXzhTSXVpSXdqVE5IVW8xOWxRYTZQeWFpdGpnSDdFZm1UclVIMkVkMkt6VzVROUFwQU5RUlhQeGdNcFZMdFZxNmRhbGI5d3JLM1dQZTVrUVhiZll3bmFyOFZpM0VWQkRuX2VqTw?oc=5</t>
+        </is>
+      </c>
+      <c r="F305" t="n">
+        <v>7</v>
+      </c>
+      <c r="G305" s="2" t="n">
+        <v>46028.66666666666</v>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
+          <t>Current_Affairs</t>
+        </is>
+      </c>
+      <c r="B306" t="inlineStr">
+        <is>
+          <t>(geopolitics OR migration OR economy OR conflict OR legislation OR terrorism OR disinformation OR misinformation OR government OR policy OR regulation) AND (briefing OR analysis OR update OR report)</t>
+        </is>
+      </c>
+      <c r="C306" t="inlineStr">
+        <is>
+          <t>Beyond the forecast: Six themes for Canada’s economy in 2026 - RBC</t>
+        </is>
+      </c>
+      <c r="D306" t="inlineStr">
+        <is>
+          <t>Tue, 06 Jan 2026 14:48:17 GMT</t>
+        </is>
+      </c>
+      <c r="E306" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi0wFBVV95cUxOci05VlJoR1BvX2p3dF92OFJKTGFPRUJjdUtCd3d1bmtIQ1hrd0Q0a2cwcFIwT1UtZGRCZDZXT2Q5elYxSkNEejJ4TlFWZHJBOEZrVTI5LWNrRnFFdzhyT1p3dGxHV1pRb0VnSmt1V1VIWmI3enM0aklFTWVaVEJaWXQ4aTY4Nk5BcC1NeS1qNW5lZDRVdkQ1WnQ3QklzTW5zUnVvVWRKZFRTSzRrYjRtbmJqcTNTRDhXWDRyREdSTzc0NENLMXVFRVVlYmpKOEh0SjBn?oc=5</t>
+        </is>
+      </c>
+      <c r="F306" t="n">
+        <v>7</v>
+      </c>
+      <c r="G306" s="2" t="n">
+        <v>46028.61686342592</v>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="inlineStr">
+        <is>
+          <t>Current_Affairs</t>
+        </is>
+      </c>
+      <c r="B307" t="inlineStr">
+        <is>
+          <t>(geopolitics OR migration OR economy OR conflict OR legislation OR terrorism OR disinformation OR misinformation OR government OR policy OR regulation) AND (briefing OR analysis OR update OR report)</t>
+        </is>
+      </c>
+      <c r="C307" t="inlineStr">
+        <is>
+          <t>Ten humanitarian trends to keep an eye on in 2026 - The New Humanitarian</t>
+        </is>
+      </c>
+      <c r="D307" t="inlineStr">
+        <is>
+          <t>Mon, 05 Jan 2026 14:32:00 GMT</t>
+        </is>
+      </c>
+      <c r="E307" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxNQlBDQmtmQXZBbmFTSGNuMmtPZm5kNWM1c2RMZ1VxMmNvakk0T0w1NnhBb2ZacEtmU0lSUGlscmt1dmJyLWwwUEROMkFLbzc5SEh1YTFhRnJnbFYtMjRXanBHQlpmQzBZanJTNHFMMVU5VG9zdGpDb1JRanZJQ2dxeEJ5SklnOUs0ZXBKaUZ2d0kxVkx6Z3NB?oc=5</t>
+        </is>
+      </c>
+      <c r="F307" t="n">
+        <v>7</v>
+      </c>
+      <c r="G307" s="2" t="n">
+        <v>46027.60555555556</v>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="inlineStr">
+        <is>
+          <t>Current_Affairs</t>
+        </is>
+      </c>
+      <c r="B308" t="inlineStr">
+        <is>
+          <t>(geopolitics OR migration OR economy OR conflict OR legislation OR terrorism OR disinformation OR misinformation OR government OR policy OR regulation) AND (briefing OR analysis OR update OR report)</t>
+        </is>
+      </c>
+      <c r="C308" t="inlineStr">
+        <is>
+          <t>Trump administration sets meetings with oil companies on Venezuela: Report - Al Jazeera</t>
+        </is>
+      </c>
+      <c r="D308" t="inlineStr">
+        <is>
+          <t>Mon, 05 Jan 2026 22:34:10 GMT</t>
+        </is>
+      </c>
+      <c r="E308" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxOY0g5RGlrQVBvOUY5WXlNdTd3Q19BeElxZmxncTNfeWIwMzQ4bHNtenFwWHIwZWdUMldONGNwU3J6UnN5V0ZOLU5XTmhUZjlnaVVRV01GMFVkVHVhV0MtOHFfWkNQWjhYYkdMWk91QnZNMTRyem80TTExWThYTmN4NFR3SXQwMFpYQ05pQ3VNcl81NHZINnJMMHg5WnpHRi1UWlZNMXlKWXhSdllKdlg1Q1lOdnYxRVXSAbwBQVVfeXFMT3dnZ0tCaG1sZFpiWVJrNERabk9UMnBQS1lnRWh2RDNJV2xoNXpSMlI3VjBNNkUxWS1SM2dLWXZzamhBUDRtalc5clRkeGZYd2xPV015VUxuYno4NjFaQ0hsR1V5WGpmUjhyT1pDaHVMbElwYjBTRS1Ga3A0aWxoUDJHa1psTllOSFlvWXVnMVY3RVFnNzZrUUZza3JNSWx0TzVjazFKTzBpbmJLUFFGSWVDVDdhZE1NRXBPQ00?oc=5</t>
+        </is>
+      </c>
+      <c r="F308" t="n">
+        <v>7</v>
+      </c>
+      <c r="G308" s="2" t="n">
+        <v>46027.94039351852</v>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="inlineStr">
+        <is>
+          <t>Current_Affairs</t>
+        </is>
+      </c>
+      <c r="B309" t="inlineStr">
+        <is>
+          <t>(geopolitics OR migration OR economy OR conflict OR legislation OR terrorism OR disinformation OR misinformation OR government OR policy OR regulation) AND (briefing OR analysis OR update OR report)</t>
+        </is>
+      </c>
+      <c r="C309" t="inlineStr">
+        <is>
+          <t>Maduro’s Superseding Indictment Highlights Cryptocurrency’s Dual Role In Venezuela’s Sanctions-Hit Economy : Analysis - Crowdfund Insider</t>
+        </is>
+      </c>
+      <c r="D309" t="inlineStr">
+        <is>
+          <t>Tue, 06 Jan 2026 15:06:00 GMT</t>
+        </is>
+      </c>
+      <c r="E309" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi8wFBVV95cUxQbTZMNkFjWHA5TG9pcDFSS2Yxa29kSVlreW5lcVd1WGE5UDJ6V2R5Q0QzeUVZYzdEdmRfbkpnSDNrVjFLYXRzM2lPeDhCZTBGWC04d2U0eEtZUVc5STJZUkpMeVd5c1hzc2JLMGtGZDFLZE9LYjhCaEhyM0twUE12TGg4d1R3amdwR0RFVGMzRmdaMEROeTliV3dHMVdWTnpRelFXYzVYVXNpTzdHWnRhWjdKeG1wV3NSN05lMHdmRnphX2pfSUd6TmJHZE4wSmVtTWJHLWg1Z3BDUWRlMFZyZGhUVHJZSVhMbzJMemRsTVRpd3M?oc=5</t>
+        </is>
+      </c>
+      <c r="F309" t="n">
+        <v>7</v>
+      </c>
+      <c r="G309" s="2" t="n">
+        <v>46028.62916666667</v>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="inlineStr">
+        <is>
+          <t>Current_Affairs</t>
+        </is>
+      </c>
+      <c r="B310" t="inlineStr">
+        <is>
+          <t>(geopolitics OR migration OR economy OR conflict OR legislation OR terrorism OR disinformation OR misinformation OR government OR policy OR regulation) AND (briefing OR analysis OR update OR report)</t>
+        </is>
+      </c>
+      <c r="C310" t="inlineStr">
+        <is>
+          <t>Public Health Situation Analysis - Cambodia-Thailand Conflict (18 December 2025) - ReliefWeb</t>
+        </is>
+      </c>
+      <c r="D310" t="inlineStr">
+        <is>
+          <t>Tue, 06 Jan 2026 03:33:09 GMT</t>
+        </is>
+      </c>
+      <c r="E310" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxPV1RZU0pQa1BWT0w5QTBVUVU5OGh5cVFVY2hudV9QQ2szVnpPb0thUENaSjZXWnhIMlo3MnNHSXZfejZjNEVxTlUyUHBNSDB5NjRsRDJGbVNtRlhlNXp4cTFLU2VxUlEyZ0U0bHBiUzRlR1lGWnlTLVFsNHpMbWdPTzJkMU5jT19tYnUyUFAxWTJ0QXRJZkl4YVlEZjc5OXRIcllNRHNpMUxDTzgtNGFwWTJpbEU?oc=5</t>
+        </is>
+      </c>
+      <c r="F310" t="n">
+        <v>7</v>
+      </c>
+      <c r="G310" s="2" t="n">
+        <v>46028.14802083333</v>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="inlineStr">
+        <is>
+          <t>Current_Affairs</t>
+        </is>
+      </c>
+      <c r="B311" t="inlineStr">
+        <is>
+          <t>(geopolitics OR migration OR economy OR conflict OR legislation OR terrorism OR disinformation OR misinformation OR government OR policy OR regulation) AND (briefing OR analysis OR update OR report)</t>
+        </is>
+      </c>
+      <c r="C311" t="inlineStr">
+        <is>
+          <t>Government issues firework ban update after petition reaches 189,000 signatures - Manchester Evening News</t>
+        </is>
+      </c>
+      <c r="D311" t="inlineStr">
+        <is>
+          <t>Mon, 05 Jan 2026 17:46:00 GMT</t>
+        </is>
+      </c>
+      <c r="E311" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxPQlFXcTU4SGZBb2tTZHpxbDU2LTJwWjIxUWhtS1lCZ2RzUTZldkhyVFZIaUlmX2VYTFhQVzF3aTVXNFRhT3JGejcwcDNDalVkM052amRES1NpMXN3YVFjVFdyZVRIUzlKLS1ENkZVQVNQbEJJV053NGVTcmVIdXYtdWRacHRNYUsxM0pBeC1VRHl0TGtVLU5Ta3J5cUxoRWNs0gGmAUFVX3lxTE1nRF9Bd19WeXp0TUR6dlhzMHhnZDEwZjFZN3ZlcnZ0ejN0S1FoWWpzTUc3VVhpbVZjZzJ2ckxtNFBNcWpPa0xfQXNDMHZNdXg4UU8wWkNfOVFGVGhTRmhvbkJRQmwyVHQxUEhJOGNMTVAySW5NRGI4cHlnQWxWUklFU2NwS3hIc2J0OWZMQTYzMG1ySjE1S1E1SHJ5Wm1oWXZMeENDUGc?oc=5</t>
+        </is>
+      </c>
+      <c r="F311" t="n">
+        <v>7</v>
+      </c>
+      <c r="G311" s="2" t="n">
+        <v>46027.74027777778</v>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="inlineStr">
+        <is>
+          <t>Supply_Chain</t>
+        </is>
+      </c>
+      <c r="B312" t="inlineStr">
+        <is>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+        </is>
+      </c>
+      <c r="C312" t="inlineStr">
+        <is>
+          <t>US Supreme Court expected to rule on tariffs on Friday - Al Jazeera</t>
+        </is>
+      </c>
+      <c r="D312" t="inlineStr">
+        <is>
+          <t>Tue, 06 Jan 2026 21:22:38 GMT</t>
+        </is>
+      </c>
+      <c r="E312" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxPOWlDdkFOSTFSMUhHUXRkbFREaDR1TjhqandDRUN6NEVnakVUMTZQNzdlY0l6WF9oc2dBU2tYRUxVejhuQjRWTFBzeDM3NndjbUZQVHFla0J4RDdfQm0xZ3pvX1l3SXo4c1NoSHVyTWt0Uzk1Y3JrNmgwczhIMmlyUS0zcTRmcF9paTRydDBFNU5HUXY0eVFIcXQ1R3YwZ9IBowFBVV95cUxPZWxjdWpWMVpQdWNJdzd6c2J4SnNPVElVZDRWTHhwS3pXekd2UXBmUlZfTEI1QlR2VEMxWWhfZmJUQ0d3QTZNMEduc2dfSUM5Z2xvUWw2V0lXTFZYbXYzdnozaVNoTktDNmthX1lNczlxRUxJd0tVcGZ2cEo1eHNFVFdTTDVWUE93Z1hnVHFQMkVxT2VEZW9xM0ttVmd3SzYySktN?oc=5</t>
+        </is>
+      </c>
+      <c r="F312" t="n">
+        <v>7</v>
+      </c>
+      <c r="G312" s="2" t="n">
+        <v>46028.89071759259</v>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="inlineStr">
+        <is>
+          <t>Supply_Chain</t>
+        </is>
+      </c>
+      <c r="B313" t="inlineStr">
+        <is>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+        </is>
+      </c>
+      <c r="C313" t="inlineStr">
+        <is>
+          <t>US may seize oil tanker heading for Europe, reports say - BBC</t>
+        </is>
+      </c>
+      <c r="D313" t="inlineStr">
+        <is>
+          <t>Tue, 06 Jan 2026 19:47:29 GMT</t>
+        </is>
+      </c>
+      <c r="E313" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTFBhMW5ySE1fR0VpMDRQSnViUG9lLVdWMU9JV0JoT1pZNXg4cTVOcl9kSWozM2FrTWhueHFpMm5pQlFPSkdrMEhCdTc0akpIOV9qMVJ3NUFOYnRrZ9IBX0FVX3lxTE5FWlZNLTRab2t6WlhBcnNzUlZSNEJCMmo4WDNCVW1TbTlVMkJfUUFhNmNmeUd3N2tKTVdNTTBRRkctOFRDclZOLVBiV18ya05PalA5V3Vvak5hWUlFWWpr?oc=5</t>
+        </is>
+      </c>
+      <c r="F313" t="n">
+        <v>7</v>
+      </c>
+      <c r="G313" s="2" t="n">
+        <v>46028.8246412037</v>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="inlineStr">
+        <is>
+          <t>Supply_Chain</t>
+        </is>
+      </c>
+      <c r="B314" t="inlineStr">
+        <is>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+        </is>
+      </c>
+      <c r="C314" t="inlineStr">
+        <is>
+          <t>Supply Chain Disruptions Hobble Strong Holiday Sales Season - Publishers Weekly</t>
+        </is>
+      </c>
+      <c r="D314" t="inlineStr">
+        <is>
+          <t>Tue, 06 Jan 2026 15:48:16 GMT</t>
+        </is>
+      </c>
+      <c r="E314" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi6gFBVV95cUxOLV85MlJfSkRMc0Z0MWVjZmxoTnlKRF9MU3BZbE1kQ0VIaTBHT2RINUVyR0dFajlqdmNXLWhZTXhUVWRRVHNDb0lTSzFjSFNTbVZiVEI1UUpzNk5YUGZBdzlLOGZ2ZnFrWmFDVnVsbEM0V2hyTDM5LXEzYmhBeEY5cGU5b1VwcVBvVDl4Wl9CczM5dlFEcHdlS1RudEduUWlyNF9hTXNvcVR1aml1N196NDlUUWR0RFRmVWpTZXV4UHZNR1ZzVldxcERVMk9WR2FBRWpwZmw0c2tJcjluaUUyMGZSRzF5RURnV0E?oc=5</t>
+        </is>
+      </c>
+      <c r="F314" t="n">
+        <v>7</v>
+      </c>
+      <c r="G314" s="2" t="n">
+        <v>46028.65851851852</v>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="inlineStr">
+        <is>
+          <t>Supply_Chain</t>
+        </is>
+      </c>
+      <c r="B315" t="inlineStr">
+        <is>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+        </is>
+      </c>
+      <c r="C315" t="inlineStr">
+        <is>
+          <t>Danish Shipping Targets Seafarer Training - Marine News Magazine</t>
+        </is>
+      </c>
+      <c r="D315" t="inlineStr">
+        <is>
+          <t>Tue, 06 Jan 2026 21:09:11 GMT</t>
+        </is>
+      </c>
+      <c r="E315" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMihwFBVV95cUxQb2JqZThxUVlaOGloTkw1bFhUX19HVXdSUGxBTEM4VV9NcHB0LWdOZW5jdjUzYWtVUWhYbVdkZndZOFZlUUhfcGhERDBweUk3NXJBTHhuWWpRM2RYMXdVUGZQbzVmQVpzdUc5bXgxSzE2cXZtWlhPTWR6VXdlWE51RHJXWkI2Qlk?oc=5</t>
+        </is>
+      </c>
+      <c r="F315" t="n">
+        <v>7</v>
+      </c>
+      <c r="G315" s="2" t="n">
+        <v>46028.88137731481</v>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="inlineStr">
+        <is>
+          <t>Supply_Chain</t>
+        </is>
+      </c>
+      <c r="B316" t="inlineStr">
+        <is>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+        </is>
+      </c>
+      <c r="C316" t="inlineStr">
+        <is>
+          <t>New operating company launches and lines up private equity logistics partnership - Green Street News</t>
+        </is>
+      </c>
+      <c r="D316" t="inlineStr">
+        <is>
+          <t>Tue, 06 Jan 2026 15:16:37 GMT</t>
+        </is>
+      </c>
+      <c r="E316" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxONk9lVkpHR3RFUTk5a3ZmWXBQT2FiTzdMMjV4UTcyZHNFb2lWSU5IMjlkMi1fc0FtdklmdGg4d2tQc3ZyYUE3LS1LS1gwMDFxS0VtQjlEdWYyR285TTlYR0VIUUNCQW01d1EzdmF5RTNRU1ZBeDBjU3NNUUNhd1lmNUY3TzZ5MkpHSjBZZi1uNmZ0RU1qQlplMTU4a0p1WXNUaklLX3M0SkJNbkxOR1p3?oc=5</t>
+        </is>
+      </c>
+      <c r="F316" t="n">
+        <v>7</v>
+      </c>
+      <c r="G316" s="2" t="n">
+        <v>46028.63653935185</v>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="inlineStr">
+        <is>
+          <t>Supply_Chain</t>
+        </is>
+      </c>
+      <c r="B317" t="inlineStr">
+        <is>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+        </is>
+      </c>
+      <c r="C317" t="inlineStr">
+        <is>
+          <t>Digital supply chain maturity is advancing - Supply Chain Management Review</t>
+        </is>
+      </c>
+      <c r="D317" t="inlineStr">
+        <is>
+          <t>Tue, 06 Jan 2026 21:01:00 GMT</t>
+        </is>
+      </c>
+      <c r="E317" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMilgFBVV95cUxPdVNLRU1lbTE0NUtOVTRWRGNGNHRPSkpaWmpObnIzLTJtRGZ2cG1TSGY1bWE2aUZGeWFNOU82NEc2TnZIT21udDItUzJfY01BUHI2OVNLSmp4WnR5a3NaNF81dW92VVZzTzBwOHRCZl84Uk1BbEdxTkhMOEQ4X25ZYmIyYnVKbjFJUUxLN2lqY3ZEZHBhWUE?oc=5</t>
+        </is>
+      </c>
+      <c r="F317" t="n">
+        <v>7</v>
+      </c>
+      <c r="G317" s="2" t="n">
+        <v>46028.87569444445</v>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="inlineStr">
+        <is>
+          <t>Supply_Chain</t>
+        </is>
+      </c>
+      <c r="B318" t="inlineStr">
+        <is>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+        </is>
+      </c>
+      <c r="C318" t="inlineStr">
+        <is>
+          <t>Jon Brady officially appointed as new First-Team Manager - Port Vale Football Club</t>
+        </is>
+      </c>
+      <c r="D318" t="inlineStr">
+        <is>
+          <t>Tue, 06 Jan 2026 09:17:38 GMT</t>
+        </is>
+      </c>
+      <c r="E318" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMijwFBVV95cUxQVWdBUDVROTlUcVpoSzVaOEVlQU1IcG04YUNJbDN0TEVFVXRYSWhLYWtWU0F5eVNMakdTTUZSaDFDWDFNeFk0b3FFZVRmSF8zMVo0b3FrMElLaGNpZGhKRmIxWHRJR0ZDWWNQd2p0amNBYmw3MmNLS3hhWFYzVE5WcExmY1lUVXBYRVRzWEdhMA?oc=5</t>
+        </is>
+      </c>
+      <c r="F318" t="n">
+        <v>7</v>
+      </c>
+      <c r="G318" s="2" t="n">
+        <v>46028.38724537037</v>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="inlineStr">
+        <is>
+          <t>Supply_Chain</t>
+        </is>
+      </c>
+      <c r="B319" t="inlineStr">
+        <is>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+        </is>
+      </c>
+      <c r="C319" t="inlineStr">
+        <is>
+          <t>£7m upgrade boosts Scotland’s rail freight network - Network Rail media centre</t>
+        </is>
+      </c>
+      <c r="D319" t="inlineStr">
+        <is>
+          <t>Mon, 05 Jan 2026 09:40:16 GMT</t>
+        </is>
+      </c>
+      <c r="E319" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxPeTkzQjVvVkpObUJjdlE2dHRRQkQ3Q1c2a09mQWtvZV9RbXRBU2I0VjhmYUJadEtqZHpTemtScTFYT001REdZbGZsZklNR01pWHc4S0FyLWt5TzFaQUhiMUY0dV9ZOGJ6c09ESVZSQzI0VHl5WERPZ3l2bXY4VVZDeDY4MWtGYzhKeTVVWFlONlJUckdBOE00RmY4RXdraDQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F319" t="n">
+        <v>7</v>
+      </c>
+      <c r="G319" s="2" t="n">
+        <v>46027.40296296297</v>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="inlineStr">
+        <is>
+          <t>Supply_Chain</t>
+        </is>
+      </c>
+      <c r="B320" t="inlineStr">
+        <is>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+        </is>
+      </c>
+      <c r="C320" t="inlineStr">
+        <is>
+          <t>Poland will be "lead country" on logistics for Ukraine peace deal, says Tusk after Paris talks - Notes From Poland</t>
+        </is>
+      </c>
+      <c r="D320" t="inlineStr">
+        <is>
+          <t>Tue, 06 Jan 2026 21:55:59 GMT</t>
+        </is>
+      </c>
+      <c r="E320" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxQNjVDYmFra3JFV2FsRlRtWnkzREJSUXpnUzRDblRYRURSYW5CZjlZYXBpRkZZSU91dnVCbEs2dENTa1FheDhJaHE0RUtLZzRDeGlXREFMejdGLTdaVmIyX2JjRGgyT1J5QlhyRjBpUzZJMmRKQTRhWDJmNkN3V29lVzFyRHhRcXJyMDMwVWoxTUZMNDItYlpLUUVrSk9vZlNTTGtOXzNOcmp0Mnc5RXhxYzdBQ1FkQUYtcGNySWZGUHppN3d6dlZzWmg3WQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F320" t="n">
+        <v>7</v>
+      </c>
+      <c r="G320" s="2" t="n">
+        <v>46028.91387731482</v>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="inlineStr">
+        <is>
+          <t>Supply_Chain</t>
+        </is>
+      </c>
+      <c r="B321" t="inlineStr">
+        <is>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+        </is>
+      </c>
+      <c r="C321" t="inlineStr">
+        <is>
+          <t>Philippine antitrust commission clears EMIF II–Ayala logistics joint venture - MLex</t>
+        </is>
+      </c>
+      <c r="D321" t="inlineStr">
+        <is>
+          <t>Wed, 07 Jan 2026 01:12:00 GMT</t>
+        </is>
+      </c>
+      <c r="E321" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxPM2tHMWxnd1V0MXpUOWdiWU5iX0hhMGFwaGRtTWdHeFRDZ0hiY1N0LXZlTnhfRzJrVE40c1NZaVhfeDdZS21GeWE4SGphaFBRX0JlQmM5M2I5WUVaaklEZjNYd05QNFpIcnVfZjJJNTE0NDJxTmwyVWtkck8waDNrRjY1NndsS29jaU52OUtZRW9TQjdzOWFRLVd6WlRRN1lXWWpUbTY5bE5QWDVjTWEza29NZzgweXBITnNB0gFaQVVfeXFMTXA5RTF4d3RJdHExWWNjeWZ3UXhsdUlIMGxKVjVlcUtPcHNQRlJyeUNOR1MzaUs0aVVTc2Y2RmVBSklTSHdqb2tDSzdPUzJOMmQ5bUpVV1lyeEt3?oc=5</t>
+        </is>
+      </c>
+      <c r="F321" t="n">
+        <v>7</v>
+      </c>
+      <c r="G321" s="2" t="n">
+        <v>46029.05</v>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="inlineStr">
+        <is>
+          <t>Supply_Chain</t>
+        </is>
+      </c>
+      <c r="B322" t="inlineStr">
+        <is>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+        </is>
+      </c>
+      <c r="C322" t="inlineStr">
+        <is>
+          <t>Jaguar Land Rover sales slump sharply amid US tariffs and cyber-attack - The Guardian</t>
+        </is>
+      </c>
+      <c r="D322" t="inlineStr">
+        <is>
+          <t>Tue, 06 Jan 2026 08:30:44 GMT</t>
+        </is>
+      </c>
+      <c r="E322" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxNanU1SnlFQ3ZwOW50aHE1ajZ5REowdEFPVm5RQV9DejU2SzVxcmcySEVrUTFBRGhLX2NjVUVPeGQ2Rk0yZEw5Y2gwcTVsQTlxbThndGYwNXlYbmZ0dUJ3MWhTczRUSEJiOFNHR1FxSGxMbGpGQWt5WlJjUzd6eUJ1NlplUWNoWldhemJMOWY3SW1xbkRfYS1pNFk1Q1ZsWkNyV29CNFpIYkdLeWF1bDhWU0NoZnliZw?oc=5</t>
+        </is>
+      </c>
+      <c r="F322" t="n">
+        <v>7</v>
+      </c>
+      <c r="G322" s="2" t="n">
+        <v>46028.35467592593</v>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="inlineStr">
+        <is>
+          <t>Supply_Chain</t>
+        </is>
+      </c>
+      <c r="B323" t="inlineStr">
+        <is>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+        </is>
+      </c>
+      <c r="C323" t="inlineStr">
+        <is>
+          <t>Progress Despite Fragmentation: The Energy Transition to 2030 - BloombergNEF</t>
+        </is>
+      </c>
+      <c r="D323" t="inlineStr">
+        <is>
+          <t>Tue, 06 Jan 2026 14:51:52 GMT</t>
+        </is>
+      </c>
+      <c r="E323" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxNaHkzMHZ0c2pibDA4WFI2b1kydzNHWTRlQ1EyQmRaaXdqbHFpb0sxa09YaUxUVGlHT1RrbE9adTRoVm00aGFaR2dNZ05qMlQtTFliN05FOUNXUEdSd2dDbktRT0c2clc0V2tRSk1LMGZzS1dPRDhhUlEyRWh6aG5LeFU4Q2k4dXVzWGRFQTNWWHVvS3MwbnVVajFuYUxqeXo0VTRYTlY0UGZKQQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F323" t="n">
+        <v>7</v>
+      </c>
+      <c r="G323" s="2" t="n">
+        <v>46028.61935185185</v>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="inlineStr">
+        <is>
+          <t>Supply_Chain</t>
+        </is>
+      </c>
+      <c r="B324" t="inlineStr">
+        <is>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+        </is>
+      </c>
+      <c r="C324" t="inlineStr">
+        <is>
+          <t>US tariffs that are at risk of court-ordered refunds exceed $133.5 billion - Reuters</t>
+        </is>
+      </c>
+      <c r="D324" t="inlineStr">
+        <is>
+          <t>Tue, 06 Jan 2026 21:20:01 GMT</t>
+        </is>
+      </c>
+      <c r="E324" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxNSFJ1aThqUkhpMFdoMmZKZm9LbjdLRXpqZkFMNWRWUHoyclliSHJiTjVhVF9nYmViZzF1WEt5Rmh4NDJBMEtnZjdMNXlnNUFReTFDTW5JWnhvUmZOQk1KVWx1WmVRcUtaVEQtNTRrTUtIUkZQMmZxZE1mcWZVQXNrQkhaZGF3dHc1UUlDa3AwUjViRHJNWmxtTmhEekFBYW5icGhvbk9maVpvQXJxVkNnRw?oc=5</t>
+        </is>
+      </c>
+      <c r="F324" t="n">
+        <v>7</v>
+      </c>
+      <c r="G324" s="2" t="n">
+        <v>46028.88890046296</v>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="inlineStr">
+        <is>
+          <t>Supply_Chain</t>
+        </is>
+      </c>
+      <c r="B325" t="inlineStr">
+        <is>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+        </is>
+      </c>
+      <c r="C325" t="inlineStr">
+        <is>
+          <t>V.Group buys fuel efficiency firm founded by Maersk Tankers - Shipping Telegraph</t>
+        </is>
+      </c>
+      <c r="D325" t="inlineStr">
+        <is>
+          <t>Wed, 07 Jan 2026 01:50:28 GMT</t>
+        </is>
+      </c>
+      <c r="E325" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxPd2VHVEVPSHF5Z2xWSTFkSmdHSnp6VDZrMWFOa3paOVJPa3c0b0VCRVg5d0YyczBLdklHR2xHd0lYWmtlZ0x0ZzVLTXZ0V1czc3FpWGt5YkJtV2MwYnV1WXR6QkE1dFN3WTBLQTBpRk90OURtUmQwNEVhaFhDTVJsSVhJdnNQMndITXNLaFhWUGZjb0M4MTNoLVFVV2Y5a2lmT2sza3lyZHVvR1E?oc=5</t>
+        </is>
+      </c>
+      <c r="F325" t="n">
+        <v>7</v>
+      </c>
+      <c r="G325" s="2" t="n">
+        <v>46029.07671296296</v>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="inlineStr">
+        <is>
+          <t>Supply_Chain</t>
+        </is>
+      </c>
+      <c r="B326" t="inlineStr">
+        <is>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+        </is>
+      </c>
+      <c r="C326" t="inlineStr">
+        <is>
+          <t>US slashes proposed tariffs on Italian pasta imports - BBC</t>
+        </is>
+      </c>
+      <c r="D326" t="inlineStr">
+        <is>
+          <t>Fri, 02 Jan 2026 14:20:35 GMT</t>
+        </is>
+      </c>
+      <c r="E326" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTE5IU0doenhfTjUzX05ZMVpyOHJYWkVmaHhxYTVrVERCTFJLWEtxX1ZCLUk0OGNkSXByZXpydURPNEFJMHlCOElaMWhDdjNhZkF4Y05YazNHQThNZ9IBX0FVX3lxTE1DU1ZZenoweUpHVEV2NmhCelJvVW1KV3lIeDZGSXJDbGxPVmZWWHN1TU5DQ3NMaVFmcE8zZ21TTWF4SHhYSmZEajRMRmUzd0tkT3NTREVzcXZlVTJETjEw?oc=5</t>
+        </is>
+      </c>
+      <c r="F326" t="n">
+        <v>7</v>
+      </c>
+      <c r="G326" s="2" t="n">
+        <v>46024.59762731481</v>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="inlineStr">
+        <is>
+          <t>Supply_Chain</t>
+        </is>
+      </c>
+      <c r="B327" t="inlineStr">
+        <is>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+        </is>
+      </c>
+      <c r="C327" t="inlineStr">
+        <is>
+          <t>Punta Arenas port upgrade enables larger cruise ships to dock - Seatrade Cruise News</t>
+        </is>
+      </c>
+      <c r="D327" t="inlineStr">
+        <is>
+          <t>Tue, 06 Jan 2026 22:05:42 GMT</t>
+        </is>
+      </c>
+      <c r="E327" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxNWF96M0NVSV9weFo5cUhFNUFfUE5GZk04YWhqOVlFMDEwbU5IZGxPSGQ5aUZ5ZlFHdklhU19sajk1cW5haTZfVktBOWg2SWo3dThjS2U0V0hIbF9qZGNjdDE2OGc0QlE2QnljWVJkVy1jajNrU2U1VmJ3M09USkNvRlFrMmtHZ2lDVm5yWHA4QjdTc25QWDdCeG1nd1J0S2tUY2VSVjhNV25hQlRSMkVpU0hn?oc=5</t>
+        </is>
+      </c>
+      <c r="F327" t="n">
+        <v>7</v>
+      </c>
+      <c r="G327" s="2" t="n">
+        <v>46028.920625</v>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="inlineStr">
+        <is>
+          <t>Supply_Chain</t>
+        </is>
+      </c>
+      <c r="B328" t="inlineStr">
+        <is>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+        </is>
+      </c>
+      <c r="C328" t="inlineStr">
+        <is>
+          <t>$500M in Telegram Bonds Frozen in Russia Due to Sanctions – FT - The Moscow Times</t>
+        </is>
+      </c>
+      <c r="D328" t="inlineStr">
+        <is>
+          <t>Tue, 06 Jan 2026 12:13:00 GMT</t>
+        </is>
+      </c>
+      <c r="E328" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxOMkdfaElKblBHdzFrZXVZYXVNUDZuaU1rWVE1R0Y5VVdrWHdQS0V0TjdSdXl2MzJVeWJKMWtkREFKRTluZGpNTGNCa0JDdnJZY3hpbWxjbm9NNFRnelJDRFF0QVNNTWlRN1dwMF9PUDlmVGpzOGItVDAtZlJaNU5qUXpyTV9mcklZQlFPX2tBbWRqRTRQMEZQOVpwRmR6R0VWMUF3ai03SmlkZ09a?oc=5</t>
+        </is>
+      </c>
+      <c r="F328" t="n">
+        <v>7</v>
+      </c>
+      <c r="G328" s="2" t="n">
+        <v>46028.50902777778</v>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="inlineStr">
+        <is>
+          <t>Supply_Chain</t>
+        </is>
+      </c>
+      <c r="B329" t="inlineStr">
+        <is>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+        </is>
+      </c>
+      <c r="C329" t="inlineStr">
+        <is>
+          <t>European tanker owners regain share in Russian oil trade - Shipping Telegraph</t>
+        </is>
+      </c>
+      <c r="D329" t="inlineStr">
+        <is>
+          <t>Wed, 07 Jan 2026 02:00:30 GMT</t>
+        </is>
+      </c>
+      <c r="E329" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxPMXV3N0d1MVE2Y0xCRDBsR2ItaG5VZ0VlMndXel8tMjg0cllfR0VEMXJDa3YwVDJSZ3I3Qlo3alpEcm91eVo0Xzg2MlhoLXJnbGRUVXQ4V1ROX2RQemd3WEZ5MzFwMWJoajlUTXZ4YlBSa2FqZXFZaThEZmNtUUZxdmJTWmx5OUNGVUVwVFFERlZYWldsdDF5c3pmYw?oc=5</t>
+        </is>
+      </c>
+      <c r="F329" t="n">
+        <v>7</v>
+      </c>
+      <c r="G329" s="2" t="n">
+        <v>46029.08368055556</v>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="inlineStr">
+        <is>
+          <t>Supply_Chain</t>
+        </is>
+      </c>
+      <c r="B330" t="inlineStr">
+        <is>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+        </is>
+      </c>
+      <c r="C330" t="inlineStr">
+        <is>
+          <t>What Can History Tell Us About Tariff Shocks? - Federal Reserve Bank of San Francisco</t>
+        </is>
+      </c>
+      <c r="D330" t="inlineStr">
+        <is>
+          <t>Mon, 05 Jan 2026 18:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="E330" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxPaGkxVU84ZEFNbS1NenBjdzBNZWZyX0dUYm12WU5rYTEzaGw3dTNHNEpDVFNscTNlNzYxX0N0bW9udzZTZXlEalM0VDZ2dlF1NGZzZGxBbGlqblVCU1c3dnFWZi1xU2g3NVJWUnp4UGtUU0JrVzFmSzJjcHZkVjZraUxRNDBocWlLOWpjRERDVUYxTDBjXzVpSHhnODFSVzlNVmtjc2wzajlkSWlMMkpZdVFWeVVyU1k4UVU5aVMta2tFY0Nj?oc=5</t>
+        </is>
+      </c>
+      <c r="F330" t="n">
+        <v>7</v>
+      </c>
+      <c r="G330" s="2" t="n">
+        <v>46027.75</v>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="inlineStr">
+        <is>
+          <t>Supply_Chain</t>
+        </is>
+      </c>
+      <c r="B331" t="inlineStr">
+        <is>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+        </is>
+      </c>
+      <c r="C331" t="inlineStr">
+        <is>
+          <t>Trump's trade tariffs are turning out to be a huge dud and Wall Street is pretty happy about it - Fortune</t>
+        </is>
+      </c>
+      <c r="D331" t="inlineStr">
+        <is>
+          <t>Tue, 06 Jan 2026 11:23:00 GMT</t>
+        </is>
+      </c>
+      <c r="E331" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiggFBVV95cUxQOC1XY3c4ZVBQd1ViUEpNN0p4Z1FQYkQ0a0hfb3gyN2xRc3lWUkpYejN0WEtBNGRESE8zQ3NveWJpNnZtOF9mTFdHVVhEWGdJcHUyMEhjdng2VE1sR01ZYm13eENiWk0yMEVhZ2VGRDZuWnhfSU1IYzQwN3h0bkN5eVdB?oc=5</t>
+        </is>
+      </c>
+      <c r="F331" t="n">
+        <v>7</v>
+      </c>
+      <c r="G331" s="2" t="n">
+        <v>46028.47430555556</v>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="inlineStr">
+        <is>
+          <t>Supply_Chain</t>
+        </is>
+      </c>
+      <c r="B332" t="inlineStr">
+        <is>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+        </is>
+      </c>
+      <c r="C332" t="inlineStr">
+        <is>
+          <t>Trump's 2026 Alcohol Tariffs Are Coming — Here's What'll Hurt The Most - HuffPost</t>
+        </is>
+      </c>
+      <c r="D332" t="inlineStr">
+        <is>
+          <t>Tue, 06 Jan 2026 12:00:17 GMT</t>
+        </is>
+      </c>
+      <c r="E332" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxPN0xncDJmd2hSWFZPMWl6cF91R0dyaTlmVHNoLUdHQ0hXMnNkVXg0cklfUFkwY1JKd01lU05mQlg0TExlT1k5Ujl1ank0c1FEZUlIeEJQdUpkQzB2N1ZNN2tDaGdKMm9FbVBCNVBITi15cmlreTNudnRubDRSTkVKbTF3c0VxUG1JUXdidTZ2MjNyczlYOGF6ZnJMMW5CcExRRTZnTUVvcG9OamvSAbABQVVfeXFMTS0ySzdXdC00NzQwMUFWWnBWSEdGN2ctc1BoY3hTSWMzdUhXOXRhR1NGblpFWWd5ZThSbkZIYjNfMEZyZ3VUTUVRSkFpYmRBZndQcWlWakFBUXl6M2REN0hZcXJLdXAzSHByaWd3V0ZGWkVobVpzZmFRX2V6dkRMUWc0V0dhMU9aV21BZk56dnAySUtpek9KR2toU3I3ckwzM3ZteDB2cXpuUWgzU3JQUHo?oc=5</t>
+        </is>
+      </c>
+      <c r="F332" t="n">
+        <v>7</v>
+      </c>
+      <c r="G332" s="2" t="n">
+        <v>46028.50019675926</v>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="inlineStr">
+        <is>
+          <t>Supply_Chain</t>
+        </is>
+      </c>
+      <c r="B333" t="inlineStr">
+        <is>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+        </is>
+      </c>
+      <c r="C333" t="inlineStr">
+        <is>
+          <t>Wind turbine almost as tall as Humber Bridge approved at Port of Immingham - Grimsby Live</t>
+        </is>
+      </c>
+      <c r="D333" t="inlineStr">
+        <is>
+          <t>Tue, 06 Jan 2026 14:50:00 GMT</t>
+        </is>
+      </c>
+      <c r="E333" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMilgFBVV95cUxOQTJWWktaZllqRVhtQUZFV2V6VzRJZGRGRWpRa2tHYnpqaUtYYzgzVnVtVUliaHpUUVlLVy1iczNXTU9iVzl3UDZCdU45c192aGJ5aTlqTEZHMktDME9tNGRHaUZ5VzlXcEJrcHlqQTFhandRQ1YzcmZZWHc4ZURXUzZMaWluVmc3cjAyX0w3YzNHS25NYlHSAZsBQVVfeXFMTnN2T2M2UHBIMlUtVUtzM05tQml5X1ZrOUdsMDZCRVhnaEtHRkF0OFZsbERGOGlaZmJmM2I3QlFXVm43b2VXMUVDMDh4Tm9HNUJ0ZGJPNnV4ckhYVERCWlcxTW5Val83WUFhSU1iV0pBRnF6ak9KVWJuOVlTRXBrRDdqX0Vld2pUclRXaWp1aG5tYmhEbVI0UjdwVzA?oc=5</t>
+        </is>
+      </c>
+      <c r="F333" t="n">
+        <v>7</v>
+      </c>
+      <c r="G333" s="2" t="n">
+        <v>46028.61805555555</v>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="inlineStr">
+        <is>
+          <t>Supply_Chain</t>
+        </is>
+      </c>
+      <c r="B334" t="inlineStr">
+        <is>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+        </is>
+      </c>
+      <c r="C334" t="inlineStr">
+        <is>
+          <t>Celebrating 25 Years of Leadership in Freight Advocacy - The Maritime Executive</t>
+        </is>
+      </c>
+      <c r="D334" t="inlineStr">
+        <is>
+          <t>Wed, 07 Jan 2026 00:41:59 GMT</t>
+        </is>
+      </c>
+      <c r="E334" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxOYTJWTTFHWXNuZm14b1FqQmF3TkRycWJaaUNrelNBcm9BdUJNelpTUHdHZkRnd2g0dm8wWlE1UU43bktESFdldVBxM1BNclpVZTY1U0RSOGtNZFJ4bnJKVWVhUnBWbjRpbS1ZUkxDemFoY1pLbDY1QmlOeVNWTktxOTB6SG15amt4UEpMaVNSVS01NFE3eW8yRXlTRQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F334" t="n">
+        <v>7</v>
+      </c>
+      <c r="G334" s="2" t="n">
+        <v>46029.02915509259</v>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="inlineStr">
+        <is>
+          <t>Supply_Chain</t>
+        </is>
+      </c>
+      <c r="B335" t="inlineStr">
+        <is>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+        </is>
+      </c>
+      <c r="C335" t="inlineStr">
+        <is>
+          <t>What will happen to oil tankers subject to US sanctions in Venezuela? - Shipping Telegraph</t>
+        </is>
+      </c>
+      <c r="D335" t="inlineStr">
+        <is>
+          <t>Wed, 07 Jan 2026 02:00:30 GMT</t>
+        </is>
+      </c>
+      <c r="E335" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxQeXdBQWpIOUswOExFdE0xM2hpaXRHTkFEVzN2VWJPcXIxaUxkR3BvUk5PSFAyRXh0NG03NDc4enpEa2FIWWVFM2dFOGpPajRiVDRrZURoRmk0ZXlOUWVWQUluenhQbTlHYllYc2dEVFBScUZGWm13Si1RY244QTBNbWt1SnNrdkV4Qk9SVlhXZzQydVJpY2NNMDhPdzhfOVhxZzhPTXdmUUhlRG1ua2xwWkpFajl2NW5DVGxSWjZYOG4?oc=5</t>
+        </is>
+      </c>
+      <c r="F335" t="n">
+        <v>7</v>
+      </c>
+      <c r="G335" s="2" t="n">
+        <v>46029.08368055556</v>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="inlineStr">
+        <is>
+          <t>Supply_Chain</t>
+        </is>
+      </c>
+      <c r="B336" t="inlineStr">
+        <is>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+        </is>
+      </c>
+      <c r="C336" t="inlineStr">
+        <is>
+          <t>Russia’s Arctic Empire Is Crumbling—Rotting Ports, Sanctions, and China’s Silence - UNITED24 Media</t>
+        </is>
+      </c>
+      <c r="D336" t="inlineStr">
+        <is>
+          <t>Tue, 06 Jan 2026 14:55:22 GMT</t>
+        </is>
+      </c>
+      <c r="E336" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMivgFBVV95cUxNMG1FWDRaQnpmMXpGc3VIY21sYS14SERPMDNqVnpLWDEydVhBcWg0M1U3ZVFoaC1peVMyRXVRRDB5NEZFMTRjWURKNFlZUFBQaUNCbWtmREpIUGdrT3NNNUVucy1QVERuOHZvWUMyQTZabkNJSnRRSGo1OVJmNkZGWVdWeUJBSUJmVnk1OF9XRXRCWFBDOUdlaWdlSkpSWEltaEFKWlBiVGF6aElSYmxoc1ZZQUh3anBGUTh0a1lR?oc=5</t>
+        </is>
+      </c>
+      <c r="F336" t="n">
+        <v>7</v>
+      </c>
+      <c r="G336" s="2" t="n">
+        <v>46028.6217824074</v>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="inlineStr">
+        <is>
+          <t>Supply_Chain</t>
+        </is>
+      </c>
+      <c r="B337" t="inlineStr">
+        <is>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+        </is>
+      </c>
+      <c r="C337" t="inlineStr">
+        <is>
+          <t>News | Industrial tenants not rushing to lease bulk logistics space in North Texas - CoStar</t>
+        </is>
+      </c>
+      <c r="D337" t="inlineStr">
+        <is>
+          <t>Tue, 06 Jan 2026 22:18:35 GMT</t>
+        </is>
+      </c>
+      <c r="E337" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxPLUlab0ZjeDRoOE5fM2JKY2E0dUQtcDhJS1lsSHRURnNScF9aQjRkaFZEY1F3U294UXFRc2hyblI3ZWpLbXNjTXRKb2diWUdlcU1YbW9mMmllODhFUy05dFV2NzFJNndvMTZfU2lQNUZWeXd2MG9qWm1YRXp6dnRYVERWLTRBWVNIRzVRbGE2UXVzMkE1ZGxZU21VUnY0MjFGbHBXbTNHNmZwcVhTaFVibkI1YXNEWms?oc=5</t>
+        </is>
+      </c>
+      <c r="F337" t="n">
+        <v>7</v>
+      </c>
+      <c r="G337" s="2" t="n">
+        <v>46028.92957175926</v>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="inlineStr">
+        <is>
+          <t>Supply_Chain</t>
+        </is>
+      </c>
+      <c r="B338" t="inlineStr">
+        <is>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+        </is>
+      </c>
+      <c r="C338" t="inlineStr">
+        <is>
+          <t>Chevron continues to ship Venezuelan oil, but loading on hold for Chinese buyers, shipping data shows - Reuters</t>
+        </is>
+      </c>
+      <c r="D338" t="inlineStr">
+        <is>
+          <t>Tue, 06 Jan 2026 17:24:09 GMT</t>
+        </is>
+      </c>
+      <c r="E338" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMizAFBVV95cUxNUHBvR3dmekVhOGt5ckd3YURFN1Rpa1FpQm1fakdEMUpITGZNbk1QY3VaQVctTGhDSHVld1RYMF9sN3B5SXRwMWFTWUx6YVhSa1pzbDlYa08xeEFseV9NNFlsOUktZEhWQzBzRnZNRzd4azVZOTgzbHJNNV9PdlRYbXdndjB3Vl9FMGxiZHYxSjIxaTVTMFhQNnZaVkhob2dTZGpJLVpFcURvNWNKUENtWjdrTEJ3TVFnVDZyM054Z2p3V29RT2lYalVsN00?oc=5</t>
+        </is>
+      </c>
+      <c r="F338" t="n">
+        <v>7</v>
+      </c>
+      <c r="G338" s="2" t="n">
+        <v>46028.72510416667</v>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="inlineStr">
+        <is>
+          <t>Supply_Chain</t>
+        </is>
+      </c>
+      <c r="B339" t="inlineStr">
+        <is>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+        </is>
+      </c>
+      <c r="C339" t="inlineStr">
+        <is>
+          <t>Millions on DWP benefits eligible for social tariffs broadband or phone - Beccles &amp; Bungay Journal</t>
+        </is>
+      </c>
+      <c r="D339" t="inlineStr">
+        <is>
+          <t>Tue, 06 Jan 2026 14:08:47 GMT</t>
+        </is>
+      </c>
+      <c r="E339" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxPajc2QTRDb3ZiZzNiNUU2VjYyVEdxNlNhT1UzbTQ1TE8tS25tWGtvbTFFc0M0TEZFM3BMbjBuaEVjVC01T3hKSkI0UF82Z0lKOXIzM2R0aHc5VnYyZlZudEw5eXRYem5IdmtpTHF2aWJwRlhqYmN2Z3R6T0xyRS1FV01LbWFGN0JQcTJqWVlMUWlFZF9zaE8wTGJOV01ZUGs3UjF4Wm1EcTNXMUw1YkpzM2RLcG91UUowaHRMaEhkVDY3eG9sMXc?oc=5</t>
+        </is>
+      </c>
+      <c r="F339" t="n">
+        <v>7</v>
+      </c>
+      <c r="G339" s="2" t="n">
+        <v>46028.58943287037</v>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="inlineStr">
+        <is>
+          <t>Supply_Chain</t>
+        </is>
+      </c>
+      <c r="B340" t="inlineStr">
+        <is>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+        </is>
+      </c>
+      <c r="C340" t="inlineStr">
+        <is>
+          <t>Former Wycombe Wanderers player named manager of League One team - Bucks Free Press</t>
+        </is>
+      </c>
+      <c r="D340" t="inlineStr">
+        <is>
+          <t>Tue, 06 Jan 2026 18:03:14 GMT</t>
+        </is>
+      </c>
+      <c r="E340" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxPb19Eb0QweWE1U21pUXFTdFBudVVQcTJIV1E0bjdpRkdRbmxsWV9RTjNNVmROQ1R4Wkd5QlpTeFRfaEZZU3JMTDNNOHYzSTQtTVhiSG8yQ2FRekJqTlIwNHk2S0QwOFljRGRrWXFpQl9sV1ZxaWJIUU9jc2tMaVdqcU5ZemJQUWZ6WC1kcjA5ZGlyWmlIVkw0WngyYWozWXE5U0E?oc=5</t>
+        </is>
+      </c>
+      <c r="F340" t="n">
+        <v>7</v>
+      </c>
+      <c r="G340" s="2" t="n">
+        <v>46028.75224537037</v>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="inlineStr">
+        <is>
+          <t>Supply_Chain</t>
+        </is>
+      </c>
+      <c r="B341" t="inlineStr">
+        <is>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+        </is>
+      </c>
+      <c r="C341" t="inlineStr">
+        <is>
+          <t>Should you invest in gold? - Yahoo Finance UK</t>
+        </is>
+      </c>
+      <c r="D341" t="inlineStr">
+        <is>
+          <t>Mon, 05 Jan 2026 16:30:12 GMT</t>
+        </is>
+      </c>
+      <c r="E341" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiggFBVV95cUxQMUZSdV9COHRmaWR1RFBhemVUdmpKbmVQZEFOamVzNFAwbnRPUDZfQXNtLVNUQnM1N0Z3cXczZUhpLTZwWGZwZFh5ZDJ5VkNWQUtLT1MtQmI2NW9GLVNsVnozYklpb3Y1WjZtUnRfUXI4VTFoaVVlVHVQRnJUY3pENWJB?oc=5</t>
+        </is>
+      </c>
+      <c r="F341" t="n">
+        <v>7</v>
+      </c>
+      <c r="G341" s="2" t="n">
+        <v>46027.68763888889</v>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="inlineStr">
+        <is>
+          <t>Supply_Chain</t>
+        </is>
+      </c>
+      <c r="B342" t="inlineStr">
+        <is>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+        </is>
+      </c>
+      <c r="C342" t="inlineStr">
+        <is>
+          <t>'Right-wing network' marked by inherent fragmentation, experts say - China Daily</t>
+        </is>
+      </c>
+      <c r="D342" t="inlineStr">
+        <is>
+          <t>Wed, 07 Jan 2026 01:29:00 GMT</t>
+        </is>
+      </c>
+      <c r="E342" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMifkFVX3lxTE5SYUV5OTREelNndTg3NTJqOEZMbjJpcktlSjdfUVJqejlyOXVsWmhVVkRfdmdmVGpReWluY01wXzJXNGNNZTUwRzNYalR6R1ZLcFVYdElib0dZbDNPLTM0RlpMT1BvTVFaeWNoNTFucHM3Njd1dnZBbjBRMGlnZw?oc=5</t>
+        </is>
+      </c>
+      <c r="F342" t="n">
+        <v>7</v>
+      </c>
+      <c r="G342" s="2" t="n">
+        <v>46029.06180555555</v>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="inlineStr">
+        <is>
+          <t>Supply_Chain</t>
+        </is>
+      </c>
+      <c r="B343" t="inlineStr">
+        <is>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+        </is>
+      </c>
+      <c r="C343" t="inlineStr">
+        <is>
+          <t>Qingdao Port debuts China's 1st vacuum-based automated mooring system - Nation Thailand</t>
+        </is>
+      </c>
+      <c r="D343" t="inlineStr">
+        <is>
+          <t>Wed, 07 Jan 2026 01:52:00 GMT</t>
+        </is>
+      </c>
+      <c r="E343" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiX0FVX3lxTFBQMWZKSDJrTXdzWmhETjJNLXh5aUNuU1BYNWpZZmFMRTRoUWFKWGhJaVNqWXVrZUtid3ViWTQ3bjhMUS1BeGx5RGRfTkhxWm1JOUFIUDdWbTRUUXNtVVdZ?oc=5</t>
+        </is>
+      </c>
+      <c r="F343" t="n">
+        <v>7</v>
+      </c>
+      <c r="G343" s="2" t="n">
+        <v>46029.07777777778</v>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="inlineStr">
+        <is>
+          <t>Supply_Chain</t>
+        </is>
+      </c>
+      <c r="B344" t="inlineStr">
+        <is>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+        </is>
+      </c>
+      <c r="C344" t="inlineStr">
+        <is>
+          <t>Bolton Wanderers' next Vertu Trophy opponents appoint new boss in Jon Brady - The Bolton News</t>
+        </is>
+      </c>
+      <c r="D344" t="inlineStr">
+        <is>
+          <t>Tue, 06 Jan 2026 15:42:24 GMT</t>
+        </is>
+      </c>
+      <c r="E344" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxORXN1bDI2Rm5BX0RMNG9mMkNuNV9jbWtGQVdFTVZ6U3gxMVp4bGF0VDBhYWFWaklUOHQ5UmFHMWROb2hvaXMyMUxjcHF6bFc2TG50R1VLZklEYmVjMjlOb05RcGNjU3BBU1JVcFRyTWtfaW5pVFZFUmNGZnFjRWFSM0E2NlhaaldMVXhTa3pPMnlVc0VNQ2JLQnQtWDFQT1JfZHc?oc=5</t>
+        </is>
+      </c>
+      <c r="F344" t="n">
+        <v>7</v>
+      </c>
+      <c r="G344" s="2" t="n">
+        <v>46028.65444444444</v>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="inlineStr">
+        <is>
+          <t>Supply_Chain</t>
+        </is>
+      </c>
+      <c r="B345" t="inlineStr">
+        <is>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+        </is>
+      </c>
+      <c r="C345" t="inlineStr">
+        <is>
+          <t>Trump warns of higher tariffs on India over Russian oil purchases - Reuters</t>
+        </is>
+      </c>
+      <c r="D345" t="inlineStr">
+        <is>
+          <t>Mon, 05 Jan 2026 08:47:16 GMT</t>
+        </is>
+      </c>
+      <c r="E345" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxNcnFQTDFyQ2JPTFZkdWpiclQ2QXd3cHgzVWt4TlNNeVZ1MkZ5aTF5YjI2UVczRjZ6OEpva1FLTG9DWG1wb1R6eHVaYVVWTXZjSW1WYzhiYUlMbERIMlkyWl8waklPOFhrMlNpYnBPUDkwUk1vaHpkdXFLRXlyTzlUdkV6bkM4WHpLeUFvd1lKMl9mamhTUzdBT3IwVVR2NE1lMGlGeXVDdHF6QWQxRTlSUA?oc=5</t>
+        </is>
+      </c>
+      <c r="F345" t="n">
+        <v>7</v>
+      </c>
+      <c r="G345" s="2" t="n">
+        <v>46027.36615740741</v>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="inlineStr">
+        <is>
+          <t>Supply_Chain</t>
+        </is>
+      </c>
+      <c r="B346" t="inlineStr">
+        <is>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+        </is>
+      </c>
+      <c r="C346" t="inlineStr">
+        <is>
+          <t>HCOB finances John T. Essberger chemical tanker newbuilding duo - Shipping Telegraph</t>
+        </is>
+      </c>
+      <c r="D346" t="inlineStr">
+        <is>
+          <t>Wed, 07 Jan 2026 01:55:47 GMT</t>
+        </is>
+      </c>
+      <c r="E346" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxOU0VNbldtLU5ueUZhdUkwa1c0VTctcjgtbXVVWl9xbWVvNTU3Y2FEX2Qtd0dYWjJJeGVVZkNzWVBNRGlqSGdiTDVXczZLQ0gzcVh2Y1N1TUR6OEdjMU9oZGNzc1lBZTh6ZmRreTVhdXRXUlRwQWJGNVdsb0d6a2FMNmgzeTk4Ry1NdU85aHR3b1U3dDg1OU44Y2VQR1Nsb256ai1R?oc=5</t>
+        </is>
+      </c>
+      <c r="F346" t="n">
+        <v>7</v>
+      </c>
+      <c r="G346" s="2" t="n">
+        <v>46029.08040509259</v>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="inlineStr">
+        <is>
+          <t>Supply_Chain</t>
+        </is>
+      </c>
+      <c r="B347" t="inlineStr">
+        <is>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+        </is>
+      </c>
+      <c r="C347" t="inlineStr">
+        <is>
+          <t>Korean Register welcomes Lee Yongsok as new chairman and CEO - Shipping Telegraph</t>
+        </is>
+      </c>
+      <c r="D347" t="inlineStr">
+        <is>
+          <t>Wed, 07 Jan 2026 01:40:27 GMT</t>
+        </is>
+      </c>
+      <c r="E347" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxNSXhWcVVHd2xrVnRYNmRucU43NzQtazNsWEN6RGRMajdWYzV0MlU1U1ZzelNVTElUWFlxbUt1Q08wdkh6WEEyYjRadUJ2eV9HZUNTaVhEVHV3QnZWUkJ1NFBqZUpUTldHcWZ4QUZ4M2l0LWx2Vk5JSUN1Mkx0T3ZqYzhjRXd6bEVoQmdQdVRXTEhVSmUwZ1FVa0ZEMXNyT21FZWZUQWJOVVQ3MTA5?oc=5</t>
+        </is>
+      </c>
+      <c r="F347" t="n">
+        <v>7</v>
+      </c>
+      <c r="G347" s="2" t="n">
+        <v>46029.06975694445</v>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="inlineStr">
+        <is>
+          <t>Supply_Chain</t>
+        </is>
+      </c>
+      <c r="B348" t="inlineStr">
+        <is>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+        </is>
+      </c>
+      <c r="C348" t="inlineStr">
+        <is>
+          <t>FTSE 100 posts best day in six months as stock market rally continues – as it happened - The Guardian</t>
+        </is>
+      </c>
+      <c r="D348" t="inlineStr">
+        <is>
+          <t>Tue, 06 Jan 2026 07:28:00 GMT</t>
+        </is>
+      </c>
+      <c r="E348" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi_gFBVV95cUxNVUl4RXR0VkJzZnB3MHlUcE43Y3diQ2NlckRnMGZZa3BGWVE2REhzWjJ3ZDlzSjZJU0t5dUthTGxjaU1Ma25lWFhocjZzT0RzTkY2MUxtRmhfSElRUGY5bjRyQmVuM1poa054OHRNamUyb3VYQWlEVE1uLWZERU5NOHJjd2w0Y0FXZWItRWhVeVdHSk5MRXRzNG9rYm5GZFpxNVNmS3VaSG52d2ZsV2IzUWRtV3FjaVYzMWQ3SUs0S3hiVTZrUW9fVVkzVkpweFIydlB0QmsxUlV0NnBCN0lhVW80cy1CbkZjSTQ4SDhaTzN0SE9fcmdweDhlYl9fZw?oc=5</t>
+        </is>
+      </c>
+      <c r="F348" t="n">
+        <v>7</v>
+      </c>
+      <c r="G348" s="2" t="n">
+        <v>46028.31111111111</v>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="inlineStr">
+        <is>
+          <t>Supply_Chain</t>
+        </is>
+      </c>
+      <c r="B349" t="inlineStr">
+        <is>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+        </is>
+      </c>
+      <c r="C349" t="inlineStr">
+        <is>
+          <t>Borr Drilling signs two drilling contracts in the Americas - Shipping Telegraph</t>
+        </is>
+      </c>
+      <c r="D349" t="inlineStr">
+        <is>
+          <t>Wed, 07 Jan 2026 01:40:27 GMT</t>
+        </is>
+      </c>
+      <c r="E349" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxOS2xjcnEtaHpISHVkUlRNOVZDdmFydDRCWDA5Q01MYU5vN1JENjlsS2I3LXJ1dTBMYjU5YXlvc0R3MHZFdGM2a0tFNVBxczRlNWg2aWJGYjljbC01Z21UeUV6RVg4b3l3RVdkdmF6NXhRZE82UDVSNERXYWhDNUQ4MXB3dFNDU1kwTXVjVU5mRlhTbG04a3FGTXRtMjd0WkQ5YjFBVHNn?oc=5</t>
+        </is>
+      </c>
+      <c r="F349" t="n">
+        <v>7</v>
+      </c>
+      <c r="G349" s="2" t="n">
+        <v>46029.06975694445</v>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="inlineStr">
+        <is>
+          <t>Supply_Chain</t>
+        </is>
+      </c>
+      <c r="B350" t="inlineStr">
+        <is>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+        </is>
+      </c>
+      <c r="C350" t="inlineStr">
+        <is>
+          <t>UN chief deeply concerned over ‘possible intensification of instability’ in Venezuela - UN News</t>
+        </is>
+      </c>
+      <c r="D350" t="inlineStr">
+        <is>
+          <t>Mon, 05 Jan 2026 16:43:08 GMT</t>
+        </is>
+      </c>
+      <c r="E350" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiV0FVX3lxTE1Qa1pkcmIxNXpjb2NXc194a0toaENwbWE1bU9WSmt3ZmFrTXlaWUhDeDB0Z3lNZFlPd01rb3NWbDRXSlk1Sll5UFpnV3ZMajhISU9wY29TWQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F350" t="n">
+        <v>7</v>
+      </c>
+      <c r="G350" s="2" t="n">
+        <v>46027.69662037037</v>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="inlineStr">
+        <is>
+          <t>Supply_Chain</t>
+        </is>
+      </c>
+      <c r="B351" t="inlineStr">
+        <is>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+        </is>
+      </c>
+      <c r="C351" t="inlineStr">
+        <is>
+          <t>Head of registry embroiled in sanctions chaos quits as government steps in - Tradewinds News</t>
+        </is>
+      </c>
+      <c r="D351" t="inlineStr">
+        <is>
+          <t>Mon, 05 Jan 2026 09:15:49 GMT</t>
+        </is>
+      </c>
+      <c r="E351" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMixwFBVV95cUxPaGk2TzVfMjBRLWc3LUxKX0J3N24yNGl1elpPZ2lTanBBZGJZdWwwbG9hczJJelhvSFg1MkRlY2NUZlc0Z0xCcFd0NlZrUk1qZE9QNkhOTEEtOWl5LS03YlJ4LW55M25uRlVvaGEyRG1QQm5INlA0QWJITWpPV3h6Tkw5dEtQT0Mxd2lHTk9fNXFCeEUyb01ndXJrRVlLUTRGQmREWDB0STB0ODJEaEFQeDBQNmFzUUJGZGVUUW92a3dsRHkyMXFN?oc=5</t>
+        </is>
+      </c>
+      <c r="F351" t="n">
+        <v>7</v>
+      </c>
+      <c r="G351" s="2" t="n">
+        <v>46027.3859837963</v>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="inlineStr">
+        <is>
+          <t>Protest</t>
+        </is>
+      </c>
+      <c r="B352" t="inlineStr">
+        <is>
+          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally)</t>
+        </is>
+      </c>
+      <c r="C352" t="inlineStr">
+        <is>
+          <t>Further strike dates for London Metropolitan Police staff announced - Unite the Union</t>
+        </is>
+      </c>
+      <c r="D352" t="inlineStr">
+        <is>
+          <t>Tue, 06 Jan 2026 12:35:57 GMT</t>
+        </is>
+      </c>
+      <c r="E352" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxNRFdHOFFUTExlMU5iamlFclB4em5yQngxdnVuNU1rbm9XSVJOaGNWTkxzVEd5VEpCSUZ4MjFLQ2VHV2VvNHJwajd5SnZxTHpiWFZtQlRZX3R3NEV5VFo1Rnl0bHZRRjVwaUVSTnNzeXNlX1MzWWhsVzF5ZTF5ZjRmTDBaa09BVnRjaGRqT05ISnI4Q19YYWczSTJRN2w5aWJCemt4NW41XzJySEI0YkowWWNETF9lbDVmZnBhTmlkR3RfSW14dmc?oc=5</t>
+        </is>
+      </c>
+      <c r="F352" t="n">
+        <v>7</v>
+      </c>
+      <c r="G352" s="2" t="n">
+        <v>46028.52496527778</v>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="inlineStr">
+        <is>
+          <t>Protest</t>
+        </is>
+      </c>
+      <c r="B353" t="inlineStr">
+        <is>
+          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally)</t>
+        </is>
+      </c>
+      <c r="C353" t="inlineStr">
+        <is>
+          <t>At least 36 people killed during Iran protests, rights group says - BBC</t>
+        </is>
+      </c>
+      <c r="D353" t="inlineStr">
+        <is>
+          <t>Tue, 06 Jan 2026 23:31:03 GMT</t>
+        </is>
+      </c>
+      <c r="E353" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTE40NVJGcnB5bDZxZE1yTXFWT3NFQTBfUHVJdnBfdmJIVzZpVlo4MGVva0ItblpTZTdlQW9Ic3h4U0g0T1RfTGVQT0FVZ2NsQWpScnA2UWNHMG55Z9IBX0FVX3lxTE5KOEpPY2x5aDFXMk1BN1pjSWJnQVUtNlpnMFNWYlZiUFpaV2lXbkd5cnpRaFdSRWxabEhMUGdNMmlrUkRoNi1odnllRXd6WmpzMGduNk12a3pFQjFjcmdZ?oc=5</t>
+        </is>
+      </c>
+      <c r="F353" t="n">
+        <v>7</v>
+      </c>
+      <c r="G353" s="2" t="n">
+        <v>46028.97989583333</v>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="inlineStr">
+        <is>
+          <t>Protest</t>
+        </is>
+      </c>
+      <c r="B354" t="inlineStr">
+        <is>
+          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally)</t>
+        </is>
+      </c>
+      <c r="C354" t="inlineStr">
+        <is>
+          <t>Iran orders probe into riot police hospital raid during protests - ایران اینترنشنال</t>
+        </is>
+      </c>
+      <c r="D354" t="inlineStr">
+        <is>
+          <t>Tue, 06 Jan 2026 13:53:20 GMT</t>
+        </is>
+      </c>
+      <c r="E354" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiUkFVX3lxTE1VZlZJbHJGanJfd2dUYmowcnd5TFBkV01UU0p0SVd6M25USGNQWkZ1RUc4R3h0cWtfR2JteldyVFVUWDJiREdJSWVwZzNyRTQwLUE?oc=5</t>
+        </is>
+      </c>
+      <c r="F354" t="n">
+        <v>7</v>
+      </c>
+      <c r="G354" s="2" t="n">
+        <v>46028.5787037037</v>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="inlineStr">
+        <is>
+          <t>Protest</t>
+        </is>
+      </c>
+      <c r="B355" t="inlineStr">
+        <is>
+          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally)</t>
+        </is>
+      </c>
+      <c r="C355" t="inlineStr">
+        <is>
+          <t>Police officer killed in western Iran amid anti-government protests - Anadolu Ajansı</t>
+        </is>
+      </c>
+      <c r="D355" t="inlineStr">
+        <is>
+          <t>Tue, 06 Jan 2026 17:28:52 GMT</t>
+        </is>
+      </c>
+      <c r="E355" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxNRDBqNngxZEdpZzFwWDNTWkVQNW0wckNpbGc5eEpzN1k5ZWRQMEE0ejBmVVJfalYzWEx5eTZnXy03bFpqeS11dlk1RWNvUGJ5UEpHSHR2THN6T3RsUnRfaDlEZ29iSU94LWxhR1JSQzZLTEtseE91MWdmTXJZb2pIdEdtMS11N2g1dUFTMUJ0YnpJc3dNeUxnejNQZUY5b2FZX2o2aVlEdjczZFdiajN0TzVn?oc=5</t>
+        </is>
+      </c>
+      <c r="F355" t="n">
+        <v>7</v>
+      </c>
+      <c r="G355" s="2" t="n">
+        <v>46028.72837962963</v>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="inlineStr">
+        <is>
+          <t>Protest</t>
+        </is>
+      </c>
+      <c r="B356" t="inlineStr">
+        <is>
+          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally)</t>
+        </is>
+      </c>
+      <c r="C356" t="inlineStr">
+        <is>
+          <t>Protests grow as Iran’s government makes meager offer amid tanking economy - Al Jazeera</t>
+        </is>
+      </c>
+      <c r="D356" t="inlineStr">
+        <is>
+          <t>Tue, 06 Jan 2026 22:51:01 GMT</t>
+        </is>
+      </c>
+      <c r="E356" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxPME1DOXAyTzR4Nko5TG0tU3NCZ2xxREN5N1ZxRkktZUVJa1ZDY0pTOWJXOFJRQ18tV2NGQmFHR25Kb3ZQM3pOQzBCY1YxaGo3b2FNaWNvblRvSC05OUNsczd3bl8wUnRTX1BnQUZOSmp5WU9scHhaV3JXUUc5WTAtMU9MWnNOdXlaMDFyMGFZZHYyQVprQWdvRmlJSkhvY3gyMklOZXBiRjQxODBJSHFyVTRGVdIBuAFBVV95cUxQYU9Qb3M3MVVUNmZoRGRCM2FqVWowdUdJUmVKbGZVZW1KdXRsbzNWODluOWlSQUh3RFp6NndlVmRJdTJFUk9ob0VuempSN1hEY2ZTNy1TcUpZenFudGRVUUZJT1N1Sy1ULUFXczBtak1sMU5qYWI4Mzc1T1o1amVlNDVzemJOUGw5bUViYW5obkVjQjA3V3FLZ0pERFBmeE5Dbjk0d3B4ck9ULW82SU8zbTFyMlhXRzlv?oc=5</t>
+        </is>
+      </c>
+      <c r="F356" t="n">
+        <v>7</v>
+      </c>
+      <c r="G356" s="2" t="n">
+        <v>46028.95209490741</v>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="inlineStr">
+        <is>
+          <t>Protest</t>
+        </is>
+      </c>
+      <c r="B357" t="inlineStr">
+        <is>
+          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally)</t>
+        </is>
+      </c>
+      <c r="C357" t="inlineStr">
+        <is>
+          <t>Essex Police strike against organised drug gangs with 460 arrests this year - Essex Police</t>
+        </is>
+      </c>
+      <c r="D357" t="inlineStr">
+        <is>
+          <t>Thu, 01 Jan 2026 08:05:00 GMT</t>
+        </is>
+      </c>
+      <c r="E357" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxPMFpvdTcxMWEtRnBWM28tTFN2X1hvbU1LM2RHUU5zeEQ3dE9nekxQMGVfRkx5eFRwVFZMWlpBSU1qYmM2SDRjMGVWNjdGRTh2dmVfWkFqQmhrS2xVRkF6WWxYb0hROFF4WERSWDh5RkFRSy03Q1lhTENUNXhGSDVNUHBYUVZiZFJWQ1d6aEppbHRZMW1BVFlUeGcycFV5NTRj?oc=5</t>
+        </is>
+      </c>
+      <c r="F357" t="n">
+        <v>7</v>
+      </c>
+      <c r="G357" s="2" t="n">
+        <v>46023.33680555555</v>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="inlineStr">
+        <is>
+          <t>Protest</t>
+        </is>
+      </c>
+      <c r="B358" t="inlineStr">
+        <is>
+          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally)</t>
+        </is>
+      </c>
+      <c r="C358" t="inlineStr">
+        <is>
+          <t>Police: Bus driver says he was attacked by protesters before running over, killing teen - The Times of Israel</t>
+        </is>
+      </c>
+      <c r="D358" t="inlineStr">
+        <is>
+          <t>Wed, 07 Jan 2026 00:14:07 GMT</t>
+        </is>
+      </c>
+      <c r="E358" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiZkFVX3lxTE10b1lBcWJwTFIxdzhudElvcElaMkM2dmFDa1pQTUo3em9FWjJtMnR0SWI4VG1JWGYwbjNKZ3ZQMW1MajM0d2J1SC1WaDVucUJqTUFnREw4RTFNd3dOcnJxdWQ1VTNSQdIBa0FVX3lxTE8tYkNKMGEyZE9rVWFOWkNDRE14TFJWak9EZnRwVnY5d2dOdmsydFZ4X0xMWDRvT0hBUVlEcnhqR0RqUU82NmpFSFdMb1BmZWYwblFLd1NLWlYwWVlBcDA5QTNNdDVpNnNvdTlB?oc=5</t>
+        </is>
+      </c>
+      <c r="F358" t="n">
+        <v>7</v>
+      </c>
+      <c r="G358" s="2" t="n">
+        <v>46029.00980324074</v>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="inlineStr">
+        <is>
+          <t>Protest</t>
+        </is>
+      </c>
+      <c r="B359" t="inlineStr">
+        <is>
+          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally)</t>
+        </is>
+      </c>
+      <c r="C359" t="inlineStr">
+        <is>
+          <t>Russian strikes on Kyiv kill two in first deadly attack on the capital - Vatican News</t>
+        </is>
+      </c>
+      <c r="D359" t="inlineStr">
+        <is>
+          <t>Tue, 06 Jan 2026 14:53:35 GMT</t>
+        </is>
+      </c>
+      <c r="E359" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxOUTROaTItemtoT2lPdWl1eDNmSjhrOTVBYlpQWTdRVnhVWVFmSjNIdnJBaXBSOEpCZmx4eG1QTmZNbDJNRGxESjFQT2pPbmNoYzVtTzlGUk4xbkVvb2RaV1ZpZ2UxclB5UVJHU3dOV0piNVJyYkZaQUY3ZGpDY3VlTUdaV0tId205OHJzekpYak9uTG83SGx4WXRZU1hEdDZuVWdwLWVEWkJkSW9PUktSM3hEMFdEam1M?oc=5</t>
+        </is>
+      </c>
+      <c r="F359" t="n">
+        <v>7</v>
+      </c>
+      <c r="G359" s="2" t="n">
+        <v>46028.62054398148</v>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="inlineStr">
+        <is>
+          <t>Protest</t>
+        </is>
+      </c>
+      <c r="B360" t="inlineStr">
+        <is>
+          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally)</t>
+        </is>
+      </c>
+      <c r="C360" t="inlineStr">
+        <is>
+          <t>Police update on arrested pair as baby remains in 'critical condition' - Cambs Times</t>
+        </is>
+      </c>
+      <c r="D360" t="inlineStr">
+        <is>
+          <t>Tue, 06 Jan 2026 10:12:35 GMT</t>
+        </is>
+      </c>
+      <c r="E360" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMikgFBVV95cUxQd1ZSbzJpNmphWHE5X2o0V2FMc3ZucUpJNjU0Tmt0NF85cURORUt3Zlcwd0ptcjVEa1RHbzlUR1RzbjJlY0REUjEyNTM3MU5IalVoWUtzNmpqVncwdzltZmhkajY2UWIyRnE2N3BmdS1DdDc3SUxxWEtqWi1RbjJrTFYtTmJWSXo0YXNTOTNZamRaZw?oc=5</t>
+        </is>
+      </c>
+      <c r="F360" t="n">
+        <v>7</v>
+      </c>
+      <c r="G360" s="2" t="n">
+        <v>46028.4254050926</v>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" t="inlineStr">
+        <is>
+          <t>Protest</t>
+        </is>
+      </c>
+      <c r="B361" t="inlineStr">
+        <is>
+          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally)</t>
+        </is>
+      </c>
+      <c r="C361" t="inlineStr">
+        <is>
+          <t>Police commissioner says extension ‘not about stopping free speech’ – as it happened - The Guardian</t>
+        </is>
+      </c>
+      <c r="D361" t="inlineStr">
+        <is>
+          <t>Tue, 06 Jan 2026 07:32:00 GMT</t>
+        </is>
+      </c>
+      <c r="E361" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMihAJBVV95cUxORzY1aVFDaHE0S0YwNmpnSWpTQklIWEw0Q3Q3NGtoNmNGNHR0ZF9nUUNVVGRYeURsYTVTTHZRUmE3ZmZTN0hRa0c1aGFMMWFyRVdzbkphOUQ2ZjRjdVNqdkc0WGstNkFWdnhZclJLSkZ6Y0FlWEkzbDNhN0U1YXFHVmRsVHBsbWdPdDlsT1lQVE1UUzZBc2luaHJwNjNYaHFFZ0ViUXhWSlEyMmJBUU0xcmZOSlBhUzI3TG93ZWJqQjFvbEhlWUpsM2tjZTRsbm04U1dQRDhRTkZmODVVSFRhblhWVmZ3bnRwMTg0VnROaDNuelMwb0ZQNjYzNGV6QkdqZ1FiWQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F361" t="n">
+        <v>7</v>
+      </c>
+      <c r="G361" s="2" t="n">
+        <v>46028.31388888889</v>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" t="inlineStr">
+        <is>
+          <t>Protest</t>
+        </is>
+      </c>
+      <c r="B362" t="inlineStr">
+        <is>
+          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally)</t>
+        </is>
+      </c>
+      <c r="C362" t="inlineStr">
+        <is>
+          <t>Pepper spray, assaults, detentions: a hunger strike protest turned ugly thanks to West Yorkshire Police - thecanary.co</t>
+        </is>
+      </c>
+      <c r="D362" t="inlineStr">
+        <is>
+          <t>Sun, 04 Jan 2026 18:50:44 GMT</t>
+        </is>
+      </c>
+      <c r="E362" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMihgFBVV95cUxOMGpoOUJFc0U1Nm8zNThvcFRJZndlcmtSZXRDRUhnMHU0T2x0MHlBTXNCYlg0d0JjWXhsZW9HMkJON3BvN2xxRUM0cWVUVUg5OHcwU2d3eUVTaGZVR0hzTTRrVFQ1U3g2MTU4aGNFZEtKR0RNQS1JVmdSOGRJLW1EN3h0YkxGQQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F362" t="n">
+        <v>7</v>
+      </c>
+      <c r="G362" s="2" t="n">
+        <v>46026.78523148148</v>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" t="inlineStr">
+        <is>
+          <t>Protest</t>
+        </is>
+      </c>
+      <c r="B363" t="inlineStr">
+        <is>
+          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally)</t>
+        </is>
+      </c>
+      <c r="C363" t="inlineStr">
+        <is>
+          <t>Trump White House attempts to rewrite history of Jan. 6, accuses Capitol Police of escalating tensions - ABC News</t>
+        </is>
+      </c>
+      <c r="D363" t="inlineStr">
+        <is>
+          <t>Wed, 07 Jan 2026 00:00:39 GMT</t>
+        </is>
+      </c>
+      <c r="E363" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxNU0tEaEJvOGVqamZxenhBSkh4bERQalp5bC10b0E3bGpTbkREelp1dlpDcWZqMUpZOWdtajdudXFUeTdOc2tIdDdmeTZuaUN6bjlONFR0YUxSSWdUYlVMRUpxb2F1YVZSdnlHOTl0QmNBSlR1dy0zVDRMcTdWMV85elEyY0pmRk9tTElIY1lmZW8tRnVnYm02SEJFaGhqVENh0gGmAUFVX3lxTE9ZVmZ3TXp5NTRzS2ZqTmdsSEFfVHZLeS1iYjNZWTd1akdMa1NfSExYZkNocE1fT1ZVeHA3RXFpZjdlRnE0c2lnbk9VOXhxUTI4am5GejFaT3lzMnZCUk9VMjJxbXpqUEFFeVdMLTh3dE04YnZHOWZZdnNfa0xQQXNvOEJRMndIRXBfS1h1MXBBbnQybWRfeTRyMFdNN0NaTjhqOEIxX0E?oc=5</t>
+        </is>
+      </c>
+      <c r="F363" t="n">
+        <v>7</v>
+      </c>
+      <c r="G363" s="2" t="n">
+        <v>46029.00045138889</v>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" t="inlineStr">
+        <is>
+          <t>Protest</t>
+        </is>
+      </c>
+      <c r="B364" t="inlineStr">
+        <is>
+          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally)</t>
+        </is>
+      </c>
+      <c r="C364" t="inlineStr">
+        <is>
+          <t>January 6: A Date Which Will Live in Infamy - The White House (.gov)</t>
+        </is>
+      </c>
+      <c r="D364" t="inlineStr">
+        <is>
+          <t>Tue, 06 Jan 2026 17:29:02 GMT</t>
+        </is>
+      </c>
+      <c r="E364" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiREFVX3lxTE5UWHVjRk9VY21yLTN2R1NDRDNZQWFjRTJTMGtnX1Q5aVZ5TS1SbWRpTF9WaEVJYkNQaXVycDlBUk1PM3Rr?oc=5</t>
+        </is>
+      </c>
+      <c r="F364" t="n">
+        <v>7</v>
+      </c>
+      <c r="G364" s="2" t="n">
+        <v>46028.72849537037</v>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" t="inlineStr">
+        <is>
+          <t>Protest</t>
+        </is>
+      </c>
+      <c r="B365" t="inlineStr">
+        <is>
+          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally)</t>
+        </is>
+      </c>
+      <c r="C365" t="inlineStr">
+        <is>
+          <t>Iran protests: UN warns against further bloodshed - UN News</t>
+        </is>
+      </c>
+      <c r="D365" t="inlineStr">
+        <is>
+          <t>Mon, 05 Jan 2026 20:55:39 GMT</t>
+        </is>
+      </c>
+      <c r="E365" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiV0FVX3lxTE9hVlNqa2RWbnRpZ2dzeWFBRnFVZmJBb1RRS05pbTVkUjNJcjAzTjVMOGl4WHNpQWs5VzVuOHNqYjBCb1pGXzFzVDZqQkhKRGVudU9sQnJzTQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F365" t="n">
+        <v>7</v>
+      </c>
+      <c r="G365" s="2" t="n">
+        <v>46027.87197916667</v>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" t="inlineStr">
+        <is>
+          <t>Protest</t>
+        </is>
+      </c>
+      <c r="B366" t="inlineStr">
+        <is>
+          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally)</t>
+        </is>
+      </c>
+      <c r="C366" t="inlineStr">
+        <is>
+          <t>Sydney protest restrictions extended for 14 days as activist group vows to file legal challenge this week - The Guardian</t>
+        </is>
+      </c>
+      <c r="D366" t="inlineStr">
+        <is>
+          <t>Tue, 06 Jan 2026 08:38:00 GMT</t>
+        </is>
+      </c>
+      <c r="E366" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi-wFBVV95cUxPTUQxZ3A2bDhuY1Q4MDRhV21EUG1tc2k1TDIyRE1qZzZGLVp2OU96MDJ3b0ZoQnFjVC1CVG40Yl9Mb3h3UXZJeVg4b3VDSFNEUWRCOFA1c2hrSHVXRFdOM3AxR05DZEd1d1N3bzNvc19iRFFxY28zQ28xTGNvc25zRl9ISlo4dFdVUXVwUTY4VkN3YlFRUVNiN3NHd1p2V0k4WUxTQ05ZR0RxQ2FzR3Q2UDNlb2R6ZFpoQVhiS0h3VGFHZm9LU3g0YlFZc3pWNy1pS0VNYy1mZEx0bTl5N0JYWUhZU1RGVUpfcjdtaExKSkVlN3pxbmlmaGIxZw?oc=5</t>
+        </is>
+      </c>
+      <c r="F366" t="n">
+        <v>7</v>
+      </c>
+      <c r="G366" s="2" t="n">
+        <v>46028.35972222222</v>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" t="inlineStr">
+        <is>
+          <t>Protest</t>
+        </is>
+      </c>
+      <c r="B367" t="inlineStr">
+        <is>
+          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally)</t>
+        </is>
+      </c>
+      <c r="C367" t="inlineStr">
+        <is>
+          <t>There's a new lightning capital of the US. It's no longer Florida - USA Today</t>
+        </is>
+      </c>
+      <c r="D367" t="inlineStr">
+        <is>
+          <t>Tue, 06 Jan 2026 22:50:00 GMT</t>
+        </is>
+      </c>
+      <c r="E367" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxQd3h2ZGlhRXVScDFKWWQ4OHhTN2llR1VJNmV4ZW5aUk1JbGh2cU1NNF91YnFQZ0tRWDR3cHFhR21fcHhieVBCenhWc3laZ21Idk9ENUpSbkZDVGFlajByUGE5WnhBWmlGQjJ0Sk1zLUhVTUxOZ05meUNwYWYtZ0dBOHFYbnhId0tZVTRZVlZyTXloYmJ4ZVJTeU9FQVdPZ2Nfbzhodk8wcFY?oc=5</t>
+        </is>
+      </c>
+      <c r="F367" t="n">
+        <v>7</v>
+      </c>
+      <c r="G367" s="2" t="n">
+        <v>46028.95138888889</v>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" t="inlineStr">
+        <is>
+          <t>Protest</t>
+        </is>
+      </c>
+      <c r="B368" t="inlineStr">
+        <is>
+          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally)</t>
+        </is>
+      </c>
+      <c r="C368" t="inlineStr">
+        <is>
+          <t>Protest organizer arrested mid-interview in Grand Rapids at rally calling for Maduro’s release - Michigan Advance</t>
+        </is>
+      </c>
+      <c r="D368" t="inlineStr">
+        <is>
+          <t>Tue, 06 Jan 2026 22:31:43 GMT</t>
+        </is>
+      </c>
+      <c r="E368" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiyAFBVV95cUxNa2lPQ0hoSHlPZzQxVTZzS0trRXdRX1lCVG9HUS1LRndkOWdMZHY3eW92VkNhcHJUdGZGR2t5bVRhb0VvY3EtUXJMYy00ZlB3c3phZUhsRWtiVjZUMkEtVldGNWVRSGtmcXlnR2JHVnhGclphQkRlanRJWkNSaFVyNkpjYnpMRVk2V09NZG1yMFhkWHVSeXRPd3hiTWRVdTFDRWc4MmVkWXl5WElqT2w4R2wzQTdxaUxDR0ljUU5OaWdsaTFxUHR3WQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F368" t="n">
+        <v>7</v>
+      </c>
+      <c r="G368" s="2" t="n">
+        <v>46028.93869212963</v>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" t="inlineStr">
+        <is>
+          <t>Protest</t>
+        </is>
+      </c>
+      <c r="B369" t="inlineStr">
+        <is>
+          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally)</t>
+        </is>
+      </c>
+      <c r="C369" t="inlineStr">
+        <is>
+          <t>Man charged after London restaurant patron hurls racial slurs, strikes worker - London Free Press</t>
+        </is>
+      </c>
+      <c r="D369" t="inlineStr">
+        <is>
+          <t>Tue, 06 Jan 2026 18:12:14 GMT</t>
+        </is>
+      </c>
+      <c r="E369" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxNamY2eHVkZEsxMGFxZFYyUFB5c1ZMblVSWVpKUTFBaVFjbXFvZnlOTHFReDF2SlVBSWJCdGVDRDJSWWZXVVBVaGhuVENseTYzUURLTXAtdGxCeVl6b0pxNHVHR3M3MjdnWEVtUHlqdk93OW1vTS1nOW1IZ3AwMVpwd0FNRWt0OVJnMnZHR1AwVmhmSG9nWG51SGJ2czR1SUhxSVBjZDBTRnh1bHhtSEoyVzlR?oc=5</t>
+        </is>
+      </c>
+      <c r="F369" t="n">
+        <v>7</v>
+      </c>
+      <c r="G369" s="2" t="n">
+        <v>46028.75849537037</v>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" t="inlineStr">
+        <is>
+          <t>Protest</t>
+        </is>
+      </c>
+      <c r="B370" t="inlineStr">
+        <is>
+          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally)</t>
+        </is>
+      </c>
+      <c r="C370" t="inlineStr">
+        <is>
+          <t>Furious Celtic fans face down police during front door protest - Daily Record</t>
+        </is>
+      </c>
+      <c r="D370" t="inlineStr">
+        <is>
+          <t>Sat, 03 Jan 2026 18:51:00 GMT</t>
+        </is>
+      </c>
+      <c r="E370" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxPRlBUcjY3bXY4UVNoUjlaVmpVb1lnbWpqdThDcXZ3TEdOZzBtTUtkQURQaFhrY25nM29HdmlKYUtheHRFWUd3dHZBdEhmU1dBc3BMTGU0NzZFUjlyLTJvdWlWZThSaUs3QVhtU3VkOXFjNUF2WnhiMVN3eFdZd3A4MWVwS2ZaU0JXTWhYLWtfUVB1bVJkMWswQXJXM1VaT1FPOXfSAacBQVVfeXFMTVI1MndhRUxTeTk5aG9MVGxUdER0eHBGR1BNcTFVbjFMZGJIS25OT1U5UVp2MUV1VzZkUUFJcDBWNDBSaU9PNWFRenJOX0FHWmZrcWdfd2hVTFNQcXVDd1RmeXY5Z0hFMzhKcUlRdi1ITm43SUlPX0ZXWnZ5TUZnOHNvOWo4UWt1OC1TNzZLVXlnT2JoYjFlR0ExY084Rkh6ZHpCY1Z2aTA?oc=5</t>
+        </is>
+      </c>
+      <c r="F370" t="n">
+        <v>7</v>
+      </c>
+      <c r="G370" s="2" t="n">
+        <v>46025.78541666667</v>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" t="inlineStr">
+        <is>
+          <t>Protest</t>
+        </is>
+      </c>
+      <c r="B371" t="inlineStr">
+        <is>
+          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally)</t>
+        </is>
+      </c>
+      <c r="C371" t="inlineStr">
+        <is>
+          <t>Woman wearing ‘globalise the intifada’ jacket among three arrested at Sydney protest against US action in Venezuela - The Guardian</t>
+        </is>
+      </c>
+      <c r="D371" t="inlineStr">
+        <is>
+          <t>Sun, 04 Jan 2026 23:51:00 GMT</t>
+        </is>
+      </c>
+      <c r="E371" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxONUxKR1Jzd1VKU294SFA2S0ZKM0JybTlrOU1BUUszY1hzQXRob1NsbTdza1FzNndtYmVONVQxcWNDSnNEYUFIQVV1V005RkRMckNzcFBPSjN5V0NwQjJGQ2tDczRFbFEwQkJTcVpjVUgySVFKaHhNdzh5TmVrY2FKd2J0QVhBSjVSMVQ2SVdNNzNHbHduQlZLbDU4QVVheWFiQTF3aWo4Rjk3QldaTXE2R3VQMDlCdlh3?oc=5</t>
+        </is>
+      </c>
+      <c r="F371" t="n">
+        <v>7</v>
+      </c>
+      <c r="G371" s="2" t="n">
+        <v>46026.99375</v>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" t="inlineStr">
+        <is>
+          <t>Protest</t>
+        </is>
+      </c>
+      <c r="B372" t="inlineStr">
+        <is>
+          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally)</t>
+        </is>
+      </c>
+      <c r="C372" t="inlineStr">
+        <is>
+          <t>Aviva shares edge up after Direct Line capital model nod, with March results next catalyst - ts2.tech</t>
+        </is>
+      </c>
+      <c r="D372" t="inlineStr">
+        <is>
+          <t>Tue, 06 Jan 2026 11:09:48 GMT</t>
+        </is>
+      </c>
+      <c r="E372" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxNOXp0T3kwYlByQnRqMG5PeEFYcWRJNFhFaVBWeUxONkd6NFg3eGFNcDdkcF9iQmNUbnFWc3Brc0RhcjVKS0F3UnR2SXQ5c2dVM3RoLVBUdVc2dlAxNnhHYVFtSDJJdDRvSUpERzAwa1JzS0FNWFNVN2ZKcVY3dGZwS1FUYXNhQVlZdDV4Z0FwYUgzZ1BjVEZIUU9jWnY4c0ZMS0I1ZUtPaHlLZE1VRG9J?oc=5</t>
+        </is>
+      </c>
+      <c r="F372" t="n">
+        <v>7</v>
+      </c>
+      <c r="G372" s="2" t="n">
+        <v>46028.46513888889</v>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" t="inlineStr">
+        <is>
+          <t>Protest</t>
+        </is>
+      </c>
+      <c r="B373" t="inlineStr">
+        <is>
+          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally)</t>
+        </is>
+      </c>
+      <c r="C373" t="inlineStr">
+        <is>
+          <t>Bangladesh police blame Awami League for student leader Hadi's murder - thefederal.com</t>
+        </is>
+      </c>
+      <c r="D373" t="inlineStr">
+        <is>
+          <t>Tue, 06 Jan 2026 14:55:58 GMT</t>
+        </is>
+      </c>
+      <c r="E373" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxNb1ZnYy10a0swVnprWlRqbWQ4OHRZTWFkVnZiUzg4ZDlwNzJIVzZzU0tKZVZ0eDZSclZ5dmllX3FpSHIxaWlacnN0X2tqYlJmeURibXU0NzZxRVJZRk5HV0VaMXRkbzJtVVB5M2sycTU4U1BMVWQ1OEpHYkVCWldJY21wdDRIUGxwX1R0ekdnOW5reVZuUmpwaGw0eDNVZkhxODc0eVV2eGJyUVZ3RVJr?oc=5</t>
+        </is>
+      </c>
+      <c r="F373" t="n">
+        <v>7</v>
+      </c>
+      <c r="G373" s="2" t="n">
+        <v>46028.62219907407</v>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B374" t="inlineStr">
+        <is>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+        </is>
+      </c>
+      <c r="C374" t="inlineStr">
+        <is>
+          <t>Policy trends in technology and telecommunications in 2026 - Telefónica</t>
+        </is>
+      </c>
+      <c r="D374" t="inlineStr">
+        <is>
+          <t>Tue, 06 Jan 2026 18:02:24 GMT</t>
+        </is>
+      </c>
+      <c r="E374" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxOSy1oaEJhTkgwRG5xclVWRW5uSGdFOUNXRW1XdWtYZkpWVmdXd2RvWmlPTURIdTY0LXBaWTNvYzJhZXdyWF9iZm9sM1dWNlM0MHFaNE52ekJCSXhYY3hLQ3hjNVE1T3JXZk01bGNnZTc5bEw3NHpoUGgxSjREMXlLdVB6NVVkLTZ0Q2ZpRlRFcTZtaXZfYmRMN1p6YWozMUhMRGwwSXB3?oc=5</t>
+        </is>
+      </c>
+      <c r="F374" t="n">
+        <v>7</v>
+      </c>
+      <c r="G374" s="2" t="n">
+        <v>46028.75166666666</v>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B375" t="inlineStr">
+        <is>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+        </is>
+      </c>
+      <c r="C375" t="inlineStr">
+        <is>
+          <t>Five Trends in AI and Data Science for 2026 | Thomas H. Davenport and Randy Bean - MIT Sloan Management Review</t>
+        </is>
+      </c>
+      <c r="D375" t="inlineStr">
+        <is>
+          <t>Tue, 06 Jan 2026 12:00:05 GMT</t>
+        </is>
+      </c>
+      <c r="E375" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMihwFBVV95cUxQNndhTkhudjNwMy1lYjhjcWl5azdhSTQyY1F2Y3Rud0FiZUtQczJ5N2doNmdZVl9zd1k5RWxCd3pITlBYdUxFNmZJcWRtQkFNWnYwSmhsdHoteFhuOUhMbi1Db0hQZUZmSldVWE5DRm50ZmllLV9Wbm1DeDhtMWp3VzZ5WHBocnc?oc=5</t>
+        </is>
+      </c>
+      <c r="F375" t="n">
+        <v>7</v>
+      </c>
+      <c r="G375" s="2" t="n">
+        <v>46028.50005787037</v>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B376" t="inlineStr">
+        <is>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+        </is>
+      </c>
+      <c r="C376" t="inlineStr">
+        <is>
+          <t>The problem with AI and ‘empathy’ - Financial Times</t>
+        </is>
+      </c>
+      <c r="D376" t="inlineStr">
+        <is>
+          <t>Tue, 06 Jan 2026 05:00:27 GMT</t>
+        </is>
+      </c>
+      <c r="E376" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMicEFVX3lxTE1SeUxZMUF3UDhuYmlCOG9rcE4zcXBWeUhTWTJIam13Q25oRFFOUUs0bkNjc0ZLbGRIS1MtVkc3VWxoLXRXUV8wT0tQeVpoNm84NUwyeTZUQXZDdjE1UDhYaGc0MW5KOUdzMFJFTGdoODU?oc=5</t>
+        </is>
+      </c>
+      <c r="F376" t="n">
+        <v>7</v>
+      </c>
+      <c r="G376" s="2" t="n">
+        <v>46028.20864583334</v>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B377" t="inlineStr">
+        <is>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+        </is>
+      </c>
+      <c r="C377" t="inlineStr">
+        <is>
+          <t>PepsiCo Announces Industry-First AI and Digital Twin Collaboration with Siemens and NVIDIA - PR Newswire</t>
+        </is>
+      </c>
+      <c r="D377" t="inlineStr">
+        <is>
+          <t>Tue, 06 Jan 2026 16:30:00 GMT</t>
+        </is>
+      </c>
+      <c r="E377" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi3wFBVV95cUxQcnNNX0Z0dFU3TFE2RnZ6OXdFWGpQNHNGTjIyWUlnLW9Wa3RyVEZFb1FUd002aDN4NnIzVGhYTy1ic0x0REJUcERBRGR0ZWRXbmN0WE9jV2FCVk9acmVLVWsxRFBfZUVVSHBaX0o2NjBrR2VhcGN0MERYajJEeGp6eE9OMXE0MnJDMWpxUElGejFOOG9tZ3NDczNULTlwdFh1MTJrWEhOazhabFpES2QtLTVncVU3LXV2Q04wWFdfcG9zck9tbnFTMXF1OGtObzFpQmJLRUNZYWxUS2Z3RG5R?oc=5</t>
+        </is>
+      </c>
+      <c r="F377" t="n">
+        <v>7</v>
+      </c>
+      <c r="G377" s="2" t="n">
+        <v>46028.6875</v>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B378" t="inlineStr">
+        <is>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+        </is>
+      </c>
+      <c r="C378" t="inlineStr">
+        <is>
+          <t>Ten AI regulatory upsets to prepare for in 2026 - TheBanker.com</t>
+        </is>
+      </c>
+      <c r="D378" t="inlineStr">
+        <is>
+          <t>Tue, 06 Jan 2026 18:16:39 GMT</t>
+        </is>
+      </c>
+      <c r="E378" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiekFVX3lxTE1NSmFxWC1NSGhBMmhiSW1FVW5TU2VZWTZHNWp4YTNxYkVGQlM0b2lIeFc2TFAtMEtsY0tVVXk1QVhZT3pkeU50OEl1OGVzY3V0TnE0RVl0Rld6U2xRTE4waVF4SXJoSkdYMHBSVjVnN3piajZ6QlBXeFJn?oc=5</t>
+        </is>
+      </c>
+      <c r="F378" t="n">
+        <v>7</v>
+      </c>
+      <c r="G378" s="2" t="n">
+        <v>46028.7615625</v>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B379" t="inlineStr">
+        <is>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+        </is>
+      </c>
+      <c r="C379" t="inlineStr">
+        <is>
+          <t>Exclusive: Wimbledon and IBM extend AI and cloud tech partnership - SportsPro</t>
+        </is>
+      </c>
+      <c r="D379" t="inlineStr">
+        <is>
+          <t>Tue, 06 Jan 2026 11:02:04 GMT</t>
+        </is>
+      </c>
+      <c r="E379" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxNRWRUOFZPZnlNRDVsTVFYMEZ6dzNQN0dmbnNQOXNvYVdMUGFMTmczTDcwMzdEQjRQbXhTcHlKN1pVQ2czemI4aTVaNFREdGFYSGlmSE5od2FRTTFQYV9ybVVSNlRrRUFHOHlJZFNoZ3RkYUg3YkJaVks1MkhMTmVnd2JsZ0tGS1kwQjRTdHM1Z0pHRm9Zb1pRQjlzZ1k2WW5MT3NKNFNSQ3o?oc=5</t>
+        </is>
+      </c>
+      <c r="F379" t="n">
+        <v>7</v>
+      </c>
+      <c r="G379" s="2" t="n">
+        <v>46028.45976851852</v>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B380" t="inlineStr">
+        <is>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+        </is>
+      </c>
+      <c r="C380" t="inlineStr">
+        <is>
+          <t>AI and the Human Condition - Stratechery by Ben Thompson</t>
+        </is>
+      </c>
+      <c r="D380" t="inlineStr">
+        <is>
+          <t>Mon, 05 Jan 2026 11:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="E380" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiZ0FVX3lxTE9FeFhaZWtlQzdJbURYeXg4MzVuQTBHdnRSWkdaVmoyYkc3S1NNY0lZcVBaZkEteGxRSHdEaGFzZnBLbmE5ZzhpUVNfRTlYZjZTQXozN2lZUXhTWHhfdlVpd3NrRlFDQUk?oc=5</t>
+        </is>
+      </c>
+      <c r="F380" t="n">
+        <v>7</v>
+      </c>
+      <c r="G380" s="2" t="n">
+        <v>46027.45833333334</v>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B381" t="inlineStr">
+        <is>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+        </is>
+      </c>
+      <c r="C381" t="inlineStr">
+        <is>
+          <t>42 Technology and Innatera partner to advance neuromorphic Edge AI - Cambridge Network</t>
+        </is>
+      </c>
+      <c r="D381" t="inlineStr">
+        <is>
+          <t>Tue, 06 Jan 2026 12:01:53 GMT</t>
+        </is>
+      </c>
+      <c r="E381" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxNSmFlOTNOdGk4ZFpHUFdiYndMY1RiZEUxWXMzY016V0NQRm5ScW80alJwbmc2cVhBWFNrNkxNelp6U2F6cmJhXzdfUGVaTTc4NGZvMVl4Z1Q2bnJVeEd1V0tjNWhWb0FNSlgwYlFna2tUMDhjNFdlaWc3NFhGdE4zX1c5NzBwUmVQb0NXY1dRb290V1FjUTE1c2RzQ0F1MFd0RTBDTmJxYkc?oc=5</t>
+        </is>
+      </c>
+      <c r="F381" t="n">
+        <v>7</v>
+      </c>
+      <c r="G381" s="2" t="n">
+        <v>46028.50130787037</v>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B382" t="inlineStr">
+        <is>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+        </is>
+      </c>
+      <c r="C382" t="inlineStr">
+        <is>
+          <t>NIST Publishes Preliminary Draft of Cybersecurity Framework Profile for Artificial Intelligence for Public Comment - Global Policy Watch</t>
+        </is>
+      </c>
+      <c r="D382" t="inlineStr">
+        <is>
+          <t>Tue, 06 Jan 2026 18:11:33 GMT</t>
+        </is>
+      </c>
+      <c r="E382" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi7gFBVV95cUxNeFJ4enMtQ25PaHdSSFVhMWJPNVpLNUdPdF9yZklhNnVQQ0thR3VqVkNMX3E3RG5WamdhdUl4eU9aY3FQMEVHNUhmenBpZmxXdmFLR2lYZFdKUnBvTUVRNjE3Z3d6clBtdDBqUDllbnowN2JaTlo2b2hBY3EyNUFqdWZKMjduY08wLXhKeG1EOTVlUVh1cDFjZXFtelNfUy1fTXBnUV9nWGRwV3B3eUhzWDg3Vk0yS094ZUNXRUlVS3Y5NXgwQ2M4ODBJMVcxZmRCYXpoMXNHMXZNa0pyYk5fZC1JM0RwLXdUa2N3dUVn?oc=5</t>
+        </is>
+      </c>
+      <c r="F382" t="n">
+        <v>7</v>
+      </c>
+      <c r="G382" s="2" t="n">
+        <v>46028.75802083333</v>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B383" t="inlineStr">
+        <is>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+        </is>
+      </c>
+      <c r="C383" t="inlineStr">
+        <is>
+          <t>Why Wealth Managers Should Think Differently About AI - MSCI</t>
+        </is>
+      </c>
+      <c r="D383" t="inlineStr">
+        <is>
+          <t>Tue, 06 Jan 2026 22:52:01 GMT</t>
+        </is>
+      </c>
+      <c r="E383" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxPblo0TUZHYU5kRzQ1eGU3Yl9LNzZoQy10dkdCbkg1eVZRUVZNYlA0alFSa3ZyUFJIQnA4VWxnaHJlaU9Lai1yWFRHQWRONGxTMFl6akFDTzJLMVlHY2FpRzhiTlRwSzVpcXZ5RFphb1YycWhiZ0tKZlZBaUtBbkgybzJyeFExSFBsWE9udkV4cVVNZzhOcEx3VmpXcFFjS2FHcVRKN0MwdUNSZw?oc=5</t>
+        </is>
+      </c>
+      <c r="F383" t="n">
+        <v>7</v>
+      </c>
+      <c r="G383" s="2" t="n">
+        <v>46028.95278935185</v>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B384" t="inlineStr">
+        <is>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+        </is>
+      </c>
+      <c r="C384" t="inlineStr">
+        <is>
+          <t>2026 Corporate Compass: Market resilience, AI and geopolitics - J.P. Morgan</t>
+        </is>
+      </c>
+      <c r="D384" t="inlineStr">
+        <is>
+          <t>Tue, 06 Jan 2026 20:57:50 GMT</t>
+        </is>
+      </c>
+      <c r="E384" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiiwFBVV95cUxOU1dJYmZyV1ZYYkY0dzk3QVNsLWFrcFpPRThVRFVJbjJUWUxnZ3FNME5vWU9SMUNPejB2M19kSDZQNnZnRk1Gc1RqTVZ5VjJrd0ZUdjI1RndmSW5VbnFzV1dhdjB6N1d2RGczbm53eDB3XzRhbHpHaEhRUF9EVlBlbE9aWWNpcXpMbFRv?oc=5</t>
+        </is>
+      </c>
+      <c r="F384" t="n">
+        <v>7</v>
+      </c>
+      <c r="G384" s="2" t="n">
+        <v>46028.87349537037</v>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B385" t="inlineStr">
+        <is>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+        </is>
+      </c>
+      <c r="C385" t="inlineStr">
+        <is>
+          <t>‘My Co-Worker Uses AI, and I’m Sick of Redoing Her Work’ - The Cut</t>
+        </is>
+      </c>
+      <c r="D385" t="inlineStr">
+        <is>
+          <t>Tue, 06 Jan 2026 17:00:03 GMT</t>
+        </is>
+      </c>
+      <c r="E385" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMif0FVX3lxTE9HYnNoSmtxdG10SHNCUkJRaXZrR3Z1MXc3anMyMlFzSmpmXzM4NnRDcUxpNG4yQno2ek5FQnBQSWEtZzhyQW9zbExnck51SVo0NmxHTWVWUGxKRkRlWTlXZWd2WjdISzNMNUlNYWY5LTlzX1Bldy01QzlkY3BlZWs?oc=5</t>
+        </is>
+      </c>
+      <c r="F385" t="n">
+        <v>7</v>
+      </c>
+      <c r="G385" s="2" t="n">
+        <v>46028.70836805556</v>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B386" t="inlineStr">
+        <is>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+        </is>
+      </c>
+      <c r="C386" t="inlineStr">
+        <is>
+          <t>Siemens and NVIDIA Expand Partnership to Build the Industrial AI Operating System - NVIDIA Newsroom</t>
+        </is>
+      </c>
+      <c r="D386" t="inlineStr">
+        <is>
+          <t>Tue, 06 Jan 2026 16:35:59 GMT</t>
+        </is>
+      </c>
+      <c r="E386" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxPUmJMaENXQXFzZHJTamNqcmtXT3E0bHNyM2RjZ1VnSEIzYUFXU2s0RGZ1MmZoWWlBMGY4OWlkbFJhUVdkNnNESTB4TWxqZkttZUtadWhGbWJaWHVQNGNzMnVsaXNTUzFIRnk3V1FpNVk0U3NjUk5kLVZXb3FjbzhGaGZVVlVNaXI4WjZLQWk5eDZlV2JYNzV5SHVWRHBwY1FSNDd5Z0Jn?oc=5</t>
+        </is>
+      </c>
+      <c r="F386" t="n">
+        <v>7</v>
+      </c>
+      <c r="G386" s="2" t="n">
+        <v>46028.6916550926</v>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B387" t="inlineStr">
+        <is>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+        </is>
+      </c>
+      <c r="C387" t="inlineStr">
+        <is>
+          <t>Generation AI: fears of ‘social divide’ unless all children learn computing skills - The Guardian</t>
+        </is>
+      </c>
+      <c r="D387" t="inlineStr">
+        <is>
+          <t>Mon, 05 Jan 2026 17:34:00 GMT</t>
+        </is>
+      </c>
+      <c r="E387" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiyAFBVV95cUxOMk5GMm8xdlJoSS1jSTZtOHpEdlFvMnNkbTV3aWxrMk5IX24tZWUwbU1ucnl1SGVpcjVOVDUzeWNyd0xpUHc0UDViTkFtUk9SSVlZYXd3M3RyYVd3SWpSNElaaTJaMUZ1S3RvVDlVYjBIRllMWFVYd0pGRlQ2RGNqWHBoOUtmOHpfV0FFaDNoUmFJZTNBdDhkQkI0NURWdU5WWUFOUGxEMl9HU2dVZk5TMlltc0M1UWhqaGdhVE05aG0zNlR0aDhXZA?oc=5</t>
+        </is>
+      </c>
+      <c r="F387" t="n">
+        <v>7</v>
+      </c>
+      <c r="G387" s="2" t="n">
+        <v>46027.73194444444</v>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B388" t="inlineStr">
+        <is>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+        </is>
+      </c>
+      <c r="C388" t="inlineStr">
+        <is>
+          <t>Harnessing technology to transform demining - The HALO Trust</t>
+        </is>
+      </c>
+      <c r="D388" t="inlineStr">
+        <is>
+          <t>Tue, 06 Jan 2026 17:22:08 GMT</t>
+        </is>
+      </c>
+      <c r="E388" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMia0FVX3lxTE1BNm9SR1gxdlBjVXVPcURMMTF6alVrbTR5ZWljX1l6OG5CSnRxVUQ2RWdTdzNXSWlRN3VQNW1qMmtqUmtfemlwTEFPeXlWVHN5S1VMekIwcW1qQ3VKYUc5NVFPSklKYl9hOHVJ?oc=5</t>
+        </is>
+      </c>
+      <c r="F388" t="n">
+        <v>7</v>
+      </c>
+      <c r="G388" s="2" t="n">
+        <v>46028.7237037037</v>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B389" t="inlineStr">
+        <is>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+        </is>
+      </c>
+      <c r="C389" t="inlineStr">
+        <is>
+          <t>Expert issues dire AI warning and ‘doom timeline’ - The Independent</t>
+        </is>
+      </c>
+      <c r="D389" t="inlineStr">
+        <is>
+          <t>Tue, 06 Jan 2026 16:34:00 GMT</t>
+        </is>
+      </c>
+      <c r="E389" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxOLWNzRHFHU1dYZjlZc3RMXzVybEVycHZYczlucDYyQktJclRtWFZOYlZZdmNKbkxab0tMYVZJdE5fR3RVd25Jck5NZk1SOXF3LXdBdkdQN2kxYVc5VE13Nk52azNwVjRVMldjNl9rUHZjOUFfZUR3R2p4NUhyWmJYc0F4aDFEaDdreGcyU1hQeWNNdW5DTE1ReE5sQ2xFLU9WT2c?oc=5</t>
+        </is>
+      </c>
+      <c r="F389" t="n">
+        <v>7</v>
+      </c>
+      <c r="G389" s="2" t="n">
+        <v>46028.69027777778</v>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B390" t="inlineStr">
+        <is>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+        </is>
+      </c>
+      <c r="C390" t="inlineStr">
+        <is>
+          <t>Government seeks views to modernise laws on powered mobility devices - GOV.UK</t>
+        </is>
+      </c>
+      <c r="D390" t="inlineStr">
+        <is>
+          <t>Tue, 06 Jan 2026 10:26:27 GMT</t>
+        </is>
+      </c>
+      <c r="E390" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxOa2dHMl9Gc1puTkhrZXJ5enp5ZVpvSzdmYTk4WngzcXBpSFpZTGw1dUs3TV8xUGU1Sm9WZUpPU2tDakNBLXhJd0ZHOEYyemoxRlZUbVE0LWNyZ0JWcjA3SXhCeWQ0YU1MLUpXT3RHY0VXZ3UxdDRFbEdPRU51QXBIdElwRm9fbHB2UEVjeURFZFA4R0N2ZEx4UG9xMVViWWdNVU9VY1J3?oc=5</t>
+        </is>
+      </c>
+      <c r="F390" t="n">
+        <v>7</v>
+      </c>
+      <c r="G390" s="2" t="n">
+        <v>46028.43503472222</v>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B391" t="inlineStr">
+        <is>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+        </is>
+      </c>
+      <c r="C391" t="inlineStr">
+        <is>
+          <t>China reviews Meta’s $2bn purchase of AI start-up Manus - Financial Times</t>
+        </is>
+      </c>
+      <c r="D391" t="inlineStr">
+        <is>
+          <t>Wed, 07 Jan 2026 01:30:15 GMT</t>
+        </is>
+      </c>
+      <c r="E391" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMicEFVX3lxTFBoV2ZjMUhyQUthbG9RNFZZSUUwelAtOEVMOFVEWXFVc2V5RUI1SnN0LWl5X2s1bjI2V2pvczFhcFBYd1d1c2RzQ0g5SFZ4aVBLal9wQTE4MzN4TXZSSExMdFhLbjEzdzdTUUVVZHFVVko?oc=5</t>
+        </is>
+      </c>
+      <c r="F391" t="n">
+        <v>7</v>
+      </c>
+      <c r="G391" s="2" t="n">
+        <v>46029.06267361111</v>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B392" t="inlineStr">
+        <is>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+        </is>
+      </c>
+      <c r="C392" t="inlineStr">
+        <is>
+          <t>How RICOH Intelligent Automation accelerates digital transformation | Global - Ricoh Global</t>
+        </is>
+      </c>
+      <c r="D392" t="inlineStr">
+        <is>
+          <t>Wed, 07 Jan 2026 01:06:21 GMT</t>
+        </is>
+      </c>
+      <c r="E392" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMifEFVX3lxTFBxakVmbGlfOWJyYzUzWWJJWVR1QVF2MjFaWEFCaUxLU0pZUDVXXzhFcl9OM0NMcFJWRVpadldLdXN1bXNLYnBIQXlNR1IxdGxKRjFxQWt0c0c3cFVRUUpXRnVsNlpsX3pXckszb0tqRWhoX1hIY052bjNJQnM?oc=5</t>
+        </is>
+      </c>
+      <c r="F392" t="n">
+        <v>7</v>
+      </c>
+      <c r="G392" s="2" t="n">
+        <v>46029.04607638889</v>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B393" t="inlineStr">
+        <is>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+        </is>
+      </c>
+      <c r="C393" t="inlineStr">
+        <is>
+          <t>Mobileye to acquire humanoid robotics startup Mentee for $900 million - Reuters</t>
+        </is>
+      </c>
+      <c r="D393" t="inlineStr">
+        <is>
+          <t>Tue, 06 Jan 2026 21:22:11 GMT</t>
+        </is>
+      </c>
+      <c r="E393" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxQUm5SMjlicDNlSlFlZV9pODNxa3czZFJXOXhSaWRIYVhQdDNGZGdRSDlQVHY4RXdVUjlncmJBZmRPajIyZE9BRXU4SVlBdjlRRTEtNk9ZS3JRVTVLTjc0U3l4OE5tcHZ4dlhSVlZOOFpRRkdzdVpLSC1OMTNRTDVzUnJCcFNyZHlpazJvNW9JR0VZS2loU09CcEcyaHJVdmdVbUNhU21MeExsQnFRUUNlNnJRZUNha1U?oc=5</t>
+        </is>
+      </c>
+      <c r="F393" t="n">
+        <v>7</v>
+      </c>
+      <c r="G393" s="2" t="n">
+        <v>46028.89040509259</v>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B394" t="inlineStr">
+        <is>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+        </is>
+      </c>
+      <c r="C394" t="inlineStr">
+        <is>
+          <t>Why AI Boosts Creativity for Some Employees but Not Others - Harvard Business Review</t>
+        </is>
+      </c>
+      <c r="D394" t="inlineStr">
+        <is>
+          <t>Tue, 06 Jan 2026 13:44:04 GMT</t>
+        </is>
+      </c>
+      <c r="E394" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiigFBVV95cUxPUllGcVp5VXo3T0tOWDV6QWpiYktDU0RMclJlVUtCTDRneVJQZHJsNnZBSDFGRUJ0N1VlMFY0TExLQlBEOW1rNGtKMmpWX3g1Z2tQZnZfTzVoaVpSTm43NWh3bDNxQkRiMEsxSUZnN0NyNGVzSmJPcjRtb2NKRGNjWVRrRjRnN2R2MEE?oc=5</t>
+        </is>
+      </c>
+      <c r="F394" t="n">
+        <v>7</v>
+      </c>
+      <c r="G394" s="2" t="n">
+        <v>46028.57226851852</v>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B395" t="inlineStr">
+        <is>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+        </is>
+      </c>
+      <c r="C395" t="inlineStr">
+        <is>
+          <t>Sainsbury’s launches new graduate programme with AI focus - AOL.co.uk</t>
+        </is>
+      </c>
+      <c r="D395" t="inlineStr">
+        <is>
+          <t>Wed, 07 Jan 2026 00:01:00 GMT</t>
+        </is>
+      </c>
+      <c r="E395" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMijwFBVV95cUxOcTBrT3B1TnRBbm12bmw3cXRJNFVDNlR1WUZOZENFVnNLbmFBcy1ZVzVReTFBaDJZSHBfYVdsSm01Y3NPN3FHVFJ2ZnJIbk8zdEw3cUhfb2g0ZWM1d2pFN3VoQ1pVakpXR2JCek0xSnRzYkduczJwenFqR0JKbmI4Z1NnMTJfbHhxemJrcm1PQQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F395" t="n">
+        <v>7</v>
+      </c>
+      <c r="G395" s="2" t="n">
+        <v>46029.00069444445</v>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B396" t="inlineStr">
+        <is>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+        </is>
+      </c>
+      <c r="C396" t="inlineStr">
+        <is>
+          <t>News | AI and defence are 2026 buzzwords but malls and prime offices should be watchwords - CoStar</t>
+        </is>
+      </c>
+      <c r="D396" t="inlineStr">
+        <is>
+          <t>Tue, 06 Jan 2026 14:57:21 GMT</t>
+        </is>
+      </c>
+      <c r="E396" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxNR0J2NzBXQl95RlhuTEpadDJOQ1ZHSDFqMW90ZUNFdTYwbDVuNnlpRFdmcDJaSU1HX0hRWmw0X1FUY3VhU0REdjNRUVhtUGRLNkpLNUx3Sjcydzg4bkhBRWVKSFNlb29DbWo4Mm5hT0JnVWxMak90NktQbFZROUs5ODhvU1YwWWF4MmdHcm1jb1I4aWx6TG43UTUzUW5PRFZCT29mWk11NXM0SGQ4Z3F0TEhrZnd4QW03ZTlTRTY5RFQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F396" t="n">
+        <v>7</v>
+      </c>
+      <c r="G396" s="2" t="n">
+        <v>46028.62315972222</v>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B397" t="inlineStr">
+        <is>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+        </is>
+      </c>
+      <c r="C397" t="inlineStr">
+        <is>
+          <t>AstraZeneca and BostonGene leverage AI for smarter oncology trials - FirstWord</t>
+        </is>
+      </c>
+      <c r="D397" t="inlineStr">
+        <is>
+          <t>Tue, 06 Jan 2026 21:55:31 GMT</t>
+        </is>
+      </c>
+      <c r="E397" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiU0FVX3lxTFA5b3lfNEp0ZGIzd3hTWjVTb19SaGZxWWtVYzItVUd4YUlSVjI4cnlJQTJUdUdHZzkySExMMlh2VGtEUk5FWnRlc0ZpckpmNzd6U3JZ?oc=5</t>
+        </is>
+      </c>
+      <c r="F397" t="n">
+        <v>7</v>
+      </c>
+      <c r="G397" s="2" t="n">
+        <v>46028.91355324074</v>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B398" t="inlineStr">
+        <is>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+        </is>
+      </c>
+      <c r="C398" t="inlineStr">
+        <is>
+          <t>Reflecting on a Year of Public Sector Innovation - Google Cloud</t>
+        </is>
+      </c>
+      <c r="D398" t="inlineStr">
+        <is>
+          <t>Tue, 06 Jan 2026 15:16:22 GMT</t>
+        </is>
+      </c>
+      <c r="E398" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxQajAybkNpS00zdWNrTG1kVHEzNjlURExYTGRGcEtzMEw5QWhBcGpubGJIYTFKNDZ0MGhCSGx1UjczdjlaaWxFYzVXc011V3BOSWlLZ1RxaVNfaDhaRnBDbjdMYjFneDRMR0JTQXNnc0ZHMEtCWkF0U3NSYmtuN3lFRV8wQ1ZGWjM3Q2RmYjQyVUdWX3dmeVJoU2tscmtLRlhwVnZIS1hfRlRYTnM1TnNpaGZBWXlLWlBPMHc?oc=5</t>
+        </is>
+      </c>
+      <c r="F398" t="n">
+        <v>7</v>
+      </c>
+      <c r="G398" s="2" t="n">
+        <v>46028.63636574074</v>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B399" t="inlineStr">
+        <is>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+        </is>
+      </c>
+      <c r="C399" t="inlineStr">
+        <is>
+          <t>How will AI reshape the news in 2026? Forecasts by 17 experts from around the world - reutersinstitute.politics.ox.ac.uk</t>
+        </is>
+      </c>
+      <c r="D399" t="inlineStr">
+        <is>
+          <t>Mon, 05 Jan 2026 07:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="E399" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxPZ1p2cDlqT1ZPbDdHSGEwNVoxd1J0TzZ4dExIb1FtRDdmSlpYWnlYNG1PNVR1UDItTzBlMXA0bFRYMEIzX0VBaHZxbVRla1c0bncydWhuTTl3alVqcWNwR0ZHNURrcGpjSVRBNzZoNTZJaVVoQTBjSXFGWUJFN1pKYXhtLU9pRXdGa1V6WkFCcTFuc1BKOC1ESDFTekxWVklSNlBXQVh0ajVlSnFIT1FV?oc=5</t>
+        </is>
+      </c>
+      <c r="F399" t="n">
+        <v>7</v>
+      </c>
+      <c r="G399" s="2" t="n">
+        <v>46027.29166666666</v>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B400" t="inlineStr">
+        <is>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+        </is>
+      </c>
+      <c r="C400" t="inlineStr">
+        <is>
+          <t>Baratunde Thurston on Natural vs. Artificial Intelligence - atmos.earth</t>
+        </is>
+      </c>
+      <c r="D400" t="inlineStr">
+        <is>
+          <t>Tue, 06 Jan 2026 11:33:44 GMT</t>
+        </is>
+      </c>
+      <c r="E400" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMijgFBVV95cUxOZE9YUmdPaVg3R0lqN2JYVTQzTld3bUlrSUhtMUoxUFNkM2Y5MDJwYlZ6NV92UXRBUWJveTVXTVcyb183TnBKYS1rc2swWXFzUHk0ZmdWNkdWekx1RVBSZnl5VHdIWlZ0UU5pcUFYeEU0eEhOc0k5aVllbjlMNy0xalcxaHgzTE0yaHR4ekF3?oc=5</t>
+        </is>
+      </c>
+      <c r="F400" t="n">
+        <v>7</v>
+      </c>
+      <c r="G400" s="2" t="n">
+        <v>46028.48175925926</v>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B401" t="inlineStr">
+        <is>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+        </is>
+      </c>
+      <c r="C401" t="inlineStr">
+        <is>
+          <t>Cybersecurity Failures Prompt U.K. Government to Set New Path (Jan 6, 2026) - VitalLaw.com</t>
+        </is>
+      </c>
+      <c r="D401" t="inlineStr">
+        <is>
+          <t>Wed, 07 Jan 2026 02:21:18 GMT</t>
+        </is>
+      </c>
+      <c r="E401" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiyAFBVV95cUxPRnR4MGxyOWZERGYyMVlOeDk1UE12clAyTU1JNkJjMlh0bVczYl9YZ0Y5QmtXNG9rZkJlRjJWa3M0MUtBOHlUU3pOWTlnZEVocFBYRnh3V3FTMlNvUmJ1aHRXREVPQ3hNdUhZdXZHZXRXQVFYNUdPaFRJQUFnMjFsdExCeGp3UlZJQXRmejlPTlhWa2VmM0FoeEpSMUJGX3pDeUdnanRJQTBHVThzczE4bDFfazlVTXhWM1lmUWhudmJ3SmFXUjRaYg?oc=5</t>
+        </is>
+      </c>
+      <c r="F401" t="n">
+        <v>7</v>
+      </c>
+      <c r="G401" s="2" t="n">
+        <v>46029.098125</v>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B402" t="inlineStr">
+        <is>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+        </is>
+      </c>
+      <c r="C402" t="inlineStr">
+        <is>
+          <t>Tech and compliance 2026: What to watch for in AI, cybersecurity and quantum computing - Compliance Week</t>
+        </is>
+      </c>
+      <c r="D402" t="inlineStr">
+        <is>
+          <t>Tue, 06 Jan 2026 13:21:43 GMT</t>
+        </is>
+      </c>
+      <c r="E402" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi0wFBVV95cUxPTVFzUkxxV29QQm9IRmtyVy1feERpUFNXQThyYzJxQ240Z01XRzlHU2RBbHgycE4wTmZzYzZQNnN0S00zcU8wTEJPMjFNeHRuNEpZRExBQVFMd2VKamU0N2ZuUTJXckFjdVcwSnh6THRpdHpKLWFWOEdTRGtFS0RBRF85czBlUXlvSElzZlRnQXZ6Nm5SUG1xTkVaVS1EdEhiVEpUM25TSUwwNklrYXNwRE9yRkNkenFHWERGM2U4Ry1jVlE2SXc5R3JBLW53bWhJOGE0?oc=5</t>
+        </is>
+      </c>
+      <c r="F402" t="n">
+        <v>7</v>
+      </c>
+      <c r="G402" s="2" t="n">
+        <v>46028.55674768519</v>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B403" t="inlineStr">
+        <is>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+        </is>
+      </c>
+      <c r="C403" t="inlineStr">
+        <is>
+          <t>Accenture buys British AI start-up in $1bn deal - The Times</t>
+        </is>
+      </c>
+      <c r="D403" t="inlineStr">
+        <is>
+          <t>Tue, 06 Jan 2026 19:20:00 GMT</t>
+        </is>
+      </c>
+      <c r="E403" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMisANBVV95cUxOT25Yc3JtMFRBLTdmNVg0cjU4YWt6RU5ZUmF4QVVPYlRfay1IY3ZSb0dkdHFvdndYbmFvMDUzR3RuODdhbFE3MUJkX29hMVVrQndjM0V5dTc0S1lRWl9mTmxzdGNjUWlYc3lTQXNHYVQydnFMZGVMTnV4cDBzdng2NzRIMHlOWEJfRk5mWWZJZk1fWVltcHNOMTN1TzRoeWNWNThabTk4Qnlqb0h6ZHBWR0ZxRDRWaWZJV3VqdXpBckxZRVI3M3VoQUhvb2VacGJhN0dnMXRYZTZmRzZVcHFLM1hLaXRSSTl0Q3N6S19NYUJfeDdkNmxKbHMtVXZPNG9RRWtLZHhPQjhFT3RMWGJ6TklXZXpmbkhVX09aSlpZRHZnMENwQmt1MVl3eWlnSzVFeU5TVjNwbjJiQnduMk5NRVFkRDRLYnlrNTdScHNDSDNPeGxSVGJPdjA1MVZWVDA5dW01TVM2VjFpZWJIQnZzOXhwdnhKQS1ZVFFYckJLU3ZsbkU5d1NvVlVwTDEtVTQzaFNCZXVqeWRLTUNUV2FtOXFRYWhwSGRuUUVtVHdwaTQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F403" t="n">
+        <v>7</v>
+      </c>
+      <c r="G403" s="2" t="n">
+        <v>46028.80555555555</v>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B404" t="inlineStr">
+        <is>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+        </is>
+      </c>
+      <c r="C404" t="inlineStr">
+        <is>
+          <t>The Modern Data Software Landscape: Data Observability - Carlsquare Corporate Finance</t>
+        </is>
+      </c>
+      <c r="D404" t="inlineStr">
+        <is>
+          <t>Tue, 06 Jan 2026 16:44:57 GMT</t>
+        </is>
+      </c>
+      <c r="E404" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMijwFBVV95cUxONVFpNFpRaXdTSXJCVnVCYmg2T3VNb3BHWTdXaml5U1NHVlBTa2RqSFJsYzV0T1pyS1lRd1lYS28xWUNiR0dIZ3FOTWZJVHVZSDBqNmFlaGZ3MmMtQlFMaHlIMkFyNng5X181Q2Y4MlI3UzU5OGF5bEpVbDhUaDBVUGNLbnU0R3VkalpOSE1Kbw?oc=5</t>
+        </is>
+      </c>
+      <c r="F404" t="n">
+        <v>7</v>
+      </c>
+      <c r="G404" s="2" t="n">
+        <v>46028.69788194444</v>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B405" t="inlineStr">
+        <is>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+        </is>
+      </c>
+      <c r="C405" t="inlineStr">
+        <is>
+          <t>AI is quick but risky for updating old software, researchers warn - Tech Xplore</t>
+        </is>
+      </c>
+      <c r="D405" t="inlineStr">
+        <is>
+          <t>Tue, 06 Jan 2026 22:21:28 GMT</t>
+        </is>
+      </c>
+      <c r="E405" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMickFVX3lxTE01dWIta0xBSFlvcFlpOFhsUm84MVNRZmw4QVdzN2s2cm96a3Y5a1BMSnI3WjgzWE9wQS1HRUF5M2lqQzZTQ3pmbHhQU3JOYU9wc0I5YkN5dTFmbTNxanJHNk5BMmVLRF9jMVU0cHpjV2FXQQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F405" t="n">
+        <v>7</v>
+      </c>
+      <c r="G405" s="2" t="n">
+        <v>46028.93157407407</v>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B406" t="inlineStr">
+        <is>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+        </is>
+      </c>
+      <c r="C406" t="inlineStr">
+        <is>
+          <t>Officials and Executives Discuss Cyber Labels, Agentic AI, and Resilience - Broadband Breakfast</t>
+        </is>
+      </c>
+      <c r="D406" t="inlineStr">
+        <is>
+          <t>Wed, 07 Jan 2026 00:21:20 GMT</t>
+        </is>
+      </c>
+      <c r="E406" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxPV1JaOUxPQVQxaGpxbmhhTjVNV21SR29iZmNhVFpQSmpOUmxBSFN5Yk1ZMjFiYU5xdXFaWi1JU29nbmZsbE9fV2dMTnhodnB0U2xxLVJUbWhfcHBFMDIzb0JVb2RFZjIyeHJrMUJEVUdvZjJKNkQtNzFuMFc2MDFkNTRKdnNrdGs5MktRcjNnd1VJRzdXbEpuRHlXNA?oc=5</t>
+        </is>
+      </c>
+      <c r="F406" t="n">
+        <v>7</v>
+      </c>
+      <c r="G406" s="2" t="n">
+        <v>46029.01481481481</v>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B407" t="inlineStr">
+        <is>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+        </is>
+      </c>
+      <c r="C407" t="inlineStr">
+        <is>
+          <t>10 CEE-Founded Robotics Startups You Should Know - The Recursive</t>
+        </is>
+      </c>
+      <c r="D407" t="inlineStr">
+        <is>
+          <t>Tue, 06 Jan 2026 15:41:18 GMT</t>
+        </is>
+      </c>
+      <c r="E407" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMickFVX3lxTFBuS056X3d2eXNLbWJEbzVENVJEdndQaHN4RURsRy1JWlNFcW5zTXNYNnUwTkdBSlJsSUk2V2N6b1FqQ08tU3JzY2tTVjZlRG5pQlUtWmo5LVhxZVotV0FnaU5tNkdIamhpV2l6M094R0NKdw?oc=5</t>
+        </is>
+      </c>
+      <c r="F407" t="n">
+        <v>7</v>
+      </c>
+      <c r="G407" s="2" t="n">
+        <v>46028.65368055556</v>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B408" t="inlineStr">
+        <is>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+        </is>
+      </c>
+      <c r="C408" t="inlineStr">
+        <is>
+          <t>Nvidia unveils self-driving car tech as part of physical AI push - BBC</t>
+        </is>
+      </c>
+      <c r="D408" t="inlineStr">
+        <is>
+          <t>Tue, 06 Jan 2026 10:30:23 GMT</t>
+        </is>
+      </c>
+      <c r="E408" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTFBPYkdXNnRJTE4xN3dKMzFXVnNwYmItUDgtcmJ6Z01Xdmo4NXFWVWdpQWhaQzU5Z2FmS0NuUHBfbkdac2Zjc1hUM004UlN2bGxBOFJMTE13b21fd9IBX0FVX3lxTFBpMXZRa3JmTF9FSGFkak1UVUkybWZDNU5JLUtmN1ZxNWRkbTRGNU55S3hidnMwNTVRblZNTUdoUHRmdmh3SHlVek1STlFJejM3bnR4LUpYTnpaY01Wd0pN?oc=5</t>
+        </is>
+      </c>
+      <c r="F408" t="n">
+        <v>7</v>
+      </c>
+      <c r="G408" s="2" t="n">
+        <v>46028.4377662037</v>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B409" t="inlineStr">
+        <is>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+        </is>
+      </c>
+      <c r="C409" t="inlineStr">
+        <is>
+          <t>Selema Masekela on the Algorithm Era, Why Brands Can’t Rely On AI, and Why He Likes Kooks - The Inertia</t>
+        </is>
+      </c>
+      <c r="D409" t="inlineStr">
+        <is>
+          <t>Tue, 06 Jan 2026 20:22:39 GMT</t>
+        </is>
+      </c>
+      <c r="E409" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMie0FVX3lxTE94SkJlb0hGeTEzRU1jZHczMVFybHk3MXNfb2d2dEhIWkNQdURoQW5fekJfV0I1dldqUkZBTEtYZXFjQWtzX3ZoaWtocUVRVjhuc1NKV0NHRGttWWExZGZYd2RHMXFZTHZoLXl4cnNYMHlOMTdNRFhZRkVQRQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F409" t="n">
+        <v>7</v>
+      </c>
+      <c r="G409" s="2" t="n">
+        <v>46028.8490625</v>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B410" t="inlineStr">
+        <is>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+        </is>
+      </c>
+      <c r="C410" t="inlineStr">
+        <is>
+          <t>Cloud Agent in 2025: A Year of Scale, Security, and Smarter Visibility - Qualys</t>
+        </is>
+      </c>
+      <c r="D410" t="inlineStr">
+        <is>
+          <t>Tue, 06 Jan 2026 16:59:35 GMT</t>
+        </is>
+      </c>
+      <c r="E410" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMifEFVX3lxTFB4ekJocjhZOUxWem9fWmFhQUJFRjZiOGtHS3UwM3pyLUpyaVVORWhSdEZTeTNUZWVUUVB0M3BYWWJ0Q3Rab3ZobjJGRjNTMzFpcEEwUGVTZ1MzaFFIREhtT0ZiaWdzMEo2OFN2OUhrajRydl9BaFlxQWk4bnI?oc=5</t>
+        </is>
+      </c>
+      <c r="F410" t="n">
+        <v>7</v>
+      </c>
+      <c r="G410" s="2" t="n">
+        <v>46028.70804398148</v>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B411" t="inlineStr">
+        <is>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+        </is>
+      </c>
+      <c r="C411" t="inlineStr">
+        <is>
+          <t>Siemens unveils technologies to accelerate the industrial AI revol ... - Siemens press</t>
+        </is>
+      </c>
+      <c r="D411" t="inlineStr">
+        <is>
+          <t>Tue, 06 Jan 2026 16:51:15 GMT</t>
+        </is>
+      </c>
+      <c r="E411" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxNWUl4Q2NONi03VDladkJlXzFVMWZpQzZHeGN6blhyQjZhMGE3cXktdFFHUVpqWnBWVEtUZzBWYzBVenNwMHNLVzNUenBYb0NuUjdyRGhLeGlCV0dZZ3V0NXRaNlZUbGV2UUlqdDJ6ZWNFODZRSjNTTmRJYkdROXlPX1pPWDRfMlNKb0NhUWFaNnZMdDlrNE1MeTVYQlBub0dmdm5tSUlHLWFfdWZUM1p4SVB5T2UyWkVmbmhVX21KTQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F411" t="n">
+        <v>7</v>
+      </c>
+      <c r="G411" s="2" t="n">
+        <v>46028.70225694445</v>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B412" t="inlineStr">
+        <is>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+        </is>
+      </c>
+      <c r="C412" t="inlineStr">
+        <is>
+          <t>AI-designed molecular sensors could enable early detection of cancer - News-Medical</t>
+        </is>
+      </c>
+      <c r="D412" t="inlineStr">
+        <is>
+          <t>Wed, 07 Jan 2026 00:58:00 GMT</t>
+        </is>
+      </c>
+      <c r="E412" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxOWW9yQi0tSUJFRnUxWlcwWWY0OHhHeU11VWJJMkxTZ2Zoa3ByQXdIUUxtVmtPbDBqWGE0REVSa1ZZYXpLSDFzTkpRRXJIZlVsbHBoYUJtOVpRUElvY2RodU9jdHYwblpIb013UjRfZmtNdUdwWWRXTTYwb0V6aFIwelN4d3p6dUZsT2J0UnlzSFJMSm1XNFNwWDNlZVM3c2tGYm4wRVlQc0ZCX0oybENCUjBlb1hFcEE?oc=5</t>
+        </is>
+      </c>
+      <c r="F412" t="n">
+        <v>7</v>
+      </c>
+      <c r="G412" s="2" t="n">
+        <v>46029.04027777778</v>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B413" t="inlineStr">
+        <is>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+        </is>
+      </c>
+      <c r="C413" t="inlineStr">
+        <is>
+          <t>How to navigate the age of agentic AI - MIT Sloan</t>
+        </is>
+      </c>
+      <c r="D413" t="inlineStr">
+        <is>
+          <t>Tue, 06 Jan 2026 14:47:34 GMT</t>
+        </is>
+      </c>
+      <c r="E413" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiggFBVV95cUxNcnowNlhrbXk1SXNqZzJMS2FGNzMyOVZMZHlvYmJhUkZBaU5fOHlYX0lFakZCS0JvUEc1R0liVzREd3lLRVJxWURCSGZ4TS1KblZLZTJIZGR5dUM5QTdtRWthVEhyV2xIUVF5eTVvQTRXRzc3dlRsdHpDWkx1NXVMMm1R?oc=5</t>
+        </is>
+      </c>
+      <c r="F413" t="n">
+        <v>7</v>
+      </c>
+      <c r="G413" s="2" t="n">
+        <v>46028.61636574074</v>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B414" t="inlineStr">
+        <is>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+        </is>
+      </c>
+      <c r="C414" t="inlineStr">
+        <is>
+          <t>Pentagon looks to use AI, automation for zero trust assessments - DefenseScoop</t>
+        </is>
+      </c>
+      <c r="D414" t="inlineStr">
+        <is>
+          <t>Tue, 06 Jan 2026 21:31:31 GMT</t>
+        </is>
+      </c>
+      <c r="E414" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMigwFBVV95cUxOYnFmekVMQmRSczhmOFFpbmstTGxEVXU0bnNhdTU2TnljWW1mNXZfMW44YmY0UlluSmxDQmpwWE9oZ1VvbGVPY1h4S3ZQSzZqUlVCYUtqbG53U1J0cFdIX1ZQNW1FQjhWdG8wTVVxOWdtR2NtcmJ3STJ4T1V1RFhLZG04cw?oc=5</t>
+        </is>
+      </c>
+      <c r="F414" t="n">
+        <v>7</v>
+      </c>
+      <c r="G414" s="2" t="n">
+        <v>46028.89688657408</v>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B415" t="inlineStr">
+        <is>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+        </is>
+      </c>
+      <c r="C415" t="inlineStr">
+        <is>
+          <t>Dunelm's reduced January sale bedding is 'like sleeping on a cloud' and 'keeps you so warm' - Wales Online</t>
+        </is>
+      </c>
+      <c r="D415" t="inlineStr">
+        <is>
+          <t>Tue, 06 Jan 2026 10:50:00 GMT</t>
+        </is>
+      </c>
+      <c r="E415" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxQeDF1WEs2cjRkZXNWMENXZ1Q0ODhfU0dtWFREMlpQeld0V1ItQ0ZYSUlFNzIxX21zdFFSaHR0UGUzaHA5WVRQdHFMb3pJRU5ZekRYRXYyVTZ6RDA0LWgtRW5acFZNeWhMaGJ0UFJCWkExX3Rzb0Z0c2c0ZXlxNGRqWEt0UENGdXFnZnRnME8zMzFiX2V2dWZSNdIBngFBVV95cUxOb1VSX0Jpa1hrak1GRU5aR3dWNThLTmVHVEFLREd5LVBfN3BSREtsNlVLcWlNeUlmR2NDdXNkOFBCY0xrWXN4NG5Xa2djWTJtWEkwTGh5MUJGVThhS2FQWTJuQ3JUamJtcnQyMmdFTFo2MXI3Y09rY284bFJrTEJjWFB3Qmt1YUJFbEZiV295SkJ6Q3BnRkpiSXFPTGRhdw?oc=5</t>
+        </is>
+      </c>
+      <c r="F415" t="n">
+        <v>7</v>
+      </c>
+      <c r="G415" s="2" t="n">
+        <v>46028.45138888889</v>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B416" t="inlineStr">
+        <is>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+        </is>
+      </c>
+      <c r="C416" t="inlineStr">
+        <is>
+          <t>InsertsPRO software solution for automated grinding - Machinery Market</t>
+        </is>
+      </c>
+      <c r="D416" t="inlineStr">
+        <is>
+          <t>Tue, 06 Jan 2026 17:16:28 GMT</t>
+        </is>
+      </c>
+      <c r="E416" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxQZDJzcVJ4a19rbVBWcGxWcFNOY2JZNlpPLUxqQkJXZF9TU1Y1bTQzbjZxUU1RMElaQU5XeE1HUmMxZnUxenU2YlVGSlJvS3BFWEpVYVJuMEpKOGZMdkdwcVlUa1V1eHJIZFlkWU5IbGtuRUlVU0VVN2RzV0VtQ0VpQWxLWkdJcUlmTEJqRU5HWWhyWS1hb2JCN2pNRUNWZw?oc=5</t>
+        </is>
+      </c>
+      <c r="F416" t="n">
+        <v>7</v>
+      </c>
+      <c r="G416" s="2" t="n">
+        <v>46028.71976851852</v>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B417" t="inlineStr">
+        <is>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+        </is>
+      </c>
+      <c r="C417" t="inlineStr">
+        <is>
+          <t>A Dynamic Duo: Why AI and Blockchain Work Well Together - Independent Mail</t>
+        </is>
+      </c>
+      <c r="D417" t="inlineStr">
+        <is>
+          <t>Tue, 06 Jan 2026 19:05:00 GMT</t>
+        </is>
+      </c>
+      <c r="E417" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi3AFBVV95cUxNS01sODJ3cHZiWkVVQVBva1hpSS0zSnVtNnRqMGM4V1NyaWVWOUdJbkhkVU9ETUhiVXJyYnVCLXhNWlAzMzExNmxSZ2tkbC10dmJsaFBZUkNjbDJ2amZyY3ItUzdfRE84RU9Ydk9WU2pxdENacjJpVkNfN3JFTnJmVDJPU0R2RmF6SWlFbVpRaHMzRkVlaVZUNVBBNWU0eWhLUDZvWkRfTnZpUURleUhRcDhCNzVQd0Z3OVRNbXRqbm5BVTlJVDNoZVk4RFZpdWVreDV1MzBWX1dUQUl4?oc=5</t>
+        </is>
+      </c>
+      <c r="F417" t="n">
+        <v>7</v>
+      </c>
+      <c r="G417" s="2" t="n">
+        <v>46028.79513888889</v>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B418" t="inlineStr">
+        <is>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+        </is>
+      </c>
+      <c r="C418" t="inlineStr">
+        <is>
+          <t>Is AI going to make work worse? - GovTech</t>
+        </is>
+      </c>
+      <c r="D418" t="inlineStr">
+        <is>
+          <t>Wed, 07 Jan 2026 00:20:52 GMT</t>
+        </is>
+      </c>
+      <c r="E418" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMif0FVX3lxTE1sbF9RbUVSeVVCaXYwVjl2NGpMVE81TTY4T2pKVWVMMTc4VVNxQWRJclQyVWZURFVZTWdWcnZBRXJRNVlKYVk0dFd2Zk5XQ3FvbGlEUzI1VXIxOV9nLVhYbU5QZ0tUR3h0ZVpJNmJNN18yRTYxMWlGS0RaWV9FRmM?oc=5</t>
+        </is>
+      </c>
+      <c r="F418" t="n">
+        <v>7</v>
+      </c>
+      <c r="G418" s="2" t="n">
+        <v>46029.01449074074</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/topic_feeds.xlsx
+++ b/data/topic_feeds.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G418"/>
+  <dimension ref="A1:G554"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14230,6 +14230,4494 @@
         <v>46029.01449074074</v>
       </c>
     </row>
+    <row r="419">
+      <c r="A419" t="inlineStr">
+        <is>
+          <t>Current_Affairs</t>
+        </is>
+      </c>
+      <c r="B419" t="inlineStr">
+        <is>
+          <t>(geopolitics OR migration OR economy OR conflict OR legislation OR terrorism OR disinformation OR misinformation OR government OR policy OR regulation) AND (briefing OR analysis OR update OR report)</t>
+        </is>
+      </c>
+      <c r="C419" t="inlineStr">
+        <is>
+          <t>Government responds to Cash ISA report - UK Parliament</t>
+        </is>
+      </c>
+      <c r="D419" t="inlineStr">
+        <is>
+          <t>Wed, 14 Jan 2026 11:37:30 GMT</t>
+        </is>
+      </c>
+      <c r="E419" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxOYmwyclRPRmhSNll6VnJtOHVwUXQ1alpwZ0lMWFdDdlJ6a3B5dVlJcXFMc1ptLWVqUnlSNW5CM2xfbHR4R0g0dHkycWtMNXJoMEx1dmJlMFVyOUdZLWc5R3V0OWh0TXpHS2NIS1RHdW1rOGdFNzQwTl8yankzcm9DZS1wQTJWVm1QLTR6ZXIydG01ZEw3TlU0c0FFMHJ4MmVWTVJ4blpXaDdsMExqYy0xcElBWjkyV0FN?oc=5</t>
+        </is>
+      </c>
+      <c r="F419" t="n">
+        <v>10</v>
+      </c>
+      <c r="G419" s="2" t="n">
+        <v>46036.484375</v>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" t="inlineStr">
+        <is>
+          <t>Current_Affairs</t>
+        </is>
+      </c>
+      <c r="B420" t="inlineStr">
+        <is>
+          <t>(geopolitics OR migration OR economy OR conflict OR legislation OR terrorism OR disinformation OR misinformation OR government OR policy OR regulation) AND (briefing OR analysis OR update OR report)</t>
+        </is>
+      </c>
+      <c r="C420" t="inlineStr">
+        <is>
+          <t>January Monthly Terrorism Update - Pool Reinsurance</t>
+        </is>
+      </c>
+      <c r="D420" t="inlineStr">
+        <is>
+          <t>Thu, 15 Jan 2026 09:40:16 GMT</t>
+        </is>
+      </c>
+      <c r="E420" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMilAFBVV95cUxNWGM1Nm9xSEhYRmxKRFV3a3VremVaT05UclI4N3Y5YmtDdTR3Tnh0UWRrX0tTaHpuWjdnU2xOZzktUUV2Mk1TWThUQmtqaEtQR3hwMWViZEhDS3BMUHlwbnJtdUJoSXVRSmdtX21BWFlnQUtTa0wycGVIXzJmLXlxS1AwX3VmQllNZDRpbl94SGszb1Bw?oc=5</t>
+        </is>
+      </c>
+      <c r="F420" t="n">
+        <v>10</v>
+      </c>
+      <c r="G420" s="2" t="n">
+        <v>46037.40296296297</v>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" t="inlineStr">
+        <is>
+          <t>Current_Affairs</t>
+        </is>
+      </c>
+      <c r="B421" t="inlineStr">
+        <is>
+          <t>(geopolitics OR migration OR economy OR conflict OR legislation OR terrorism OR disinformation OR misinformation OR government OR policy OR regulation) AND (briefing OR analysis OR update OR report)</t>
+        </is>
+      </c>
+      <c r="C421" t="inlineStr">
+        <is>
+          <t>A False Compromise - Policy Exchange</t>
+        </is>
+      </c>
+      <c r="D421" t="inlineStr">
+        <is>
+          <t>Wed, 14 Jan 2026 22:01:39 GMT</t>
+        </is>
+      </c>
+      <c r="E421" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMibkFVX3lxTFA5d18yNjJCNEV6NWoxSjRaUi1XVGxFZ09yNnNKVjgzX3JHTHkyTWttZXJTMVpOLS1mNF9zMVNqWHRDcXVkSFVwZ3MxYmdlVWlNZUFOZ2pmNDk3dmRIRUhmclJEVUVCVTYwYTY1bTVR?oc=5</t>
+        </is>
+      </c>
+      <c r="F421" t="n">
+        <v>10</v>
+      </c>
+      <c r="G421" s="2" t="n">
+        <v>46036.9178125</v>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" t="inlineStr">
+        <is>
+          <t>Current_Affairs</t>
+        </is>
+      </c>
+      <c r="B422" t="inlineStr">
+        <is>
+          <t>(geopolitics OR migration OR economy OR conflict OR legislation OR terrorism OR disinformation OR misinformation OR government OR policy OR regulation) AND (briefing OR analysis OR update OR report)</t>
+        </is>
+      </c>
+      <c r="C422" t="inlineStr">
+        <is>
+          <t>Industry News: Scottish Government Update on 2026 Non Domestic Rates Revaluation - Scottish Tourism Alliance</t>
+        </is>
+      </c>
+      <c r="D422" t="inlineStr">
+        <is>
+          <t>Thu, 15 Jan 2026 15:28:29 GMT</t>
+        </is>
+      </c>
+      <c r="E422" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxObVNSZVZVUmZOVlVNSHJWT3hxcFdtN1E0cWRieWNSbFk3ZDhfVllpNTVkR0YyNnI0eE1ad2xYUnRGSU1jQWZnT0VTd19HYzNTako0cC1hWWl3TWFsdXVMQ1hDWHpwamVta3FMMXdYMzlCNFF1TG5YM1FDME5za0NjeFJKOXFwbC1DMHQ0cXpvemxyZDBlczRablNMYV9OQ0h1a1pfX21ORFFLNVRpZktOdHd0QV9ZdU5vN2c?oc=5</t>
+        </is>
+      </c>
+      <c r="F422" t="n">
+        <v>10</v>
+      </c>
+      <c r="G422" s="2" t="n">
+        <v>46037.6447800926</v>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" t="inlineStr">
+        <is>
+          <t>Current_Affairs</t>
+        </is>
+      </c>
+      <c r="B423" t="inlineStr">
+        <is>
+          <t>(geopolitics OR migration OR economy OR conflict OR legislation OR terrorism OR disinformation OR misinformation OR government OR policy OR regulation) AND (briefing OR analysis OR update OR report)</t>
+        </is>
+      </c>
+      <c r="C423" t="inlineStr">
+        <is>
+          <t>Immediate response to the Scottish Budget and Spending Review - IFS | Institute for Fiscal Studies</t>
+        </is>
+      </c>
+      <c r="D423" t="inlineStr">
+        <is>
+          <t>Tue, 13 Jan 2026 17:31:02 GMT</t>
+        </is>
+      </c>
+      <c r="E423" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiigFBVV95cUxNNU9INmF5dGpwUXpyTFkxdXMtOExIdldQTlVpTGxCN1dSNnkwZEtBcFVJMm83b2xSbDlDMnQzM25FWXB2SmpKY2gxLTllQ0gzMmxvNExzQVg3azJmRnVESHVqRGFfM2ZRZmtITlVuN0k0MlBlWmtrRVA1bTNudnI3MUNmb19RamVUWWc?oc=5</t>
+        </is>
+      </c>
+      <c r="F423" t="n">
+        <v>10</v>
+      </c>
+      <c r="G423" s="2" t="n">
+        <v>46035.72988425926</v>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" t="inlineStr">
+        <is>
+          <t>Current_Affairs</t>
+        </is>
+      </c>
+      <c r="B424" t="inlineStr">
+        <is>
+          <t>(geopolitics OR migration OR economy OR conflict OR legislation OR terrorism OR disinformation OR misinformation OR government OR policy OR regulation) AND (briefing OR analysis OR update OR report)</t>
+        </is>
+      </c>
+      <c r="C424" t="inlineStr">
+        <is>
+          <t>Fuelling the Future: How Business, Finance and Policy can Accelerate the Clean Fuels Market - The World Economic Forum</t>
+        </is>
+      </c>
+      <c r="D424" t="inlineStr">
+        <is>
+          <t>Thu, 15 Jan 2026 08:20:35 GMT</t>
+        </is>
+      </c>
+      <c r="E424" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxNU3VlaFpzWGpMT1gwdTZGdDJEcHJ6dnI4eTBjWlJkMmhraFUtNWswRy0tci1rcjZobHBiVF90SUVUX2JkaW1SbWIwQ0xrVm1uY2ZEbmJaYU1OajhUblJTS0VEWXFYYUtKYVNHakpVRjFLdWU3bjRhT0ZxMG9tcm9oZUtZN1phSUhIRG5FMmdxbXZkZlhuNDJOMkliZ1NCVzlIUkxJQ0ZfVkkwenZlSHZ4dU4xd3NOSGhUN1hSeU5YaVBKcVp4VEE?oc=5</t>
+        </is>
+      </c>
+      <c r="F424" t="n">
+        <v>10</v>
+      </c>
+      <c r="G424" s="2" t="n">
+        <v>46037.34762731481</v>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" t="inlineStr">
+        <is>
+          <t>Current_Affairs</t>
+        </is>
+      </c>
+      <c r="B425" t="inlineStr">
+        <is>
+          <t>(geopolitics OR migration OR economy OR conflict OR legislation OR terrorism OR disinformation OR misinformation OR government OR policy OR regulation) AND (briefing OR analysis OR update OR report)</t>
+        </is>
+      </c>
+      <c r="C425" t="inlineStr">
+        <is>
+          <t>Frontex report: What the drop in migration figures does not tell us - Table.Briefings</t>
+        </is>
+      </c>
+      <c r="D425" t="inlineStr">
+        <is>
+          <t>Fri, 16 Jan 2026 04:37:33 GMT</t>
+        </is>
+      </c>
+      <c r="E425" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxPamx2VmpGdEpYSHdmVDlwQjQtdktvTmp3a3Yxb3d6aW90ckQwVHJINGF0cUNkUjNoMlNOMTBEWmlxSlZ3X3phODRZQjMyaVJyaUtEOEl3czFZQTF6d3g4VHB5NC1kZzhERFBfV3VvU05wM0NNOC0wbzdhdVU4a01qa3pIWDlwNTM3N3lCRzdLblM5ekpkQ1dXODkwMFZVWGI3TE1fRllqWQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F425" t="n">
+        <v>10</v>
+      </c>
+      <c r="G425" s="2" t="n">
+        <v>46038.19274305556</v>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" t="inlineStr">
+        <is>
+          <t>Current_Affairs</t>
+        </is>
+      </c>
+      <c r="B426" t="inlineStr">
+        <is>
+          <t>(geopolitics OR migration OR economy OR conflict OR legislation OR terrorism OR disinformation OR misinformation OR government OR policy OR regulation) AND (briefing OR analysis OR update OR report)</t>
+        </is>
+      </c>
+      <c r="C426" t="inlineStr">
+        <is>
+          <t>Gutting the Employment Rights Bill saved businesses billions, government analysis claims - Institute of Employment Rights</t>
+        </is>
+      </c>
+      <c r="D426" t="inlineStr">
+        <is>
+          <t>Wed, 14 Jan 2026 12:13:21 GMT</t>
+        </is>
+      </c>
+      <c r="E426" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxPcHhuVTlwLUl5RnlRTzRaVjU4VVIwMDF3ZEI1V0FFYnZ0TzZNR2R4Vml1ZW4yZ1AzRzFoXzM4dXlsMEZkQVNRTUhrR3ZiQ0JGYWlmNU1XZWZxTzVnNmVjYVVraVZJV013eFNWNUlWcEZxeFRRX2RTbFI0ZWs5NjNxQ1VoWkRNWUVBSFF3cC0yWGxnRGtwUlIwSzh3enJIZ2RFZTFuOFBaNGE0TkdMTFdkaGllZXZtT1U?oc=5</t>
+        </is>
+      </c>
+      <c r="F426" t="n">
+        <v>10</v>
+      </c>
+      <c r="G426" s="2" t="n">
+        <v>46036.50927083333</v>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" t="inlineStr">
+        <is>
+          <t>Current_Affairs</t>
+        </is>
+      </c>
+      <c r="B427" t="inlineStr">
+        <is>
+          <t>(geopolitics OR migration OR economy OR conflict OR legislation OR terrorism OR disinformation OR misinformation OR government OR policy OR regulation) AND (briefing OR analysis OR update OR report)</t>
+        </is>
+      </c>
+      <c r="C427" t="inlineStr">
+        <is>
+          <t>ACAPS Briefing Note: Syria - Displacement resulting from conflict escalation in Aleppo (15 January 2026) - ReliefWeb</t>
+        </is>
+      </c>
+      <c r="D427" t="inlineStr">
+        <is>
+          <t>Thu, 15 Jan 2026 16:33:10 GMT</t>
+        </is>
+      </c>
+      <c r="E427" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi2AFBVV95cUxQV1VvUXo4ODVVRTVOQmxqYWs4Y2NCck1vT1RqdV9VWldSaDVBRUdySmZkdkhMOE5MeHVvalhkZWFJNjIzSTFYdnlrZDM2RE9jVm1zZlJld2doLUZjOFVvR1loeWZ4TndqQ1lUMG8xMHk1ZWJSMWxzNU9nS29Yb1NCNFNNc2JRT1VLdnFEMHZRZTlvanR4Y0trMmZZTklZWHdtLVIzM0RBU2lCWlhwVVEyMUZhZ1NxQk1vUkR1RUREUnhLZk13Z3h0WGlldzR0ODJYYThtX0RDUHk?oc=5</t>
+        </is>
+      </c>
+      <c r="F427" t="n">
+        <v>10</v>
+      </c>
+      <c r="G427" s="2" t="n">
+        <v>46037.68969907407</v>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" t="inlineStr">
+        <is>
+          <t>Current_Affairs</t>
+        </is>
+      </c>
+      <c r="B428" t="inlineStr">
+        <is>
+          <t>(geopolitics OR migration OR economy OR conflict OR legislation OR terrorism OR disinformation OR misinformation OR government OR policy OR regulation) AND (briefing OR analysis OR update OR report)</t>
+        </is>
+      </c>
+      <c r="C428" t="inlineStr">
+        <is>
+          <t>China leads global surge in digital-economy patents in 2024, CNIPA report says - MLex</t>
+        </is>
+      </c>
+      <c r="D428" t="inlineStr">
+        <is>
+          <t>Fri, 16 Jan 2026 08:27:00 GMT</t>
+        </is>
+      </c>
+      <c r="E428" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxQWllIbE1jbjU1YzI1UFJxWnplazRGVVVrcExjNEtlLTFBQ1JrZUdCMUpsdUJiTFVnR3o3bVVNbmNmN3EwZmtnSEVsaTVMTnFDcmVydTk0V0tZVDFCMmZYcFNSV09nc3Ywakl4bnZSYmV6RENyZzBYX2llQU4tSTZJbDE0c1lBZ0NkZlYtYUZxMDNVTmVyYWM1YXFHTjJ2MXcxRnJ6c1MySGVrZzR4SXRTWjVkdUl0d9IBWkFVX3lxTE8yUy1fY0pxaTJaLS1EdkswdHNKYXRjVF9hNnY4YWFOeVlRbmdtMEZ6SWZNcWhHMUFDRlNYcDRMQkwxWGZxTm41eE9BLTRnai14OXBNeUR2dDlOUQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F428" t="n">
+        <v>10</v>
+      </c>
+      <c r="G428" s="2" t="n">
+        <v>46038.35208333333</v>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" t="inlineStr">
+        <is>
+          <t>Current_Affairs</t>
+        </is>
+      </c>
+      <c r="B429" t="inlineStr">
+        <is>
+          <t>(geopolitics OR migration OR economy OR conflict OR legislation OR terrorism OR disinformation OR misinformation OR government OR policy OR regulation) AND (briefing OR analysis OR update OR report)</t>
+        </is>
+      </c>
+      <c r="C429" t="inlineStr">
+        <is>
+          <t>Akin Space Law, Regulation and Policy Update | January 12, 2026 - akingump.com</t>
+        </is>
+      </c>
+      <c r="D429" t="inlineStr">
+        <is>
+          <t>Mon, 12 Jan 2026 20:00:41 GMT</t>
+        </is>
+      </c>
+      <c r="E429" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxPQmhESGdiUEQ0dlZsUDVJdk1zYUl6V1BMOW55bEpac2lKN1Rwc1o3MWZ6ZU1pSGtpVm9YS0NYUFVLMkJvWl9mYUdJOVIteWN6MF9mUXZHTzRDUHc4NGRzYS1ZWXFHRXhwVVYzdmtUWHVQMkp4Ri1TMGFGLVZSSUs2TU9Ed05oRWpOencyMEdnaFp2YkpJYVVKSGYzcU5RdDNzN0FNVjJIOGRMdWhSTzNkVA?oc=5</t>
+        </is>
+      </c>
+      <c r="F429" t="n">
+        <v>10</v>
+      </c>
+      <c r="G429" s="2" t="n">
+        <v>46034.83380787037</v>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" t="inlineStr">
+        <is>
+          <t>Current_Affairs</t>
+        </is>
+      </c>
+      <c r="B430" t="inlineStr">
+        <is>
+          <t>(geopolitics OR migration OR economy OR conflict OR legislation OR terrorism OR disinformation OR misinformation OR government OR policy OR regulation) AND (briefing OR analysis OR update OR report)</t>
+        </is>
+      </c>
+      <c r="C430" t="inlineStr">
+        <is>
+          <t>New report calls for Circular Economy Act to toughen chemical policy and avoid future public health crisis - Zero Waste Europe</t>
+        </is>
+      </c>
+      <c r="D430" t="inlineStr">
+        <is>
+          <t>Tue, 13 Jan 2026 23:02:01 GMT</t>
+        </is>
+      </c>
+      <c r="E430" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi4gFBVV95cUxPRFRETldnR1V3SXNFMGY4eUdPTWdZMFA5bzhKRmdCWXFYYWFDbUM5WFNVX19mMU9mcUVKTEh1c2RHM3pIdjZvQWRUV3hpY3haNHBOZFg0M0xTcDNzZjk0NVhEbC1LeG52ckxjYWpqQXNSYWdkZFNoUjUwQkczdGN3eWczdERaZHZVVGJEelNqX09TVnl5S3E3bncxTVVraVg4SUk4ZWVYelRMb2hYZk1NX2NDVnR0S25Ud25CX05DNk1UZVptbFR1OHU0NkdsVHRZODJia25ZT01RcVhuX1RpcmtB?oc=5</t>
+        </is>
+      </c>
+      <c r="F430" t="n">
+        <v>10</v>
+      </c>
+      <c r="G430" s="2" t="n">
+        <v>46035.9597337963</v>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" t="inlineStr">
+        <is>
+          <t>Current_Affairs</t>
+        </is>
+      </c>
+      <c r="B431" t="inlineStr">
+        <is>
+          <t>(geopolitics OR migration OR economy OR conflict OR legislation OR terrorism OR disinformation OR misinformation OR government OR policy OR regulation) AND (briefing OR analysis OR update OR report)</t>
+        </is>
+      </c>
+      <c r="C431" t="inlineStr">
+        <is>
+          <t>Macroeconomic implications of immigration flows in 2025 and 2026: January 2026 update - Brookings</t>
+        </is>
+      </c>
+      <c r="D431" t="inlineStr">
+        <is>
+          <t>Tue, 13 Jan 2026 14:01:49 GMT</t>
+        </is>
+      </c>
+      <c r="E431" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxNWld2RXZhMVNXY2hXWjVUSmFDU3htUkJoakRnSzZJT3hWRkZCbzd0ZnZBcG43a2NCMWtpUDUtdnBfaHAzdFVaNElHXzZhcUxCMjhJR2lFN3c3NXh0Y3pDcVNScVFBNlhrU185dUtNc0hLUk1mYUxBRlRVVzNuQlVjaXpsaTdBdDJtQW5NQWprZ2t1YU1obUhBYmdjR2hIXzRIVFd6VVZsRXRVY0pwNE9xSEZGdlQ1ckFUZ01Baw?oc=5</t>
+        </is>
+      </c>
+      <c r="F431" t="n">
+        <v>10</v>
+      </c>
+      <c r="G431" s="2" t="n">
+        <v>46035.58459490741</v>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" t="inlineStr">
+        <is>
+          <t>Current_Affairs</t>
+        </is>
+      </c>
+      <c r="B432" t="inlineStr">
+        <is>
+          <t>(geopolitics OR migration OR economy OR conflict OR legislation OR terrorism OR disinformation OR misinformation OR government OR policy OR regulation) AND (briefing OR analysis OR update OR report)</t>
+        </is>
+      </c>
+      <c r="C432" t="inlineStr">
+        <is>
+          <t>World Economic Forum - The World Economic Forum</t>
+        </is>
+      </c>
+      <c r="D432" t="inlineStr">
+        <is>
+          <t>Wed, 14 Jan 2026 12:28:10 GMT</t>
+        </is>
+      </c>
+      <c r="E432" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMieEFVX3lxTE9vaHVWN0hydDZzb3NKMS11SkZCYllmODJVbmdHckxncURRM3d2RUNlQzBYX0NjUVFOS0xmWU9HWGdsdXg5b2pzdG9LOUYtLWViTDhlNFpLa0tlNFdVOUlJNHNwV01VNkZEMTJHbEw2NkMtcVk4RlBReA?oc=5</t>
+        </is>
+      </c>
+      <c r="F432" t="n">
+        <v>10</v>
+      </c>
+      <c r="G432" s="2" t="n">
+        <v>46036.51956018519</v>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" t="inlineStr">
+        <is>
+          <t>Current_Affairs</t>
+        </is>
+      </c>
+      <c r="B433" t="inlineStr">
+        <is>
+          <t>(geopolitics OR migration OR economy OR conflict OR legislation OR terrorism OR disinformation OR misinformation OR government OR policy OR regulation) AND (briefing OR analysis OR update OR report)</t>
+        </is>
+      </c>
+      <c r="C433" t="inlineStr">
+        <is>
+          <t>Mozambique Conflict Monitor Update: 14 January 2026 - ReliefWeb</t>
+        </is>
+      </c>
+      <c r="D433" t="inlineStr">
+        <is>
+          <t>Thu, 15 Jan 2026 02:23:04 GMT</t>
+        </is>
+      </c>
+      <c r="E433" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMilAFBVV95cUxObVhmdzJBY3J0UjdPZWVXaFFhNjNGQ3k2T0pRV3BUdXVTTlZTNTR5VGJKYWVmZ2l2UzJaeklYUGM4eE5xeUJtRllkQUtOZnU2bXlNLU5GN0EzLTBtTnU3d0xZZG9FM2dGSUx5bHR1X3JwSjRIby1Nb25ZRHFhSzlYYm9IVG9pQXpldlpvVzZ6U1pxTVNa?oc=5</t>
+        </is>
+      </c>
+      <c r="F433" t="n">
+        <v>10</v>
+      </c>
+      <c r="G433" s="2" t="n">
+        <v>46037.09935185185</v>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" t="inlineStr">
+        <is>
+          <t>Current_Affairs</t>
+        </is>
+      </c>
+      <c r="B434" t="inlineStr">
+        <is>
+          <t>(geopolitics OR migration OR economy OR conflict OR legislation OR terrorism OR disinformation OR misinformation OR government OR policy OR regulation) AND (briefing OR analysis OR update OR report)</t>
+        </is>
+      </c>
+      <c r="C434" t="inlineStr">
+        <is>
+          <t>Mexico market intelligence report, produced in partnership with Gamingsoft - igamingbusiness.com</t>
+        </is>
+      </c>
+      <c r="D434" t="inlineStr">
+        <is>
+          <t>Thu, 15 Jan 2026 17:05:33 GMT</t>
+        </is>
+      </c>
+      <c r="E434" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiigFBVV95cUxNOTExckVLeU9STE0tQVQtbVBFVWktZ2N6SkVEV1QxMVFCOVZLRXdzZGJ2UzFFQThqaWJhNUU1bG1MbHgzdWc5Mm5ZVm1QVFZhZklrLWZmN2pkV09aRzBXVHp0SUVGNllnNUthS1c3WXBSbm5pN1BnUF9vRnFHeElWUmRPVElIaU9qTFE?oc=5</t>
+        </is>
+      </c>
+      <c r="F434" t="n">
+        <v>10</v>
+      </c>
+      <c r="G434" s="2" t="n">
+        <v>46037.7121875</v>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" t="inlineStr">
+        <is>
+          <t>Current_Affairs</t>
+        </is>
+      </c>
+      <c r="B435" t="inlineStr">
+        <is>
+          <t>(geopolitics OR migration OR economy OR conflict OR legislation OR terrorism OR disinformation OR misinformation OR government OR policy OR regulation) AND (briefing OR analysis OR update OR report)</t>
+        </is>
+      </c>
+      <c r="C435" t="inlineStr">
+        <is>
+          <t>Anthropic Economic Index report: Economic primitives - Anthropic</t>
+        </is>
+      </c>
+      <c r="D435" t="inlineStr">
+        <is>
+          <t>Thu, 15 Jan 2026 10:15:25 GMT</t>
+        </is>
+      </c>
+      <c r="E435" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMihgFBVV95cUxONjBKV3ctWnNQbFZYMXAxalVSNllfM0VTb3U2ZmhFWEZoanFLc1FZMFY4bW1ydnViOUtTU0JjbTRBRlFidmRzUnZiTjFHNWFKMG9taDREVVJFb3FSUWNrdDY0NUVPZV9RS0RoNGlMQ1RLZk5lN0pHR3lYV21SemhZU0xaMjNDdw?oc=5</t>
+        </is>
+      </c>
+      <c r="F435" t="n">
+        <v>10</v>
+      </c>
+      <c r="G435" s="2" t="n">
+        <v>46037.42737268518</v>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" t="inlineStr">
+        <is>
+          <t>Current_Affairs</t>
+        </is>
+      </c>
+      <c r="B436" t="inlineStr">
+        <is>
+          <t>(geopolitics OR migration OR economy OR conflict OR legislation OR terrorism OR disinformation OR misinformation OR government OR policy OR regulation) AND (briefing OR analysis OR update OR report)</t>
+        </is>
+      </c>
+      <c r="C436" t="inlineStr">
+        <is>
+          <t>Italy Tractor Market Research Report 2025-2030: Government Subsidies, CAP Funding, and Expanding Organic Farming Accelerate Equipment Demand - Yahoo Finance UK</t>
+        </is>
+      </c>
+      <c r="D436" t="inlineStr">
+        <is>
+          <t>Thu, 15 Jan 2026 10:05:00 GMT</t>
+        </is>
+      </c>
+      <c r="E436" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMijgFBVV95cUxOSnVwQjdoN3p6VnBrb25wN0dfMS0yRXM4MVZBNnBHY1VrZGdDOEhBZmlUTUpLWkVQNFpfMFBQNFAzRC1vVU51Sk1DazhkdzNiLVdOREFqVUZUdjc0bGd4ZU1VTE1nVlJtOGoySHVseFlQM3ZxUmw5aTRsbWFDeFlFQ0VoQlFXekFISVBhV0dn?oc=5</t>
+        </is>
+      </c>
+      <c r="F436" t="n">
+        <v>10</v>
+      </c>
+      <c r="G436" s="2" t="n">
+        <v>46037.42013888889</v>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" t="inlineStr">
+        <is>
+          <t>Current_Affairs</t>
+        </is>
+      </c>
+      <c r="B437" t="inlineStr">
+        <is>
+          <t>(geopolitics OR migration OR economy OR conflict OR legislation OR terrorism OR disinformation OR misinformation OR government OR policy OR regulation) AND (briefing OR analysis OR update OR report)</t>
+        </is>
+      </c>
+      <c r="C437" t="inlineStr">
+        <is>
+          <t>Sri Lanka: Report on conflict-related sexual violence - ohchr</t>
+        </is>
+      </c>
+      <c r="D437" t="inlineStr">
+        <is>
+          <t>Tue, 13 Jan 2026 11:33:08 GMT</t>
+        </is>
+      </c>
+      <c r="E437" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxOLUJPaC1ZN0hRaWRKZG1MYXhjVTFHZlp4V3hlMC0tcTM2bXVYOVBudUFtLWMtRmNvVFdyclFaTGo5eHNmblB2UGR1TUwyb0s1Z1NCMWRNQTRuWnJPNV9zOGxOVHk1aVozX2NiLUpyTzdFZE5hR2RjZzNuVkVzX1c3Nm1ETmprRVFQN1gxX2g1dDR1VU9SdHhnX2dtakhpOE5xTzVvREVB?oc=5</t>
+        </is>
+      </c>
+      <c r="F437" t="n">
+        <v>10</v>
+      </c>
+      <c r="G437" s="2" t="n">
+        <v>46035.48134259259</v>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" t="inlineStr">
+        <is>
+          <t>Current_Affairs</t>
+        </is>
+      </c>
+      <c r="B438" t="inlineStr">
+        <is>
+          <t>(geopolitics OR migration OR economy OR conflict OR legislation OR terrorism OR disinformation OR misinformation OR government OR policy OR regulation) AND (briefing OR analysis OR update OR report)</t>
+        </is>
+      </c>
+      <c r="C438" t="inlineStr">
+        <is>
+          <t>US, for 1st time in 50 years, experienced negative net migration in 2025: Report - Yahoo News UK</t>
+        </is>
+      </c>
+      <c r="D438" t="inlineStr">
+        <is>
+          <t>Tue, 13 Jan 2026 23:30:35 GMT</t>
+        </is>
+      </c>
+      <c r="E438" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMibkFVX3lxTFBiaXNoV1RjSnQzNnNuZVNXVGE3QXVnak9Sa1lCeEdRSHo2TW9JWHo0NWZ1MDAxdl9xS19ldXcxVjl0WTh1MWU2SVFkQ0VCUEJvX3FYNXlHcVFLSlMzRTk3NTdTVVprbFZHZVU0d2tn?oc=5</t>
+        </is>
+      </c>
+      <c r="F438" t="n">
+        <v>10</v>
+      </c>
+      <c r="G438" s="2" t="n">
+        <v>46035.97957175926</v>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" t="inlineStr">
+        <is>
+          <t>Current_Affairs</t>
+        </is>
+      </c>
+      <c r="B439" t="inlineStr">
+        <is>
+          <t>(geopolitics OR migration OR economy OR conflict OR legislation OR terrorism OR disinformation OR misinformation OR government OR policy OR regulation) AND (briefing OR analysis OR update OR report)</t>
+        </is>
+      </c>
+      <c r="C439" t="inlineStr">
+        <is>
+          <t>Russia Loses Venezuela, the Avocado Ally - Center for European Policy Analysis (CEPA)</t>
+        </is>
+      </c>
+      <c r="D439" t="inlineStr">
+        <is>
+          <t>Tue, 13 Jan 2026 14:37:35 GMT</t>
+        </is>
+      </c>
+      <c r="E439" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMic0FVX3lxTE9IS1diZnVyemFQMjJ1cHNvZGxuaFFEaWlnVGlrMnpuTG1mRl9XakItUFV4ZTlWMllXWGpGVnBncDJoS3B3bUdqbFRudFdMeUN3TE9YWkVhMWtCVWVka2V6TU1nZWUyNV9MUnlLS1JkTm9qTUE?oc=5</t>
+        </is>
+      </c>
+      <c r="F439" t="n">
+        <v>10</v>
+      </c>
+      <c r="G439" s="2" t="n">
+        <v>46035.60943287037</v>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" t="inlineStr">
+        <is>
+          <t>Current_Affairs</t>
+        </is>
+      </c>
+      <c r="B440" t="inlineStr">
+        <is>
+          <t>(geopolitics OR migration OR economy OR conflict OR legislation OR terrorism OR disinformation OR misinformation OR government OR policy OR regulation) AND (briefing OR analysis OR update OR report)</t>
+        </is>
+      </c>
+      <c r="C440" t="inlineStr">
+        <is>
+          <t>Iran Endgame? Protests, Repression, and the Trump Administration - The Washington Institute</t>
+        </is>
+      </c>
+      <c r="D440" t="inlineStr">
+        <is>
+          <t>Wed, 14 Jan 2026 13:40:15 GMT</t>
+        </is>
+      </c>
+      <c r="E440" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxNVkJOaFZydFQ3ZTFvWFVsQ3NLWmlzTXBNRUxNc29DdUZXenFVdFQ4X1VsWUhMdlZ3dlZpRHJfYjR1RW95Nk5ZQTF1S3dXWG1OTFBxR1BiVGlIZnEweUN2M0NjSVhOa1lRckU4UlNXMVo2cHlfV1lJczkxSEJ1MzkzcXRzOUVSdDRmSnBZSzU3RkVWMkRnSVlBaFhVZU9tbVVfR19tbUxJZWtlV3VUUlE?oc=5</t>
+        </is>
+      </c>
+      <c r="F440" t="n">
+        <v>10</v>
+      </c>
+      <c r="G440" s="2" t="n">
+        <v>46036.56961805555</v>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" t="inlineStr">
+        <is>
+          <t>Current_Affairs</t>
+        </is>
+      </c>
+      <c r="B441" t="inlineStr">
+        <is>
+          <t>(geopolitics OR migration OR economy OR conflict OR legislation OR terrorism OR disinformation OR misinformation OR government OR policy OR regulation) AND (briefing OR analysis OR update OR report)</t>
+        </is>
+      </c>
+      <c r="C441" t="inlineStr">
+        <is>
+          <t>Government update issued on 'dangerous dogs' breed bans like XL Bullies in UK - The Mirror</t>
+        </is>
+      </c>
+      <c r="D441" t="inlineStr">
+        <is>
+          <t>Mon, 12 Jan 2026 05:10:00 GMT</t>
+        </is>
+      </c>
+      <c r="E441" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMijwFBVV95cUxOOWNGb2k2ZGdmY29mNk4xbTJmNVYwejN0bk5neTlQTnhPUkk0UXpJTDNBZWFOZHJQYVNvMDBQOXdyY0sxT2ZRZHRrRVRZN1Z4Tzd4NXFmUjRlV3RwNkNFZTJ2X2ZEdW1OWl9TWHNxVVVSN0FkNDhHcmNfU2JQeE9fZm44ZlNsQUFkdjl2SGlrQdIBlAFBVV95cUxOODJkNlcwR3lFQnp6bTdlYTMtRTZSS3FWaWJHNjlXOFJTZ3ZZWGI0NEVPcWl2VzhkbFJvc0xteGJuZklvY0k5TllaT0IyaEFXdnJnMkd4YmhqekcwSEtOSEoxemxGbGxRZmt2Qm5BRjY0N1lwRDVtX09PQjVTUjFfVUlfbWdjLV9iY1ZLUkY4RmhwNGVR?oc=5</t>
+        </is>
+      </c>
+      <c r="F441" t="n">
+        <v>10</v>
+      </c>
+      <c r="G441" s="2" t="n">
+        <v>46034.21527777778</v>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" t="inlineStr">
+        <is>
+          <t>Supply_Chain</t>
+        </is>
+      </c>
+      <c r="B442" t="inlineStr">
+        <is>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+        </is>
+      </c>
+      <c r="C442" t="inlineStr">
+        <is>
+          <t>China and Canada announce tariffs relief after a high-stakes meeting - BBC</t>
+        </is>
+      </c>
+      <c r="D442" t="inlineStr">
+        <is>
+          <t>Fri, 16 Jan 2026 10:41:05 GMT</t>
+        </is>
+      </c>
+      <c r="E442" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTE05OEw5WHl2amlqTE1pbXJhNmFfZlhyZ3pSQVhrc0c3aUhCNmRNQkl2TUhudS0wbXc1OW9kcVlMeDhSWWxzWk1JbktKREpmemZwUTM5a19HOUlHZ9IBX0FVX3lxTFA0YlRDSE1oRGRSSkZHa2ZmT2lvUkdKOTFGNU5qZDdoUXF1bU1ReHRwYy1iUGtxTHpIeWRjYktIU3hYWDJ0LS1BRmRGQWgtLUw3aDJuOVdMdVJ2VTB0Tmw0?oc=5</t>
+        </is>
+      </c>
+      <c r="F442" t="n">
+        <v>10</v>
+      </c>
+      <c r="G442" s="2" t="n">
+        <v>46038.44519675926</v>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" t="inlineStr">
+        <is>
+          <t>Supply_Chain</t>
+        </is>
+      </c>
+      <c r="B443" t="inlineStr">
+        <is>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+        </is>
+      </c>
+      <c r="C443" t="inlineStr">
+        <is>
+          <t>Greenland: new shipping routes, hidden minerals – and a frontline between the US and Russia? - The Guardian</t>
+        </is>
+      </c>
+      <c r="D443" t="inlineStr">
+        <is>
+          <t>Fri, 16 Jan 2026 02:30:00 GMT</t>
+        </is>
+      </c>
+      <c r="E443" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMizgFBVV95cUxNZHJES1dSSjdBNnV0dVN0M2xweEJGb3FjTUpGLU11SkozNXF2eXpWT3lKUVhkckpTLUVvZUw0cFdLczA1MUpYMEloVF9LeldyeGpkbVFSb0VETDEtOExEelpISTBBZkZwTHZpOW14Zm9TTTU2dGNlbHZsb2J5THJGX1FBMWkwX1lWdWhLSkdWRk5FUGQwVEV6Y1laYTQ3U3lJMy1WQjhubVVpYjNEOGNQTXdmOWVQWjZ2WEFOV3lQcnZyWmtrbGF0UHlQSnU1QQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F443" t="n">
+        <v>10</v>
+      </c>
+      <c r="G443" s="2" t="n">
+        <v>46038.10416666666</v>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" t="inlineStr">
+        <is>
+          <t>Supply_Chain</t>
+        </is>
+      </c>
+      <c r="B444" t="inlineStr">
+        <is>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+        </is>
+      </c>
+      <c r="C444" t="inlineStr">
+        <is>
+          <t>Discover the benefits of digitising warehouse workflows at Sustainable Supply Chain Exhibition - Logistics Manager</t>
+        </is>
+      </c>
+      <c r="D444" t="inlineStr">
+        <is>
+          <t>Fri, 16 Jan 2026 09:00:12 GMT</t>
+        </is>
+      </c>
+      <c r="E444" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxQTE9ZYlNXaXJvS0JuUUxEM0JEcWhEbnZVOUZ2Z3QxRFAwell2akFtSm9SNFl2ZC1vY2FaUHhwQ1pIdFFlYU84aEM4WDVUSzFXTDBfVXNoNWkyY0p2bDJGRTBOQTlwaFJIQXcxS2dQZ0xSbUJWWkpZaXp0cHJtYkt6WHd4UDg3ZlkweTJIaDQtWmlqUTZROGxOTUdxOHhZNnpTTnc?oc=5</t>
+        </is>
+      </c>
+      <c r="F444" t="n">
+        <v>10</v>
+      </c>
+      <c r="G444" s="2" t="n">
+        <v>46038.37513888889</v>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445" t="inlineStr">
+        <is>
+          <t>Supply_Chain</t>
+        </is>
+      </c>
+      <c r="B445" t="inlineStr">
+        <is>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+        </is>
+      </c>
+      <c r="C445" t="inlineStr">
+        <is>
+          <t>This Week's Top Five Stories in Supply Chain - Supply Chain Digital Magazine</t>
+        </is>
+      </c>
+      <c r="D445" t="inlineStr">
+        <is>
+          <t>Fri, 16 Jan 2026 11:08:53 GMT</t>
+        </is>
+      </c>
+      <c r="E445" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMijwFBVV95cUxNR0oyUGJOei1WTHJOcTRTbFRCV2NtRy0zSzBXR1QxTldaSXNGMzBQZVUwdTRhVFpOU1Z0S0plM0dGSndFejlrWDllVkprYTRNdE9hWTBQT1hRLVplaXlaRW42NUZuSFVld2dWNVUwbjJXMzgwQ25OVGN0Wnc2X2VNSEhJMWxOVHhLa2lGQW1KOA?oc=5</t>
+        </is>
+      </c>
+      <c r="F445" t="n">
+        <v>10</v>
+      </c>
+      <c r="G445" s="2" t="n">
+        <v>46038.46450231481</v>
+      </c>
+    </row>
+    <row r="446">
+      <c r="A446" t="inlineStr">
+        <is>
+          <t>Supply_Chain</t>
+        </is>
+      </c>
+      <c r="B446" t="inlineStr">
+        <is>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+        </is>
+      </c>
+      <c r="C446" t="inlineStr">
+        <is>
+          <t>Swissport partners up with Scan Global Logistics and launches its first dedicated perishables centre in the UK - Scan Global Logistics</t>
+        </is>
+      </c>
+      <c r="D446" t="inlineStr">
+        <is>
+          <t>Fri, 16 Jan 2026 09:04:50 GMT</t>
+        </is>
+      </c>
+      <c r="E446" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi1gFBVV95cUxPdnFIUTRfeHdTMFkyaFM0b0RhVnQ1U2MwY1NNZjA4WXZXalJOenBPaEhydmN1Q2lOVlFCdTFvb2xBWVJrMHp3MFhfbDlZTV9Eb0FRRVRZQWRNc0M0bnNnLXVOaWktTWVqM0QwQVpsYmQxaGRLdWJkbFJUOFZBTkptVHFPcUxGR1ptRXB0UTZNaFoyd2xLb2p5U21SbVFyWEVjNkRCSzlUekl1ZjM2X2dvRUg0T2JPWDZ2ZmpxQ3otSWZQLWdEei16a2pmMGh4UXQxVUxwRzBR?oc=5</t>
+        </is>
+      </c>
+      <c r="F446" t="n">
+        <v>10</v>
+      </c>
+      <c r="G446" s="2" t="n">
+        <v>46038.37835648148</v>
+      </c>
+    </row>
+    <row r="447">
+      <c r="A447" t="inlineStr">
+        <is>
+          <t>Supply_Chain</t>
+        </is>
+      </c>
+      <c r="B447" t="inlineStr">
+        <is>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+        </is>
+      </c>
+      <c r="C447" t="inlineStr">
+        <is>
+          <t>Maersk resumes shipping through Red Sea after ceasefire - Financial Times</t>
+        </is>
+      </c>
+      <c r="D447" t="inlineStr">
+        <is>
+          <t>Thu, 15 Jan 2026 12:44:08 GMT</t>
+        </is>
+      </c>
+      <c r="E447" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMicEFVX3lxTE1qS042VlVfcEk2NWxqZi16cVpNVFI0NE43ZWZVTWY3R3ZORXNMd1NVOFJmdk12SUNjZ1diYkIwV1JYTWZiT29ZMW9hUmY1QWR2RkNvQ18tdElwXzhreVJocC0xUFh3WFFwbTFNM1p2SWs?oc=5</t>
+        </is>
+      </c>
+      <c r="F447" t="n">
+        <v>10</v>
+      </c>
+      <c r="G447" s="2" t="n">
+        <v>46037.53064814815</v>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" t="inlineStr">
+        <is>
+          <t>Supply_Chain</t>
+        </is>
+      </c>
+      <c r="B448" t="inlineStr">
+        <is>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+        </is>
+      </c>
+      <c r="C448" t="inlineStr">
+        <is>
+          <t>Trump puts silver, other critical minerals tariffs on hold - ING THINK economic and financial analysis | ING Think</t>
+        </is>
+      </c>
+      <c r="D448" t="inlineStr">
+        <is>
+          <t>Thu, 15 Jan 2026 12:38:42 GMT</t>
+        </is>
+      </c>
+      <c r="E448" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMic0FVX3lxTE5ESGptamE2MW53NnltOWZQREZraG9WejBfNk5uT19FMFI4NnBBSTBHRFJndEcwWTRRX01nRG1aVmt1R2VTclQ1VUtaZGNha3k5NmFZX3RUMm1CRjJEd2N6VnFTMEExUnBZQjNYUWxLMktIWHc?oc=5</t>
+        </is>
+      </c>
+      <c r="F448" t="n">
+        <v>10</v>
+      </c>
+      <c r="G448" s="2" t="n">
+        <v>46037.526875</v>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449" t="inlineStr">
+        <is>
+          <t>Supply_Chain</t>
+        </is>
+      </c>
+      <c r="B449" t="inlineStr">
+        <is>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+        </is>
+      </c>
+      <c r="C449" t="inlineStr">
+        <is>
+          <t>Research examines social landlords’ compliance with human rights law - Scottish Housing News</t>
+        </is>
+      </c>
+      <c r="D449" t="inlineStr">
+        <is>
+          <t>Fri, 16 Jan 2026 09:24:06 GMT</t>
+        </is>
+      </c>
+      <c r="E449" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxPTHZkdnlCNVl5aHduaFpXSnAteG5NS3V5YU9lUlBMX2FPeVBtZmpfajBVSzFveFJ4MXd6QzNhYmdhZmZ0V3VZdGF6ZFpHcEttcHlqRDNINFdFTGVvLVN2R21GdHZVWFhhUFVwblZBMU90bkZRblY2RU1wanBSVzRDQkhXa0NCcF81bFdDekdLVmYtdHRveUxIOEFrRjF2YUxoMkhMVUd0LVBnWTcxSWJqRGlB?oc=5</t>
+        </is>
+      </c>
+      <c r="F449" t="n">
+        <v>10</v>
+      </c>
+      <c r="G449" s="2" t="n">
+        <v>46038.39173611111</v>
+      </c>
+    </row>
+    <row r="450">
+      <c r="A450" t="inlineStr">
+        <is>
+          <t>Supply_Chain</t>
+        </is>
+      </c>
+      <c r="B450" t="inlineStr">
+        <is>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+        </is>
+      </c>
+      <c r="C450" t="inlineStr">
+        <is>
+          <t>Taiwan and US seal deal to lower tariffs, boost chip investment - Al Jazeera</t>
+        </is>
+      </c>
+      <c r="D450" t="inlineStr">
+        <is>
+          <t>Fri, 16 Jan 2026 08:53:28 GMT</t>
+        </is>
+      </c>
+      <c r="E450" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxPOUk4UC05RXpJQTk2YkxveVpBRVRGZ0h3UEI1YVFhMDRNT1pZTGZxVGs3V0hSZ2FkWGJOdk9pbFhzQzFXcFdNQUJPMW5nY1AtaWpncFR1UGFhQnRNVUJ2SThmZmtYc09PTnVRelY0d2l6ZmhDU2M4VzNOTEM5ZEMzamY1S3pzcU9XMXRDMzJHamI4akVtTVFpamc2U2M0YTl2dkVxOUN30gGrAUFVX3lxTE9XSUVIYnl3WHN5TlV0endpTUpCZHZINXVfTXJ2NkRRZlVXaUFxR1VlY0tNMnBpTnZieGVTMngxckt4cUFXZVRZZ3JKeHNpRVdPcTA5d2NpNUM4dmRfa3lJR1l3ZGdXRE1uVkRPVXdSWnhfdmN0cENhNDI1cnpzU09PRk1CdWFmMXlvZDZuS01RUkpJaDRLUS1Fd3pHVTBNcFNjc1l2dlVKWjBEZw?oc=5</t>
+        </is>
+      </c>
+      <c r="F450" t="n">
+        <v>10</v>
+      </c>
+      <c r="G450" s="2" t="n">
+        <v>46038.37046296296</v>
+      </c>
+    </row>
+    <row r="451">
+      <c r="A451" t="inlineStr">
+        <is>
+          <t>Supply_Chain</t>
+        </is>
+      </c>
+      <c r="B451" t="inlineStr">
+        <is>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+        </is>
+      </c>
+      <c r="C451" t="inlineStr">
+        <is>
+          <t>How is XPO Prioritising Sustainability in Logistics? - Sustainability Magazine</t>
+        </is>
+      </c>
+      <c r="D451" t="inlineStr">
+        <is>
+          <t>Fri, 16 Jan 2026 10:21:11 GMT</t>
+        </is>
+      </c>
+      <c r="E451" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiggFBVV95cUxPZjFLRDNVU0hrRXZCRzVTblNQbEQ4TWwwbzBtR2FBekJsbVdVUDN1c2hLZWZUbGZXbkxkUkd3YXNRQlBRU0NrRXczSHU3dFJWNG03eUc5ZWhvWF9YYTF2OWNWX21sN1lfa0I0bXFyYTRoRURkc2gzeUUyZFNBY2tmcmZR?oc=5</t>
+        </is>
+      </c>
+      <c r="F451" t="n">
+        <v>10</v>
+      </c>
+      <c r="G451" s="2" t="n">
+        <v>46038.43137731482</v>
+      </c>
+    </row>
+    <row r="452">
+      <c r="A452" t="inlineStr">
+        <is>
+          <t>Supply_Chain</t>
+        </is>
+      </c>
+      <c r="B452" t="inlineStr">
+        <is>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+        </is>
+      </c>
+      <c r="C452" t="inlineStr">
+        <is>
+          <t>Dun &amp; Bradstreet outlines seven key compliance trends - IT Brief UK</t>
+        </is>
+      </c>
+      <c r="D452" t="inlineStr">
+        <is>
+          <t>Fri, 16 Jan 2026 09:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="E452" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMihgFBVV95cUxPMVlWR2o4QlFlZXVDakFPRUVmNGI2QmlOYnFzN2l2b3RELWpKdmhucndMS3JLMnZqOGhQenpFR3NXNU5WMm53dWxqM3NoUnJtU3pnV0JhSi1JYWxNc3Z2RDByWGVMbzA3ZkU1M3BqX0R3amlidk94a21ZdTNKR0RJNkVRdWYtZw?oc=5</t>
+        </is>
+      </c>
+      <c r="F452" t="n">
+        <v>10</v>
+      </c>
+      <c r="G452" s="2" t="n">
+        <v>46038.375</v>
+      </c>
+    </row>
+    <row r="453">
+      <c r="A453" t="inlineStr">
+        <is>
+          <t>Supply_Chain</t>
+        </is>
+      </c>
+      <c r="B453" t="inlineStr">
+        <is>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+        </is>
+      </c>
+      <c r="C453" t="inlineStr">
+        <is>
+          <t>Athens breaks EU ranks to side with US and Saudi Arabia in green shipping row - Euractiv</t>
+        </is>
+      </c>
+      <c r="D453" t="inlineStr">
+        <is>
+          <t>Fri, 16 Jan 2026 10:52:00 GMT</t>
+        </is>
+      </c>
+      <c r="E453" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxOUGlFaXNzWVhSZnd3YndBQ3Y0SmZoYkNYZEZYZTFjTC1jQVlCNU1vWjAtU3RaM3dYMWpZZHZYSGVuQ0U5Q0p1bmFGeEFBdzdIYndac1pFcHdWVHQzbFRFSW1TZ2xrcXBwWGlJd1cxaTNDdGdNbGNrT2NVa2xIVlFrMU5EbWRyWE1UOGY2UUR3REladzNQVGpNa0xtQnRoRWV5Z0dSNWJKdVNRZG9f?oc=5</t>
+        </is>
+      </c>
+      <c r="F453" t="n">
+        <v>10</v>
+      </c>
+      <c r="G453" s="2" t="n">
+        <v>46038.45277777778</v>
+      </c>
+    </row>
+    <row r="454">
+      <c r="A454" t="inlineStr">
+        <is>
+          <t>Supply_Chain</t>
+        </is>
+      </c>
+      <c r="B454" t="inlineStr">
+        <is>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+        </is>
+      </c>
+      <c r="C454" t="inlineStr">
+        <is>
+          <t>UBCivils benefit from Podfather logistics software - Agg-Net</t>
+        </is>
+      </c>
+      <c r="D454" t="inlineStr">
+        <is>
+          <t>Fri, 16 Jan 2026 08:35:50 GMT</t>
+        </is>
+      </c>
+      <c r="E454" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMihgFBVV95cUxOQm5QQXFNVnVrSnpDZU1lZERZWEk5X0VSSDN5a3FTMmNQemhQblVqRm1kS1BHWGlJMjJVWWxZTjdwLVNKQ2lkZUdRLU5PLXRrMWV1NDg0ZUI0Y1d3X2ppNGhjalktM01LdTVxeEt2NFgxVFdtbUE3U1lxNk1yRGZ4N2pxODZWQQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F454" t="n">
+        <v>10</v>
+      </c>
+      <c r="G454" s="2" t="n">
+        <v>46038.35821759259</v>
+      </c>
+    </row>
+    <row r="455">
+      <c r="A455" t="inlineStr">
+        <is>
+          <t>Supply_Chain</t>
+        </is>
+      </c>
+      <c r="B455" t="inlineStr">
+        <is>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+        </is>
+      </c>
+      <c r="C455" t="inlineStr">
+        <is>
+          <t>What are tariffs, how do they work and why is Trump using them? - BBC</t>
+        </is>
+      </c>
+      <c r="D455" t="inlineStr">
+        <is>
+          <t>Wed, 14 Jan 2026 16:32:50 GMT</t>
+        </is>
+      </c>
+      <c r="E455" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTFBweHdveUp5S2F0aGJwSEs2U2lOMkF6NzRNZTd3bEJUdTQwVjhRX0pjZmFzZ25hRzk4MHE0WW9KVkEtUjIxRUNWbXRzX3pmd1A5UWhyaE5Ja1ZWd9IBX0FVX3lxTE82Y0Q0dVVkNUhXb1o4Tkt6V1AycjA1dmkzbUs3d3JydDktMVNrSnNsNDI1Zk9BdmpMc1BQbGJneThSUDBmUkdUdFhDVTZaTTRGaGlwdDhnR3NPeXhDYW9F?oc=5</t>
+        </is>
+      </c>
+      <c r="F455" t="n">
+        <v>10</v>
+      </c>
+      <c r="G455" s="2" t="n">
+        <v>46036.68946759259</v>
+      </c>
+    </row>
+    <row r="456">
+      <c r="A456" t="inlineStr">
+        <is>
+          <t>Supply_Chain</t>
+        </is>
+      </c>
+      <c r="B456" t="inlineStr">
+        <is>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+        </is>
+      </c>
+      <c r="C456" t="inlineStr">
+        <is>
+          <t>White House sets tariffs to take 25% cut of Nvidia and AMD sales in China - Financial Times</t>
+        </is>
+      </c>
+      <c r="D456" t="inlineStr">
+        <is>
+          <t>Wed, 14 Jan 2026 23:54:51 GMT</t>
+        </is>
+      </c>
+      <c r="E456" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMicEFVX3lxTE5fYS1DbVhzSWEtSF9BVGRxcThLM0R2T2YyNm1yX2lqRGMtV2V2dG5EOU9iR1FhWUVHbGVlUWV5SVFNUHhLOER5QkgyNnV2TTRubEp1WWZ5a1JQQW9Ba3JDSFkyTHo0a1ZpbUlwYlh2V2c?oc=5</t>
+        </is>
+      </c>
+      <c r="F456" t="n">
+        <v>10</v>
+      </c>
+      <c r="G456" s="2" t="n">
+        <v>46036.99642361111</v>
+      </c>
+    </row>
+    <row r="457">
+      <c r="A457" t="inlineStr">
+        <is>
+          <t>Supply_Chain</t>
+        </is>
+      </c>
+      <c r="B457" t="inlineStr">
+        <is>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+        </is>
+      </c>
+      <c r="C457" t="inlineStr">
+        <is>
+          <t>US military seizes Venezuela oil tanker under Trump sanctions - The Guardian</t>
+        </is>
+      </c>
+      <c r="D457" t="inlineStr">
+        <is>
+          <t>Fri, 16 Jan 2026 02:30:00 GMT</t>
+        </is>
+      </c>
+      <c r="E457" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMijAFBVV95cUxPTzI4Qy1zSWU2amVTN0ZSaWRINWFpYmpmQ0dxTzljem9uVTQzNC05M1ZkZGJuQ19oREpSSXJJSWRpakpqbnpvMm9kNDNGeUtCZGJzZ0pVYzlDR0Y3c05WTUpoQkVndzc2YVVIN1NYcUZrSmNEN2I0bUZYTDRPc3F3VW5uMWZhcXdLM1pudQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F457" t="n">
+        <v>10</v>
+      </c>
+      <c r="G457" s="2" t="n">
+        <v>46038.10416666666</v>
+      </c>
+    </row>
+    <row r="458">
+      <c r="A458" t="inlineStr">
+        <is>
+          <t>Supply_Chain</t>
+        </is>
+      </c>
+      <c r="B458" t="inlineStr">
+        <is>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+        </is>
+      </c>
+      <c r="C458" t="inlineStr">
+        <is>
+          <t>Chinese leader Xi Jinping hails 'turnaround' in China-Canada ties as Mark Carney visits Beijing - BBC</t>
+        </is>
+      </c>
+      <c r="D458" t="inlineStr">
+        <is>
+          <t>Fri, 16 Jan 2026 09:57:13 GMT</t>
+        </is>
+      </c>
+      <c r="E458" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiVEFVX3lxTE1OM1A3NDNhemV3YU1jZk9ENHltOXdCT3puT3F0dXhGT1Vsa1BuRDZoNEZjcnlVbmlINlE3Zm9FcXBRTlpZV1R4SHpINzFVVGNCY0lXMQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F458" t="n">
+        <v>10</v>
+      </c>
+      <c r="G458" s="2" t="n">
+        <v>46038.41473379629</v>
+      </c>
+    </row>
+    <row r="459">
+      <c r="A459" t="inlineStr">
+        <is>
+          <t>Supply_Chain</t>
+        </is>
+      </c>
+      <c r="B459" t="inlineStr">
+        <is>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+        </is>
+      </c>
+      <c r="C459" t="inlineStr">
+        <is>
+          <t>China reports record trillion-dollar trade surplus despite Trump tariffs - The Guardian</t>
+        </is>
+      </c>
+      <c r="D459" t="inlineStr">
+        <is>
+          <t>Wed, 14 Jan 2026 15:08:00 GMT</t>
+        </is>
+      </c>
+      <c r="E459" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxNQ0RKdmF5eXBiMl9VUzJZT3YzMHI4UmNQeWt6Z21IWG1MbWZqV1U3MHpwWnZya0ZpWktuOGdOVXd4Vlp1aTFXZElBT2dfUnJlVWxOWnRBX2gwUTJkYlJGRzJZRXN3ck0zbUxWRzNWbWxKRWlVVXI4cDdKd2pLU3lDQlliNUVEaVhJQ1p5MTloTEI1VS1zQ2FkVFRyOEhlX01rVXJodU5tQ0FNU2RGMGJ2aUhZdWJoeWtJTlE?oc=5</t>
+        </is>
+      </c>
+      <c r="F459" t="n">
+        <v>10</v>
+      </c>
+      <c r="G459" s="2" t="n">
+        <v>46036.63055555556</v>
+      </c>
+    </row>
+    <row r="460">
+      <c r="A460" t="inlineStr">
+        <is>
+          <t>Supply_Chain</t>
+        </is>
+      </c>
+      <c r="B460" t="inlineStr">
+        <is>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+        </is>
+      </c>
+      <c r="C460" t="inlineStr">
+        <is>
+          <t>Green Shipping Corridors Can Help Scale India’s Green Hydrogen Ecosystem - RMI</t>
+        </is>
+      </c>
+      <c r="D460" t="inlineStr">
+        <is>
+          <t>Fri, 16 Jan 2026 11:37:31 GMT</t>
+        </is>
+      </c>
+      <c r="E460" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMikgFBVV95cUxQUlBBVUMwLXIyMElfbE1HaXdhbHgzdWx3anZiNHZNLWJzQ3NfUmdGQUY3QjRVcGloZDNIZlFnYW9YUFUyYVROME1hSXJrWG40NVh1c3p6M3MyWDlQU1JmUnFsaE1OSHRJbHFvUkxNRkFrQWhmc1ZwWUZTZzF2TVZsT0hJU0xMeWtMWTJIMXBCZkhLZw?oc=5</t>
+        </is>
+      </c>
+      <c r="F460" t="n">
+        <v>10</v>
+      </c>
+      <c r="G460" s="2" t="n">
+        <v>46038.48438657408</v>
+      </c>
+    </row>
+    <row r="461">
+      <c r="A461" t="inlineStr">
+        <is>
+          <t>Supply_Chain</t>
+        </is>
+      </c>
+      <c r="B461" t="inlineStr">
+        <is>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+        </is>
+      </c>
+      <c r="C461" t="inlineStr">
+        <is>
+          <t>Inchcape Shipping Services opens new office in Peru, strengthening presence in South America — SMI DIGITAL - shipmanagementinternational.com</t>
+        </is>
+      </c>
+      <c r="D461" t="inlineStr">
+        <is>
+          <t>Fri, 16 Jan 2026 10:06:46 GMT</t>
+        </is>
+      </c>
+      <c r="E461" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi2gFBVV95cUxOV3N1NWJudDV5VUNfSVFxTm1DamhHaG9qUGRPQld1TEpxRk9TajFUNE1zSkFRY3o1U3lwZURzZUpDREgxTVVJT2VTWUU4bW1OSEQtYXF2X25DLUxsd1BrVWFiMXdiWlFXdnJBZ2ttbGZzSGZDNk5ZRUN6SHp5Y1owQ19malZqcW5fSU04UWZiQVIyZ1FuNWp0ZXFORGFXTGdJcVAwMXkxYTI2MWRJUFo4TFpaWGR1R2psNWEzUEpTWnJJaEFhWWZRX0dCd1lETjZEUVFXcFZTcVpVZw?oc=5</t>
+        </is>
+      </c>
+      <c r="F461" t="n">
+        <v>10</v>
+      </c>
+      <c r="G461" s="2" t="n">
+        <v>46038.42136574074</v>
+      </c>
+    </row>
+    <row r="462">
+      <c r="A462" t="inlineStr">
+        <is>
+          <t>Supply_Chain</t>
+        </is>
+      </c>
+      <c r="B462" t="inlineStr">
+        <is>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+        </is>
+      </c>
+      <c r="C462" t="inlineStr">
+        <is>
+          <t>Port of Prince Rupert handles 26 million tonnes in 2025 - Port Technology International</t>
+        </is>
+      </c>
+      <c r="D462" t="inlineStr">
+        <is>
+          <t>Fri, 16 Jan 2026 10:07:43 GMT</t>
+        </is>
+      </c>
+      <c r="E462" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxOanQ5QWxuTFgySjRVZ3dOWnpEaTdSN3pseDgyZjM5S2V0SjhfY2ZGREY1S21QWFRsVWt0N3RLR09ZLVFxeFp5eFB3cXExcE5PQ3RzbUpVLXlwN1RHTXhXM0VYeXRzNGNtNllLaDVzR2U0WDA5UHA5UzVNeTE4VWtIdjhFQU9OeEVXWklFcS16eU1OUXJHVlhr?oc=5</t>
+        </is>
+      </c>
+      <c r="F462" t="n">
+        <v>10</v>
+      </c>
+      <c r="G462" s="2" t="n">
+        <v>46038.42202546296</v>
+      </c>
+    </row>
+    <row r="463">
+      <c r="A463" t="inlineStr">
+        <is>
+          <t>Supply_Chain</t>
+        </is>
+      </c>
+      <c r="B463" t="inlineStr">
+        <is>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+        </is>
+      </c>
+      <c r="C463" t="inlineStr">
+        <is>
+          <t>Volunteers clean beaches in Sussex after shipping container spills - BBC</t>
+        </is>
+      </c>
+      <c r="D463" t="inlineStr">
+        <is>
+          <t>Thu, 15 Jan 2026 06:07:03 GMT</t>
+        </is>
+      </c>
+      <c r="E463" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiXEFVX3lxTFA5Wl85Um9tUmhFbTJxbFFVT3VMbjktRHVtRmhYSTlMTl8zNllZVUR4QXN0eW8ydlhpM1FFWXZqVGdqVlo4UUhTMGtzTjR4WFBJYTNWWVBFVU1FRUVh0gFiQVVfeXFMTjNkbjVlWlRWc3ZPR093X094cUVMSDgyNWdCVk93QjFDT28xZGJKMk55ZkNMc1Y2Mld4b2d1Y2Fzc2puRjBLM0JWbk9iaWN1UUVzbHV0UGF2MWJFZjBJZ240MHc?oc=5</t>
+        </is>
+      </c>
+      <c r="F463" t="n">
+        <v>10</v>
+      </c>
+      <c r="G463" s="2" t="n">
+        <v>46037.25489583334</v>
+      </c>
+    </row>
+    <row r="464">
+      <c r="A464" t="inlineStr">
+        <is>
+          <t>Supply_Chain</t>
+        </is>
+      </c>
+      <c r="B464" t="inlineStr">
+        <is>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+        </is>
+      </c>
+      <c r="C464" t="inlineStr">
+        <is>
+          <t>Lottery retailers achieve record age check compliance - Better Retailing</t>
+        </is>
+      </c>
+      <c r="D464" t="inlineStr">
+        <is>
+          <t>Fri, 16 Jan 2026 10:13:38 GMT</t>
+        </is>
+      </c>
+      <c r="E464" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMijwFBVV95cUxNTHpmdkFBZjJHdDdOc2ZEWmNpTFI1R0JxaVJOa3lrQkJiM2J3eXFIX0s3NXR6MG82WWUzb1BxWUJIc0xWOG1sY1NsT216YXZJeEF4aUJXTUdkTGVSdkhhN1pQZ0lvdDIxbVJHcXg5bzdfTi00dGZCeUpJdzVlSDZYNTFDS1BKUlp3U1Q2MHp6dw?oc=5</t>
+        </is>
+      </c>
+      <c r="F464" t="n">
+        <v>10</v>
+      </c>
+      <c r="G464" s="2" t="n">
+        <v>46038.42613425926</v>
+      </c>
+    </row>
+    <row r="465">
+      <c r="A465" t="inlineStr">
+        <is>
+          <t>Supply_Chain</t>
+        </is>
+      </c>
+      <c r="B465" t="inlineStr">
+        <is>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+        </is>
+      </c>
+      <c r="C465" t="inlineStr">
+        <is>
+          <t>James Kemball becomes Felixstowe’s largest off-dock provider - Port Technology International</t>
+        </is>
+      </c>
+      <c r="D465" t="inlineStr">
+        <is>
+          <t>Fri, 16 Jan 2026 10:57:45 GMT</t>
+        </is>
+      </c>
+      <c r="E465" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxPVVVjaGRpQ1lSZDg1MTQ5M1c0alpta1ZhX2hLMnAxMmQwR1ZTQ2VFZnBrVjhiQ2I3SGx6TnM5M1YxNE1uWUtYTmF3d2NZMjV1MGR3ZFFKWnNsY1MxeTM4TDlSejNfcmY0YUdrbkt4Y3J5d3pIRlMxSXN1MG1QY0dhX0tSTWNwRzhMZXV5aEszQjhMdDJqWTlFZENlRVE?oc=5</t>
+        </is>
+      </c>
+      <c r="F465" t="n">
+        <v>10</v>
+      </c>
+      <c r="G465" s="2" t="n">
+        <v>46038.45677083333</v>
+      </c>
+    </row>
+    <row r="466">
+      <c r="A466" t="inlineStr">
+        <is>
+          <t>Supply_Chain</t>
+        </is>
+      </c>
+      <c r="B466" t="inlineStr">
+        <is>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+        </is>
+      </c>
+      <c r="C466" t="inlineStr">
+        <is>
+          <t>Strategic Insights: Leveraging Compliance and Nutritional Innovations in the Infant Formula Ingredients Market - Yahoo Finance UK</t>
+        </is>
+      </c>
+      <c r="D466" t="inlineStr">
+        <is>
+          <t>Fri, 16 Jan 2026 09:09:00 GMT</t>
+        </is>
+      </c>
+      <c r="E466" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxPTkJCdGxLeUVBSTE5RlNRaGJzQThjQ2FHZDQ5bFE0QkVzeUNtNVZtMEdEMUgtTUNkdFphcG5DOGhYdDF5eDNHUWloMWcxUTVXUDl0TXFoZHhoN1pLVUhTeE1HWDVHc3ZtSm92N3N3NlJYai04bXVnRUdUWTNiUnM5SXJfdHRxNVFDRFRRSlZENF9vVjJlMW9OZ2owZWkzcEp2LVFr?oc=5</t>
+        </is>
+      </c>
+      <c r="F466" t="n">
+        <v>10</v>
+      </c>
+      <c r="G466" s="2" t="n">
+        <v>46038.38125</v>
+      </c>
+    </row>
+    <row r="467">
+      <c r="A467" t="inlineStr">
+        <is>
+          <t>Supply_Chain</t>
+        </is>
+      </c>
+      <c r="B467" t="inlineStr">
+        <is>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+        </is>
+      </c>
+      <c r="C467" t="inlineStr">
+        <is>
+          <t>Statement of the President of the Union of Greek Shipowners about targeting shipping — SMI DIGITAL - shipmanagementinternational.com</t>
+        </is>
+      </c>
+      <c r="D467" t="inlineStr">
+        <is>
+          <t>Fri, 16 Jan 2026 10:11:33 GMT</t>
+        </is>
+      </c>
+      <c r="E467" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi8gFBVV95cUxNMVBCckxMOXpCUXl2emYwSlNST1Q2bjEtb1dQUlo1czQ2Q0h6MlFqOGRxQnpNVkQ1VnBIZ0ZqcndWRWY4Wll4U0tneUlPTUNDdXhGYS1DTnhCT1JVMFBEdUpjaFlvckQtVkwzUHNHYWdQeUM0MUkwUjVOazdiLVUxQUZBSER3YlRBQkh0TEhRT1dFMU1NR19TS0VGTTVnMzB2T3Y0SmxNZk9UeFo2bWlyQktqS05BRzZHTHY2dU5GbDc3UUl4TWxMRW5uM2lnUzhtTmZWMWNDMDNYOXE5c1VLaDV5aExHdWdoYlhqcXM2eDItZw?oc=5</t>
+        </is>
+      </c>
+      <c r="F467" t="n">
+        <v>10</v>
+      </c>
+      <c r="G467" s="2" t="n">
+        <v>46038.4246875</v>
+      </c>
+    </row>
+    <row r="468">
+      <c r="A468" t="inlineStr">
+        <is>
+          <t>Supply_Chain</t>
+        </is>
+      </c>
+      <c r="B468" t="inlineStr">
+        <is>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+        </is>
+      </c>
+      <c r="C468" t="inlineStr">
+        <is>
+          <t>Austria to tighten airport asylum procedures, expand sanctions under new EU rules - Anadolu Ajansı</t>
+        </is>
+      </c>
+      <c r="D468" t="inlineStr">
+        <is>
+          <t>Fri, 16 Jan 2026 10:01:48 GMT</t>
+        </is>
+      </c>
+      <c r="E468" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxOLTFwa05nMTgyY1ltSllPaFoyV0EwbS1hNDFwTF9zR3p0VGNjUnFhRl9GWXB0bEJYUll3ZThxaXdIQzZFTno2S2dlc2pCZF9vWmJoZkVkaTM2QWM3emItcW90aE1WTHRkcHBmY2ppbEsyYVVJUk9vTGZzcXdwNUJPUWtrbjVXWm5VckNmQlZ5ZVlUMU1JdHpvU0o5Y29sSE1FdXlSV1YwbVh5YUFPemc4MTBTazl3M2phYk5VeA?oc=5</t>
+        </is>
+      </c>
+      <c r="F468" t="n">
+        <v>10</v>
+      </c>
+      <c r="G468" s="2" t="n">
+        <v>46038.41791666667</v>
+      </c>
+    </row>
+    <row r="469">
+      <c r="A469" t="inlineStr">
+        <is>
+          <t>Supply_Chain</t>
+        </is>
+      </c>
+      <c r="B469" t="inlineStr">
+        <is>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+        </is>
+      </c>
+      <c r="C469" t="inlineStr">
+        <is>
+          <t>Maersk ramps up Suez Canal return that could dampen freight rates - Reuters</t>
+        </is>
+      </c>
+      <c r="D469" t="inlineStr">
+        <is>
+          <t>Thu, 15 Jan 2026 18:50:33 GMT</t>
+        </is>
+      </c>
+      <c r="E469" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxPRDVPeWhBWlRhY1AyZDNrWGFVVTBqS2pzWFVMbVZ0cGtQWkM5dUZPXzNwSnpCNHdlQnUwell0N0ZtZk43MTRUbElQUGFmSHk1NTJsNEdaODdJNFNZc21pM09wSDRhZ3E4QmVaNm1MMmExWUcwSW9zOUtNdDlKS0wydFZjMTQ0T0E5ZC05SFktR1dGWGpxdmcwSlZVVkJxeFkxYXc?oc=5</t>
+        </is>
+      </c>
+      <c r="F469" t="n">
+        <v>10</v>
+      </c>
+      <c r="G469" s="2" t="n">
+        <v>46037.78510416667</v>
+      </c>
+    </row>
+    <row r="470">
+      <c r="A470" t="inlineStr">
+        <is>
+          <t>Supply_Chain</t>
+        </is>
+      </c>
+      <c r="B470" t="inlineStr">
+        <is>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+        </is>
+      </c>
+      <c r="C470" t="inlineStr">
+        <is>
+          <t>When Politics Overtakes Supply and Demand in Shipping - StoneX</t>
+        </is>
+      </c>
+      <c r="D470" t="inlineStr">
+        <is>
+          <t>Thu, 15 Jan 2026 18:30:00 GMT</t>
+        </is>
+      </c>
+      <c r="E470" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxNNUNqLWRCVVRIVFNnWjBST0dtX1dRRHhrNFlxYXUyNTJKQlZGa0tBYUNvX0Z5MlJmWFQ0WmJ2VmZuM1NhanhPY2NYd2w0cThuUmtOQUYwcWxqRXpCblZyelpQS2hVUHV0LVJreHhRSnhHcVQ5ZEJzbW40aTJrWDNUU1NfUFY0anRLMThtZkpJU2pSV3pIdkJYMU9NZ0lpY2lPZnc?oc=5</t>
+        </is>
+      </c>
+      <c r="F470" t="n">
+        <v>10</v>
+      </c>
+      <c r="G470" s="2" t="n">
+        <v>46037.77083333334</v>
+      </c>
+    </row>
+    <row r="471">
+      <c r="A471" t="inlineStr">
+        <is>
+          <t>Supply_Chain</t>
+        </is>
+      </c>
+      <c r="B471" t="inlineStr">
+        <is>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+        </is>
+      </c>
+      <c r="C471" t="inlineStr">
+        <is>
+          <t>EU Sanctions and the Undoing of International Investment Arbitration - EJIL: Talk!</t>
+        </is>
+      </c>
+      <c r="D471" t="inlineStr">
+        <is>
+          <t>Thu, 15 Jan 2026 13:08:13 GMT</t>
+        </is>
+      </c>
+      <c r="E471" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxQLW9Vc1BqUFZQR3NiaUkzVVFpUGR5bzZtQ2NlUnZydFVaeDBZUXdCczFSejBIX3ZzM2NSN2w4Q2VodFhsZHZDc09wcHVJQ1MwdGxkMjFzUGRKOVM5UmpXLXJNQmxEYVRWNUJfaTVURmp6bXdGTjNObjdUZzExdTBWTzFOYjFmZS1mYXItNXpGMThMc3pTTkJ2dDF3?oc=5</t>
+        </is>
+      </c>
+      <c r="F471" t="n">
+        <v>10</v>
+      </c>
+      <c r="G471" s="2" t="n">
+        <v>46037.54737268519</v>
+      </c>
+    </row>
+    <row r="472">
+      <c r="A472" t="inlineStr">
+        <is>
+          <t>Supply_Chain</t>
+        </is>
+      </c>
+      <c r="B472" t="inlineStr">
+        <is>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+        </is>
+      </c>
+      <c r="C472" t="inlineStr">
+        <is>
+          <t>EXCLUSIVE: EU mulls tariffs on Chinese hybrid cars - Euractiv</t>
+        </is>
+      </c>
+      <c r="D472" t="inlineStr">
+        <is>
+          <t>Thu, 15 Jan 2026 18:11:15 GMT</t>
+        </is>
+      </c>
+      <c r="E472" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMihwFBVV95cUxPN05Tak43Z2c2dDZXUFMxU2VBVENrUjJUTHlVYWxrVkRjSmVvRzJfY0xOYkw4clJrcUhobHotX0U4VThiSGxQM050VURjdTVGTkJuQnRhUDRPcnhSZTQ5MnFBaHJja2wtTUVOalp1djc0QVNWdS0tZEpIZE9xalZZY0l4cVVMS1k?oc=5</t>
+        </is>
+      </c>
+      <c r="F472" t="n">
+        <v>10</v>
+      </c>
+      <c r="G472" s="2" t="n">
+        <v>46037.7578125</v>
+      </c>
+    </row>
+    <row r="473">
+      <c r="A473" t="inlineStr">
+        <is>
+          <t>Supply_Chain</t>
+        </is>
+      </c>
+      <c r="B473" t="inlineStr">
+        <is>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+        </is>
+      </c>
+      <c r="C473" t="inlineStr">
+        <is>
+          <t>India’s exports to China surge in December while shipments to U.S. decline as Trump tariffs bite - CNBC</t>
+        </is>
+      </c>
+      <c r="D473" t="inlineStr">
+        <is>
+          <t>Fri, 16 Jan 2026 03:29:00 GMT</t>
+        </is>
+      </c>
+      <c r="E473" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMihgFBVV95cUxNVDU0UE1pV1Z6bEd0YW1XZGgydlVROFFlcFdxQURYZFhaMzZUSkdUek5JUFB2WmZ1ZFBoNFpFeE9CbTZUelBJUGZ0SzhYNjNWM19GdWtKTmsxcDlaSUVJMFFJeHJJWG9LNDVsT3BpeS1KSi00ME5GWFpRSktxdmd3WUt5ZlI3QdIBiwFBVV95cUxOM2VjTmlfY3RNSWw1bE1xRnc2ZnNUa19XNXQzWDlMU18xMk91N21mamdlUmI3NVBDU2VkbGJjdE56WTNNeC11cDBKZW1SdmRxTExZVjI4c1BsQ2MzVTFRMU9qUWV2VUJ2RmpIWVZ5VjRsdkhJaDNBbm9UU3U0S2tFaWtWaU9DNnFJYXk4?oc=5</t>
+        </is>
+      </c>
+      <c r="F473" t="n">
+        <v>10</v>
+      </c>
+      <c r="G473" s="2" t="n">
+        <v>46038.14513888889</v>
+      </c>
+    </row>
+    <row r="474">
+      <c r="A474" t="inlineStr">
+        <is>
+          <t>Supply_Chain</t>
+        </is>
+      </c>
+      <c r="B474" t="inlineStr">
+        <is>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+        </is>
+      </c>
+      <c r="C474" t="inlineStr">
+        <is>
+          <t>EU-backed study will put logistics at heart of offshore tendering - Project Cargo Journal</t>
+        </is>
+      </c>
+      <c r="D474" t="inlineStr">
+        <is>
+          <t>Fri, 16 Jan 2026 09:51:06 GMT</t>
+        </is>
+      </c>
+      <c r="E474" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxPUFdENXpCQmVOR1lYcExtdlRYM2dteGFKQkZNazlpejZSbGZQOHRaVTBZVnpyV3FMQ2tPNUtlU0pNdzNZYjlkSjgtYjdmbVhEd0V3eEdZbmtRclNPaTVWS3JmVmRSVXFsSG5fR1lVY3NJWWxLajZOQWFoTV9HSlJNNHlSU1NaS2FLNVZJY2c4c2lnSEJVVXFuOElrVmVyNEpVdFlDVElyX0p0MjZnSDZaZnRKYVFzeHp4WnM4SWF6MV9uNXhZTVlLMnU5VQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F474" t="n">
+        <v>10</v>
+      </c>
+      <c r="G474" s="2" t="n">
+        <v>46038.41048611111</v>
+      </c>
+    </row>
+    <row r="475">
+      <c r="A475" t="inlineStr">
+        <is>
+          <t>Supply_Chain</t>
+        </is>
+      </c>
+      <c r="B475" t="inlineStr">
+        <is>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+        </is>
+      </c>
+      <c r="C475" t="inlineStr">
+        <is>
+          <t>Canada Breaks With U.S. to Slash Tariffs on Some Chinese Electric Vehicles - The New York Times</t>
+        </is>
+      </c>
+      <c r="D475" t="inlineStr">
+        <is>
+          <t>Fri, 16 Jan 2026 08:33:08 GMT</t>
+        </is>
+      </c>
+      <c r="E475" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMijgFBVV95cUxQUWtrMDM0cVpBQzRsY2xyTXhPQktzVHM0QVl0djFMWWYteURHX3pvRmI3MTIta3FWOEx4QWpzdXNCOWE2QkJQVDN1Vy0ydHdGU250bkJLNTREUy02Mm8tMS1CMHU5VktUSGlURFY1LTh4eFp4d0dRWmwwX3B5bnZqek82Q19FOVd5R1hlaEJ3?oc=5</t>
+        </is>
+      </c>
+      <c r="F475" t="n">
+        <v>10</v>
+      </c>
+      <c r="G475" s="2" t="n">
+        <v>46038.35634259259</v>
+      </c>
+    </row>
+    <row r="476">
+      <c r="A476" t="inlineStr">
+        <is>
+          <t>Supply_Chain</t>
+        </is>
+      </c>
+      <c r="B476" t="inlineStr">
+        <is>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+        </is>
+      </c>
+      <c r="C476" t="inlineStr">
+        <is>
+          <t>Thug stabbed pal to death at flats in Port Glasgow - Daily Record</t>
+        </is>
+      </c>
+      <c r="D476" t="inlineStr">
+        <is>
+          <t>Thu, 15 Jan 2026 16:45:00 GMT</t>
+        </is>
+      </c>
+      <c r="E476" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMijwFBVV95cUxOM044ekJOZlBBNDJtWW1MemU5ZDNZYkxDNnlyZ0txNEZTcWhHMURaV0lRcGpscDJ2X3FndUFqaDZXR0l1Nk54ZVk2enRoUV9ZQV9OZ0k3NFZIVFNrLW85Uy1MWkNxMlJYdDRrODhmdUMzNDZubDJHYnR4LTdkVlJWNjFMenBPdDg2cWNPN1k1TdIBlAFBVV95cUxOUXptQldkeTlQbkRjT29xdHVreWY1S0MzS0tQRGh3OFlUZV9ERzh5ZnpfZ2pRYk9GSm5rTTJHYkZUMDBUR0ZGTk1kQnk1WENaTkN6Z2lDNU05N1hFNVZsYi1LRXZ3UWo4Z29SYThiTnJWVVZuZjhQZXRoZFN5bHV0ekl3MlBHLW9Ib25uQWlPSDZ1bUpN?oc=5</t>
+        </is>
+      </c>
+      <c r="F476" t="n">
+        <v>10</v>
+      </c>
+      <c r="G476" s="2" t="n">
+        <v>46037.69791666666</v>
+      </c>
+    </row>
+    <row r="477">
+      <c r="A477" t="inlineStr">
+        <is>
+          <t>Supply_Chain</t>
+        </is>
+      </c>
+      <c r="B477" t="inlineStr">
+        <is>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+        </is>
+      </c>
+      <c r="C477" t="inlineStr">
+        <is>
+          <t>Port of Singapore Seeks More LNG Fuel Suppliers - Rigzone</t>
+        </is>
+      </c>
+      <c r="D477" t="inlineStr">
+        <is>
+          <t>Fri, 16 Jan 2026 09:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="E477" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxQMjZaUFpveVpwaUhIVDFCd2dHOUJORUNfSnFtdTFCaG9vX1Q4TjhzZkdIV1hPQ0w0ZFV2NTJ5QXhsc2VEdHdDVlVwLXBKdnNRYUtyMmZmUmpVX0t3WktIQ3lhUzJCdXZfN3NSY3JqQnFSRkhkRm12V1ZOTERZZ2pLdkpyaXdTVkhSSUtjbjFkeWlTTTdrSVozeTF1blUycVI3X0pPa1QwQQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F477" t="n">
+        <v>10</v>
+      </c>
+      <c r="G477" s="2" t="n">
+        <v>46038.375</v>
+      </c>
+    </row>
+    <row r="478">
+      <c r="A478" t="inlineStr">
+        <is>
+          <t>Supply_Chain</t>
+        </is>
+      </c>
+      <c r="B478" t="inlineStr">
+        <is>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+        </is>
+      </c>
+      <c r="C478" t="inlineStr">
+        <is>
+          <t>Broadband ISP YouFibre UK Set to Block Internet Email Port 25 from Friday UPDATE - ISPreview UK</t>
+        </is>
+      </c>
+      <c r="D478" t="inlineStr">
+        <is>
+          <t>Wed, 14 Jan 2026 17:43:00 GMT</t>
+        </is>
+      </c>
+      <c r="E478" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxNQnpVS3hmb2xoa1lhR2dSdFQ3QU8tcmk5RFVlWkJ6VXhtLTZYTWhqbjdhbmgtSmJqdEo4V1QwLWxUVG9rUGNPX1lwZEFRVkg0STZ4eDhRYnR3b09qR2RIOXl4YldMcGVDQ3gyb20xZUtOTTU3VmZHYXAwc015WGcxZ0VuWUNWeHNqQ2pZN01pdWp6T0RzdDVQdGJHUVRrRUNiQk9nUkJCNWc0UG5yQ2xxMVlFdTRTemNlN1F6M2NkS3BNZw?oc=5</t>
+        </is>
+      </c>
+      <c r="F478" t="n">
+        <v>10</v>
+      </c>
+      <c r="G478" s="2" t="n">
+        <v>46036.73819444444</v>
+      </c>
+    </row>
+    <row r="479">
+      <c r="A479" t="inlineStr">
+        <is>
+          <t>Supply_Chain</t>
+        </is>
+      </c>
+      <c r="B479" t="inlineStr">
+        <is>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+        </is>
+      </c>
+      <c r="C479" t="inlineStr">
+        <is>
+          <t>Marina Port Valencia Obtains LEED Platinum - Yachting Pages</t>
+        </is>
+      </c>
+      <c r="D479" t="inlineStr">
+        <is>
+          <t>Fri, 16 Jan 2026 11:37:14 GMT</t>
+        </is>
+      </c>
+      <c r="E479" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxNQVBYWFp5dEtRTG81cmZ6UkJTZU9ZNlBOQnVSQ0ZtakpJT0tKODZscHM0WHRjWVJBUllILVFid1l1OGNCNlJtQW1DM1Z4QkNyS1F3ZWM3dGtsb0k4VEdlTGZ4Vl9ib1ZwcHBEZ2VVc2hJRDR5eG9GMFE5am1jX3VZTl9lc0JYcHJsb1dJNE9kLTI?oc=5</t>
+        </is>
+      </c>
+      <c r="F479" t="n">
+        <v>10</v>
+      </c>
+      <c r="G479" s="2" t="n">
+        <v>46038.48418981482</v>
+      </c>
+    </row>
+    <row r="480">
+      <c r="A480" t="inlineStr">
+        <is>
+          <t>Supply_Chain</t>
+        </is>
+      </c>
+      <c r="B480" t="inlineStr">
+        <is>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+        </is>
+      </c>
+      <c r="C480" t="inlineStr">
+        <is>
+          <t>One person left with serious leg injuries in Ellesmere Port collision - Chester Standard</t>
+        </is>
+      </c>
+      <c r="D480" t="inlineStr">
+        <is>
+          <t>Fri, 16 Jan 2026 09:15:42 GMT</t>
+        </is>
+      </c>
+      <c r="E480" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxPWndBeFUwOTQzSlNHTmx3blYzcjBObXZPN3hDN1RFM0pfN3F4RUdvUE1zZjJZdnFNMFJiOWd3a3hmVENISFprWkZ2YkVITHJHMEMwRnFtSDNPTklSUExiNkMyenowVS1NZXR1Ty1qSVplazcwYjZoV0tWSFVJMzR3S1JLeUNxOVlnMlFLM0poclNFTTdGcWk0Y25XRkR2U1hTT0QyZEFpRms?oc=5</t>
+        </is>
+      </c>
+      <c r="F480" t="n">
+        <v>10</v>
+      </c>
+      <c r="G480" s="2" t="n">
+        <v>46038.38590277778</v>
+      </c>
+    </row>
+    <row r="481">
+      <c r="A481" t="inlineStr">
+        <is>
+          <t>Protest</t>
+        </is>
+      </c>
+      <c r="B481" t="inlineStr">
+        <is>
+          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally)</t>
+        </is>
+      </c>
+      <c r="C481" t="inlineStr">
+        <is>
+          <t>Met Police staff strike suspended for new pay offer vote - BBC</t>
+        </is>
+      </c>
+      <c r="D481" t="inlineStr">
+        <is>
+          <t>Tue, 13 Jan 2026 11:21:19 GMT</t>
+        </is>
+      </c>
+      <c r="E481" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiXEFVX3lxTE9ab1ZlaXdqYmJzQ0tGakpQMDFBc1QwTGlSd3hoNTBlVGJhVzhJZkFUYXR4S2ZsUWNYNzJ6dWhYdXMwdXRoZ2s2M05XdTVUdE1Bd1A3UWpKOHR4S2x60gFiQVVfeXFMTjRleHJoTkk4bTNmbzZzb1VZSkNiMmUxR3ZmWld1OWFHQUVDdlVQUE1rSXpUWHpYVlV0OTVCSVRrQ09rUDg0MlBlSTluUkp2cEhHODQ2Q2dnTHVORDJiTHhtaUE?oc=5</t>
+        </is>
+      </c>
+      <c r="F481" t="n">
+        <v>10</v>
+      </c>
+      <c r="G481" s="2" t="n">
+        <v>46035.47313657407</v>
+      </c>
+    </row>
+    <row r="482">
+      <c r="A482" t="inlineStr">
+        <is>
+          <t>Protest</t>
+        </is>
+      </c>
+      <c r="B482" t="inlineStr">
+        <is>
+          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally)</t>
+        </is>
+      </c>
+      <c r="C482" t="inlineStr">
+        <is>
+          <t>Iran deploys riot police to shut down protests - France 24</t>
+        </is>
+      </c>
+      <c r="D482" t="inlineStr">
+        <is>
+          <t>Fri, 16 Jan 2026 09:37:40 GMT</t>
+        </is>
+      </c>
+      <c r="E482" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMif0FVX3lxTE5Sc0E3RFctNmtpMGdlYkM2cWdlRWF1NzU4MnZ2ajdzUHVxMkRzaUcySmZ6ZXBDcC1HQl8wQzN1MkNmZVRYQnhfVW5zMEZsOHJEUWp6em5EYzhyd1BzSjhyV1MyWUQxaC1hNWpMbFVob3UyTl9WSlQtSEpSX1pKbnM?oc=5</t>
+        </is>
+      </c>
+      <c r="F482" t="n">
+        <v>10</v>
+      </c>
+      <c r="G482" s="2" t="n">
+        <v>46038.40115740741</v>
+      </c>
+    </row>
+    <row r="483">
+      <c r="A483" t="inlineStr">
+        <is>
+          <t>Protest</t>
+        </is>
+      </c>
+      <c r="B483" t="inlineStr">
+        <is>
+          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally)</t>
+        </is>
+      </c>
+      <c r="C483" t="inlineStr">
+        <is>
+          <t>Eyewitness: a New Year and resource draining protests recommence - Police Oracle</t>
+        </is>
+      </c>
+      <c r="D483" t="inlineStr">
+        <is>
+          <t>Thu, 15 Jan 2026 16:45:43 GMT</t>
+        </is>
+      </c>
+      <c r="E483" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxQVk9zNkhpVE1hRUU0LTJMd3lJYXF5WVVEM0kySFNqYlFDVXQwOXNpS0dVVGxsQVBsS1lDZ1pjZDluU3dDS0ZXSnZrb2hFVG5vWVh2MUJaUFhhQ2NxVHhQMFdGQnRpNEJ1WERibDdhNHVoN281bXBiWlo4SzEtaG51XzlTYlMwQmZCaFJrZEpSSENfTVBpNXNuUWNKVzkyeGVNdGdfTDN3c0JMbEpNUmc?oc=5</t>
+        </is>
+      </c>
+      <c r="F483" t="n">
+        <v>10</v>
+      </c>
+      <c r="G483" s="2" t="n">
+        <v>46037.69841435185</v>
+      </c>
+    </row>
+    <row r="484">
+      <c r="A484" t="inlineStr">
+        <is>
+          <t>Protest</t>
+        </is>
+      </c>
+      <c r="B484" t="inlineStr">
+        <is>
+          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally)</t>
+        </is>
+      </c>
+      <c r="C484" t="inlineStr">
+        <is>
+          <t>Police called in over weekly Palestine protests outside Royal Stoke - Stoke-on-Trent Live</t>
+        </is>
+      </c>
+      <c r="D484" t="inlineStr">
+        <is>
+          <t>Thu, 15 Jan 2026 17:04:00 GMT</t>
+        </is>
+      </c>
+      <c r="E484" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxOQlJIWm5OS1dpOTFRQVg2VHpVOE5NNDJlaGEyd1c2MWtSMWRoVXdaMFE5QlhrbUVuY3VyeHhWRzY4YzdNTy1TZWxDMUZoUC0zWkZPZzZyMi1sb3p2bzBRanNJR2hoMG00a3dmekd2cW5lT09VTE1rc0ZxWVVJQ2N1c2ViSkM5ZDhJcUU5eHVVQWxUZVdiV3B5cDl1dUJJdTR1Mjcw0gGoAUFVX3lxTE1PSkRuOS1vaVJLMmg1Z2RoNDduVDNoNVh0QnNJb2x0TTlGQ2ZDOERnaVQ4OG5vd1pZYm42eGpfM0NuWS01eUU2YUdCbThLS05ZekdETmF2dl96b1BwN0UweXJSVjRleHREbGdVYkZXSURQUWw2MXh1QzB1VG4wWVpqY0VsazR1MXNtNlQ4V1g0ampVUUdTRzdlTlloV0V2eExJaElKVEs1Uw?oc=5</t>
+        </is>
+      </c>
+      <c r="F484" t="n">
+        <v>10</v>
+      </c>
+      <c r="G484" s="2" t="n">
+        <v>46037.71111111111</v>
+      </c>
+    </row>
+    <row r="485">
+      <c r="A485" t="inlineStr">
+        <is>
+          <t>Protest</t>
+        </is>
+      </c>
+      <c r="B485" t="inlineStr">
+        <is>
+          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally)</t>
+        </is>
+      </c>
+      <c r="C485" t="inlineStr">
+        <is>
+          <t>World to unite in blue to honour fallen police officers on 7 March - Interpol</t>
+        </is>
+      </c>
+      <c r="D485" t="inlineStr">
+        <is>
+          <t>Wed, 07 Jan 2026 13:34:35 GMT</t>
+        </is>
+      </c>
+      <c r="E485" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxPRl81VVRsZGM1bThTOC1TdVZnWnRlRDBuZUNDYlBKV21oQm9tZF9rU1dJYzhFeUIyQkFJVmphQ1dtUlh6dzBlNDdQSFktSzZKQ2ZRSzVUZzZxa2FVYWFyTExSWF9fTXd4VUpwLUFZQmUwdEd0VzVLbG02MzdDV3hqTXB2aFc4NTZScUtUODhudVBHLW1ZZUNGNFdDRGp2a3NVdDhjMGdTZ2N3LWc3S2xjVl9pODhoNlBM?oc=5</t>
+        </is>
+      </c>
+      <c r="F485" t="n">
+        <v>10</v>
+      </c>
+      <c r="G485" s="2" t="n">
+        <v>46029.56568287037</v>
+      </c>
+    </row>
+    <row r="486">
+      <c r="A486" t="inlineStr">
+        <is>
+          <t>Protest</t>
+        </is>
+      </c>
+      <c r="B486" t="inlineStr">
+        <is>
+          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally)</t>
+        </is>
+      </c>
+      <c r="C486" t="inlineStr">
+        <is>
+          <t>Protester ‘fakes’ being struck by police patrol car during ICE demonstration - The Independent</t>
+        </is>
+      </c>
+      <c r="D486" t="inlineStr">
+        <is>
+          <t>Wed, 14 Jan 2026 13:45:00 GMT</t>
+        </is>
+      </c>
+      <c r="E486" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxOWFM3VnpoZkxXR3M4UWRJMy10U1JURXVTN0JoMWYzY01ITnNJdkdGUVRhcWk5RHJUb0NzWGhUdUxsZGJyTzlROHVVZzRKMlBHZVlSc1dGdmFzTG1vLVBkWjNMTUR2R0JDbW9haHA3UXNfckdVZG91QXRlLThpRW9xd2hCS09qeTB0eUVIMmZqSWw4VHVrWHdDb3JKOA?oc=5</t>
+        </is>
+      </c>
+      <c r="F486" t="n">
+        <v>10</v>
+      </c>
+      <c r="G486" s="2" t="n">
+        <v>46036.57291666666</v>
+      </c>
+    </row>
+    <row r="487">
+      <c r="A487" t="inlineStr">
+        <is>
+          <t>Protest</t>
+        </is>
+      </c>
+      <c r="B487" t="inlineStr">
+        <is>
+          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally)</t>
+        </is>
+      </c>
+      <c r="C487" t="inlineStr">
+        <is>
+          <t>Police strike again as bowling alley thief convicted in Cornwall - Yahoo News UK</t>
+        </is>
+      </c>
+      <c r="D487" t="inlineStr">
+        <is>
+          <t>Wed, 14 Jan 2026 10:44:14 GMT</t>
+        </is>
+      </c>
+      <c r="E487" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMif0FVX3lxTFBlWHlwc0tRSHdKcTEycHpCNzRnQV9sWVluaEFRQ0N3QXM4M01JZGpQOFlfN0dpVVBjdjZ0TTVqSy1FRUhrbVpEclU2LVNtYjhXSFlsZnVOY2JaTXF6c3l5TEhYRXZtQTB0eE9xRnduVTg5bVk5V21IOWE2LWFRRlU?oc=5</t>
+        </is>
+      </c>
+      <c r="F487" t="n">
+        <v>10</v>
+      </c>
+      <c r="G487" s="2" t="n">
+        <v>46036.44738425926</v>
+      </c>
+    </row>
+    <row r="488">
+      <c r="A488" t="inlineStr">
+        <is>
+          <t>Protest</t>
+        </is>
+      </c>
+      <c r="B488" t="inlineStr">
+        <is>
+          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally)</t>
+        </is>
+      </c>
+      <c r="C488" t="inlineStr">
+        <is>
+          <t>Anti-Israel protesters gather in Sydney, as Minns’ bans marches - dailytelegraph.com.au</t>
+        </is>
+      </c>
+      <c r="D488" t="inlineStr">
+        <is>
+          <t>Fri, 16 Jan 2026 08:31:19 GMT</t>
+        </is>
+      </c>
+      <c r="E488" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi5gFBVV95cUxNamU1NlljYkRubFNlWk93bXh5SWFPb1JnUC04WVo5cHJidEI2ZjZpQ1B1bGdMdm9VdkxnejlnWVVMd3V5WXRmcEpyc1pFMGp2QVYyX0NYMl9hdkVpUWo2YlJibWlVR2h1WklCZzZOdUdjdjhscGRicE1BUnItandTRm94RzVMUjN2OFkyMW5oZ0tXanFwWkVOaDNwMnQ5enByYmZlbGE0UlhHTW5OclFLb2N3S2lQSTdqVTEwNWZXME1IMlBBcW0wY2JYUDF4X2swS2NoV0J4Wll5U19fQ0kwdy1uNzFqUdIB6wFBVV95cUxObGZsMnhuajk3RFY0cVIzU1FoZmk1U2hqNTZNOXRsNWtvUGU5OXJQQVJxWTBvUFRFMVhLMXh3MllQUHdUUFo2dHk3dmd0QlBtajNicTFiTWc2a3cwaDRaakV4OTh6SHhZdnJDOGJHQTFwUW0waUJOOHAzejFiU2MzaEJ1UjdPU0NQQTh0b3N3eVh1QWNyTVloQjdLUUJBaDIzNU54czNyY21kVXFUNE5JSXphSFlyWnNFa2taWVJSWTRRcmlpN0tuTlNNTkhVcWo4alZkX1Y3Mlh0R0pfRlBJUTJmRDU4RnhPUnE4?oc=5</t>
+        </is>
+      </c>
+      <c r="F488" t="n">
+        <v>10</v>
+      </c>
+      <c r="G488" s="2" t="n">
+        <v>46038.35508101852</v>
+      </c>
+    </row>
+    <row r="489">
+      <c r="A489" t="inlineStr">
+        <is>
+          <t>Protest</t>
+        </is>
+      </c>
+      <c r="B489" t="inlineStr">
+        <is>
+          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally)</t>
+        </is>
+      </c>
+      <c r="C489" t="inlineStr">
+        <is>
+          <t>RBC Capital Reaffirms Their Hold Rating on Strike Energy Limited (STX) - The Globe and Mail</t>
+        </is>
+      </c>
+      <c r="D489" t="inlineStr">
+        <is>
+          <t>Fri, 16 Jan 2026 02:16:07 GMT</t>
+        </is>
+      </c>
+      <c r="E489" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi5AFBVV95cUxOeHdFNkR6Z0MwS0tRWEdMQ1VOb09YdjRETVdianY1WlRlOF82bWZfb3lFbWdmOFV0Si1mUVlKdmcxZEp6YURjVUtnSTNxWEt0dHAyZHRoRlk3bW40S2NZazYxME5RMENWeXV2NFprbmxoUDhCLXl0eFRheEN6SjFQR2NTRTdzXzBUVUFSeWxjbFJJdVV0cDBqUWNGUGlxeXlLR0VPdGVBUlRWcnpFVnlVdzlQWHExRXVmWFZIdEt0T1dBMXQydmw0WUZlVFp4T1hDWkFvX1gxSi14ajlJT3BmWE1KUjI?oc=5</t>
+        </is>
+      </c>
+      <c r="F489" t="n">
+        <v>10</v>
+      </c>
+      <c r="G489" s="2" t="n">
+        <v>46038.09452546296</v>
+      </c>
+    </row>
+    <row r="490">
+      <c r="A490" t="inlineStr">
+        <is>
+          <t>Protest</t>
+        </is>
+      </c>
+      <c r="B490" t="inlineStr">
+        <is>
+          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally)</t>
+        </is>
+      </c>
+      <c r="C490" t="inlineStr">
+        <is>
+          <t>In Kharkiv region, Russian troops strike police car heading to evacuate people - Ukrinform</t>
+        </is>
+      </c>
+      <c r="D490" t="inlineStr">
+        <is>
+          <t>Thu, 15 Jan 2026 12:09:00 GMT</t>
+        </is>
+      </c>
+      <c r="E490" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxQT1Y2N0lmcWJSOW4yN3RudnRUQjlyTWtPS0syc2lQNEhwWEkyY2tDNUlnMnZyWGZsallVRWZIR0FsSV9vQWZrN3ctbWlLQU9nc2ZLX1lmUHlSX1pEN05BZElyLUF0RzNLSE51R1U0U1NYcnB4NDRYTXJzQ2JJSTNMa0hTNmNEYW9DWWFwbExLa1ZmOUYzZ1BHdzJCaVlpQWhnZi1ZY2NFMGNtcHJnRzJCLWU5OFVkb2NZX1pSdW9lZzViSWhqU0E?oc=5</t>
+        </is>
+      </c>
+      <c r="F490" t="n">
+        <v>10</v>
+      </c>
+      <c r="G490" s="2" t="n">
+        <v>46037.50625</v>
+      </c>
+    </row>
+    <row r="491">
+      <c r="A491" t="inlineStr">
+        <is>
+          <t>Protest</t>
+        </is>
+      </c>
+      <c r="B491" t="inlineStr">
+        <is>
+          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally)</t>
+        </is>
+      </c>
+      <c r="C491" t="inlineStr">
+        <is>
+          <t>Hindu Villagers Protest and Police Stop Mosque Work in UP’s Jaunpur - Clarion India</t>
+        </is>
+      </c>
+      <c r="D491" t="inlineStr">
+        <is>
+          <t>Fri, 16 Jan 2026 06:53:56 GMT</t>
+        </is>
+      </c>
+      <c r="E491" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxNcmNGOHl2N1FEeXpTSWJ1a1Z4MElXeHRnWlFiV2VhZnd0VW1KZ0p1ZjVBdmh1N3l3WkpYMTJscnJPOVlUMno0WTFGbkpRWXVFQmYweS01Yk5CR2NvNU1NcFMtcnpoWXV5MXNybFVwQThnMTBIRTFUUllKSmJ2UzhFSzNSVHVUS1k3RzhuOFhEcjI5eE9PcXl3?oc=5</t>
+        </is>
+      </c>
+      <c r="F491" t="n">
+        <v>10</v>
+      </c>
+      <c r="G491" s="2" t="n">
+        <v>46038.28745370371</v>
+      </c>
+    </row>
+    <row r="492">
+      <c r="A492" t="inlineStr">
+        <is>
+          <t>Protest</t>
+        </is>
+      </c>
+      <c r="B492" t="inlineStr">
+        <is>
+          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally)</t>
+        </is>
+      </c>
+      <c r="C492" t="inlineStr">
+        <is>
+          <t>‘People’s State of the State’ protest makes homelessness center of attention - Ocean State Media</t>
+        </is>
+      </c>
+      <c r="D492" t="inlineStr">
+        <is>
+          <t>Wed, 14 Jan 2026 17:18:12 GMT</t>
+        </is>
+      </c>
+      <c r="E492" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxNRjJMeFVveFJJT1FabGlCVlJkZllsaWZFUDZZZFBzMENKRUh4dHJLUjdQZGZfN19oQWJ5eWN4X0xVUE9VcUVsSDY2bk1tTl9KV29Obnk5SkZ5ZFhLbjROdi1iOHdKSGEyaGtXT3NsRVFnNVk4RHhIeFhMRWV0dHc4R3UxYV9MUWVWcm11SVFoVlZfTlRtZnBmaUJCeHVBd3ltR09qZlpFeUhLeG1DRVdRSjZHOA?oc=5</t>
+        </is>
+      </c>
+      <c r="F492" t="n">
+        <v>10</v>
+      </c>
+      <c r="G492" s="2" t="n">
+        <v>46036.72097222223</v>
+      </c>
+    </row>
+    <row r="493">
+      <c r="A493" t="inlineStr">
+        <is>
+          <t>Protest</t>
+        </is>
+      </c>
+      <c r="B493" t="inlineStr">
+        <is>
+          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally)</t>
+        </is>
+      </c>
+      <c r="C493" t="inlineStr">
+        <is>
+          <t>Excelsior Capital Calls Board Spill Meeting After Second Strike on Pay Report - TipRanks</t>
+        </is>
+      </c>
+      <c r="D493" t="inlineStr">
+        <is>
+          <t>Fri, 16 Jan 2026 03:00:32 GMT</t>
+        </is>
+      </c>
+      <c r="E493" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiyAFBVV95cUxNM0tGN3N0ODZjRU5jcWEtQm05Z0tKak5QZVJyUmlHWWJvWlhERy02X0VNdjNYVGVyblp5NUNBM2dPXzZDd0xEQnd0OUI0SzhtRXVWLTFGZ1ZJS19lUnpPZUZJdk04TFo3WVdYcWUyenRreHhQeTU1blFWMlVmR2tscWMzZUhMWWd3c21xRmV1ZWdKeldYenFXajY0LUI5ZEt3WDFoNzQ0dXNkdE5ubjNNUzRtVGl3TUY4VXE4VGkwTlRabDNfZ2V5VA?oc=5</t>
+        </is>
+      </c>
+      <c r="F493" t="n">
+        <v>10</v>
+      </c>
+      <c r="G493" s="2" t="n">
+        <v>46038.12537037037</v>
+      </c>
+    </row>
+    <row r="494">
+      <c r="A494" t="inlineStr">
+        <is>
+          <t>Protest</t>
+        </is>
+      </c>
+      <c r="B494" t="inlineStr">
+        <is>
+          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally)</t>
+        </is>
+      </c>
+      <c r="C494" t="inlineStr">
+        <is>
+          <t>March shooting involving Colorado Springs police ruled justified - KKTV</t>
+        </is>
+      </c>
+      <c r="D494" t="inlineStr">
+        <is>
+          <t>Fri, 16 Jan 2026 01:32:00 GMT</t>
+        </is>
+      </c>
+      <c r="E494" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxQUFZJZGpGWnBHbzJyczkwOElHSWtLMEZCeW1BZkVRWTg1QmFaNFh5al9hYzhIZ0hXbjQ5TC0xelc3ZkNQTVZwTjUyTkdQYkgzVFFNaWZnamtHMTU4WU1oTW5yb3Z6OWtkSjZfT1VrQnVSMExtOGtCZlllYTl5dmxZb3RXSF9sYkdtT3hZZWxobmFxazY1TEhOb3BuVERHZ9IBsgFBVV95cUxOX0FCaE45c2xXLTRYYkVzbHB1QUhKc3FPcTBOSXpjTkdQVGxBbWlITFNGMmxjcUpTSXQ5RTNtMFFGMXBDa21Rb2w4VnpYYlNvM3lHeGZkOXBnOWFDVGlmYnQtengyNWxCOTRaMjRGX3kwN192WVhOTWRFN1l0RU1NR1ZCNG11U2lQaHpUMmhBb2FWT2h0eERHRkkyeGM2SjEzcEN0cXRHcXdNdXBiQ2l6cUZn?oc=5</t>
+        </is>
+      </c>
+      <c r="F494" t="n">
+        <v>10</v>
+      </c>
+      <c r="G494" s="2" t="n">
+        <v>46038.06388888889</v>
+      </c>
+    </row>
+    <row r="495">
+      <c r="A495" t="inlineStr">
+        <is>
+          <t>Protest</t>
+        </is>
+      </c>
+      <c r="B495" t="inlineStr">
+        <is>
+          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally)</t>
+        </is>
+      </c>
+      <c r="C495" t="inlineStr">
+        <is>
+          <t>Protests after man shot during US federal raid in Minneapolis - Al Jazeera</t>
+        </is>
+      </c>
+      <c r="D495" t="inlineStr">
+        <is>
+          <t>Thu, 15 Jan 2026 10:04:01 GMT</t>
+        </is>
+      </c>
+      <c r="E495" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxPOU1vMG9TSEhkc3B3R3VWUDNaY3lTdk5iYnV0U01lbUNINl9CckVKN3ZkZFJ5ZC1TTkhWc2MzdTNQbThsMTRObDBrVEcxNUR3RUpmRTFTTVJVMmxGS3haQlY5eVdxWFdUemZ5eDQxYXJPUUlnc0kzOUVaeVlLckpSbDRfMTZnVHdQU043OGpaNWMtZ2VrQmgwdkU4NWhxWm9VTjFMRFFBSDc0elktUmtDSHpn0gG3AUFVX3lxTE5sbnV5dnhBeGpLQlhxX0lBbWhaR1hkQWpOOHpjNDVwdTg1N3NGbTV5eFQ1NWF0ODJCcWtKZnlCbkY4aWNoMi1wVE9nVjJoYTFCLXUyU3ZXUXQyXzFKSXRBaDRBM1ZvcGVHTTJWczFTV2FHVmZ5X3Nqay16X2k3YmxxYkNtUHZqbjYyYWJKeWY3akhQTGpWT2ZwcXZKZmlIak1WSGx2RnRubGVDMnEzM3NZX3BJQm5Ndw?oc=5</t>
+        </is>
+      </c>
+      <c r="F495" t="n">
+        <v>10</v>
+      </c>
+      <c r="G495" s="2" t="n">
+        <v>46037.41945601852</v>
+      </c>
+    </row>
+    <row r="496">
+      <c r="A496" t="inlineStr">
+        <is>
+          <t>Protest</t>
+        </is>
+      </c>
+      <c r="B496" t="inlineStr">
+        <is>
+          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally)</t>
+        </is>
+      </c>
+      <c r="C496" t="inlineStr">
+        <is>
+          <t>Court Slams Israel Police Over Mishandling of Bibileaks Case - Haaretz</t>
+        </is>
+      </c>
+      <c r="D496" t="inlineStr">
+        <is>
+          <t>Wed, 14 Jan 2026 21:47:00 GMT</t>
+        </is>
+      </c>
+      <c r="E496" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi9wFBVV95cUxPOUYyNG5TbVNzZjBiZ0xXXy1WV2h4RmNZaHhuSXNQLVpkUmJHOGhteGd5enpFLUdNQ0o5a01qZlNfMEZZdnJieGZBaTA3NHZqaENQZmJ0Yno5b25rcWdpaWd6XzlWY1AwRzFzQkJNSGdmQnFSeWpJU1IxejE2RGFhVW9VUWs0dkxQcUNfYWxKTVA2T2JuRVdXbkY2aHN2OTRGa3NaZEV6YlFVaTBHY1ZIZktESnRBU28waVV2cmh6b2NpYVBWdXc3WUpQaEpGYVhjVnVvb0xFWl92RXNqamhQbXh0YndpYzJXam0wR1FYNkZpQXlBYnpR?oc=5</t>
+        </is>
+      </c>
+      <c r="F496" t="n">
+        <v>10</v>
+      </c>
+      <c r="G496" s="2" t="n">
+        <v>46036.90763888889</v>
+      </c>
+    </row>
+    <row r="497">
+      <c r="A497" t="inlineStr">
+        <is>
+          <t>Protest</t>
+        </is>
+      </c>
+      <c r="B497" t="inlineStr">
+        <is>
+          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally)</t>
+        </is>
+      </c>
+      <c r="C497" t="inlineStr">
+        <is>
+          <t>How to Protest Safely in the Age of Surveillance - WIRED</t>
+        </is>
+      </c>
+      <c r="D497" t="inlineStr">
+        <is>
+          <t>Thu, 08 Jan 2026 08:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="E497" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMihgFBVV95cUxQZHZxNnNlR181bU1KYkh4ODNCbUFwQ2I1WXBnWTJka1UwbUpRemNtVGdrOGt2UDl5dl8tc2VZS0lHX1dPVDVTZ3VGR1lCRE8xWm1rQ1pheFJ6eWJjYzF6UVY0UmdFdEZVMEVfWHRuNzhqeXotcW5xeVlZWFZwU0d1Ri0ydm1RZw?oc=5</t>
+        </is>
+      </c>
+      <c r="F497" t="n">
+        <v>10</v>
+      </c>
+      <c r="G497" s="2" t="n">
+        <v>46030.33333333334</v>
+      </c>
+    </row>
+    <row r="498">
+      <c r="A498" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B498" t="inlineStr">
+        <is>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+        </is>
+      </c>
+      <c r="C498" t="inlineStr">
+        <is>
+          <t>Red tape to be slashed for British robotics and defence innovators - GOV.UK</t>
+        </is>
+      </c>
+      <c r="D498" t="inlineStr">
+        <is>
+          <t>Fri, 16 Jan 2026 00:07:36 GMT</t>
+        </is>
+      </c>
+      <c r="E498" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxNNnlWNl9MNzlDYVB2eUc2M2ExYlFIUWdYbE0tUVJHN2RNeG12QjViTG5scFFNVEFpNjhLajk0U3IwSEJvMUphWU0td3BLT1JJN2xZOUY4RnNwOTZ5RkhILXl6cU9qY0JGMlh4TzFib1RQeVRjYmtUWC1MRUZiQVNxaWJPWFVXNE16NW5udklyRG5RN2pWSjlFT2c3N19NSV84cnpF?oc=5</t>
+        </is>
+      </c>
+      <c r="F498" t="n">
+        <v>10</v>
+      </c>
+      <c r="G498" s="2" t="n">
+        <v>46038.00527777777</v>
+      </c>
+    </row>
+    <row r="499">
+      <c r="A499" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B499" t="inlineStr">
+        <is>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+        </is>
+      </c>
+      <c r="C499" t="inlineStr">
+        <is>
+          <t>Sadiq Khan says AI could destroy London jobs if not controlled - BBC</t>
+        </is>
+      </c>
+      <c r="D499" t="inlineStr">
+        <is>
+          <t>Thu, 15 Jan 2026 22:07:33 GMT</t>
+        </is>
+      </c>
+      <c r="E499" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTFBZQ3NJbXV0eE1wal9OZGFiVVRWYXlJQkZocVo4d3RER3REZngxLWpzZGNWTlA2cnVBZlFRSjNYLWYwMWtNWXgyb2hUV1I0YXdwbWZxeW5lNGx4d9IBX0FVX3lxTE1JZ2JibGFwOC01ZDFRMFNzUzNRRGd0ZkpfRm5tSU50czFRZkRDcmNsR1lZTVZOYUlOdzJsdVZ6V3M5eXpadngtMFpmaFRYVFdWNUtoOGE3N2V2M1RsQm9v?oc=5</t>
+        </is>
+      </c>
+      <c r="F499" t="n">
+        <v>10</v>
+      </c>
+      <c r="G499" s="2" t="n">
+        <v>46037.92190972222</v>
+      </c>
+    </row>
+    <row r="500">
+      <c r="A500" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B500" t="inlineStr">
+        <is>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+        </is>
+      </c>
+      <c r="C500" t="inlineStr">
+        <is>
+          <t>AI in pensions admin: Start with members, not technology - Professional Pensions</t>
+        </is>
+      </c>
+      <c r="D500" t="inlineStr">
+        <is>
+          <t>Fri, 16 Jan 2026 10:31:41 GMT</t>
+        </is>
+      </c>
+      <c r="E500" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxOb1BYdU5DaWxiblFNNUZkakZvUV9mVkc4RUFEbDFlN0U1UVJQQWQ3U2dTWWhvWmxmWTlpWmJIWmo1SnFSQThYc1BZLXJxTENHMjdQRC1aOVNVNnlUQ0FaYy0yalJtZTJFYldSOGU1NUZMTlN1VXBURTNMRHhuNTNkbXlrWG1PWXlONTBSX0xSQ0ZueFIydDBSRThmSQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F500" t="n">
+        <v>10</v>
+      </c>
+      <c r="G500" s="2" t="n">
+        <v>46038.43866898148</v>
+      </c>
+    </row>
+    <row r="501">
+      <c r="A501" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B501" t="inlineStr">
+        <is>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+        </is>
+      </c>
+      <c r="C501" t="inlineStr">
+        <is>
+          <t>AI will transform the ‘human job’ and enhance skills, says science minister - The Guardian</t>
+        </is>
+      </c>
+      <c r="D501" t="inlineStr">
+        <is>
+          <t>Fri, 16 Jan 2026 09:46:00 GMT</t>
+        </is>
+      </c>
+      <c r="E501" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxOeTQ5ZVZtcHJzVXhidWl6Y3pCaXVPc0QtTS1Nb29xTTB2RnR2c2FxektwTk5WclM3TzRrWlQ0dDRlcEFKVkJZYXJQQ2pTeUVtcTJMRF9uSy0ydG1JY29ZYXk2Qk9lenJEM2FrTGMzN2NnR3ZkRlpham5FZWJ1YmtXRGw5SmJFSm9fc2ozcmZHX20tV0xVX0dZYTJLSFduSmVBOUFGQWs1Zmp1NzJzTE1hNE9EWGtPamhvMnlHRmVmNEc?oc=5</t>
+        </is>
+      </c>
+      <c r="F501" t="n">
+        <v>10</v>
+      </c>
+      <c r="G501" s="2" t="n">
+        <v>46038.40694444445</v>
+      </c>
+    </row>
+    <row r="502">
+      <c r="A502" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B502" t="inlineStr">
+        <is>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+        </is>
+      </c>
+      <c r="C502" t="inlineStr">
+        <is>
+          <t>Singapore: MAS consortium releases comprehensive AI Risk Management Handbook for financial institutions - Linklaters</t>
+        </is>
+      </c>
+      <c r="D502" t="inlineStr">
+        <is>
+          <t>Fri, 16 Jan 2026 10:26:33 GMT</t>
+        </is>
+      </c>
+      <c r="E502" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi0AFBVV95cUxPZVhOdTRQWktZWnAzbDdUbTFFcFRQLUhZYWFLYnFBMldjNXpZZlotYm4tb0Nmb0poV3lPMTNrRGZKMzlWVWFib3hfajB2ZUlCSFNrODJEcW5uVFo0RVpoV2gxbFFkMC0zZVEyNjY5VURHZGR5aFoxTFp6TkpZU2dEVmEwZW41X285Y3RrUy1lejdBRm03b0lGTUVQcVRWeTBJYjlOLXdBNk9kaVRINjZkeTVxTWZZX0tiWHFFdjkyU240dWJaYU41RHBfZHJPaFRJ?oc=5</t>
+        </is>
+      </c>
+      <c r="F502" t="n">
+        <v>10</v>
+      </c>
+      <c r="G502" s="2" t="n">
+        <v>46038.43510416667</v>
+      </c>
+    </row>
+    <row r="503">
+      <c r="A503" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B503" t="inlineStr">
+        <is>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+        </is>
+      </c>
+      <c r="C503" t="inlineStr">
+        <is>
+          <t>New office for AI to 'explore opportunities' for Isle of Man - BBC</t>
+        </is>
+      </c>
+      <c r="D503" t="inlineStr">
+        <is>
+          <t>Fri, 16 Jan 2026 10:06:29 GMT</t>
+        </is>
+      </c>
+      <c r="E503" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiXEFVX3lxTE9oOGtJaFp1R3B3VjkwZkdGaFF4U0U3Vi15cEV3SWh1V014WW10d0dfclladTBVUWtyalVNRmlTSnBiWnZURW03a2dxSm1oOVhiaGdYR0N6VThtVE9x0gFiQVVfeXFMTUpDRnBMM1I3WHlITEJEVllXYU53MS1mSGE0Z0lERl9oQU5RejFCT1VDNklndEpiMzBvdXhVdDVWdURRMTBRWU8zYWFwbzVPa05YNjEzZTRfLVpDb0tzdDJIaVE?oc=5</t>
+        </is>
+      </c>
+      <c r="F503" t="n">
+        <v>10</v>
+      </c>
+      <c r="G503" s="2" t="n">
+        <v>46038.42116898148</v>
+      </c>
+    </row>
+    <row r="504">
+      <c r="A504" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B504" t="inlineStr">
+        <is>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+        </is>
+      </c>
+      <c r="C504" t="inlineStr">
+        <is>
+          <t>AI, Robotics and Human Reskilling: The State of Hospitality Report 2025-2026 published by Les Roches Spark - FE News</t>
+        </is>
+      </c>
+      <c r="D504" t="inlineStr">
+        <is>
+          <t>Fri, 16 Jan 2026 11:39:31 GMT</t>
+        </is>
+      </c>
+      <c r="E504" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi4AFBVV95cUxQc1BfOWJ3WHctd1lLMmtKYU9IVEctLWRBTXZsTks1NGJQSFpyZlY5aC02c2NoLTMzTEliZk0wQlhYUGVGbThvY2FYSVMtNjBSUnVmaW4zTlB6N2F6YkpCMUUxWDNMcUR5ZE5FbVBGbmU3Z2lGQllNb0RUWldMTXFnYzlfU2hQdFdmVFFMX0NkTGVJaEE3V05udTBkaENYZmRESWVENFJLNkdsOHVWSmFVMVFFcms3NUpLM1ktOTg1N28tai1yZ1l3eWJJR3J6U3ZwNjVGQm1zM3JIaksxTklXMg?oc=5</t>
+        </is>
+      </c>
+      <c r="F504" t="n">
+        <v>10</v>
+      </c>
+      <c r="G504" s="2" t="n">
+        <v>46038.48577546296</v>
+      </c>
+    </row>
+    <row r="505">
+      <c r="A505" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B505" t="inlineStr">
+        <is>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+        </is>
+      </c>
+      <c r="C505" t="inlineStr">
+        <is>
+          <t>Cybersecurity and Digital Rights - coe.int</t>
+        </is>
+      </c>
+      <c r="D505" t="inlineStr">
+        <is>
+          <t>Thu, 15 Jan 2026 13:36:56 GMT</t>
+        </is>
+      </c>
+      <c r="E505" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMifkFVX3lxTE9sN0V4UjJvV2ozM3EyZjFvbVlSM2hFMklQOXZ0NXhhWE9GRm83TXV0c1o1OC1uWldOWEtTQ3pJU0s2MlpTWjhfOGkybm1kUHRXa0VhRjh1bG9hZENnVEh2d3NZY3U1WkV2Q0FKcnYtMzRmWVJxaXNwb0VLQzFsQQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F505" t="n">
+        <v>10</v>
+      </c>
+      <c r="G505" s="2" t="n">
+        <v>46037.56731481481</v>
+      </c>
+    </row>
+    <row r="506">
+      <c r="A506" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B506" t="inlineStr">
+        <is>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+        </is>
+      </c>
+      <c r="C506" t="inlineStr">
+        <is>
+          <t>NHS England launches supplier registry for AI scribing tech - Home | Digital Health</t>
+        </is>
+      </c>
+      <c r="D506" t="inlineStr">
+        <is>
+          <t>Fri, 16 Jan 2026 07:31:25 GMT</t>
+        </is>
+      </c>
+      <c r="E506" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxPemg1Tk9ESTlMVWNTaVdnMzE2azNBYk82WlNySkZMRzhKNnBDUVR4MDVsWW4yVmlCYjBjWVQ4T3h6bHpyaGVYY3hFS2l1ek9oMmVPOTZ5b2toZTRzc3RiVFJLSW54QTh2bXd0Vl9LZUVvbUNZLXloZWxUOExOZ2pCWXZ2aUFZdkJORkJTbDdDSXRBc3otTWlXS09WalIxdk0?oc=5</t>
+        </is>
+      </c>
+      <c r="F506" t="n">
+        <v>10</v>
+      </c>
+      <c r="G506" s="2" t="n">
+        <v>46038.31348379629</v>
+      </c>
+    </row>
+    <row r="507">
+      <c r="A507" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B507" t="inlineStr">
+        <is>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+        </is>
+      </c>
+      <c r="C507" t="inlineStr">
+        <is>
+          <t>AI and creativity ‘at a tipping point’ - PR Week UK</t>
+        </is>
+      </c>
+      <c r="D507" t="inlineStr">
+        <is>
+          <t>Fri, 16 Jan 2026 11:10:11 GMT</t>
+        </is>
+      </c>
+      <c r="E507" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMie0FVX3lxTFBTMy0xamJBaUJjcF9NMlRwMFc3dDRCNHJLaC1Cc1laa2tzT2Y2a0JoZldhNHpuampPQW5xeElMcDNibVRTM3BSM2RMX1padEVTbWNvay0wdy12NHFTTjhQSnpJTFN4LXNfRzZYQk1ESERScVZTZ2hjc1RBYw?oc=5</t>
+        </is>
+      </c>
+      <c r="F507" t="n">
+        <v>10</v>
+      </c>
+      <c r="G507" s="2" t="n">
+        <v>46038.46540509259</v>
+      </c>
+    </row>
+    <row r="508">
+      <c r="A508" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B508" t="inlineStr">
+        <is>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+        </is>
+      </c>
+      <c r="C508" t="inlineStr">
+        <is>
+          <t>Société Générale Drops Internal AI for Copilot - DirectIndustry e-Magazine</t>
+        </is>
+      </c>
+      <c r="D508" t="inlineStr">
+        <is>
+          <t>Fri, 16 Jan 2026 09:03:00 GMT</t>
+        </is>
+      </c>
+      <c r="E508" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxOSmZpMkFCVEt6V010Z1F3S3dOZXBadWlFYU10ODNTV2RxSjVXRzJjWWc3SHY4Nm42clFmXzJBMVN6aGVyNEVmdXNkSjgxUm5xWFV2WWoxWGhENk1HZ3ZSUnhRS3BPVTJXa0VpaFJLUzQtcWNfQ2g5R1ZiMWhBZ2tMcElyQVN1UUc5NjRPVGt0SkhDbU1IRlcxbHpUSzNTRVdkcU16XzUzNA?oc=5</t>
+        </is>
+      </c>
+      <c r="F508" t="n">
+        <v>10</v>
+      </c>
+      <c r="G508" s="2" t="n">
+        <v>46038.37708333333</v>
+      </c>
+    </row>
+    <row r="509">
+      <c r="A509" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B509" t="inlineStr">
+        <is>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+        </is>
+      </c>
+      <c r="C509" t="inlineStr">
+        <is>
+          <t>Reuters digital report 2026: journalism’s pivot – navigating the AI and creators squeeze - International Federation of Journalists - IFJ</t>
+        </is>
+      </c>
+      <c r="D509" t="inlineStr">
+        <is>
+          <t>Fri, 16 Jan 2026 11:40:47 GMT</t>
+        </is>
+      </c>
+      <c r="E509" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi4wFBVV95cUxQSEdZX3lHN3REUFIzNTRZU0UzUTM4dFJneHl2UnFnbV9RTGZCWG9EcDFvRHF3d1B4Xy1ZckRMb01GZUtQYmVNVkgzLVJ6UzFzblVwNmZrVS1naGdBVG5fUFlsa3hnWUx6T3VsUmJ1UGhhN2hZQTBnTkowS0lOektyaWd5djdGTmhvQk0zREVkWWZabzFYeloxcl9wMS0tYWFKQzRmTWNYYTlPeFo2QWpCLWpzU3g3RDZuYmxDTTRfa0R0NHB4RHJja2ZxYWxybWNkV2JYa2xLbnlyamU1djhxNC1mMA?oc=5</t>
+        </is>
+      </c>
+      <c r="F509" t="n">
+        <v>10</v>
+      </c>
+      <c r="G509" s="2" t="n">
+        <v>46038.48665509259</v>
+      </c>
+    </row>
+    <row r="510">
+      <c r="A510" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B510" t="inlineStr">
+        <is>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+        </is>
+      </c>
+      <c r="C510" t="inlineStr">
+        <is>
+          <t>Column: People can't just rely on AI to function in the real world - Exmouth Journal</t>
+        </is>
+      </c>
+      <c r="D510" t="inlineStr">
+        <is>
+          <t>Fri, 16 Jan 2026 05:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="E510" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxPelZYbEFZZl91dThfZ1BYY0Z3S0xJTm5xWk9qb3o2VDNtRHl2d3pmbDI5dVRvZTJ6clNMN1VwTG82WWdIRVE2UExlWWxqX1lsN1hqZ3J4Um9RY0dBWDhrVElPeU5aMGlDQ28tcEM5cHpsNmNfazFxbWdxd0h2UzFEbS1kckZQRkZ1c1dxWFMxRmdXS05fcEtxTTFURERQTkpBZXlIWmtn?oc=5</t>
+        </is>
+      </c>
+      <c r="F510" t="n">
+        <v>10</v>
+      </c>
+      <c r="G510" s="2" t="n">
+        <v>46038.20833333334</v>
+      </c>
+    </row>
+    <row r="511">
+      <c r="A511" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B511" t="inlineStr">
+        <is>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+        </is>
+      </c>
+      <c r="C511" t="inlineStr">
+        <is>
+          <t>Regulatory delays hinder UK tech &amp; AI project delivery - IT Brief UK</t>
+        </is>
+      </c>
+      <c r="D511" t="inlineStr">
+        <is>
+          <t>Fri, 16 Jan 2026 09:15:00 GMT</t>
+        </is>
+      </c>
+      <c r="E511" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMihwFBVV95cUxORk1DNTE1clhqdjdoeml0NEx4ZDRiMzlQNS1NaHpnRTFUa3hGRk11RldERUItUi1QTkRwdEdlMUtsdDFuN0Z2UjFhV25LbGhYUmxGNnNnQjhRT3ViU2ZzQ2F5M0FKTzE5dkVmQnNLN0otM2Z3Z3M3X3dQUVo1aTRoZnNYam11aG8?oc=5</t>
+        </is>
+      </c>
+      <c r="F511" t="n">
+        <v>10</v>
+      </c>
+      <c r="G511" s="2" t="n">
+        <v>46038.38541666666</v>
+      </c>
+    </row>
+    <row r="512">
+      <c r="A512" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B512" t="inlineStr">
+        <is>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+        </is>
+      </c>
+      <c r="C512" t="inlineStr">
+        <is>
+          <t>Explainable AI and the future of financial crime prevention - FinTech Global</t>
+        </is>
+      </c>
+      <c r="D512" t="inlineStr">
+        <is>
+          <t>Thu, 15 Jan 2026 17:31:22 GMT</t>
+        </is>
+      </c>
+      <c r="E512" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxNZGdGN1ZGZWJvTndfdkpvTFgycHdzOHFSWmVTbWVsekRzNVJXWDFzenVPYlZPVUJYZ0NVMnNIR0ZyekJUeHZOZVljTDJNdktISjNFYUtYZEZyVnNCd0lINHFkSGVrZmRybUJqNFZvbFBKLTdjUmJjdlFpejJWTnBjQUZJZ0xSTl9nYVI4aDZ6eFY0anVZbUJSalFB?oc=5</t>
+        </is>
+      </c>
+      <c r="F512" t="n">
+        <v>10</v>
+      </c>
+      <c r="G512" s="2" t="n">
+        <v>46037.73011574074</v>
+      </c>
+    </row>
+    <row r="513">
+      <c r="A513" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B513" t="inlineStr">
+        <is>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+        </is>
+      </c>
+      <c r="C513" t="inlineStr">
+        <is>
+          <t>MongoDB adds Voyage 4 AI models &amp; automates vector search - IT Brief UK</t>
+        </is>
+      </c>
+      <c r="D513" t="inlineStr">
+        <is>
+          <t>Fri, 16 Jan 2026 08:45:00 GMT</t>
+        </is>
+      </c>
+      <c r="E513" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiiwFBVV95cUxQSDUxcUpONGZYRXItWF85bko1eW92T0trbFR2TkpDcnV3MXh2STlCZndQRlZaQ2Z5VG9MRUllRjhyZmZ2MVVrNWM3UHlUa01ZbEl6aklQaElOdkFrc3pVSG8ySDhNZVBRS3k1ZENZY2hkMXdzYmZNbmdBb3VCTjMyNEdGU0ItbUZrdGNn?oc=5</t>
+        </is>
+      </c>
+      <c r="F513" t="n">
+        <v>10</v>
+      </c>
+      <c r="G513" s="2" t="n">
+        <v>46038.36458333334</v>
+      </c>
+    </row>
+    <row r="514">
+      <c r="A514" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B514" t="inlineStr">
+        <is>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+        </is>
+      </c>
+      <c r="C514" t="inlineStr">
+        <is>
+          <t>Small Cell Forum maps 2026 push for scalable 5G growth - IT Brief UK</t>
+        </is>
+      </c>
+      <c r="D514" t="inlineStr">
+        <is>
+          <t>Fri, 16 Jan 2026 09:15:00 GMT</t>
+        </is>
+      </c>
+      <c r="E514" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiigFBVV95cUxOQWhsVU40UFVXajNER0U4eG9NcVEzWlQxakhIZXFpZnJSX3U2cl9GWTFEN2tZUEhyeGp1WEZESExGSTZhZ0tqTktRVVdJZUZEMGxQVDlpYXJ4VXM4MVN1ZEdHT1NvMGN3RDZ3aGpGZlNyTmR5RDdGbXhEVGVPTE5nRUFDcjI2NGdlbVE?oc=5</t>
+        </is>
+      </c>
+      <c r="F514" t="n">
+        <v>10</v>
+      </c>
+      <c r="G514" s="2" t="n">
+        <v>46038.38541666666</v>
+      </c>
+    </row>
+    <row r="515">
+      <c r="A515" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B515" t="inlineStr">
+        <is>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+        </is>
+      </c>
+      <c r="C515" t="inlineStr">
+        <is>
+          <t>AI will ‘turbocharge’ Britain’s transport network, says Transport Committee chair - Fleet World</t>
+        </is>
+      </c>
+      <c r="D515" t="inlineStr">
+        <is>
+          <t>Fri, 16 Jan 2026 08:24:43 GMT</t>
+        </is>
+      </c>
+      <c r="E515" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxNN19hay1TSTBieDZKdkZKN1lCTm1lX0JNUEVTbnNENXNKb1J4UThRMjNRUFV2b0RPbXdjOTdPdVFUN2d5NXBlMzA3UW1BZHRQYnkxRGxZMzFTWkFUdVk0M3BBNEwtYTAzcTgxcmluRmVxX3VocFVTS3d2NUd2akd3cWQtMVpWN0MzX0YtempzcXhGZVVzbktIc2NBV3FDdWpJcVQwdjBn?oc=5</t>
+        </is>
+      </c>
+      <c r="F515" t="n">
+        <v>10</v>
+      </c>
+      <c r="G515" s="2" t="n">
+        <v>46038.35049768518</v>
+      </c>
+    </row>
+    <row r="516">
+      <c r="A516" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B516" t="inlineStr">
+        <is>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+        </is>
+      </c>
+      <c r="C516" t="inlineStr">
+        <is>
+          <t>Cisco's HR chief says AI and ML roles are 'really hard' to fill. Getting execs on the phone helps. - Business Insider</t>
+        </is>
+      </c>
+      <c r="D516" t="inlineStr">
+        <is>
+          <t>Fri, 16 Jan 2026 10:52:00 GMT</t>
+        </is>
+      </c>
+      <c r="E516" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMigwFBVV95cUxOaHJINFBoS2tXYVFST2xSQWlYdkZ4czQyUHo2QmdfNFRqSTZycGdCZWhoNkhYVUVDT2RiSTNCcEpwazFOdFBUVDhkeWplTzBCdlY3djF6VUFMWGxhVDRvY0Fvb3pJRXBGN2Z1WElhYmxncFVzWUNqdVhhdnkzREdjRWx1OA?oc=5</t>
+        </is>
+      </c>
+      <c r="F516" t="n">
+        <v>10</v>
+      </c>
+      <c r="G516" s="2" t="n">
+        <v>46038.45277777778</v>
+      </c>
+    </row>
+    <row r="517">
+      <c r="A517" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B517" t="inlineStr">
+        <is>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+        </is>
+      </c>
+      <c r="C517" t="inlineStr">
+        <is>
+          <t>Goertzel &amp; Lanier clash over AI autonomy &amp; control - IT Brief UK</t>
+        </is>
+      </c>
+      <c r="D517" t="inlineStr">
+        <is>
+          <t>Fri, 16 Jan 2026 08:45:00 GMT</t>
+        </is>
+      </c>
+      <c r="E517" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMif0FVX3lxTFBYTjYyZGNEb0FyN01UU1FIMHUtMmdhRXFrTk9MR241UUh1V3NtM1d6WDBzVzN3QzdZZmhoN2VWWW1MRGFJU3Y0QWVQQ25jenZ4Ti04UkM4aFRRR2RVNnhVWTRZZGFualB6TThvQ0gtZmdmM05NTm1rM3lObGZHOWs?oc=5</t>
+        </is>
+      </c>
+      <c r="F517" t="n">
+        <v>10</v>
+      </c>
+      <c r="G517" s="2" t="n">
+        <v>46038.36458333334</v>
+      </c>
+    </row>
+    <row r="518">
+      <c r="A518" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B518" t="inlineStr">
+        <is>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+        </is>
+      </c>
+      <c r="C518" t="inlineStr">
+        <is>
+          <t>TCS teams up with AMD to scale AI adoption across industries - verdict.co.uk</t>
+        </is>
+      </c>
+      <c r="D518" t="inlineStr">
+        <is>
+          <t>Fri, 16 Jan 2026 06:15:25 GMT</t>
+        </is>
+      </c>
+      <c r="E518" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiYEFVX3lxTE1OaU55ZHF4ZU1JLTF3MlRZeE5YdTJRY3B1eS1KNHdkMVByUTVBVTRDQW9fZzBvU2h1cDNpeng2QThYZUprT2VkS2EwRlZOWTR0enl0X19LVHZKWEVwc0Z6cA?oc=5</t>
+        </is>
+      </c>
+      <c r="F518" t="n">
+        <v>10</v>
+      </c>
+      <c r="G518" s="2" t="n">
+        <v>46038.26070601852</v>
+      </c>
+    </row>
+    <row r="519">
+      <c r="A519" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B519" t="inlineStr">
+        <is>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+        </is>
+      </c>
+      <c r="C519" t="inlineStr">
+        <is>
+          <t>Gaps and policies in AI- and algorithm-driven discrimination in Europe - coe.int</t>
+        </is>
+      </c>
+      <c r="D519" t="inlineStr">
+        <is>
+          <t>Thu, 15 Jan 2026 10:35:24 GMT</t>
+        </is>
+      </c>
+      <c r="E519" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxPbU5UeUpqcnp1eWxjanozcUc0WWNON1FGNXFXS2ktLXpZdlVLaUxKSmh5TkhITlVQX3MyV3duMU1kTUl0VlBHWGs5UFBGRHFuYmxOZmlHR3NTbGZhdThURmU1NWU1RnJjZFZaS2Qyc185RTREM2JtZW5xQTdJX1FJbk90RktyTktxQTZBRFNyYTBXWDRzZEs0OS1mWDFkX05HcWJPR3VwSFU?oc=5</t>
+        </is>
+      </c>
+      <c r="F519" t="n">
+        <v>10</v>
+      </c>
+      <c r="G519" s="2" t="n">
+        <v>46037.44125</v>
+      </c>
+    </row>
+    <row r="520">
+      <c r="A520" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B520" t="inlineStr">
+        <is>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+        </is>
+      </c>
+      <c r="C520" t="inlineStr">
+        <is>
+          <t>Bridging technology and peacemaking at the marking of CMI’s 25 years - CMI - Martti Ahtisaari Peace Foundation</t>
+        </is>
+      </c>
+      <c r="D520" t="inlineStr">
+        <is>
+          <t>Fri, 16 Jan 2026 11:44:22 GMT</t>
+        </is>
+      </c>
+      <c r="E520" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxORVhNV1h6YzZLWWhCNDZidDJrZTFPLXlTaG1DOURhRmN3ZGVIdVZRYllhWlNsc2FvVWsxNDBVWEtYY3daUUxmaDdEWVFBcDFEYzdEUFVWT0t0RzdielBmdUNWTFlXMDg1Z1MxVmVnSmw2QmlWc2ltY1ptOXp0eFpYN2s4TDNCVUUxLWFWOEdQaUd2WFQ5eUR5WHJR?oc=5</t>
+        </is>
+      </c>
+      <c r="F520" t="n">
+        <v>10</v>
+      </c>
+      <c r="G520" s="2" t="n">
+        <v>46038.48914351852</v>
+      </c>
+    </row>
+    <row r="521">
+      <c r="A521" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B521" t="inlineStr">
+        <is>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+        </is>
+      </c>
+      <c r="C521" t="inlineStr">
+        <is>
+          <t>Matthew McConaughey trademarks iconic phrase to stop AI misuse - BBC</t>
+        </is>
+      </c>
+      <c r="D521" t="inlineStr">
+        <is>
+          <t>Thu, 15 Jan 2026 18:34:41 GMT</t>
+        </is>
+      </c>
+      <c r="E521" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTFBJMFdGVWI0UlM4bkVzUnBKT1hCeTliSnE0RjZ2WEE1dk02Q0pNSGNSZUI4U2tjUjRHb0YyUHMxQ2VqcWV5S25nNEkxdXhNejhlUUJIQm1FeHIzQdIBX0FVX3lxTE1VLUhqVW1ISWpCbEhuMU10cTBsVmlLQUVuLS1JM0w5cjJWbzN4czlxaEZWVWV6Y2xFdVB5X3hPNnFmbTdWT0dFMEpGT0JYTTM3LWlDUngxd2JzNmNFWHBF?oc=5</t>
+        </is>
+      </c>
+      <c r="F521" t="n">
+        <v>10</v>
+      </c>
+      <c r="G521" s="2" t="n">
+        <v>46037.77408564815</v>
+      </c>
+    </row>
+    <row r="522">
+      <c r="A522" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B522" t="inlineStr">
+        <is>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+        </is>
+      </c>
+      <c r="C522" t="inlineStr">
+        <is>
+          <t>Fred. Olsen unveils AI ‘digital twin’ cruise campaign - IT Brief UK</t>
+        </is>
+      </c>
+      <c r="D522" t="inlineStr">
+        <is>
+          <t>Fri, 16 Jan 2026 09:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="E522" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMihAFBVV95cUxPUnhyRVVWQlptNjFIbUZ0aGdDQWNYR0tXeFJwMTdVQjdVWHZoOEVRbWROaG1uLU1CVTFwaXdfdldYZk1Fem5aVmpGaVRXNHd6Z2ZZc2EzSHdkTlkxTDEtLV9TUzlhR2pGOGJUN3pUbkROanc5RVN5ZWMyaDZhNEJybTJiazI?oc=5</t>
+        </is>
+      </c>
+      <c r="F522" t="n">
+        <v>10</v>
+      </c>
+      <c r="G522" s="2" t="n">
+        <v>46038.375</v>
+      </c>
+    </row>
+    <row r="523">
+      <c r="A523" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B523" t="inlineStr">
+        <is>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+        </is>
+      </c>
+      <c r="C523" t="inlineStr">
+        <is>
+          <t>Digital Pathology Market Growing at 9.9% CAGR to 2031 as AI Adoption Accelerates, says a 2026 Mordor Intelligence Report - PR Newswire UK</t>
+        </is>
+      </c>
+      <c r="D523" t="inlineStr">
+        <is>
+          <t>Fri, 16 Jan 2026 08:30:00 GMT</t>
+        </is>
+      </c>
+      <c r="E523" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMihwJBVV95cUxNeTdDWm1NWXFacG1QNVNtQTNVU1Uxc0FpaUZDUnhZbkVxYVZNa0RCOXU2SlBMajNoTGIzZ0RBTUFnV2VUdllNR01UcklISWFuT25PSUxnT3BhNXRFbVFndGlFZ0ZyV1J1ZVIzSjc5ZEd0OFlZOHo4VXRqZE5IbzhOYjg3UlhDT2RpNUc4WlRNbVo2Y0dWS1I4dElWTVh5a3N5aGQ5ajJaWEY5YVdMdXU4S0pObDREVElyN2pZMVVGVE5VOFh6ZjB0VWpUcHBiNXJaNkpTdTdHUG5ZeFZfczd3VjdLbmJTeXFpRmhSZkQ4aDVjRzdmdkpaeFFQVUFuZjhmLTlXZE5pQQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F523" t="n">
+        <v>10</v>
+      </c>
+      <c r="G523" s="2" t="n">
+        <v>46038.35416666666</v>
+      </c>
+    </row>
+    <row r="524">
+      <c r="A524" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B524" t="inlineStr">
+        <is>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+        </is>
+      </c>
+      <c r="C524" t="inlineStr">
+        <is>
+          <t>Blog: AI-Prosperity Alignment: A Pathway to a Flourishing Future - UCL | University College London</t>
+        </is>
+      </c>
+      <c r="D524" t="inlineStr">
+        <is>
+          <t>Thu, 15 Jan 2026 15:44:48 GMT</t>
+        </is>
+      </c>
+      <c r="E524" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxQYjdRa2l1UkFLd2taQTB0NVlPbDd3WnQ3d3J1UDZYNV9ieTl6TTl0X2o3RXhtblhQOElhTXJpXzBJVzJ3Tnl5WlpsUVcwS3F0TkpRZ0REWVhmYmJSMXJMVlROQ3lJcmJRTzVjb0liR2tGUFVjdFZvcEd6VmFaV243T1lQekoxelE5dkRNUzNmOHFmLURORTRMTGE0blRnUnF3aVdz?oc=5</t>
+        </is>
+      </c>
+      <c r="F524" t="n">
+        <v>10</v>
+      </c>
+      <c r="G524" s="2" t="n">
+        <v>46037.65611111111</v>
+      </c>
+    </row>
+    <row r="525">
+      <c r="A525" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B525" t="inlineStr">
+        <is>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+        </is>
+      </c>
+      <c r="C525" t="inlineStr">
+        <is>
+          <t>Stop referencing fake case citations, judges warned - The Law Society Gazette</t>
+        </is>
+      </c>
+      <c r="D525" t="inlineStr">
+        <is>
+          <t>Fri, 16 Jan 2026 10:09:04 GMT</t>
+        </is>
+      </c>
+      <c r="E525" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxOQkNCVW1wb0MwVEhZVEJNM3luc2ppQXRLU2p5ZVUzMm5KRW9OaVBpNWN2ZGNnSGowWWRndmljYjJxYkRqdXJOazAzcHctSUdhWnRvVzBONWxrNjhHYVJnZmF2ZkZ3RmRJVFpwSW5MOVJRQUQ2cHdhMmgyT2taNzRPT0NPMFNlaVYyYmtTQ0tqbnBzYVFQZVp4Sm5YNFQ0VG5TVHc?oc=5</t>
+        </is>
+      </c>
+      <c r="F525" t="n">
+        <v>10</v>
+      </c>
+      <c r="G525" s="2" t="n">
+        <v>46038.42296296296</v>
+      </c>
+    </row>
+    <row r="526">
+      <c r="A526" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B526" t="inlineStr">
+        <is>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+        </is>
+      </c>
+      <c r="C526" t="inlineStr">
+        <is>
+          <t>How SAP Frames AI Sustainability in Data Centre Efficiency - Data Centre Magazine</t>
+        </is>
+      </c>
+      <c r="D526" t="inlineStr">
+        <is>
+          <t>Fri, 16 Jan 2026 09:22:58 GMT</t>
+        </is>
+      </c>
+      <c r="E526" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMihwFBVV95cUxNLTZ4MlZ2WTJlZ3FCUlhSaUxmYkhrT21UNktjN1JVZkEwZnlJSEV3V2Y3Yi11aE9UYl9aaldNMi1jcHN2US03ZnoxelBSQzNubjRJY05ycW4temZ2QkVQakVtclBZaWhOR24teGI3cGlhUlJRMjlnT3V0YnItckhVdF9yUlU3OG8?oc=5</t>
+        </is>
+      </c>
+      <c r="F526" t="n">
+        <v>10</v>
+      </c>
+      <c r="G526" s="2" t="n">
+        <v>46038.39094907408</v>
+      </c>
+    </row>
+    <row r="527">
+      <c r="A527" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B527" t="inlineStr">
+        <is>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+        </is>
+      </c>
+      <c r="C527" t="inlineStr">
+        <is>
+          <t>Not Just Travel launches AI tool for homeworkers - Travel Gossip</t>
+        </is>
+      </c>
+      <c r="D527" t="inlineStr">
+        <is>
+          <t>Fri, 16 Jan 2026 11:23:29 GMT</t>
+        </is>
+      </c>
+      <c r="E527" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxNUV85eUxTLXNxV0VoR01XN3Y5dE42dUQwbExWMklxSURmZkVjRXFKeW5IeVJqVGhUaDFONmJZNGs0a1hTb2NIQWdMa3I3aFZJVUxCWkVHMVZWVFc1N2ZQMXdRLU1GeUUxQXduOWtEaThBZVE5cGM0QnQ5VEJCbmhLZWVDeDBvRGJPZFdVOExFbUc?oc=5</t>
+        </is>
+      </c>
+      <c r="F527" t="n">
+        <v>10</v>
+      </c>
+      <c r="G527" s="2" t="n">
+        <v>46038.47464120371</v>
+      </c>
+    </row>
+    <row r="528">
+      <c r="A528" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B528" t="inlineStr">
+        <is>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+        </is>
+      </c>
+      <c r="C528" t="inlineStr">
+        <is>
+          <t>EMA and FDA set common principles for AI in medicine development - European Medicines Agency</t>
+        </is>
+      </c>
+      <c r="D528" t="inlineStr">
+        <is>
+          <t>Wed, 14 Jan 2026 15:18:03 GMT</t>
+        </is>
+      </c>
+      <c r="E528" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxOQ1pkYXNMX0FyNjB3UzRJQkd2NUdQTklPT1hsZlZPdkFkY2JBZ3U1UHl3azJKYjdJdGtpN3hmUGEzRXVtWm93dTFWMjlnU2tYbDZFakE4dXZiRWl2N190b24waG1TcXdmTEtTSWtmZ3UzVHRzQ21pNG90R3J4T3pQLWtJT2RqdHNmZFp3cUxwN1ctbG8?oc=5</t>
+        </is>
+      </c>
+      <c r="F528" t="n">
+        <v>10</v>
+      </c>
+      <c r="G528" s="2" t="n">
+        <v>46036.63753472222</v>
+      </c>
+    </row>
+    <row r="529">
+      <c r="A529" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B529" t="inlineStr">
+        <is>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+        </is>
+      </c>
+      <c r="C529" t="inlineStr">
+        <is>
+          <t>Accenture Named a Leader in Gartner® Magic Quadrant™ for Digital Technology and Business Consulting Services - Accenture</t>
+        </is>
+      </c>
+      <c r="D529" t="inlineStr">
+        <is>
+          <t>Thu, 15 Jan 2026 09:08:25 GMT</t>
+        </is>
+      </c>
+      <c r="E529" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi4AFBVV95cUxPLWFQeG1aX2tia2JscHpwWERVd3FGVjRoN3dTMHowWFJZNVJ2RWNsc0JKRWdUanZxOUZuWHd4cXdDczAxMUN2ZFc3LWtmMEdwdWVReWJEUlEwMHRjeFM5QWE3MDhoN2hXR0ZPRHFUbGFBc1JTQmQ4cDFGSFlxM1Q5ODlBLWN3VjBwOTZCWXloN0I4ekk4emhnek03RVZSYlViR25mLTBSOHJfZTRBamhWMzVrbHBnN3VNaDBmUFdJYkhqLTRsUG92V1N1UGVudTQ0ZWhQZGdXVlVyX25yZW5Tag?oc=5</t>
+        </is>
+      </c>
+      <c r="F529" t="n">
+        <v>10</v>
+      </c>
+      <c r="G529" s="2" t="n">
+        <v>46037.38084490741</v>
+      </c>
+    </row>
+    <row r="530">
+      <c r="A530" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B530" t="inlineStr">
+        <is>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+        </is>
+      </c>
+      <c r="C530" t="inlineStr">
+        <is>
+          <t>Qualitative researchers’ AI rejection is based on identity, not reason - Times Higher Education</t>
+        </is>
+      </c>
+      <c r="D530" t="inlineStr">
+        <is>
+          <t>Fri, 16 Jan 2026 00:01:32 GMT</t>
+        </is>
+      </c>
+      <c r="E530" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxOTVpPTUFGYVhBYTQ3YWVjNlQyOHB0dWlQZk55ZTluZVNPaEIyUEotaFBDalNrVjFyZVNiUmdTdl80ejhuc3FWZGNTX1ZJVVhKN1NHU2FqeXZPZlM5Qm9VdTBiSVdPRy1fMU9pVjJNVHNHaWkyOGt3bzdoTFJIeGxxeWFDcWpDNkxHUHgtbksyQms4YlMxaWpTclg2UlhTWnY3d1h4X3paR1pBN2c?oc=5</t>
+        </is>
+      </c>
+      <c r="F530" t="n">
+        <v>10</v>
+      </c>
+      <c r="G530" s="2" t="n">
+        <v>46038.00106481482</v>
+      </c>
+    </row>
+    <row r="531">
+      <c r="A531" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B531" t="inlineStr">
+        <is>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+        </is>
+      </c>
+      <c r="C531" t="inlineStr">
+        <is>
+          <t>AI-generated virtual psychedelics bridge digital and therapeutic frontiers in mental health research - Nature</t>
+        </is>
+      </c>
+      <c r="D531" t="inlineStr">
+        <is>
+          <t>Fri, 16 Jan 2026 10:11:27 GMT</t>
+        </is>
+      </c>
+      <c r="E531" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiX0FVX3lxTE9vMjNFZHUtUEhvV0xmM3BMUWJPNUVwQUJHTFhISHc4LURGaHFaRWJPSE5RdDFENmtMVi1oWEcxVWhUTFk5MTJjczVkbUJyeW95SEh6LWp0NUlkelJRVmFV?oc=5</t>
+        </is>
+      </c>
+      <c r="F531" t="n">
+        <v>10</v>
+      </c>
+      <c r="G531" s="2" t="n">
+        <v>46038.42461805556</v>
+      </c>
+    </row>
+    <row r="532">
+      <c r="A532" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B532" t="inlineStr">
+        <is>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+        </is>
+      </c>
+      <c r="C532" t="inlineStr">
+        <is>
+          <t>Technology must enhance real-world learning - not replace it: Danny Metters - Yorkshire Post</t>
+        </is>
+      </c>
+      <c r="D532" t="inlineStr">
+        <is>
+          <t>Fri, 16 Jan 2026 05:45:00 GMT</t>
+        </is>
+      </c>
+      <c r="E532" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMivgFBVV95cUxPMFNEOWs0bzMtbWxjX3ZMLWpZVEpiLTN6UmVjNC14TXFuWk55azE2aDA3aUttLVhGUnZaZVBoTEdkRl9DdFB4SXltTnpuRUk0UkxiZXVhbTBQTE4xeHAxX1hzX1N3SXRBUkNYOUVNT29NcWFuTmRfMTZRTC1lZVl6amEzb1pFOGZqbnJWeGJvS2VsVnZISmdGejZoVWx5NFdIM2txNGRBdDhUREliUl9wSnRvRXl4ZHEzQl9ndjJ3?oc=5</t>
+        </is>
+      </c>
+      <c r="F532" t="n">
+        <v>10</v>
+      </c>
+      <c r="G532" s="2" t="n">
+        <v>46038.23958333334</v>
+      </c>
+    </row>
+    <row r="533">
+      <c r="A533" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B533" t="inlineStr">
+        <is>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+        </is>
+      </c>
+      <c r="C533" t="inlineStr">
+        <is>
+          <t>AI and Network Science for Emotional Risk Measurement in Stock Markets | Newswise - Newswise</t>
+        </is>
+      </c>
+      <c r="D533" t="inlineStr">
+        <is>
+          <t>Fri, 16 Jan 2026 10:45:00 GMT</t>
+        </is>
+      </c>
+      <c r="E533" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxOODRBd1R3OFFRUmR5MndhXzFobnRub3ZyQ05DQzFmc0pzcUVQcWRtUlNDUzI1SVFzTDg3R2JRQ3RpR0sxbW5sSG1DTzdZbm5QZEEtUUFvSjF4WmpSN3NXX3VhQXpSeW5tc29JdmpURy1sUTdkWnZwYmt0MVA2TlRTMUlOZkt0bVF1MTFtLXBWWXpBMVFQWUlIME9uenZlUDhZb1R3V1hhNNIBpwFBVV95cUxOODRBd1R3OFFRUmR5MndhXzFobnRub3ZyQ05DQzFmc0pzcUVQcWRtUlNDUzI1SVFzTDg3R2JRQ3RpR0sxbW5sSG1DTzdZbm5QZEEtUUFvSjF4WmpSN3NXX3VhQXpSeW5tc29JdmpURy1sUTdkWnZwYmt0MVA2TlRTMUlOZkt0bVF1MTFtLXBWWXpBMVFQWUlIME9uenZlUDhZb1R3V1hhNA?oc=5</t>
+        </is>
+      </c>
+      <c r="F533" t="n">
+        <v>10</v>
+      </c>
+      <c r="G533" s="2" t="n">
+        <v>46038.44791666666</v>
+      </c>
+    </row>
+    <row r="534">
+      <c r="A534" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B534" t="inlineStr">
+        <is>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+        </is>
+      </c>
+      <c r="C534" t="inlineStr">
+        <is>
+          <t>A new direction for students in an AI world: Prosper, prepare, protect - Brookings</t>
+        </is>
+      </c>
+      <c r="D534" t="inlineStr">
+        <is>
+          <t>Wed, 14 Jan 2026 13:43:05 GMT</t>
+        </is>
+      </c>
+      <c r="E534" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxOLUFiQzhMMWhpeC1VRVc2aUZ5UUFFN2pNQ3JqMHgtR0U0N2wyQUZzTXhfY09lMWMwUVpfdUNPNm00NFBLNEMtZXdIRDNiTnJEQlQ0ZjFHNy1TbkpJWHozWDdNSU5EaHpSbU14V09MVTc1YWpkOUpLem9keldIeDRWUU55aXBoZmN0MWczVTNyUVpreFViOHNKeE9OaGVmdlo3d1J4MTFn?oc=5</t>
+        </is>
+      </c>
+      <c r="F534" t="n">
+        <v>10</v>
+      </c>
+      <c r="G534" s="2" t="n">
+        <v>46036.57158564815</v>
+      </c>
+    </row>
+    <row r="535">
+      <c r="A535" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B535" t="inlineStr">
+        <is>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+        </is>
+      </c>
+      <c r="C535" t="inlineStr">
+        <is>
+          <t>Argonne Uses AI and Robotics for 6,000 Battery Experiments - Battery Technology</t>
+        </is>
+      </c>
+      <c r="D535" t="inlineStr">
+        <is>
+          <t>Thu, 15 Jan 2026 19:52:05 GMT</t>
+        </is>
+      </c>
+      <c r="E535" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxQS1RpUEVNRG1Ec0VNczMza3l6azlhZXVpVjZXd0FJc0gycGxCSW5FRWRWMzZTaHV6Qzc0ZUsyUi12RXhMVHd6cFVxTldHVEMwc3A0eWdPM3dwU0pZTm1jeVNjZVFOdTl1ak4xdGxWdU1QN3drSXJ1M3V1V3Y1SkQ3UXhKcDR6T0NVelhyNFJPR0ZFNHRIeXZGMU82bE9SemtGdVlVaw?oc=5</t>
+        </is>
+      </c>
+      <c r="F535" t="n">
+        <v>10</v>
+      </c>
+      <c r="G535" s="2" t="n">
+        <v>46037.82783564815</v>
+      </c>
+    </row>
+    <row r="536">
+      <c r="A536" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B536" t="inlineStr">
+        <is>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+        </is>
+      </c>
+      <c r="C536" t="inlineStr">
+        <is>
+          <t>Why AI and cameras are the future of fleet safety | opinion - Fleet News</t>
+        </is>
+      </c>
+      <c r="D536" t="inlineStr">
+        <is>
+          <t>Wed, 14 Jan 2026 11:35:35 GMT</t>
+        </is>
+      </c>
+      <c r="E536" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMilAFBVV95cUxQX3E5WTlvV2lkSUE5cTRzRjZWQ1ZTVXBUU0RSeERTYzVZNzhsTHJpQVhUbHJCMXl2UnRyY0V2X2FXYmVlam1mbVZ1ZFo2UjgzaWduMUx5WUJsZURCTlg3TmJBTDktS2VLY2FBR1ktMTNMdm9jd1IxTEFzMmNVWEdFVktyeGdrU1RBMGZ0bGlPNlJ6TTVy?oc=5</t>
+        </is>
+      </c>
+      <c r="F536" t="n">
+        <v>10</v>
+      </c>
+      <c r="G536" s="2" t="n">
+        <v>46036.48304398148</v>
+      </c>
+    </row>
+    <row r="537">
+      <c r="A537" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B537" t="inlineStr">
+        <is>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+        </is>
+      </c>
+      <c r="C537" t="inlineStr">
+        <is>
+          <t>Looking ahead: AI and the future of the financial services customer journey - Dentons</t>
+        </is>
+      </c>
+      <c r="D537" t="inlineStr">
+        <is>
+          <t>Tue, 13 Jan 2026 15:16:25 GMT</t>
+        </is>
+      </c>
+      <c r="E537" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi0AFBVV95cUxQbHJwQzlMUk5xQWJibzdZekRWSnEwX0tDX3FuVzBxaHRZSU5WNktZMDE0Y3dzT2lRUkdybEEwUEJHY041Tk14M05wRTlrd09LbUF4S056bjdZdWo0b0UxRXg3WnNCck12dDVsekpUQlV5eEMzTjVFWWQtU3RuTUp3RW5vQ19GY25NcHlXMHFLSk04Z2pWaVRGbVRDTnJkZmhUcU4ydldWNzhQSUhURlBMaDJaNl9EeGVycnFPdTZPNnZrdkxvb1pNNllid1dkUHRQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F537" t="n">
+        <v>10</v>
+      </c>
+      <c r="G537" s="2" t="n">
+        <v>46035.63640046296</v>
+      </c>
+    </row>
+    <row r="538">
+      <c r="A538" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B538" t="inlineStr">
+        <is>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+        </is>
+      </c>
+      <c r="C538" t="inlineStr">
+        <is>
+          <t>PsiQuantum and Airbus Collaborate on Fault-Tolerant Quantum Algorithms for Aerospace - The Quantum Insider</t>
+        </is>
+      </c>
+      <c r="D538" t="inlineStr">
+        <is>
+          <t>Fri, 16 Jan 2026 06:25:58 GMT</t>
+        </is>
+      </c>
+      <c r="E538" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxNaU9fMGtwdkkxWThrZHlIYWYwVTdqdU9SZ0w5Y0t5bUxLUE5LNDdjOF9ldkEycmp2MTVuX3RyUkI5aG5QU2UtaVR4cGZTQTg2R2Utd2J1WHNiX2V5RmIyOGVHYzNOOGxXXzk4YUYyYUkxWFNTOHl0WFlnU1ZYWFJrc0kwSUJtVFJLS1FkZjFlN001N1NfM2MwaGh3a0lXRjJQRThOYmJzcTZjNUlWNDA2NGhpanE4VHZlUzl5c1lnMWVaMVVh?oc=5</t>
+        </is>
+      </c>
+      <c r="F538" t="n">
+        <v>10</v>
+      </c>
+      <c r="G538" s="2" t="n">
+        <v>46038.26803240741</v>
+      </c>
+    </row>
+    <row r="539">
+      <c r="A539" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B539" t="inlineStr">
+        <is>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+        </is>
+      </c>
+      <c r="C539" t="inlineStr">
+        <is>
+          <t>Automation joins AI and cybersecurity as digital priorities for Indian pharma - European Pharmaceutical Review</t>
+        </is>
+      </c>
+      <c r="D539" t="inlineStr">
+        <is>
+          <t>Thu, 15 Jan 2026 12:37:47 GMT</t>
+        </is>
+      </c>
+      <c r="E539" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMivgFBVV95cUxOTGM5WVpqRUVwZlgySWhnaWpuVk5aTUdGbTlpaFR6NTlqVE1rZGRhVEJfRWhZUTJJZWh1dThBT1VEVGZOSklEY1d0Ylc0UGZvYXNuWmdBX3lYWDlzZmNWbG5RZ1dWVmVHLURlMHktVWs4OEpfVUJ4eGUyM2dMbVFGV1lFTGVxSS1acURrb3ozWVZfRlRCNDI3dDF1WjRERnVjT0t4UzloX0t3ck1JSDZEMXlScGM1S1ZPcUhjaEJB?oc=5</t>
+        </is>
+      </c>
+      <c r="F539" t="n">
+        <v>10</v>
+      </c>
+      <c r="G539" s="2" t="n">
+        <v>46037.52623842593</v>
+      </c>
+    </row>
+    <row r="540">
+      <c r="A540" t="inlineStr">
+        <is>
+          <t>UNMAPPED_LINE</t>
+        </is>
+      </c>
+      <c r="B540" t="inlineStr">
+        <is>
+          <t>Insider Risk ("insider risk" OR "insider threat" OR "internal threat" OR "employee misconduct" OR "data exfiltration" OR "privileged access abuse" OR "malicious insider" OR "negligent insider" OR "insider attack" OR "corporate espionage" OR "information leakage" OR "unauthorised access" OR "policy violation" OR "security breach" OR "insider vulnerability")</t>
+        </is>
+      </c>
+      <c r="C540" t="inlineStr">
+        <is>
+          <t>Insider risk in an age of workforce volatility - csoonline.com</t>
+        </is>
+      </c>
+      <c r="D540" t="inlineStr">
+        <is>
+          <t>Fri, 16 Jan 2026 07:03:45 GMT</t>
+        </is>
+      </c>
+      <c r="E540" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxPZFlhRWdIX1hIdERkRVVmeWJ0MjBVbzBDenFpajlaNkFHZ3N4YWZ4Zks2RFRQVUNNazh2R3dNUUVzQ215Q3M2aVRrMjZUWGdRbUxUWVhHQW5vVEpFRzNoTXRUazlORVc1UUt0MGRiMGtzdzFMV0lOcnAtRG9oX0FqcFc1ODZ1VTM3NkFKVm1pYWxHQUlQSEluUA?oc=5</t>
+        </is>
+      </c>
+      <c r="F540" t="n">
+        <v>10</v>
+      </c>
+      <c r="G540" s="2" t="n">
+        <v>46038.29427083334</v>
+      </c>
+    </row>
+    <row r="541">
+      <c r="A541" t="inlineStr">
+        <is>
+          <t>UNMAPPED_LINE</t>
+        </is>
+      </c>
+      <c r="B541" t="inlineStr">
+        <is>
+          <t>Insider Risk ("insider risk" OR "insider threat" OR "internal threat" OR "employee misconduct" OR "data exfiltration" OR "privileged access abuse" OR "malicious insider" OR "negligent insider" OR "insider attack" OR "corporate espionage" OR "information leakage" OR "unauthorised access" OR "policy violation" OR "security breach" OR "insider vulnerability")</t>
+        </is>
+      </c>
+      <c r="C541" t="inlineStr">
+        <is>
+          <t>Why the Start of the Year Is Prime Time for Insider Risk - eSecurity Planet</t>
+        </is>
+      </c>
+      <c r="D541" t="inlineStr">
+        <is>
+          <t>Mon, 12 Jan 2026 22:47:15 GMT</t>
+        </is>
+      </c>
+      <c r="E541" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxPMWd4UjQxckptb3NwNXNZN1JjXzJFUlUybklxTGVhTVFzQkl5eTVkV0YzMUJoN1pqZ1ZfSGRPNXpLakExY0JBRlV3cUJ2VXM5Q0NYWTBJVUpobUFVWnJQVlVCTUpoQjNkeHAzcHlZSklwZGlqQTlScUV6NkpjeEExc0ljZ2RkQVY5Vl9Ncm16b3VrTHFDdVoxZXNTR01DUQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F541" t="n">
+        <v>10</v>
+      </c>
+      <c r="G541" s="2" t="n">
+        <v>46034.94947916667</v>
+      </c>
+    </row>
+    <row r="542">
+      <c r="A542" t="inlineStr">
+        <is>
+          <t>UNMAPPED_LINE</t>
+        </is>
+      </c>
+      <c r="B542" t="inlineStr">
+        <is>
+          <t>Insider Risk ("insider risk" OR "insider threat" OR "internal threat" OR "employee misconduct" OR "data exfiltration" OR "privileged access abuse" OR "malicious insider" OR "negligent insider" OR "insider attack" OR "corporate espionage" OR "information leakage" OR "unauthorised access" OR "policy violation" OR "security breach" OR "insider vulnerability")</t>
+        </is>
+      </c>
+      <c r="C542" t="inlineStr">
+        <is>
+          <t>The Latest GigaOm Radar Insights For Insider Risk Management - LinkedIn</t>
+        </is>
+      </c>
+      <c r="D542" t="inlineStr">
+        <is>
+          <t>Thu, 15 Jan 2026 12:00:18 GMT</t>
+        </is>
+      </c>
+      <c r="E542" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxQZ0Y4d0NPMXBvSEdnamRwQ1BCeFM3THhpS0ZHNTV6Nk9IOUJTTlJpeE1ITEt6WDFNc2haNkxjZ2JOMnozcDZqbHVyVU5ZM3lQdC1ReXFuM2RqUTlUM3RNVUlZdVpiRVlhMVpPRmFxajNnckwzRWpDRjVHNXRXSlJ3RmtvRE1kWWw3NHk4WmE4T1lyV0k?oc=5</t>
+        </is>
+      </c>
+      <c r="F542" t="n">
+        <v>10</v>
+      </c>
+      <c r="G542" s="2" t="n">
+        <v>46037.50020833333</v>
+      </c>
+    </row>
+    <row r="543">
+      <c r="A543" t="inlineStr">
+        <is>
+          <t>UNMAPPED_LINE</t>
+        </is>
+      </c>
+      <c r="B543" t="inlineStr">
+        <is>
+          <t>Insider Risk ("insider risk" OR "insider threat" OR "internal threat" OR "employee misconduct" OR "data exfiltration" OR "privileged access abuse" OR "malicious insider" OR "negligent insider" OR "insider attack" OR "corporate espionage" OR "information leakage" OR "unauthorised access" OR "policy violation" OR "security breach" OR "insider vulnerability")</t>
+        </is>
+      </c>
+      <c r="C543" t="inlineStr">
+        <is>
+          <t>What happens to insider risk when AI becomes a coworker - Help Net Security</t>
+        </is>
+      </c>
+      <c r="D543" t="inlineStr">
+        <is>
+          <t>Thu, 08 Jan 2026 06:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="E543" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiggFBVV95cUxPYnFBanQtWlVhbERiRUloMXd5OXlTb3k0aDBZbi1NZ1ExdnQwR1FidWhuZm9hU2hHM2tHNzc5RVpTcWdOUkZDZjgtejdXTGJ3amZJQVVvSk5sQ1RJQTFwMWp2dEJyTWtiRmtwOWtkTzB4c1NYUjYtcUh4OS02T2k1M3N3?oc=5</t>
+        </is>
+      </c>
+      <c r="F543" t="n">
+        <v>10</v>
+      </c>
+      <c r="G543" s="2" t="n">
+        <v>46030.25</v>
+      </c>
+    </row>
+    <row r="544">
+      <c r="A544" t="inlineStr">
+        <is>
+          <t>UNMAPPED_LINE</t>
+        </is>
+      </c>
+      <c r="B544" t="inlineStr">
+        <is>
+          <t>Insider Risk ("insider risk" OR "insider threat" OR "internal threat" OR "employee misconduct" OR "data exfiltration" OR "privileged access abuse" OR "malicious insider" OR "negligent insider" OR "insider attack" OR "corporate espionage" OR "information leakage" OR "unauthorised access" OR "policy violation" OR "security breach" OR "insider vulnerability")</t>
+        </is>
+      </c>
+      <c r="C544" t="inlineStr">
+        <is>
+          <t>Cyberhaven Partners with O’Reilly to Publish Insider Risk Management Guide - TipRanks</t>
+        </is>
+      </c>
+      <c r="D544" t="inlineStr">
+        <is>
+          <t>Thu, 15 Jan 2026 00:36:34 GMT</t>
+        </is>
+      </c>
+      <c r="E544" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMivgFBVV95cUxNMGVUdXoyYzYyU2ZMRHBEOEZTbTA3SnBxcGhBQzZWbGlzamVEdEpZTEtTR0dnZHY3dWJJY1Yya1h5VlJ6TXdaVGhOeExkQ3FyT251R2Nzb0dBT3QtYVllQ3NHMHR4bjFaZjZLZjQtMHBYMVJOcXdtaFNMNEVaV3VnUkdPNk9CbUJpNWNXa19UVnZVXzRzRWpWdnZxbjl6RDVTUlNoZG5Sb1BDRVNGVDdTRmNyUXZFYW12U093cWp3?oc=5</t>
+        </is>
+      </c>
+      <c r="F544" t="n">
+        <v>10</v>
+      </c>
+      <c r="G544" s="2" t="n">
+        <v>46037.02539351852</v>
+      </c>
+    </row>
+    <row r="545">
+      <c r="A545" t="inlineStr">
+        <is>
+          <t>UNMAPPED_LINE</t>
+        </is>
+      </c>
+      <c r="B545" t="inlineStr">
+        <is>
+          <t>Fraud/Scam ("fraud" OR "scam" OR "phishing" OR "identity theft" OR "account takeover" OR "payment fraud" OR "credit card fraud" OR "wire fraud" OR "business email compromise" OR "fake invoice" OR "social engineering" OR "advance fee fraud")</t>
+        </is>
+      </c>
+      <c r="C545" t="inlineStr">
+        <is>
+          <t>Romance scam victims left devastated as dating fraud surges across South Wales - Swansea Bay News</t>
+        </is>
+      </c>
+      <c r="D545" t="inlineStr">
+        <is>
+          <t>Tue, 13 Jan 2026 14:07:59 GMT</t>
+        </is>
+      </c>
+      <c r="E545" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxPMW14dmxPNDlmOFVMem9vcEI1QVNOSXpKOHZrU3RISUdWcTlTTWdwVEhkRnhrTDNPT1JSdWVLdlBTOVlKaGFtTTAxMzVQTGFTTnVWUXVyOVZnYTA4VEpmNnU1Qi1zUFItTTY5RFlDVE9uRGdOdDNzZ3I5SjY5am1FNk51WFV4WEl3Z1lENnJCTmljSUNtaUZuRm96cWVXOXVEOUpZQjNHLWJZZw?oc=5</t>
+        </is>
+      </c>
+      <c r="F545" t="n">
+        <v>10</v>
+      </c>
+      <c r="G545" s="2" t="n">
+        <v>46035.58887731482</v>
+      </c>
+    </row>
+    <row r="546">
+      <c r="A546" t="inlineStr">
+        <is>
+          <t>UNMAPPED_LINE</t>
+        </is>
+      </c>
+      <c r="B546" t="inlineStr">
+        <is>
+          <t>Fraud/Scam ("fraud" OR "scam" OR "phishing" OR "identity theft" OR "account takeover" OR "payment fraud" OR "credit card fraud" OR "wire fraud" OR "business email compromise" OR "fake invoice" OR "social engineering" OR "advance fee fraud")</t>
+        </is>
+      </c>
+      <c r="C546" t="inlineStr">
+        <is>
+          <t>Phishing Scams Exploit Browser-in-the-Browser Attacks to Steal Facebook Passwords - Infosecurity Magazine</t>
+        </is>
+      </c>
+      <c r="D546" t="inlineStr">
+        <is>
+          <t>Tue, 13 Jan 2026 14:40:00 GMT</t>
+        </is>
+      </c>
+      <c r="E546" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMif0FVX3lxTE9oSHJvcDdadDgyeUFDRjNPS2h5ZjVvcWV6SHFZWEN2Zlh4NkRLRzVjS1FoSVlCQ1RKRzU5NVVJZVhvaDBBdjE5WUE2ZGlmMEVHSnZVWlpWMjk1UENBemJ0T1pKT0FsRzBCZDdBbHhsN0tOUzJSNjZCRE1fX1IzSlU?oc=5</t>
+        </is>
+      </c>
+      <c r="F546" t="n">
+        <v>10</v>
+      </c>
+      <c r="G546" s="2" t="n">
+        <v>46035.61111111111</v>
+      </c>
+    </row>
+    <row r="547">
+      <c r="A547" t="inlineStr">
+        <is>
+          <t>UNMAPPED_LINE</t>
+        </is>
+      </c>
+      <c r="B547" t="inlineStr">
+        <is>
+          <t>Fraud/Scam ("fraud" OR "scam" OR "phishing" OR "identity theft" OR "account takeover" OR "payment fraud" OR "credit card fraud" OR "wire fraud" OR "business email compromise" OR "fake invoice" OR "social engineering" OR "advance fee fraud")</t>
+        </is>
+      </c>
+      <c r="C547" t="inlineStr">
+        <is>
+          <t>Nationwide issues warning to customers after fraud cases - London Evening Standard</t>
+        </is>
+      </c>
+      <c r="D547" t="inlineStr">
+        <is>
+          <t>Tue, 13 Jan 2026 17:49:38 GMT</t>
+        </is>
+      </c>
+      <c r="E547" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxQMzlXZ1lPNzRRSkFFeEJibkZMOTdRLVpBVmZEYVVjUTRvRERaT1RTRjV3eGxORDRTTjF2ZURSZWF0bHRpVGVFZUJja3VwMGNxUk1TMVVILVNLZG1iZ2ZoTHZEY200ZnpETkFmei1GMWFaTkpudWpyXzl5VHlhNENkdDZhOFVMTnIwTlJzRmdoYWw?oc=5</t>
+        </is>
+      </c>
+      <c r="F547" t="n">
+        <v>10</v>
+      </c>
+      <c r="G547" s="2" t="n">
+        <v>46035.74280092592</v>
+      </c>
+    </row>
+    <row r="548">
+      <c r="A548" t="inlineStr">
+        <is>
+          <t>UNMAPPED_LINE</t>
+        </is>
+      </c>
+      <c r="B548" t="inlineStr">
+        <is>
+          <t>Fraud/Scam ("fraud" OR "scam" OR "phishing" OR "identity theft" OR "account takeover" OR "payment fraud" OR "credit card fraud" OR "wire fraud" OR "business email compromise" OR "fake invoice" OR "social engineering" OR "advance fee fraud")</t>
+        </is>
+      </c>
+      <c r="C548" t="inlineStr">
+        <is>
+          <t>San Diego man pleads guilty to role in international elder fraud scam - 10News.com</t>
+        </is>
+      </c>
+      <c r="D548" t="inlineStr">
+        <is>
+          <t>Thu, 15 Jan 2026 21:08:50 GMT</t>
+        </is>
+      </c>
+      <c r="E548" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxNbXZwcEMteTZFU3hpVmlDeUdYdDVWWDY2dU1uYWxJVWVjVHh0bTRRWEhMdE9Vay1haVAzMGFaQjVUVzUyTWh5U285NXZoRzdwazlaRlNTcmg4aldZck5LZGZDWGpqSHcyVjdGVHVwQ2c4VTVZWDlDa2VHd0QxS1VJaG9tVDZZYTd0Ty1vdktJQ202dFlYZ3U2VnJ1UmN5RGtmSGNkOFNCMlZ5Qldx?oc=5</t>
+        </is>
+      </c>
+      <c r="F548" t="n">
+        <v>10</v>
+      </c>
+      <c r="G548" s="2" t="n">
+        <v>46037.88113425926</v>
+      </c>
+    </row>
+    <row r="549">
+      <c r="A549" t="inlineStr">
+        <is>
+          <t>UNMAPPED_LINE</t>
+        </is>
+      </c>
+      <c r="B549" t="inlineStr">
+        <is>
+          <t>Fraud/Scam ("fraud" OR "scam" OR "phishing" OR "identity theft" OR "account takeover" OR "payment fraud" OR "credit card fraud" OR "wire fraud" OR "business email compromise" OR "fake invoice" OR "social engineering" OR "advance fee fraud")</t>
+        </is>
+      </c>
+      <c r="C549" t="inlineStr">
+        <is>
+          <t>Behind the Top Scams Consumers Face and the Defenses That Work - PYMNTS.com</t>
+        </is>
+      </c>
+      <c r="D549" t="inlineStr">
+        <is>
+          <t>Wed, 14 Jan 2026 17:01:23 GMT</t>
+        </is>
+      </c>
+      <c r="E549" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxPa3VZUzNiank4bGNzNUpuXzZsM0VSY1ZfVUpUTlc5TV9WUXBGZ1NZWVBZb2ZlMTFtRVFqLUV0aGlRTWI1UXNsZkg2bnVtRHFTeXBiQVJybjRFaEYtazdFMXNHT2xPRERMVXdfUUhSd1BlT1hlMXlFZXlFTktPU0JjVUo2QTY3TnlYazY5VGE0UFlRY0s3bFVsMnJGQU5lenFSYUNvXzQ3cw?oc=5</t>
+        </is>
+      </c>
+      <c r="F549" t="n">
+        <v>10</v>
+      </c>
+      <c r="G549" s="2" t="n">
+        <v>46036.70929398148</v>
+      </c>
+    </row>
+    <row r="550">
+      <c r="A550" t="inlineStr">
+        <is>
+          <t>UNMAPPED_LINE</t>
+        </is>
+      </c>
+      <c r="B550" t="inlineStr">
+        <is>
+          <t>Fraud/Scam ("fraud" OR "scam" OR "phishing" OR "identity theft" OR "account takeover" OR "payment fraud" OR "credit card fraud" OR "wire fraud" OR "business email compromise" OR "fake invoice" OR "social engineering" OR "advance fee fraud")</t>
+        </is>
+      </c>
+      <c r="C550" t="inlineStr">
+        <is>
+          <t>Lifespan offers peer-to-peer program to help fraud survivors - Spectrum News</t>
+        </is>
+      </c>
+      <c r="D550" t="inlineStr">
+        <is>
+          <t>Thu, 15 Jan 2026 13:30:00 GMT</t>
+        </is>
+      </c>
+      <c r="E550" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxQMm1RMlRSTFBWeVFZR0dfZEFJNEVCWDFTNFhJS01CZTk1UmhuNUF3ZE9PazlOc1J2Znh3VmVlemZPb3psNm1xWGFwbkEzUWFDcGRYbmMtaE5nTzM2TUVLQXdkWFFhYm5DbFdKd3QyNDZqbzl5MWNqTDZMeEs0NFlURGUtUGNMV0M5b3FUZzFFbEdDdDFEN3NjTw?oc=5</t>
+        </is>
+      </c>
+      <c r="F550" t="n">
+        <v>10</v>
+      </c>
+      <c r="G550" s="2" t="n">
+        <v>46037.5625</v>
+      </c>
+    </row>
+    <row r="551">
+      <c r="A551" t="inlineStr">
+        <is>
+          <t>UNMAPPED_LINE</t>
+        </is>
+      </c>
+      <c r="B551" t="inlineStr">
+        <is>
+          <t>Fraud/Scam ("fraud" OR "scam" OR "phishing" OR "identity theft" OR "account takeover" OR "payment fraud" OR "credit card fraud" OR "wire fraud" OR "business email compromise" OR "fake invoice" OR "social engineering" OR "advance fee fraud")</t>
+        </is>
+      </c>
+      <c r="C551" t="inlineStr">
+        <is>
+          <t>Warren County leaders pointing fingers after $3 million fraud scam - WAMC</t>
+        </is>
+      </c>
+      <c r="D551" t="inlineStr">
+        <is>
+          <t>Fri, 09 Jan 2026 22:12:00 GMT</t>
+        </is>
+      </c>
+      <c r="E551" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxQcnp4ZnZjTGlLblVIckVteUZaSFdxR1JNME8tb25nMzJ5RkpRbUtPZFlqTVA5M3p1RHFjN2VBTmtVLXAzSWkwSnlWN1hoM3k0TXlOQU9zOTZRTFJnZTFYTmdVdjV5UXBwWTBWZ1NlNmU4c1pCdUZlZ3otekU5ZXRxT0E4RUxYT3Vpc0ZGTzBDM241WUNiRGM0bFJpOXZ4ZHZxdEdvT3lTc3RpWkxybTFIdUx5RkQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F551" t="n">
+        <v>10</v>
+      </c>
+      <c r="G551" s="2" t="n">
+        <v>46031.925</v>
+      </c>
+    </row>
+    <row r="552">
+      <c r="A552" t="inlineStr">
+        <is>
+          <t>UNMAPPED_LINE</t>
+        </is>
+      </c>
+      <c r="B552" t="inlineStr">
+        <is>
+          <t>Fraud/Scam ("fraud" OR "scam" OR "phishing" OR "identity theft" OR "account takeover" OR "payment fraud" OR "credit card fraud" OR "wire fraud" OR "business email compromise" OR "fake invoice" OR "social engineering" OR "advance fee fraud")</t>
+        </is>
+      </c>
+      <c r="C552" t="inlineStr">
+        <is>
+          <t>Matrimonial Scam: Man posing as doctor dupes woman of Rs 22.7 lakh - Medical Dialogues</t>
+        </is>
+      </c>
+      <c r="D552" t="inlineStr">
+        <is>
+          <t>Thu, 15 Jan 2026 12:12:51 GMT</t>
+        </is>
+      </c>
+      <c r="E552" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxQbkxWV2t6c2dSaFdMdnR0d2o2dS15NzdVVzBBR19tdHpZMW5uVUcyNWY4RWtuWEQ0M2NjMkhzejkxaGx2d2RpMzBNN1ZLOFY5YTFMQS01YV9fTnViT25mbWl5ZEo1RjkyM0VxUDRweklRYjZKLTRtWF8yS1NTdTd0d3U5VkRWeXN5WW04S05rekZnLTVWdkJYUWcxaDRqcHhQRGI4VFlhZDd0RDlNQXN5QUk3RTFBdkRBS0hv0gHAAUFVX3lxTE5WODZMQVdra1VhYUNteG02T3hieG02TXphSlQyNU9BbzBqM3czZWJHUEp3bnlhMkxvejJ2SmxWc2pvWnVOS3F3MXdGUlE0cTN0V3dla1FpeHoxQXpWYUdLTHdrRE9YYnd2OG9ia3lPdGRCaDJtcmlhMDAxOVBiRzNlNmJLc0VET1gwa2xoTUUxRWFLTlV0UUhYMldVN2d5eTNkMzlUbEVNbUdLeFhWNXlQNTJJR0UzX0dYZkJGdWFoTA?oc=5</t>
+        </is>
+      </c>
+      <c r="F552" t="n">
+        <v>10</v>
+      </c>
+      <c r="G552" s="2" t="n">
+        <v>46037.50892361111</v>
+      </c>
+    </row>
+    <row r="553">
+      <c r="A553" t="inlineStr">
+        <is>
+          <t>UNMAPPED_LINE</t>
+        </is>
+      </c>
+      <c r="B553" t="inlineStr">
+        <is>
+          <t>Fraud/Scam ("fraud" OR "scam" OR "phishing" OR "identity theft" OR "account takeover" OR "payment fraud" OR "credit card fraud" OR "wire fraud" OR "business email compromise" OR "fake invoice" OR "social engineering" OR "advance fee fraud")</t>
+        </is>
+      </c>
+      <c r="C553" t="inlineStr">
+        <is>
+          <t>A Houston woman thought she was protecting her money after receiving a fraud alert text. Instead, she lost everything. - KHOU</t>
+        </is>
+      </c>
+      <c r="D553" t="inlineStr">
+        <is>
+          <t>Wed, 14 Jan 2026 03:59:49 GMT</t>
+        </is>
+      </c>
+      <c r="E553" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMivgFBVV95cUxPOEREWGhqNjdiRFlYbVVkT3JQRGVkX09HMXJwMkJycW1sWWZ2TkFQQ2xvVTk2TDdFRjc3Q3pMMWw5enBjT2phSUp5elctMnNNV3ZudXVrTXdfdjBWLVBySVg0RUc0dmpHbHA3eEQ0NFJSZlh2RWM2R1M0RXhlYWdsRnRSMWIzOXQwQzgtNDF2UVNNQXBOd2hZU3AtdkVDVFIxQUU2WmdIdTA5UXRrSDNEWXpkOHd6cjNpSWMyU2Fn?oc=5</t>
+        </is>
+      </c>
+      <c r="F553" t="n">
+        <v>10</v>
+      </c>
+      <c r="G553" s="2" t="n">
+        <v>46036.16653935185</v>
+      </c>
+    </row>
+    <row r="554">
+      <c r="A554" t="inlineStr">
+        <is>
+          <t>UNMAPPED_LINE</t>
+        </is>
+      </c>
+      <c r="B554" t="inlineStr">
+        <is>
+          <t>Fraud/Scam ("fraud" OR "scam" OR "phishing" OR "identity theft" OR "account takeover" OR "payment fraud" OR "credit card fraud" OR "wire fraud" OR "business email compromise" OR "fake invoice" OR "social engineering" OR "advance fee fraud")</t>
+        </is>
+      </c>
+      <c r="C554" t="inlineStr">
+        <is>
+          <t>N.J. school district says $178K in taxpayer money vanished in email scam - NJ.com</t>
+        </is>
+      </c>
+      <c r="D554" t="inlineStr">
+        <is>
+          <t>Thu, 15 Jan 2026 16:17:00 GMT</t>
+        </is>
+      </c>
+      <c r="E554" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxQb05tZGhRb0N0amxneUcwM3JNYkhOWXVvWHlrOG1iMVVabFBCQXlnV0xLbDlIVlhlQWF1YzJqQm0zRHZIbXpvNW1jVDdmN3ZBMnRTTVR6ZDZ2MGtYSWVOaVJMUjZneW1zUHhxbkh0MDRia1UzakFHT2xDdGdGakRTUzkzbTNqU2lyam91WkY3RDltNXZ2NXhTVzBmWHVKUFJPT2pyZWc5XzA3YkVUbmpNTw?oc=5</t>
+        </is>
+      </c>
+      <c r="F554" t="n">
+        <v>10</v>
+      </c>
+      <c r="G554" s="2" t="n">
+        <v>46037.67847222222</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/topic_feeds.xlsx
+++ b/data/topic_feeds.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F162"/>
+  <dimension ref="A1:F170"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5290,6 +5290,246 @@
         <v>7</v>
       </c>
     </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>Current_Affairs</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>(geopolitics OR migration OR economy OR conflict OR legislation OR terrorism OR disinformation OR misinformation OR government OR policy OR regulation) AND (briefing OR analysis OR update OR report)</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>Situation Report On The 24-Hour Economy Market Project - Modern Ghana</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>Fri, 16 Jan 2026 10:59:00 GMT</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxOSzRyQ0g0SU1CckxmZjJFZkwwSG1DOURtTlhPWC10ZUJkajNsbk41dGQ5RVhTeFhwZXdlWEx5WFNoSTZJOGxYN2dabml3ZHhFSDhMcTRGN2ZqT2ttbjE1WTFld0N6ajhUQjF1SldJOHpFYWVqekdueGpLNnVBRGVKTmVBY0ZVb0hZWEVXLTJmTGhGSFh4Q1NN0gGWAUFVX3lxTFB5N2VIS1hwSnM2SG9hNmlNWmVYU3pVbTZIdk01eEdvdEtUODhNRUc3WVRNNTB5T0VnaXU1amVVV0xiOEhkWThpcXU2cjVQSlNCZTBGbXQ3MDNiaEJLYlMtY21mNlg2LXdycXNmc3RZY2RXMndESXB4b3dwTkVDLWxBMU5MR05TRll4azBwOXpRR2RxMnZGUQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F163" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>Supply_Chain</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>UAE and Nigeria agree trade deal - Logistics Manager</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>Fri, 16 Jan 2026 12:11:44 GMT</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMidEFVX3lxTE93MWM3bGhGYWxna2RUaDBVMkJJYUZNcE40WDlGc1BNSXZGaTY0ZWZ6VFg4cVFieVFMdlljUGxQZ3NXQ2hDNVpSM3hvOEw5aXJjSGxscFFQdG40S0JwZjVVbFI3Y1lZeW9pZE9OMWFCMmN0ZDBz?oc=5</t>
+        </is>
+      </c>
+      <c r="F164" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>Supply_Chain</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>Global report shows rapid growth in hourly matching renewable electricity tariffs - International Water Power</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>Fri, 16 Jan 2026 12:21:01 GMT</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxQY2tGaGdaY3RkM3p5Z3gyVy1BZnNQUmkyd0JwRmxUUEN5bEVKS2w1Zk5YNi13dF9weDZGcGZ5OVZQNEk0WkRacWluQ04yS2cyaElmaklUQ04yQnc0alJ4X3ZJaHQ2YWZieDV5ZmpRdXA5TmR4bEp0TmRhWnBKMnE5bXoxTktKRTItdFMxempQaWNMWm0tS0tyMEUxNGlZMEF0bVF4Zk9EaFhET3hWdzNkc3NxYmpySFFpU2JuVlNoaw?oc=5</t>
+        </is>
+      </c>
+      <c r="F165" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>Protest</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally)</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>Police powers: Protests - The House of Commons Library</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>Thu, 08 Jan 2026 08:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMickFVX3lxTE9xMlE1N0RZekhySENxSkFWejdESXFPS0czV0p1LVZBbllxR2ZIaUJVM255SEpnREpvZWxoaEpnUHAtN0JCdzBvWjYtNnlKUnRmd29JbmxIU3N4NDV2bVQ2OUJHLTkwb3h0UGVrTjhydDYwdw?oc=5</t>
+        </is>
+      </c>
+      <c r="F166" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>Protest</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally)</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>World to unite in blue to honour fallen police officers on 7 March - Interpol</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>Wed, 07 Jan 2026 13:34:35 GMT</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxPRl81VVRsZGM1bThTOC1TdVZnWnRlRDBuZUNDYlBKV21oQm9tZF9rU1dJYzhFeUIyQkFJVmphQ1dtUlh6dzBlNDdQSFktSzZKQ2ZRSzVUZzZxa2FVYWFyTExSWF9fTXd4VUpwLUFZQmUwdEd0VzVLbG02MzdDV3hqTXB2aFc4NTZScUtUODhudVBHLW1ZZUNGNFdDRGp2a3NVdDhjMGdTZ2N3LWc3S2xjVl9pODhoNlBM?oc=5</t>
+        </is>
+      </c>
+      <c r="F167" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>Protest</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally)</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>Exiled prince says thousands of police, troops stayed home amid protests - ایران اینترنشنال</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>Tue, 13 Jan 2026 09:31:30 GMT</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiUkFVX3lxTE9nQnVLVllkQzFZUXRSOGFfbTdyTXhYYms1VmNjRXdjLVA5S0Q2ODhvX2Znc0xiaUpGY29VYjdQVXFYVVhpTWlCdE5vRlgtRng1OWc?oc=5</t>
+        </is>
+      </c>
+      <c r="F168" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>Protest</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally)</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>Police remind people of e-scooter and e-bike laws after more seized - Fenland Citizen</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>Wed, 14 Jan 2026 06:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxQeXpKXzhIT3JQUjBGQlB5ajdXTU9JcDBNc016NGl3ZjdMdzdJWkNMWFdHdmVJM05fOHg4dWMzc2JhdE12OWFxU2xhQTBZcFM4b21QU2djaWtncEhCUGFzeVB2TmlUcWZ0RnB5alhKRnI1OXFITzJYZmVibzF3ckJpbTAxRWs1M3p0N0N2N2ptOEVpcXR1R29KVmJjMHo1d1ZjSGE1b2wzNG1GU3M?oc=5</t>
+        </is>
+      </c>
+      <c r="F169" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>Insider_Risk</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>("insider risk" OR "insider threat" OR "internal threat" OR "employee misconduct" OR "data exfiltration" OR "privileged access abuse" OR "malicious insider" OR "negligent insider" OR "insider attack" OR "corporate espionage" OR "information leakage" OR "unauthorised access" OR "policy violation" OR "security breach" OR "insider vulnerability")</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>OpenAI fixes weakness that could have enabled server-side data exfiltration - SC Media</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>Thu, 08 Jan 2026 20:53:48 GMT</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxOaVdGMEhmdVBESFZoZmNKLTI1Qklkcmp3cXYxVWEwRFYyaG1hRlc2ZktfS00yb1RQZDlnQ0QwYmZUenYzaE5QbzdiY0hDZUZTcndoTUkzMFQxU2p1eHdUeUNuVzh2LWpWcER6SVdwdkgtT29jUzVwYkZiZ3VFN1lnUi1oVFdwRmN6T3ZMT3VDMjJ2UTNTR2ZxYTFFcWNFUE1xTENIZzB1NA?oc=5</t>
+        </is>
+      </c>
+      <c r="F170" t="n">
+        <v>10</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/topic_feeds.xlsx
+++ b/data/topic_feeds.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F170"/>
+  <dimension ref="A1:F181"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4477,7 +4477,7 @@
         </is>
       </c>
       <c r="F135" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="136">
@@ -4507,7 +4507,7 @@
         </is>
       </c>
       <c r="F136" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="137">
@@ -4537,7 +4537,7 @@
         </is>
       </c>
       <c r="F137" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="138">
@@ -4567,7 +4567,7 @@
         </is>
       </c>
       <c r="F138" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="139">
@@ -4597,7 +4597,7 @@
         </is>
       </c>
       <c r="F139" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="140">
@@ -4627,7 +4627,7 @@
         </is>
       </c>
       <c r="F140" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="141">
@@ -4657,7 +4657,7 @@
         </is>
       </c>
       <c r="F141" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="142">
@@ -4687,7 +4687,7 @@
         </is>
       </c>
       <c r="F142" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="143">
@@ -4717,7 +4717,7 @@
         </is>
       </c>
       <c r="F143" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="144">
@@ -4747,7 +4747,7 @@
         </is>
       </c>
       <c r="F144" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="145">
@@ -4777,7 +4777,7 @@
         </is>
       </c>
       <c r="F145" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="146">
@@ -4807,7 +4807,7 @@
         </is>
       </c>
       <c r="F146" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="147">
@@ -4837,7 +4837,7 @@
         </is>
       </c>
       <c r="F147" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="148">
@@ -4867,7 +4867,7 @@
         </is>
       </c>
       <c r="F148" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="149">
@@ -4897,7 +4897,7 @@
         </is>
       </c>
       <c r="F149" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="150">
@@ -4927,7 +4927,7 @@
         </is>
       </c>
       <c r="F150" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="151">
@@ -4957,7 +4957,7 @@
         </is>
       </c>
       <c r="F151" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="152">
@@ -4987,7 +4987,7 @@
         </is>
       </c>
       <c r="F152" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="153">
@@ -5017,7 +5017,7 @@
         </is>
       </c>
       <c r="F153" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="154">
@@ -5047,7 +5047,7 @@
         </is>
       </c>
       <c r="F154" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="155">
@@ -5077,7 +5077,7 @@
         </is>
       </c>
       <c r="F155" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="156">
@@ -5107,7 +5107,7 @@
         </is>
       </c>
       <c r="F156" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="157">
@@ -5137,7 +5137,7 @@
         </is>
       </c>
       <c r="F157" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="158">
@@ -5167,7 +5167,7 @@
         </is>
       </c>
       <c r="F158" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="159">
@@ -5197,7 +5197,7 @@
         </is>
       </c>
       <c r="F159" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="160">
@@ -5227,7 +5227,7 @@
         </is>
       </c>
       <c r="F160" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="161">
@@ -5257,7 +5257,7 @@
         </is>
       </c>
       <c r="F161" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="162">
@@ -5287,7 +5287,7 @@
         </is>
       </c>
       <c r="F162" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="163">
@@ -5527,6 +5527,336 @@
         </is>
       </c>
       <c r="F170" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>Current_Affairs</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>(geopolitics OR migration OR economy OR conflict OR legislation OR terrorism OR disinformation OR misinformation OR government OR policy OR regulation) AND (briefing OR analysis OR update OR report)</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>Financial Services Regulation Committee publishes private markets report - UK Parliament</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>Fri, 09 Jan 2026 00:01:49 GMT</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiggJBVV95cUxPdlBRYmxCRnRjTkJLZnFWV0RrdGQza2k3LUpSb1JkTFhBT3BPb1VQYVFvd00wNS1pZWtXNTU5NkcxeDJVQ3RKRmRldnByZEpjRjlkeTIxZ0dBVWc0VG9UeDVrOEV4QkttU0VXVkJ2eFJET056VjBEblBLWVJ0dnZiblBjb1pjRV9kaFR2dWFlcnAzR0MtZkJ3REw2TjRKZE5YMFpHaHFTVTlPNm84QkNnMEtFU0JZNWFvdXF6TkJGbDQ2TUVaNzhTYTl1NTdlSHRFcm53bDU4Q3czY3Q5NjhhVjhoMlV6dFNoMllJSkhmNTJpSmVCRk12RlJZSWJEOExjcFE?oc=5</t>
+        </is>
+      </c>
+      <c r="F171" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>Supply_Chain</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>US says it reached deal with Taiwan to lower tariffs and boost investments - The Guardian</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>Fri, 16 Jan 2026 02:53:00 GMT</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMieEFVX3lxTFAyLWwtTlhtOHc0NGZ0YTNuTW1uX0FEZ2M5WnUteGswaXEzdTRyUVo1TDJabmdJcHoxNHBLQmxDM1FRQXdocnVHa3piaXQwWEhwNzNhUU5FV0ROT1Q0M3FCeTgwYlROMzZWTmN6bDk1MlE5YzdNTnVuWA?oc=5</t>
+        </is>
+      </c>
+      <c r="F172" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>Supply_Chain</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>Germany launches €3bn EV subsidy programme - AirQualityNews</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>Fri, 16 Jan 2026 12:29:48 GMT</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxOZGw0ZHU2Nm5WWG83VHVzeHRtakZlTnVuMnMwQTFzeFVVTkNhSFRBSkM5RzdrWnI1aFN1TlZxVVdrWmp2aExlbWdyeUM3eHdkcDBfdUhzNjhBX3BKcDFrd2t4eVpLNkE0ZVhJb0pPODNWQm9kdHRWMWJBWXBkaGR4TW5nRE9zcFYxYjZuXzNLcTg3dDZ5aHRReA?oc=5</t>
+        </is>
+      </c>
+      <c r="F173" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>Supply_Chain</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>Electric Power for Sustainable Handling - Logistics Business</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>Fri, 16 Jan 2026 12:33:15 GMT</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxPcXJMS3N2TnppWl9BcDJ0SVViUFhYb3NwaUxPTnV1QWlEbU0wOVhLdjJqazRqemZhUHhLTjc3dEZNYnBueHRjRXB2WmRmVVpRVW1ZeXZaWmJReGhNTWdfZFlmbFNhTS13azY4SmxDSENqUDJWM0t5ZERwWUt1bFl6MndMZEZ4bzAzWFliQjY2YXlJb0RVcTQ1OUFQV2R0TWNpTk5DanZ0MjF5WWROZ0k4MUtsU2F1QjY5R1E?oc=5</t>
+        </is>
+      </c>
+      <c r="F174" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>Supply_Chain</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>Two men jailed for series of burglaries after entering UK through Essex port - Colchester Gazette</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>Fri, 16 Jan 2026 11:35:18 GMT</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxNOUtOSTFaWHB5Ny1SOS04NXNDcnVlSmtyVm1NeGEtSWtFZ1c1VEVXdWtweGh6X2JHZmtEX3ZIY1k1djZiTmd4RkIxUk1HQXZ6LXBWcFhmdHV0N1NQWVIwczJNZFFwX2FhUGg1WkN1c2FtblZQaFYtM3NkLW9tT003SVdvZWtLbzEwMXhyaTdvVkxDWHVpTVM0QUJR?oc=5</t>
+        </is>
+      </c>
+      <c r="F175" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>Supply_Chain</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>Morrison infrastructure fund invests in US pharmacy logistics platform Fillex - IPE Real Assets</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>Fri, 16 Jan 2026 12:46:56 GMT</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxQUUhLNFp3cEVJUjlrVF9FVzhUbDhHSlBsT2Y5aF8zSXFDRnN6WHBXYWIzYkg4NE80eUhJbk4zWXo5OVpVZHNzaVlFOTNUckFPUmJYM3lHT09Sc04xRnVUdXVZUEotalVDT0lFSGUwLWhYeEhoLW9vYUFja0F6TDZrSUJsUm0yMU85WVFwWmVDdzVsVjRXMk84WjZPOGp6QklLZlF1VnZ5bTdlWmczZ2hqWGljek5fXzRmakFPR3Z3RW44cG1i?oc=5</t>
+        </is>
+      </c>
+      <c r="F176" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>Supply_Chain</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>Marina Port Valencia Targets LEED Platinum - Yachting Pages</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>Fri, 16 Jan 2026 11:32:14 GMT</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxPZlZVLTZfaTA0U1ZyMlNRWFlTOExXVWdwalAxQmozOV9uOWxlZ2hGbmg1UHJYQ0ZGZDlvYXZnazg0V0MwUC0yaW9QcTVFaWdRbHlVdVEzdWF0aWN5UDdFYnBlTkRubnB3WVhVMDR2aC1Zejc5VlI1Ni1kUXlPakNJYnFkbnBseS1TZlc3RWhTRUs?oc=5</t>
+        </is>
+      </c>
+      <c r="F177" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>Supply_Chain</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>Drug gang who operated across Ellesmere Port and Chester ordered to pay back £1.5m - Wirral Globe</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>Fri, 16 Jan 2026 11:42:28 GMT</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMilgFBVV95cUxPYVNrM2F4M0d0SjJaTV9FLWhvOTRCb1lXbWtCN2hzWldtbFhOR1JuMDFrR0xIRy1Ga0EyOThiZV95dTNScDZrbkFrZ1lHUE52cGgtWnZMeFdyMTg0Y081eXdvY2hQbjBoTC1GaUQyUTE0UUEtTklDWFdINkJaUmVZU1BDVzQwdTJZWWJ2OU1XemlQOF9tUnc?oc=5</t>
+        </is>
+      </c>
+      <c r="F178" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>EU allocates $356 million for AI and digital technologies - Digital Watch Observatory</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>Fri, 16 Jan 2026 12:25:17 GMT</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiekFVX3lxTFBWZ2U0WHRHdzF6TWV6bktxZlVEdXRhSnp5cHdvc1VMdlE4MmJ2NzhIcnRoWmRob2dGaGpuM1Q5VEVIWnJTNFE5YndrVkRSNWp6UUR0TUltNTJPT1dYeGQ5VVluaWp3cnBSSDNNeVgxWVB5TFgzSmZDMXlB?oc=5</t>
+        </is>
+      </c>
+      <c r="F179" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>TCS and AMD Announce Strategic Collaboration to Drive AI Adoption at Scale - Tata Consultancy Services</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>Fri, 16 Jan 2026 05:07:48 GMT</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxPMEFIX3RmLUYwclFIMXBMX1UtVHJ4eDVJZjkwekw0ZDNlNlI5THhTRlJIVWpyeXV0T3otNDZwcmlyNF9RSHhxbEw3Q0ZHeTZINWRZUjZ4Yy1rRGlhanFMMEVOYU1MaFRocElkQlUtTGtNcUc1amYxZ202cHZzdEVFdHM5WG5IYm85TFRTaTMxWjZyMTM3YWZBNEVVZVNoTGs5a3lnaEwxN1g2djFURmZBV3RJYnJPLUhNWWc?oc=5</t>
+        </is>
+      </c>
+      <c r="F180" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>In a shift from AI hype to AI realism, organizations are increasing their AI investmentswith a focus on long-term value - Capgemini</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>Fri, 16 Jan 2026 12:47:02 GMT</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMigAJBVV95cUxNdS1OX2JHSElodE13ZE9WVmtTVXhjUXZwU1I0ZFFPaHpla0EzSHR2U2ZRek9DR3BFX0gtOExSYmQ0UkRDaGJEYlMxX1luVTItNVZSbjBnRXFjb2dsNWNndjdjS2k0Z2hrOU9qR0t6SWpwQkJaN1hyVjN0bE9POUVnSHU3RWVuOE1ONENYU1FxTUotZ2lkc3VxR1ZPLVFpOVl0eUFFM3lWRlV1cmg5VlBVVkZ6czQ3b01FWk1vc01WTk1OVmFBMW5jR3l4WnBVUWQyWWFsLS1FOFpDT2JRV08yZWpPaUg5akRKTUdNbzM4cEJuZENCcmtuZm1rYnlWUXY5?oc=5</t>
+        </is>
+      </c>
+      <c r="F181" t="n">
         <v>10</v>
       </c>
     </row>

--- a/data/topic_feeds.xlsx
+++ b/data/topic_feeds.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F181"/>
+  <dimension ref="A1:F273"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -487,7 +487,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="3">
@@ -517,7 +517,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4">
@@ -547,7 +547,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5">
@@ -577,7 +577,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6">
@@ -593,21 +593,21 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Immediate response to the Scottish Budget and Spending Review - IFS | Institute for Fiscal Studies</t>
+          <t>Fuelling the Future: How Business, Finance and Policy can Accelerate the Clean Fuels Market - The World Economic Forum</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Tue, 13 Jan 2026 17:31:02 GMT</t>
+          <t>Thu, 15 Jan 2026 08:20:35 GMT</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiigFBVV95cUxNNU9INmF5dGpwUXpyTFkxdXMtOExIdldQTlVpTGxCN1dSNnkwZEtBcFVJMm83b2xSbDlDMnQzM25FWXB2SmpKY2gxLTllQ0gzMmxvNExzQVg3azJmRnVESHVqRGFfM2ZRZmtITlVuN0k0MlBlWmtrRVA1bTNudnI3MUNmb19RamVUWWc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxNU3VlaFpzWGpMT1gwdTZGdDJEcHJ6dnI4eTBjWlJkMmhraFUtNWswRy0tci1rcjZobHBiVF90SUVUX2JkaW1SbWIwQ0xrVm1uY2ZEbmJaYU1OajhUblJTS0VEWXFYYUtKYVNHakpVRjFLdWU3bjRhT0ZxMG9tcm9oZUtZN1phSUhIRG5FMmdxbXZkZlhuNDJOMkliZ1NCVzlIUkxJQ0ZfVkkwenZlSHZ4dU4xd3NOSGhUN1hSeU5YaVBKcVp4VEE?oc=5</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="7">
@@ -623,21 +623,21 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Fuelling the Future: How Business, Finance and Policy can Accelerate the Clean Fuels Market - The World Economic Forum</t>
+          <t>Frontex report: What the drop in migration figures does not tell us - Table.Briefings</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Thu, 15 Jan 2026 08:20:35 GMT</t>
+          <t>Fri, 16 Jan 2026 04:37:33 GMT</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxNU3VlaFpzWGpMT1gwdTZGdDJEcHJ6dnI4eTBjWlJkMmhraFUtNWswRy0tci1rcjZobHBiVF90SUVUX2JkaW1SbWIwQ0xrVm1uY2ZEbmJaYU1OajhUblJTS0VEWXFYYUtKYVNHakpVRjFLdWU3bjRhT0ZxMG9tcm9oZUtZN1phSUhIRG5FMmdxbXZkZlhuNDJOMkliZ1NCVzlIUkxJQ0ZfVkkwenZlSHZ4dU4xd3NOSGhUN1hSeU5YaVBKcVp4VEE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxPamx2VmpGdEpYSHdmVDlwQjQtdktvTmp3a3Yxb3d6aW90ckQwVHJINGF0cUNkUjNoMlNOMTBEWmlxSlZ3X3phODRZQjMyaVJyaUtEOEl3czFZQTF6d3g4VHB5NC1kZzhERFBfV3VvU05wM0NNOC0wbzdhdVU4a01qa3pIWDlwNTM3N3lCRzdLblM5ekpkQ1dXODkwMFZVWGI3TE1fRllqWQ?oc=5</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8">
@@ -653,21 +653,21 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Frontex report: What the drop in migration figures does not tell us - Table.Briefings</t>
+          <t>Gutting the Employment Rights Bill saved businesses billions, government analysis claims - Institute of Employment Rights</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Fri, 16 Jan 2026 04:37:33 GMT</t>
+          <t>Wed, 14 Jan 2026 12:13:21 GMT</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxPamx2VmpGdEpYSHdmVDlwQjQtdktvTmp3a3Yxb3d6aW90ckQwVHJINGF0cUNkUjNoMlNOMTBEWmlxSlZ3X3phODRZQjMyaVJyaUtEOEl3czFZQTF6d3g4VHB5NC1kZzhERFBfV3VvU05wM0NNOC0wbzdhdVU4a01qa3pIWDlwNTM3N3lCRzdLblM5ekpkQ1dXODkwMFZVWGI3TE1fRllqWQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxPcHhuVTlwLUl5RnlRTzRaVjU4VVIwMDF3ZEI1V0FFYnZ0TzZNR2R4Vml1ZW4yZ1AzRzFoXzM4dXlsMEZkQVNRTUhrR3ZiQ0JGYWlmNU1XZWZxTzVnNmVjYVVraVZJV013eFNWNUlWcEZxeFRRX2RTbFI0ZWs5NjNxQ1VoWkRNWUVBSFF3cC0yWGxnRGtwUlIwSzh3enJIZ2RFZTFuOFBaNGE0TkdMTFdkaGllZXZtT1U?oc=5</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9">
@@ -683,21 +683,21 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Gutting the Employment Rights Bill saved businesses billions, government analysis claims - Institute of Employment Rights</t>
+          <t>ACAPS Briefing Note: Syria - Displacement resulting from conflict escalation in Aleppo (15 January 2026) - ReliefWeb</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Wed, 14 Jan 2026 12:13:21 GMT</t>
+          <t>Thu, 15 Jan 2026 16:33:10 GMT</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxPcHhuVTlwLUl5RnlRTzRaVjU4VVIwMDF3ZEI1V0FFYnZ0TzZNR2R4Vml1ZW4yZ1AzRzFoXzM4dXlsMEZkQVNRTUhrR3ZiQ0JGYWlmNU1XZWZxTzVnNmVjYVVraVZJV013eFNWNUlWcEZxeFRRX2RTbFI0ZWs5NjNxQ1VoWkRNWUVBSFF3cC0yWGxnRGtwUlIwSzh3enJIZ2RFZTFuOFBaNGE0TkdMTFdkaGllZXZtT1U?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi2AFBVV95cUxQV1VvUXo4ODVVRTVOQmxqYWs4Y2NCck1vT1RqdV9VWldSaDVBRUdySmZkdkhMOE5MeHVvalhkZWFJNjIzSTFYdnlrZDM2RE9jVm1zZlJld2doLUZjOFVvR1loeWZ4TndqQ1lUMG8xMHk1ZWJSMWxzNU9nS29Yb1NCNFNNc2JRT1VLdnFEMHZRZTlvanR4Y0trMmZZTklZWHdtLVIzM0RBU2lCWlhwVVEyMUZhZ1NxQk1vUkR1RUREUnhLZk13Z3h0WGlldzR0ODJYYThtX0RDUHk?oc=5</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="10">
@@ -713,21 +713,21 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>ACAPS Briefing Note: Syria - Displacement resulting from conflict escalation in Aleppo (15 January 2026) - ReliefWeb</t>
+          <t>China leads global surge in digital-economy patents in 2024, CNIPA report says - MLex</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Thu, 15 Jan 2026 16:33:10 GMT</t>
+          <t>Fri, 16 Jan 2026 08:27:00 GMT</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi2AFBVV95cUxQV1VvUXo4ODVVRTVOQmxqYWs4Y2NCck1vT1RqdV9VWldSaDVBRUdySmZkdkhMOE5MeHVvalhkZWFJNjIzSTFYdnlrZDM2RE9jVm1zZlJld2doLUZjOFVvR1loeWZ4TndqQ1lUMG8xMHk1ZWJSMWxzNU9nS29Yb1NCNFNNc2JRT1VLdnFEMHZRZTlvanR4Y0trMmZZTklZWHdtLVIzM0RBU2lCWlhwVVEyMUZhZ1NxQk1vUkR1RUREUnhLZk13Z3h0WGlldzR0ODJYYThtX0RDUHk?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxQWllIbE1jbjU1YzI1UFJxWnplazRGVVVrcExjNEtlLTFBQ1JrZUdCMUpsdUJiTFVnR3o3bVVNbmNmN3EwZmtnSEVsaTVMTnFDcmVydTk0V0tZVDFCMmZYcFNSV09nc3Ywakl4bnZSYmV6RENyZzBYX2llQU4tSTZJbDE0c1lBZ0NkZlYtYUZxMDNVTmVyYWM1YXFHTjJ2MXcxRnJ6c1MySGVrZzR4SXRTWjVkdUl0d9IBWkFVX3lxTE8yUy1fY0pxaTJaLS1EdkswdHNKYXRjVF9hNnY4YWFOeVlRbmdtMEZ6SWZNcWhHMUFDRlNYcDRMQkwxWGZxTm41eE9BLTRnai14OXBNeUR2dDlOUQ?oc=5</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="11">
@@ -743,21 +743,21 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>China leads global surge in digital-economy patents in 2024, CNIPA report says - MLex</t>
+          <t>World Economic Forum - The World Economic Forum</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Fri, 16 Jan 2026 08:27:00 GMT</t>
+          <t>Wed, 14 Jan 2026 12:28:10 GMT</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxQWllIbE1jbjU1YzI1UFJxWnplazRGVVVrcExjNEtlLTFBQ1JrZUdCMUpsdUJiTFVnR3o3bVVNbmNmN3EwZmtnSEVsaTVMTnFDcmVydTk0V0tZVDFCMmZYcFNSV09nc3Ywakl4bnZSYmV6RENyZzBYX2llQU4tSTZJbDE0c1lBZ0NkZlYtYUZxMDNVTmVyYWM1YXFHTjJ2MXcxRnJ6c1MySGVrZzR4SXRTWjVkdUl0d9IBWkFVX3lxTE8yUy1fY0pxaTJaLS1EdkswdHNKYXRjVF9hNnY4YWFOeVlRbmdtMEZ6SWZNcWhHMUFDRlNYcDRMQkwxWGZxTm41eE9BLTRnai14OXBNeUR2dDlOUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMieEFVX3lxTE9vaHVWN0hydDZzb3NKMS11SkZCYllmODJVbmdHckxncURRM3d2RUNlQzBYX0NjUVFOS0xmWU9HWGdsdXg5b2pzdG9LOUYtLWViTDhlNFpLa0tlNFdVOUlJNHNwV01VNkZEMTJHbEw2NkMtcVk4RlBReA?oc=5</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="12">
@@ -773,21 +773,21 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Akin Space Law, Regulation and Policy Update | January 12, 2026 - akingump.com</t>
+          <t>Mozambique Conflict Monitor Update: 14 January 2026 - ReliefWeb</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Mon, 12 Jan 2026 20:00:41 GMT</t>
+          <t>Thu, 15 Jan 2026 02:23:04 GMT</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxPQmhESGdiUEQ0dlZsUDVJdk1zYUl6V1BMOW55bEpac2lKN1Rwc1o3MWZ6ZU1pSGtpVm9YS0NYUFVLMkJvWl9mYUdJOVIteWN6MF9mUXZHTzRDUHc4NGRzYS1ZWXFHRXhwVVYzdmtUWHVQMkp4Ri1TMGFGLVZSSUs2TU9Ed05oRWpOencyMEdnaFp2YkpJYVVKSGYzcU5RdDNzN0FNVjJIOGRMdWhSTzNkVA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilAFBVV95cUxObVhmdzJBY3J0UjdPZWVXaFFhNjNGQ3k2T0pRV3BUdXVTTlZTNTR5VGJKYWVmZ2l2UzJaeklYUGM4eE5xeUJtRllkQUtOZnU2bXlNLU5GN0EzLTBtTnU3d0xZZG9FM2dGSUx5bHR1X3JwSjRIby1Nb25ZRHFhSzlYYm9IVG9pQXpldlpvVzZ6U1pxTVNa?oc=5</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="13">
@@ -803,21 +803,21 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>New report calls for Circular Economy Act to toughen chemical policy and avoid future public health crisis - Zero Waste Europe</t>
+          <t>Mexico market intelligence report, produced in partnership with Gamingsoft - igamingbusiness.com</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Tue, 13 Jan 2026 23:02:01 GMT</t>
+          <t>Thu, 15 Jan 2026 17:05:33 GMT</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi4gFBVV95cUxPRFRETldnR1V3SXNFMGY4eUdPTWdZMFA5bzhKRmdCWXFYYWFDbUM5WFNVX19mMU9mcUVKTEh1c2RHM3pIdjZvQWRUV3hpY3haNHBOZFg0M0xTcDNzZjk0NVhEbC1LeG52ckxjYWpqQXNSYWdkZFNoUjUwQkczdGN3eWczdERaZHZVVGJEelNqX09TVnl5S3E3bncxTVVraVg4SUk4ZWVYelRMb2hYZk1NX2NDVnR0S25Ud25CX05DNk1UZVptbFR1OHU0NkdsVHRZODJia25ZT01RcVhuX1RpcmtB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiigFBVV95cUxNOTExckVLeU9STE0tQVQtbVBFVWktZ2N6SkVEV1QxMVFCOVZLRXdzZGJ2UzFFQThqaWJhNUU1bG1MbHgzdWc5Mm5ZVm1QVFZhZklrLWZmN2pkV09aRzBXVHp0SUVGNllnNUthS1c3WXBSbm5pN1BnUF9vRnFHeElWUmRPVElIaU9qTFE?oc=5</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="14">
@@ -833,21 +833,21 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Macroeconomic implications of immigration flows in 2025 and 2026: January 2026 update - Brookings</t>
+          <t>Anthropic Economic Index report: Economic primitives - Anthropic</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Tue, 13 Jan 2026 14:01:49 GMT</t>
+          <t>Thu, 15 Jan 2026 10:15:25 GMT</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxNWld2RXZhMVNXY2hXWjVUSmFDU3htUkJoakRnSzZJT3hWRkZCbzd0ZnZBcG43a2NCMWtpUDUtdnBfaHAzdFVaNElHXzZhcUxCMjhJR2lFN3c3NXh0Y3pDcVNScVFBNlhrU185dUtNc0hLUk1mYUxBRlRVVzNuQlVjaXpsaTdBdDJtQW5NQWprZ2t1YU1obUhBYmdjR2hIXzRIVFd6VVZsRXRVY0pwNE9xSEZGdlQ1ckFUZ01Baw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMihgFBVV95cUxONjBKV3ctWnNQbFZYMXAxalVSNllfM0VTb3U2ZmhFWEZoanFLc1FZMFY4bW1ydnViOUtTU0JjbTRBRlFidmRzUnZiTjFHNWFKMG9taDREVVJFb3FSUWNrdDY0NUVPZV9RS0RoNGlMQ1RLZk5lN0pHR3lYV21SemhZU0xaMjNDdw?oc=5</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="15">
@@ -863,21 +863,21 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>World Economic Forum - The World Economic Forum</t>
+          <t>Italy Tractor Market Research Report 2025-2030: Government Subsidies, CAP Funding, and Expanding Organic Farming Accelerate Equipment Demand - Yahoo Finance UK</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Wed, 14 Jan 2026 12:28:10 GMT</t>
+          <t>Thu, 15 Jan 2026 10:05:00 GMT</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMieEFVX3lxTE9vaHVWN0hydDZzb3NKMS11SkZCYllmODJVbmdHckxncURRM3d2RUNlQzBYX0NjUVFOS0xmWU9HWGdsdXg5b2pzdG9LOUYtLWViTDhlNFpLa0tlNFdVOUlJNHNwV01VNkZEMTJHbEw2NkMtcVk4RlBReA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijgFBVV95cUxOSnVwQjdoN3p6VnBrb25wN0dfMS0yRXM4MVZBNnBHY1VrZGdDOEhBZmlUTUpLWkVQNFpfMFBQNFAzRC1vVU51Sk1DazhkdzNiLVdOREFqVUZUdjc0bGd4ZU1VTE1nVlJtOGoySHVseFlQM3ZxUmw5aTRsbWFDeFlFQ0VoQlFXekFISVBhV0dn?oc=5</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="16">
@@ -893,261 +893,261 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Mozambique Conflict Monitor Update: 14 January 2026 - ReliefWeb</t>
+          <t>Iran Endgame? Protests, Repression, and the Trump Administration - The Washington Institute</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Thu, 15 Jan 2026 02:23:04 GMT</t>
+          <t>Wed, 14 Jan 2026 13:40:15 GMT</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilAFBVV95cUxObVhmdzJBY3J0UjdPZWVXaFFhNjNGQ3k2T0pRV3BUdXVTTlZTNTR5VGJKYWVmZ2l2UzJaeklYUGM4eE5xeUJtRllkQUtOZnU2bXlNLU5GN0EzLTBtTnU3d0xZZG9FM2dGSUx5bHR1X3JwSjRIby1Nb25ZRHFhSzlYYm9IVG9pQXpldlpvVzZ6U1pxTVNa?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxNVkJOaFZydFQ3ZTFvWFVsQ3NLWmlzTXBNRUxNc29DdUZXenFVdFQ4X1VsWUhMdlZ3dlZpRHJfYjR1RW95Nk5ZQTF1S3dXWG1OTFBxR1BiVGlIZnEweUN2M0NjSVhOa1lRckU4UlNXMVo2cHlfV1lJczkxSEJ1MzkzcXRzOUVSdDRmSnBZSzU3RkVWMkRnSVlBaFhVZU9tbVVfR19tbUxJZWtlV3VUUlE?oc=5</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Current_Affairs</t>
+          <t>Supply_Chain</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>(geopolitics OR migration OR economy OR conflict OR legislation OR terrorism OR disinformation OR misinformation OR government OR policy OR regulation) AND (briefing OR analysis OR update OR report)</t>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Mexico market intelligence report, produced in partnership with Gamingsoft - igamingbusiness.com</t>
+          <t>China and Canada announce tariffs relief after a high-stakes meeting - BBC</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Thu, 15 Jan 2026 17:05:33 GMT</t>
+          <t>Fri, 16 Jan 2026 10:41:05 GMT</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiigFBVV95cUxNOTExckVLeU9STE0tQVQtbVBFVWktZ2N6SkVEV1QxMVFCOVZLRXdzZGJ2UzFFQThqaWJhNUU1bG1MbHgzdWc5Mm5ZVm1QVFZhZklrLWZmN2pkV09aRzBXVHp0SUVGNllnNUthS1c3WXBSbm5pN1BnUF9vRnFHeElWUmRPVElIaU9qTFE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTE05OEw5WHl2amlqTE1pbXJhNmFfZlhyZ3pSQVhrc0c3aUhCNmRNQkl2TUhudS0wbXc1OW9kcVlMeDhSWWxzWk1JbktKREpmemZwUTM5a19HOUlHZ9IBX0FVX3lxTFA0YlRDSE1oRGRSSkZHa2ZmT2lvUkdKOTFGNU5qZDdoUXF1bU1ReHRwYy1iUGtxTHpIeWRjYktIU3hYWDJ0LS1BRmRGQWgtLUw3aDJuOVdMdVJ2VTB0Tmw0?oc=5</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Current_Affairs</t>
+          <t>Supply_Chain</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>(geopolitics OR migration OR economy OR conflict OR legislation OR terrorism OR disinformation OR misinformation OR government OR policy OR regulation) AND (briefing OR analysis OR update OR report)</t>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Anthropic Economic Index report: Economic primitives - Anthropic</t>
+          <t>Greenland: new shipping routes, hidden minerals – and a frontline between the US and Russia? - The Guardian</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Thu, 15 Jan 2026 10:15:25 GMT</t>
+          <t>Fri, 16 Jan 2026 02:30:00 GMT</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihgFBVV95cUxONjBKV3ctWnNQbFZYMXAxalVSNllfM0VTb3U2ZmhFWEZoanFLc1FZMFY4bW1ydnViOUtTU0JjbTRBRlFidmRzUnZiTjFHNWFKMG9taDREVVJFb3FSUWNrdDY0NUVPZV9RS0RoNGlMQ1RLZk5lN0pHR3lYV21SemhZU0xaMjNDdw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizgFBVV95cUxNZHJES1dSSjdBNnV0dVN0M2xweEJGb3FjTUpGLU11SkozNXF2eXpWT3lKUVhkckpTLUVvZUw0cFdLczA1MUpYMEloVF9LeldyeGpkbVFSb0VETDEtOExEelpISTBBZkZwTHZpOW14Zm9TTTU2dGNlbHZsb2J5THJGX1FBMWkwX1lWdWhLSkdWRk5FUGQwVEV6Y1laYTQ3U3lJMy1WQjhubVVpYjNEOGNQTXdmOWVQWjZ2WEFOV3lQcnZyWmtrbGF0UHlQSnU1QQ?oc=5</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Current_Affairs</t>
+          <t>Supply_Chain</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>(geopolitics OR migration OR economy OR conflict OR legislation OR terrorism OR disinformation OR misinformation OR government OR policy OR regulation) AND (briefing OR analysis OR update OR report)</t>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Italy Tractor Market Research Report 2025-2030: Government Subsidies, CAP Funding, and Expanding Organic Farming Accelerate Equipment Demand - Yahoo Finance UK</t>
+          <t>Discover the benefits of digitising warehouse workflows at Sustainable Supply Chain Exhibition - Logistics Manager</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Thu, 15 Jan 2026 10:05:00 GMT</t>
+          <t>Fri, 16 Jan 2026 09:00:12 GMT</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijgFBVV95cUxOSnVwQjdoN3p6VnBrb25wN0dfMS0yRXM4MVZBNnBHY1VrZGdDOEhBZmlUTUpLWkVQNFpfMFBQNFAzRC1vVU51Sk1DazhkdzNiLVdOREFqVUZUdjc0bGd4ZU1VTE1nVlJtOGoySHVseFlQM3ZxUmw5aTRsbWFDeFlFQ0VoQlFXekFISVBhV0dn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxQTE9ZYlNXaXJvS0JuUUxEM0JEcWhEbnZVOUZ2Z3QxRFAwell2akFtSm9SNFl2ZC1vY2FaUHhwQ1pIdFFlYU84aEM4WDVUSzFXTDBfVXNoNWkyY0p2bDJGRTBOQTlwaFJIQXcxS2dQZ0xSbUJWWkpZaXp0cHJtYkt6WHd4UDg3ZlkweTJIaDQtWmlqUTZROGxOTUdxOHhZNnpTTnc?oc=5</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Current_Affairs</t>
+          <t>Supply_Chain</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>(geopolitics OR migration OR economy OR conflict OR legislation OR terrorism OR disinformation OR misinformation OR government OR policy OR regulation) AND (briefing OR analysis OR update OR report)</t>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Sri Lanka: Report on conflict-related sexual violence - ohchr</t>
+          <t>This Week's Top Five Stories in Supply Chain - Supply Chain Digital Magazine</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Tue, 13 Jan 2026 11:33:08 GMT</t>
+          <t>Fri, 16 Jan 2026 11:08:53 GMT</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxOLUJPaC1ZN0hRaWRKZG1MYXhjVTFHZlp4V3hlMC0tcTM2bXVYOVBudUFtLWMtRmNvVFdyclFaTGo5eHNmblB2UGR1TUwyb0s1Z1NCMWRNQTRuWnJPNV9zOGxOVHk1aVozX2NiLUpyTzdFZE5hR2RjZzNuVkVzX1c3Nm1ETmprRVFQN1gxX2g1dDR1VU9SdHhnX2dtakhpOE5xTzVvREVB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijwFBVV95cUxNR0oyUGJOei1WTHJOcTRTbFRCV2NtRy0zSzBXR1QxTldaSXNGMzBQZVUwdTRhVFpOU1Z0S0plM0dGSndFejlrWDllVkprYTRNdE9hWTBQT1hRLVplaXlaRW42NUZuSFVld2dWNVUwbjJXMzgwQ25OVGN0Wnc2X2VNSEhJMWxOVHhLa2lGQW1KOA?oc=5</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Current_Affairs</t>
+          <t>Supply_Chain</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>(geopolitics OR migration OR economy OR conflict OR legislation OR terrorism OR disinformation OR misinformation OR government OR policy OR regulation) AND (briefing OR analysis OR update OR report)</t>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>US, for 1st time in 50 years, experienced negative net migration in 2025: Report - Yahoo News UK</t>
+          <t>Swissport partners up with Scan Global Logistics and launches its first dedicated perishables centre in the UK - Scan Global Logistics</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Tue, 13 Jan 2026 23:30:35 GMT</t>
+          <t>Fri, 16 Jan 2026 09:04:50 GMT</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMibkFVX3lxTFBiaXNoV1RjSnQzNnNuZVNXVGE3QXVnak9Sa1lCeEdRSHo2TW9JWHo0NWZ1MDAxdl9xS19ldXcxVjl0WTh1MWU2SVFkQ0VCUEJvX3FYNXlHcVFLSlMzRTk3NTdTVVprbFZHZVU0d2tn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi1gFBVV95cUxPdnFIUTRfeHdTMFkyaFM0b0RhVnQ1U2MwY1NNZjA4WXZXalJOenBPaEhydmN1Q2lOVlFCdTFvb2xBWVJrMHp3MFhfbDlZTV9Eb0FRRVRZQWRNc0M0bnNnLXVOaWktTWVqM0QwQVpsYmQxaGRLdWJkbFJUOFZBTkptVHFPcUxGR1ptRXB0UTZNaFoyd2xLb2p5U21SbVFyWEVjNkRCSzlUekl1ZjM2X2dvRUg0T2JPWDZ2ZmpxQ3otSWZQLWdEei16a2pmMGh4UXQxVUxwRzBR?oc=5</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Current_Affairs</t>
+          <t>Supply_Chain</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>(geopolitics OR migration OR economy OR conflict OR legislation OR terrorism OR disinformation OR misinformation OR government OR policy OR regulation) AND (briefing OR analysis OR update OR report)</t>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Russia Loses Venezuela, the Avocado Ally - Center for European Policy Analysis (CEPA)</t>
+          <t>Maersk resumes shipping through Red Sea after ceasefire - Financial Times</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Tue, 13 Jan 2026 14:37:35 GMT</t>
+          <t>Thu, 15 Jan 2026 12:44:08 GMT</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMic0FVX3lxTE9IS1diZnVyemFQMjJ1cHNvZGxuaFFEaWlnVGlrMnpuTG1mRl9XakItUFV4ZTlWMllXWGpGVnBncDJoS3B3bUdqbFRudFdMeUN3TE9YWkVhMWtCVWVka2V6TU1nZWUyNV9MUnlLS1JkTm9qTUE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMicEFVX3lxTE1qS042VlVfcEk2NWxqZi16cVpNVFI0NE43ZWZVTWY3R3ZORXNMd1NVOFJmdk12SUNjZ1diYkIwV1JYTWZiT29ZMW9hUmY1QWR2RkNvQ18tdElwXzhreVJocC0xUFh3WFFwbTFNM1p2SWs?oc=5</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Current_Affairs</t>
+          <t>Supply_Chain</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>(geopolitics OR migration OR economy OR conflict OR legislation OR terrorism OR disinformation OR misinformation OR government OR policy OR regulation) AND (briefing OR analysis OR update OR report)</t>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Iran Endgame? Protests, Repression, and the Trump Administration - The Washington Institute</t>
+          <t>Trump puts silver, other critical minerals tariffs on hold - ING THINK economic and financial analysis | ING Think</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Wed, 14 Jan 2026 13:40:15 GMT</t>
+          <t>Thu, 15 Jan 2026 12:38:42 GMT</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxNVkJOaFZydFQ3ZTFvWFVsQ3NLWmlzTXBNRUxNc29DdUZXenFVdFQ4X1VsWUhMdlZ3dlZpRHJfYjR1RW95Nk5ZQTF1S3dXWG1OTFBxR1BiVGlIZnEweUN2M0NjSVhOa1lRckU4UlNXMVo2cHlfV1lJczkxSEJ1MzkzcXRzOUVSdDRmSnBZSzU3RkVWMkRnSVlBaFhVZU9tbVVfR19tbUxJZWtlV3VUUlE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMic0FVX3lxTE5ESGptamE2MW53NnltOWZQREZraG9WejBfNk5uT19FMFI4NnBBSTBHRFJndEcwWTRRX01nRG1aVmt1R2VTclQ1VUtaZGNha3k5NmFZX3RUMm1CRjJEd2N6VnFTMEExUnBZQjNYUWxLMktIWHc?oc=5</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Current_Affairs</t>
+          <t>Supply_Chain</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>(geopolitics OR migration OR economy OR conflict OR legislation OR terrorism OR disinformation OR misinformation OR government OR policy OR regulation) AND (briefing OR analysis OR update OR report)</t>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Government update issued on 'dangerous dogs' breed bans like XL Bullies in UK - The Mirror</t>
+          <t>Research examines social landlords’ compliance with human rights law - Scottish Housing News</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Mon, 12 Jan 2026 05:10:00 GMT</t>
+          <t>Fri, 16 Jan 2026 09:24:06 GMT</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijwFBVV95cUxOOWNGb2k2ZGdmY29mNk4xbTJmNVYwejN0bk5neTlQTnhPUkk0UXpJTDNBZWFOZHJQYVNvMDBQOXdyY0sxT2ZRZHRrRVRZN1Z4Tzd4NXFmUjRlV3RwNkNFZTJ2X2ZEdW1OWl9TWHNxVVVSN0FkNDhHcmNfU2JQeE9fZm44ZlNsQUFkdjl2SGlrQdIBlAFBVV95cUxOODJkNlcwR3lFQnp6bTdlYTMtRTZSS3FWaWJHNjlXOFJTZ3ZZWGI0NEVPcWl2VzhkbFJvc0xteGJuZklvY0k5TllaT0IyaEFXdnJnMkd4YmhqekcwSEtOSEoxemxGbGxRZmt2Qm5BRjY0N1lwRDVtX09PQjVTUjFfVUlfbWdjLV9iY1ZLUkY4RmhwNGVR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxPTHZkdnlCNVl5aHduaFpXSnAteG5NS3V5YU9lUlBMX2FPeVBtZmpfajBVSzFveFJ4MXd6QzNhYmdhZmZ0V3VZdGF6ZFpHcEttcHlqRDNINFdFTGVvLVN2R21GdHZVWFhhUFVwblZBMU90bkZRblY2RU1wanBSVzRDQkhXa0NCcF81bFdDekdLVmYtdHRveUxIOEFrRjF2YUxoMkhMVUd0LVBnWTcxSWJqRGlB?oc=5</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="25">
@@ -1163,21 +1163,21 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>China and Canada announce tariffs relief after a high-stakes meeting - BBC</t>
+          <t>Taiwan and US seal deal to lower tariffs, boost chip investment - Al Jazeera</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Fri, 16 Jan 2026 10:41:05 GMT</t>
+          <t>Fri, 16 Jan 2026 08:53:28 GMT</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTE05OEw5WHl2amlqTE1pbXJhNmFfZlhyZ3pSQVhrc0c3aUhCNmRNQkl2TUhudS0wbXc1OW9kcVlMeDhSWWxzWk1JbktKREpmemZwUTM5a19HOUlHZ9IBX0FVX3lxTFA0YlRDSE1oRGRSSkZHa2ZmT2lvUkdKOTFGNU5qZDdoUXF1bU1ReHRwYy1iUGtxTHpIeWRjYktIU3hYWDJ0LS1BRmRGQWgtLUw3aDJuOVdMdVJ2VTB0Tmw0?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxPOUk4UC05RXpJQTk2YkxveVpBRVRGZ0h3UEI1YVFhMDRNT1pZTGZxVGs3V0hSZ2FkWGJOdk9pbFhzQzFXcFdNQUJPMW5nY1AtaWpncFR1UGFhQnRNVUJ2SThmZmtYc09PTnVRelY0d2l6ZmhDU2M4VzNOTEM5ZEMzamY1S3pzcU9XMXRDMzJHamI4akVtTVFpamc2U2M0YTl2dkVxOUN30gGrAUFVX3lxTE9XSUVIYnl3WHN5TlV0endpTUpCZHZINXVfTXJ2NkRRZlVXaUFxR1VlY0tNMnBpTnZieGVTMngxckt4cUFXZVRZZ3JKeHNpRVdPcTA5d2NpNUM4dmRfa3lJR1l3ZGdXRE1uVkRPVXdSWnhfdmN0cENhNDI1cnpzU09PRk1CdWFmMXlvZDZuS01RUkpJaDRLUS1Fd3pHVTBNcFNjc1l2dlVKWjBEZw?oc=5</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="26">
@@ -1193,21 +1193,21 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Greenland: new shipping routes, hidden minerals – and a frontline between the US and Russia? - The Guardian</t>
+          <t>How is XPO Prioritising Sustainability in Logistics? - Sustainability Magazine</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Fri, 16 Jan 2026 02:30:00 GMT</t>
+          <t>Fri, 16 Jan 2026 10:21:11 GMT</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizgFBVV95cUxNZHJES1dSSjdBNnV0dVN0M2xweEJGb3FjTUpGLU11SkozNXF2eXpWT3lKUVhkckpTLUVvZUw0cFdLczA1MUpYMEloVF9LeldyeGpkbVFSb0VETDEtOExEelpISTBBZkZwTHZpOW14Zm9TTTU2dGNlbHZsb2J5THJGX1FBMWkwX1lWdWhLSkdWRk5FUGQwVEV6Y1laYTQ3U3lJMy1WQjhubVVpYjNEOGNQTXdmOWVQWjZ2WEFOV3lQcnZyWmtrbGF0UHlQSnU1QQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiggFBVV95cUxPZjFLRDNVU0hrRXZCRzVTblNQbEQ4TWwwbzBtR2FBekJsbVdVUDN1c2hLZWZUbGZXbkxkUkd3YXNRQlBRU0NrRXczSHU3dFJWNG03eUc5ZWhvWF9YYTF2OWNWX21sN1lfa0I0bXFyYTRoRURkc2gzeUUyZFNBY2tmcmZR?oc=5</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="27">
@@ -1223,21 +1223,21 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Discover the benefits of digitising warehouse workflows at Sustainable Supply Chain Exhibition - Logistics Manager</t>
+          <t>Dun &amp; Bradstreet outlines seven key compliance trends - IT Brief UK</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Fri, 16 Jan 2026 09:00:12 GMT</t>
+          <t>Fri, 16 Jan 2026 09:00:00 GMT</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxQTE9ZYlNXaXJvS0JuUUxEM0JEcWhEbnZVOUZ2Z3QxRFAwell2akFtSm9SNFl2ZC1vY2FaUHhwQ1pIdFFlYU84aEM4WDVUSzFXTDBfVXNoNWkyY0p2bDJGRTBOQTlwaFJIQXcxS2dQZ0xSbUJWWkpZaXp0cHJtYkt6WHd4UDg3ZlkweTJIaDQtWmlqUTZROGxOTUdxOHhZNnpTTnc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMihgFBVV95cUxPMVlWR2o4QlFlZXVDakFPRUVmNGI2QmlOYnFzN2l2b3RELWpKdmhucndMS3JLMnZqOGhQenpFR3NXNU5WMm53dWxqM3NoUnJtU3pnV0JhSi1JYWxNc3Z2RDByWGVMbzA3ZkU1M3BqX0R3amlidk94a21ZdTNKR0RJNkVRdWYtZw?oc=5</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="28">
@@ -1253,21 +1253,21 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>This Week's Top Five Stories in Supply Chain - Supply Chain Digital Magazine</t>
+          <t>Athens breaks EU ranks to side with US and Saudi Arabia in green shipping row - Euractiv</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Fri, 16 Jan 2026 11:08:53 GMT</t>
+          <t>Fri, 16 Jan 2026 10:52:00 GMT</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijwFBVV95cUxNR0oyUGJOei1WTHJOcTRTbFRCV2NtRy0zSzBXR1QxTldaSXNGMzBQZVUwdTRhVFpOU1Z0S0plM0dGSndFejlrWDllVkprYTRNdE9hWTBQT1hRLVplaXlaRW42NUZuSFVld2dWNVUwbjJXMzgwQ25OVGN0Wnc2X2VNSEhJMWxOVHhLa2lGQW1KOA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxOUGlFaXNzWVhSZnd3YndBQ3Y0SmZoYkNYZEZYZTFjTC1jQVlCNU1vWjAtU3RaM3dYMWpZZHZYSGVuQ0U5Q0p1bmFGeEFBdzdIYndac1pFcHdWVHQzbFRFSW1TZ2xrcXBwWGlJd1cxaTNDdGdNbGNrT2NVa2xIVlFrMU5EbWRyWE1UOGY2UUR3REladzNQVGpNa0xtQnRoRWV5Z0dSNWJKdVNRZG9f?oc=5</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="29">
@@ -1283,21 +1283,21 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Swissport partners up with Scan Global Logistics and launches its first dedicated perishables centre in the UK - Scan Global Logistics</t>
+          <t>UBCivils benefit from Podfather logistics software - Agg-Net</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Fri, 16 Jan 2026 09:04:50 GMT</t>
+          <t>Fri, 16 Jan 2026 08:35:50 GMT</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi1gFBVV95cUxPdnFIUTRfeHdTMFkyaFM0b0RhVnQ1U2MwY1NNZjA4WXZXalJOenBPaEhydmN1Q2lOVlFCdTFvb2xBWVJrMHp3MFhfbDlZTV9Eb0FRRVRZQWRNc0M0bnNnLXVOaWktTWVqM0QwQVpsYmQxaGRLdWJkbFJUOFZBTkptVHFPcUxGR1ptRXB0UTZNaFoyd2xLb2p5U21SbVFyWEVjNkRCSzlUekl1ZjM2X2dvRUg0T2JPWDZ2ZmpxQ3otSWZQLWdEei16a2pmMGh4UXQxVUxwRzBR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMihgFBVV95cUxOQm5QQXFNVnVrSnpDZU1lZERZWEk5X0VSSDN5a3FTMmNQemhQblVqRm1kS1BHWGlJMjJVWWxZTjdwLVNKQ2lkZUdRLU5PLXRrMWV1NDg0ZUI0Y1d3X2ppNGhjalktM01LdTVxeEt2NFgxVFdtbUE3U1lxNk1yRGZ4N2pxODZWQQ?oc=5</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="30">
@@ -1313,21 +1313,21 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Maersk resumes shipping through Red Sea after ceasefire - Financial Times</t>
+          <t>What are tariffs, how do they work and why is Trump using them? - BBC</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Thu, 15 Jan 2026 12:44:08 GMT</t>
+          <t>Wed, 14 Jan 2026 16:32:50 GMT</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMicEFVX3lxTE1qS042VlVfcEk2NWxqZi16cVpNVFI0NE43ZWZVTWY3R3ZORXNMd1NVOFJmdk12SUNjZ1diYkIwV1JYTWZiT29ZMW9hUmY1QWR2RkNvQ18tdElwXzhreVJocC0xUFh3WFFwbTFNM1p2SWs?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTFBweHdveUp5S2F0aGJwSEs2U2lOMkF6NzRNZTd3bEJUdTQwVjhRX0pjZmFzZ25hRzk4MHE0WW9KVkEtUjIxRUNWbXRzX3pmd1A5UWhyaE5Ja1ZWd9IBX0FVX3lxTE82Y0Q0dVVkNUhXb1o4Tkt6V1AycjA1dmkzbUs3d3JydDktMVNrSnNsNDI1Zk9BdmpMc1BQbGJneThSUDBmUkdUdFhDVTZaTTRGaGlwdDhnR3NPeXhDYW9F?oc=5</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="31">
@@ -1343,21 +1343,21 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Trump puts silver, other critical minerals tariffs on hold - ING THINK economic and financial analysis | ING Think</t>
+          <t>White House sets tariffs to take 25% cut of Nvidia and AMD sales in China - Financial Times</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Thu, 15 Jan 2026 12:38:42 GMT</t>
+          <t>Wed, 14 Jan 2026 23:54:51 GMT</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMic0FVX3lxTE5ESGptamE2MW53NnltOWZQREZraG9WejBfNk5uT19FMFI4NnBBSTBHRFJndEcwWTRRX01nRG1aVmt1R2VTclQ1VUtaZGNha3k5NmFZX3RUMm1CRjJEd2N6VnFTMEExUnBZQjNYUWxLMktIWHc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMicEFVX3lxTE5fYS1DbVhzSWEtSF9BVGRxcThLM0R2T2YyNm1yX2lqRGMtV2V2dG5EOU9iR1FhWUVHbGVlUWV5SVFNUHhLOER5QkgyNnV2TTRubEp1WWZ5a1JQQW9Ba3JDSFkyTHo0a1ZpbUlwYlh2V2c?oc=5</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="32">
@@ -1373,21 +1373,21 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Research examines social landlords’ compliance with human rights law - Scottish Housing News</t>
+          <t>US military seizes Venezuela oil tanker under Trump sanctions - The Guardian</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Fri, 16 Jan 2026 09:24:06 GMT</t>
+          <t>Fri, 16 Jan 2026 02:30:00 GMT</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxPTHZkdnlCNVl5aHduaFpXSnAteG5NS3V5YU9lUlBMX2FPeVBtZmpfajBVSzFveFJ4MXd6QzNhYmdhZmZ0V3VZdGF6ZFpHcEttcHlqRDNINFdFTGVvLVN2R21GdHZVWFhhUFVwblZBMU90bkZRblY2RU1wanBSVzRDQkhXa0NCcF81bFdDekdLVmYtdHRveUxIOEFrRjF2YUxoMkhMVUd0LVBnWTcxSWJqRGlB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijAFBVV95cUxPTzI4Qy1zSWU2amVTN0ZSaWRINWFpYmpmQ0dxTzljem9uVTQzNC05M1ZkZGJuQ19oREpSSXJJSWRpakpqbnpvMm9kNDNGeUtCZGJzZ0pVYzlDR0Y3c05WTUpoQkVndzc2YVVIN1NYcUZrSmNEN2I0bUZYTDRPc3F3VW5uMWZhcXdLM1pudQ?oc=5</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="33">
@@ -1403,21 +1403,21 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Taiwan and US seal deal to lower tariffs, boost chip investment - Al Jazeera</t>
+          <t>Chinese leader Xi Jinping hails 'turnaround' in China-Canada ties as Mark Carney visits Beijing - BBC</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Fri, 16 Jan 2026 08:53:28 GMT</t>
+          <t>Fri, 16 Jan 2026 09:57:13 GMT</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxPOUk4UC05RXpJQTk2YkxveVpBRVRGZ0h3UEI1YVFhMDRNT1pZTGZxVGs3V0hSZ2FkWGJOdk9pbFhzQzFXcFdNQUJPMW5nY1AtaWpncFR1UGFhQnRNVUJ2SThmZmtYc09PTnVRelY0d2l6ZmhDU2M4VzNOTEM5ZEMzamY1S3pzcU9XMXRDMzJHamI4akVtTVFpamc2U2M0YTl2dkVxOUN30gGrAUFVX3lxTE9XSUVIYnl3WHN5TlV0endpTUpCZHZINXVfTXJ2NkRRZlVXaUFxR1VlY0tNMnBpTnZieGVTMngxckt4cUFXZVRZZ3JKeHNpRVdPcTA5d2NpNUM4dmRfa3lJR1l3ZGdXRE1uVkRPVXdSWnhfdmN0cENhNDI1cnpzU09PRk1CdWFmMXlvZDZuS01RUkpJaDRLUS1Fd3pHVTBNcFNjc1l2dlVKWjBEZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiVEFVX3lxTE1OM1A3NDNhemV3YU1jZk9ENHltOXdCT3puT3F0dXhGT1Vsa1BuRDZoNEZjcnlVbmlINlE3Zm9FcXBRTlpZV1R4SHpINzFVVGNCY0lXMQ?oc=5</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="34">
@@ -1433,21 +1433,21 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>How is XPO Prioritising Sustainability in Logistics? - Sustainability Magazine</t>
+          <t>China reports record trillion-dollar trade surplus despite Trump tariffs - The Guardian</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Fri, 16 Jan 2026 10:21:11 GMT</t>
+          <t>Wed, 14 Jan 2026 15:08:00 GMT</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiggFBVV95cUxPZjFLRDNVU0hrRXZCRzVTblNQbEQ4TWwwbzBtR2FBekJsbVdVUDN1c2hLZWZUbGZXbkxkUkd3YXNRQlBRU0NrRXczSHU3dFJWNG03eUc5ZWhvWF9YYTF2OWNWX21sN1lfa0I0bXFyYTRoRURkc2gzeUUyZFNBY2tmcmZR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxNQ0RKdmF5eXBiMl9VUzJZT3YzMHI4UmNQeWt6Z21IWG1MbWZqV1U3MHpwWnZya0ZpWktuOGdOVXd4Vlp1aTFXZElBT2dfUnJlVWxOWnRBX2gwUTJkYlJGRzJZRXN3ck0zbUxWRzNWbWxKRWlVVXI4cDdKd2pLU3lDQlliNUVEaVhJQ1p5MTloTEI1VS1zQ2FkVFRyOEhlX01rVXJodU5tQ0FNU2RGMGJ2aUhZdWJoeWtJTlE?oc=5</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="35">
@@ -1463,21 +1463,21 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Dun &amp; Bradstreet outlines seven key compliance trends - IT Brief UK</t>
+          <t>Green Shipping Corridors Can Help Scale India’s Green Hydrogen Ecosystem - RMI</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Fri, 16 Jan 2026 09:00:00 GMT</t>
+          <t>Fri, 16 Jan 2026 11:37:31 GMT</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihgFBVV95cUxPMVlWR2o4QlFlZXVDakFPRUVmNGI2QmlOYnFzN2l2b3RELWpKdmhucndMS3JLMnZqOGhQenpFR3NXNU5WMm53dWxqM3NoUnJtU3pnV0JhSi1JYWxNc3Z2RDByWGVMbzA3ZkU1M3BqX0R3amlidk94a21ZdTNKR0RJNkVRdWYtZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikgFBVV95cUxQUlBBVUMwLXIyMElfbE1HaXdhbHgzdWx3anZiNHZNLWJzQ3NfUmdGQUY3QjRVcGloZDNIZlFnYW9YUFUyYVROME1hSXJrWG40NVh1c3p6M3MyWDlQU1JmUnFsaE1OSHRJbHFvUkxNRkFrQWhmc1ZwWUZTZzF2TVZsT0hJU0xMeWtMWTJIMXBCZkhLZw?oc=5</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="36">
@@ -1493,21 +1493,21 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Athens breaks EU ranks to side with US and Saudi Arabia in green shipping row - Euractiv</t>
+          <t>Inchcape Shipping Services opens new office in Peru, strengthening presence in South America — SMI DIGITAL - shipmanagementinternational.com</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Fri, 16 Jan 2026 10:52:00 GMT</t>
+          <t>Fri, 16 Jan 2026 10:06:46 GMT</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxOUGlFaXNzWVhSZnd3YndBQ3Y0SmZoYkNYZEZYZTFjTC1jQVlCNU1vWjAtU3RaM3dYMWpZZHZYSGVuQ0U5Q0p1bmFGeEFBdzdIYndac1pFcHdWVHQzbFRFSW1TZ2xrcXBwWGlJd1cxaTNDdGdNbGNrT2NVa2xIVlFrMU5EbWRyWE1UOGY2UUR3REladzNQVGpNa0xtQnRoRWV5Z0dSNWJKdVNRZG9f?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi2gFBVV95cUxOV3N1NWJudDV5VUNfSVFxTm1DamhHaG9qUGRPQld1TEpxRk9TajFUNE1zSkFRY3o1U3lwZURzZUpDREgxTVVJT2VTWUU4bW1OSEQtYXF2X25DLUxsd1BrVWFiMXdiWlFXdnJBZ2ttbGZzSGZDNk5ZRUN6SHp5Y1owQ19malZqcW5fSU04UWZiQVIyZ1FuNWp0ZXFORGFXTGdJcVAwMXkxYTI2MWRJUFo4TFpaWGR1R2psNWEzUEpTWnJJaEFhWWZRX0dCd1lETjZEUVFXcFZTcVpVZw?oc=5</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="37">
@@ -1523,21 +1523,21 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>UBCivils benefit from Podfather logistics software - Agg-Net</t>
+          <t>Port of Prince Rupert handles 26 million tonnes in 2025 - Port Technology International</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Fri, 16 Jan 2026 08:35:50 GMT</t>
+          <t>Fri, 16 Jan 2026 10:07:43 GMT</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihgFBVV95cUxOQm5QQXFNVnVrSnpDZU1lZERZWEk5X0VSSDN5a3FTMmNQemhQblVqRm1kS1BHWGlJMjJVWWxZTjdwLVNKQ2lkZUdRLU5PLXRrMWV1NDg0ZUI0Y1d3X2ppNGhjalktM01LdTVxeEt2NFgxVFdtbUE3U1lxNk1yRGZ4N2pxODZWQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxOanQ5QWxuTFgySjRVZ3dOWnpEaTdSN3pseDgyZjM5S2V0SjhfY2ZGREY1S21QWFRsVWt0N3RLR09ZLVFxeFp5eFB3cXExcE5PQ3RzbUpVLXlwN1RHTXhXM0VYeXRzNGNtNllLaDVzR2U0WDA5UHA5UzVNeTE4VWtIdjhFQU9OeEVXWklFcS16eU1OUXJHVlhr?oc=5</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="38">
@@ -1553,21 +1553,21 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>What are tariffs, how do they work and why is Trump using them? - BBC</t>
+          <t>Volunteers clean beaches in Sussex after shipping container spills - BBC</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Wed, 14 Jan 2026 16:32:50 GMT</t>
+          <t>Thu, 15 Jan 2026 06:07:03 GMT</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTFBweHdveUp5S2F0aGJwSEs2U2lOMkF6NzRNZTd3bEJUdTQwVjhRX0pjZmFzZ25hRzk4MHE0WW9KVkEtUjIxRUNWbXRzX3pmd1A5UWhyaE5Ja1ZWd9IBX0FVX3lxTE82Y0Q0dVVkNUhXb1o4Tkt6V1AycjA1dmkzbUs3d3JydDktMVNrSnNsNDI1Zk9BdmpMc1BQbGJneThSUDBmUkdUdFhDVTZaTTRGaGlwdDhnR3NPeXhDYW9F?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiXEFVX3lxTFA5Wl85Um9tUmhFbTJxbFFVT3VMbjktRHVtRmhYSTlMTl8zNllZVUR4QXN0eW8ydlhpM1FFWXZqVGdqVlo4UUhTMGtzTjR4WFBJYTNWWVBFVU1FRUVh0gFiQVVfeXFMTjNkbjVlWlRWc3ZPR093X094cUVMSDgyNWdCVk93QjFDT28xZGJKMk55ZkNMc1Y2Mld4b2d1Y2Fzc2puRjBLM0JWbk9iaWN1UUVzbHV0UGF2MWJFZjBJZ240MHc?oc=5</t>
         </is>
       </c>
       <c r="F38" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="39">
@@ -1583,21 +1583,21 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>White House sets tariffs to take 25% cut of Nvidia and AMD sales in China - Financial Times</t>
+          <t>Lottery retailers achieve record age check compliance - Better Retailing</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Wed, 14 Jan 2026 23:54:51 GMT</t>
+          <t>Fri, 16 Jan 2026 10:13:38 GMT</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMicEFVX3lxTE5fYS1DbVhzSWEtSF9BVGRxcThLM0R2T2YyNm1yX2lqRGMtV2V2dG5EOU9iR1FhWUVHbGVlUWV5SVFNUHhLOER5QkgyNnV2TTRubEp1WWZ5a1JQQW9Ba3JDSFkyTHo0a1ZpbUlwYlh2V2c?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijwFBVV95cUxNTHpmdkFBZjJHdDdOc2ZEWmNpTFI1R0JxaVJOa3lrQkJiM2J3eXFIX0s3NXR6MG82WWUzb1BxWUJIc0xWOG1sY1NsT216YXZJeEF4aUJXTUdkTGVSdkhhN1pQZ0lvdDIxbVJHcXg5bzdfTi00dGZCeUpJdzVlSDZYNTFDS1BKUlp3U1Q2MHp6dw?oc=5</t>
         </is>
       </c>
       <c r="F39" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="40">
@@ -1613,21 +1613,21 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>US military seizes Venezuela oil tanker under Trump sanctions - The Guardian</t>
+          <t>James Kemball becomes Felixstowe’s largest off-dock provider - Port Technology International</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Fri, 16 Jan 2026 02:30:00 GMT</t>
+          <t>Fri, 16 Jan 2026 10:57:45 GMT</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijAFBVV95cUxPTzI4Qy1zSWU2amVTN0ZSaWRINWFpYmpmQ0dxTzljem9uVTQzNC05M1ZkZGJuQ19oREpSSXJJSWRpakpqbnpvMm9kNDNGeUtCZGJzZ0pVYzlDR0Y3c05WTUpoQkVndzc2YVVIN1NYcUZrSmNEN2I0bUZYTDRPc3F3VW5uMWZhcXdLM1pudQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxPVVVjaGRpQ1lSZDg1MTQ5M1c0alpta1ZhX2hLMnAxMmQwR1ZTQ2VFZnBrVjhiQ2I3SGx6TnM5M1YxNE1uWUtYTmF3d2NZMjV1MGR3ZFFKWnNsY1MxeTM4TDlSejNfcmY0YUdrbkt4Y3J5d3pIRlMxSXN1MG1QY0dhX0tSTWNwRzhMZXV5aEszQjhMdDJqWTlFZENlRVE?oc=5</t>
         </is>
       </c>
       <c r="F40" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="41">
@@ -1643,21 +1643,21 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Chinese leader Xi Jinping hails 'turnaround' in China-Canada ties as Mark Carney visits Beijing - BBC</t>
+          <t>Strategic Insights: Leveraging Compliance and Nutritional Innovations in the Infant Formula Ingredients Market - Yahoo Finance UK</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Fri, 16 Jan 2026 09:57:13 GMT</t>
+          <t>Fri, 16 Jan 2026 09:09:00 GMT</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiVEFVX3lxTE1OM1A3NDNhemV3YU1jZk9ENHltOXdCT3puT3F0dXhGT1Vsa1BuRDZoNEZjcnlVbmlINlE3Zm9FcXBRTlpZV1R4SHpINzFVVGNCY0lXMQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxPTkJCdGxLeUVBSTE5RlNRaGJzQThjQ2FHZDQ5bFE0QkVzeUNtNVZtMEdEMUgtTUNkdFphcG5DOGhYdDF5eDNHUWloMWcxUTVXUDl0TXFoZHhoN1pLVUhTeE1HWDVHc3ZtSm92N3N3NlJYai04bXVnRUdUWTNiUnM5SXJfdHRxNVFDRFRRSlZENF9vVjJlMW9OZ2owZWkzcEp2LVFr?oc=5</t>
         </is>
       </c>
       <c r="F41" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="42">
@@ -1673,21 +1673,21 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>China reports record trillion-dollar trade surplus despite Trump tariffs - The Guardian</t>
+          <t>Statement of the President of the Union of Greek Shipowners about targeting shipping — SMI DIGITAL - shipmanagementinternational.com</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Wed, 14 Jan 2026 15:08:00 GMT</t>
+          <t>Fri, 16 Jan 2026 10:11:33 GMT</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxNQ0RKdmF5eXBiMl9VUzJZT3YzMHI4UmNQeWt6Z21IWG1MbWZqV1U3MHpwWnZya0ZpWktuOGdOVXd4Vlp1aTFXZElBT2dfUnJlVWxOWnRBX2gwUTJkYlJGRzJZRXN3ck0zbUxWRzNWbWxKRWlVVXI4cDdKd2pLU3lDQlliNUVEaVhJQ1p5MTloTEI1VS1zQ2FkVFRyOEhlX01rVXJodU5tQ0FNU2RGMGJ2aUhZdWJoeWtJTlE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi8gFBVV95cUxNMVBCckxMOXpCUXl2emYwSlNST1Q2bjEtb1dQUlo1czQ2Q0h6MlFqOGRxQnpNVkQ1VnBIZ0ZqcndWRWY4Wll4U0tneUlPTUNDdXhGYS1DTnhCT1JVMFBEdUpjaFlvckQtVkwzUHNHYWdQeUM0MUkwUjVOazdiLVUxQUZBSER3YlRBQkh0TEhRT1dFMU1NR19TS0VGTTVnMzB2T3Y0SmxNZk9UeFo2bWlyQktqS05BRzZHTHY2dU5GbDc3UUl4TWxMRW5uM2lnUzhtTmZWMWNDMDNYOXE5c1VLaDV5aExHdWdoYlhqcXM2eDItZw?oc=5</t>
         </is>
       </c>
       <c r="F42" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="43">
@@ -1703,21 +1703,21 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Green Shipping Corridors Can Help Scale India’s Green Hydrogen Ecosystem - RMI</t>
+          <t>Austria to tighten airport asylum procedures, expand sanctions under new EU rules - Anadolu Ajansı</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Fri, 16 Jan 2026 11:37:31 GMT</t>
+          <t>Fri, 16 Jan 2026 10:01:48 GMT</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikgFBVV95cUxQUlBBVUMwLXIyMElfbE1HaXdhbHgzdWx3anZiNHZNLWJzQ3NfUmdGQUY3QjRVcGloZDNIZlFnYW9YUFUyYVROME1hSXJrWG40NVh1c3p6M3MyWDlQU1JmUnFsaE1OSHRJbHFvUkxNRkFrQWhmc1ZwWUZTZzF2TVZsT0hJU0xMeWtMWTJIMXBCZkhLZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxOLTFwa05nMTgyY1ltSllPaFoyV0EwbS1hNDFwTF9zR3p0VGNjUnFhRl9GWXB0bEJYUll3ZThxaXdIQzZFTno2S2dlc2pCZF9vWmJoZkVkaTM2QWM3emItcW90aE1WTHRkcHBmY2ppbEsyYVVJUk9vTGZzcXdwNUJPUWtrbjVXWm5VckNmQlZ5ZVlUMU1JdHpvU0o5Y29sSE1FdXlSV1YwbVh5YUFPemc4MTBTazl3M2phYk5VeA?oc=5</t>
         </is>
       </c>
       <c r="F43" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="44">
@@ -1733,21 +1733,21 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Inchcape Shipping Services opens new office in Peru, strengthening presence in South America — SMI DIGITAL - shipmanagementinternational.com</t>
+          <t>Maersk ramps up Suez Canal return that could dampen freight rates - Reuters</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Fri, 16 Jan 2026 10:06:46 GMT</t>
+          <t>Thu, 15 Jan 2026 18:50:33 GMT</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi2gFBVV95cUxOV3N1NWJudDV5VUNfSVFxTm1DamhHaG9qUGRPQld1TEpxRk9TajFUNE1zSkFRY3o1U3lwZURzZUpDREgxTVVJT2VTWUU4bW1OSEQtYXF2X25DLUxsd1BrVWFiMXdiWlFXdnJBZ2ttbGZzSGZDNk5ZRUN6SHp5Y1owQ19malZqcW5fSU04UWZiQVIyZ1FuNWp0ZXFORGFXTGdJcVAwMXkxYTI2MWRJUFo4TFpaWGR1R2psNWEzUEpTWnJJaEFhWWZRX0dCd1lETjZEUVFXcFZTcVpVZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxPRDVPeWhBWlRhY1AyZDNrWGFVVTBqS2pzWFVMbVZ0cGtQWkM5dUZPXzNwSnpCNHdlQnUwell0N0ZtZk43MTRUbElQUGFmSHk1NTJsNEdaODdJNFNZc21pM09wSDRhZ3E4QmVaNm1MMmExWUcwSW9zOUtNdDlKS0wydFZjMTQ0T0E5ZC05SFktR1dGWGpxdmcwSlZVVkJxeFkxYXc?oc=5</t>
         </is>
       </c>
       <c r="F44" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="45">
@@ -1763,21 +1763,21 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Port of Prince Rupert handles 26 million tonnes in 2025 - Port Technology International</t>
+          <t>When Politics Overtakes Supply and Demand in Shipping - StoneX</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Fri, 16 Jan 2026 10:07:43 GMT</t>
+          <t>Thu, 15 Jan 2026 18:30:00 GMT</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxOanQ5QWxuTFgySjRVZ3dOWnpEaTdSN3pseDgyZjM5S2V0SjhfY2ZGREY1S21QWFRsVWt0N3RLR09ZLVFxeFp5eFB3cXExcE5PQ3RzbUpVLXlwN1RHTXhXM0VYeXRzNGNtNllLaDVzR2U0WDA5UHA5UzVNeTE4VWtIdjhFQU9OeEVXWklFcS16eU1OUXJHVlhr?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxNNUNqLWRCVVRIVFNnWjBST0dtX1dRRHhrNFlxYXUyNTJKQlZGa0tBYUNvX0Z5MlJmWFQ0WmJ2VmZuM1NhanhPY2NYd2w0cThuUmtOQUYwcWxqRXpCblZyelpQS2hVUHV0LVJreHhRSnhHcVQ5ZEJzbW40aTJrWDNUU1NfUFY0anRLMThtZkpJU2pSV3pIdkJYMU9NZ0lpY2lPZnc?oc=5</t>
         </is>
       </c>
       <c r="F45" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="46">
@@ -1793,21 +1793,21 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Volunteers clean beaches in Sussex after shipping container spills - BBC</t>
+          <t>EU Sanctions and the Undoing of International Investment Arbitration - EJIL: Talk!</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Thu, 15 Jan 2026 06:07:03 GMT</t>
+          <t>Thu, 15 Jan 2026 13:08:13 GMT</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiXEFVX3lxTFA5Wl85Um9tUmhFbTJxbFFVT3VMbjktRHVtRmhYSTlMTl8zNllZVUR4QXN0eW8ydlhpM1FFWXZqVGdqVlo4UUhTMGtzTjR4WFBJYTNWWVBFVU1FRUVh0gFiQVVfeXFMTjNkbjVlWlRWc3ZPR093X094cUVMSDgyNWdCVk93QjFDT28xZGJKMk55ZkNMc1Y2Mld4b2d1Y2Fzc2puRjBLM0JWbk9iaWN1UUVzbHV0UGF2MWJFZjBJZ240MHc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxQLW9Vc1BqUFZQR3NiaUkzVVFpUGR5bzZtQ2NlUnZydFVaeDBZUXdCczFSejBIX3ZzM2NSN2w4Q2VodFhsZHZDc09wcHVJQ1MwdGxkMjFzUGRKOVM5UmpXLXJNQmxEYVRWNUJfaTVURmp6bXdGTjNObjdUZzExdTBWTzFOYjFmZS1mYXItNXpGMThMc3pTTkJ2dDF3?oc=5</t>
         </is>
       </c>
       <c r="F46" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="47">
@@ -1823,21 +1823,21 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Lottery retailers achieve record age check compliance - Better Retailing</t>
+          <t>EXCLUSIVE: EU mulls tariffs on Chinese hybrid cars - Euractiv</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Fri, 16 Jan 2026 10:13:38 GMT</t>
+          <t>Thu, 15 Jan 2026 18:11:15 GMT</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijwFBVV95cUxNTHpmdkFBZjJHdDdOc2ZEWmNpTFI1R0JxaVJOa3lrQkJiM2J3eXFIX0s3NXR6MG82WWUzb1BxWUJIc0xWOG1sY1NsT216YXZJeEF4aUJXTUdkTGVSdkhhN1pQZ0lvdDIxbVJHcXg5bzdfTi00dGZCeUpJdzVlSDZYNTFDS1BKUlp3U1Q2MHp6dw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMihwFBVV95cUxPN05Tak43Z2c2dDZXUFMxU2VBVENrUjJUTHlVYWxrVkRjSmVvRzJfY0xOYkw4clJrcUhobHotX0U4VThiSGxQM050VURjdTVGTkJuQnRhUDRPcnhSZTQ5MnFBaHJja2wtTUVOalp1djc0QVNWdS0tZEpIZE9xalZZY0l4cVVMS1k?oc=5</t>
         </is>
       </c>
       <c r="F47" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="48">
@@ -1853,21 +1853,21 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>James Kemball becomes Felixstowe’s largest off-dock provider - Port Technology International</t>
+          <t>India’s exports to China surge in December while shipments to U.S. decline as Trump tariffs bite - CNBC</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Fri, 16 Jan 2026 10:57:45 GMT</t>
+          <t>Fri, 16 Jan 2026 03:29:00 GMT</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxPVVVjaGRpQ1lSZDg1MTQ5M1c0alpta1ZhX2hLMnAxMmQwR1ZTQ2VFZnBrVjhiQ2I3SGx6TnM5M1YxNE1uWUtYTmF3d2NZMjV1MGR3ZFFKWnNsY1MxeTM4TDlSejNfcmY0YUdrbkt4Y3J5d3pIRlMxSXN1MG1QY0dhX0tSTWNwRzhMZXV5aEszQjhMdDJqWTlFZENlRVE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMihgFBVV95cUxNVDU0UE1pV1Z6bEd0YW1XZGgydlVROFFlcFdxQURYZFhaMzZUSkdUek5JUFB2WmZ1ZFBoNFpFeE9CbTZUelBJUGZ0SzhYNjNWM19GdWtKTmsxcDlaSUVJMFFJeHJJWG9LNDVsT3BpeS1KSi00ME5GWFpRSktxdmd3WUt5ZlI3QdIBiwFBVV95cUxOM2VjTmlfY3RNSWw1bE1xRnc2ZnNUa19XNXQzWDlMU18xMk91N21mamdlUmI3NVBDU2VkbGJjdE56WTNNeC11cDBKZW1SdmRxTExZVjI4c1BsQ2MzVTFRMU9qUWV2VUJ2RmpIWVZ5VjRsdkhJaDNBbm9UU3U0S2tFaWtWaU9DNnFJYXk4?oc=5</t>
         </is>
       </c>
       <c r="F48" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="49">
@@ -1883,21 +1883,21 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Strategic Insights: Leveraging Compliance and Nutritional Innovations in the Infant Formula Ingredients Market - Yahoo Finance UK</t>
+          <t>EU-backed study will put logistics at heart of offshore tendering - Project Cargo Journal</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Fri, 16 Jan 2026 09:09:00 GMT</t>
+          <t>Fri, 16 Jan 2026 09:51:06 GMT</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxPTkJCdGxLeUVBSTE5RlNRaGJzQThjQ2FHZDQ5bFE0QkVzeUNtNVZtMEdEMUgtTUNkdFphcG5DOGhYdDF5eDNHUWloMWcxUTVXUDl0TXFoZHhoN1pLVUhTeE1HWDVHc3ZtSm92N3N3NlJYai04bXVnRUdUWTNiUnM5SXJfdHRxNVFDRFRRSlZENF9vVjJlMW9OZ2owZWkzcEp2LVFr?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxPUFdENXpCQmVOR1lYcExtdlRYM2dteGFKQkZNazlpejZSbGZQOHRaVTBZVnpyV3FMQ2tPNUtlU0pNdzNZYjlkSjgtYjdmbVhEd0V3eEdZbmtRclNPaTVWS3JmVmRSVXFsSG5fR1lVY3NJWWxLajZOQWFoTV9HSlJNNHlSU1NaS2FLNVZJY2c4c2lnSEJVVXFuOElrVmVyNEpVdFlDVElyX0p0MjZnSDZaZnRKYVFzeHp4WnM4SWF6MV9uNXhZTVlLMnU5VQ?oc=5</t>
         </is>
       </c>
       <c r="F49" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="50">
@@ -1913,21 +1913,21 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Statement of the President of the Union of Greek Shipowners about targeting shipping — SMI DIGITAL - shipmanagementinternational.com</t>
+          <t>Canada Breaks With U.S. to Slash Tariffs on Some Chinese Electric Vehicles - The New York Times</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Fri, 16 Jan 2026 10:11:33 GMT</t>
+          <t>Fri, 16 Jan 2026 08:33:08 GMT</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi8gFBVV95cUxNMVBCckxMOXpCUXl2emYwSlNST1Q2bjEtb1dQUlo1czQ2Q0h6MlFqOGRxQnpNVkQ1VnBIZ0ZqcndWRWY4Wll4U0tneUlPTUNDdXhGYS1DTnhCT1JVMFBEdUpjaFlvckQtVkwzUHNHYWdQeUM0MUkwUjVOazdiLVUxQUZBSER3YlRBQkh0TEhRT1dFMU1NR19TS0VGTTVnMzB2T3Y0SmxNZk9UeFo2bWlyQktqS05BRzZHTHY2dU5GbDc3UUl4TWxMRW5uM2lnUzhtTmZWMWNDMDNYOXE5c1VLaDV5aExHdWdoYlhqcXM2eDItZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijgFBVV95cUxQUWtrMDM0cVpBQzRsY2xyTXhPQktzVHM0QVl0djFMWWYteURHX3pvRmI3MTIta3FWOEx4QWpzdXNCOWE2QkJQVDN1Vy0ydHdGU250bkJLNTREUy02Mm8tMS1CMHU5VktUSGlURFY1LTh4eFp4d0dRWmwwX3B5bnZqek82Q19FOVd5R1hlaEJ3?oc=5</t>
         </is>
       </c>
       <c r="F50" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="51">
@@ -1943,21 +1943,21 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Austria to tighten airport asylum procedures, expand sanctions under new EU rules - Anadolu Ajansı</t>
+          <t>Thug stabbed pal to death at flats in Port Glasgow - Daily Record</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Fri, 16 Jan 2026 10:01:48 GMT</t>
+          <t>Thu, 15 Jan 2026 16:45:00 GMT</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxOLTFwa05nMTgyY1ltSllPaFoyV0EwbS1hNDFwTF9zR3p0VGNjUnFhRl9GWXB0bEJYUll3ZThxaXdIQzZFTno2S2dlc2pCZF9vWmJoZkVkaTM2QWM3emItcW90aE1WTHRkcHBmY2ppbEsyYVVJUk9vTGZzcXdwNUJPUWtrbjVXWm5VckNmQlZ5ZVlUMU1JdHpvU0o5Y29sSE1FdXlSV1YwbVh5YUFPemc4MTBTazl3M2phYk5VeA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijwFBVV95cUxOM044ekJOZlBBNDJtWW1MemU5ZDNZYkxDNnlyZ0txNEZTcWhHMURaV0lRcGpscDJ2X3FndUFqaDZXR0l1Nk54ZVk2enRoUV9ZQV9OZ0k3NFZIVFNrLW85Uy1MWkNxMlJYdDRrODhmdUMzNDZubDJHYnR4LTdkVlJWNjFMenBPdDg2cWNPN1k1TdIBlAFBVV95cUxOUXptQldkeTlQbkRjT29xdHVreWY1S0MzS0tQRGh3OFlUZV9ERzh5ZnpfZ2pRYk9GSm5rTTJHYkZUMDBUR0ZGTk1kQnk1WENaTkN6Z2lDNU05N1hFNVZsYi1LRXZ3UWo4Z29SYThiTnJWVVZuZjhQZXRoZFN5bHV0ekl3MlBHLW9Ib25uQWlPSDZ1bUpN?oc=5</t>
         </is>
       </c>
       <c r="F51" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="52">
@@ -1973,21 +1973,21 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Maersk ramps up Suez Canal return that could dampen freight rates - Reuters</t>
+          <t>Port of Singapore Seeks More LNG Fuel Suppliers - Rigzone</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Thu, 15 Jan 2026 18:50:33 GMT</t>
+          <t>Fri, 16 Jan 2026 09:00:00 GMT</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxPRDVPeWhBWlRhY1AyZDNrWGFVVTBqS2pzWFVMbVZ0cGtQWkM5dUZPXzNwSnpCNHdlQnUwell0N0ZtZk43MTRUbElQUGFmSHk1NTJsNEdaODdJNFNZc21pM09wSDRhZ3E4QmVaNm1MMmExWUcwSW9zOUtNdDlKS0wydFZjMTQ0T0E5ZC05SFktR1dGWGpxdmcwSlZVVkJxeFkxYXc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxQMjZaUFpveVpwaUhIVDFCd2dHOUJORUNfSnFtdTFCaG9vX1Q4TjhzZkdIV1hPQ0w0ZFV2NTJ5QXhsc2VEdHdDVlVwLXBKdnNRYUtyMmZmUmpVX0t3WktIQ3lhUzJCdXZfN3NSY3JqQnFSRkhkRm12V1ZOTERZZ2pLdkpyaXdTVkhSSUtjbjFkeWlTTTdrSVozeTF1blUycVI3X0pPa1QwQQ?oc=5</t>
         </is>
       </c>
       <c r="F52" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="53">
@@ -2003,21 +2003,21 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>When Politics Overtakes Supply and Demand in Shipping - StoneX</t>
+          <t>Broadband ISP YouFibre UK Set to Block Internet Email Port 25 from Friday UPDATE - ISPreview UK</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Thu, 15 Jan 2026 18:30:00 GMT</t>
+          <t>Wed, 14 Jan 2026 17:43:00 GMT</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxNNUNqLWRCVVRIVFNnWjBST0dtX1dRRHhrNFlxYXUyNTJKQlZGa0tBYUNvX0Z5MlJmWFQ0WmJ2VmZuM1NhanhPY2NYd2w0cThuUmtOQUYwcWxqRXpCblZyelpQS2hVUHV0LVJreHhRSnhHcVQ5ZEJzbW40aTJrWDNUU1NfUFY0anRLMThtZkpJU2pSV3pIdkJYMU9NZ0lpY2lPZnc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxNQnpVS3hmb2xoa1lhR2dSdFQ3QU8tcmk5RFVlWkJ6VXhtLTZYTWhqbjdhbmgtSmJqdEo4V1QwLWxUVG9rUGNPX1lwZEFRVkg0STZ4eDhRYnR3b09qR2RIOXl4YldMcGVDQ3gyb20xZUtOTTU3VmZHYXAwc015WGcxZ0VuWUNWeHNqQ2pZN01pdWp6T0RzdDVQdGJHUVRrRUNiQk9nUkJCNWc0UG5yQ2xxMVlFdTRTemNlN1F6M2NkS3BNZw?oc=5</t>
         </is>
       </c>
       <c r="F53" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="54">
@@ -2033,21 +2033,21 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>EU Sanctions and the Undoing of International Investment Arbitration - EJIL: Talk!</t>
+          <t>Marina Port Valencia Obtains LEED Platinum - Yachting Pages</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Thu, 15 Jan 2026 13:08:13 GMT</t>
+          <t>Fri, 16 Jan 2026 11:37:14 GMT</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxQLW9Vc1BqUFZQR3NiaUkzVVFpUGR5bzZtQ2NlUnZydFVaeDBZUXdCczFSejBIX3ZzM2NSN2w4Q2VodFhsZHZDc09wcHVJQ1MwdGxkMjFzUGRKOVM5UmpXLXJNQmxEYVRWNUJfaTVURmp6bXdGTjNObjdUZzExdTBWTzFOYjFmZS1mYXItNXpGMThMc3pTTkJ2dDF3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxNQVBYWFp5dEtRTG81cmZ6UkJTZU9ZNlBOQnVSQ0ZtakpJT0tKODZscHM0WHRjWVJBUllILVFid1l1OGNCNlJtQW1DM1Z4QkNyS1F3ZWM3dGtsb0k4VEdlTGZ4Vl9ib1ZwcHBEZ2VVc2hJRDR5eG9GMFE5am1jX3VZTl9lc0JYcHJsb1dJNE9kLTI?oc=5</t>
         </is>
       </c>
       <c r="F54" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="55">
@@ -2063,261 +2063,261 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>EXCLUSIVE: EU mulls tariffs on Chinese hybrid cars - Euractiv</t>
+          <t>One person left with serious leg injuries in Ellesmere Port collision - Chester Standard</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Thu, 15 Jan 2026 18:11:15 GMT</t>
+          <t>Fri, 16 Jan 2026 09:15:42 GMT</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihwFBVV95cUxPN05Tak43Z2c2dDZXUFMxU2VBVENrUjJUTHlVYWxrVkRjSmVvRzJfY0xOYkw4clJrcUhobHotX0U4VThiSGxQM050VURjdTVGTkJuQnRhUDRPcnhSZTQ5MnFBaHJja2wtTUVOalp1djc0QVNWdS0tZEpIZE9xalZZY0l4cVVMS1k?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxPWndBeFUwOTQzSlNHTmx3blYzcjBObXZPN3hDN1RFM0pfN3F4RUdvUE1zZjJZdnFNMFJiOWd3a3hmVENISFprWkZ2YkVITHJHMEMwRnFtSDNPTklSUExiNkMyenowVS1NZXR1Ty1qSVplazcwYjZoV0tWSFVJMzR3S1JLeUNxOVlnMlFLM0poclNFTTdGcWk0Y25XRkR2U1hTT0QyZEFpRms?oc=5</t>
         </is>
       </c>
       <c r="F55" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Supply_Chain</t>
+          <t>Protest</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally)</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>India’s exports to China surge in December while shipments to U.S. decline as Trump tariffs bite - CNBC</t>
+          <t>Iran deploys riot police to shut down protests - France 24</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Fri, 16 Jan 2026 03:29:00 GMT</t>
+          <t>Fri, 16 Jan 2026 09:37:40 GMT</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihgFBVV95cUxNVDU0UE1pV1Z6bEd0YW1XZGgydlVROFFlcFdxQURYZFhaMzZUSkdUek5JUFB2WmZ1ZFBoNFpFeE9CbTZUelBJUGZ0SzhYNjNWM19GdWtKTmsxcDlaSUVJMFFJeHJJWG9LNDVsT3BpeS1KSi00ME5GWFpRSktxdmd3WUt5ZlI3QdIBiwFBVV95cUxOM2VjTmlfY3RNSWw1bE1xRnc2ZnNUa19XNXQzWDlMU18xMk91N21mamdlUmI3NVBDU2VkbGJjdE56WTNNeC11cDBKZW1SdmRxTExZVjI4c1BsQ2MzVTFRMU9qUWV2VUJ2RmpIWVZ5VjRsdkhJaDNBbm9UU3U0S2tFaWtWaU9DNnFJYXk4?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMif0FVX3lxTE5Sc0E3RFctNmtpMGdlYkM2cWdlRWF1NzU4MnZ2ajdzUHVxMkRzaUcySmZ6ZXBDcC1HQl8wQzN1MkNmZVRYQnhfVW5zMEZsOHJEUWp6em5EYzhyd1BzSjhyV1MyWUQxaC1hNWpMbFVob3UyTl9WSlQtSEpSX1pKbnM?oc=5</t>
         </is>
       </c>
       <c r="F56" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Supply_Chain</t>
+          <t>Protest</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally)</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>EU-backed study will put logistics at heart of offshore tendering - Project Cargo Journal</t>
+          <t>Eyewitness: a New Year and resource draining protests recommence - Police Oracle</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Fri, 16 Jan 2026 09:51:06 GMT</t>
+          <t>Thu, 15 Jan 2026 16:45:43 GMT</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxPUFdENXpCQmVOR1lYcExtdlRYM2dteGFKQkZNazlpejZSbGZQOHRaVTBZVnpyV3FMQ2tPNUtlU0pNdzNZYjlkSjgtYjdmbVhEd0V3eEdZbmtRclNPaTVWS3JmVmRSVXFsSG5fR1lVY3NJWWxLajZOQWFoTV9HSlJNNHlSU1NaS2FLNVZJY2c4c2lnSEJVVXFuOElrVmVyNEpVdFlDVElyX0p0MjZnSDZaZnRKYVFzeHp4WnM4SWF6MV9uNXhZTVlLMnU5VQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxQVk9zNkhpVE1hRUU0LTJMd3lJYXF5WVVEM0kySFNqYlFDVXQwOXNpS0dVVGxsQVBsS1lDZ1pjZDluU3dDS0ZXSnZrb2hFVG5vWVh2MUJaUFhhQ2NxVHhQMFdGQnRpNEJ1WERibDdhNHVoN281bXBiWlo4SzEtaG51XzlTYlMwQmZCaFJrZEpSSENfTVBpNXNuUWNKVzkyeGVNdGdfTDN3c0JMbEpNUmc?oc=5</t>
         </is>
       </c>
       <c r="F57" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Supply_Chain</t>
+          <t>Protest</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally)</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Canada Breaks With U.S. to Slash Tariffs on Some Chinese Electric Vehicles - The New York Times</t>
+          <t>Police called in over weekly Palestine protests outside Royal Stoke - Stoke-on-Trent Live</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Fri, 16 Jan 2026 08:33:08 GMT</t>
+          <t>Thu, 15 Jan 2026 17:04:00 GMT</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijgFBVV95cUxQUWtrMDM0cVpBQzRsY2xyTXhPQktzVHM0QVl0djFMWWYteURHX3pvRmI3MTIta3FWOEx4QWpzdXNCOWE2QkJQVDN1Vy0ydHdGU250bkJLNTREUy02Mm8tMS1CMHU5VktUSGlURFY1LTh4eFp4d0dRWmwwX3B5bnZqek82Q19FOVd5R1hlaEJ3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxOQlJIWm5OS1dpOTFRQVg2VHpVOE5NNDJlaGEyd1c2MWtSMWRoVXdaMFE5QlhrbUVuY3VyeHhWRzY4YzdNTy1TZWxDMUZoUC0zWkZPZzZyMi1sb3p2bzBRanNJR2hoMG00a3dmekd2cW5lT09VTE1rc0ZxWVVJQ2N1c2ViSkM5ZDhJcUU5eHVVQWxUZVdiV3B5cDl1dUJJdTR1Mjcw0gGoAUFVX3lxTE1PSkRuOS1vaVJLMmg1Z2RoNDduVDNoNVh0QnNJb2x0TTlGQ2ZDOERnaVQ4OG5vd1pZYm42eGpfM0NuWS01eUU2YUdCbThLS05ZekdETmF2dl96b1BwN0UweXJSVjRleHREbGdVYkZXSURQUWw2MXh1QzB1VG4wWVpqY0VsazR1MXNtNlQ4V1g0ampVUUdTRzdlTlloV0V2eExJaElKVEs1Uw?oc=5</t>
         </is>
       </c>
       <c r="F58" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Supply_Chain</t>
+          <t>Protest</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally)</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Thug stabbed pal to death at flats in Port Glasgow - Daily Record</t>
+          <t>Protester ‘fakes’ being struck by police patrol car during ICE demonstration - The Independent</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Thu, 15 Jan 2026 16:45:00 GMT</t>
+          <t>Wed, 14 Jan 2026 13:45:00 GMT</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijwFBVV95cUxOM044ekJOZlBBNDJtWW1MemU5ZDNZYkxDNnlyZ0txNEZTcWhHMURaV0lRcGpscDJ2X3FndUFqaDZXR0l1Nk54ZVk2enRoUV9ZQV9OZ0k3NFZIVFNrLW85Uy1MWkNxMlJYdDRrODhmdUMzNDZubDJHYnR4LTdkVlJWNjFMenBPdDg2cWNPN1k1TdIBlAFBVV95cUxOUXptQldkeTlQbkRjT29xdHVreWY1S0MzS0tQRGh3OFlUZV9ERzh5ZnpfZ2pRYk9GSm5rTTJHYkZUMDBUR0ZGTk1kQnk1WENaTkN6Z2lDNU05N1hFNVZsYi1LRXZ3UWo4Z29SYThiTnJWVVZuZjhQZXRoZFN5bHV0ekl3MlBHLW9Ib25uQWlPSDZ1bUpN?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxOWFM3VnpoZkxXR3M4UWRJMy10U1JURXVTN0JoMWYzY01ITnNJdkdGUVRhcWk5RHJUb0NzWGhUdUxsZGJyTzlROHVVZzRKMlBHZVlSc1dGdmFzTG1vLVBkWjNMTUR2R0JDbW9haHA3UXNfckdVZG91QXRlLThpRW9xd2hCS09qeTB0eUVIMmZqSWw4VHVrWHdDb3JKOA?oc=5</t>
         </is>
       </c>
       <c r="F59" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Supply_Chain</t>
+          <t>Protest</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally)</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Port of Singapore Seeks More LNG Fuel Suppliers - Rigzone</t>
+          <t>Police strike again as bowling alley thief convicted in Cornwall - Yahoo News UK</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Fri, 16 Jan 2026 09:00:00 GMT</t>
+          <t>Wed, 14 Jan 2026 10:44:14 GMT</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxQMjZaUFpveVpwaUhIVDFCd2dHOUJORUNfSnFtdTFCaG9vX1Q4TjhzZkdIV1hPQ0w0ZFV2NTJ5QXhsc2VEdHdDVlVwLXBKdnNRYUtyMmZmUmpVX0t3WktIQ3lhUzJCdXZfN3NSY3JqQnFSRkhkRm12V1ZOTERZZ2pLdkpyaXdTVkhSSUtjbjFkeWlTTTdrSVozeTF1blUycVI3X0pPa1QwQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMif0FVX3lxTFBlWHlwc0tRSHdKcTEycHpCNzRnQV9sWVluaEFRQ0N3QXM4M01JZGpQOFlfN0dpVVBjdjZ0TTVqSy1FRUhrbVpEclU2LVNtYjhXSFlsZnVOY2JaTXF6c3l5TEhYRXZtQTB0eE9xRnduVTg5bVk5V21IOWE2LWFRRlU?oc=5</t>
         </is>
       </c>
       <c r="F60" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Supply_Chain</t>
+          <t>Protest</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally)</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Broadband ISP YouFibre UK Set to Block Internet Email Port 25 from Friday UPDATE - ISPreview UK</t>
+          <t>Anti-Israel protesters gather in Sydney, as Minns’ bans marches - dailytelegraph.com.au</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Wed, 14 Jan 2026 17:43:00 GMT</t>
+          <t>Fri, 16 Jan 2026 08:31:19 GMT</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxNQnpVS3hmb2xoa1lhR2dSdFQ3QU8tcmk5RFVlWkJ6VXhtLTZYTWhqbjdhbmgtSmJqdEo4V1QwLWxUVG9rUGNPX1lwZEFRVkg0STZ4eDhRYnR3b09qR2RIOXl4YldMcGVDQ3gyb20xZUtOTTU3VmZHYXAwc015WGcxZ0VuWUNWeHNqQ2pZN01pdWp6T0RzdDVQdGJHUVRrRUNiQk9nUkJCNWc0UG5yQ2xxMVlFdTRTemNlN1F6M2NkS3BNZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi5gFBVV95cUxNamU1NlljYkRubFNlWk93bXh5SWFPb1JnUC04WVo5cHJidEI2ZjZpQ1B1bGdMdm9VdkxnejlnWVVMd3V5WXRmcEpyc1pFMGp2QVYyX0NYMl9hdkVpUWo2YlJibWlVR2h1WklCZzZOdUdjdjhscGRicE1BUnItandTRm94RzVMUjN2OFkyMW5oZ0tXanFwWkVOaDNwMnQ5enByYmZlbGE0UlhHTW5OclFLb2N3S2lQSTdqVTEwNWZXME1IMlBBcW0wY2JYUDF4X2swS2NoV0J4Wll5U19fQ0kwdy1uNzFqUdIB6wFBVV95cUxObGZsMnhuajk3RFY0cVIzU1FoZmk1U2hqNTZNOXRsNWtvUGU5OXJQQVJxWTBvUFRFMVhLMXh3MllQUHdUUFo2dHk3dmd0QlBtajNicTFiTWc2a3cwaDRaakV4OTh6SHhZdnJDOGJHQTFwUW0waUJOOHAzejFiU2MzaEJ1UjdPU0NQQTh0b3N3eVh1QWNyTVloQjdLUUJBaDIzNU54czNyY21kVXFUNE5JSXphSFlyWnNFa2taWVJSWTRRcmlpN0tuTlNNTkhVcWo4alZkX1Y3Mlh0R0pfRlBJUTJmRDU4RnhPUnE4?oc=5</t>
         </is>
       </c>
       <c r="F61" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Supply_Chain</t>
+          <t>Protest</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally)</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Marina Port Valencia Obtains LEED Platinum - Yachting Pages</t>
+          <t>RBC Capital Reaffirms Their Hold Rating on Strike Energy Limited (STX) - The Globe and Mail</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Fri, 16 Jan 2026 11:37:14 GMT</t>
+          <t>Fri, 16 Jan 2026 02:16:07 GMT</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxNQVBYWFp5dEtRTG81cmZ6UkJTZU9ZNlBOQnVSQ0ZtakpJT0tKODZscHM0WHRjWVJBUllILVFid1l1OGNCNlJtQW1DM1Z4QkNyS1F3ZWM3dGtsb0k4VEdlTGZ4Vl9ib1ZwcHBEZ2VVc2hJRDR5eG9GMFE5am1jX3VZTl9lc0JYcHJsb1dJNE9kLTI?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi5AFBVV95cUxOeHdFNkR6Z0MwS0tRWEdMQ1VOb09YdjRETVdianY1WlRlOF82bWZfb3lFbWdmOFV0Si1mUVlKdmcxZEp6YURjVUtnSTNxWEt0dHAyZHRoRlk3bW40S2NZazYxME5RMENWeXV2NFprbmxoUDhCLXl0eFRheEN6SjFQR2NTRTdzXzBUVUFSeWxjbFJJdVV0cDBqUWNGUGlxeXlLR0VPdGVBUlRWcnpFVnlVdzlQWHExRXVmWFZIdEt0T1dBMXQydmw0WUZlVFp4T1hDWkFvX1gxSi14ajlJT3BmWE1KUjI?oc=5</t>
         </is>
       </c>
       <c r="F62" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Supply_Chain</t>
+          <t>Protest</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally)</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>One person left with serious leg injuries in Ellesmere Port collision - Chester Standard</t>
+          <t>In Kharkiv region, Russian troops strike police car heading to evacuate people - Ukrinform</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Fri, 16 Jan 2026 09:15:42 GMT</t>
+          <t>Thu, 15 Jan 2026 12:09:00 GMT</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxPWndBeFUwOTQzSlNHTmx3blYzcjBObXZPN3hDN1RFM0pfN3F4RUdvUE1zZjJZdnFNMFJiOWd3a3hmVENISFprWkZ2YkVITHJHMEMwRnFtSDNPTklSUExiNkMyenowVS1NZXR1Ty1qSVplazcwYjZoV0tWSFVJMzR3S1JLeUNxOVlnMlFLM0poclNFTTdGcWk0Y25XRkR2U1hTT0QyZEFpRms?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxQT1Y2N0lmcWJSOW4yN3RudnRUQjlyTWtPS0syc2lQNEhwWEkyY2tDNUlnMnZyWGZsallVRWZIR0FsSV9vQWZrN3ctbWlLQU9nc2ZLX1lmUHlSX1pEN05BZElyLUF0RzNLSE51R1U0U1NYcnB4NDRYTXJzQ2JJSTNMa0hTNmNEYW9DWWFwbExLa1ZmOUYzZ1BHdzJCaVlpQWhnZi1ZY2NFMGNtcHJnRzJCLWU5OFVkb2NZX1pSdW9lZzViSWhqU0E?oc=5</t>
         </is>
       </c>
       <c r="F63" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="64">
@@ -2333,21 +2333,21 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Met Police staff strike suspended for new pay offer vote - BBC</t>
+          <t>Hindu Villagers Protest and Police Stop Mosque Work in UP’s Jaunpur - Clarion India</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Tue, 13 Jan 2026 11:21:19 GMT</t>
+          <t>Fri, 16 Jan 2026 06:53:56 GMT</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiXEFVX3lxTE9ab1ZlaXdqYmJzQ0tGakpQMDFBc1QwTGlSd3hoNTBlVGJhVzhJZkFUYXR4S2ZsUWNYNzJ6dWhYdXMwdXRoZ2s2M05XdTVUdE1Bd1A3UWpKOHR4S2x60gFiQVVfeXFMTjRleHJoTkk4bTNmbzZzb1VZSkNiMmUxR3ZmWld1OWFHQUVDdlVQUE1rSXpUWHpYVlV0OTVCSVRrQ09rUDg0MlBlSTluUkp2cEhHODQ2Q2dnTHVORDJiTHhtaUE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxNcmNGOHl2N1FEeXpTSWJ1a1Z4MElXeHRnWlFiV2VhZnd0VW1KZ0p1ZjVBdmh1N3l3WkpYMTJscnJPOVlUMno0WTFGbkpRWXVFQmYweS01Yk5CR2NvNU1NcFMtcnpoWXV5MXNybFVwQThnMTBIRTFUUllKSmJ2UzhFSzNSVHVUS1k3RzhuOFhEcjI5eE9PcXl3?oc=5</t>
         </is>
       </c>
       <c r="F64" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="65">
@@ -2363,21 +2363,21 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Iran deploys riot police to shut down protests - France 24</t>
+          <t>‘People’s State of the State’ protest makes homelessness center of attention - Ocean State Media</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Fri, 16 Jan 2026 09:37:40 GMT</t>
+          <t>Wed, 14 Jan 2026 17:18:12 GMT</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMif0FVX3lxTE5Sc0E3RFctNmtpMGdlYkM2cWdlRWF1NzU4MnZ2ajdzUHVxMkRzaUcySmZ6ZXBDcC1HQl8wQzN1MkNmZVRYQnhfVW5zMEZsOHJEUWp6em5EYzhyd1BzSjhyV1MyWUQxaC1hNWpMbFVob3UyTl9WSlQtSEpSX1pKbnM?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxNRjJMeFVveFJJT1FabGlCVlJkZllsaWZFUDZZZFBzMENKRUh4dHJLUjdQZGZfN19oQWJ5eWN4X0xVUE9VcUVsSDY2bk1tTl9KV29Obnk5SkZ5ZFhLbjROdi1iOHdKSGEyaGtXT3NsRVFnNVk4RHhIeFhMRWV0dHc4R3UxYV9MUWVWcm11SVFoVlZfTlRtZnBmaUJCeHVBd3ltR09qZlpFeUhLeG1DRVdRSjZHOA?oc=5</t>
         </is>
       </c>
       <c r="F65" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="66">
@@ -2393,21 +2393,21 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Eyewitness: a New Year and resource draining protests recommence - Police Oracle</t>
+          <t>Excelsior Capital Calls Board Spill Meeting After Second Strike on Pay Report - TipRanks</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Thu, 15 Jan 2026 16:45:43 GMT</t>
+          <t>Fri, 16 Jan 2026 03:00:32 GMT</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxQVk9zNkhpVE1hRUU0LTJMd3lJYXF5WVVEM0kySFNqYlFDVXQwOXNpS0dVVGxsQVBsS1lDZ1pjZDluU3dDS0ZXSnZrb2hFVG5vWVh2MUJaUFhhQ2NxVHhQMFdGQnRpNEJ1WERibDdhNHVoN281bXBiWlo4SzEtaG51XzlTYlMwQmZCaFJrZEpSSENfTVBpNXNuUWNKVzkyeGVNdGdfTDN3c0JMbEpNUmc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiyAFBVV95cUxNM0tGN3N0ODZjRU5jcWEtQm05Z0tKak5QZVJyUmlHWWJvWlhERy02X0VNdjNYVGVyblp5NUNBM2dPXzZDd0xEQnd0OUI0SzhtRXVWLTFGZ1ZJS19lUnpPZUZJdk04TFo3WVdYcWUyenRreHhQeTU1blFWMlVmR2tscWMzZUhMWWd3c21xRmV1ZWdKeldYenFXajY0LUI5ZEt3WDFoNzQ0dXNkdE5ubjNNUzRtVGl3TUY4VXE4VGkwTlRabDNfZ2V5VA?oc=5</t>
         </is>
       </c>
       <c r="F66" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="67">
@@ -2423,21 +2423,21 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Police called in over weekly Palestine protests outside Royal Stoke - Stoke-on-Trent Live</t>
+          <t>March shooting involving Colorado Springs police ruled justified - KKTV</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Thu, 15 Jan 2026 17:04:00 GMT</t>
+          <t>Fri, 16 Jan 2026 01:32:00 GMT</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxOQlJIWm5OS1dpOTFRQVg2VHpVOE5NNDJlaGEyd1c2MWtSMWRoVXdaMFE5QlhrbUVuY3VyeHhWRzY4YzdNTy1TZWxDMUZoUC0zWkZPZzZyMi1sb3p2bzBRanNJR2hoMG00a3dmekd2cW5lT09VTE1rc0ZxWVVJQ2N1c2ViSkM5ZDhJcUU5eHVVQWxUZVdiV3B5cDl1dUJJdTR1Mjcw0gGoAUFVX3lxTE1PSkRuOS1vaVJLMmg1Z2RoNDduVDNoNVh0QnNJb2x0TTlGQ2ZDOERnaVQ4OG5vd1pZYm42eGpfM0NuWS01eUU2YUdCbThLS05ZekdETmF2dl96b1BwN0UweXJSVjRleHREbGdVYkZXSURQUWw2MXh1QzB1VG4wWVpqY0VsazR1MXNtNlQ4V1g0ampVUUdTRzdlTlloV0V2eExJaElKVEs1Uw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxQUFZJZGpGWnBHbzJyczkwOElHSWtLMEZCeW1BZkVRWTg1QmFaNFh5al9hYzhIZ0hXbjQ5TC0xelc3ZkNQTVZwTjUyTkdQYkgzVFFNaWZnamtHMTU4WU1oTW5yb3Z6OWtkSjZfT1VrQnVSMExtOGtCZlllYTl5dmxZb3RXSF9sYkdtT3hZZWxobmFxazY1TEhOb3BuVERHZ9IBsgFBVV95cUxOX0FCaE45c2xXLTRYYkVzbHB1QUhKc3FPcTBOSXpjTkdQVGxBbWlITFNGMmxjcUpTSXQ5RTNtMFFGMXBDa21Rb2w4VnpYYlNvM3lHeGZkOXBnOWFDVGlmYnQtengyNWxCOTRaMjRGX3kwN192WVhOTWRFN1l0RU1NR1ZCNG11U2lQaHpUMmhBb2FWT2h0eERHRkkyeGM2SjEzcEN0cXRHcXdNdXBiQ2l6cUZn?oc=5</t>
         </is>
       </c>
       <c r="F67" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="68">
@@ -2453,21 +2453,21 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Protester ‘fakes’ being struck by police patrol car during ICE demonstration - The Independent</t>
+          <t>Protests after man shot during US federal raid in Minneapolis - Al Jazeera</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Wed, 14 Jan 2026 13:45:00 GMT</t>
+          <t>Thu, 15 Jan 2026 10:04:01 GMT</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxOWFM3VnpoZkxXR3M4UWRJMy10U1JURXVTN0JoMWYzY01ITnNJdkdGUVRhcWk5RHJUb0NzWGhUdUxsZGJyTzlROHVVZzRKMlBHZVlSc1dGdmFzTG1vLVBkWjNMTUR2R0JDbW9haHA3UXNfckdVZG91QXRlLThpRW9xd2hCS09qeTB0eUVIMmZqSWw4VHVrWHdDb3JKOA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxPOU1vMG9TSEhkc3B3R3VWUDNaY3lTdk5iYnV0U01lbUNINl9CckVKN3ZkZFJ5ZC1TTkhWc2MzdTNQbThsMTRObDBrVEcxNUR3RUpmRTFTTVJVMmxGS3haQlY5eVdxWFdUemZ5eDQxYXJPUUlnc0kzOUVaeVlLckpSbDRfMTZnVHdQU043OGpaNWMtZ2VrQmgwdkU4NWhxWm9VTjFMRFFBSDc0elktUmtDSHpn0gG3AUFVX3lxTE5sbnV5dnhBeGpLQlhxX0lBbWhaR1hkQWpOOHpjNDVwdTg1N3NGbTV5eFQ1NWF0ODJCcWtKZnlCbkY4aWNoMi1wVE9nVjJoYTFCLXUyU3ZXUXQyXzFKSXRBaDRBM1ZvcGVHTTJWczFTV2FHVmZ5X3Nqay16X2k3YmxxYkNtUHZqbjYyYWJKeWY3akhQTGpWT2ZwcXZKZmlIak1WSGx2RnRubGVDMnEzM3NZX3BJQm5Ndw?oc=5</t>
         </is>
       </c>
       <c r="F68" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="69">
@@ -2483,291 +2483,291 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Police strike again as bowling alley thief convicted in Cornwall - Yahoo News UK</t>
+          <t>Court Slams Israel Police Over Mishandling of Bibileaks Case - Haaretz</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Wed, 14 Jan 2026 10:44:14 GMT</t>
+          <t>Wed, 14 Jan 2026 21:47:00 GMT</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMif0FVX3lxTFBlWHlwc0tRSHdKcTEycHpCNzRnQV9sWVluaEFRQ0N3QXM4M01JZGpQOFlfN0dpVVBjdjZ0TTVqSy1FRUhrbVpEclU2LVNtYjhXSFlsZnVOY2JaTXF6c3l5TEhYRXZtQTB0eE9xRnduVTg5bVk5V21IOWE2LWFRRlU?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi9wFBVV95cUxPOUYyNG5TbVNzZjBiZ0xXXy1WV2h4RmNZaHhuSXNQLVpkUmJHOGhteGd5enpFLUdNQ0o5a01qZlNfMEZZdnJieGZBaTA3NHZqaENQZmJ0Yno5b25rcWdpaWd6XzlWY1AwRzFzQkJNSGdmQnFSeWpJU1IxejE2RGFhVW9VUWs0dkxQcUNfYWxKTVA2T2JuRVdXbkY2aHN2OTRGa3NaZEV6YlFVaTBHY1ZIZktESnRBU28waVV2cmh6b2NpYVBWdXc3WUpQaEpGYVhjVnVvb0xFWl92RXNqamhQbXh0YndpYzJXam0wR1FYNkZpQXlBYnpR?oc=5</t>
         </is>
       </c>
       <c r="F69" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Protest</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally)</t>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Anti-Israel protesters gather in Sydney, as Minns’ bans marches - dailytelegraph.com.au</t>
+          <t>Red tape to be slashed for British robotics and defence innovators - GOV.UK</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Fri, 16 Jan 2026 08:31:19 GMT</t>
+          <t>Fri, 16 Jan 2026 00:07:36 GMT</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi5gFBVV95cUxNamU1NlljYkRubFNlWk93bXh5SWFPb1JnUC04WVo5cHJidEI2ZjZpQ1B1bGdMdm9VdkxnejlnWVVMd3V5WXRmcEpyc1pFMGp2QVYyX0NYMl9hdkVpUWo2YlJibWlVR2h1WklCZzZOdUdjdjhscGRicE1BUnItandTRm94RzVMUjN2OFkyMW5oZ0tXanFwWkVOaDNwMnQ5enByYmZlbGE0UlhHTW5OclFLb2N3S2lQSTdqVTEwNWZXME1IMlBBcW0wY2JYUDF4X2swS2NoV0J4Wll5U19fQ0kwdy1uNzFqUdIB6wFBVV95cUxObGZsMnhuajk3RFY0cVIzU1FoZmk1U2hqNTZNOXRsNWtvUGU5OXJQQVJxWTBvUFRFMVhLMXh3MllQUHdUUFo2dHk3dmd0QlBtajNicTFiTWc2a3cwaDRaakV4OTh6SHhZdnJDOGJHQTFwUW0waUJOOHAzejFiU2MzaEJ1UjdPU0NQQTh0b3N3eVh1QWNyTVloQjdLUUJBaDIzNU54czNyY21kVXFUNE5JSXphSFlyWnNFa2taWVJSWTRRcmlpN0tuTlNNTkhVcWo4alZkX1Y3Mlh0R0pfRlBJUTJmRDU4RnhPUnE4?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxNNnlWNl9MNzlDYVB2eUc2M2ExYlFIUWdYbE0tUVJHN2RNeG12QjViTG5scFFNVEFpNjhLajk0U3IwSEJvMUphWU0td3BLT1JJN2xZOUY4RnNwOTZ5RkhILXl6cU9qY0JGMlh4TzFib1RQeVRjYmtUWC1MRUZiQVNxaWJPWFVXNE16NW5udklyRG5RN2pWSjlFT2c3N19NSV84cnpF?oc=5</t>
         </is>
       </c>
       <c r="F70" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Protest</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally)</t>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>RBC Capital Reaffirms Their Hold Rating on Strike Energy Limited (STX) - The Globe and Mail</t>
+          <t>Sadiq Khan says AI could destroy London jobs if not controlled - BBC</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Fri, 16 Jan 2026 02:16:07 GMT</t>
+          <t>Thu, 15 Jan 2026 22:07:33 GMT</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi5AFBVV95cUxOeHdFNkR6Z0MwS0tRWEdMQ1VOb09YdjRETVdianY1WlRlOF82bWZfb3lFbWdmOFV0Si1mUVlKdmcxZEp6YURjVUtnSTNxWEt0dHAyZHRoRlk3bW40S2NZazYxME5RMENWeXV2NFprbmxoUDhCLXl0eFRheEN6SjFQR2NTRTdzXzBUVUFSeWxjbFJJdVV0cDBqUWNGUGlxeXlLR0VPdGVBUlRWcnpFVnlVdzlQWHExRXVmWFZIdEt0T1dBMXQydmw0WUZlVFp4T1hDWkFvX1gxSi14ajlJT3BmWE1KUjI?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTFBZQ3NJbXV0eE1wal9OZGFiVVRWYXlJQkZocVo4d3RER3REZngxLWpzZGNWTlA2cnVBZlFRSjNYLWYwMWtNWXgyb2hUV1I0YXdwbWZxeW5lNGx4d9IBX0FVX3lxTE1JZ2JibGFwOC01ZDFRMFNzUzNRRGd0ZkpfRm5tSU50czFRZkRDcmNsR1lZTVZOYUlOdzJsdVZ6V3M5eXpadngtMFpmaFRYVFdWNUtoOGE3N2V2M1RsQm9v?oc=5</t>
         </is>
       </c>
       <c r="F71" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Protest</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally)</t>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>In Kharkiv region, Russian troops strike police car heading to evacuate people - Ukrinform</t>
+          <t>AI in pensions admin: Start with members, not technology - Professional Pensions</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Thu, 15 Jan 2026 12:09:00 GMT</t>
+          <t>Fri, 16 Jan 2026 10:31:41 GMT</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxQT1Y2N0lmcWJSOW4yN3RudnRUQjlyTWtPS0syc2lQNEhwWEkyY2tDNUlnMnZyWGZsallVRWZIR0FsSV9vQWZrN3ctbWlLQU9nc2ZLX1lmUHlSX1pEN05BZElyLUF0RzNLSE51R1U0U1NYcnB4NDRYTXJzQ2JJSTNMa0hTNmNEYW9DWWFwbExLa1ZmOUYzZ1BHdzJCaVlpQWhnZi1ZY2NFMGNtcHJnRzJCLWU5OFVkb2NZX1pSdW9lZzViSWhqU0E?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxOb1BYdU5DaWxiblFNNUZkakZvUV9mVkc4RUFEbDFlN0U1UVJQQWQ3U2dTWWhvWmxmWTlpWmJIWmo1SnFSQThYc1BZLXJxTENHMjdQRC1aOVNVNnlUQ0FaYy0yalJtZTJFYldSOGU1NUZMTlN1VXBURTNMRHhuNTNkbXlrWG1PWXlONTBSX0xSQ0ZueFIydDBSRThmSQ?oc=5</t>
         </is>
       </c>
       <c r="F72" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Protest</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally)</t>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Hindu Villagers Protest and Police Stop Mosque Work in UP’s Jaunpur - Clarion India</t>
+          <t>AI will transform the ‘human job’ and enhance skills, says science minister - The Guardian</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Fri, 16 Jan 2026 06:53:56 GMT</t>
+          <t>Fri, 16 Jan 2026 09:46:00 GMT</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxNcmNGOHl2N1FEeXpTSWJ1a1Z4MElXeHRnWlFiV2VhZnd0VW1KZ0p1ZjVBdmh1N3l3WkpYMTJscnJPOVlUMno0WTFGbkpRWXVFQmYweS01Yk5CR2NvNU1NcFMtcnpoWXV5MXNybFVwQThnMTBIRTFUUllKSmJ2UzhFSzNSVHVUS1k3RzhuOFhEcjI5eE9PcXl3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxOeTQ5ZVZtcHJzVXhidWl6Y3pCaXVPc0QtTS1Nb29xTTB2RnR2c2FxektwTk5WclM3TzRrWlQ0dDRlcEFKVkJZYXJQQ2pTeUVtcTJMRF9uSy0ydG1JY29ZYXk2Qk9lenJEM2FrTGMzN2NnR3ZkRlpham5FZWJ1YmtXRGw5SmJFSm9fc2ozcmZHX20tV0xVX0dZYTJLSFduSmVBOUFGQWs1Zmp1NzJzTE1hNE9EWGtPamhvMnlHRmVmNEc?oc=5</t>
         </is>
       </c>
       <c r="F73" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Protest</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally)</t>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>‘People’s State of the State’ protest makes homelessness center of attention - Ocean State Media</t>
+          <t>Singapore: MAS consortium releases comprehensive AI Risk Management Handbook for financial institutions - Linklaters</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Wed, 14 Jan 2026 17:18:12 GMT</t>
+          <t>Fri, 16 Jan 2026 10:26:33 GMT</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxNRjJMeFVveFJJT1FabGlCVlJkZllsaWZFUDZZZFBzMENKRUh4dHJLUjdQZGZfN19oQWJ5eWN4X0xVUE9VcUVsSDY2bk1tTl9KV29Obnk5SkZ5ZFhLbjROdi1iOHdKSGEyaGtXT3NsRVFnNVk4RHhIeFhMRWV0dHc4R3UxYV9MUWVWcm11SVFoVlZfTlRtZnBmaUJCeHVBd3ltR09qZlpFeUhLeG1DRVdRSjZHOA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0AFBVV95cUxPZVhOdTRQWktZWnAzbDdUbTFFcFRQLUhZYWFLYnFBMldjNXpZZlotYm4tb0Nmb0poV3lPMTNrRGZKMzlWVWFib3hfajB2ZUlCSFNrODJEcW5uVFo0RVpoV2gxbFFkMC0zZVEyNjY5VURHZGR5aFoxTFp6TkpZU2dEVmEwZW41X285Y3RrUy1lejdBRm03b0lGTUVQcVRWeTBJYjlOLXdBNk9kaVRINjZkeTVxTWZZX0tiWHFFdjkyU240dWJaYU41RHBfZHJPaFRJ?oc=5</t>
         </is>
       </c>
       <c r="F74" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Protest</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally)</t>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Excelsior Capital Calls Board Spill Meeting After Second Strike on Pay Report - TipRanks</t>
+          <t>New office for AI to 'explore opportunities' for Isle of Man - BBC</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Fri, 16 Jan 2026 03:00:32 GMT</t>
+          <t>Fri, 16 Jan 2026 10:06:29 GMT</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiyAFBVV95cUxNM0tGN3N0ODZjRU5jcWEtQm05Z0tKak5QZVJyUmlHWWJvWlhERy02X0VNdjNYVGVyblp5NUNBM2dPXzZDd0xEQnd0OUI0SzhtRXVWLTFGZ1ZJS19lUnpPZUZJdk04TFo3WVdYcWUyenRreHhQeTU1blFWMlVmR2tscWMzZUhMWWd3c21xRmV1ZWdKeldYenFXajY0LUI5ZEt3WDFoNzQ0dXNkdE5ubjNNUzRtVGl3TUY4VXE4VGkwTlRabDNfZ2V5VA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiXEFVX3lxTE9oOGtJaFp1R3B3VjkwZkdGaFF4U0U3Vi15cEV3SWh1V014WW10d0dfclladTBVUWtyalVNRmlTSnBiWnZURW03a2dxSm1oOVhiaGdYR0N6VThtVE9x0gFiQVVfeXFMTUpDRnBMM1I3WHlITEJEVllXYU53MS1mSGE0Z0lERl9oQU5RejFCT1VDNklndEpiMzBvdXhVdDVWdURRMTBRWU8zYWFwbzVPa05YNjEzZTRfLVpDb0tzdDJIaVE?oc=5</t>
         </is>
       </c>
       <c r="F75" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Protest</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally)</t>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>March shooting involving Colorado Springs police ruled justified - KKTV</t>
+          <t>AI, Robotics and Human Reskilling: The State of Hospitality Report 2025-2026 published by Les Roches Spark - FE News</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Fri, 16 Jan 2026 01:32:00 GMT</t>
+          <t>Fri, 16 Jan 2026 11:39:31 GMT</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxQUFZJZGpGWnBHbzJyczkwOElHSWtLMEZCeW1BZkVRWTg1QmFaNFh5al9hYzhIZ0hXbjQ5TC0xelc3ZkNQTVZwTjUyTkdQYkgzVFFNaWZnamtHMTU4WU1oTW5yb3Z6OWtkSjZfT1VrQnVSMExtOGtCZlllYTl5dmxZb3RXSF9sYkdtT3hZZWxobmFxazY1TEhOb3BuVERHZ9IBsgFBVV95cUxOX0FCaE45c2xXLTRYYkVzbHB1QUhKc3FPcTBOSXpjTkdQVGxBbWlITFNGMmxjcUpTSXQ5RTNtMFFGMXBDa21Rb2w4VnpYYlNvM3lHeGZkOXBnOWFDVGlmYnQtengyNWxCOTRaMjRGX3kwN192WVhOTWRFN1l0RU1NR1ZCNG11U2lQaHpUMmhBb2FWT2h0eERHRkkyeGM2SjEzcEN0cXRHcXdNdXBiQ2l6cUZn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi4AFBVV95cUxQc1BfOWJ3WHctd1lLMmtKYU9IVEctLWRBTXZsTks1NGJQSFpyZlY5aC02c2NoLTMzTEliZk0wQlhYUGVGbThvY2FYSVMtNjBSUnVmaW4zTlB6N2F6YkpCMUUxWDNMcUR5ZE5FbVBGbmU3Z2lGQllNb0RUWldMTXFnYzlfU2hQdFdmVFFMX0NkTGVJaEE3V05udTBkaENYZmRESWVENFJLNkdsOHVWSmFVMVFFcms3NUpLM1ktOTg1N28tai1yZ1l3eWJJR3J6U3ZwNjVGQm1zM3JIaksxTklXMg?oc=5</t>
         </is>
       </c>
       <c r="F76" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Protest</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally)</t>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Protests after man shot during US federal raid in Minneapolis - Al Jazeera</t>
+          <t>Cybersecurity and Digital Rights - coe.int</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Thu, 15 Jan 2026 10:04:01 GMT</t>
+          <t>Thu, 15 Jan 2026 13:36:56 GMT</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxPOU1vMG9TSEhkc3B3R3VWUDNaY3lTdk5iYnV0U01lbUNINl9CckVKN3ZkZFJ5ZC1TTkhWc2MzdTNQbThsMTRObDBrVEcxNUR3RUpmRTFTTVJVMmxGS3haQlY5eVdxWFdUemZ5eDQxYXJPUUlnc0kzOUVaeVlLckpSbDRfMTZnVHdQU043OGpaNWMtZ2VrQmgwdkU4NWhxWm9VTjFMRFFBSDc0elktUmtDSHpn0gG3AUFVX3lxTE5sbnV5dnhBeGpLQlhxX0lBbWhaR1hkQWpOOHpjNDVwdTg1N3NGbTV5eFQ1NWF0ODJCcWtKZnlCbkY4aWNoMi1wVE9nVjJoYTFCLXUyU3ZXUXQyXzFKSXRBaDRBM1ZvcGVHTTJWczFTV2FHVmZ5X3Nqay16X2k3YmxxYkNtUHZqbjYyYWJKeWY3akhQTGpWT2ZwcXZKZmlIak1WSGx2RnRubGVDMnEzM3NZX3BJQm5Ndw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMifkFVX3lxTE9sN0V4UjJvV2ozM3EyZjFvbVlSM2hFMklQOXZ0NXhhWE9GRm83TXV0c1o1OC1uWldOWEtTQ3pJU0s2MlpTWjhfOGkybm1kUHRXa0VhRjh1bG9hZENnVEh2d3NZY3U1WkV2Q0FKcnYtMzRmWVJxaXNwb0VLQzFsQQ?oc=5</t>
         </is>
       </c>
       <c r="F77" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Protest</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally)</t>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Court Slams Israel Police Over Mishandling of Bibileaks Case - Haaretz</t>
+          <t>NHS England launches supplier registry for AI scribing tech - Home | Digital Health</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Wed, 14 Jan 2026 21:47:00 GMT</t>
+          <t>Fri, 16 Jan 2026 07:31:25 GMT</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi9wFBVV95cUxPOUYyNG5TbVNzZjBiZ0xXXy1WV2h4RmNZaHhuSXNQLVpkUmJHOGhteGd5enpFLUdNQ0o5a01qZlNfMEZZdnJieGZBaTA3NHZqaENQZmJ0Yno5b25rcWdpaWd6XzlWY1AwRzFzQkJNSGdmQnFSeWpJU1IxejE2RGFhVW9VUWs0dkxQcUNfYWxKTVA2T2JuRVdXbkY2aHN2OTRGa3NaZEV6YlFVaTBHY1ZIZktESnRBU28waVV2cmh6b2NpYVBWdXc3WUpQaEpGYVhjVnVvb0xFWl92RXNqamhQbXh0YndpYzJXam0wR1FYNkZpQXlBYnpR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxPemg1Tk9ESTlMVWNTaVdnMzE2azNBYk82WlNySkZMRzhKNnBDUVR4MDVsWW4yVmlCYjBjWVQ4T3h6bHpyaGVYY3hFS2l1ek9oMmVPOTZ5b2toZTRzc3RiVFJLSW54QTh2bXd0Vl9LZUVvbUNZLXloZWxUOExOZ2pCWXZ2aUFZdkJORkJTbDdDSXRBc3otTWlXS09WalIxdk0?oc=5</t>
         </is>
       </c>
       <c r="F78" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="79">
@@ -2783,21 +2783,21 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Red tape to be slashed for British robotics and defence innovators - GOV.UK</t>
+          <t>AI and creativity ‘at a tipping point’ - PR Week UK</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Fri, 16 Jan 2026 00:07:36 GMT</t>
+          <t>Fri, 16 Jan 2026 11:10:11 GMT</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxNNnlWNl9MNzlDYVB2eUc2M2ExYlFIUWdYbE0tUVJHN2RNeG12QjViTG5scFFNVEFpNjhLajk0U3IwSEJvMUphWU0td3BLT1JJN2xZOUY4RnNwOTZ5RkhILXl6cU9qY0JGMlh4TzFib1RQeVRjYmtUWC1MRUZiQVNxaWJPWFVXNE16NW5udklyRG5RN2pWSjlFT2c3N19NSV84cnpF?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMie0FVX3lxTFBTMy0xamJBaUJjcF9NMlRwMFc3dDRCNHJLaC1Cc1laa2tzT2Y2a0JoZldhNHpuampPQW5xeElMcDNibVRTM3BSM2RMX1padEVTbWNvay0wdy12NHFTTjhQSnpJTFN4LXNfRzZYQk1ESERScVZTZ2hjc1RBYw?oc=5</t>
         </is>
       </c>
       <c r="F79" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="80">
@@ -2813,21 +2813,21 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Sadiq Khan says AI could destroy London jobs if not controlled - BBC</t>
+          <t>Société Générale Drops Internal AI for Copilot - DirectIndustry e-Magazine</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Thu, 15 Jan 2026 22:07:33 GMT</t>
+          <t>Fri, 16 Jan 2026 09:03:00 GMT</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTFBZQ3NJbXV0eE1wal9OZGFiVVRWYXlJQkZocVo4d3RER3REZngxLWpzZGNWTlA2cnVBZlFRSjNYLWYwMWtNWXgyb2hUV1I0YXdwbWZxeW5lNGx4d9IBX0FVX3lxTE1JZ2JibGFwOC01ZDFRMFNzUzNRRGd0ZkpfRm5tSU50czFRZkRDcmNsR1lZTVZOYUlOdzJsdVZ6V3M5eXpadngtMFpmaFRYVFdWNUtoOGE3N2V2M1RsQm9v?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxOSmZpMkFCVEt6V010Z1F3S3dOZXBadWlFYU10ODNTV2RxSjVXRzJjWWc3SHY4Nm42clFmXzJBMVN6aGVyNEVmdXNkSjgxUm5xWFV2WWoxWGhENk1HZ3ZSUnhRS3BPVTJXa0VpaFJLUzQtcWNfQ2g5R1ZiMWhBZ2tMcElyQVN1UUc5NjRPVGt0SkhDbU1IRlcxbHpUSzNTRVdkcU16XzUzNA?oc=5</t>
         </is>
       </c>
       <c r="F80" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="81">
@@ -2843,21 +2843,21 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>AI in pensions admin: Start with members, not technology - Professional Pensions</t>
+          <t>Reuters digital report 2026: journalism’s pivot – navigating the AI and creators squeeze - International Federation of Journalists - IFJ</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Fri, 16 Jan 2026 10:31:41 GMT</t>
+          <t>Fri, 16 Jan 2026 11:40:47 GMT</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxOb1BYdU5DaWxiblFNNUZkakZvUV9mVkc4RUFEbDFlN0U1UVJQQWQ3U2dTWWhvWmxmWTlpWmJIWmo1SnFSQThYc1BZLXJxTENHMjdQRC1aOVNVNnlUQ0FaYy0yalJtZTJFYldSOGU1NUZMTlN1VXBURTNMRHhuNTNkbXlrWG1PWXlONTBSX0xSQ0ZueFIydDBSRThmSQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi4wFBVV95cUxQSEdZX3lHN3REUFIzNTRZU0UzUTM4dFJneHl2UnFnbV9RTGZCWG9EcDFvRHF3d1B4Xy1ZckRMb01GZUtQYmVNVkgzLVJ6UzFzblVwNmZrVS1naGdBVG5fUFlsa3hnWUx6T3VsUmJ1UGhhN2hZQTBnTkowS0lOektyaWd5djdGTmhvQk0zREVkWWZabzFYeloxcl9wMS0tYWFKQzRmTWNYYTlPeFo2QWpCLWpzU3g3RDZuYmxDTTRfa0R0NHB4RHJja2ZxYWxybWNkV2JYa2xLbnlyamU1djhxNC1mMA?oc=5</t>
         </is>
       </c>
       <c r="F81" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="82">
@@ -2873,21 +2873,21 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>AI will transform the ‘human job’ and enhance skills, says science minister - The Guardian</t>
+          <t>Column: People can't just rely on AI to function in the real world - Exmouth Journal</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Fri, 16 Jan 2026 09:46:00 GMT</t>
+          <t>Fri, 16 Jan 2026 05:00:00 GMT</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxOeTQ5ZVZtcHJzVXhidWl6Y3pCaXVPc0QtTS1Nb29xTTB2RnR2c2FxektwTk5WclM3TzRrWlQ0dDRlcEFKVkJZYXJQQ2pTeUVtcTJMRF9uSy0ydG1JY29ZYXk2Qk9lenJEM2FrTGMzN2NnR3ZkRlpham5FZWJ1YmtXRGw5SmJFSm9fc2ozcmZHX20tV0xVX0dZYTJLSFduSmVBOUFGQWs1Zmp1NzJzTE1hNE9EWGtPamhvMnlHRmVmNEc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxPelZYbEFZZl91dThfZ1BYY0Z3S0xJTm5xWk9qb3o2VDNtRHl2d3pmbDI5dVRvZTJ6clNMN1VwTG82WWdIRVE2UExlWWxqX1lsN1hqZ3J4Um9RY0dBWDhrVElPeU5aMGlDQ28tcEM5cHpsNmNfazFxbWdxd0h2UzFEbS1kckZQRkZ1c1dxWFMxRmdXS05fcEtxTTFURERQTkpBZXlIWmtn?oc=5</t>
         </is>
       </c>
       <c r="F82" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="83">
@@ -2903,21 +2903,21 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Singapore: MAS consortium releases comprehensive AI Risk Management Handbook for financial institutions - Linklaters</t>
+          <t>Regulatory delays hinder UK tech &amp; AI project delivery - IT Brief UK</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Fri, 16 Jan 2026 10:26:33 GMT</t>
+          <t>Fri, 16 Jan 2026 09:15:00 GMT</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0AFBVV95cUxPZVhOdTRQWktZWnAzbDdUbTFFcFRQLUhZYWFLYnFBMldjNXpZZlotYm4tb0Nmb0poV3lPMTNrRGZKMzlWVWFib3hfajB2ZUlCSFNrODJEcW5uVFo0RVpoV2gxbFFkMC0zZVEyNjY5VURHZGR5aFoxTFp6TkpZU2dEVmEwZW41X285Y3RrUy1lejdBRm03b0lGTUVQcVRWeTBJYjlOLXdBNk9kaVRINjZkeTVxTWZZX0tiWHFFdjkyU240dWJaYU41RHBfZHJPaFRJ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMihwFBVV95cUxORk1DNTE1clhqdjdoeml0NEx4ZDRiMzlQNS1NaHpnRTFUa3hGRk11RldERUItUi1QTkRwdEdlMUtsdDFuN0Z2UjFhV25LbGhYUmxGNnNnQjhRT3ViU2ZzQ2F5M0FKTzE5dkVmQnNLN0otM2Z3Z3M3X3dQUVo1aTRoZnNYam11aG8?oc=5</t>
         </is>
       </c>
       <c r="F83" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="84">
@@ -2933,21 +2933,21 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>New office for AI to 'explore opportunities' for Isle of Man - BBC</t>
+          <t>Explainable AI and the future of financial crime prevention - FinTech Global</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Fri, 16 Jan 2026 10:06:29 GMT</t>
+          <t>Thu, 15 Jan 2026 17:31:22 GMT</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiXEFVX3lxTE9oOGtJaFp1R3B3VjkwZkdGaFF4U0U3Vi15cEV3SWh1V014WW10d0dfclladTBVUWtyalVNRmlTSnBiWnZURW03a2dxSm1oOVhiaGdYR0N6VThtVE9x0gFiQVVfeXFMTUpDRnBMM1I3WHlITEJEVllXYU53MS1mSGE0Z0lERl9oQU5RejFCT1VDNklndEpiMzBvdXhVdDVWdURRMTBRWU8zYWFwbzVPa05YNjEzZTRfLVpDb0tzdDJIaVE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxNZGdGN1ZGZWJvTndfdkpvTFgycHdzOHFSWmVTbWVsekRzNVJXWDFzenVPYlZPVUJYZ0NVMnNIR0ZyekJUeHZOZVljTDJNdktISjNFYUtYZEZyVnNCd0lINHFkSGVrZmRybUJqNFZvbFBKLTdjUmJjdlFpejJWTnBjQUZJZ0xSTl9nYVI4aDZ6eFY0anVZbUJSalFB?oc=5</t>
         </is>
       </c>
       <c r="F84" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="85">
@@ -2963,21 +2963,21 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>AI, Robotics and Human Reskilling: The State of Hospitality Report 2025-2026 published by Les Roches Spark - FE News</t>
+          <t>MongoDB adds Voyage 4 AI models &amp; automates vector search - IT Brief UK</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Fri, 16 Jan 2026 11:39:31 GMT</t>
+          <t>Fri, 16 Jan 2026 08:45:00 GMT</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi4AFBVV95cUxQc1BfOWJ3WHctd1lLMmtKYU9IVEctLWRBTXZsTks1NGJQSFpyZlY5aC02c2NoLTMzTEliZk0wQlhYUGVGbThvY2FYSVMtNjBSUnVmaW4zTlB6N2F6YkpCMUUxWDNMcUR5ZE5FbVBGbmU3Z2lGQllNb0RUWldMTXFnYzlfU2hQdFdmVFFMX0NkTGVJaEE3V05udTBkaENYZmRESWVENFJLNkdsOHVWSmFVMVFFcms3NUpLM1ktOTg1N28tai1yZ1l3eWJJR3J6U3ZwNjVGQm1zM3JIaksxTklXMg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiiwFBVV95cUxQSDUxcUpONGZYRXItWF85bko1eW92T0trbFR2TkpDcnV3MXh2STlCZndQRlZaQ2Z5VG9MRUllRjhyZmZ2MVVrNWM3UHlUa01ZbEl6aklQaElOdkFrc3pVSG8ySDhNZVBRS3k1ZENZY2hkMXdzYmZNbmdBb3VCTjMyNEdGU0ItbUZrdGNn?oc=5</t>
         </is>
       </c>
       <c r="F85" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="86">
@@ -2993,21 +2993,21 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Cybersecurity and Digital Rights - coe.int</t>
+          <t>Small Cell Forum maps 2026 push for scalable 5G growth - IT Brief UK</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Thu, 15 Jan 2026 13:36:56 GMT</t>
+          <t>Fri, 16 Jan 2026 09:15:00 GMT</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMifkFVX3lxTE9sN0V4UjJvV2ozM3EyZjFvbVlSM2hFMklQOXZ0NXhhWE9GRm83TXV0c1o1OC1uWldOWEtTQ3pJU0s2MlpTWjhfOGkybm1kUHRXa0VhRjh1bG9hZENnVEh2d3NZY3U1WkV2Q0FKcnYtMzRmWVJxaXNwb0VLQzFsQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiigFBVV95cUxOQWhsVU40UFVXajNER0U4eG9NcVEzWlQxakhIZXFpZnJSX3U2cl9GWTFEN2tZUEhyeGp1WEZESExGSTZhZ0tqTktRVVdJZUZEMGxQVDlpYXJ4VXM4MVN1ZEdHT1NvMGN3RDZ3aGpGZlNyTmR5RDdGbXhEVGVPTE5nRUFDcjI2NGdlbVE?oc=5</t>
         </is>
       </c>
       <c r="F86" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="87">
@@ -3023,21 +3023,21 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>NHS England launches supplier registry for AI scribing tech - Home | Digital Health</t>
+          <t>AI will ‘turbocharge’ Britain’s transport network, says Transport Committee chair - Fleet World</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Fri, 16 Jan 2026 07:31:25 GMT</t>
+          <t>Fri, 16 Jan 2026 08:24:43 GMT</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxPemg1Tk9ESTlMVWNTaVdnMzE2azNBYk82WlNySkZMRzhKNnBDUVR4MDVsWW4yVmlCYjBjWVQ4T3h6bHpyaGVYY3hFS2l1ek9oMmVPOTZ5b2toZTRzc3RiVFJLSW54QTh2bXd0Vl9LZUVvbUNZLXloZWxUOExOZ2pCWXZ2aUFZdkJORkJTbDdDSXRBc3otTWlXS09WalIxdk0?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxNN19hay1TSTBieDZKdkZKN1lCTm1lX0JNUEVTbnNENXNKb1J4UThRMjNRUFV2b0RPbXdjOTdPdVFUN2d5NXBlMzA3UW1BZHRQYnkxRGxZMzFTWkFUdVk0M3BBNEwtYTAzcTgxcmluRmVxX3VocFVTS3d2NUd2akd3cWQtMVpWN0MzX0YtempzcXhGZVVzbktIc2NBV3FDdWpJcVQwdjBn?oc=5</t>
         </is>
       </c>
       <c r="F87" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="88">
@@ -3053,21 +3053,21 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>AI and creativity ‘at a tipping point’ - PR Week UK</t>
+          <t>Cisco's HR chief says AI and ML roles are 'really hard' to fill. Getting execs on the phone helps. - Business Insider</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Fri, 16 Jan 2026 11:10:11 GMT</t>
+          <t>Fri, 16 Jan 2026 10:52:00 GMT</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMie0FVX3lxTFBTMy0xamJBaUJjcF9NMlRwMFc3dDRCNHJLaC1Cc1laa2tzT2Y2a0JoZldhNHpuampPQW5xeElMcDNibVRTM3BSM2RMX1padEVTbWNvay0wdy12NHFTTjhQSnpJTFN4LXNfRzZYQk1ESERScVZTZ2hjc1RBYw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMigwFBVV95cUxOaHJINFBoS2tXYVFST2xSQWlYdkZ4czQyUHo2QmdfNFRqSTZycGdCZWhoNkhYVUVDT2RiSTNCcEpwazFOdFBUVDhkeWplTzBCdlY3djF6VUFMWGxhVDRvY0Fvb3pJRXBGN2Z1WElhYmxncFVzWUNqdVhhdnkzREdjRWx1OA?oc=5</t>
         </is>
       </c>
       <c r="F88" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="89">
@@ -3083,21 +3083,21 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Société Générale Drops Internal AI for Copilot - DirectIndustry e-Magazine</t>
+          <t>Goertzel &amp; Lanier clash over AI autonomy &amp; control - IT Brief UK</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Fri, 16 Jan 2026 09:03:00 GMT</t>
+          <t>Fri, 16 Jan 2026 08:45:00 GMT</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxOSmZpMkFCVEt6V010Z1F3S3dOZXBadWlFYU10ODNTV2RxSjVXRzJjWWc3SHY4Nm42clFmXzJBMVN6aGVyNEVmdXNkSjgxUm5xWFV2WWoxWGhENk1HZ3ZSUnhRS3BPVTJXa0VpaFJLUzQtcWNfQ2g5R1ZiMWhBZ2tMcElyQVN1UUc5NjRPVGt0SkhDbU1IRlcxbHpUSzNTRVdkcU16XzUzNA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMif0FVX3lxTFBYTjYyZGNEb0FyN01UU1FIMHUtMmdhRXFrTk9MR241UUh1V3NtM1d6WDBzVzN3QzdZZmhoN2VWWW1MRGFJU3Y0QWVQQ25jenZ4Ti04UkM4aFRRR2RVNnhVWTRZZGFualB6TThvQ0gtZmdmM05NTm1rM3lObGZHOWs?oc=5</t>
         </is>
       </c>
       <c r="F89" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="90">
@@ -3113,21 +3113,21 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Reuters digital report 2026: journalism’s pivot – navigating the AI and creators squeeze - International Federation of Journalists - IFJ</t>
+          <t>TCS teams up with AMD to scale AI adoption across industries - verdict.co.uk</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Fri, 16 Jan 2026 11:40:47 GMT</t>
+          <t>Fri, 16 Jan 2026 06:15:25 GMT</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi4wFBVV95cUxQSEdZX3lHN3REUFIzNTRZU0UzUTM4dFJneHl2UnFnbV9RTGZCWG9EcDFvRHF3d1B4Xy1ZckRMb01GZUtQYmVNVkgzLVJ6UzFzblVwNmZrVS1naGdBVG5fUFlsa3hnWUx6T3VsUmJ1UGhhN2hZQTBnTkowS0lOektyaWd5djdGTmhvQk0zREVkWWZabzFYeloxcl9wMS0tYWFKQzRmTWNYYTlPeFo2QWpCLWpzU3g3RDZuYmxDTTRfa0R0NHB4RHJja2ZxYWxybWNkV2JYa2xLbnlyamU1djhxNC1mMA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiYEFVX3lxTE1OaU55ZHF4ZU1JLTF3MlRZeE5YdTJRY3B1eS1KNHdkMVByUTVBVTRDQW9fZzBvU2h1cDNpeng2QThYZUprT2VkS2EwRlZOWTR0enl0X19LVHZKWEVwc0Z6cA?oc=5</t>
         </is>
       </c>
       <c r="F90" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="91">
@@ -3143,21 +3143,21 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Column: People can't just rely on AI to function in the real world - Exmouth Journal</t>
+          <t>Gaps and policies in AI- and algorithm-driven discrimination in Europe - coe.int</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Fri, 16 Jan 2026 05:00:00 GMT</t>
+          <t>Thu, 15 Jan 2026 10:35:24 GMT</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxPelZYbEFZZl91dThfZ1BYY0Z3S0xJTm5xWk9qb3o2VDNtRHl2d3pmbDI5dVRvZTJ6clNMN1VwTG82WWdIRVE2UExlWWxqX1lsN1hqZ3J4Um9RY0dBWDhrVElPeU5aMGlDQ28tcEM5cHpsNmNfazFxbWdxd0h2UzFEbS1kckZQRkZ1c1dxWFMxRmdXS05fcEtxTTFURERQTkpBZXlIWmtn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxPbU5UeUpqcnp1eWxjanozcUc0WWNON1FGNXFXS2ktLXpZdlVLaUxKSmh5TkhITlVQX3MyV3duMU1kTUl0VlBHWGs5UFBGRHFuYmxOZmlHR3NTbGZhdThURmU1NWU1RnJjZFZaS2Qyc185RTREM2JtZW5xQTdJX1FJbk90RktyTktxQTZBRFNyYTBXWDRzZEs0OS1mWDFkX05HcWJPR3VwSFU?oc=5</t>
         </is>
       </c>
       <c r="F91" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="92">
@@ -3173,21 +3173,21 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Regulatory delays hinder UK tech &amp; AI project delivery - IT Brief UK</t>
+          <t>Bridging technology and peacemaking at the marking of CMI’s 25 years - CMI - Martti Ahtisaari Peace Foundation</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Fri, 16 Jan 2026 09:15:00 GMT</t>
+          <t>Fri, 16 Jan 2026 11:44:22 GMT</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihwFBVV95cUxORk1DNTE1clhqdjdoeml0NEx4ZDRiMzlQNS1NaHpnRTFUa3hGRk11RldERUItUi1QTkRwdEdlMUtsdDFuN0Z2UjFhV25LbGhYUmxGNnNnQjhRT3ViU2ZzQ2F5M0FKTzE5dkVmQnNLN0otM2Z3Z3M3X3dQUVo1aTRoZnNYam11aG8?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxORVhNV1h6YzZLWWhCNDZidDJrZTFPLXlTaG1DOURhRmN3ZGVIdVZRYllhWlNsc2FvVWsxNDBVWEtYY3daUUxmaDdEWVFBcDFEYzdEUFVWT0t0RzdielBmdUNWTFlXMDg1Z1MxVmVnSmw2QmlWc2ltY1ptOXp0eFpYN2s4TDNCVUUxLWFWOEdQaUd2WFQ5eUR5WHJR?oc=5</t>
         </is>
       </c>
       <c r="F92" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="93">
@@ -3203,21 +3203,21 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Explainable AI and the future of financial crime prevention - FinTech Global</t>
+          <t>Matthew McConaughey trademarks iconic phrase to stop AI misuse - BBC</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Thu, 15 Jan 2026 17:31:22 GMT</t>
+          <t>Thu, 15 Jan 2026 18:34:41 GMT</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxNZGdGN1ZGZWJvTndfdkpvTFgycHdzOHFSWmVTbWVsekRzNVJXWDFzenVPYlZPVUJYZ0NVMnNIR0ZyekJUeHZOZVljTDJNdktISjNFYUtYZEZyVnNCd0lINHFkSGVrZmRybUJqNFZvbFBKLTdjUmJjdlFpejJWTnBjQUZJZ0xSTl9nYVI4aDZ6eFY0anVZbUJSalFB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTFBJMFdGVWI0UlM4bkVzUnBKT1hCeTliSnE0RjZ2WEE1dk02Q0pNSGNSZUI4U2tjUjRHb0YyUHMxQ2VqcWV5S25nNEkxdXhNejhlUUJIQm1FeHIzQdIBX0FVX3lxTE1VLUhqVW1ISWpCbEhuMU10cTBsVmlLQUVuLS1JM0w5cjJWbzN4czlxaEZWVWV6Y2xFdVB5X3hPNnFmbTdWT0dFMEpGT0JYTTM3LWlDUngxd2JzNmNFWHBF?oc=5</t>
         </is>
       </c>
       <c r="F93" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="94">
@@ -3233,21 +3233,21 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>MongoDB adds Voyage 4 AI models &amp; automates vector search - IT Brief UK</t>
+          <t>Fred. Olsen unveils AI ‘digital twin’ cruise campaign - IT Brief UK</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Fri, 16 Jan 2026 08:45:00 GMT</t>
+          <t>Fri, 16 Jan 2026 09:00:00 GMT</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiiwFBVV95cUxQSDUxcUpONGZYRXItWF85bko1eW92T0trbFR2TkpDcnV3MXh2STlCZndQRlZaQ2Z5VG9MRUllRjhyZmZ2MVVrNWM3UHlUa01ZbEl6aklQaElOdkFrc3pVSG8ySDhNZVBRS3k1ZENZY2hkMXdzYmZNbmdBb3VCTjMyNEdGU0ItbUZrdGNn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMihAFBVV95cUxPUnhyRVVWQlptNjFIbUZ0aGdDQWNYR0tXeFJwMTdVQjdVWHZoOEVRbWROaG1uLU1CVTFwaXdfdldYZk1Fem5aVmpGaVRXNHd6Z2ZZc2EzSHdkTlkxTDEtLV9TUzlhR2pGOGJUN3pUbkROanc5RVN5ZWMyaDZhNEJybTJiazI?oc=5</t>
         </is>
       </c>
       <c r="F94" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="95">
@@ -3263,21 +3263,21 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Small Cell Forum maps 2026 push for scalable 5G growth - IT Brief UK</t>
+          <t>Digital Pathology Market Growing at 9.9% CAGR to 2031 as AI Adoption Accelerates, says a 2026 Mordor Intelligence Report - PR Newswire UK</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Fri, 16 Jan 2026 09:15:00 GMT</t>
+          <t>Fri, 16 Jan 2026 08:30:00 GMT</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiigFBVV95cUxOQWhsVU40UFVXajNER0U4eG9NcVEzWlQxakhIZXFpZnJSX3U2cl9GWTFEN2tZUEhyeGp1WEZESExGSTZhZ0tqTktRVVdJZUZEMGxQVDlpYXJ4VXM4MVN1ZEdHT1NvMGN3RDZ3aGpGZlNyTmR5RDdGbXhEVGVPTE5nRUFDcjI2NGdlbVE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMihwJBVV95cUxNeTdDWm1NWXFacG1QNVNtQTNVU1Uxc0FpaUZDUnhZbkVxYVZNa0RCOXU2SlBMajNoTGIzZ0RBTUFnV2VUdllNR01UcklISWFuT25PSUxnT3BhNXRFbVFndGlFZ0ZyV1J1ZVIzSjc5ZEd0OFlZOHo4VXRqZE5IbzhOYjg3UlhDT2RpNUc4WlRNbVo2Y0dWS1I4dElWTVh5a3N5aGQ5ajJaWEY5YVdMdXU4S0pObDREVElyN2pZMVVGVE5VOFh6ZjB0VWpUcHBiNXJaNkpTdTdHUG5ZeFZfczd3VjdLbmJTeXFpRmhSZkQ4aDVjRzdmdkpaeFFQVUFuZjhmLTlXZE5pQQ?oc=5</t>
         </is>
       </c>
       <c r="F95" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="96">
@@ -3293,21 +3293,21 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>AI will ‘turbocharge’ Britain’s transport network, says Transport Committee chair - Fleet World</t>
+          <t>Blog: AI-Prosperity Alignment: A Pathway to a Flourishing Future - UCL | University College London</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Fri, 16 Jan 2026 08:24:43 GMT</t>
+          <t>Thu, 15 Jan 2026 15:44:48 GMT</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxNN19hay1TSTBieDZKdkZKN1lCTm1lX0JNUEVTbnNENXNKb1J4UThRMjNRUFV2b0RPbXdjOTdPdVFUN2d5NXBlMzA3UW1BZHRQYnkxRGxZMzFTWkFUdVk0M3BBNEwtYTAzcTgxcmluRmVxX3VocFVTS3d2NUd2akd3cWQtMVpWN0MzX0YtempzcXhGZVVzbktIc2NBV3FDdWpJcVQwdjBn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxQYjdRa2l1UkFLd2taQTB0NVlPbDd3WnQ3d3J1UDZYNV9ieTl6TTl0X2o3RXhtblhQOElhTXJpXzBJVzJ3Tnl5WlpsUVcwS3F0TkpRZ0REWVhmYmJSMXJMVlROQ3lJcmJRTzVjb0liR2tGUFVjdFZvcEd6VmFaV243T1lQekoxelE5dkRNUzNmOHFmLURORTRMTGE0blRnUnF3aVdz?oc=5</t>
         </is>
       </c>
       <c r="F96" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="97">
@@ -3323,21 +3323,21 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Cisco's HR chief says AI and ML roles are 'really hard' to fill. Getting execs on the phone helps. - Business Insider</t>
+          <t>Stop referencing fake case citations, judges warned - The Law Society Gazette</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Fri, 16 Jan 2026 10:52:00 GMT</t>
+          <t>Fri, 16 Jan 2026 10:09:04 GMT</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMigwFBVV95cUxOaHJINFBoS2tXYVFST2xSQWlYdkZ4czQyUHo2QmdfNFRqSTZycGdCZWhoNkhYVUVDT2RiSTNCcEpwazFOdFBUVDhkeWplTzBCdlY3djF6VUFMWGxhVDRvY0Fvb3pJRXBGN2Z1WElhYmxncFVzWUNqdVhhdnkzREdjRWx1OA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxOQkNCVW1wb0MwVEhZVEJNM3luc2ppQXRLU2p5ZVUzMm5KRW9OaVBpNWN2ZGNnSGowWWRndmljYjJxYkRqdXJOazAzcHctSUdhWnRvVzBONWxrNjhHYVJnZmF2ZkZ3RmRJVFpwSW5MOVJRQUQ2cHdhMmgyT2taNzRPT0NPMFNlaVYyYmtTQ0tqbnBzYVFQZVp4Sm5YNFQ0VG5TVHc?oc=5</t>
         </is>
       </c>
       <c r="F97" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="98">
@@ -3353,21 +3353,21 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Goertzel &amp; Lanier clash over AI autonomy &amp; control - IT Brief UK</t>
+          <t>How SAP Frames AI Sustainability in Data Centre Efficiency - Data Centre Magazine</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Fri, 16 Jan 2026 08:45:00 GMT</t>
+          <t>Fri, 16 Jan 2026 09:22:58 GMT</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMif0FVX3lxTFBYTjYyZGNEb0FyN01UU1FIMHUtMmdhRXFrTk9MR241UUh1V3NtM1d6WDBzVzN3QzdZZmhoN2VWWW1MRGFJU3Y0QWVQQ25jenZ4Ti04UkM4aFRRR2RVNnhVWTRZZGFualB6TThvQ0gtZmdmM05NTm1rM3lObGZHOWs?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMihwFBVV95cUxNLTZ4MlZ2WTJlZ3FCUlhSaUxmYkhrT21UNktjN1JVZkEwZnlJSEV3V2Y3Yi11aE9UYl9aaldNMi1jcHN2US03ZnoxelBSQzNubjRJY05ycW4temZ2QkVQakVtclBZaWhOR24teGI3cGlhUlJRMjlnT3V0YnItckhVdF9yUlU3OG8?oc=5</t>
         </is>
       </c>
       <c r="F98" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="99">
@@ -3383,21 +3383,21 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>TCS teams up with AMD to scale AI adoption across industries - verdict.co.uk</t>
+          <t>Not Just Travel launches AI tool for homeworkers - Travel Gossip</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Fri, 16 Jan 2026 06:15:25 GMT</t>
+          <t>Fri, 16 Jan 2026 11:23:29 GMT</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiYEFVX3lxTE1OaU55ZHF4ZU1JLTF3MlRZeE5YdTJRY3B1eS1KNHdkMVByUTVBVTRDQW9fZzBvU2h1cDNpeng2QThYZUprT2VkS2EwRlZOWTR0enl0X19LVHZKWEVwc0Z6cA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxNUV85eUxTLXNxV0VoR01XN3Y5dE42dUQwbExWMklxSURmZkVjRXFKeW5IeVJqVGhUaDFONmJZNGs0a1hTb2NIQWdMa3I3aFZJVUxCWkVHMVZWVFc1N2ZQMXdRLU1GeUUxQXduOWtEaThBZVE5cGM0QnQ5VEJCbmhLZWVDeDBvRGJPZFdVOExFbUc?oc=5</t>
         </is>
       </c>
       <c r="F99" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="100">
@@ -3413,21 +3413,21 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Gaps and policies in AI- and algorithm-driven discrimination in Europe - coe.int</t>
+          <t>EMA and FDA set common principles for AI in medicine development - European Medicines Agency</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Thu, 15 Jan 2026 10:35:24 GMT</t>
+          <t>Wed, 14 Jan 2026 15:18:03 GMT</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxPbU5UeUpqcnp1eWxjanozcUc0WWNON1FGNXFXS2ktLXpZdlVLaUxKSmh5TkhITlVQX3MyV3duMU1kTUl0VlBHWGs5UFBGRHFuYmxOZmlHR3NTbGZhdThURmU1NWU1RnJjZFZaS2Qyc185RTREM2JtZW5xQTdJX1FJbk90RktyTktxQTZBRFNyYTBXWDRzZEs0OS1mWDFkX05HcWJPR3VwSFU?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxOQ1pkYXNMX0FyNjB3UzRJQkd2NUdQTklPT1hsZlZPdkFkY2JBZ3U1UHl3azJKYjdJdGtpN3hmUGEzRXVtWm93dTFWMjlnU2tYbDZFakE4dXZiRWl2N190b24waG1TcXdmTEtTSWtmZ3UzVHRzQ21pNG90R3J4T3pQLWtJT2RqdHNmZFp3cUxwN1ctbG8?oc=5</t>
         </is>
       </c>
       <c r="F100" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="101">
@@ -3443,21 +3443,21 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Bridging technology and peacemaking at the marking of CMI’s 25 years - CMI - Martti Ahtisaari Peace Foundation</t>
+          <t>Accenture Named a Leader in Gartner® Magic Quadrant™ for Digital Technology and Business Consulting Services - Accenture</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Fri, 16 Jan 2026 11:44:22 GMT</t>
+          <t>Thu, 15 Jan 2026 09:08:25 GMT</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxORVhNV1h6YzZLWWhCNDZidDJrZTFPLXlTaG1DOURhRmN3ZGVIdVZRYllhWlNsc2FvVWsxNDBVWEtYY3daUUxmaDdEWVFBcDFEYzdEUFVWT0t0RzdielBmdUNWTFlXMDg1Z1MxVmVnSmw2QmlWc2ltY1ptOXp0eFpYN2s4TDNCVUUxLWFWOEdQaUd2WFQ5eUR5WHJR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi4AFBVV95cUxPLWFQeG1aX2tia2JscHpwWERVd3FGVjRoN3dTMHowWFJZNVJ2RWNsc0JKRWdUanZxOUZuWHd4cXdDczAxMUN2ZFc3LWtmMEdwdWVReWJEUlEwMHRjeFM5QWE3MDhoN2hXR0ZPRHFUbGFBc1JTQmQ4cDFGSFlxM1Q5ODlBLWN3VjBwOTZCWXloN0I4ekk4emhnek03RVZSYlViR25mLTBSOHJfZTRBamhWMzVrbHBnN3VNaDBmUFdJYkhqLTRsUG92V1N1UGVudTQ0ZWhQZGdXVlVyX25yZW5Tag?oc=5</t>
         </is>
       </c>
       <c r="F101" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="102">
@@ -3473,21 +3473,21 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Matthew McConaughey trademarks iconic phrase to stop AI misuse - BBC</t>
+          <t>Qualitative researchers’ AI rejection is based on identity, not reason - Times Higher Education</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Thu, 15 Jan 2026 18:34:41 GMT</t>
+          <t>Fri, 16 Jan 2026 00:01:32 GMT</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTFBJMFdGVWI0UlM4bkVzUnBKT1hCeTliSnE0RjZ2WEE1dk02Q0pNSGNSZUI4U2tjUjRHb0YyUHMxQ2VqcWV5S25nNEkxdXhNejhlUUJIQm1FeHIzQdIBX0FVX3lxTE1VLUhqVW1ISWpCbEhuMU10cTBsVmlLQUVuLS1JM0w5cjJWbzN4czlxaEZWVWV6Y2xFdVB5X3hPNnFmbTdWT0dFMEpGT0JYTTM3LWlDUngxd2JzNmNFWHBF?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxOTVpPTUFGYVhBYTQ3YWVjNlQyOHB0dWlQZk55ZTluZVNPaEIyUEotaFBDalNrVjFyZVNiUmdTdl80ejhuc3FWZGNTX1ZJVVhKN1NHU2FqeXZPZlM5Qm9VdTBiSVdPRy1fMU9pVjJNVHNHaWkyOGt3bzdoTFJIeGxxeWFDcWpDNkxHUHgtbksyQms4YlMxaWpTclg2UlhTWnY3d1h4X3paR1pBN2c?oc=5</t>
         </is>
       </c>
       <c r="F102" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="103">
@@ -3503,21 +3503,21 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Fred. Olsen unveils AI ‘digital twin’ cruise campaign - IT Brief UK</t>
+          <t>AI-generated virtual psychedelics bridge digital and therapeutic frontiers in mental health research - Nature</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Fri, 16 Jan 2026 09:00:00 GMT</t>
+          <t>Fri, 16 Jan 2026 10:11:27 GMT</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihAFBVV95cUxPUnhyRVVWQlptNjFIbUZ0aGdDQWNYR0tXeFJwMTdVQjdVWHZoOEVRbWROaG1uLU1CVTFwaXdfdldYZk1Fem5aVmpGaVRXNHd6Z2ZZc2EzSHdkTlkxTDEtLV9TUzlhR2pGOGJUN3pUbkROanc5RVN5ZWMyaDZhNEJybTJiazI?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiX0FVX3lxTE9vMjNFZHUtUEhvV0xmM3BMUWJPNUVwQUJHTFhISHc4LURGaHFaRWJPSE5RdDFENmtMVi1oWEcxVWhUTFk5MTJjczVkbUJyeW95SEh6LWp0NUlkelJRVmFV?oc=5</t>
         </is>
       </c>
       <c r="F103" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="104">
@@ -3533,21 +3533,21 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Digital Pathology Market Growing at 9.9% CAGR to 2031 as AI Adoption Accelerates, says a 2026 Mordor Intelligence Report - PR Newswire UK</t>
+          <t>Technology must enhance real-world learning - not replace it: Danny Metters - Yorkshire Post</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Fri, 16 Jan 2026 08:30:00 GMT</t>
+          <t>Fri, 16 Jan 2026 05:45:00 GMT</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihwJBVV95cUxNeTdDWm1NWXFacG1QNVNtQTNVU1Uxc0FpaUZDUnhZbkVxYVZNa0RCOXU2SlBMajNoTGIzZ0RBTUFnV2VUdllNR01UcklISWFuT25PSUxnT3BhNXRFbVFndGlFZ0ZyV1J1ZVIzSjc5ZEd0OFlZOHo4VXRqZE5IbzhOYjg3UlhDT2RpNUc4WlRNbVo2Y0dWS1I4dElWTVh5a3N5aGQ5ajJaWEY5YVdMdXU4S0pObDREVElyN2pZMVVGVE5VOFh6ZjB0VWpUcHBiNXJaNkpTdTdHUG5ZeFZfczd3VjdLbmJTeXFpRmhSZkQ4aDVjRzdmdkpaeFFQVUFuZjhmLTlXZE5pQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivgFBVV95cUxPMFNEOWs0bzMtbWxjX3ZMLWpZVEpiLTN6UmVjNC14TXFuWk55azE2aDA3aUttLVhGUnZaZVBoTEdkRl9DdFB4SXltTnpuRUk0UkxiZXVhbTBQTE4xeHAxX1hzX1N3SXRBUkNYOUVNT29NcWFuTmRfMTZRTC1lZVl6amEzb1pFOGZqbnJWeGJvS2VsVnZISmdGejZoVWx5NFdIM2txNGRBdDhUREliUl9wSnRvRXl4ZHEzQl9ndjJ3?oc=5</t>
         </is>
       </c>
       <c r="F104" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="105">
@@ -3563,21 +3563,21 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Blog: AI-Prosperity Alignment: A Pathway to a Flourishing Future - UCL | University College London</t>
+          <t>AI and Network Science for Emotional Risk Measurement in Stock Markets | Newswise - Newswise</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>Thu, 15 Jan 2026 15:44:48 GMT</t>
+          <t>Fri, 16 Jan 2026 10:45:00 GMT</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxQYjdRa2l1UkFLd2taQTB0NVlPbDd3WnQ3d3J1UDZYNV9ieTl6TTl0X2o3RXhtblhQOElhTXJpXzBJVzJ3Tnl5WlpsUVcwS3F0TkpRZ0REWVhmYmJSMXJMVlROQ3lJcmJRTzVjb0liR2tGUFVjdFZvcEd6VmFaV243T1lQekoxelE5dkRNUzNmOHFmLURORTRMTGE0blRnUnF3aVdz?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxOODRBd1R3OFFRUmR5MndhXzFobnRub3ZyQ05DQzFmc0pzcUVQcWRtUlNDUzI1SVFzTDg3R2JRQ3RpR0sxbW5sSG1DTzdZbm5QZEEtUUFvSjF4WmpSN3NXX3VhQXpSeW5tc29JdmpURy1sUTdkWnZwYmt0MVA2TlRTMUlOZkt0bVF1MTFtLXBWWXpBMVFQWUlIME9uenZlUDhZb1R3V1hhNNIBpwFBVV95cUxOODRBd1R3OFFRUmR5MndhXzFobnRub3ZyQ05DQzFmc0pzcUVQcWRtUlNDUzI1SVFzTDg3R2JRQ3RpR0sxbW5sSG1DTzdZbm5QZEEtUUFvSjF4WmpSN3NXX3VhQXpSeW5tc29JdmpURy1sUTdkWnZwYmt0MVA2TlRTMUlOZkt0bVF1MTFtLXBWWXpBMVFQWUlIME9uenZlUDhZb1R3V1hhNA?oc=5</t>
         </is>
       </c>
       <c r="F105" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="106">
@@ -3593,21 +3593,21 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Stop referencing fake case citations, judges warned - The Law Society Gazette</t>
+          <t>A new direction for students in an AI world: Prosper, prepare, protect - Brookings</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>Fri, 16 Jan 2026 10:09:04 GMT</t>
+          <t>Wed, 14 Jan 2026 13:43:05 GMT</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxOQkNCVW1wb0MwVEhZVEJNM3luc2ppQXRLU2p5ZVUzMm5KRW9OaVBpNWN2ZGNnSGowWWRndmljYjJxYkRqdXJOazAzcHctSUdhWnRvVzBONWxrNjhHYVJnZmF2ZkZ3RmRJVFpwSW5MOVJRQUQ2cHdhMmgyT2taNzRPT0NPMFNlaVYyYmtTQ0tqbnBzYVFQZVp4Sm5YNFQ0VG5TVHc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxOLUFiQzhMMWhpeC1VRVc2aUZ5UUFFN2pNQ3JqMHgtR0U0N2wyQUZzTXhfY09lMWMwUVpfdUNPNm00NFBLNEMtZXdIRDNiTnJEQlQ0ZjFHNy1TbkpJWHozWDdNSU5EaHpSbU14V09MVTc1YWpkOUpLem9keldIeDRWUU55aXBoZmN0MWczVTNyUVpreFViOHNKeE9OaGVmdlo3d1J4MTFn?oc=5</t>
         </is>
       </c>
       <c r="F106" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="107">
@@ -3623,21 +3623,21 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>How SAP Frames AI Sustainability in Data Centre Efficiency - Data Centre Magazine</t>
+          <t>Argonne Uses AI and Robotics for 6,000 Battery Experiments - Battery Technology</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Fri, 16 Jan 2026 09:22:58 GMT</t>
+          <t>Thu, 15 Jan 2026 19:52:05 GMT</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihwFBVV95cUxNLTZ4MlZ2WTJlZ3FCUlhSaUxmYkhrT21UNktjN1JVZkEwZnlJSEV3V2Y3Yi11aE9UYl9aaldNMi1jcHN2US03ZnoxelBSQzNubjRJY05ycW4temZ2QkVQakVtclBZaWhOR24teGI3cGlhUlJRMjlnT3V0YnItckhVdF9yUlU3OG8?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxQS1RpUEVNRG1Ec0VNczMza3l6azlhZXVpVjZXd0FJc0gycGxCSW5FRWRWMzZTaHV6Qzc0ZUsyUi12RXhMVHd6cFVxTldHVEMwc3A0eWdPM3dwU0pZTm1jeVNjZVFOdTl1ak4xdGxWdU1QN3drSXJ1M3V1V3Y1SkQ3UXhKcDR6T0NVelhyNFJPR0ZFNHRIeXZGMU82bE9SemtGdVlVaw?oc=5</t>
         </is>
       </c>
       <c r="F107" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="108">
@@ -3653,21 +3653,21 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Not Just Travel launches AI tool for homeworkers - Travel Gossip</t>
+          <t>Why AI and cameras are the future of fleet safety | opinion - Fleet News</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Fri, 16 Jan 2026 11:23:29 GMT</t>
+          <t>Wed, 14 Jan 2026 11:35:35 GMT</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxNUV85eUxTLXNxV0VoR01XN3Y5dE42dUQwbExWMklxSURmZkVjRXFKeW5IeVJqVGhUaDFONmJZNGs0a1hTb2NIQWdMa3I3aFZJVUxCWkVHMVZWVFc1N2ZQMXdRLU1GeUUxQXduOWtEaThBZVE5cGM0QnQ5VEJCbmhLZWVDeDBvRGJPZFdVOExFbUc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilAFBVV95cUxQX3E5WTlvV2lkSUE5cTRzRjZWQ1ZTVXBUU0RSeERTYzVZNzhsTHJpQVhUbHJCMXl2UnRyY0V2X2FXYmVlam1mbVZ1ZFo2UjgzaWduMUx5WUJsZURCTlg3TmJBTDktS2VLY2FBR1ktMTNMdm9jd1IxTEFzMmNVWEdFVktyeGdrU1RBMGZ0bGlPNlJ6TTVy?oc=5</t>
         </is>
       </c>
       <c r="F108" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="109">
@@ -3683,21 +3683,21 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>EMA and FDA set common principles for AI in medicine development - European Medicines Agency</t>
+          <t>PsiQuantum and Airbus Collaborate on Fault-Tolerant Quantum Algorithms for Aerospace - The Quantum Insider</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Wed, 14 Jan 2026 15:18:03 GMT</t>
+          <t>Fri, 16 Jan 2026 06:25:58 GMT</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxOQ1pkYXNMX0FyNjB3UzRJQkd2NUdQTklPT1hsZlZPdkFkY2JBZ3U1UHl3azJKYjdJdGtpN3hmUGEzRXVtWm93dTFWMjlnU2tYbDZFakE4dXZiRWl2N190b24waG1TcXdmTEtTSWtmZ3UzVHRzQ21pNG90R3J4T3pQLWtJT2RqdHNmZFp3cUxwN1ctbG8?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxNaU9fMGtwdkkxWThrZHlIYWYwVTdqdU9SZ0w5Y0t5bUxLUE5LNDdjOF9ldkEycmp2MTVuX3RyUkI5aG5QU2UtaVR4cGZTQTg2R2Utd2J1WHNiX2V5RmIyOGVHYzNOOGxXXzk4YUYyYUkxWFNTOHl0WFlnU1ZYWFJrc0kwSUJtVFJLS1FkZjFlN001N1NfM2MwaGh3a0lXRjJQRThOYmJzcTZjNUlWNDA2NGhpanE4VHZlUzl5c1lnMWVaMVVh?oc=5</t>
         </is>
       </c>
       <c r="F109" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="110">
@@ -3713,1581 +3713,1581 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Accenture Named a Leader in Gartner® Magic Quadrant™ for Digital Technology and Business Consulting Services - Accenture</t>
+          <t>Automation joins AI and cybersecurity as digital priorities for Indian pharma - European Pharmaceutical Review</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Thu, 15 Jan 2026 09:08:25 GMT</t>
+          <t>Thu, 15 Jan 2026 12:37:47 GMT</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi4AFBVV95cUxPLWFQeG1aX2tia2JscHpwWERVd3FGVjRoN3dTMHowWFJZNVJ2RWNsc0JKRWdUanZxOUZuWHd4cXdDczAxMUN2ZFc3LWtmMEdwdWVReWJEUlEwMHRjeFM5QWE3MDhoN2hXR0ZPRHFUbGFBc1JTQmQ4cDFGSFlxM1Q5ODlBLWN3VjBwOTZCWXloN0I4ekk4emhnek03RVZSYlViR25mLTBSOHJfZTRBamhWMzVrbHBnN3VNaDBmUFdJYkhqLTRsUG92V1N1UGVudTQ0ZWhQZGdXVlVyX25yZW5Tag?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivgFBVV95cUxOTGM5WVpqRUVwZlgySWhnaWpuVk5aTUdGbTlpaFR6NTlqVE1rZGRhVEJfRWhZUTJJZWh1dThBT1VEVGZOSklEY1d0Ylc0UGZvYXNuWmdBX3lYWDlzZmNWbG5RZ1dWVmVHLURlMHktVWs4OEpfVUJ4eGUyM2dMbVFGV1lFTGVxSS1acURrb3ozWVZfRlRCNDI3dDF1WjRERnVjT0t4UzloX0t3ck1JSDZEMXlScGM1S1ZPcUhjaEJB?oc=5</t>
         </is>
       </c>
       <c r="F110" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>UNMAPPED_LINE</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+          <t>Insider Risk ("insider risk" OR "insider threat" OR "internal threat" OR "employee misconduct" OR "data exfiltration" OR "privileged access abuse" OR "malicious insider" OR "negligent insider" OR "insider attack" OR "corporate espionage" OR "information leakage" OR "unauthorised access" OR "policy violation" OR "security breach" OR "insider vulnerability")</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Qualitative researchers’ AI rejection is based on identity, not reason - Times Higher Education</t>
+          <t>Insider risk in an age of workforce volatility - csoonline.com</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Fri, 16 Jan 2026 00:01:32 GMT</t>
+          <t>Fri, 16 Jan 2026 07:03:45 GMT</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxOTVpPTUFGYVhBYTQ3YWVjNlQyOHB0dWlQZk55ZTluZVNPaEIyUEotaFBDalNrVjFyZVNiUmdTdl80ejhuc3FWZGNTX1ZJVVhKN1NHU2FqeXZPZlM5Qm9VdTBiSVdPRy1fMU9pVjJNVHNHaWkyOGt3bzdoTFJIeGxxeWFDcWpDNkxHUHgtbksyQms4YlMxaWpTclg2UlhTWnY3d1h4X3paR1pBN2c?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxPZFlhRWdIX1hIdERkRVVmeWJ0MjBVbzBDenFpajlaNkFHZ3N4YWZ4Zks2RFRQVUNNazh2R3dNUUVzQ215Q3M2aVRrMjZUWGdRbUxUWVhHQW5vVEpFRzNoTXRUazlORVc1UUt0MGRiMGtzdzFMV0lOcnAtRG9oX0FqcFc1ODZ1VTM3NkFKVm1pYWxHQUlQSEluUA?oc=5</t>
         </is>
       </c>
       <c r="F111" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>UNMAPPED_LINE</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+          <t>Insider Risk ("insider risk" OR "insider threat" OR "internal threat" OR "employee misconduct" OR "data exfiltration" OR "privileged access abuse" OR "malicious insider" OR "negligent insider" OR "insider attack" OR "corporate espionage" OR "information leakage" OR "unauthorised access" OR "policy violation" OR "security breach" OR "insider vulnerability")</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>AI-generated virtual psychedelics bridge digital and therapeutic frontiers in mental health research - Nature</t>
+          <t>The Latest GigaOm Radar Insights For Insider Risk Management - LinkedIn</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Fri, 16 Jan 2026 10:11:27 GMT</t>
+          <t>Thu, 15 Jan 2026 12:00:18 GMT</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiX0FVX3lxTE9vMjNFZHUtUEhvV0xmM3BMUWJPNUVwQUJHTFhISHc4LURGaHFaRWJPSE5RdDFENmtMVi1oWEcxVWhUTFk5MTJjczVkbUJyeW95SEh6LWp0NUlkelJRVmFV?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxQZ0Y4d0NPMXBvSEdnamRwQ1BCeFM3THhpS0ZHNTV6Nk9IOUJTTlJpeE1ITEt6WDFNc2haNkxjZ2JOMnozcDZqbHVyVU5ZM3lQdC1ReXFuM2RqUTlUM3RNVUlZdVpiRVlhMVpPRmFxajNnckwzRWpDRjVHNXRXSlJ3RmtvRE1kWWw3NHk4WmE4T1lyV0k?oc=5</t>
         </is>
       </c>
       <c r="F112" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>UNMAPPED_LINE</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+          <t>Insider Risk ("insider risk" OR "insider threat" OR "internal threat" OR "employee misconduct" OR "data exfiltration" OR "privileged access abuse" OR "malicious insider" OR "negligent insider" OR "insider attack" OR "corporate espionage" OR "information leakage" OR "unauthorised access" OR "policy violation" OR "security breach" OR "insider vulnerability")</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Technology must enhance real-world learning - not replace it: Danny Metters - Yorkshire Post</t>
+          <t>Cyberhaven Partners with O’Reilly to Publish Insider Risk Management Guide - TipRanks</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>Fri, 16 Jan 2026 05:45:00 GMT</t>
+          <t>Thu, 15 Jan 2026 00:36:34 GMT</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivgFBVV95cUxPMFNEOWs0bzMtbWxjX3ZMLWpZVEpiLTN6UmVjNC14TXFuWk55azE2aDA3aUttLVhGUnZaZVBoTEdkRl9DdFB4SXltTnpuRUk0UkxiZXVhbTBQTE4xeHAxX1hzX1N3SXRBUkNYOUVNT29NcWFuTmRfMTZRTC1lZVl6amEzb1pFOGZqbnJWeGJvS2VsVnZISmdGejZoVWx5NFdIM2txNGRBdDhUREliUl9wSnRvRXl4ZHEzQl9ndjJ3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivgFBVV95cUxNMGVUdXoyYzYyU2ZMRHBEOEZTbTA3SnBxcGhBQzZWbGlzamVEdEpZTEtTR0dnZHY3dWJJY1Yya1h5VlJ6TXdaVGhOeExkQ3FyT251R2Nzb0dBT3QtYVllQ3NHMHR4bjFaZjZLZjQtMHBYMVJOcXdtaFNMNEVaV3VnUkdPNk9CbUJpNWNXa19UVnZVXzRzRWpWdnZxbjl6RDVTUlNoZG5Sb1BDRVNGVDdTRmNyUXZFYW12U093cWp3?oc=5</t>
         </is>
       </c>
       <c r="F113" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>UNMAPPED_LINE</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+          <t>Fraud/Scam ("fraud" OR "scam" OR "phishing" OR "identity theft" OR "account takeover" OR "payment fraud" OR "credit card fraud" OR "wire fraud" OR "business email compromise" OR "fake invoice" OR "social engineering" OR "advance fee fraud")</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>AI and Network Science for Emotional Risk Measurement in Stock Markets | Newswise - Newswise</t>
+          <t>San Diego man pleads guilty to role in international elder fraud scam - 10News.com</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>Fri, 16 Jan 2026 10:45:00 GMT</t>
+          <t>Thu, 15 Jan 2026 21:08:50 GMT</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxOODRBd1R3OFFRUmR5MndhXzFobnRub3ZyQ05DQzFmc0pzcUVQcWRtUlNDUzI1SVFzTDg3R2JRQ3RpR0sxbW5sSG1DTzdZbm5QZEEtUUFvSjF4WmpSN3NXX3VhQXpSeW5tc29JdmpURy1sUTdkWnZwYmt0MVA2TlRTMUlOZkt0bVF1MTFtLXBWWXpBMVFQWUlIME9uenZlUDhZb1R3V1hhNNIBpwFBVV95cUxOODRBd1R3OFFRUmR5MndhXzFobnRub3ZyQ05DQzFmc0pzcUVQcWRtUlNDUzI1SVFzTDg3R2JRQ3RpR0sxbW5sSG1DTzdZbm5QZEEtUUFvSjF4WmpSN3NXX3VhQXpSeW5tc29JdmpURy1sUTdkWnZwYmt0MVA2TlRTMUlOZkt0bVF1MTFtLXBWWXpBMVFQWUlIME9uenZlUDhZb1R3V1hhNA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxNbXZwcEMteTZFU3hpVmlDeUdYdDVWWDY2dU1uYWxJVWVjVHh0bTRRWEhMdE9Vay1haVAzMGFaQjVUVzUyTWh5U285NXZoRzdwazlaRlNTcmg4aldZck5LZGZDWGpqSHcyVjdGVHVwQ2c4VTVZWDlDa2VHd0QxS1VJaG9tVDZZYTd0Ty1vdktJQ202dFlYZ3U2VnJ1UmN5RGtmSGNkOFNCMlZ5Qldx?oc=5</t>
         </is>
       </c>
       <c r="F114" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>UNMAPPED_LINE</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+          <t>Fraud/Scam ("fraud" OR "scam" OR "phishing" OR "identity theft" OR "account takeover" OR "payment fraud" OR "credit card fraud" OR "wire fraud" OR "business email compromise" OR "fake invoice" OR "social engineering" OR "advance fee fraud")</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>A new direction for students in an AI world: Prosper, prepare, protect - Brookings</t>
+          <t>Behind the Top Scams Consumers Face and the Defenses That Work - PYMNTS.com</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>Wed, 14 Jan 2026 13:43:05 GMT</t>
+          <t>Wed, 14 Jan 2026 17:01:23 GMT</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxOLUFiQzhMMWhpeC1VRVc2aUZ5UUFFN2pNQ3JqMHgtR0U0N2wyQUZzTXhfY09lMWMwUVpfdUNPNm00NFBLNEMtZXdIRDNiTnJEQlQ0ZjFHNy1TbkpJWHozWDdNSU5EaHpSbU14V09MVTc1YWpkOUpLem9keldIeDRWUU55aXBoZmN0MWczVTNyUVpreFViOHNKeE9OaGVmdlo3d1J4MTFn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxPa3VZUzNiank4bGNzNUpuXzZsM0VSY1ZfVUpUTlc5TV9WUXBGZ1NZWVBZb2ZlMTFtRVFqLUV0aGlRTWI1UXNsZkg2bnVtRHFTeXBiQVJybjRFaEYtazdFMXNHT2xPRERMVXdfUUhSd1BlT1hlMXlFZXlFTktPU0JjVUo2QTY3TnlYazY5VGE0UFlRY0s3bFVsMnJGQU5lenFSYUNvXzQ3cw?oc=5</t>
         </is>
       </c>
       <c r="F115" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>UNMAPPED_LINE</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+          <t>Fraud/Scam ("fraud" OR "scam" OR "phishing" OR "identity theft" OR "account takeover" OR "payment fraud" OR "credit card fraud" OR "wire fraud" OR "business email compromise" OR "fake invoice" OR "social engineering" OR "advance fee fraud")</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Argonne Uses AI and Robotics for 6,000 Battery Experiments - Battery Technology</t>
+          <t>Lifespan offers peer-to-peer program to help fraud survivors - Spectrum News</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>Thu, 15 Jan 2026 19:52:05 GMT</t>
+          <t>Thu, 15 Jan 2026 13:30:00 GMT</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxQS1RpUEVNRG1Ec0VNczMza3l6azlhZXVpVjZXd0FJc0gycGxCSW5FRWRWMzZTaHV6Qzc0ZUsyUi12RXhMVHd6cFVxTldHVEMwc3A0eWdPM3dwU0pZTm1jeVNjZVFOdTl1ak4xdGxWdU1QN3drSXJ1M3V1V3Y1SkQ3UXhKcDR6T0NVelhyNFJPR0ZFNHRIeXZGMU82bE9SemtGdVlVaw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxQMm1RMlRSTFBWeVFZR0dfZEFJNEVCWDFTNFhJS01CZTk1UmhuNUF3ZE9PazlOc1J2Znh3VmVlemZPb3psNm1xWGFwbkEzUWFDcGRYbmMtaE5nTzM2TUVLQXdkWFFhYm5DbFdKd3QyNDZqbzl5MWNqTDZMeEs0NFlURGUtUGNMV0M5b3FUZzFFbEdDdDFEN3NjTw?oc=5</t>
         </is>
       </c>
       <c r="F116" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>UNMAPPED_LINE</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+          <t>Fraud/Scam ("fraud" OR "scam" OR "phishing" OR "identity theft" OR "account takeover" OR "payment fraud" OR "credit card fraud" OR "wire fraud" OR "business email compromise" OR "fake invoice" OR "social engineering" OR "advance fee fraud")</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Why AI and cameras are the future of fleet safety | opinion - Fleet News</t>
+          <t>Matrimonial Scam: Man posing as doctor dupes woman of Rs 22.7 lakh - Medical Dialogues</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>Wed, 14 Jan 2026 11:35:35 GMT</t>
+          <t>Thu, 15 Jan 2026 12:12:51 GMT</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilAFBVV95cUxQX3E5WTlvV2lkSUE5cTRzRjZWQ1ZTVXBUU0RSeERTYzVZNzhsTHJpQVhUbHJCMXl2UnRyY0V2X2FXYmVlam1mbVZ1ZFo2UjgzaWduMUx5WUJsZURCTlg3TmJBTDktS2VLY2FBR1ktMTNMdm9jd1IxTEFzMmNVWEdFVktyeGdrU1RBMGZ0bGlPNlJ6TTVy?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxQbkxWV2t6c2dSaFdMdnR0d2o2dS15NzdVVzBBR19tdHpZMW5uVUcyNWY4RWtuWEQ0M2NjMkhzejkxaGx2d2RpMzBNN1ZLOFY5YTFMQS01YV9fTnViT25mbWl5ZEo1RjkyM0VxUDRweklRYjZKLTRtWF8yS1NTdTd0d3U5VkRWeXN5WW04S05rekZnLTVWdkJYUWcxaDRqcHhQRGI4VFlhZDd0RDlNQXN5QUk3RTFBdkRBS0hv0gHAAUFVX3lxTE5WODZMQVdra1VhYUNteG02T3hieG02TXphSlQyNU9BbzBqM3czZWJHUEp3bnlhMkxvejJ2SmxWc2pvWnVOS3F3MXdGUlE0cTN0V3dla1FpeHoxQXpWYUdLTHdrRE9YYnd2OG9ia3lPdGRCaDJtcmlhMDAxOVBiRzNlNmJLc0VET1gwa2xoTUUxRWFLTlV0UUhYMldVN2d5eTNkMzlUbEVNbUdLeFhWNXlQNTJJR0UzX0dYZkJGdWFoTA?oc=5</t>
         </is>
       </c>
       <c r="F117" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>UNMAPPED_LINE</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+          <t>Fraud/Scam ("fraud" OR "scam" OR "phishing" OR "identity theft" OR "account takeover" OR "payment fraud" OR "credit card fraud" OR "wire fraud" OR "business email compromise" OR "fake invoice" OR "social engineering" OR "advance fee fraud")</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Looking ahead: AI and the future of the financial services customer journey - Dentons</t>
+          <t>A Houston woman thought she was protecting her money after receiving a fraud alert text. Instead, she lost everything. - KHOU</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>Tue, 13 Jan 2026 15:16:25 GMT</t>
+          <t>Wed, 14 Jan 2026 03:59:49 GMT</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0AFBVV95cUxQbHJwQzlMUk5xQWJibzdZekRWSnEwX0tDX3FuVzBxaHRZSU5WNktZMDE0Y3dzT2lRUkdybEEwUEJHY041Tk14M05wRTlrd09LbUF4S056bjdZdWo0b0UxRXg3WnNCck12dDVsekpUQlV5eEMzTjVFWWQtU3RuTUp3RW5vQ19GY25NcHlXMHFLSk04Z2pWaVRGbVRDTnJkZmhUcU4ydldWNzhQSUhURlBMaDJaNl9EeGVycnFPdTZPNnZrdkxvb1pNNllid1dkUHRQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivgFBVV95cUxPOEREWGhqNjdiRFlYbVVkT3JQRGVkX09HMXJwMkJycW1sWWZ2TkFQQ2xvVTk2TDdFRjc3Q3pMMWw5enBjT2phSUp5elctMnNNV3ZudXVrTXdfdjBWLVBySVg0RUc0dmpHbHA3eEQ0NFJSZlh2RWM2R1M0RXhlYWdsRnRSMWIzOXQwQzgtNDF2UVNNQXBOd2hZU3AtdkVDVFIxQUU2WmdIdTA5UXRrSDNEWXpkOHd6cjNpSWMyU2Fn?oc=5</t>
         </is>
       </c>
       <c r="F118" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>UNMAPPED_LINE</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+          <t>Fraud/Scam ("fraud" OR "scam" OR "phishing" OR "identity theft" OR "account takeover" OR "payment fraud" OR "credit card fraud" OR "wire fraud" OR "business email compromise" OR "fake invoice" OR "social engineering" OR "advance fee fraud")</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>PsiQuantum and Airbus Collaborate on Fault-Tolerant Quantum Algorithms for Aerospace - The Quantum Insider</t>
+          <t>N.J. school district says $178K in taxpayer money vanished in email scam - NJ.com</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>Fri, 16 Jan 2026 06:25:58 GMT</t>
+          <t>Thu, 15 Jan 2026 16:17:00 GMT</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxNaU9fMGtwdkkxWThrZHlIYWYwVTdqdU9SZ0w5Y0t5bUxLUE5LNDdjOF9ldkEycmp2MTVuX3RyUkI5aG5QU2UtaVR4cGZTQTg2R2Utd2J1WHNiX2V5RmIyOGVHYzNOOGxXXzk4YUYyYUkxWFNTOHl0WFlnU1ZYWFJrc0kwSUJtVFJLS1FkZjFlN001N1NfM2MwaGh3a0lXRjJQRThOYmJzcTZjNUlWNDA2NGhpanE4VHZlUzl5c1lnMWVaMVVh?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxQb05tZGhRb0N0amxneUcwM3JNYkhOWXVvWHlrOG1iMVVabFBCQXlnV0xLbDlIVlhlQWF1YzJqQm0zRHZIbXpvNW1jVDdmN3ZBMnRTTVR6ZDZ2MGtYSWVOaVJMUjZneW1zUHhxbkh0MDRia1UzakFHT2xDdGdGakRTUzkzbTNqU2lyam91WkY3RDltNXZ2NXhTVzBmWHVKUFJPT2pyZWc5XzA3YkVUbmpNTw?oc=5</t>
         </is>
       </c>
       <c r="F119" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Current_Affairs</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+          <t>(geopolitics OR migration OR economy OR conflict OR legislation OR terrorism OR disinformation OR misinformation OR government OR policy OR regulation) AND (briefing OR analysis OR update OR report)</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Automation joins AI and cybersecurity as digital priorities for Indian pharma - European Pharmaceutical Review</t>
+          <t>PAC report on children’s care homes – LGA response - Local Government Association</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>Thu, 15 Jan 2026 12:37:47 GMT</t>
+          <t>Fri, 16 Jan 2026 00:13:36 GMT</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivgFBVV95cUxOTGM5WVpqRUVwZlgySWhnaWpuVk5aTUdGbTlpaFR6NTlqVE1rZGRhVEJfRWhZUTJJZWh1dThBT1VEVGZOSklEY1d0Ylc0UGZvYXNuWmdBX3lYWDlzZmNWbG5RZ1dWVmVHLURlMHktVWs4OEpfVUJ4eGUyM2dMbVFGV1lFTGVxSS1acURrb3ozWVZfRlRCNDI3dDF1WjRERnVjT0t4UzloX0t3ck1JSDZEMXlScGM1S1ZPcUhjaEJB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMihwFBVV95cUxNeU56dGZaNU5WVkd6SGlJc2pLOUl3TnJudmFpZ0FXMFMwS0IyRFRHbmRCQ29PQzNuZXFUb05MRUg5UWxjRm8tWFJLWVN6Tzl6YWJ1M19zTi0xSGJBVkxoUEtmWWN0bGcyMHZ1cGp0ZlhuaWtkcEg1TkF3NWNNZ0xtcnQyUGVqelE?oc=5</t>
         </is>
       </c>
       <c r="F120" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>UNMAPPED_LINE</t>
+          <t>Current_Affairs</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Insider Risk ("insider risk" OR "insider threat" OR "internal threat" OR "employee misconduct" OR "data exfiltration" OR "privileged access abuse" OR "malicious insider" OR "negligent insider" OR "insider attack" OR "corporate espionage" OR "information leakage" OR "unauthorised access" OR "policy violation" OR "security breach" OR "insider vulnerability")</t>
+          <t>(geopolitics OR migration OR economy OR conflict OR legislation OR terrorism OR disinformation OR misinformation OR government OR policy OR regulation) AND (briefing OR analysis OR update OR report)</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Insider risk in an age of workforce volatility - csoonline.com</t>
+          <t>Insight - Trend report: stock, rents and regulation in supported housing - Social Housing</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>Fri, 16 Jan 2026 07:03:45 GMT</t>
+          <t>Fri, 16 Jan 2026 12:00:00 GMT</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxPZFlhRWdIX1hIdERkRVVmeWJ0MjBVbzBDenFpajlaNkFHZ3N4YWZ4Zks2RFRQVUNNazh2R3dNUUVzQ215Q3M2aVRrMjZUWGdRbUxUWVhHQW5vVEpFRzNoTXRUazlORVc1UUt0MGRiMGtzdzFMV0lOcnAtRG9oX0FqcFc1ODZ1VTM3NkFKVm1pYWxHQUlQSEluUA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxNZFJhOWl3MHdkUXNndHV6UTJZa3FGT2tLTjB2SHpyRmd2aDJUVVNDTGJUYTFkZEVDWTJnWWtBY3JGV3pPWm1zbVk0TjMtQTA4M2R0bUdNVnFzY0lha3haQlpQODVQWDNnQlZKckRENHA5OWNCUDVGSXFrQy1ZcHptaG0za1RxMjk3RWZ5V1B1SkFBUERfdnVLaklWX1F4eEoyNm9fRDBRSnVZZw?oc=5</t>
         </is>
       </c>
       <c r="F121" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>UNMAPPED_LINE</t>
+          <t>Supply_Chain</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Insider Risk ("insider risk" OR "insider threat" OR "internal threat" OR "employee misconduct" OR "data exfiltration" OR "privileged access abuse" OR "malicious insider" OR "negligent insider" OR "insider attack" OR "corporate espionage" OR "information leakage" OR "unauthorised access" OR "policy violation" OR "security breach" OR "insider vulnerability")</t>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Why the Start of the Year Is Prime Time for Insider Risk - eSecurity Planet</t>
+          <t>News Content Hub - Greek owners urge EU to take 'immediate' action to protect shipping after Black Sea attacks - rivieramm.com</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>Mon, 12 Jan 2026 22:47:15 GMT</t>
+          <t>Fri, 16 Jan 2026 12:00:38 GMT</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxPMWd4UjQxckptb3NwNXNZN1JjXzJFUlUybklxTGVhTVFzQkl5eTVkV0YzMUJoN1pqZ1ZfSGRPNXpLakExY0JBRlV3cUJ2VXM5Q0NYWTBJVUpobUFVWnJQVlVCTUpoQjNkeHAzcHlZSklwZGlqQTlScUV6NkpjeEExc0ljZ2RkQVY5Vl9Ncm16b3VrTHFDdVoxZXNTR01DUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi1AFBVV95cUxONTBBaTczdDFVTmE0dmh3VGZsZkNmUWNycHJwd0VzMklCM0JfOThNVFBoSGJqaXQ1YWh3UVhfcFJLZGk0bXM4Z3hQbEtkYXpiQ0tHNVNtOXVIV3RVLThBTWNaYjlzVi1xSFBNTzdhcXZjRWgwMGIwRk9UQjc4UXF0QVNJLW1SeDUxNm9MeHhvOW1QQlVkN2VvanZWSUdfSGxfb0dBTmJFOG5Ub1Blb1UyNjNIbTRiTVBQODVqSHcxcWc4X09fMmR1REFwcEc3NXRPYWxKZQ?oc=5</t>
         </is>
       </c>
       <c r="F122" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>UNMAPPED_LINE</t>
+          <t>Supply_Chain</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Insider Risk ("insider risk" OR "insider threat" OR "internal threat" OR "employee misconduct" OR "data exfiltration" OR "privileged access abuse" OR "malicious insider" OR "negligent insider" OR "insider attack" OR "corporate espionage" OR "information leakage" OR "unauthorised access" OR "policy violation" OR "security breach" OR "insider vulnerability")</t>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>The Latest GigaOm Radar Insights For Insider Risk Management - LinkedIn</t>
+          <t>Laskaridis Shipping linked to order for Suezmax pair in South Korea, signalling tanker expansion - rivieramm.com</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>Thu, 15 Jan 2026 12:00:18 GMT</t>
+          <t>Fri, 16 Jan 2026 12:00:00 GMT</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxQZ0Y4d0NPMXBvSEdnamRwQ1BCeFM3THhpS0ZHNTV6Nk9IOUJTTlJpeE1ITEt6WDFNc2haNkxjZ2JOMnozcDZqbHVyVU5ZM3lQdC1ReXFuM2RqUTlUM3RNVUlZdVpiRVlhMVpPRmFxajNnckwzRWpDRjVHNXRXSlJ3RmtvRE1kWWw3NHk4WmE4T1lyV0k?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi3AFBVV95cUxQdjgwRjdrREl1SUJXanJjRzM1SzdOMlVoRWJFb09Oc1RDd29YWEl6Y2p0SVkteVh0WmJQSGF5WlBpR3lYNVFaSVo2Tkt1dVVSRWdUakwxbFNMb20xcHQ4UFY1ak1kQ1RaTlFkaWw3T0F0bEdaTmdSOVl1T3NkYmk3NnlOVHU4M0VtbElhRlhFekVDLUotQ3ZLY1NVLVNMeWNZbkd3MkdCcUhLX2hoakstd0dYRTRRT0lzbnRTcWNrNGVZZ2dJUEpJUy1yRS14NEZuY0ZfZzZmcXR1RC05?oc=5</t>
         </is>
       </c>
       <c r="F123" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>UNMAPPED_LINE</t>
+          <t>Supply_Chain</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Insider Risk ("insider risk" OR "insider threat" OR "internal threat" OR "employee misconduct" OR "data exfiltration" OR "privileged access abuse" OR "malicious insider" OR "negligent insider" OR "insider attack" OR "corporate espionage" OR "information leakage" OR "unauthorised access" OR "policy violation" OR "security breach" OR "insider vulnerability")</t>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Cyberhaven Partners with O’Reilly to Publish Insider Risk Management Guide - TipRanks</t>
+          <t>Gulf Marine commissions lubricant barge as industry braces for new EU sanctions - Lloyd's List</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>Thu, 15 Jan 2026 00:36:34 GMT</t>
+          <t>Fri, 16 Jan 2026 12:08:12 GMT</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivgFBVV95cUxNMGVUdXoyYzYyU2ZMRHBEOEZTbTA3SnBxcGhBQzZWbGlzamVEdEpZTEtTR0dnZHY3dWJJY1Yya1h5VlJ6TXdaVGhOeExkQ3FyT251R2Nzb0dBT3QtYVllQ3NHMHR4bjFaZjZLZjQtMHBYMVJOcXdtaFNMNEVaV3VnUkdPNk9CbUJpNWNXa19UVnZVXzRzRWpWdnZxbjl6RDVTUlNoZG5Sb1BDRVNGVDdTRmNyUXZFYW12U093cWp3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirgJBVV95cUxPQXBXdktjUjUwQUNxa1U5TTduR3BrQzVfc3ZkYm5qTkFSQWZBZkVDRFBKSU9uY2o2eGZJTUVHSnAxR1V4QTExWjRzeS00d2d5b1dfR3Rlai1hQWxhQlVnSlhYSlpaVjZBTnRaRFduUkllWWxWNWF3T19hY05MMU1WX3cxUmpJMlFNdm53UVNqRjhIVk80VHUzaGpaOC1fVk5saWdHQjZtQzJlNUYtT3hJWXNjRmN1VGlTdmVmR25OU0h1TUN1UFJDVXpyM09oNjlYcEQ3ek9JUFdRZVRubVNieUZiTHhvd09Rekp2em16OEVYYUdQTlZON2pFcG45WjZnQ1VONEx3ZVNuOUZfMVZaVXJ0NXdSZUQzUXdCcENsQ3NRemIzZ0ppM3N3alYtdw?oc=5</t>
         </is>
       </c>
       <c r="F124" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>UNMAPPED_LINE</t>
+          <t>Supply_Chain</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Fraud/Scam ("fraud" OR "scam" OR "phishing" OR "identity theft" OR "account takeover" OR "payment fraud" OR "credit card fraud" OR "wire fraud" OR "business email compromise" OR "fake invoice" OR "social engineering" OR "advance fee fraud")</t>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Romance scam victims left devastated as dating fraud surges across South Wales - Swansea Bay News</t>
+          <t>Hambantota International Port hit 428,036 TEUs in 2025 - Port Technology International</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>Tue, 13 Jan 2026 14:07:59 GMT</t>
+          <t>Fri, 16 Jan 2026 11:58:14 GMT</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxPMW14dmxPNDlmOFVMem9vcEI1QVNOSXpKOHZrU3RISUdWcTlTTWdwVEhkRnhrTDNPT1JSdWVLdlBTOVlKaGFtTTAxMzVQTGFTTnVWUXVyOVZnYTA4VEpmNnU1Qi1zUFItTTY5RFlDVE9uRGdOdDNzZ3I5SjY5am1FNk51WFV4WEl3Z1lENnJCTmljSUNtaUZuRm96cWVXOXVEOUpZQjNHLWJZZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilAFBVV95cUxOeXdhUGZXcjFYZWFCUXRXNGR6NU81U19EVHRjTkdHUUo2SV9XMnc0T2J4VTk0SWJBT1l2WDVZLUQ1ckdIeUFfaXAwX1JrMWp5TzFwQXM3OEZjRXA4Umd2M2xvd3d3bDlyVUh2d1c5djVpRE9WSVJvbkotRFpOaXg0TW1iM1Y3V0Fyb0RHYkZQOHBOdWlP?oc=5</t>
         </is>
       </c>
       <c r="F125" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>UNMAPPED_LINE</t>
+          <t>Supply_Chain</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Fraud/Scam ("fraud" OR "scam" OR "phishing" OR "identity theft" OR "account takeover" OR "payment fraud" OR "credit card fraud" OR "wire fraud" OR "business email compromise" OR "fake invoice" OR "social engineering" OR "advance fee fraud")</t>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Phishing Scams Exploit Browser-in-the-Browser Attacks to Steal Facebook Passwords - Infosecurity Magazine</t>
+          <t>Record Freight Volumes on Stena Line Belfast-Routes to Scotland and England - afloat.ie</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>Tue, 13 Jan 2026 14:40:00 GMT</t>
+          <t>Fri, 16 Jan 2026 12:09:37 GMT</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMif0FVX3lxTE9oSHJvcDdadDgyeUFDRjNPS2h5ZjVvcWV6SHFZWEN2Zlh4NkRLRzVjS1FoSVlCQ1RKRzU5NVVJZVhvaDBBdjE5WUE2ZGlmMEVHSnZVWlpWMjk1UENBemJ0T1pKT0FsRzBCZDdBbHhsN0tOUzJSNjZCRE1fX1IzSlU?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxNRHJHTDRzUGxMeWNjNTJDX0psMHBCcTlXN0taSGVzeVlqOWdWR1pMVkRacFVwamFfcERpZkxiNW9tMXBOa1RJa21UWldDeUNSNzJpLXBlMVVvUnI0UnBEMzh1QlN2WF82dS1pdEpIZHI0X2J5Y0g1Y21KUzNqMjl1MVQtTUtPUnQwcWtYeVJjWmlaTmktdUltOG5VUFllblRhR3RzOHRWQnBSOXRzMHFJVVhZMjV0aXpNbkE?oc=5</t>
         </is>
       </c>
       <c r="F126" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>UNMAPPED_LINE</t>
+          <t>Protest</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Fraud/Scam ("fraud" OR "scam" OR "phishing" OR "identity theft" OR "account takeover" OR "payment fraud" OR "credit card fraud" OR "wire fraud" OR "business email compromise" OR "fake invoice" OR "social engineering" OR "advance fee fraud")</t>
+          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally)</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Nationwide issues warning to customers after fraud cases - London Evening Standard</t>
+          <t>How the unrest of 2020 cast a long shadow on Minneapolis in its conflict with ICE - CNN</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>Tue, 13 Jan 2026 17:49:38 GMT</t>
+          <t>Fri, 16 Jan 2026 11:01:01 GMT</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxQMzlXZ1lPNzRRSkFFeEJibkZMOTdRLVpBVmZEYVVjUTRvRERaT1RTRjV3eGxORDRTTjF2ZURSZWF0bHRpVGVFZUJja3VwMGNxUk1TMVVILVNLZG1iZ2ZoTHZEY200ZnpETkFmei1GMWFaTkpudWpyXzl5VHlhNENkdDZhOFVMTnIwTlJzRmdoYWw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMifEFVX3lxTE1FVWRBVzBabTVGSm9hazQzbzJWV2JnRWNrVi1rYzJ0R2g3YWs1UmZLTW1XRkhfXzJST0wtM0JCSXVMZGRkRVBWSWdFZDRBUVBUc09YZ0traE5Wczh4QW9qd2szTXhFdjJhTGEzS2lmaHRrandObzJxT21HMkc?oc=5</t>
         </is>
       </c>
       <c r="F127" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>UNMAPPED_LINE</t>
+          <t>Protest</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Fraud/Scam ("fraud" OR "scam" OR "phishing" OR "identity theft" OR "account takeover" OR "payment fraud" OR "credit card fraud" OR "wire fraud" OR "business email compromise" OR "fake invoice" OR "social engineering" OR "advance fee fraud")</t>
+          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally)</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>San Diego man pleads guilty to role in international elder fraud scam - 10News.com</t>
+          <t>Minnesota Live Updates: Trump Threatens Insurrection Act After Shootings in Minneapolis - The New York Times</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>Thu, 15 Jan 2026 21:08:50 GMT</t>
+          <t>Fri, 16 Jan 2026 03:03:00 GMT</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxNbXZwcEMteTZFU3hpVmlDeUdYdDVWWDY2dU1uYWxJVWVjVHh0bTRRWEhMdE9Vay1haVAzMGFaQjVUVzUyTWh5U285NXZoRzdwazlaRlNTcmg4aldZck5LZGZDWGpqSHcyVjdGVHVwQ2c4VTVZWDlDa2VHd0QxS1VJaG9tVDZZYTd0Ty1vdktJQ202dFlYZ3U2VnJ1UmN5RGtmSGNkOFNCMlZ5Qldx?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMidkFVX3lxTE45V0VrMzRQSVhZdV9EN3pPYUhKY29oV2ZuZDQydmg2dHRMck9yUkxIbWw5OVhTTFNRWUhYV3B3Ml9mdWJFM2dwWjdrU0tTc3lXNzlZUVY2Ulk1ZV92d3NCbVgzakt3bXZjNnM5eG1hQ2JJNHgyRVE?oc=5</t>
         </is>
       </c>
       <c r="F128" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>UNMAPPED_LINE</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Fraud/Scam ("fraud" OR "scam" OR "phishing" OR "identity theft" OR "account takeover" OR "payment fraud" OR "credit card fraud" OR "wire fraud" OR "business email compromise" OR "fake invoice" OR "social engineering" OR "advance fee fraud")</t>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Behind the Top Scams Consumers Face and the Defenses That Work - PYMNTS.com</t>
+          <t>SCOR supports major new AI infrastructure insurance facility as lead insurer - Reinsurance News</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>Wed, 14 Jan 2026 17:01:23 GMT</t>
+          <t>Fri, 16 Jan 2026 12:05:09 GMT</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxPa3VZUzNiank4bGNzNUpuXzZsM0VSY1ZfVUpUTlc5TV9WUXBGZ1NZWVBZb2ZlMTFtRVFqLUV0aGlRTWI1UXNsZkg2bnVtRHFTeXBiQVJybjRFaEYtazdFMXNHT2xPRERMVXdfUUhSd1BlT1hlMXlFZXlFTktPU0JjVUo2QTY3TnlYazY5VGE0UFlRY0s3bFVsMnJGQU5lenFSYUNvXzQ3cw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxPUk41OGpQTTdPcllxS2VHMkdUVWstRTRyblMtNkxmY2daYjNpYkUtVlAxWGlLVVE0X0l6cWJ0MGxVOEsyQ1doUGwxMU45R2FGcWE4LXowX1Y0a3ZFNlVBSmhsODRUaFNiS1BaTHk0bXB6WlVrSXkwUzNnTWVlM3BqOGNsMm1yV093OUdQWFA0N3dzUlBIMEl5eGtYeWVKa0tUR0FSZ1VKamZSUQ?oc=5</t>
         </is>
       </c>
       <c r="F129" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>UNMAPPED_LINE</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Fraud/Scam ("fraud" OR "scam" OR "phishing" OR "identity theft" OR "account takeover" OR "payment fraud" OR "credit card fraud" OR "wire fraud" OR "business email compromise" OR "fake invoice" OR "social engineering" OR "advance fee fraud")</t>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Lifespan offers peer-to-peer program to help fraud survivors - Spectrum News</t>
+          <t>IHG appoints top AI leader as part of tech investment strategy - Hotel Designs</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>Thu, 15 Jan 2026 13:30:00 GMT</t>
+          <t>Fri, 16 Jan 2026 09:03:01 GMT</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxQMm1RMlRSTFBWeVFZR0dfZEFJNEVCWDFTNFhJS01CZTk1UmhuNUF3ZE9PazlOc1J2Znh3VmVlemZPb3psNm1xWGFwbkEzUWFDcGRYbmMtaE5nTzM2TUVLQXdkWFFhYm5DbFdKd3QyNDZqbzl5MWNqTDZMeEs0NFlURGUtUGNMV0M5b3FUZzFFbEdDdDFEN3NjTw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilgFBVV95cUxNVE9VOVBsSUFSQi03X3drUjRHQjRZMklMcFNkVDlac0tzQnlLQjkwR3ZYekZ1alNlREdQQWZCSVhmSnhUbXlscXVyanlvemozU25aT3R0UHlzYmNNQXhBZ1lUNlZtakozY2EtZExwbDhlaWFiWDFESFFkS0FvdTRpZDZBaVF3cWF6bzYxblpBN1hqOGN5cEE?oc=5</t>
         </is>
       </c>
       <c r="F130" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>UNMAPPED_LINE</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Fraud/Scam ("fraud" OR "scam" OR "phishing" OR "identity theft" OR "account takeover" OR "payment fraud" OR "credit card fraud" OR "wire fraud" OR "business email compromise" OR "fake invoice" OR "social engineering" OR "advance fee fraud")</t>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Warren County leaders pointing fingers after $3 million fraud scam - WAMC</t>
+          <t>Weekend weather: A mixed spell to come with rain, cloud, mist and fog - Met Office</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>Fri, 09 Jan 2026 22:12:00 GMT</t>
+          <t>Fri, 16 Jan 2026 11:09:00 GMT</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxQcnp4ZnZjTGlLblVIckVteUZaSFdxR1JNME8tb25nMzJ5RkpRbUtPZFlqTVA5M3p1RHFjN2VBTmtVLXAzSWkwSnlWN1hoM3k0TXlOQU9zOTZRTFJnZTFYTmdVdjV5UXBwWTBWZ1NlNmU4c1pCdUZlZ3otekU5ZXRxT0E4RUxYT3Vpc0ZGTzBDM241WUNiRGM0bFJpOXZ4ZHZxdEdvT3lTc3RpWkxybTFIdUx5RkQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxOYlZiS3NzWFdfRmREekRnRUZjRVJvc1FHTVdNTndHYVh3QUZMbHVoXzRyMHMyaF9Lc2Q2VDNXWHN0NHNKRHI1c1E2MTJDUnpvdzVvVm9Cb1drbXdhMGIxajViUWJWdHNReE9hMDNYcXlfaTNWMFVJSVdUb1RoakZSa1pfNzNDSFV3YUlxZmF3ajVjSFFiLTlHYWFB?oc=5</t>
         </is>
       </c>
       <c r="F131" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>UNMAPPED_LINE</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Fraud/Scam ("fraud" OR "scam" OR "phishing" OR "identity theft" OR "account takeover" OR "payment fraud" OR "credit card fraud" OR "wire fraud" OR "business email compromise" OR "fake invoice" OR "social engineering" OR "advance fee fraud")</t>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Matrimonial Scam: Man posing as doctor dupes woman of Rs 22.7 lakh - Medical Dialogues</t>
+          <t>ECI Software Solutions Named ERP Product Leader from Frost &amp; Sullivan - TECHNOLOGY RESELLER</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>Thu, 15 Jan 2026 12:12:51 GMT</t>
+          <t>Fri, 16 Jan 2026 05:28:46 GMT</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxQbkxWV2t6c2dSaFdMdnR0d2o2dS15NzdVVzBBR19tdHpZMW5uVUcyNWY4RWtuWEQ0M2NjMkhzejkxaGx2d2RpMzBNN1ZLOFY5YTFMQS01YV9fTnViT25mbWl5ZEo1RjkyM0VxUDRweklRYjZKLTRtWF8yS1NTdTd0d3U5VkRWeXN5WW04S05rekZnLTVWdkJYUWcxaDRqcHhQRGI4VFlhZDd0RDlNQXN5QUk3RTFBdkRBS0hv0gHAAUFVX3lxTE5WODZMQVdra1VhYUNteG02T3hieG02TXphSlQyNU9BbzBqM3czZWJHUEp3bnlhMkxvejJ2SmxWc2pvWnVOS3F3MXdGUlE0cTN0V3dla1FpeHoxQXpWYUdLTHdrRE9YYnd2OG9ia3lPdGRCaDJtcmlhMDAxOVBiRzNlNmJLc0VET1gwa2xoTUUxRWFLTlV0UUhYMldVN2d5eTNkMzlUbEVNbUdLeFhWNXlQNTJJR0UzX0dYZkJGdWFoTA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxQQU91dklnWnBEVXhfM0ltRTJyZE5fdE94RnBRRW9SbDZlalVnUmVfOTJPSUNEQVByWmZ4LW1FQWlUTzdtc3lDTV9VbWYybkVMMnQ2Vm9lYy1xaUVBY0pPSzhfUVI0V3dlNlR1OTlHU0VFVUxGOU5NN2dhLVZjZlgxS2h0VkRTakZwVjRodENxT05LdFlORmJnRVpaN2Q5ZFU?oc=5</t>
         </is>
       </c>
       <c r="F132" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>UNMAPPED_LINE</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Fraud/Scam ("fraud" OR "scam" OR "phishing" OR "identity theft" OR "account takeover" OR "payment fraud" OR "credit card fraud" OR "wire fraud" OR "business email compromise" OR "fake invoice" OR "social engineering" OR "advance fee fraud")</t>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>A Houston woman thought she was protecting her money after receiving a fraud alert text. Instead, she lost everything. - KHOU</t>
+          <t>It Was A Big Year For Cybersecurity - Crunchbase News</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>Wed, 14 Jan 2026 03:59:49 GMT</t>
+          <t>Fri, 16 Jan 2026 12:00:29 GMT</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivgFBVV95cUxPOEREWGhqNjdiRFlYbVVkT3JQRGVkX09HMXJwMkJycW1sWWZ2TkFQQ2xvVTk2TDdFRjc3Q3pMMWw5enBjT2phSUp5elctMnNNV3ZudXVrTXdfdjBWLVBySVg0RUc0dmpHbHA3eEQ0NFJSZlh2RWM2R1M0RXhlYWdsRnRSMWIzOXQwQzgtNDF2UVNNQXBOd2hZU3AtdkVDVFIxQUU2WmdIdTA5UXRrSDNEWXpkOHd6cjNpSWMyU2Fn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMihwFBVV95cUxQOXBPcGtpTW5lWVpYcmRYLVJiZmxDRHFOMGdYMXFHR2ZXb0ZEWUZfNFBrQXdRb3cyX0FWcmRNOHJMWE1tazVkRkhzT1Y4YU1qVzhFRmdaZWp6UEFqb3EyR1h0SE85a0UwWEc0cXowZUJma2dEQkFPWGhvOHgyQzFzVlNYWDJieFU?oc=5</t>
         </is>
       </c>
       <c r="F133" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>UNMAPPED_LINE</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Fraud/Scam ("fraud" OR "scam" OR "phishing" OR "identity theft" OR "account takeover" OR "payment fraud" OR "credit card fraud" OR "wire fraud" OR "business email compromise" OR "fake invoice" OR "social engineering" OR "advance fee fraud")</t>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>N.J. school district says $178K in taxpayer money vanished in email scam - NJ.com</t>
+          <t>3 things 'The Pitt' episode '8:00 AM' gets right about AI in medicine, and 1 big thing it gets wrong - Mashable</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>Thu, 15 Jan 2026 16:17:00 GMT</t>
+          <t>Fri, 16 Jan 2026 06:05:38 GMT</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxQb05tZGhRb0N0amxneUcwM3JNYkhOWXVvWHlrOG1iMVVabFBCQXlnV0xLbDlIVlhlQWF1YzJqQm0zRHZIbXpvNW1jVDdmN3ZBMnRTTVR6ZDZ2MGtYSWVOaVJMUjZneW1zUHhxbkh0MDRia1UzakFHT2xDdGdGakRTUzkzbTNqU2lyam91WkY3RDltNXZ2NXhTVzBmWHVKUFJPT2pyZWc5XzA3YkVUbmpNTw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiekFVX3lxTE1iTXBKLXdZY3lneFlvVWxvQ0tzcnBEN1FVZjZFSDRONDdIMFk4OHNFYmxiaWxnUUFwSFNoSlVvQVdabTd5S3dGQkhKRHVUS0dNeENxWHNZOS1rbXFRa0p6MFg0NTlfWjV1X05sdjBHbUxMU0dCRXNNS19B?oc=5</t>
         </is>
       </c>
       <c r="F134" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Current_Affairs</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>(geopolitics OR migration OR economy OR conflict OR legislation OR terrorism OR disinformation OR misinformation OR government OR policy OR regulation) AND (briefing OR analysis OR update OR report)</t>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>PAC report on children’s care homes – LGA response - Local Government Association</t>
+          <t>What’s New and What’s Next: Navigating AI in Technology Transactions - Morgan Lewis</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>Fri, 16 Jan 2026 00:13:36 GMT</t>
+          <t>Thu, 15 Jan 2026 20:37:55 GMT</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihwFBVV95cUxNeU56dGZaNU5WVkd6SGlJc2pLOUl3TnJudmFpZ0FXMFMwS0IyRFRHbmRCQ29PQzNuZXFUb05MRUg5UWxjRm8tWFJLWVN6Tzl6YWJ1M19zTi0xSGJBVkxoUEtmWWN0bGcyMHZ1cGp0ZlhuaWtkcEg1TkF3NWNNZ0xtcnQyUGVqelE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiyAFBVV95cUxNcklOdFYwSVFCQmVNNVR6dGpGSlRxUnFPMzJTZTlka2NacWRKeXR0VkNIV3k2UUluUENpYWFRd0ZpQkl6aEtrUXlvNF9INlk2NFZoTE9jdXYycVVZQ183UklWSFpralQtYTR0VktRNkRXcUp0VV9yY0VxbXd4bVk4cVJiMkhtd1FlZk40VThzNkE2Mlo2bmtqN1ExRzJiNW1YaE10R2dKSkprZjRKQ0RHdWpiaS1OYlY4NU15T3hPVmJZdHhMVGt1bA?oc=5</t>
         </is>
       </c>
       <c r="F135" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Current_Affairs</t>
+          <t>Insider_Risk</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>(geopolitics OR migration OR economy OR conflict OR legislation OR terrorism OR disinformation OR misinformation OR government OR policy OR regulation) AND (briefing OR analysis OR update OR report)</t>
+          <t>("insider risk" OR "insider threat" OR "internal threat" OR "employee misconduct" OR "data exfiltration" OR "privileged access abuse" OR "malicious insider" OR "negligent insider" OR "insider attack" OR "corporate espionage" OR "information leakage" OR "unauthorised access" OR "policy violation" OR "security breach" OR "insider vulnerability")</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Insight - Trend report: stock, rents and regulation in supported housing - Social Housing</t>
+          <t>One click is all it takes: How ‘Reprompt’ turned Microsoft Copilot into a data exfiltration tool - Computerworld</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>Fri, 16 Jan 2026 12:00:00 GMT</t>
+          <t>Fri, 16 Jan 2026 03:11:40 GMT</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxNZFJhOWl3MHdkUXNndHV6UTJZa3FGT2tLTjB2SHpyRmd2aDJUVVNDTGJUYTFkZEVDWTJnWWtBY3JGV3pPWm1zbVk0TjMtQTA4M2R0bUdNVnFzY0lha3haQlpQODVQWDNnQlZKckRENHA5OWNCUDVGSXFrQy1ZcHptaG0za1RxMjk3RWZ5V1B1SkFBUERfdnVLaklWX1F4eEoyNm9fRDBRSnVZZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi3AFBVV95cUxOTVMzczNDaFFZVlFiZEowWE5jaF9LRTd1X2gyWWpEOXNTQXcwTUd1elVGRFdHeFlHZ3RiVExqbUNvNTFnb19pdzZrMy0wWTNBWUdMUnNBc0lseFhUSmpLc0dlcV9ZT2E3UmtGMVQyZHpMOXZyX045aC1fQ1dQVUV6MGVnMFMyX1Q5VzBoYnRDcW9ZdHhiV21BSFdLakdoUUlDQTM0ZlpqTHZ6NS1QeFQ2cF8tMzBaY255SjZJR2tEVVFMR1JKSHlGbEtfTUJqNVRKSXIxWXhmb1Jia3NV?oc=5</t>
         </is>
       </c>
       <c r="F136" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Supply_Chain</t>
+          <t>Insider_Risk</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+          <t>("insider risk" OR "insider threat" OR "internal threat" OR "employee misconduct" OR "data exfiltration" OR "privileged access abuse" OR "malicious insider" OR "negligent insider" OR "insider attack" OR "corporate espionage" OR "information leakage" OR "unauthorised access" OR "policy violation" OR "security breach" OR "insider vulnerability")</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Trump warns of 'mess' if Supreme Court rules against tariffs - BBC</t>
+          <t>The Vertex Project’s Insider Threat Challenge - OODAloop</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>Mon, 12 Jan 2026 20:55:05 GMT</t>
+          <t>Fri, 16 Jan 2026 08:46:59 GMT</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiXEFVX3lxTE1tT2xmbkpMTVNYeG9zSzZMbVBKMFhqSkhLZW9MZTNtSTdKTTc1U01ramliaXhXdEhYYkNQejNpUHd5UlVOMElNUFA1ZWZOc1d0cllTVmJjRTV1M1ZT?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxNd3MzdS16X2dSamdvQXRfTUxWZmtaWHJZX3lNSndaU2ZNQmRhWGRmZy1QbVNldGxFejBKQ05CYzZLMVpKbTNfcmtNZGtLRkdmdDNELXl3VXlBRG1EdjFEVk1VMUhKd2pvMDIzS09iUnFmaEtBQmFweHBXN2pQN1hyaDJnbkNiVEJCZ1duWFVjM3hrM28?oc=5</t>
         </is>
       </c>
       <c r="F137" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Supply_Chain</t>
+          <t>Fraud_Scam</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+          <t>("fraud" OR "scam" OR "phishing" OR "identity theft" OR "account takeover" OR "payment fraud" OR "credit card fraud" OR "wire fraud" OR "business email compromise" OR "fake invoice" OR "social engineering" OR "advance fee fraud")</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>News Content Hub - Greek owners urge EU to take 'immediate' action to protect shipping after Black Sea attacks - rivieramm.com</t>
+          <t>SFO announces investigation in social housing sector - GOV.UK</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>Fri, 16 Jan 2026 12:00:38 GMT</t>
+          <t>Wed, 14 Jan 2026 14:18:47 GMT</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi1AFBVV95cUxONTBBaTczdDFVTmE0dmh3VGZsZkNmUWNycHJwd0VzMklCM0JfOThNVFBoSGJqaXQ1YWh3UVhfcFJLZGk0bXM4Z3hQbEtkYXpiQ0tHNVNtOXVIV3RVLThBTWNaYjlzVi1xSFBNTzdhcXZjRWgwMGIwRk9UQjc4UXF0QVNJLW1SeDUxNm9MeHhvOW1QQlVkN2VvanZWSUdfSGxfb0dBTmJFOG5Ub1Blb1UyNjNIbTRiTVBQODVqSHcxcWc4X09fMmR1REFwcEc3NXRPYWxKZQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxPa1RyYlA4U0FEVkRNRmN0cDV1VVZhQ0RtTFVXNGxkTkM0U0pmcGJKSHFYaG1PZkdXT3AtbFItaXhLczhUSkZlaTlsY3J0eklsclUyS2ZnUnB6QVRvUllZQ1QxZGNDaWhGNkpOWFI5azFJRkJheWpOQ2NCRHJZVEtwaFhkNVpEYlFlamNDNE9wWmY?oc=5</t>
         </is>
       </c>
       <c r="F138" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Supply_Chain</t>
+          <t>Fraud_Scam</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+          <t>("fraud" OR "scam" OR "phishing" OR "identity theft" OR "account takeover" OR "payment fraud" OR "credit card fraud" OR "wire fraud" OR "business email compromise" OR "fake invoice" OR "social engineering" OR "advance fee fraud")</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Laskaridis Shipping linked to order for Suezmax pair in South Korea, signalling tanker expansion - rivieramm.com</t>
+          <t>What is the Minnesota social welfare scandal that has drawn Trump's ire? - Reuters</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>Fri, 16 Jan 2026 12:00:00 GMT</t>
+          <t>Wed, 14 Jan 2026 18:50:02 GMT</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi3AFBVV95cUxQdjgwRjdrREl1SUJXanJjRzM1SzdOMlVoRWJFb09Oc1RDd29YWEl6Y2p0SVkteVh0WmJQSGF5WlBpR3lYNVFaSVo2Tkt1dVVSRWdUakwxbFNMb20xcHQ4UFY1ak1kQ1RaTlFkaWw3T0F0bEdaTmdSOVl1T3NkYmk3NnlOVHU4M0VtbElhRlhFekVDLUotQ3ZLY1NVLVNMeWNZbkd3MkdCcUhLX2hoakstd0dYRTRRT0lzbnRTcWNrNGVZZ2dJUEpJUy1yRS14NEZuY0ZfZzZmcXR1RC05?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxOTjc1bUM5Z2x4cEVYVkxkUFU1VDJGc0lhX3M2NFVkLUIySHR2YnhCM2FCZEF0eG82WHRScHdrc0VURllXMXBCNl92X0o1UGhBTEw5V3ZuMjUxd0NBQlY1X3pRTGF5c2xRZTdzMmkwcVJhMDhSazcwLXpkV2l2dU8xdFF2cHYyUWMwZjdNZnhIZ3NLTmNXOXZQSlBZMFd0UC1fazRibEVoNFM3bHEyQkV5Y18tMGExM3Rld053?oc=5</t>
         </is>
       </c>
       <c r="F139" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Supply_Chain</t>
+          <t>Fraud_Scam</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+          <t>("fraud" OR "scam" OR "phishing" OR "identity theft" OR "account takeover" OR "payment fraud" OR "credit card fraud" OR "wire fraud" OR "business email compromise" OR "fake invoice" OR "social engineering" OR "advance fee fraud")</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Gulf Marine commissions lubricant barge as industry braces for new EU sanctions - Lloyd's List</t>
+          <t>Reese Witherspoon become victim to severe social media scam - Geo News</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>Fri, 16 Jan 2026 12:08:12 GMT</t>
+          <t>Thu, 15 Jan 2026 02:48:00 GMT</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirgJBVV95cUxPQXBXdktjUjUwQUNxa1U5TTduR3BrQzVfc3ZkYm5qTkFSQWZBZkVDRFBKSU9uY2o2eGZJTUVHSnAxR1V4QTExWjRzeS00d2d5b1dfR3Rlai1hQWxhQlVnSlhYSlpaVjZBTnRaRFduUkllWWxWNWF3T19hY05MMU1WX3cxUmpJMlFNdm53UVNqRjhIVk80VHUzaGpaOC1fVk5saWdHQjZtQzJlNUYtT3hJWXNjRmN1VGlTdmVmR25OU0h1TUN1UFJDVXpyM09oNjlYcEQ3ek9JUFdRZVRubVNieUZiTHhvd09Rekp2em16OEVYYUdQTlZON2pFcG45WjZnQ1VONEx3ZVNuOUZfMVZaVXJ0NXdSZUQzUXdCcENsQ3NRemIzZ0ppM3N3alYtdw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxOWUozLWhmNjlBWXRmVHpLYTdWaFZOLXBOVm9rX3FGZVl4VEpTWndVNlhYVVZFY1gxcERPRTh2NFVCcHE0ckRXWG56SUQxeXpJZ083NENLUUhjWUg4M3lySlA2dm9TWmc2bVlHLVpWRHM0OWItSi0wbmFfbEZGX05pZ3lydTMxZmFSZ1pEU1F6TWhJU1VFNEhJ?oc=5</t>
         </is>
       </c>
       <c r="F140" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Supply_Chain</t>
+          <t>Fraud_Scam</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+          <t>("fraud" OR "scam" OR "phishing" OR "identity theft" OR "account takeover" OR "payment fraud" OR "credit card fraud" OR "wire fraud" OR "business email compromise" OR "fake invoice" OR "social engineering" OR "advance fee fraud")</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Hambantota International Port hit 428,036 TEUs in 2025 - Port Technology International</t>
+          <t>Six Prosecutors Quit Over Push to Investigate ICE Shooting Victim’s Widow - The New York Times</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>Fri, 16 Jan 2026 11:58:14 GMT</t>
+          <t>Thu, 15 Jan 2026 15:56:00 GMT</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilAFBVV95cUxOeXdhUGZXcjFYZWFCUXRXNGR6NU81U19EVHRjTkdHUUo2SV9XMnc0T2J4VTk0SWJBT1l2WDVZLUQ1ckdIeUFfaXAwX1JrMWp5TzFwQXM3OEZjRXA4Umd2M2xvd3d3bDlyVUh2d1c5djVpRE9WSVJvbkotRFpOaXg0TW1iM1Y3V0Fyb0RHYkZQOHBOdWlP?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiiwFBVV95cUxQVWdaWUNoaGswUjdPVmp2M25Lc3FkdjgzVkhMOG5tRkZkLTcxRnJLenMwamFpaGJtNHRHQXdKRW1aWGtGdmxZek9mSF9OR2ZRRXRzREItdVdZV2hmTkwtM0FzcHFEd2RnaVR1cXJFd2hVVndUSm13N0Z2TEFLeGUtZ3ZKdDBmX3RGSjRv?oc=5</t>
         </is>
       </c>
       <c r="F141" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Supply_Chain</t>
+          <t>Fraud_Scam</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+          <t>("fraud" OR "scam" OR "phishing" OR "identity theft" OR "account takeover" OR "payment fraud" OR "credit card fraud" OR "wire fraud" OR "business email compromise" OR "fake invoice" OR "social engineering" OR "advance fee fraud")</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Record Freight Volumes on Stena Line Belfast-Routes to Scotland and England - afloat.ie</t>
+          <t>Carraig Donn fraud warning as fake websites target customers on social media - Dublin Live</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>Fri, 16 Jan 2026 12:09:37 GMT</t>
+          <t>Thu, 15 Jan 2026 15:10:59 GMT</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxNRHJHTDRzUGxMeWNjNTJDX0psMHBCcTlXN0taSGVzeVlqOWdWR1pMVkRacFVwamFfcERpZkxiNW9tMXBOa1RJa21UWldDeUNSNzJpLXBlMVVvUnI0UnBEMzh1QlN2WF82dS1pdEpIZHI0X2J5Y0g1Y21KUzNqMjl1MVQtTUtPUnQwcWtYeVJjWmlaTmktdUltOG5VUFllblRhR3RzOHRWQnBSOXRzMHFJVVhZMjV0aXpNbkE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiiwFBVV95cUxOTHNud0JTc3VEQlY2UTdnSjhRV29obEdkOFdEVk91bGxhOHlmeXZKd0tybVJJQ0V0SzBPa0VVMGVkUzJnUkFyb1NSR0hfb1J1a20tNVNSNjRFREhlZWhhWFJOUTRPc3RIQV9jM3BiXzByYUhxZUh5YTNnUDh2SVVtVk1FVnMtcTM3NGNz0gGQAUFVX3lxTE9OcHNibDVLckVvdTJEZVFDWjM4ZHNOUzhmcGt6cHRvT2xMYjZ4Y2RCQWdQdnNFalNLRVhubUlFTm8yYTNBX3R4bW5GT3d1bzdOQ2ZDV09nb24zcXRuWDJKLTR0WTE3WEt1UXJta0UtaVdBOTdYcXFjSm1PN1VkaWlFdjdVLUJITWl0RTRkZGhPbA?oc=5</t>
         </is>
       </c>
       <c r="F142" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Protest</t>
+          <t>Fraud_Scam</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally)</t>
+          <t>("fraud" OR "scam" OR "phishing" OR "identity theft" OR "account takeover" OR "payment fraud" OR "credit card fraud" OR "wire fraud" OR "business email compromise" OR "fake invoice" OR "social engineering" OR "advance fee fraud")</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>How the unrest of 2020 cast a long shadow on Minneapolis in its conflict with ICE - CNN</t>
+          <t>Two scammers plead guilty to $68M Brooklyn adult day care fraud scheme - New York Post</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>Fri, 16 Jan 2026 11:01:01 GMT</t>
+          <t>Fri, 16 Jan 2026 03:30:00 GMT</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMifEFVX3lxTE1FVWRBVzBabTVGSm9hazQzbzJWV2JnRWNrVi1rYzJ0R2g3YWs1UmZLTW1XRkhfXzJST0wtM0JCSXVMZGRkRVBWSWdFZDRBUVBUc09YZ0traE5Wczh4QW9qd2szTXhFdjJhTGEzS2lmaHRrandObzJxT21HMkc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxNVWQySG9DVFZTR0d6azNMRFRoekxOTVV2OGw3VU5EZ19UVVN4ckNSZlk3aE9NY2FFOE9jd0FWMGp3Y3pZUHpiT3U0V3h3TnVEXzJGUW9KTGtvbXZ5YVdLUjJrMUN5dHRRMWpGa0t5QWJlZmkzdWFZVTVGZ09KSDQ3NTZ1Q2ppaW1QZ2ZERnYwVENZdjdqY2hna2NHNk9ocFJqeG0zaDFzUDh4bTRz?oc=5</t>
         </is>
       </c>
       <c r="F143" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Protest</t>
+          <t>Current_Affairs</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally)</t>
+          <t>(geopolitics OR migration OR economy OR conflict OR legislation OR terrorism OR disinformation OR misinformation OR government OR policy OR regulation) AND (briefing OR analysis OR update OR report)</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Minnesota Live Updates: Trump Threatens Insurrection Act After Shootings in Minneapolis - The New York Times</t>
+          <t>Situation Report On The 24-Hour Economy Market Project - Modern Ghana</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>Fri, 16 Jan 2026 03:03:00 GMT</t>
+          <t>Fri, 16 Jan 2026 10:59:00 GMT</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMidkFVX3lxTE45V0VrMzRQSVhZdV9EN3pPYUhKY29oV2ZuZDQydmg2dHRMck9yUkxIbWw5OVhTTFNRWUhYV3B3Ml9mdWJFM2dwWjdrU0tTc3lXNzlZUVY2Ulk1ZV92d3NCbVgzakt3bXZjNnM5eG1hQ2JJNHgyRVE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxOSzRyQ0g0SU1CckxmZjJFZkwwSG1DOURtTlhPWC10ZUJkajNsbk41dGQ5RVhTeFhwZXdlWEx5WFNoSTZJOGxYN2dabml3ZHhFSDhMcTRGN2ZqT2ttbjE1WTFld0N6ajhUQjF1SldJOHpFYWVqekdueGpLNnVBRGVKTmVBY0ZVb0hZWEVXLTJmTGhGSFh4Q1NN0gGWAUFVX3lxTFB5N2VIS1hwSnM2SG9hNmlNWmVYU3pVbTZIdk01eEdvdEtUODhNRUc3WVRNNTB5T0VnaXU1amVVV0xiOEhkWThpcXU2cjVQSlNCZTBGbXQ3MDNiaEJLYlMtY21mNlg2LXdycXNmc3RZY2RXMndESXB4b3dwTkVDLWxBMU5MR05TRll4azBwOXpRR2RxMnZGUQ?oc=5</t>
         </is>
       </c>
       <c r="F144" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Supply_Chain</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>SCOR supports major new AI infrastructure insurance facility as lead insurer - Reinsurance News</t>
+          <t>UAE and Nigeria agree trade deal - Logistics Manager</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>Fri, 16 Jan 2026 12:05:09 GMT</t>
+          <t>Fri, 16 Jan 2026 12:11:44 GMT</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxPUk41OGpQTTdPcllxS2VHMkdUVWstRTRyblMtNkxmY2daYjNpYkUtVlAxWGlLVVE0X0l6cWJ0MGxVOEsyQ1doUGwxMU45R2FGcWE4LXowX1Y0a3ZFNlVBSmhsODRUaFNiS1BaTHk0bXB6WlVrSXkwUzNnTWVlM3BqOGNsMm1yV093OUdQWFA0N3dzUlBIMEl5eGtYeWVKa0tUR0FSZ1VKamZSUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMidEFVX3lxTE93MWM3bGhGYWxna2RUaDBVMkJJYUZNcE40WDlGc1BNSXZGaTY0ZWZ6VFg4cVFieVFMdlljUGxQZ3NXQ2hDNVpSM3hvOEw5aXJjSGxscFFQdG40S0JwZjVVbFI3Y1lZeW9pZE9OMWFCMmN0ZDBz?oc=5</t>
         </is>
       </c>
       <c r="F145" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Supply_Chain</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>IHG appoints top AI leader as part of tech investment strategy - Hotel Designs</t>
+          <t>Global report shows rapid growth in hourly matching renewable electricity tariffs - International Water Power</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>Fri, 16 Jan 2026 09:03:01 GMT</t>
+          <t>Fri, 16 Jan 2026 12:21:01 GMT</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilgFBVV95cUxNVE9VOVBsSUFSQi03X3drUjRHQjRZMklMcFNkVDlac0tzQnlLQjkwR3ZYekZ1alNlREdQQWZCSVhmSnhUbXlscXVyanlvemozU25aT3R0UHlzYmNNQXhBZ1lUNlZtakozY2EtZExwbDhlaWFiWDFESFFkS0FvdTRpZDZBaVF3cWF6bzYxblpBN1hqOGN5cEE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxQY2tGaGdaY3RkM3p5Z3gyVy1BZnNQUmkyd0JwRmxUUEN5bEVKS2w1Zk5YNi13dF9weDZGcGZ5OVZQNEk0WkRacWluQ04yS2cyaElmaklUQ04yQnc0alJ4X3ZJaHQ2YWZieDV5ZmpRdXA5TmR4bEp0TmRhWnBKMnE5bXoxTktKRTItdFMxempQaWNMWm0tS0tyMEUxNGlZMEF0bVF4Zk9EaFhET3hWdzNkc3NxYmpySFFpU2JuVlNoaw?oc=5</t>
         </is>
       </c>
       <c r="F146" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Protest</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally)</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Weekend weather: A mixed spell to come with rain, cloud, mist and fog - Met Office</t>
+          <t>Police remind people of e-scooter and e-bike laws after more seized - Fenland Citizen</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>Fri, 16 Jan 2026 11:09:00 GMT</t>
+          <t>Wed, 14 Jan 2026 06:00:00 GMT</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxOYlZiS3NzWFdfRmREekRnRUZjRVJvc1FHTVdNTndHYVh3QUZMbHVoXzRyMHMyaF9Lc2Q2VDNXWHN0NHNKRHI1c1E2MTJDUnpvdzVvVm9Cb1drbXdhMGIxajViUWJWdHNReE9hMDNYcXlfaTNWMFVJSVdUb1RoakZSa1pfNzNDSFV3YUlxZmF3ajVjSFFiLTlHYWFB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxQeXpKXzhIT3JQUjBGQlB5ajdXTU9JcDBNc016NGl3ZjdMdzdJWkNMWFdHdmVJM05fOHg4dWMzc2JhdE12OWFxU2xhQTBZcFM4b21QU2djaWtncEhCUGFzeVB2TmlUcWZ0RnB5alhKRnI1OXFITzJYZmVibzF3ckJpbTAxRWs1M3p0N0N2N2ptOEVpcXR1R29KVmJjMHo1d1ZjSGE1b2wzNG1GU3M?oc=5</t>
         </is>
       </c>
       <c r="F147" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Supply_Chain</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>ECI Software Solutions Named ERP Product Leader from Frost &amp; Sullivan - TECHNOLOGY RESELLER</t>
+          <t>US says it reached deal with Taiwan to lower tariffs and boost investments - The Guardian</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>Fri, 16 Jan 2026 05:28:46 GMT</t>
+          <t>Fri, 16 Jan 2026 02:53:00 GMT</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxQQU91dklnWnBEVXhfM0ltRTJyZE5fdE94RnBRRW9SbDZlalVnUmVfOTJPSUNEQVByWmZ4LW1FQWlUTzdtc3lDTV9VbWYybkVMMnQ2Vm9lYy1xaUVBY0pPSzhfUVI0V3dlNlR1OTlHU0VFVUxGOU5NN2dhLVZjZlgxS2h0VkRTakZwVjRodENxT05LdFlORmJnRVpaN2Q5ZFU?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMieEFVX3lxTFAyLWwtTlhtOHc0NGZ0YTNuTW1uX0FEZ2M5WnUteGswaXEzdTRyUVo1TDJabmdJcHoxNHBLQmxDM1FRQXdocnVHa3piaXQwWEhwNzNhUU5FV0ROT1Q0M3FCeTgwYlROMzZWTmN6bDk1MlE5YzdNTnVuWA?oc=5</t>
         </is>
       </c>
       <c r="F148" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Supply_Chain</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>It Was A Big Year For Cybersecurity - Crunchbase News</t>
+          <t>Germany launches €3bn EV subsidy programme - AirQualityNews</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>Fri, 16 Jan 2026 12:00:29 GMT</t>
+          <t>Fri, 16 Jan 2026 12:29:48 GMT</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihwFBVV95cUxQOXBPcGtpTW5lWVpYcmRYLVJiZmxDRHFOMGdYMXFHR2ZXb0ZEWUZfNFBrQXdRb3cyX0FWcmRNOHJMWE1tazVkRkhzT1Y4YU1qVzhFRmdaZWp6UEFqb3EyR1h0SE85a0UwWEc0cXowZUJma2dEQkFPWGhvOHgyQzFzVlNYWDJieFU?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxOZGw0ZHU2Nm5WWG83VHVzeHRtakZlTnVuMnMwQTFzeFVVTkNhSFRBSkM5RzdrWnI1aFN1TlZxVVdrWmp2aExlbWdyeUM3eHdkcDBfdUhzNjhBX3BKcDFrd2t4eVpLNkE0ZVhJb0pPODNWQm9kdHRWMWJBWXBkaGR4TW5nRE9zcFYxYjZuXzNLcTg3dDZ5aHRReA?oc=5</t>
         </is>
       </c>
       <c r="F149" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Supply_Chain</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Britain seeks 'reset' in copyright battle between AI and creators - Reuters</t>
+          <t>Electric Power for Sustainable Handling - Logistics Business</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>Tue, 13 Jan 2026 19:00:12 GMT</t>
+          <t>Fri, 16 Jan 2026 12:33:15 GMT</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxQN1RNSkNXMDF2bXVkOVV5VnIyRW5GNk9JMzljdmd1dlB2TVFTLXI3bWMzUGJYWG9JLTFRNHFaUHlqcjlRNjFhQ2c2cDhVMVdqYU91VWYtQ01JRUE0ZTgyLXFVcEowVXYzcGd3bUtLaF9Xa1RORW1CdnBuVmMtakVqbkJFNzZab0w2OUdQaFlFMi04N0NMRU16Nzdfajc3SHRFbHd1ckt0cGNZOU9FcnpoTnEzSS1tQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxPcXJMS3N2TnppWl9BcDJ0SVViUFhYb3NwaUxPTnV1QWlEbU0wOVhLdjJqazRqemZhUHhLTjc3dEZNYnBueHRjRXB2WmRmVVpRVW1ZeXZaWmJReGhNTWdfZFlmbFNhTS13azY4SmxDSENqUDJWM0t5ZERwWUt1bFl6MndMZEZ4bzAzWFliQjY2YXlJb0RVcTQ1OUFQV2R0TWNpTk5DanZ0MjF5WWROZ0k4MUtsU2F1QjY5R1E?oc=5</t>
         </is>
       </c>
       <c r="F150" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Supply_Chain</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>3 things 'The Pitt' episode '8:00 AM' gets right about AI in medicine, and 1 big thing it gets wrong - Mashable</t>
+          <t>Two men jailed for series of burglaries after entering UK through Essex port - Colchester Gazette</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>Fri, 16 Jan 2026 06:05:38 GMT</t>
+          <t>Fri, 16 Jan 2026 11:35:18 GMT</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiekFVX3lxTE1iTXBKLXdZY3lneFlvVWxvQ0tzcnBEN1FVZjZFSDRONDdIMFk4OHNFYmxiaWxnUUFwSFNoSlVvQVdabTd5S3dGQkhKRHVUS0dNeENxWHNZOS1rbXFRa0p6MFg0NTlfWjV1X05sdjBHbUxMU0dCRXNNS19B?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxNOUtOSTFaWHB5Ny1SOS04NXNDcnVlSmtyVm1NeGEtSWtFZ1c1VEVXdWtweGh6X2JHZmtEX3ZIY1k1djZiTmd4RkIxUk1HQXZ6LXBWcFhmdHV0N1NQWVIwczJNZFFwX2FhUGg1WkN1c2FtblZQaFYtM3NkLW9tT003SVdvZWtLbzEwMXhyaTdvVkxDWHVpTVM0QUJR?oc=5</t>
         </is>
       </c>
       <c r="F151" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Supply_Chain</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>What’s New and What’s Next: Navigating AI in Technology Transactions - Morgan Lewis</t>
+          <t>Morrison infrastructure fund invests in US pharmacy logistics platform Fillex - IPE Real Assets</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>Thu, 15 Jan 2026 20:37:55 GMT</t>
+          <t>Fri, 16 Jan 2026 12:46:56 GMT</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiyAFBVV95cUxNcklOdFYwSVFCQmVNNVR6dGpGSlRxUnFPMzJTZTlka2NacWRKeXR0VkNIV3k2UUluUENpYWFRd0ZpQkl6aEtrUXlvNF9INlk2NFZoTE9jdXYycVVZQ183UklWSFpralQtYTR0VktRNkRXcUp0VV9yY0VxbXd4bVk4cVJiMkhtd1FlZk40VThzNkE2Mlo2bmtqN1ExRzJiNW1YaE10R2dKSkprZjRKQ0RHdWpiaS1OYlY4NU15T3hPVmJZdHhMVGt1bA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxQUUhLNFp3cEVJUjlrVF9FVzhUbDhHSlBsT2Y5aF8zSXFDRnN6WHBXYWIzYkg4NE80eUhJbk4zWXo5OVpVZHNzaVlFOTNUckFPUmJYM3lHT09Sc04xRnVUdXVZUEotalVDT0lFSGUwLWhYeEhoLW9vYUFja0F6TDZrSUJsUm0yMU85WVFwWmVDdzVsVjRXMk84WjZPOGp6QklLZlF1VnZ5bTdlWmczZ2hqWGljek5fXzRmakFPR3Z3RW44cG1i?oc=5</t>
         </is>
       </c>
       <c r="F152" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>Insider_Risk</t>
+          <t>Supply_Chain</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>("insider risk" OR "insider threat" OR "internal threat" OR "employee misconduct" OR "data exfiltration" OR "privileged access abuse" OR "malicious insider" OR "negligent insider" OR "insider attack" OR "corporate espionage" OR "information leakage" OR "unauthorised access" OR "policy violation" OR "security breach" OR "insider vulnerability")</t>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>One click is all it takes: How ‘Reprompt’ turned Microsoft Copilot into a data exfiltration tool - Computerworld</t>
+          <t>Marina Port Valencia Targets LEED Platinum - Yachting Pages</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>Fri, 16 Jan 2026 03:11:40 GMT</t>
+          <t>Fri, 16 Jan 2026 11:32:14 GMT</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi3AFBVV95cUxOTVMzczNDaFFZVlFiZEowWE5jaF9LRTd1X2gyWWpEOXNTQXcwTUd1elVGRFdHeFlHZ3RiVExqbUNvNTFnb19pdzZrMy0wWTNBWUdMUnNBc0lseFhUSmpLc0dlcV9ZT2E3UmtGMVQyZHpMOXZyX045aC1fQ1dQVUV6MGVnMFMyX1Q5VzBoYnRDcW9ZdHhiV21BSFdLakdoUUlDQTM0ZlpqTHZ6NS1QeFQ2cF8tMzBaY255SjZJR2tEVVFMR1JKSHlGbEtfTUJqNVRKSXIxWXhmb1Jia3NV?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxPZlZVLTZfaTA0U1ZyMlNRWFlTOExXVWdwalAxQmozOV9uOWxlZ2hGbmg1UHJYQ0ZGZDlvYXZnazg0V0MwUC0yaW9QcTVFaWdRbHlVdVEzdWF0aWN5UDdFYnBlTkRubnB3WVhVMDR2aC1Zejc5VlI1Ni1kUXlPakNJYnFkbnBseS1TZlc3RWhTRUs?oc=5</t>
         </is>
       </c>
       <c r="F153" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>Insider_Risk</t>
+          <t>Supply_Chain</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>("insider risk" OR "insider threat" OR "internal threat" OR "employee misconduct" OR "data exfiltration" OR "privileged access abuse" OR "malicious insider" OR "negligent insider" OR "insider attack" OR "corporate espionage" OR "information leakage" OR "unauthorised access" OR "policy violation" OR "security breach" OR "insider vulnerability")</t>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>The Vertex Project’s Insider Threat Challenge - OODAloop</t>
+          <t>Drug gang who operated across Ellesmere Port and Chester ordered to pay back £1.5m - Wirral Globe</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>Fri, 16 Jan 2026 08:46:59 GMT</t>
+          <t>Fri, 16 Jan 2026 11:42:28 GMT</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxNd3MzdS16X2dSamdvQXRfTUxWZmtaWHJZX3lNSndaU2ZNQmRhWGRmZy1QbVNldGxFejBKQ05CYzZLMVpKbTNfcmtNZGtLRkdmdDNELXl3VXlBRG1EdjFEVk1VMUhKd2pvMDIzS09iUnFmaEtBQmFweHBXN2pQN1hyaDJnbkNiVEJCZ1duWFVjM3hrM28?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilgFBVV95cUxPYVNrM2F4M0d0SjJaTV9FLWhvOTRCb1lXbWtCN2hzWldtbFhOR1JuMDFrR0xIRy1Ga0EyOThiZV95dTNScDZrbkFrZ1lHUE52cGgtWnZMeFdyMTg0Y081eXdvY2hQbjBoTC1GaUQyUTE0UUEtTklDWFdINkJaUmVZU1BDVzQwdTJZWWJ2OU1XemlQOF9tUnc?oc=5</t>
         </is>
       </c>
       <c r="F154" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>Fraud_Scam</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>("fraud" OR "scam" OR "phishing" OR "identity theft" OR "account takeover" OR "payment fraud" OR "credit card fraud" OR "wire fraud" OR "business email compromise" OR "fake invoice" OR "social engineering" OR "advance fee fraud")</t>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>SFO announces investigation in social housing sector - GOV.UK</t>
+          <t>EU allocates $356 million for AI and digital technologies - Digital Watch Observatory</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>Wed, 14 Jan 2026 14:18:47 GMT</t>
+          <t>Fri, 16 Jan 2026 12:25:17 GMT</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxPa1RyYlA4U0FEVkRNRmN0cDV1VVZhQ0RtTFVXNGxkTkM0U0pmcGJKSHFYaG1PZkdXT3AtbFItaXhLczhUSkZlaTlsY3J0eklsclUyS2ZnUnB6QVRvUllZQ1QxZGNDaWhGNkpOWFI5azFJRkJheWpOQ2NCRHJZVEtwaFhkNVpEYlFlamNDNE9wWmY?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiekFVX3lxTFBWZ2U0WHRHdzF6TWV6bktxZlVEdXRhSnp5cHdvc1VMdlE4MmJ2NzhIcnRoWmRob2dGaGpuM1Q5VEVIWnJTNFE5YndrVkRSNWp6UUR0TUltNTJPT1dYeGQ5VVluaWp3cnBSSDNNeVgxWVB5TFgzSmZDMXlB?oc=5</t>
         </is>
       </c>
       <c r="F155" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>Fraud_Scam</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>("fraud" OR "scam" OR "phishing" OR "identity theft" OR "account takeover" OR "payment fraud" OR "credit card fraud" OR "wire fraud" OR "business email compromise" OR "fake invoice" OR "social engineering" OR "advance fee fraud")</t>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>What is the Minnesota social welfare scandal that has drawn Trump's ire? - Reuters</t>
+          <t>TCS and AMD Announce Strategic Collaboration to Drive AI Adoption at Scale - Tata Consultancy Services</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>Wed, 14 Jan 2026 18:50:02 GMT</t>
+          <t>Fri, 16 Jan 2026 05:07:48 GMT</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxOTjc1bUM5Z2x4cEVYVkxkUFU1VDJGc0lhX3M2NFVkLUIySHR2YnhCM2FCZEF0eG82WHRScHdrc0VURllXMXBCNl92X0o1UGhBTEw5V3ZuMjUxd0NBQlY1X3pRTGF5c2xRZTdzMmkwcVJhMDhSazcwLXpkV2l2dU8xdFF2cHYyUWMwZjdNZnhIZ3NLTmNXOXZQSlBZMFd0UC1fazRibEVoNFM3bHEyQkV5Y18tMGExM3Rld053?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxPMEFIX3RmLUYwclFIMXBMX1UtVHJ4eDVJZjkwekw0ZDNlNlI5THhTRlJIVWpyeXV0T3otNDZwcmlyNF9RSHhxbEw3Q0ZHeTZINWRZUjZ4Yy1rRGlhanFMMEVOYU1MaFRocElkQlUtTGtNcUc1amYxZ202cHZzdEVFdHM5WG5IYm85TFRTaTMxWjZyMTM3YWZBNEVVZVNoTGs5a3lnaEwxN1g2djFURmZBV3RJYnJPLUhNWWc?oc=5</t>
         </is>
       </c>
       <c r="F156" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>Fraud_Scam</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>("fraud" OR "scam" OR "phishing" OR "identity theft" OR "account takeover" OR "payment fraud" OR "credit card fraud" OR "wire fraud" OR "business email compromise" OR "fake invoice" OR "social engineering" OR "advance fee fraud")</t>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Reese Witherspoon become victim to severe social media scam - Geo News</t>
+          <t>In a shift from AI hype to AI realism, organizations are increasing their AI investmentswith a focus on long-term value - Capgemini</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>Thu, 15 Jan 2026 02:48:00 GMT</t>
+          <t>Fri, 16 Jan 2026 12:47:02 GMT</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxOWUozLWhmNjlBWXRmVHpLYTdWaFZOLXBOVm9rX3FGZVl4VEpTWndVNlhYVVZFY1gxcERPRTh2NFVCcHE0ckRXWG56SUQxeXpJZ083NENLUUhjWUg4M3lySlA2dm9TWmc2bVlHLVpWRHM0OWItSi0wbmFfbEZGX05pZ3lydTMxZmFSZ1pEU1F6TWhJU1VFNEhJ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMigAJBVV95cUxNdS1OX2JHSElodE13ZE9WVmtTVXhjUXZwU1I0ZFFPaHpla0EzSHR2U2ZRek9DR3BFX0gtOExSYmQ0UkRDaGJEYlMxX1luVTItNVZSbjBnRXFjb2dsNWNndjdjS2k0Z2hrOU9qR0t6SWpwQkJaN1hyVjN0bE9POUVnSHU3RWVuOE1ONENYU1FxTUotZ2lkc3VxR1ZPLVFpOVl0eUFFM3lWRlV1cmg5VlBVVkZ6czQ3b01FWk1vc01WTk1OVmFBMW5jR3l4WnBVUWQyWWFsLS1FOFpDT2JRV08yZWpPaUg5akRKTUdNbzM4cEJuZENCcmtuZm1rYnlWUXY5?oc=5</t>
         </is>
       </c>
       <c r="F157" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>Fraud_Scam</t>
+          <t>Current_Affairs</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>("fraud" OR "scam" OR "phishing" OR "identity theft" OR "account takeover" OR "payment fraud" OR "credit card fraud" OR "wire fraud" OR "business email compromise" OR "fake invoice" OR "social engineering" OR "advance fee fraud")</t>
+          <t>(geopolitics OR migration OR economy OR conflict OR legislation OR terrorism OR disinformation OR misinformation OR government OR policy OR regulation) AND (briefing OR analysis OR update OR report)</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Chairman Comer Presses for Solutions After Massive Fraud Exposed in Minnesota’s Social Services System - House.gov</t>
+          <t>Update on the Government’s plans for audit reform legislation - GOV.UK</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>Tue, 13 Jan 2026 21:11:52 GMT</t>
+          <t>Tue, 20 Jan 2026 09:08:31 GMT</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi1AFBVV95cUxPTVBaOFJBZW1CMTdFalF0dVZvaUlsenJ5RG10UlZnNjd3ZDkxSWx3VXU4LVJIcVBwS0xSeHV0U05qbnNNNkZwUHZ6T1RGWUNQY1o0LUN5bjd0SXhIVlBnbVpZTGRQczQyLUUxaGZsOGhIdDN3N1p1TTFsZndhUF9nV21PZW43YUNYNmdPTEY3OHdkUVpLUFpyUmViMjd5YzVwMXg2UFd6WFRBZWVaYTAxb0hubTI0YkpqelJPdzVDV2VfN3VoNTRCSndJeHFCMXkxT2JrYQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxPQzVwcGdDSDAtcmppcUpFbXl3MEI5ODZFbDdjeFRNQW01S3JPTWVRSlRFMmNnQ0luTmVoejQxRDI4RS1NZW9XX0x6NlhmSEVsbjVFazhjVVc3Q3ZIQkFBWXhTdWo0Y1lrVC1MeF9nTjlTb05xMHRSaVY1VjdEZ19pMnlBa3hkS0hSRExmYmZEWVplVXM1bm9XenBzRQ?oc=5</t>
         </is>
       </c>
       <c r="F158" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>Fraud_Scam</t>
+          <t>Current_Affairs</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>("fraud" OR "scam" OR "phishing" OR "identity theft" OR "account takeover" OR "payment fraud" OR "credit card fraud" OR "wire fraud" OR "business email compromise" OR "fake invoice" OR "social engineering" OR "advance fee fraud")</t>
+          <t>(geopolitics OR migration OR economy OR conflict OR legislation OR terrorism OR disinformation OR misinformation OR government OR policy OR regulation) AND (briefing OR analysis OR update OR report)</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Six Prosecutors Quit Over Push to Investigate ICE Shooting Victim’s Widow - The New York Times</t>
+          <t>Update on Wirral Council housing policy and regeneration projects - wirralview.com</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>Thu, 15 Jan 2026 15:56:00 GMT</t>
+          <t>Tue, 20 Jan 2026 17:41:44 GMT</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiiwFBVV95cUxQVWdaWUNoaGswUjdPVmp2M25Lc3FkdjgzVkhMOG5tRkZkLTcxRnJLenMwamFpaGJtNHRHQXdKRW1aWGtGdmxZek9mSF9OR2ZRRXRzREItdVdZV2hmTkwtM0FzcHFEd2RnaVR1cXJFd2hVVndUSm13N0Z2TEFLeGUtZ3ZKdDBmX3RGSjRv?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxPU0xGSWRXQThCZkY1cVc3UmtpYkhtWThEbWttbjVvS3RFZkhmVWZHZDZBYldsdUx5T2xEeG93eXZtcHlQNXNDeklYa0JaMVBqLVRya0R6UEJMR1JkSlBSSjQ3UkgxanNVLTE1WlVudzZTYXZqTGRKUzRabktuYnVpV3ZaVkl3TERYLThoaXFSWldGZEhyd0Q5TVRHZG5VUE0?oc=5</t>
         </is>
       </c>
       <c r="F159" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>Fraud_Scam</t>
+          <t>Current_Affairs</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>("fraud" OR "scam" OR "phishing" OR "identity theft" OR "account takeover" OR "payment fraud" OR "credit card fraud" OR "wire fraud" OR "business email compromise" OR "fake invoice" OR "social engineering" OR "advance fee fraud")</t>
+          <t>(geopolitics OR migration OR economy OR conflict OR legislation OR terrorism OR disinformation OR misinformation OR government OR policy OR regulation) AND (briefing OR analysis OR update OR report)</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Phishing scam targets prominent social media accounts - pmg-ky3.com</t>
+          <t>Briefing for local authorities on the government’s Earned Settlement consultation - gmiau.org</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>Tue, 13 Jan 2026 14:13:00 GMT</t>
+          <t>Tue, 20 Jan 2026 14:00:55 GMT</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0AFBVV95cUxOQU9YT2dBalRoUXRkTHlqRVJ5WkVWVUtLd1NNR0ZmbGh1bVBMZmNWZHd3SWlQemo4a0dwalFyTUFBMGRBdHNaZERJT3pCS2FkTGI0QmxnNnJFUzQxX3ZUTUhXTkdSaXYteDVPdHRxbnhCbW9IdVVlN0ZmcUpuQU0zdVlVM25OcUx4M2lHMFhpUlBvZjNhVk0tNHRRUFJZekU4ZE50eERvUVNlREdqakM5d21QZVpSNjNRNUw2SzJFbEFVTVJzQXJmdzFUM3c0eGln?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMidkFVX3lxTE5GeS1sVkNULXVfNkxMcTYyY2huSXlQTmFmdWFLQWtGd3c3Wi15dm1vNEd3cGhlRmtPNllLaVdZTEpQMmdZOGg0T3EtRmFQQlFxdGMxajc1WklaVWU0SXk2ZVV4RDRNdl9sQlIxSFZ0QWVucTh1aVE?oc=5</t>
         </is>
       </c>
       <c r="F160" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>Fraud_Scam</t>
+          <t>Current_Affairs</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>("fraud" OR "scam" OR "phishing" OR "identity theft" OR "account takeover" OR "payment fraud" OR "credit card fraud" OR "wire fraud" OR "business email compromise" OR "fake invoice" OR "social engineering" OR "advance fee fraud")</t>
+          <t>(geopolitics OR migration OR economy OR conflict OR legislation OR terrorism OR disinformation OR misinformation OR government OR policy OR regulation) AND (briefing OR analysis OR update OR report)</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Carraig Donn fraud warning as fake websites target customers on social media - Dublin Live</t>
+          <t>Against cheap rhetoric - Policy Exchange</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>Thu, 15 Jan 2026 15:10:59 GMT</t>
+          <t>Mon, 19 Jan 2026 22:01:23 GMT</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiiwFBVV95cUxOTHNud0JTc3VEQlY2UTdnSjhRV29obEdkOFdEVk91bGxhOHlmeXZKd0tybVJJQ0V0SzBPa0VVMGVkUzJnUkFyb1NSR0hfb1J1a20tNVNSNjRFREhlZWhhWFJOUTRPc3RIQV9jM3BiXzByYUhxZUh5YTNnUDh2SVVtVk1FVnMtcTM3NGNz0gGQAUFVX3lxTE9OcHNibDVLckVvdTJEZVFDWjM4ZHNOUzhmcGt6cHRvT2xMYjZ4Y2RCQWdQdnNFalNLRVhubUlFTm8yYTNBX3R4bW5GT3d1bzdOQ2ZDV09nb24zcXRuWDJKLTR0WTE3WEt1UXJta0UtaVdBOTdYcXFjSm1PN1VkaWlFdjdVLUJITWl0RTRkZGhPbA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMic0FVX3lxTE93V3dZU3BwRFl5aXZicnJBVHJfR2ZvanJqOUFJaHdHS2twU016OFRnU1BJd2F4cjEwamJvVGllek80WVJVaTRRd1dFODFGdTE1TFAzM3YzWE9TT3FQQVBCcUJLcFNaTTZXMEM4UXM5LXZkelU?oc=5</t>
         </is>
       </c>
       <c r="F161" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>Fraud_Scam</t>
+          <t>Current_Affairs</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>("fraud" OR "scam" OR "phishing" OR "identity theft" OR "account takeover" OR "payment fraud" OR "credit card fraud" OR "wire fraud" OR "business email compromise" OR "fake invoice" OR "social engineering" OR "advance fee fraud")</t>
+          <t>(geopolitics OR migration OR economy OR conflict OR legislation OR terrorism OR disinformation OR misinformation OR government OR policy OR regulation) AND (briefing OR analysis OR update OR report)</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Two scammers plead guilty to $68M Brooklyn adult day care fraud scheme - New York Post</t>
+          <t>Kazakhstan — Migration Situation Report (July - September 2025) - ReliefWeb</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>Fri, 16 Jan 2026 03:30:00 GMT</t>
+          <t>Tue, 20 Jan 2026 12:03:21 GMT</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxNVWQySG9DVFZTR0d6azNMRFRoekxOTVV2OGw3VU5EZ19UVVN4ckNSZlk3aE9NY2FFOE9jd0FWMGp3Y3pZUHpiT3U0V3h3TnVEXzJGUW9KTGtvbXZ5YVdLUjJrMUN5dHRRMWpGa0t5QWJlZmkzdWFZVTVGZ09KSDQ3NTZ1Q2ppaW1QZ2ZERnYwVENZdjdqY2hna2NHNk9ocFJqeG0zaDFzUDh4bTRz?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxPSTV1Nk51amxqLU5HS0tLTjI1Szk4OGRVdXl0SExUc3VuN1kzZE9OeDJpQ2RCUVRQV3M5a1JIeVdkQ3BxcmVsbDJPbS1wVnN4MHlDVzFxZ2xEVGlZOWxnYVZQZGY1blRQVGQwWUJEcEpmd0E1dEtsNmd4VENFdjVDdDU4TExaaktOUUl3MmM2UFN2N19OYmhWMG9RREV0dw?oc=5</t>
         </is>
       </c>
       <c r="F162" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="163">
@@ -5303,231 +5303,231 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Situation Report On The 24-Hour Economy Market Project - Modern Ghana</t>
+          <t>Diego Garcia Military Base and British Indian Ocean Territory Bill: Consideration of Lords amendments - The House of Commons Library</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>Fri, 16 Jan 2026 10:59:00 GMT</t>
+          <t>Mon, 19 Jan 2026 08:45:55 GMT</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxOSzRyQ0g0SU1CckxmZjJFZkwwSG1DOURtTlhPWC10ZUJkajNsbk41dGQ5RVhTeFhwZXdlWEx5WFNoSTZJOGxYN2dabml3ZHhFSDhMcTRGN2ZqT2ttbjE1WTFld0N6ajhUQjF1SldJOHpFYWVqekdueGpLNnVBRGVKTmVBY0ZVb0hZWEVXLTJmTGhGSFh4Q1NN0gGWAUFVX3lxTFB5N2VIS1hwSnM2SG9hNmlNWmVYU3pVbTZIdk01eEdvdEtUODhNRUc3WVRNNTB5T0VnaXU1amVVV0xiOEhkWThpcXU2cjVQSlNCZTBGbXQ3MDNiaEJLYlMtY21mNlg2LXdycXNmc3RZY2RXMndESXB4b3dwTkVDLWxBMU5MR05TRll4azBwOXpRR2RxMnZGUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMidEFVX3lxTE16N2lSYmRndUhQcTBXZDM1NWNfNUd5RW1CVGRDLTJBTm1GdHZxZjkxUHBuaVF5MGVlLVhxM2lZeEV1Z19hX0xzMGlGVU4yR2M2SU1YM3N4UUY2UFdIUHVYMl8wS3dYSzNhSFZUeG1xMVpWUnlU?oc=5</t>
         </is>
       </c>
       <c r="F163" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>Supply_Chain</t>
+          <t>Current_Affairs</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+          <t>(geopolitics OR migration OR economy OR conflict OR legislation OR terrorism OR disinformation OR misinformation OR government OR policy OR regulation) AND (briefing OR analysis OR update OR report)</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>UAE and Nigeria agree trade deal - Logistics Manager</t>
+          <t>43% of Australian government agencies don't mention automated decision-making: Report - MLex</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>Fri, 16 Jan 2026 12:11:44 GMT</t>
+          <t>Wed, 21 Jan 2026 01:15:00 GMT</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMidEFVX3lxTE93MWM3bGhGYWxna2RUaDBVMkJJYUZNcE40WDlGc1BNSXZGaTY0ZWZ6VFg4cVFieVFMdlljUGxQZ3NXQ2hDNVpSM3hvOEw5aXJjSGxscFFQdG40S0JwZjVVbFI3Y1lZeW9pZE9OMWFCMmN0ZDBz?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi5AFBVV95cUxNdElISWNxVWNER1A1VVVHUy1PVWl4UEdBcWJCR2ppeTN1V255UDNuZVEzcHpEUkJjYnVFdlBjMmJzQWZNUHdYb1BNWnlfd3dDYkJKa1BzYmNHU1BDb3dVMHVEaXRiZ3BZbXBlellyd09SdGp4RmRjWnlsUlZ0RjFMUGNkZWtJc0pndzU5TmJYSFVUNXd1bXI1eEo3TktaY09yTDFPak5MaElKME56YVhLWmFlNmY0SS12clhTUzd2dTFhNFpDOC1rQlN1SmVZazJmN0k1N3lmRUhUUmQyYXpucHNzSHbSAVpBVV95cUxNbHdWbUtTWTloZmlNSmpROUM2a2hDbEFsRmU5S3prVFBBVkUwMkp4UE92dXFGV1dxa1AwN2JHNDhHaF9PWm84c3BPYTk1SC1SeWpuLXRRRnZxMEE?oc=5</t>
         </is>
       </c>
       <c r="F164" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>Supply_Chain</t>
+          <t>Current_Affairs</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+          <t>(geopolitics OR migration OR economy OR conflict OR legislation OR terrorism OR disinformation OR misinformation OR government OR policy OR regulation) AND (briefing OR analysis OR update OR report)</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Global report shows rapid growth in hourly matching renewable electricity tariffs - International Water Power</t>
+          <t>Syria fighting updates: Government, SDF agree to four-day ceasefire - Al Jazeera</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>Fri, 16 Jan 2026 12:21:01 GMT</t>
+          <t>Tue, 20 Jan 2026 18:16:16 GMT</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxQY2tGaGdaY3RkM3p5Z3gyVy1BZnNQUmkyd0JwRmxUUEN5bEVKS2w1Zk5YNi13dF9weDZGcGZ5OVZQNEk0WkRacWluQ04yS2cyaElmaklUQ04yQnc0alJ4X3ZJaHQ2YWZieDV5ZmpRdXA5TmR4bEp0TmRhWnBKMnE5bXoxTktKRTItdFMxempQaWNMWm0tS0tyMEUxNGlZMEF0bVF4Zk9EaFhET3hWdzNkc3NxYmpySFFpU2JuVlNoaw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxOdkxObmxEVDdQQkpNcWNqQUZTcjNQek43aVkwczVmWllRLTVXTmltV0xKVTJGWW1xaGlRUVAxLTlJejZRTVBPYmlHR2poN1pKNDgtU0ExNWY3LWRRdmhjUktDUHF1T3hybnhWREpVRXVaOVJDSGY5RW81OGpkdHVKRlJWNzFXbGp6UjVoeGpIVjdWeko5bmVUdHk1dWpVY2dWRm5ETzhfM0lqYXZ0M3NhdjRSWDJmNTNFNVZN0gHAAUFVX3lxTE1vNmE3TlB3UHhZU21IRXdiREZqUzAtNHJBSVdmZ3U5aHVSMEVIQU13b3ZsMjJjNlJrd2FMRzR3QjVQX3FQM1VsSFJDb1pveTd6dVFnb3BFbTZFTHdJd1VGMHNJMjNIQ1dFOEF0SnMwOHZwMUtWSllJSHdJUG9kd01jQk1mSl9oYUNuOEkxWTZISDRxclpGX0hhdmsxSzJzVXVwYTRtcTByTmVOSTJBS2xfVTF4UG14MFdnZ0Qtd29KdA?oc=5</t>
         </is>
       </c>
       <c r="F165" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>Protest</t>
+          <t>Current_Affairs</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally)</t>
+          <t>(geopolitics OR migration OR economy OR conflict OR legislation OR terrorism OR disinformation OR misinformation OR government OR policy OR regulation) AND (briefing OR analysis OR update OR report)</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Police powers: Protests - The House of Commons Library</t>
+          <t>Gap analysis of the legislative and policy framework in the field of violence against women and domestic violence in Azerbaijan in line with Council of Europe and other international standards - EU NEIGHBOURS east</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>Thu, 08 Jan 2026 08:00:00 GMT</t>
+          <t>Tue, 20 Jan 2026 06:00:00 GMT</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMickFVX3lxTE9xMlE1N0RZekhySENxSkFWejdESXFPS0czV0p1LVZBbllxR2ZIaUJVM255SEpnREpvZWxoaEpnUHAtN0JCdzBvWjYtNnlKUnRmd29JbmxIU3N4NDV2bVQ2OUJHLTkwb3h0UGVrTjhydDYwdw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi2wJBVV95cUxOV1k2d2FMa0xCUWVzLXZVVFF4eDdVeVpLblhFRFVKdWRRa1hEdm5fLUNOcGJRVWdqMnVUVVlSU1NQWnlRQk5OZ1BWZjluUnNQZXFDcXh4YjNWS2MxR19taHNBYVdYekZHUnpMVUJQT1pYZ0FraE1xbVBDNW9JcmJSc2ItQURKc3ladVp3bXc5cjBxcUN1dDZlNDAwUUZpX1N6V3pFeVh6Sk5xTVdPOHgyUjdCc29BRzdESF9KRjEyRWpuQXFCV21oM0tMMjlyWXJFOWxBVXQ5SHpWcEtTT0xoZVZTNXFGVkRTSHBCZFhnXzFaYTNWc3BkR3BCdmZ4LUhOa3Q1STFHLUdDUXBFLTlkQ0dSdGdpam05cVhvRG5WS054MWxCN0t0ZXlyenpxdjkyYUdaeWJMbEtza0twenRVNVBfQnJac1VDc3VwZmNGSFRZZ2lxcW85UEZZUQ?oc=5</t>
         </is>
       </c>
       <c r="F166" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>Protest</t>
+          <t>Current_Affairs</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally)</t>
+          <t>(geopolitics OR migration OR economy OR conflict OR legislation OR terrorism OR disinformation OR misinformation OR government OR policy OR regulation) AND (briefing OR analysis OR update OR report)</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>World to unite in blue to honour fallen police officers on 7 March - Interpol</t>
+          <t>Simulation Of Emerging Market Stablecoin Adoption Offers Banking And Policy Insights, Says Report - Disruption Banking</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>Wed, 07 Jan 2026 13:34:35 GMT</t>
+          <t>Tue, 20 Jan 2026 17:32:33 GMT</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxPRl81VVRsZGM1bThTOC1TdVZnWnRlRDBuZUNDYlBKV21oQm9tZF9rU1dJYzhFeUIyQkFJVmphQ1dtUlh6dzBlNDdQSFktSzZKQ2ZRSzVUZzZxa2FVYWFyTExSWF9fTXd4VUpwLUFZQmUwdEd0VzVLbG02MzdDV3hqTXB2aFc4NTZScUtUODhudVBHLW1ZZUNGNFdDRGp2a3NVdDhjMGdTZ2N3LWc3S2xjVl9pODhoNlBM?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi2gFBVV95cUxOYU9JLXkyWGZqbDBmZmFVTjB5TTA1azRDYjJhczRnODY1S0M2Vy02OHl4N1BDVVNBODY4MEV1MzBTbjBnRzV4WFlWMndteEdCZERHdGtmRHZlSElGelBtN2tPQUxKWG1sM3JrWDFNaGV5ODRQbmFEaERmODlkYW1WUng0S3ZXay03UW11VVFmSXl2ZG1uaEJ6MTBsdmdtbjk2UUZpb2FaY0FLWUtzQURIZG1JV19TdEcteThIQ0J6NzJMWW9hUVAwZEJzdHZ1ZnRuQjVWd0dCZ3llUQ?oc=5</t>
         </is>
       </c>
       <c r="F167" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>Protest</t>
+          <t>Current_Affairs</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally)</t>
+          <t>(geopolitics OR migration OR economy OR conflict OR legislation OR terrorism OR disinformation OR misinformation OR government OR policy OR regulation) AND (briefing OR analysis OR update OR report)</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Exiled prince says thousands of police, troops stayed home amid protests - ایران اینترنشنال</t>
+          <t>Global Value Chains Outlook 2026: Orchestrating Corporate and National Agility - The World Economic Forum</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>Tue, 13 Jan 2026 09:31:30 GMT</t>
+          <t>Mon, 19 Jan 2026 07:38:56 GMT</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiUkFVX3lxTE9nQnVLVllkQzFZUXRSOGFfbTdyTXhYYms1VmNjRXdjLVA5S0Q2ODhvX2Znc0xiaUpGY29VYjdQVXFYVVhpTWlCdE5vRlgtRng1OWc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxQSU5wS3dPZWZUWW56MEh1c0xNUVd2bFV0OTFCMUt2Umh1STg3Y2JBVmNteGM1clllRHRrU0s1Y3IwUGRWWWQ2MUE1U29XZ2xPZ0ZXako0dVlEc3hiY0lBMllaNmZibmZld3B3OUFaeDVuQXpmRUVaQTVRTnhoRXZzc3VGT3hQbFcwTFJIak96Y1BhOVMtSDhOTVJmQmdtRlZKLXBLcHMzeGxOSUtndFc4ZjVTSnRBQQ?oc=5</t>
         </is>
       </c>
       <c r="F168" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>Protest</t>
+          <t>Current_Affairs</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally)</t>
+          <t>(geopolitics OR migration OR economy OR conflict OR legislation OR terrorism OR disinformation OR misinformation OR government OR policy OR regulation) AND (briefing OR analysis OR update OR report)</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Police remind people of e-scooter and e-bike laws after more seized - Fenland Citizen</t>
+          <t>How the UK government laundered racist violence after the 2024 race riots - thecanary.co</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>Wed, 14 Jan 2026 06:00:00 GMT</t>
+          <t>Tue, 20 Jan 2026 13:44:14 GMT</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxQeXpKXzhIT3JQUjBGQlB5ajdXTU9JcDBNc016NGl3ZjdMdzdJWkNMWFdHdmVJM05fOHg4dWMzc2JhdE12OWFxU2xhQTBZcFM4b21QU2djaWtncEhCUGFzeVB2TmlUcWZ0RnB5alhKRnI1OXFITzJYZmVibzF3ckJpbTAxRWs1M3p0N0N2N2ptOEVpcXR1R29KVmJjMHo1d1ZjSGE1b2wzNG1GU3M?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMickFVX3lxTE9waXNjNC1iUVcxZU9Zb1ZFcUVyNkJzQnEyYVVtVDZaTTRzcHdjTjZBRVh1MzF3X0J6UExJcXUyYmVOVGFHT1o5dFdKUjdHejZwa3lvbmZYb3E3SDRfOFF6LTFoRTEwSl9WUENMa2ZkUDc2QQ?oc=5</t>
         </is>
       </c>
       <c r="F169" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>Insider_Risk</t>
+          <t>Current_Affairs</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>("insider risk" OR "insider threat" OR "internal threat" OR "employee misconduct" OR "data exfiltration" OR "privileged access abuse" OR "malicious insider" OR "negligent insider" OR "insider attack" OR "corporate espionage" OR "information leakage" OR "unauthorised access" OR "policy violation" OR "security breach" OR "insider vulnerability")</t>
+          <t>(geopolitics OR migration OR economy OR conflict OR legislation OR terrorism OR disinformation OR misinformation OR government OR policy OR regulation) AND (briefing OR analysis OR update OR report)</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>OpenAI fixes weakness that could have enabled server-side data exfiltration - SC Media</t>
+          <t>Starving in Silence: Surging Food Insecurity in Yemen | IRC Policy Briefing - January 2026 - ReliefWeb</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>Thu, 08 Jan 2026 20:53:48 GMT</t>
+          <t>Mon, 19 Jan 2026 08:03:06 GMT</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxOaVdGMEhmdVBESFZoZmNKLTI1Qklkcmp3cXYxVWEwRFYyaG1hRlc2ZktfS00yb1RQZDlnQ0QwYmZUenYzaE5QbzdiY0hDZUZTcndoTUkzMFQxU2p1eHdUeUNuVzh2LWpWcER6SVdwdkgtT29jUzVwYkZiZ3VFN1lnUi1oVFdwRmN6T3ZMT3VDMjJ2UTNTR2ZxYTFFcWNFUE1xTENIZzB1NA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxNY0V5MmVrLXhaX3k2RF82bkwtVnBkMnBiNGt2UUwzdEdTUVdRcVpncjYyZ0VwT01LeUc1aFRyaVdFTU8wWk92YUhQcDFLN3VySlBfYUpyRmFyRWh2NURMMGNRRHRtcG5NMjBEY3ZfSHFjajN1WkFlRkxhTFR4Z0REbDVrN2VZSkpLT2ZGektuMlNXcW9mc3Ffb011Y1p4LVFkM3IxQUZVWmQ1dkc1VHg0UWFsbUM?oc=5</t>
         </is>
       </c>
       <c r="F170" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="171">
@@ -5543,201 +5543,201 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Financial Services Regulation Committee publishes private markets report - UK Parliament</t>
+          <t>Government &amp; Opposition MPs clash in their responses to Inquiry report motion - Gibraltar Broadcasting Corporation</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>Fri, 09 Jan 2026 00:01:49 GMT</t>
+          <t>Tue, 20 Jan 2026 19:17:50 GMT</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiggJBVV95cUxPdlBRYmxCRnRjTkJLZnFWV0RrdGQza2k3LUpSb1JkTFhBT3BPb1VQYVFvd00wNS1pZWtXNTU5NkcxeDJVQ3RKRmRldnByZEpjRjlkeTIxZ0dBVWc0VG9UeDVrOEV4QkttU0VXVkJ2eFJET056VjBEblBLWVJ0dnZiblBjb1pjRV9kaFR2dWFlcnAzR0MtZkJ3REw2TjRKZE5YMFpHaHFTVTlPNm84QkNnMEtFU0JZNWFvdXF6TkJGbDQ2TUVaNzhTYTl1NTdlSHRFcm53bDU4Q3czY3Q5NjhhVjhoMlV6dFNoMllJSkhmNTJpSmVCRk12RlJZSWJEOExjcFE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxOZlJCUms1RFpNQzFRTE9aTkM0Ui1fNXVpNHlDS0NOUWtJRGg5cjVkdEhzZnVkVFJNMFpoNEJMMWU4N1h2b05MdXB2UkFMb0p0WVRNVGxSdU1rOVI2TGkxazVweWM4bXdSOWVvczh1LVFDZnNoWG5iSzJPTTdNR2NIZnhQcG5nOFBFOHExYUlGdVQ1bzBEd3dxM1ptQnV0MDdO?oc=5</t>
         </is>
       </c>
       <c r="F171" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>Supply_Chain</t>
+          <t>Current_Affairs</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+          <t>(geopolitics OR migration OR economy OR conflict OR legislation OR terrorism OR disinformation OR misinformation OR government OR policy OR regulation) AND (briefing OR analysis OR update OR report)</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>US says it reached deal with Taiwan to lower tariffs and boost investments - The Guardian</t>
+          <t>Football worth £820m to the Scottish economy, report reveals - The Times</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>Fri, 16 Jan 2026 02:53:00 GMT</t>
+          <t>Mon, 19 Jan 2026 17:35:16 GMT</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMieEFVX3lxTFAyLWwtTlhtOHc0NGZ0YTNuTW1uX0FEZ2M5WnUteGswaXEzdTRyUVo1TDJabmdJcHoxNHBLQmxDM1FRQXdocnVHa3piaXQwWEhwNzNhUU5FV0ROT1Q0M3FCeTgwYlROMzZWTmN6bDk1MlE5YzdNTnVuWA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikwNBVV95cUxNczJVX2VIUFYwY3BCYlc4SWJYZ2JtYjN6cVpGVk1wS0NmZG9LSENnT0Y0OXloZzhDMUtWLXdwdWo3Q0VxUVgtN2RuTUpHWV96eDNmNUM5WVVET2NhUXItS0c2UzMxem91NUZpY2tfVVh3MTg4VHhDb3lsbkFpVEh5RVhLNUJJNGdpLTZuUmRhemNFWDRqODVSLWJ0X0FEbHRhZkFnZXRRNmVmTUNPYjVidGpVYk40djExSW1IMG9hMWR4SzJBYTJ0eko1eFBzRVhsaWs3VHY4OEFKU1pROVFHdTVvNTVKYzhWLXd3ZGV0NzVGUU1HdEFXT0oxWFhmNG5rYW5fbDhfNkZadDZSQVlKdHRwdHZTRE9OWnVkZTFjVWljWG9jLVYwVjJ1VUJhUFQyam5iNzFCYzRIbzl2dFMtSVRjbGFQUG9WWXhGS1NFMUxfMDhFcmk4ZlBJYU1IMWxDUVpKaC1zTUVTVE1oTGktLU01RFBNa3FIN1lZYmxBYVdzSFFkeENrdmRsRmVaUnJoTkV3?oc=5</t>
         </is>
       </c>
       <c r="F172" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>Supply_Chain</t>
+          <t>Current_Affairs</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+          <t>(geopolitics OR migration OR economy OR conflict OR legislation OR terrorism OR disinformation OR misinformation OR government OR policy OR regulation) AND (briefing OR analysis OR update OR report)</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Germany launches €3bn EV subsidy programme - AirQualityNews</t>
+          <t>The Latest: Trump meanders through foreign policy ahead of Davos speech to global leaders - thetelegraph.com</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>Fri, 16 Jan 2026 12:29:48 GMT</t>
+          <t>Tue, 20 Jan 2026 22:41:15 GMT</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxOZGw0ZHU2Nm5WWG83VHVzeHRtakZlTnVuMnMwQTFzeFVVTkNhSFRBSkM5RzdrWnI1aFN1TlZxVVdrWmp2aExlbWdyeUM3eHdkcDBfdUhzNjhBX3BKcDFrd2t4eVpLNkE0ZVhJb0pPODNWQm9kdHRWMWJBWXBkaGR4TW5nRE9zcFYxYjZuXzNLcTg3dDZ5aHRReA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxNOWFFd2twcjZFY1hIaWFQQ1pUQmJKemVTOG9BOGVIY0pZRWlISHhWczFZRXFBekJEcVFIN3F5MTVpMXZZNGtRZElxVlFXVlVsODJaYWhTLWR5X3FVbnN4ZVlVSkRVQ2lrUmJfblMyYTk5ZkhwWmFJRTBuWkFfWm1RTVZzZjhLSVBqbXFqQnptU05UZjltVW1aNXlxemo2Tl85?oc=5</t>
         </is>
       </c>
       <c r="F173" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>Supply_Chain</t>
+          <t>Current_Affairs</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+          <t>(geopolitics OR migration OR economy OR conflict OR legislation OR terrorism OR disinformation OR misinformation OR government OR policy OR regulation) AND (briefing OR analysis OR update OR report)</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Electric Power for Sustainable Handling - Logistics Business</t>
+          <t>Syrian Arab Republic: Emergency Mobility Tracking Situation Report - Aleppo Conflict, Round 5 (18 January 2026) - ReliefWeb</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>Fri, 16 Jan 2026 12:33:15 GMT</t>
+          <t>Sun, 18 Jan 2026 08:00:00 GMT</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxPcXJMS3N2TnppWl9BcDJ0SVViUFhYb3NwaUxPTnV1QWlEbU0wOVhLdjJqazRqemZhUHhLTjc3dEZNYnBueHRjRXB2WmRmVVpRVW1ZeXZaWmJReGhNTWdfZFlmbFNhTS13azY4SmxDSENqUDJWM0t5ZERwWUt1bFl6MndMZEZ4bzAzWFliQjY2YXlJb0RVcTQ1OUFQV2R0TWNpTk5DanZ0MjF5WWROZ0k4MUtsU2F1QjY5R1E?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi6wFBVV95cUxOdFpaZUNGcmxfWVhSTDNuYnQtQXR1aVpnbXpMSHVic016NVI3WkZ6M2JQLXg2bjVzaU5zeERhLWNfQTNiRzAwa0tRa0VGYnV0OEVYOFNSMXRiYVVNclVOaFZJcnFhT2hmdURoUWZiODRiTFZMVHAtUWRKeGVfWHFWTTMzYzZVRnJxZWoxRUtkY2Rfd0UxU29HSGh3Y2FWQVFoa2t1QlJUSnpRX3ZlTXpxMmR5RmJsX0lRQkJYUk1GU09fRncwQ1ZYaFk3am5QXzd1Z2kzQ1ZWU2NTV1VubWI4dmg0YzkxUGltcDQw?oc=5</t>
         </is>
       </c>
       <c r="F174" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>Supply_Chain</t>
+          <t>Current_Affairs</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+          <t>(geopolitics OR migration OR economy OR conflict OR legislation OR terrorism OR disinformation OR misinformation OR government OR policy OR regulation) AND (briefing OR analysis OR update OR report)</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Two men jailed for series of burglaries after entering UK through Essex port - Colchester Gazette</t>
+          <t>Global Economy Shakes Off Tariff Shock Amid Tech-Driven Boom – Analysis - Eurasia Review</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>Fri, 16 Jan 2026 11:35:18 GMT</t>
+          <t>Wed, 21 Jan 2026 00:44:44 GMT</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxNOUtOSTFaWHB5Ny1SOS04NXNDcnVlSmtyVm1NeGEtSWtFZ1c1VEVXdWtweGh6X2JHZmtEX3ZIY1k1djZiTmd4RkIxUk1HQXZ6LXBWcFhmdHV0N1NQWVIwczJNZFFwX2FhUGg1WkN1c2FtblZQaFYtM3NkLW9tT003SVdvZWtLbzEwMXhyaTdvVkxDWHVpTVM0QUJR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxPUmNyUzFaNHFjZzVkT2MxQXgwTDdtc2JtV29oZ3FIOE5Fa3dEbjRyWGJmUlBpaXVOUzhkNS1tN0ZsZnBlbVBpR0tGTERqd0FWbm5KZXdfaUpGaU0wSFk1dnNGTlNJU0t1OGMwbHgwOGYyV1p4THYwUVpkeE4wUGdCLVdYb0Zpb1R6REdRalRtVVY5QmYwdEVBNUtVZFV0OFRuQ0FBSllYYjkwNV9yR1E?oc=5</t>
         </is>
       </c>
       <c r="F175" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>Supply_Chain</t>
+          <t>Current_Affairs</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+          <t>(geopolitics OR migration OR economy OR conflict OR legislation OR terrorism OR disinformation OR misinformation OR government OR policy OR regulation) AND (briefing OR analysis OR update OR report)</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Morrison infrastructure fund invests in US pharmacy logistics platform Fillex - IPE Real Assets</t>
+          <t>Government update on new planning rules that could affect anyone with a garden - chroniclelive.co.uk</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>Fri, 16 Jan 2026 12:46:56 GMT</t>
+          <t>Tue, 20 Jan 2026 09:50:00 GMT</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxQUUhLNFp3cEVJUjlrVF9FVzhUbDhHSlBsT2Y5aF8zSXFDRnN6WHBXYWIzYkg4NE80eUhJbk4zWXo5OVpVZHNzaVlFOTNUckFPUmJYM3lHT09Sc04xRnVUdXVZUEotalVDT0lFSGUwLWhYeEhoLW9vYUFja0F6TDZrSUJsUm0yMU85WVFwWmVDdzVsVjRXMk84WjZPOGp6QklLZlF1VnZ5bTdlWmczZ2hqWGljek5fXzRmakFPR3Z3RW44cG1i?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilAFBVV95cUxOUWFsSjNmZjRUeUNvSTlvSlpOV1lFNWMtMFNpdWJoQVJ5d2tGQndkZk8yd1IwalZVODdfMHBOYU9LLXltcDAxWFp0T1F1amxNM2toWUFRbEZYVmlBSjlkY1g4NDhmcU9rSWdHWGtTXzlVNHdka2drYlZ5SVJKdDNwZ2ZoV3oxMjc4a0VuZUNtdUVrY3Rk0gGaAUFVX3lxTE1QZHZYc3FPZkZZdUhaOUF4WlJxQkVzWGxacjlocmJnSVBRNk9UZEY5YVlyTnRON0FvcW8ySU9lYzZCN3dMM3FLdTZWTEVXMEVCSzhaeHpnek52RUVFMHJuN083M1pOdUl4OVRKRW5obDdKLUFKZThETzBJVWhVSzNuYWRKSnV5QzlXa3RwLVdyQmlZMFVzRnN4TXc?oc=5</t>
         </is>
       </c>
       <c r="F176" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>Supply_Chain</t>
+          <t>Current_Affairs</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+          <t>(geopolitics OR migration OR economy OR conflict OR legislation OR terrorism OR disinformation OR misinformation OR government OR policy OR regulation) AND (briefing OR analysis OR update OR report)</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Marina Port Valencia Targets LEED Platinum - Yachting Pages</t>
+          <t>Ladfa Achieves Automated Privacy Policy Analysis of Personal Data Flows with Large Language Models - Quantum Zeitgeist</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>Fri, 16 Jan 2026 11:32:14 GMT</t>
+          <t>Tue, 20 Jan 2026 12:19:07 GMT</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxPZlZVLTZfaTA0U1ZyMlNRWFlTOExXVWdwalAxQmozOV9uOWxlZ2hGbmg1UHJYQ0ZGZDlvYXZnazg0V0MwUC0yaW9QcTVFaWdRbHlVdVEzdWF0aWN5UDdFYnBlTkRubnB3WVhVMDR2aC1Zejc5VlI1Ni1kUXlPakNJYnFkbnBseS1TZlc3RWhTRUs?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijgFBVV95cUxPT29YNU10WFVOeWJWNzJvN1VmdmR6aTJpWmp3S3hwckVNa3Y3NkluWElSaWhneGN1X1BrNWtHNjlnVkJOWm13b0Fsa0c3aVloRDNuLXZyOEVKRWQtTWZHVE0xLWVwOFU5SjJIbVRHczl0STRKWEExbFdaWFY1dGlVMXhwVHlYS0pSSlNMR19R?oc=5</t>
         </is>
       </c>
       <c r="F177" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="178">
@@ -5753,111 +5753,2871 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Drug gang who operated across Ellesmere Port and Chester ordered to pay back £1.5m - Wirral Globe</t>
+          <t>Digital logistics hub to be established in Pontypool - media.service.gov.wales</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>Fri, 16 Jan 2026 11:42:28 GMT</t>
+          <t>Wed, 21 Jan 2026 00:04:31 GMT</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilgFBVV95cUxPYVNrM2F4M0d0SjJaTV9FLWhvOTRCb1lXbWtCN2hzWldtbFhOR1JuMDFrR0xIRy1Ga0EyOThiZV95dTNScDZrbkFrZ1lHUE52cGgtWnZMeFdyMTg0Y081eXdvY2hQbjBoTC1GaUQyUTE0UUEtTklDWFdINkJaUmVZU1BDVzQwdTJZWWJ2OU1XemlQOF9tUnc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxON25VTVlzZHJPM2ZtM2lZeGJ0cWVVcG1pbUlKcEdaOGlDcUhlYlFvNmJmbkVkMGNNOHBLTXI2QUh4eDBadTZKcTRoeEgxNnptZGR3LXdyN3VXNEV4N2luQ3BJVGNnVUlCWnNXOFJlMHlOUm5OLXdtb0tjcmRBOHN0bzYtcGhOc2RZYVoyRFpuQ183X3c?oc=5</t>
         </is>
       </c>
       <c r="F178" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Supply_Chain</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>EU allocates $356 million for AI and digital technologies - Digital Watch Observatory</t>
+          <t>Danish pension fund sells off US debt amid Trump-Greenland row – latest updates - The Telegraph</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>Fri, 16 Jan 2026 12:25:17 GMT</t>
+          <t>Tue, 20 Jan 2026 19:14:51 GMT</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiekFVX3lxTFBWZ2U0WHRHdzF6TWV6bktxZlVEdXRhSnp5cHdvc1VMdlE4MmJ2NzhIcnRoWmRob2dGaGpuM1Q5VEVIWnJTNFE5YndrVkRSNWp6UUR0TUltNTJPT1dYeGQ5VVluaWp3cnBSSDNNeVgxWVB5TFgzSmZDMXlB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxPTFdCbFl6a3FoSlpucUxLdkE2aU9FWUhHbUJ1akZLNTJpdHVsSU11QmJwMVhCZFBWUmRtc09GNHZCcFZnM1VxamRPcHZBS1M1R2xSMlFrYmNNZlBCVFM1YTUtQkVzQXNtSFZLenM3OTZ6eWY1NzdlRl9KbnFZdW9xSTROdnExRDNIOU1zSkZLSWg0NmpEZ1ltaXFjYXZibkhSTmJXNg?oc=5</t>
         </is>
       </c>
       <c r="F179" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Supply_Chain</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>TCS and AMD Announce Strategic Collaboration to Drive AI Adoption at Scale - Tata Consultancy Services</t>
+          <t>Trump threatens 200 percent tariffs on French wine after Macron snubs peace board - politico.eu</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>Fri, 16 Jan 2026 05:07:48 GMT</t>
+          <t>Tue, 20 Jan 2026 07:32:00 GMT</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxPMEFIX3RmLUYwclFIMXBMX1UtVHJ4eDVJZjkwekw0ZDNlNlI5THhTRlJIVWpyeXV0T3otNDZwcmlyNF9RSHhxbEw3Q0ZHeTZINWRZUjZ4Yy1rRGlhanFMMEVOYU1MaFRocElkQlUtTGtNcUc1amYxZ202cHZzdEVFdHM5WG5IYm85TFRTaTMxWjZyMTM3YWZBNEVVZVNoTGs5a3lnaEwxN1g2djFURmZBV3RJYnJPLUhNWWc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxNcHlWT29Qd3gxMjc2dGlQVHlqb05CN0FOYkVkWU5pY1UxWlBtR1dLbjdBWXY3Vl9KcTNpajVPcFhMSW8yMGdxeXJNek5hTmZ2SktsZW94VmJKVzZvSzJ0STB0SkVIYXJQdEY3a0tDb3R0UHVST0JxSHY2S2xHSlNwQS1VQkJUUTVSTzdybVVFRlZQYzE0WjRvVk1ueGdRbVlUUU5reC0yc0xBdVhLSjNzRThYMjJnMWs?oc=5</t>
         </is>
       </c>
       <c r="F180" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Supply_Chain</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>In a shift from AI hype to AI realism, organizations are increasing their AI investmentswith a focus on long-term value - Capgemini</t>
+          <t>Matt Hancock: Port Vale 'did not act too late' over Darren Moore sacking - BBC</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>Fri, 16 Jan 2026 12:47:02 GMT</t>
+          <t>Tue, 20 Jan 2026 14:59:18 GMT</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMigAJBVV95cUxNdS1OX2JHSElodE13ZE9WVmtTVXhjUXZwU1I0ZFFPaHpla0EzSHR2U2ZRek9DR3BFX0gtOExSYmQ0UkRDaGJEYlMxX1luVTItNVZSbjBnRXFjb2dsNWNndjdjS2k0Z2hrOU9qR0t6SWpwQkJaN1hyVjN0bE9POUVnSHU3RWVuOE1ONENYU1FxTUotZ2lkc3VxR1ZPLVFpOVl0eUFFM3lWRlV1cmg5VlBVVkZ6czQ3b01FWk1vc01WTk1OVmFBMW5jR3l4WnBVUWQyWWFsLS1FOFpDT2JRV08yZWpPaUg5akRKTUdNbzM4cEJuZENCcmtuZm1rYnlWUXY5?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiakFVX3lxTE53SDQtRVhWcGlCNGs0WUQwa1o5bUlkWDgtcFJCaFRiVGttMExFOXdYSHFYVEtpZW1mcTVVLTVvTkZQRFVoLTRIczRSQUFHSmtDckF2a3Q0ZlNvWG5ZbkFZem9PT1l1Q0ptYnc?oc=5</t>
         </is>
       </c>
       <c r="F181" t="n">
-        <v>10</v>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>Supply_Chain</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>Sanctions request against Netanyahu filed by UK lawyers, rights group - Al Jazeera</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>Tue, 20 Jan 2026 14:48:45 GMT</t>
+        </is>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxPNWRUUWx4ZVV2WTVYdjl1UmJrY0VzT01TVmxKTUFfR01DU3JPZmF2eU1qYUlJbm4zQkZ4T0JxZTdVenpSRUVDbmY2anhyWk0tQVhVTnZZaUlydkxSTEtuX0ZzYXlRcDA4clpyVWMwblkyVHFnT2ljV3ZxTmFzcG82T3ZOX2RYWWtpVktSYjVYeDQ5d0JacFZUQ0NMNlFuMmNlRVh2aUJobmoxZTh2MFHSAbMBQVVfeXFMT0ZHX2czM084bmtnTHhWaGV5S3c3aExlTnZRaHdvbE50OF8zdlN1RjgxdlZuR2VDU3dTQ21fbzQwYUVEcDJDM2JoeXdsdThnUl9sRTRlaG9rNHdJclYwWEhCV2FvN1hTUTNBemVJbEFHQUN6UTdsTWVTTDZTWHFvOWxxTF9sS2lYeEZXM29qV2xqWGRYX3VCV3ktU2xIZlI0ZWRYR2tLVDRjSlpwNHVaUWExZ0U?oc=5</t>
+        </is>
+      </c>
+      <c r="F182" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>Supply_Chain</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>Wall Street sees worst day since October after Trump tariff threats - The Guardian</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>Tue, 20 Jan 2026 13:34:00 GMT</t>
+        </is>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxNbmdJaFdrX0tBMWNKOHRKRFRoN3A2RXdBT3pRNjZ4d3Fra3laQlNhdE9QcEV1ZmNncW1lb3ozeFpRZEZSSVY3cEZMLVlickFGRkozM254VVdGdWw0WDIwblF0Y182Njc2LVBZVEpMcTNnR0k0VEFmREROUmVmbGhGSXFrbFhJQ1BLWkhoVVpaQUUwdHVHcFliSTQ2QndYaXJo?oc=5</t>
+        </is>
+      </c>
+      <c r="F183" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>Supply_Chain</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>Bilston company pulls out of US deal over tariff concerns - BBC</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>Tue, 20 Jan 2026 10:13:10 GMT</t>
+        </is>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiXEFVX3lxTE8xMk5ReW1XeWV6Zmo5LUVrUzFnZGMzSkJOeEQ5d2JLQk9vWUpUQ3VVdTVEc3RwODVGQnY3eVVpa1dsWVU5ZTZjSjlMWU1tWjVMR0d5am56MG04TDdm0gFiQVVfeXFMTjRNakRkekE2SHM3eVJ0OEI2LVZ2VEZ1bFFPQi1qSzdpd2Mta21xYUdjdk5reG9vMmZFUzctN3hPdjFTUDdGRjFPQ2FVdjNQeXFqQ3V6VkVYWVhVQWcxcUxkNnc?oc=5</t>
+        </is>
+      </c>
+      <c r="F184" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>Supply_Chain</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>Dow closes down 870 points as Trump threatens tariffs on European countries over Greenland - ABC News</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>Tue, 20 Jan 2026 20:58:25 GMT</t>
+        </is>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxQTFpPYWE4Z01ic1VncktNTXFfUXZiLTZsX080Y2J5eXdWRTgxMHBlQ2RiVVA1TkZnbUpaQVpoU0I0ZkZEUlBabU1Vb3VQY184SkpoMnVWM1BlWjdJd2tRaEhtcFN0MU1GWV9FOVc3ZGF1ZFNHSTk2UVNxYlVZb1VKXzd6N1poRzJDLWVja3RBbjhsZWRERXM4aWR3SXFGcms5aHhLRTF2eHloSVBaeDNrV0pDWVdyUdIBuwFBVV95cUxPaU1tY2RJX0ZxVUtaYTlDVWxZZ0JzdmJCZmZ2ZDhyVl9zcVFNaTVON1JNQXZhSjZ2WnZzcEtiN0dMM1U5cVNvVzlIeEtVUE5jRFdOSFZMdXhFekFwM1ZaLTlnT3BJUUNVOVh2eFptR1FEVnBoUnZ2WWlJTTU2b1NJdE9OVlBPSl9PZzJpMV81anprcHl1di1GWFNoRzVLUmkybmY0UkgwRkxoYjh1WU5HUDRjSUVwMXJqVmhZ?oc=5</t>
+        </is>
+      </c>
+      <c r="F185" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>Supply_Chain</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>China hits growth goal after exports defy US tariffs - BBC</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>Mon, 19 Jan 2026 06:40:23 GMT</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTFBLNU8wS3YtcXpNc25uLWZkaW5WazFZSnB0cVUzbExpNDZxQ2Zyc3VINndKRkg1cnl3UzN6T0lNYlRfbjQ0V2tFRTVqZzRmT0dhUTNEVjgzZERSQQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F186" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>Supply_Chain</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>Peloton becomes the latest business to sue the US government over tariffs - The Independent</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>Tue, 20 Jan 2026 23:35:00 GMT</t>
+        </is>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxOSzhZVlBXZThWUjlzaXg3WDhZdW55cGI1V2d4dFJ4V2dRd19HZzlRVGFVTnp4SGxZTzRKREZaMWUwNzd4TnV3SXhtb1Ezb2ZDSXJ4ZS1iZnFfeVkyRG5vSV9yaWMxYXV2LUxjVTVZbzBsdjM5TmdralNJakdBcWhHYWRiZ1huUV9qSUZCdHBJWGRGb3lpYmdwVUNRQ3lzVDU3NGZmaWxKbmk2azZWalQ0aG1uanF1ckx5bHln?oc=5</t>
+        </is>
+      </c>
+      <c r="F187" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>Supply_Chain</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>Trump’s tariffs are being paid for by Americans, study finds - The Independent</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>Mon, 19 Jan 2026 19:25:00 GMT</t>
+        </is>
+      </c>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxQUU1seURsZ01jNE9TSzNkTWVlZE54VENzZUhtTzFxRVhSNWNrQlNXR2U0LUZsdjJ2YTItU210UE5lQUFHSEZnT3NnZm5HSmZpRnlmMmhrLUxtUHRaNExJLXRMSXRETVpFampuZ1lwajJLOVJhY2dzTU5tdHdBVlhWeF9aV1V4dWZHNGV2M3dZdEhLeEpPVEZKY1pPUTlwTHJiVUp0ako2Vlkza3d1WFE?oc=5</t>
+        </is>
+      </c>
+      <c r="F188" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>Supply_Chain</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>Supreme Court Doesn't Rule on Tariffs, With Next Potential Decision in February - Bloomberg.com</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>Tue, 20 Jan 2026 21:12:33 GMT</t>
+        </is>
+      </c>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxNeGViUXV3eGhfRlVicUhmejNPLUgyN3IwRjlYazE3RlBNbkRDNEtXR2llWnhZLThCS0hwRHllbDItem9VU0pnaG1WV3M3b2ttbC1hcVEyWFZYSFZuUDFxaUpCMm5NWDYxOU5IRWo3Y0thQ211X2t0RWN5UXF4QkdjcFl4TVRqV2NmVXhqM2RrUGdUNUVqYVVxWHlYN09oN0VFVGF5YXEwcDZSUUY1elYyRVNR?oc=5</t>
+        </is>
+      </c>
+      <c r="F189" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>Supply_Chain</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>Scotland's papers: Trump tariffs 'devastating' and hospital 'cover up' - BBC</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>Tue, 20 Jan 2026 07:20:58 GMT</t>
+        </is>
+      </c>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTE42SkFvWWlQazBjMlFFTi1HNkFnQ29feHJMd21wR0VSSXhaWTFWZHZYRHI4ZjNNVGNWdHgtUl9RcVpRM3BkUms1bENpNnJ0UXZlRDl6em1mVU1wUdIBX0FVX3lxTE9mRHdyeVRZNU85Q3Z5Z0ZvQnRlbDZvQmxzWWl3QmhHc1ZrMkNuWnNOem1LVEFlaVVRMUpSMWxsMzZaQTJianpYa1h6Y2pZOGlGbDdJS0NYNVdqZFZmUHNv?oc=5</t>
+        </is>
+      </c>
+      <c r="F190" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>Supply_Chain</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>Tariffs starting to bump up product prices, Amazon CEO tells CNBC - Reuters</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>Tue, 20 Jan 2026 15:21:37 GMT</t>
+        </is>
+      </c>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxQWEhqTFQ4N2lUNXVhMWVhS19ya1ZaQ3VqMXN3YV9jLWhIOW43dzlJOHJCMHNXWlV4TXN1QjJnd0FVcjdKdjlqVWV3a095aDRMRXJfNkROaUczeVRBVWtFRjA0djgyLTVKTnRVNm1pekxHR3V1OElSZDg1WkpGR2FZdXZNd3NhczlZdGFsY3NKWDc3ajNvRVFwUzI3bzZqbTdSR3BvVlNhVGNIN2ljQ0dvS193?oc=5</t>
+        </is>
+      </c>
+      <c r="F191" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>Protest</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally)</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>The Bell Hotel protest sees Essex Police officer stunned by laser - BBC</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>Tue, 20 Jan 2026 10:11:04 GMT</t>
+        </is>
+      </c>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTE42cW1IZnAyaEhnTlBoYS02VmhoMnc0UDhZRndjTHNDTXB5QS1vVnAzb0phZHVVQlZER0JYSHZSYXFRSVZiMWtrX2stdXNsS184dHlTN3Rnd0dUZ9IBX0FVX3lxTFBDUzFueDUtNDUyWVJkdU4zVk55Qzg3RFhmekNKaGdNS1EtLXdZYUZmb3lKWXFGckJUWlJjOFI5RmZIRXdtenVvLWExX3ZwSTF3YnFzMUlsTWtpNl92VG1Z?oc=5</t>
+        </is>
+      </c>
+      <c r="F192" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>Protest</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally)</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>News Article - news.devon-cornwall.police.uk</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>Fri, 16 Jan 2026 14:19:58 GMT</t>
+        </is>
+      </c>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxNNDVBY095eExjcHBzcnlHS2hpSGEyMExyTXFFaThzUnkxMDVLRGdFX1FhQ2lGbTRQX182NkhtUjFOcWVSMERSSjFtNGQwVlMzUlNFYnRPZVQ1bVFHWS1zQlpsamZGQ3pacF9FeENCaXc1b1dTaDF0SlNrd094Q3BZckQ5SzYtdHhycnN3MEFiZmo?oc=5</t>
+        </is>
+      </c>
+      <c r="F193" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>Protest</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally)</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>West Midlands Police under fire over Birmingham bin strike failures - The Telegraph</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>Tue, 20 Jan 2026 20:05:00 GMT</t>
+        </is>
+      </c>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxPUExoLXhrUDg4T09TWTRCbFo2ejI2ajItREJIUVczOUp1OWlGTlZONHJaZUxZSjUyd3NNV29lOUFZcnI4Y1M0U0lWSzh6VlF0QmZ5TjdQb2lxNnk4NkYwdUpCMXpka0hCbHhjSTIxYmIzOEdnd20xVVhPMTVsSzNaTmxzQ1pKYk11Qk9ibWdJNFNpZ1dDaEo0M3JoQ0NNYmpESVdKVWhR?oc=5</t>
+        </is>
+      </c>
+      <c r="F194" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>Protest</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally)</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>Braintree: Dispersal order ahead of planned protest - Essex Police</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>Fri, 16 Jan 2026 16:55:00 GMT</t>
+        </is>
+      </c>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxNLUFrQVFPNkVORExCaUU2SUctZHZ2UXZkM3JMQndxcmRDY1BIaElXWFl4QzFGbFVMUHlRZFhtUG1aVURZLTFSeFpjZm52akNYMFV1TkQ3RTB5ME9kVFZsV1M1WVNWUWFwV1UteU0zdzNRV3JDUVN1LUJHNjhKX1FWaUx1eThXQk5aX3lKQVhJVTRzOTRCNEU5ZjFR?oc=5</t>
+        </is>
+      </c>
+      <c r="F195" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>Protest</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally)</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>Fresh Russian Strikes Cut Heat to Thousands in Ukraine’s Freezing Capital - The New York Times</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>Tue, 20 Jan 2026 20:01:15 GMT</t>
+        </is>
+      </c>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiigFBVV95cUxOTWNaaUVGQ2F6VnZ6WEdMSmRyeTNlRXlILXpPM2huMjJJSU5XQ2NFc3ZPejE5R3FxQ3BPMy1mR05oM2V3cXJWbVAzLWV4WEVULUZ3V29aclVCUVNBeWtremtDUGMtbmJoQVE0OGV0SHVwR0JGaU4tWHROcTVqQ2t2d1gzWE1EazZNQWc?oc=5</t>
+        </is>
+      </c>
+      <c r="F196" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>Protest</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally)</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>'Public unrest' fears over asylum seeker plan as council and police object - dailypost.co.uk</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>Tue, 20 Jan 2026 16:59:00 GMT</t>
+        </is>
+      </c>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMilAFBVV95cUxNalRUOUdITjNacGIyNjc1R1h0YURkUTc5bDVoTWJzd0U0NVNYbjQ2QWF0Y0hNV2lMaWpESV9uX3lZNWdsSXA2bUxlOXhDZWYtZS04NGNSR0NVTExRZ2d5Sk1nc2JkSnJmY2hhVEtrNXk5VEZqTHJkN3JfVk85RW9pTzVLNkk2VlAzRERVcFU3VHktVXow?oc=5</t>
+        </is>
+      </c>
+      <c r="F197" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>Protest</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally)</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>Police officer injured and two arrested following protest outside Bell Hotel - yourthurrock.com</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>Tue, 20 Jan 2026 12:18:51 GMT</t>
+        </is>
+      </c>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxPQzEybFQ4dDdiTUhoWE1BanhZcXVqclYtVnFGaldzZnJrUVl0Tm5WZ0pTYVhEdWllajJpY0NHYWRIcnN0QlpjNFVPeE1kSDFmU3UwRlVUVDNrcV9rR3BXc2c3aU5NYzFlM3hiZGtmTGM3NWQxU2Q2b2trRjdDQ2poaTVBLVRPQkZuM3JZTFdGcmRfYjVheTh1Qk9nZTd0T1RyN25QODV3VGpZaV9aU0Jfc19Rd2hOWVZr?oc=5</t>
+        </is>
+      </c>
+      <c r="F198" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>Protest</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally)</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>Guatemala mourns 10 police slain by gangsters amid state of emergency - Al Jazeera</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>Tue, 20 Jan 2026 07:21:31 GMT</t>
+        </is>
+      </c>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxQWlVpWExzSWVSWDBQeUlrV3BjU2VzTjFOMEE1bjFiSkpJTDVDVjNDNXB3eGlZSUoxNFNldjk1cUNDUDZGeGpNX29IT29pMk5fcHpWWExTZjZmMWlEVkVtZThfREtXWXlhRU5TTHRPc2MxZWV5QXl1cnRsVzVEQVJtQ25BZndpY1FkNVE2emNCRHAzWnlkandKZEktNmNqTllsUkQ3R2xEa3RseHYyMWZR0gG0AUFVX3lxTFB0a1pMZG9qbUsxUng3eHlVMmlhaFZrNXlPMlFxNHZoOUFzY25FV0lMNUZCaXlxam1kSHl2RlJNblllODRDWTlNS2RfaUxZMjRLTG42VzA0NGkxLXlsMnhtNXJDTEhfODJlVVZjZDZmWjVKVGxnNExZSzZqTlE0NXJFd0VXOENsQmJYMHk0OXVpb2luOFo1TGpHRkQ1M2VkQXkybzF1N091ZFVJUzlTbzJXWmxuag?oc=5</t>
+        </is>
+      </c>
+      <c r="F199" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>Protest</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally)</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>Iranian protesters in Yerevan blocked from march as police make arrests - The Armenian Weekly</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>Sun, 18 Jan 2026 15:39:29 GMT</t>
+        </is>
+      </c>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxOdjZUd3BsOTBIR18zQVA1Y1o1RklETjVBUmtlNzIwZUJ1UGU3ck5fNlVyY3pyNllNZFd4d3JkcnI3WDVsYVVsZW1KZ1RkZXctbFpxaTBwYUl5UUFrMktIWFUzYnBCWkFGdDdGLU1LaXlta3FOZ2tyTHRHdU9pRlMyVU1GUjZYVnFxN29PU2w5UUc3b0NWZ1RET3dJR3Z0cFR3Yy1oLW1mSG9HakY3Unkw?oc=5</t>
+        </is>
+      </c>
+      <c r="F200" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>Protest</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally)</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>Complainant protests Suwon police decision with cavalcade of cows - koreajoongangdaily.joins.com</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>Tue, 20 Jan 2026 09:37:18 GMT</t>
+        </is>
+      </c>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi4wFBVV95cUxPaTNqTGZ2U0wtODF0clBvTzNoMTFNWG9laGZLTDlESDRfUFBwczJfdXZmWklZMFNXQmRJVFZIYk1rWmZ4N2pGTkFDbXEyYlV5YWZVWVBHTWJ0NzFlSmt0bEN6anNyazVFNGNjS2txQzlhTjJwNEF2M2VjZmZMWlhYVFROZU1PWDluZW5TRzRnWEJKS0V4NG5weHNUSmxlREloZXlCTTNhQy1hX0ktRjZlTXNWdHdCeXRWRmlyWFJqSDNxY1JpVUFqVnpPa21zNGg0d19UeWpPUTFqYmFsUEIwV1VQVQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F201" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>Protest</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally)</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>Teen killed by bus; police launch investigation, deny link to nearby protest - timesofisrael.com</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>Tue, 20 Jan 2026 15:48:24 GMT</t>
+        </is>
+      </c>
+      <c r="E202" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxPSF9LT3FjdFZZOTJoc1EzRFF5eWVUNHVzWjlvRFFpd2g3ZldLamtVTUZjTmJVUVMxZGJ3cG9Ga2V1ZkxBSWJEQXE1MFhTeHVkeVpkMFJVU1Y4Yk52TWhmcWV6MFB3YkJjV29JQnViRzlUOHpsM3kwcnEtd05mcXVVWVBQOUs5Mi1LZWNEOEd6T0FyY2xWUlVWYTQ4X0c2aEdObTZwcWFfZDhGQTZjd0VrQU84S2lzZm1mUHVmcw?oc=5</t>
+        </is>
+      </c>
+      <c r="F202" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>Protest</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally)</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>Source Capital Declares March, April, and May 2026 Distribution on Common Stock - Business Wire</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>Tue, 20 Jan 2026 22:15:48 GMT</t>
+        </is>
+      </c>
+      <c r="E203" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMizwFBVV95cUxPTG9lSENxZU56RG1UVFlVOC0tVU53ZVNEZGd1UDNKeVFyZTZaNWNQYlVBenpQM0Zhb0ZjMFQySUxCMkxmY2tvbDd3OTgxU3B0cVlyak9wcEt2dTE5TlFhNkRxX2J6YlVMQ0pRMzR0Y24zbnd0YTRVUXhGWC1CZnBVSzEwRktYYy12R2lkcEY0cnZnT0xFbzNxMGxWaENfUl9KNUtfMUVrbVhLWXRWMmowQWNWM1E5eGR6aFZSTDdkVFJxRTNnN2lWZ1pOcEV4MTg?oc=5</t>
+        </is>
+      </c>
+      <c r="F203" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>Protest</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally)</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>Invasion Day and anti-immigration marches to proceed in Sydney on 26 January after protest ban scaled back - The Guardian</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>Tue, 20 Jan 2026 06:37:00 GMT</t>
+        </is>
+      </c>
+      <c r="E204" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi8wFBVV95cUxOcXZHd3d0M2FpZTRQNUVRVnYwblA1RnlpZVE0RHM2VlRja0NUNkx0dS1Tb3lqbXlYNkRFTlpHdHQ2SE51cHl1N0hDVy1TZjhXamRfelFiSWtEUk5iZHBTcXAzUERjWXhKVU11VEswdkNuQ0dEVXB3R0U4THByUTNzUkxzbG5sZXBQQ2k5cHVWYl8yZmNmMWYyUk9fbUpoNWhMaFFZenY3NTdBNjlvMDYxWUpBQ1JCTDV2Yzh3eXVDRWRvUlFhZXAyMXRpb1ZQSkRyNzlhOENtY3Z1cTNGcjhnLVN2NTEzMzVVUkk0clFEYUlmNDg?oc=5</t>
+        </is>
+      </c>
+      <c r="F204" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>Protest</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally)</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>French journalist arrested as police break up Istanbul protest over Syria offensive - Le Monde.fr</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>Mon, 19 Jan 2026 21:21:35 GMT</t>
+        </is>
+      </c>
+      <c r="E205" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi7gFBVV95cUxNY2FMZTFSSno3ZmFBWHVfQ3JHUmE3clR4eVRIQTZCYlRxekpRYW9td1BoYnZlSmQyZTBkeWF3aXJkSTdWOVZXc1U3RlBDTkc2MURiRUxyTmlqWml0d1JZSHRYd01OeDNRNVNDYkJNT2VUMkFYaUg3VFFfREdjRWpEN2VCVVZPeUp0NG9INF9kUG8wZW82WlJjeXFPS3VHMWhtbGtGYkZTVndNcnZmalFweklCVHNtSzJ2TjlHenRRUDZNUkpGdVRkYnBmQTlGWThPZ01iM29FZ2JhbDJDamhRMjl3M1kxLXlPallHS3hn?oc=5</t>
+        </is>
+      </c>
+      <c r="F205" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>Protest</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally)</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>Hundreds protest at Parliament against attacks on Kurds in Syria - NL Times</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>Tue, 20 Jan 2026 09:30:00 GMT</t>
+        </is>
+      </c>
+      <c r="E206" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMigwFBVV95cUxNNWVrUEhZU3ZXUDlLb3BoZWd1YUxwdGFxQl9IZjhyb1oyMUh6VUZkYTg3TzJPZUp3Um4tN0hjWTRicXBzUWduMUt0ZF9fTU9iRjM5bXQxSEJzei1NNmZQaVFUOGVPTUQwYUROZUJRU0RsSVFaUUlBX3E4cFltZ2tJVE96NA?oc=5</t>
+        </is>
+      </c>
+      <c r="F206" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>Protest</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally)</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>Stephen Miller claims Minneapolis police told to ‘stand down and surrender’ - The Independent</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>Mon, 19 Jan 2026 17:22:00 GMT</t>
+        </is>
+      </c>
+      <c r="E207" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxQbURZbW9UMW9RZlQ0OUJxTEdPWXJHLVBzWjFfV0dRdU9pUHhBTDVLbHNVX2tfUjJKb2pUU2RRWmJMdTRkQVNvQWFxTlRxdUlQZTl0WE85SjdoNWs0UGpJYWZ0RTJZQ19nOVhxY3g1RDRpMzJSeDA5djRmdjVJczBFRU5BbWY0REUzNEJHVmd6LXBid0N5UmFWTTBHVjZvSUxBQWltNlVCX04yT3QtUUprS2xFang4Zw?oc=5</t>
+        </is>
+      </c>
+      <c r="F207" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>Protest</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally)</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>Ratos Capital Markets Day 19 March 2026 - TradingView — Track All Markets</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>Tue, 20 Jan 2026 09:10:00 GMT</t>
+        </is>
+      </c>
+      <c r="E208" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxQS0lrQXd3UjBQc3psVllYSm1RaEMyMmJrbjhMMFFyOWk5ZWI0WTJJZDBNeEZ2UXFLT2lBNi1jUEF2U3JMRHVoTzBITko2UmZ1N0M0YWVJYlp5Y2pkNFh0VzFfd0h0UWFrOFB6TzRRbnJsa1ZUV2c4cDk2c0hNaWpkVzI5TGdaUkZfa1FhZm9IZ1FVakJfNHgyVHBBOEUzZmJleXZnZUJvakQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F208" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>Protest</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally)</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>Iran warns protesters who joined ‘riots’ to surrender within three days - timesofisrael.com</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>Mon, 19 Jan 2026 18:37:00 GMT</t>
+        </is>
+      </c>
+      <c r="E209" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxPcUxfNGlNZnlzTUN1aEJ5dHZYNm5uQThGSnA1MFpIS1NmZ0VXUG5BLXl3ZE5lMzdsS0otX3gwbjlDa1NtNzkxLXdGZ2R1a01fVWU5UFFlYkV2VjRMVzZQTFZ4bnVTcnpva1lscFV5X0FoSV94RFVwUmdoZU0ySlpJNkJIN09sbllFYjNydlZzcGk2RUZZX3V5dXNfSUREZGJOcVHSAacBQVVfeXFMUDBmQVJsaHRvSzlFaFBtRTY5Wkp0NXpNel9JT19pY2xYd2NzdnYtX1V6U09INlNsNFl3NDJsbzBBOEV0NHZyTlZCTUhLVXFPNVdLRzh2WGN5Wk9UN0xwN3hwQzhzSkxCNzlLVl9sN05BdzhmYzJQT0xSZi1zeFRJWGxlNldseTdrc1F1eVl6YVdhMV9TeERvMHBsUmdmbWFvMVpqdlZFUDA?oc=5</t>
+        </is>
+      </c>
+      <c r="F209" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>Protest</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally)</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>Police force explain the laws surrounding e-bikes and scooters - cambstimes.co.uk</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>Sat, 17 Jan 2026 06:01:00 GMT</t>
+        </is>
+      </c>
+      <c r="E210" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxOakhQSnpSQUF6d19KOEVONEFHYXJtdk9UbDVOSGRQa1QzcGFMVEQ2LVRSSE1TMGZLOGZ0TjJwVC1sWmpWTUdwRm90dnBOOGp0QXZqaHVQZGZNWW5VdEE3V0ZubDFMb0FfQkkxYXphamdRT3c4cHplb0tGX3ZNRjNGZ0RzaWtmWFJJV0VsV0pVc0JwbFJtVkdmRFVNdW9xSEE4bmc?oc=5</t>
+        </is>
+      </c>
+      <c r="F210" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>Protest</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally)</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>Route 4 opened after ultra-Orthodox protest; police say officers called ‘Nazis’ - timesofisrael.com</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>Tue, 20 Jan 2026 16:03:24 GMT</t>
+        </is>
+      </c>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxPbjdEQWJ5SUxFSThwNlNGajRmSzEwMEpwSEJsTWNYcUxFV1JuS2hjNTBleVpneUllQktvTUc5UG5QYWFrMWlIbnRzdGhQdVplTWVYdVlZcnhJb2oyTUhRQUpvTE1hak9SVGZ5NVVTYW5PLU1hLW0xbzVSYjFGdzAwZFN4SjlHcGNyam0zR1E2TlZpSk5adjRGUFRuV29aVjNhSzN2dTktd1BkeERmSmNjenVaMFd2VUNWWEVDTWpjbw?oc=5</t>
+        </is>
+      </c>
+      <c r="F211" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>Protest</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally)</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>American flags torched, riot police clash with protesters ahead of Trump Davos arrival - Fox News</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>Wed, 21 Jan 2026 01:11:49 GMT</t>
+        </is>
+      </c>
+      <c r="E212" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxNUlJBNklhTjBwclFVOVNVRUhSUWdvVFViRWFraENQVlNkOG1EdDAxdHBJN3UySXJsRnkxeFN4RDNEV2J3ay1XRlZCdFNFR1pKT1NQN0Z3RFBnM3cyWFowcXc4OU1pMlJBQ0c3UkdjczJNOEd6VTNLeVdhd0k4Z2ZuN0NRVnZFcG1YRFR4QlZGYVE2dGNfbl81S1pZeko5enJRdV9V0gGoAUFVX3lxTFAtM29EQXpIU0NDSEx2eTlTLWNXSkMwWEM2LU85Y3NKUDdaTW51VGxRYjlVWTNzVjdBZm92bFQ3TUF0OHprcTU0ZFB5ZHYxbHZYRy1yNDZWeHFyQ1EzZmJKdm1lRFQ5bFVKVnphSTRYLU1rZW5qRnN4azdfeDdZUFpFZU1zaGFMTWFrNndBWjZicllXLXhXTDVMTXpVb0F0dU1wYnpqYjRseg?oc=5</t>
+        </is>
+      </c>
+      <c r="F212" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>Protest</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally)</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>Minnesota law enforcement leaders call for ‘more supervision’ of ICE - NewsNation</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>Tue, 20 Jan 2026 17:47:35 GMT</t>
+        </is>
+      </c>
+      <c r="E213" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxPYnhHa21KeUF2ck96NXpYZ0ZDcEw1Z0lkTTdMRF92WU5qYUYxOEJEcFhfTVNKTVlIZ1FfZXJnVW9TT0luRHRCOHZ0RGJyaFctc1RiQ01HRHlpTG9hSjhOYTFLdnVVajhBamd6aE5wSFdyRHNRSXROcldqWTlfWGxGZWdlbkFsRENCQzBzeGFJUzFjNlVJNlpRZ0pLMWhoTUQ5c2JvWkZ1bG1lbXl5blJJQ25FSGI4dGZCUWFxZldrbEVUZ9IBxwFBVV95cUxNVHdTTDlydTMzZDlIdnRsb2R0UTlMVWktNXhiLTFYMF9TbWRTWVpxVElyekpEcHp5TXJsaEVjeHV0N2VrNXFFSjFtNzAxcWpJWnUyRGlDLWNSbDJDWVBGR2ZVZUZ1emUzc0VBLUlMNmtRbFl3NW5DcDl2a3BRbk5ZWm5MR3pTZ2xYZkU5aGlMUmkybTA3eTFyOGhaWFBxeEI2R1ZSS0t1WTdNcGtHQW9qa09SSERSYVF5SDNZWVlUQnRjMEFhNkpj?oc=5</t>
+        </is>
+      </c>
+      <c r="F213" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>Protest</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally)</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>Police arrest 11 in violent ultra-Orthodox protests in Jerusalem, Beit Shemesh - timesofisrael.com</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>Tue, 20 Jan 2026 15:08:24 GMT</t>
+        </is>
+      </c>
+      <c r="E214" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxOM1phTng1Z1RZNXppdUxVSFI0Njg0SW5JQkNHdlZ0WjJlOWd6bEVTTTdLWVFYbUR5enFsZWNxczU0REpnUER0Y1JZTWpGdHNsVTNMSjBXZDI3Q2JqQkF6RFVFU3g5X3ZlWmpyajd0WjdoMlhVU2I1QXptNkI4S2ZRQXFiZ2tUR2V0b3VMSFF4TC04ZS0xaDdhbWQ4RGhKUFY1NFpPRW1ReHlTdmVXYVRxZU54ZzJ6V0RRb0tnWUhCWUY?oc=5</t>
+        </is>
+      </c>
+      <c r="F214" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>Protest</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally)</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>Protesters gather at Austin City Hall urging end to police cooperation with ICE - cbsaustin.com</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>Tue, 20 Jan 2026 23:26:15 GMT</t>
+        </is>
+      </c>
+      <c r="E215" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxOc05zSTRQVm5EM3ZhX25Kc01Zd0szS212YnZxbFdZMlh2Z2x6YWNDbHNKenpuWEJMN3NVUzZkOWgxWDRLODNDazdoSnNoSm5wUTItQUZhVVJfeUFXQXhINTRuWGNOSDdjR25ZZ1VERHNmbTJ5WFZHSDNzU1pSR1pYeWpuVHJhR29HdU5DV1dQNnhyWkYteExOS1hrZVBHdFdJdVJfeWZYTnA2WlNZQURuMmt6NnRWRi1m?oc=5</t>
+        </is>
+      </c>
+      <c r="F215" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>Protest</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally)</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>Columbia University Protest Culture Is Tame Even in Anti-Trump New York - The New York Times</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>Tue, 20 Jan 2026 13:58:00 GMT</t>
+        </is>
+      </c>
+      <c r="E216" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxQZnBsbGc4eWhLOU5hMHlOLVFZOHF1MC05S2dqbmU3Nk9mSVgyZU5LcFRxc2R6UHRJX0k2NHJoTzZXR1JieFBRSlNNdE5FNkhhcnlwUEJraWZtNjBKV3A1SkYzblBXNW1TWjNORUh2cjFUY0lEUlFMNXVMN2pPeVpBSkF4enFFemhoeVpFdzZwd2VXRlhIV0dQMG53?oc=5</t>
+        </is>
+      </c>
+      <c r="F216" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>Minister Lloyd speech on software security and cyber resilience - GOV.UK</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>Tue, 20 Jan 2026 17:17:28 GMT</t>
+        </is>
+      </c>
+      <c r="E217" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxOcWJkUUN1WlVycEtWYnozR245bVl1dUNYZUxfclR3R1VZQ3RHM3dBdzhDU1hrdHJieDk0azl5REp3TWwxcENheHpvRXRKT3B3TEVfWGRyVTNLNlBOR1FZZjA2ZkJnRFhtWnNpVkZsQVAtVUhJZ0dUWEtTMmlVZHI3ZHVKdkgySFluYXpvWFdNM3Zrd0JPTWhGM19uU05jX09UWWVJLQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F217" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>Dr Sara Ratner discusses AI and Oxford - education.ox.ac.uk</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>Tue, 20 Jan 2026 17:51:42 GMT</t>
+        </is>
+      </c>
+      <c r="E218" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxNTUwyaHVGbWxhdE9LWEJSTUtMUmFuQ3ZRY1NkTWJrTFhqWXVfZUc1U1p2SlQtVWw2SFZHZDZVcFpKRGcwWGpRVWt5WDBjNW4tbmJScWhiTE5TU2ZDT3drVUNUcnlaVm1DWDRWR29nWk0tcWFtUkwxM1pVemRXRDlSdA?oc=5</t>
+        </is>
+      </c>
+      <c r="F218" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>Current approach to AI in financial services risks serious harm to consumers and wider system - UK Parliament</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>Tue, 20 Jan 2026 00:02:00 GMT</t>
+        </is>
+      </c>
+      <c r="E219" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiggJBVV95cUxPdERJUFVwU0xGWGhUemJON3pHZGtva0VGZFUzNmdVOHV6Q1BOM2w1Y09mM00zREhWTjZfcGRaU1hvQk5yZWFBMm1TenhBUE05eFBkZmt6N3p5bzYtcU9JQkJKekFrWWdXQ1gyYU0zaDlzSWxGSlZocFoxeW9ZZllSdF91UERaaXpldGhOZElQeTJJY2VqaGFwVDRLNTQyUHc2SDFONWpoRjlwTmdGNmc3ZjY3ZzVuaFJDZTRZUHljcGRMd0lpakpWOTg0dko4dTB5UVpUZS1WTllSakREVld0YmhyemVYbkxRYVEwMGs5dlI1bFZQazN0a3I5U1NPTGNFNXc?oc=5</t>
+        </is>
+      </c>
+      <c r="F219" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>Combining AI And Human Judgment In Strategic Business Decisions - Forbes</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>Tue, 20 Jan 2026 21:28:08 GMT</t>
+        </is>
+      </c>
+      <c r="E220" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxPQXJVbVFsMnloQzAzc3BVTENDM3pyTlZlaEtEamVrOXlxSm81S3lMcnEzTWdiZGtMbUt4UkkzX0NCMXlleDl1c1ljS3NVRV9TanlYRTZnTGl5UHRfZlBpOGZidjI2VEd3alN6b2h2bDVyeE8zU2Z1OUNwWEZMWV83UzN3cEtjWGhsaXhCSnRwOHk1ZVhwY2stM0NqOGo3VjFENGRnYlZiOWFlaFdWUlVaRW5QdUpSY00?oc=5</t>
+        </is>
+      </c>
+      <c r="F220" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>Synechron unveils Agentic AI suite for regulated sectors - IT Brief UK</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>Tue, 20 Jan 2026 23:31:00 GMT</t>
+        </is>
+      </c>
+      <c r="E221" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMijAFBVV95cUxQcHhGd2VrR0NOZkZJbldKLUExUFVjcFpCLWRZSlIxRjNGaE1aZE1fMGJ3UHphRDkyZm9VMFkxelpTUVc3NkNfS0I5RlVsRGt0VkVjTTdUTlp4S2R0SW92aktpQjA3VDd4eHF4STlnallwSkowYUt5ckhaNXF5RWd4OTFWd25CM0VPWFhraw?oc=5</t>
+        </is>
+      </c>
+      <c r="F221" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>Campaign launched to address concerns over charities’ use of AI - Civil Society Media</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>Tue, 20 Jan 2026 13:05:52 GMT</t>
+        </is>
+      </c>
+      <c r="E222" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxNcEloXy1qLVc4UVdWbUs0SmR2c1M4QWRfUWVnVWhveVJKcjZXTmFGcGNwNVh4YTJ2dmE0LW9iWXJ0SmFIUWc5eGZYTy1fczJ3TUFZV1d6QjE0bGYtSUxpM1NKNVdWYnNKZ2diTUVVcWU4cm5jQXFUUVowNGRteXpFanpDOFlMLUJRdG5nQlBjdENrYUhmTUh6U2tyOHZsblhnS2dCWTJ3?oc=5</t>
+        </is>
+      </c>
+      <c r="F222" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>AI and the Evolving Role of the Chief Sustainability Officer: Guest Post - ESG Today</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>Tue, 20 Jan 2026 15:46:28 GMT</t>
+        </is>
+      </c>
+      <c r="E223" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxNZENPRlpPRmRkUGR1YWxuQ09kMmoyNzlIRnFleG9BdkV5RjVIemFEU1dHWVpkYlJ1OUZldFNpVGFyQUNGdUE3OVJLLTRXY29LM0tzR1RZVm95aVRWRmRZTEI0b1dCQ2tkTnFoWGtmbWFQSEZWdHNWclZfamZFc0ZnYVNoUnBOaGczUHFtSTJQbVVnTkc5TUNrX0RZR2M0Zw?oc=5</t>
+        </is>
+      </c>
+      <c r="F223" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>Manufacturing AI and Automation Outlook 2026: 98% of Manufacturers Exploring AI, but Only 20% Fully Prepared - PR Newswire</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>Tue, 20 Jan 2026 14:02:00 GMT</t>
+        </is>
+      </c>
+      <c r="E224" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi8gFBVV95cUxOWHZOV3hQMVdyRjlhaFZqMTRlNFRlNW1RN3czeTQxMHhYakhKMmt2LXpVRUtfdVVQY1ZPakNpUU14ZkxvRnlmR0V2S3VzNFcwN0l2OUZSeG96ckh5bUZfNmFucjhMVDV3S1kxZmNkeW9ZN1RfUkVkNzJobjhjckxlMVhGcnkwR2pxMzk4aURsQnhSY2lBMzZiYzRrRHJVLXpWLTZ2VXU2YjRfZFVEaklDcFJXYzExdlQ0ZFBDOHNfdDJtaXkxWHd5RUYyT3E0R3BDZUJlM21JZlJ4ajlRZ1phTURjcmVVV2dDMjlvRjQzYmIydw?oc=5</t>
+        </is>
+      </c>
+      <c r="F224" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>EU and Luxembourg Update on the European Harmonised Rules on Artificial Intelligence—Recent Developments - K&amp;L Gates</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>Tue, 20 Jan 2026 16:47:25 GMT</t>
+        </is>
+      </c>
+      <c r="E225" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi0wFBVV95cUxQeDd3WjhhZm5nSkNoTms5RmhjWnQ3VVpOeG9POE43dzBtWjhzR2gzMUlpaGIxQmZLeng4SHlKVHdmSHR6MWtTYWQwR3pqOTNXTkZjQ0JkVHVzVExSRElTUnFKblFIak5obm5mamZ0ZXZJZ1B2aG4yS2xVODRZa2NBUUhGcEJaMTBPbGtGSC03MnE5MTFqVGVNVXBkVlExYUpUMEVHbWJBckYyOTYwWm5Lb1VoUXE5TlJheU9GU2ZtdEltUXd4YVc4Y3E1bHJGS0ZTZTY0?oc=5</t>
+        </is>
+      </c>
+      <c r="F225" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>EU invests €307m to accelerate leadership in AI and digital technologies - Innovation News Network</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>Tue, 20 Jan 2026 09:36:08 GMT</t>
+        </is>
+      </c>
+      <c r="E226" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMilgFBVV95cUxNRVRETXphRjRIVGFSZUplSy1ITFFPeGd2TEdzMDlqdG9nRGJ2MlE4TXQzQlItdG5LNmc0Z1ZrU3gyTU1YUnQ1R1lzNFliM1hmQzVMUnptVFRQRFFldERsSjFLZ1FSSkRfcWRhX2M0YnUyQ3lNbzNNQ0I1bTIxRmNKLVZnS0lVS1BNamxKdThqY2l0SFZzTWc?oc=5</t>
+        </is>
+      </c>
+      <c r="F226" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>BDO: Scotland’s mid-market turns to AI and productivity to support growth and hiring plans in 2026 - Scottish Financial News</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>Tue, 20 Jan 2026 12:54:03 GMT</t>
+        </is>
+      </c>
+      <c r="E227" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi2wFBVV95cUxNdU9FSDRTQVpXQmlualc2T1dVa1otZTFzMk55M0FfV2VGSXBfOGF2el9YUGlQVGtPZHlZSXhUYm9rV1BSeVBUejcwT1lfbnFRWlZ3NHIyQ1NOREZFcm1Fdnk1Z2dFUGp3c0t5UkhjN2h5YWh6V1V0RHB1Q3oxdEZQU3hfY1RITHVVa19tek9xMUdaUW9ubEd1RTBGU1hFSXdkSHBNQUJjVWM5QVRhT0VST2tIbEp6dktZYUhIR2xaVFlwR25mSzNQV2Z4Rm9BWXZlV19oZS1iazBmSVE?oc=5</t>
+        </is>
+      </c>
+      <c r="F227" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>Sovereignty in the Age of AI: Strategic Choices, Structural Dependencies and the Long Game Ahead - Tony Blair Institute for Global Change</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>Mon, 19 Jan 2026 00:03:06 GMT</t>
+        </is>
+      </c>
+      <c r="E228" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMixwFBVV95cUxOejdtTlVWSHFtUjZFUGMtRHFwWm00a0pTMUx4Q3Bjb25MX2ctd1d3bFE5YWc1Q3RjbHFPV2xMVExSWEVJN3ppblRleFdRNEg0ZmwzcXNscTJMMVBmaUZ6eWNIbUNLWXYySThiQ2szYmZ6Ui1FRTNPbnQxT0dQZGEtMC1mZmJkbGxfV0ctTnZXdUVvLTZzV3lKbGFOdWZGcjhuMWVMOWZPUEltaUF4MzdiN0dlY1RBUXhfVUREdGVsWkhHdzNJQ3BB?oc=5</t>
+        </is>
+      </c>
+      <c r="F228" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>AI and the future of education. Disruptions, dilemmas and directions - UNESCO</t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>Fri, 16 Jan 2026 08:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="E229" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxNVlZCV25jOUh4NF9GbzVuSWdwQmp1a1RHUFZPTlhCVUtpN2h2eUZ3U095cUFsTmh1Y2xaaEtwS2dvV0kxS2RSdDJ1dFd4VkRWUTFjWmV0UlVXQUc4Z2YxemE3YWRKLUY4MkJDZGdQckktdHdCazhURnVHbFVKNkstN1ZrTnRTM1B5S1EyS1NYalZvc1JEbC00c0hn?oc=5</t>
+        </is>
+      </c>
+      <c r="F229" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>Physical AI: robotics are poised to revolutionise business - Financial Times</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>Tue, 20 Jan 2026 10:42:11 GMT</t>
+        </is>
+      </c>
+      <c r="E230" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMicEFVX3lxTFA1YTRLNWtVYl9ZVG5DbDJLUzN3SlpzVEVMR2plYVRFeDdSMld0bWhrWEc3QU01WGV4Z0VXSWxlQmlpX1lpUmxMLXltQUt5V05DalJteHBZMDdCSUVqOUpQLUctcnpiU2VQa0taY3lzNGk?oc=5</t>
+        </is>
+      </c>
+      <c r="F230" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>Shoosmiths’ litigation report reveals AI and geopolitics reshaping disputes landscape - Scottish Legal News</t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>Tue, 20 Jan 2026 10:15:33 GMT</t>
+        </is>
+      </c>
+      <c r="E231" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxQV0l4Q1hQZjA0Ymo2ZDkyRmZKM0txNWdYOHVKajlCdnYwS2pLVTBiOEtMaExlbGFtMVM5NzZvNEFqZld5M3hVekhXcXc4aFJKMmN2UmRGeXdtZUpLWnVCS0ZzZDJ2a255MURLTmNtUzFjMEMtUFNGMm1wT3llZDdxWGFsSlgyaVhUa1VHU0lqWVQ5TzVrRnJKb3R6MDcyc3p6NTdCajFIT2VKQ0lwYVRNcEQwZFYyN195LWxfNXFabTg?oc=5</t>
+        </is>
+      </c>
+      <c r="F231" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>Extreme unveils global AI-driven partner programme - IT Brief UK</t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>Tue, 20 Jan 2026 23:31:00 GMT</t>
+        </is>
+      </c>
+      <c r="E232" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMihAFBVV95cUxNZDkzM1ltNlpIa0JEVEVpTWVHTXZmU0c3UThDY1pwWGh0M1p1dmdacnZPMUwwTG9KMTlZdWhVZ2x6LUFlTHU5SkZJTFhHYnl5U0hDWUdGZTlxbTFhRlNnWF94ZXlWdnZnd1kzNU5XbTVaSDhrZ2lhTHlyaWVTMmxjNExzYXE?oc=5</t>
+        </is>
+      </c>
+      <c r="F232" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>Physical AI And World Models Raise The Bar On What We Call ‘Smart’ ... And LLMs Are Not Enough - Forbes</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>Tue, 20 Jan 2026 22:49:19 GMT</t>
+        </is>
+      </c>
+      <c r="E233" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi2wFBVV95cUxNYVFsMEFkUVBCSkhWdVFzVkk4NFN6SVJWVm1LdE44Wktpc3BhQi04eWlTOEtTWVk0ZVRaQkx0YnNHdmZhUHNwVGYyU18xVDR6NktFa2NmWHlMTVFQSTY5VlY4anhhMnhuOTc2Tl9LU0NWZEltRTZDWFNmQU5Ndm9xdjVKUmJiWXRpbkxfbHR2YWh3UkJ5YlUwbVVhZFJIOUZmeGRFQVZ0ZWV2Wm9kMjcwR3RNQXgwdzhJbG5LWk9uSTJHVGlmdGgtRk1yVzY1RlNjVlV4YmRlajdMaUk?oc=5</t>
+        </is>
+      </c>
+      <c r="F233" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>Attachment Hacking and the Rise of AI Psychosis - [ Center for Humane Technology ] | Substack</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>Wed, 21 Jan 2026 00:09:50 GMT</t>
+        </is>
+      </c>
+      <c r="E234" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiiwFBVV95cUxORnlsazJWd1JrTjlnNFhuZEs1TTFiZVJXRTVzblZKMTJnb0NmaDFYV1Jyd19iTXYtYWRfcWdac19aSEJscDlINHU3cU1zVG80aFJLQm1DdEwyVTlwaTBLUEo2d3hOZ2hqcTV3NlA5cWhYOEdHVWk5ejFUM0JmRElwcWVkYVFRY0djSEMw?oc=5</t>
+        </is>
+      </c>
+      <c r="F234" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>AI tops UK CEOs’ investment priorities despite limited returns - HR Magazine</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>Tue, 20 Jan 2026 10:38:32 GMT</t>
+        </is>
+      </c>
+      <c r="E235" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxOTC1NMmpIbGF4cHBsV0tEeFR4WWZ1eXFwWlUtRXJYVGtaMkttTHcwa2w5bFZZUkVpYVY5WmNHSTVEYXhaX0l3Qi1BWmhDTWc3UTFjU1pzMXNpYmFlb2xJQW5kZEp2T1lsQ0lnRE56ZHBmVjBBTUtEQ256cnBObUljNEpnQlNucDFnVW9TNTJ2WW9WZTZ5SXlNTjEwV3BYZEozSWw5VmRn?oc=5</t>
+        </is>
+      </c>
+      <c r="F235" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>What a year on the ground taught me about AI and the future of music - Music Ally</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>Tue, 20 Jan 2026 17:08:52 GMT</t>
+        </is>
+      </c>
+      <c r="E236" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxQbElKc2xkdGV3eFd3Qnp6bHFoLVhVVEF6TFVkRkVjSjBEX3VqbzkyenpWNTRHeG9ySV9NZnNuemltOWRkNXZxRXdrcDRqTlFCV3Bjd1ZqeEMyNm0tNGJxeXhPUTlzV1d5QTQwNzg3cWJraEUxMGp5SnZlQllIY3hzNHdfc3Atay1rRlpoUVJYT1YycThGM0VGek9IcnU4aFhicDRUNw?oc=5</t>
+        </is>
+      </c>
+      <c r="F236" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>Two major UK hospitals to deploy AI to help detect infections - Home | Digital Health</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>Tue, 20 Jan 2026 11:36:09 GMT</t>
+        </is>
+      </c>
+      <c r="E237" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxNOHNKb2pmcF9Lcy01THRkQnc0d1MxbUd2U0F4b2VxU1g1aEs4RGtGQlVuX3gzdzFkeFJPX2VQcEF6UFBRelJ3RFBGb1dCbG5DdDZvdWdPNC04TDdPcDZpSGNILWd6M1IzbXZ0Z0I2cldXTkhmaV83RGQ4bGFSVnJxSWt0c2Z4RWpncE44UEhfUjVqM2dBVjhIZXdESjhEc0txTGc?oc=5</t>
+        </is>
+      </c>
+      <c r="F237" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>CEOs and CISOs differ on AI’s security value and risks - Cybersecurity Dive</t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>Tue, 20 Jan 2026 16:32:25 GMT</t>
+        </is>
+      </c>
+      <c r="E238" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMihwFBVV95cUxQUzNQc0pjeXVHMnF6Y1AtQ0ptWXMyam9jQllPcVRLZkRyTVpiVi1tSTRqT01tSjBpTEtrbzJBVkNhMExBUWlOUVFxVENDYU1ZMHNuZHdYbUhlRlNRY2dUQU5majBqMDNmYjBnQ2hxeE1WNjFMUHA1SnFkal9qbzkxZ0xROTRCeXM?oc=5</t>
+        </is>
+      </c>
+      <c r="F238" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>DLP For An AI-Driven, Encrypted World - SECURITY.COM</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>Tue, 20 Jan 2026 17:47:07 GMT</t>
+        </is>
+      </c>
+      <c r="E239" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMickFVX3lxTE9oOG5YZ25kX3o4aVVxZVVpa09OeXhjSW1ucnJnV3laejF6YWphTGhuV3lCMzNHTVVfYVhJTEt6cElRcDFKU2x0LWJnOExtOS1qRWlUUjB1eHdaNll0SkdOWVJXY2FRLU9CMkNaR1FUdExrUQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F239" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>Rimini Street touts Agentic AI ERP as upgrades stall - IT Brief UK</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>Tue, 20 Jan 2026 22:42:00 GMT</t>
+        </is>
+      </c>
+      <c r="E240" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMihwFBVV95cUxNRzdsMmc5Qm1fWGpKc0gxZ1BEV25BV1pmQU9xamdPMmd5NGxDaWZzWXQ4N3hDQXdmUXpReWp0V0toc3BGN29HOExpQjFvdldmV0FfckFzcjROMTF5MzNUQ3F2aXNIUzRmZGd4WmxfYk51MmItVDRTckJqVEJlTENkT0M1SzR4cWc?oc=5</t>
+        </is>
+      </c>
+      <c r="F240" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>4 Ways To Supercharge Your Team Using AI And Prevent “Cognitive Offloading” - Forbes</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>Tue, 20 Jan 2026 10:04:56 GMT</t>
+        </is>
+      </c>
+      <c r="E241" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxOVGxUX3JrekNRLUpkeVBJM2YxRENzTjVnbVRIX3h0TUp1eUJoRzBBTzdVSVg4c3VVbEhTejVIdFhxajZWTlpBaXl0d1h4cGFCRHRHUW5tVGtwaWhpQTM1TDlfRWczZmYxRTFXUzlhQm41VFN1Xzc4bmltTVI5Nll5clhZSEx1TW5Iby01bkJSQXNsLUkxM3YtY1lMeEx2RHRLdldVdE1CdE03UlF4amJtMk9nTWVPWVRVUzMyeGs2RUZCeWc?oc=5</t>
+        </is>
+      </c>
+      <c r="F241" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>OT cybersecurity: How IT/OT convergence and AI are changing security architectures - IoT Analytics</t>
+        </is>
+      </c>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>Tue, 20 Jan 2026 18:15:09 GMT</t>
+        </is>
+      </c>
+      <c r="E242" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMie0FVX3lxTE1iTTNwWHBkZ3dHdWlsdm05aXpCaE1FeW1FbGtfSnZacjdUMldlSGlpWHl4WVh0cXR3eUY0WlBxOVhKVEZkUnU5S3U4VWtTOGVPdHhmX2pCQjZvMXZYOGUxTzJhc0k2ZWd1ZzBnMFpFYk5BendfcDFBZGpTMA?oc=5</t>
+        </is>
+      </c>
+      <c r="F242" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>What Buyers Actually Mean by “Supply Chain AI” - (And Why Vendors and Buyers Often Miss Each Other) - Logistics Viewpoints -</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>Tue, 20 Jan 2026 15:22:05 GMT</t>
+        </is>
+      </c>
+      <c r="E243" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi0wFBVV95cUxNclg1bTNFaWhaM1F2NVFJWDc4M3FWMmtxaGJEa0IzNEFQUV9MMHFEV0p6Q0Y1bFIwZ0I5Q1FSakp2X1JVRE9fMU9UWk85NWZXYmVvd0ozY1hkbnpOaXRwWFdFVzZMMy1wd3JvQllYLVh6dW1mVElScWowalNJRWhIWGgwQXlSYnlVdlV5SVZjLTdrYmF3dFVjUGI5UGQtbzMwWjBaU0tBTU80TmRVQWpaVEk4SjYyQTlRaUY3YVEyaXZpT0lCd2NVWlFuX3JDdnJOZUgw?oc=5</t>
+        </is>
+      </c>
+      <c r="F243" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>Kubernetes cements role as AI &amp; cloud native backbone - IT Brief UK</t>
+        </is>
+      </c>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>Tue, 20 Jan 2026 17:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="E244" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMihgFBVV95cUxQRy1wS29LTHBFeUZIei1pelBMaUhva2xOWkE1bEFEdmt1eWFRaVJnMkNwN3pWSHctaWFfdUpKSkg2QkZrSE5LTlN6aFpJSWFFeF9GMVloNko2QkNCcVA5U2c1SUY5TzFuaFI4ZjJhZUdneU1ubGE0M2hKZU5jdkJYckFuT3h6Zw?oc=5</t>
+        </is>
+      </c>
+      <c r="F244" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>Eric Posner to present 2026 Ryerson Lecture on AI and the future of law - news.uchicago.edu</t>
+        </is>
+      </c>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>Tue, 20 Jan 2026 16:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="E245" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMilAFBVV95cUxPanYyX2I5X09RMmp2SVNMZ1lBYy1GYWkzZ1I4VXhoUGNwQlBocEYzT1JUYnBUbGxHSDRKQzhXbEhBQ0RxVHFsbkJIYTdXdmFScU1UN0ZPUnZRSUNaT3lxUERQUU41Snl2OWtVQjRVN0VZMmJ6WVptZjAxNGtZamVWVURldHp1ZGFyQ0VDU2ZkMzg0U1lz?oc=5</t>
+        </is>
+      </c>
+      <c r="F245" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>AWS is committed to customer choice and flexibility, accelerated by AI - aboutamazon.com</t>
+        </is>
+      </c>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t>Tue, 20 Jan 2026 17:50:36 GMT</t>
+        </is>
+      </c>
+      <c r="E246" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMilAFBVV95cUxQaVBrUG1lLS1yU0d6VS03UjBLTGkwazJvNElBaktIYzdubXI3YzhrdG12MTQ3S3FCNlZydFYxTFlTRFRNdG8tRWZOaHlzdzEyYjVHdzNjNXNtaWFqOTN1STdoNjlvR0lWd29GMGtHVElsS0JiTXBuZkExaGZOVV9XS252eEVtRHBockNveGdRZWxDWVhq?oc=5</t>
+        </is>
+      </c>
+      <c r="F246" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>Mayor hits back after fake AI video - LocalGov.co.uk</t>
+        </is>
+      </c>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>Tue, 20 Jan 2026 12:45:07 GMT</t>
+        </is>
+      </c>
+      <c r="E247" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMid0FVX3lxTE5KSlByWnpMd2Npb0N5b29MdGRhanczY2dfQS1BRXpxTkNMRm5BTFEwZ3Y2TGlWQk8xbHYwVEh6RVlWclkwZENLZnY0RDRwSzRBYlBrZ1RvSGZwLUxoenhhT3RpU3N1Y1lUbi1oOFBhbFF4RFpkODA0?oc=5</t>
+        </is>
+      </c>
+      <c r="F247" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+        </is>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>UST: A Guide to Building Responsible AI Systems - AI Magazine</t>
+        </is>
+      </c>
+      <c r="D248" t="inlineStr">
+        <is>
+          <t>Tue, 20 Jan 2026 12:05:38 GMT</t>
+        </is>
+      </c>
+      <c r="E248" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMijgFBVV95cUxOaWU2UTdIN3pWSVBScjNSTHdTVG5UNXBuVTlubUU1VjU2N0NCVU9xS0s5aUZIMmhWSkVUUE5qcDNSQjcwM09iRVE2V0xpa2owS0w1R1FJWjBzWUJPZGtYSmxaOHRpTjAzYi1hN0ZabW0xZ1lUQkw3NUZoUlNjaW1tWjlKZTJwd3ZjQWJpNm53?oc=5</t>
+        </is>
+      </c>
+      <c r="F248" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>Four priorities for AI-powered identity and network access security in 2026 - Microsoft</t>
+        </is>
+      </c>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>Tue, 20 Jan 2026 17:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="E249" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMizgFBVV95cUxNQmNWLWhPQl96UUJRWFhDaHcxUmZwdlFXNHpWZEQ5MWlGdURQOWIxWEExWFVaeE9IekFLcGpfNXB1bnNMM0ZFUzcwbGs0a1ROSWpULWJyY2RwNllZUDc5UUNUS0lFOEFvM3ZpbU5aa1NYR0xkdzlaVUZUaEF5SzQ4Q2RqUFRvZ29OZ1ZRcWpBN2hEajlmT2lKZ2ljSmVZcmdlOXhHWEhMUFN6SzB2TFdOc0lheG03NDBlZHlqZEx5SElWQ3otcVJ3bVFza21mZw?oc=5</t>
+        </is>
+      </c>
+      <c r="F249" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>Treble Announces Record Revenue in 2025, Accelerates Market Expansion Led by Enterprise Technology and Cybersecurity Practice Groups - Yahoo Finance UK</t>
+        </is>
+      </c>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>Tue, 20 Jan 2026 14:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="E250" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMijgFBVV95cUxNcmtqbnFuMHh4UjhBQmRRM2ZBMjdQOXU3QmN5RlhKYTUwTHZ5RmNmYmpvTUtSUVdDN1licklQLUJ5STFZbzRyMnlCT29VdG5wbzlCdTVMaEh6TGdyNnFkVk9scHFxcVcwclpodTFlMWw3VmhOZnhYUG5xa2dwdGdadDR0UFg4QVk2T1lDbUx3?oc=5</t>
+        </is>
+      </c>
+      <c r="F250" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>They hear, but do they care? What AI can teach us about listening better - BBC</t>
+        </is>
+      </c>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>Tue, 20 Jan 2026 10:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="E251" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMihwFBVV95cUxOY3dfSVlrdlZRUTZHenowSGozZ29ZZDBmQllDWFVTM29PTWl0d0k2ekRzSDVkWmU5Mlhaek9xYzJsUFBwclF5V2I0ZnRqX2NXa1BOUk5yb0ZRTFFCUUt1bWNfU2ppdW1vOFpsZ2UtOUhEMllyeFpOMzhVRi04cDBEMzRneklaTGs?oc=5</t>
+        </is>
+      </c>
+      <c r="F251" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>UK to reimburse visa fees for AI and quantum researchers - Times Higher Education</t>
+        </is>
+      </c>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t>Tue, 20 Jan 2026 00:01:34 GMT</t>
+        </is>
+      </c>
+      <c r="E252" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMilgFBVV95cUxPSWd3NmVZdkNDXy16a1QtTGROWnYxMnhuaUZmZkx1aG43QVRlNEE2VTFDQy1mbWh1MG1fdVQyRmNnVkYybVA0R0JId05aUmpPSFJRdnRCbVlydUNmaEd3WmhXb3lINGlpLTYzSEs5RnFJdC12MXEyczhvOGRZNjZVQ21jcFc0MHJTMVdHYWpzeHBDcFBCNnc?oc=5</t>
+        </is>
+      </c>
+      <c r="F252" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>Multiple autonomous AI systems spontaneously collaborate to advance materials research - EurekAlert!</t>
+        </is>
+      </c>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t>Tue, 20 Jan 2026 18:13:29 GMT</t>
+        </is>
+      </c>
+      <c r="E253" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiXEFVX3lxTE9ISVJzTlhpWXdfSUxOYzROUm5EUXA0ekNBQkdVZlhnLXNJeXRGTktOQmVQck9OVEhucTl3UVIwV04wMmFZNnN2S1lOTGIycDJhdHBiRFl4N04yQjZx?oc=5</t>
+        </is>
+      </c>
+      <c r="F253" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+        </is>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>AI and the great job unbundling - ADP Research Institute</t>
+        </is>
+      </c>
+      <c r="D254" t="inlineStr">
+        <is>
+          <t>Tue, 20 Jan 2026 13:28:06 GMT</t>
+        </is>
+      </c>
+      <c r="E254" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMickFVX3lxTE40VEZPdnZMVUtaQmxIWHlralc4LTZfOGFiUVNLcUEyODlPSU5jdXplclZOVk10LUVDVy1jVlBpcGlQZVdEb0pyQko1aGV2MGMwWUlUc01ReDdzRUwtM0pValg3dS02cUNCcFdWaE9FM3I2dw?oc=5</t>
+        </is>
+      </c>
+      <c r="F254" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>KPMG Global tech report 2026 - KPMG</t>
+        </is>
+      </c>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>Tue, 20 Jan 2026 15:14:26 GMT</t>
+        </is>
+      </c>
+      <c r="E255" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMigwFBVV95cUxPa2JielBvOGlpRndkaUxYT0ZHNXVBVXp5T251STBRWS1BMHdueVNBVW5CY3FtS0g5d2tRT09QdnYwNkNhUXBHdi1fX2Z0TWp3dE9MQ0ozVU94TEdBRWEwNWIzVm85VXNKQVNGYVVMT2tnbGk2QWJ5SFRBMGUzMDM5R2lvYw?oc=5</t>
+        </is>
+      </c>
+      <c r="F255" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+        </is>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>Using AI to understand the age of disease onset in Huntington's patients - News-Medical</t>
+        </is>
+      </c>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t>Tue, 20 Jan 2026 19:03:00 GMT</t>
+        </is>
+      </c>
+      <c r="E256" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxOam1iZ0ZYZFFKbVJTeko3QlFXRDVjcFp1eDR1MXVOLUhWdEdXNEl3Zk1kS01RbUQwbDlQVVlOR3FVQXUycjRTdTZaVW1CZzQyS2l4eC16MTJ2Y2pzMzRNampqYkUtMUxzeW42blNsY01SeWtRSWZJYkRjZTlILVhfUXp5Q0JRbkxycDdWTzVLVDBvaGVWZVBhdktXSER3eXVMQ3pNVzBkUDZwSkJld0tqd25ycHAzeDN1N0Jr?oc=5</t>
+        </is>
+      </c>
+      <c r="F256" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+        </is>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>Davos Signals a Disciplined Era for AI in Banking and FinTech - PYMNTS.com</t>
+        </is>
+      </c>
+      <c r="D257" t="inlineStr">
+        <is>
+          <t>Tue, 20 Jan 2026 20:48:54 GMT</t>
+        </is>
+      </c>
+      <c r="E257" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxPWkc3aFRsejNLRnZiQUtrR3hxMUZxcjM1SVVjOGRqTE9hODNuNGk1cjJXRHV3R0M4d3pJblB5a1FSZFNLODdWQzlTNUlJX2E4R2xLazJJS1h6QmE3YzRJNFZLcmI0TjVfQzlxNlFWMWkycGhPNFFQTVB0ZG5lb0VMU0N2WG1ERkRodF9nYzF3V19nMzJ0VEwySTd1X3A3OFE1aGVFWGNn?oc=5</t>
+        </is>
+      </c>
+      <c r="F257" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+        </is>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>Education Secretary speech at UK AI for Education Summit - GOV.UK</t>
+        </is>
+      </c>
+      <c r="D258" t="inlineStr">
+        <is>
+          <t>Mon, 19 Jan 2026 14:02:30 GMT</t>
+        </is>
+      </c>
+      <c r="E258" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxQSFh1S2tZVEdEaHlCY0xGLXdqV2tLY0JpdWViX3N6RUR1NG1pWG9BM2pzUjBnZUk3TEFmSmFpdjBfNERZMU5jY1hSYWdndGJSX1FxOWFIOXlSS3FJaEg1dmpOQTdraGxTSXg5eUg2eDl3TWsyNERrdjhWaUtKdm1nY3VxNDBQcnY1c2M2Q0NDT1hMbzhDTmY4?oc=5</t>
+        </is>
+      </c>
+      <c r="F258" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>Insider_Risk</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>("insider risk" OR "insider threat" OR "internal threat" OR "employee misconduct" OR "data exfiltration" OR "privileged access abuse" OR "malicious insider" OR "negligent insider" OR "insider attack" OR "corporate espionage" OR "information leakage" OR "unauthorised access" OR "policy violation" OR "security breach" OR "insider vulnerability")</t>
+        </is>
+      </c>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t>UK FCA data exfiltration prosecutions: a reminder of malicious insider risks - A&amp;O Shearman</t>
+        </is>
+      </c>
+      <c r="D259" t="inlineStr">
+        <is>
+          <t>Mon, 19 Jan 2026 15:57:31 GMT</t>
+        </is>
+      </c>
+      <c r="E259" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi3AFBVV95cUxQWTJERGNMY082dkQtdW9MdVlYeFpMUzRBOWx0MVZXSks2OWxKYlM5VkdCb0NyYXJ0OGE5dHpobU42UXFfRnVVWkdia3p1NHBBWUwwcDlIUXFsbnhVZ3dTVlJsWDFlN3N0aHNpWkpRaVdyUUltdWdCMlF0THRCRkcxYzUzTFh6eUZrY2pkQUVGMkZXdWZtX19rYUduV0I5djA0S1pvYjlsdkQzWWpuUlZrekMwSVgzTUxJakZBendTenhhR21QNFJ1VmFNa1MtWVJwT0R0bmtKRVdabk1Y?oc=5</t>
+        </is>
+      </c>
+      <c r="F259" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>Insider_Risk</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>("insider risk" OR "insider threat" OR "internal threat" OR "employee misconduct" OR "data exfiltration" OR "privileged access abuse" OR "malicious insider" OR "negligent insider" OR "insider attack" OR "corporate espionage" OR "information leakage" OR "unauthorised access" OR "policy violation" OR "security breach" OR "insider vulnerability")</t>
+        </is>
+      </c>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t>IP Theft: Cloud Insider Risk &amp; Forensic Readiness - FTI Consulting</t>
+        </is>
+      </c>
+      <c r="D260" t="inlineStr">
+        <is>
+          <t>Tue, 20 Jan 2026 09:48:12 GMT</t>
+        </is>
+      </c>
+      <c r="E260" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxPb2xIM0hnTzl6S3ZPNmJudm1UUWFGWEtrQkNXNi1OaFJqaC1WNVo1dUQwOENJMExzcUpOUDFtX1A0M09FUG8yclktb2RvWG1rU0RjTjR4OVpfd0hLOFVkbFhlN3M5Z0NhSDhvWlVJT3ZZQWpSWFlWT2RBU2dWNXhLY2NZZzFZN3B5ajh4bm45U3BPNU4yd2c2enFfajdnV3c?oc=5</t>
+        </is>
+      </c>
+      <c r="F260" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>Insider_Risk</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>("insider risk" OR "insider threat" OR "internal threat" OR "employee misconduct" OR "data exfiltration" OR "privileged access abuse" OR "malicious insider" OR "negligent insider" OR "insider attack" OR "corporate espionage" OR "information leakage" OR "unauthorised access" OR "policy violation" OR "security breach" OR "insider vulnerability")</t>
+        </is>
+      </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>Preventing Data Exfiltration: A Practical Implementation of VPC Service Controls at Enterprise Scale in Google Cloud Platform - infoq.com</t>
+        </is>
+      </c>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t>Mon, 19 Jan 2026 11:00:59 GMT</t>
+        </is>
+      </c>
+      <c r="E261" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMifkFVX3lxTFBxSm8tLU5YWnhaSTZJSTg5cHdUaG1hSElld1BYUzR6LUVxUHVDSmp4YXN3RlprUEJqSmxfbVBEM1NhSmxDV1VPQU5yZ19FQ2h4TW5jcFJybUdiNXUyY2xvWlBTT2t1U3daVXV1Q2x6Q1FldTFoWVNwTWFMbTg0UQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F261" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>Insider_Risk</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>("insider risk" OR "insider threat" OR "internal threat" OR "employee misconduct" OR "data exfiltration" OR "privileged access abuse" OR "malicious insider" OR "negligent insider" OR "insider attack" OR "corporate espionage" OR "information leakage" OR "unauthorised access" OR "policy violation" OR "security breach" OR "insider vulnerability")</t>
+        </is>
+      </c>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t>Investigation finds employee misconduct, policy violations at Daytona Beach Golf Club - wftv.com</t>
+        </is>
+      </c>
+      <c r="D262" t="inlineStr">
+        <is>
+          <t>Wed, 21 Jan 2026 01:57:00 GMT</t>
+        </is>
+      </c>
+      <c r="E262" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi2AFBVV95cUxQZW1UQTc3Z0luMWlvVFB6WURTd3d2c0FzZGdQdlBPaGt5ZnprcGJuZjY5RmoyWTdWdUl3X3h2a3cxTkJBX0RGVkRDdG4zOWpfR3Q1WVduaV8tZmdOTm9pTUo3cS1lQk5hVW02LXhoa2laU0s4bHY3bFZGdGtiYjhFVTRmdTlvektHUXowalBIelJ3ZWV6V3Bpelg0dWIyUnhpd2hiMFdzTHFyQThGRUJPVHEyMFZsU3RfeDdLaF8teTgzTEtGWmMyTm1MWVBOekt3N1duZjJEaHHSAewBQVVfeXFMTkFySm9adVFjZ3lXd3N4N01IYUd1aTNCa2lzZmpSTTd5LWtFTUNQWTRGaDhmQmVMblNVVnA1eDM4Ti1qZllwNnBlc1ZBR2Z5ZUtBcURHZXZ2bnEyczZxMUJrdEh2aXhzTThFcUtPMkoxTGF3OFNtV2tYN3RJUjNwZ1hPWjB0djVteWw1SjI1Q3M3bjJfVmw5b1RVSWVESzhVcFd4dDFaSEozTTAxWTVyU3RWaHMxLWRDbFptaWs4WE1uZnpwOHNMOERvVTdraEdaeVZSQk9JcDU4QXQtR2lKREoxVGxvUVlwbVlvQ2Y?oc=5</t>
+        </is>
+      </c>
+      <c r="F262" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>Insider_Risk</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>("insider risk" OR "insider threat" OR "internal threat" OR "employee misconduct" OR "data exfiltration" OR "privileged access abuse" OR "malicious insider" OR "negligent insider" OR "insider attack" OR "corporate espionage" OR "information leakage" OR "unauthorised access" OR "policy violation" OR "security breach" OR "insider vulnerability")</t>
+        </is>
+      </c>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t>KYC’s Insider Problem and the Case for Confidential A.I. - observer.com</t>
+        </is>
+      </c>
+      <c r="D263" t="inlineStr">
+        <is>
+          <t>Fri, 16 Jan 2026 20:31:22 GMT</t>
+        </is>
+      </c>
+      <c r="E263" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMib0FVX3lxTFBFNW83Q0FENXA2S0NkNjBRVWVnaWZhTkVyTjczenlYeGhEbWFHZG5DQlBNZmNhR2VfYVpHcWtSbkt5dkEyZmpWX0JaN0wwZ3lHTEcya3hkakk5UWpZZmhUZkQ2aTZwcFdZeXp5S0VITQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F263" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>Fraud_Scam</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>("fraud" OR "scam" OR "phishing" OR "identity theft" OR "account takeover" OR "payment fraud" OR "credit card fraud" OR "wire fraud" OR "business email compromise" OR "fake invoice" OR "social engineering" OR "advance fee fraud")</t>
+        </is>
+      </c>
+      <c r="C264" t="inlineStr">
+        <is>
+          <t>Brits more worried about social media scams than banking fraud, study shows - Tech Digest</t>
+        </is>
+      </c>
+      <c r="D264" t="inlineStr">
+        <is>
+          <t>Tue, 20 Jan 2026 10:05:02 GMT</t>
+        </is>
+      </c>
+      <c r="E264" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxPTzFhVF92NVVwcmJtMkhndmlaTzc5bG9abnNXWTZhanI1SV9NYzlRQkVCOEFCSnZMRUpQNkVjaTlTZ0o0ZU9aZVZGa3I1NkRuQU5qZ0NTNFFGNTFHdnZIdVRzZl9GdDVZcHBjWFlXZW1Ga3dmV1d3U18yN2dMM2JOU2otRjhKcHBkRFBDd1RuTnRwUjBQYVhWeHpWV3I3c1RndjU0WlZCaHpIbmx5QXpLclBNRQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F264" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>Fraud_Scam</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>("fraud" OR "scam" OR "phishing" OR "identity theft" OR "account takeover" OR "payment fraud" OR "credit card fraud" OR "wire fraud" OR "business email compromise" OR "fake invoice" OR "social engineering" OR "advance fee fraud")</t>
+        </is>
+      </c>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t>Six arrested over suspected £300m fraud at UK social housing fund - The Guardian</t>
+        </is>
+      </c>
+      <c r="D265" t="inlineStr">
+        <is>
+          <t>Wed, 14 Jan 2026 16:38:00 GMT</t>
+        </is>
+      </c>
+      <c r="E265" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxNamI1eC1kLXBqRnh5VG40eU1TR1l4ajA4SVl2akVyVXg3dnd3X001cFZMbmdJNXNRUGRZbG1nOWYyOTdaN3d0UExFYldKeV94NFBBbmRzS2d5R1Naa2JsLUNVVWZJMDNSVVR2c0N2V2hYeFZSM0QwalhWX1Rfal9nbjlvdG1ROHdwd1dvSXRLcDliQ2U3NlZLbVFVNWFiRlprR1ItM05aSkl0MFd0b3Vr?oc=5</t>
+        </is>
+      </c>
+      <c r="F265" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>Fraud_Scam</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>("fraud" OR "scam" OR "phishing" OR "identity theft" OR "account takeover" OR "payment fraud" OR "credit card fraud" OR "wire fraud" OR "business email compromise" OR "fake invoice" OR "social engineering" OR "advance fee fraud")</t>
+        </is>
+      </c>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t>Victim Loses $282M in Bitcoin and Litecoin to Hardware Wallet Scam - Yahoo Finance</t>
+        </is>
+      </c>
+      <c r="D266" t="inlineStr">
+        <is>
+          <t>Fri, 16 Jan 2026 18:58:21 GMT</t>
+        </is>
+      </c>
+      <c r="E266" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMihwFBVV95cUxOYjNmTDA1VUF2QTk3UVV3WER5TXlueERYTXJFMW9mLVBTZGZ0bzlvLXU1Q1E2clNlMThtRkFsN0cyZGxURW9SbDBBdEMybXpYcVJyanJZaGlhVjgxN0JsYmJBTGVXYXEtUUhsTnF3bk9EZ0FGY05FQXlOcUVfVG5DTU5ERzZsVE0?oc=5</t>
+        </is>
+      </c>
+      <c r="F266" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>Fraud_Scam</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>("fraud" OR "scam" OR "phishing" OR "identity theft" OR "account takeover" OR "payment fraud" OR "credit card fraud" OR "wire fraud" OR "business email compromise" OR "fake invoice" OR "social engineering" OR "advance fee fraud")</t>
+        </is>
+      </c>
+      <c r="C267" t="inlineStr">
+        <is>
+          <t>Four WASMO social mobilisers arrested in 123cr Nal Se Jal Scam - Times of India</t>
+        </is>
+      </c>
+      <c r="D267" t="inlineStr">
+        <is>
+          <t>Tue, 20 Jan 2026 23:12:00 GMT</t>
+        </is>
+      </c>
+      <c r="E267" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi1AFBVV95cUxPU3FCMmxJTjdhY1FnVnhQLXVUV0FJWXdzc09BbDllMU5EczE4NUs2dTNIZENhTlhyZHk2am9QZ2ttZ3ZQOV9ja3hIRmE3NUJ1bF9CMkhhcmthWENVd1FnVWo3ZHpTU3cyOGxWSG50UFRDSTVsR0xVYjM5OGhhX1kxS1V1R3pPOVMzcUN5UVQyYTdTcUo2a3hTbFk4bXYwbnhPSDRsRjdCcjZQdGwtUWFwQ3Jva2ZrX1hWYUFyd2lPcDBhTWlZd1ZqZUNTVlBHRGN5eUlTUdIB2gFBVV95cUxQeG9heFR0OURJbnk3OElXY2x1V2ZjUGJPOHp0dGpUWUxNVlZYUnk1V1ZlOEt2Nm9wclZJdW9xQ3FjaWZmMzI4ang0a0I5dzhuOEdfdTJFSkdRZV9JNkpvZEN4M0dSYVNSVmtFWnlXelVOWTlqZ3BMaTBwNWVkbHNJYkkyUXVBdVlqN2dxc0NFWnY0MkFBRGZvT1JtTjlZbWFYcjB2MDZhYzN1YzlSTE53MUE2eU85SVJ1a3BZdWhJTFJibzZTNjBzTFk0Rk5TTG9kMlQ1VHRjNUN2QQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F267" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>Fraud_Scam</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>("fraud" OR "scam" OR "phishing" OR "identity theft" OR "account takeover" OR "payment fraud" OR "credit card fraud" OR "wire fraud" OR "business email compromise" OR "fake invoice" OR "social engineering" OR "advance fee fraud")</t>
+        </is>
+      </c>
+      <c r="C268" t="inlineStr">
+        <is>
+          <t>‘Not me’: Magda Szubanski warns against social media scam - The Sydney Morning Herald</t>
+        </is>
+      </c>
+      <c r="D268" t="inlineStr">
+        <is>
+          <t>Sun, 18 Jan 2026 03:17:44 GMT</t>
+        </is>
+      </c>
+      <c r="E268" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxNdEd3cE9CMEFqZ2Z6eHV5NS1OZU9pNTFXQ3pWRlZTVl92R184eTdFQWRUNnFucVlkck1YSm9VTVE4ZldHOTE4cEZZTi1jQ0FhazRtT0xqbUpyaFdlcGhwbXdhd1JHYmR6cGhZM1g0bjFmQVA3a1o5WXNFSTRYUU1YeHlVdUtzVGpVNFNZMnlDcExSY2ExMWwzcS12WkhuTmJacnNpaEZza1dzZkVnQWJWNDhZbmp0Mlk?oc=5</t>
+        </is>
+      </c>
+      <c r="F268" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>Fraud_Scam</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>("fraud" OR "scam" OR "phishing" OR "identity theft" OR "account takeover" OR "payment fraud" OR "credit card fraud" OR "wire fraud" OR "business email compromise" OR "fake invoice" OR "social engineering" OR "advance fee fraud")</t>
+        </is>
+      </c>
+      <c r="C269" t="inlineStr">
+        <is>
+          <t>Welfare Fraud Is a Problem—For Democrats - The Atlantic</t>
+        </is>
+      </c>
+      <c r="D269" t="inlineStr">
+        <is>
+          <t>Mon, 19 Jan 2026 14:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="E269" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMifkFVX3lxTE5KdmlpclRUQmhUZDM5Q1djMDNlRFZDdjNwQ3kwQzg0VUZCTC0wRE5acXVsc05tVVVaYnpNVUphZk1BaWJHQVFjS3k2OGNYSnF0ZDhnT2dyWFVqUmZ2bk5RRUY1U2VGTXRETUU1T1hkZnY3LVAtZzFyRDQ2M3JuUQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F269" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>Fraud_Scam</t>
+        </is>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>("fraud" OR "scam" OR "phishing" OR "identity theft" OR "account takeover" OR "payment fraud" OR "credit card fraud" OR "wire fraud" OR "business email compromise" OR "fake invoice" OR "social engineering" OR "advance fee fraud")</t>
+        </is>
+      </c>
+      <c r="C270" t="inlineStr">
+        <is>
+          <t>Monero Stalls Post-ATH: How a $282M Social Engineering Scam Fueled XMR’s Rally - Bitcoin.com News</t>
+        </is>
+      </c>
+      <c r="D270" t="inlineStr">
+        <is>
+          <t>Sun, 18 Jan 2026 07:39:20 GMT</t>
+        </is>
+      </c>
+      <c r="E270" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxNMHVySXREejVlX0ZUVEZHMlV1Z2p1a3Bvckk2X1FfVVRYLVFTc3BSR0pWb3E0ODN1T0dVWGxXcnVOb2thN1duaU12NXkwb0Q2RDJyMlpUZDVmaThKZ3lpUjRMOUxPVmtnanJyYW90WVNRT1BCN3RUeEZ6c1k4TTNCUnFXTkxzaUx3VDhucThiYUpHNWxhTkxRUDJPTmJRc0o0U1lj?oc=5</t>
+        </is>
+      </c>
+      <c r="F270" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>Fraud_Scam</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>("fraud" OR "scam" OR "phishing" OR "identity theft" OR "account takeover" OR "payment fraud" OR "credit card fraud" OR "wire fraud" OR "business email compromise" OR "fake invoice" OR "social engineering" OR "advance fee fraud")</t>
+        </is>
+      </c>
+      <c r="C271" t="inlineStr">
+        <is>
+          <t>Ugly truth behind image of Magda Szubanski amid cancer fight - perthnow.com.au</t>
+        </is>
+      </c>
+      <c r="D271" t="inlineStr">
+        <is>
+          <t>Mon, 19 Jan 2026 04:23:00 GMT</t>
+        </is>
+      </c>
+      <c r="E271" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMihgJBVV95cUxNb2RXeENNSXZFVFVVRDh0aFFyOUw2dXJpdDdxQXZaNklhdkxrdm5mTjZseUUzaXF6eUQ4ZkRjclV1eDhEcnFaUVJCdWE1aDBMTHRFNmNZQ2kyLXo2N1pRaFJpT2c2MUZMSjBaZXZ5dmZrRHlqcUtJeExSX2hsTnYxRzlZWjN1aVROS3JkdmVVbEtYM3cyZEFIVjJFM3owcHlsbFBLVnpWZk9FcHFjTS1laEVRLVAyeE5ubFJscmFUb2ZJWFo3Vmw4Sk56NzZlRFQ0TmppdG0tbTN4YThPZllDUTU0dzVOWno0WmhNTFpNVnVXWUw2NUh0WTZMc1kza1diU1NiSF93?oc=5</t>
+        </is>
+      </c>
+      <c r="F271" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>Fraud_Scam</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>("fraud" OR "scam" OR "phishing" OR "identity theft" OR "account takeover" OR "payment fraud" OR "credit card fraud" OR "wire fraud" OR "business email compromise" OR "fake invoice" OR "social engineering" OR "advance fee fraud")</t>
+        </is>
+      </c>
+      <c r="C272" t="inlineStr">
+        <is>
+          <t>Thousands lost in social media fraud - FBC News</t>
+        </is>
+      </c>
+      <c r="D272" t="inlineStr">
+        <is>
+          <t>Tue, 20 Jan 2026 00:59:00 GMT</t>
+        </is>
+      </c>
+      <c r="E272" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMieEFVX3lxTE0wNFdOM2dJWVFDcXlSeGNGeWlUWWN2cThzYnl2b2t3ZGxxak9VX1hraHZ6NWxJd2pNalZXRWQ2R0RZQTc2MXpjY0RWQmowNDdKMHhwNDAwWFlZYnhBR3hKZG1tMHRXbmZBSG53YkhfemdrT3JOeFlOWQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F272" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>Fraud_Scam</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>("fraud" OR "scam" OR "phishing" OR "identity theft" OR "account takeover" OR "payment fraud" OR "credit card fraud" OR "wire fraud" OR "business email compromise" OR "fake invoice" OR "social engineering" OR "advance fee fraud")</t>
+        </is>
+      </c>
+      <c r="C273" t="inlineStr">
+        <is>
+          <t>How to spot a scam on social media - dailyexpress.com.my</t>
+        </is>
+      </c>
+      <c r="D273" t="inlineStr">
+        <is>
+          <t>Sun, 18 Jan 2026 03:00:15 GMT</t>
+        </is>
+      </c>
+      <c r="E273" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMigwFBVV95cUxQczhXU0Q1OUI4MFNmOXp5bnpRR25HdG95eWgtVTFPLTJHVWVQSFliYlNaeE1JOEVNZkc4aGpYMml3LVZfemd1YVdOTG5wdXpLam0tZGNUMW05eUV1ZXBCSkxpRUhuZjRrSXQtQ3duZmZCcGRlVmZZWmdzXzhNRnNwUkI2UQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F273" t="n">
+        <v>7</v>
       </c>
     </row>
   </sheetData>

--- a/data/topic_feeds.xlsx
+++ b/data/topic_feeds.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F117"/>
+  <dimension ref="A1:F203"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -851,17 +851,17 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Modernization of Cosmetics Regulation Act of 2022 (MoCRA) - fda.gov</t>
+          <t>London Nightlife Taskforce sets out roadmap for after-dark economy · News ⟋ RA - Resident Advisor</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Wed, 21 Jan 2026 13:59:00 GMT</t>
+          <t>Tue, 27 Jan 2026 09:02:25 GMT</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxQYTIyZkJsWURKUWp3NEptRFliaTlCeHRvcmxsbnhPVThsTTctc3MyRVhOTUxxZG1tbVE2ejZ0bXRoZTNPeHhiS3h3RHN1cXpZd1JMem92bDRyM2pQZUF1RFRhMmZoYmYydVdVa3NBc2VJeFFVTXBvN2pOX09ZUVBUM3A0MXJPM1QzNlFWMFp6MFpXM1ZjQ3JkckdXazkweUZkWW02aGM5RXRHZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiPEFVX3lxTE5VR0RFVktBTHo1TjQ3dXg2bEFsOXBXbjhJUktHNG9HNUZqdXFmUElackRubVNDSTFTanFnMQ?oc=5</t>
         </is>
       </c>
       <c r="F15" t="n">
@@ -881,17 +881,17 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>London Nightlife Taskforce sets out roadmap for after-dark economy · News ⟋ RA - Resident Advisor</t>
+          <t>UK prescription charge update as government 'takes action' - liverpoolecho.co.uk</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Tue, 27 Jan 2026 09:02:25 GMT</t>
+          <t>Tue, 27 Jan 2026 10:39:00 GMT</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiPEFVX3lxTE5VR0RFVktBTHo1TjQ3dXg2bEFsOXBXbjhJUktHNG9HNUZqdXFmUElackRubVNDSTFTanFnMQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxPaFZzcV84NkxBNWExQkxVSGowemxvb01aLS1LM01QRXU0RXIxVEtYY2ZhdDB3QVpIaWdZY2FGQjU1Uk9GOXctdldMUmppV3lSd29zSm51M0ZMbkRhR3VxRzdfQzg2T3RFUW1wMlk3ZFk4SGp6eVRwVjd6cFNkVkJwRHAtSDgxeXNkMkJPQ0hIZXRiSUl2bENBVdIBngFBVV95cUxOeXZ5TjBYdENjMTB5SWZiMFY2VE9WR0ZIVHV2RC14MUJBZVhBdnNlc0FHNjg1ZmdHdWJwTmdmNW1jcnQtYUNqQ18tbGFBWlhyV0h5dVhZcjRZcEU4NjRxVk1xYnFnUlNwM1ZRZFRBVXBNVWZxdVhTSnBRQVFNcUN1OFc4WnFVV3JvMUpMdnRRQjhyM2d6YjZPSk1QOXhkdw?oc=5</t>
         </is>
       </c>
       <c r="F16" t="n">
@@ -911,17 +911,17 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>UK prescription charge update as government 'takes action' - liverpoolecho.co.uk</t>
+          <t>Government issues 'life expectancy' in UK update amid major NHS change - The Mirror</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Tue, 27 Jan 2026 10:39:00 GMT</t>
+          <t>Tue, 27 Jan 2026 13:32:00 GMT</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxPaFZzcV84NkxBNWExQkxVSGowemxvb01aLS1LM01QRXU0RXIxVEtYY2ZhdDB3QVpIaWdZY2FGQjU1Uk9GOXctdldMUmppV3lSd29zSm51M0ZMbkRhR3VxRzdfQzg2T3RFUW1wMlk3ZFk4SGp6eVRwVjd6cFNkVkJwRHAtSDgxeXNkMkJPQ0hIZXRiSUl2bENBVdIBngFBVV95cUxOeXZ5TjBYdENjMTB5SWZiMFY2VE9WR0ZIVHV2RC14MUJBZVhBdnNlc0FHNjg1ZmdHdWJwTmdmNW1jcnQtYUNqQ18tbGFBWlhyV0h5dVhZcjRZcEU4NjRxVk1xYnFnUlNwM1ZRZFRBVXBNVWZxdVhTSnBRQVFNcUN1OFc4WnFVV3JvMUpMdnRRQjhyM2d6YjZPSk1QOXhkdw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiiwFBVV95cUxPdm02b0lqTE9iNmY3Zy1HMjFsaThSQURrR2Nuckk2MDJQQ1czcm5JajZod051RkZqdC0xc0lvRHFUUHE2T3dLSGtTWlJSUHhRQ2F1VU5xa0phWnVHU0JaaHlkSU1oVDZVNUJiNDVGa20yaURuZGc0UHpsSXYzb3NCeXFtSzJCTnVxdmdn0gGQAUFVX3lxTFBxdGNzVlR3WVNXSHFfTUhqLWNwdVRjV0ZhdjhmNFhMaWZBRE05R1pWX1VoaFFQVG56R1ROUno1QW01OVFBelNrNWJiT3pzbGpYd2F5RVN6TzAtaXpuRWFZM2ViVmNBQnYzTnV4VXNrb1JOa1JuMm54WmpzWnRyRG5LTW4wZ1AtczRvbU1rT2Zudg?oc=5</t>
         </is>
       </c>
       <c r="F17" t="n">
@@ -941,17 +941,17 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Government issues 'life expectancy' in UK update amid major NHS change - The Mirror</t>
+          <t>Nightlife sector contributes £112 billion to UK economy per year, new report reveals - Far Out Magazine</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Tue, 27 Jan 2026 13:32:00 GMT</t>
+          <t>Tue, 27 Jan 2026 17:27:44 GMT</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiiwFBVV95cUxPdm02b0lqTE9iNmY3Zy1HMjFsaThSQURrR2Nuckk2MDJQQ1czcm5JajZod051RkZqdC0xc0lvRHFUUHE2T3dLSGtTWlJSUHhRQ2F1VU5xa0phWnVHU0JaaHlkSU1oVDZVNUJiNDVGa20yaURuZGc0UHpsSXYzb3NCeXFtSzJCTnVxdmdn0gGQAUFVX3lxTFBxdGNzVlR3WVNXSHFfTUhqLWNwdVRjV0ZhdjhmNFhMaWZBRE05R1pWX1VoaFFQVG56R1ROUno1QW01OVFBelNrNWJiT3pzbGpYd2F5RVN6TzAtaXpuRWFZM2ViVmNBQnYzTnV4VXNrb1JOa1JuMm54WmpzWnRyRG5LTW4wZ1AtczRvbU1rT2Zudg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxPTXQ1ajJFMlRZM2JEV1ZQR25fclZyOXQwbDlJcXJfdjRaaC1YTTVRYXlqRU1WMEpnekhtR0t2bHAycmJJaWZFNnp0LWlnV2RVOGE4eWxzMU5sNnlqSF9BQlRZR0M4MkQtZjc0QUtWaGdrb1lHeHhzQlRaMTJKX0VvTHY1M3JlcS1XMnAybndZMlN6clRqTzQ4NA?oc=5</t>
         </is>
       </c>
       <c r="F18" t="n">
@@ -971,17 +971,17 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Nightlife sector contributes £112 billion to UK economy per year, new report reveals - Far Out Magazine</t>
+          <t>'Social media ban for under-16s' update shared by Government after demands for change - The Mirror</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Tue, 27 Jan 2026 17:27:44 GMT</t>
+          <t>Tue, 27 Jan 2026 15:01:00 GMT</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxPTXQ1ajJFMlRZM2JEV1ZQR25fclZyOXQwbDlJcXJfdjRaaC1YTTVRYXlqRU1WMEpnekhtR0t2bHAycmJJaWZFNnp0LWlnV2RVOGE4eWxzMU5sNnlqSF9BQlRZR0M4MkQtZjc0QUtWaGdrb1lHeHhzQlRaMTJKX0VvTHY1M3JlcS1XMnAybndZMlN6clRqTzQ4NA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiekFVX3lxTE5oUmVyR1pmSklKRTAzZXpLQmJ3M0VoWUhKWDU4THBiNG9vU2haeF9OaUxIZzZoRnF5bUVFSHZtbU1raFZkdkVkTnJxVmd2TlFvaWhvX1huVUV2bGRxbVhHc0dUT25wVVpzUFJvbktnQ0V3bnRPX3lWWGtB0gF_QVVfeXFMTXJVQlRVNnJvSWFmS1pFajB2V1JLMDdNV241SVFzU1pkaEdZRjVNQU5qYjY2eTFCTTRPbjhXemtUTmR3THFKYWhJQVZzYzMwVWJRN0VJVFhpVGdBb1oya1lWNlN1TlNYX0dzUlRGejc5WVZqaXR2V3g0WGh6aC1Wcw?oc=5</t>
         </is>
       </c>
       <c r="F19" t="n">
@@ -1001,17 +1001,17 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>'Social media ban for under-16s' update shared by Government after demands for change - The Mirror</t>
+          <t>Government report on racism in social care misses one important thing out - thecanary.co</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Tue, 27 Jan 2026 15:01:00 GMT</t>
+          <t>Mon, 26 Jan 2026 19:05:17 GMT</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiekFVX3lxTE5oUmVyR1pmSklKRTAzZXpLQmJ3M0VoWUhKWDU4THBiNG9vU2haeF9OaUxIZzZoRnF5bUVFSHZtbU1raFZkdkVkTnJxVmd2TlFvaWhvX1huVUV2bGRxbVhHc0dUT25wVVpzUFJvbktnQ0V3bnRPX3lWWGtB0gF_QVVfeXFMTXJVQlRVNnJvSWFmS1pFajB2V1JLMDdNV241SVFzU1pkaEdZRjVNQU5qYjY2eTFCTTRPbjhXemtUTmR3THFKYWhJQVZzYzMwVWJRN0VJVFhpVGdBb1oya1lWNlN1TlNYX0dzUlRGejc5WVZqaXR2V3g0WGh6aC1Wcw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiekFVX3lxTFA1UFVsamhLS2plWXJOM2xWN2dncElHQnlfX0FQaUlEaTdfTHdKaUViMmZ2a2ZMZDhkZFgtUDBRbld6eVpONUJ6dDh1cXVPMGhpSnFtMnplaXVUN1AxeXVnOWd2U1JXZndhWTlTaDR3V2tNa0pQREdvU0RB?oc=5</t>
         </is>
       </c>
       <c r="F20" t="n">
@@ -1021,27 +1021,27 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Current_Affairs</t>
+          <t>Supply_Chain</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>(geopolitics OR migration OR economy OR conflict OR legislation OR terrorism OR disinformation OR misinformation OR government OR policy OR regulation) AND (briefing OR analysis OR update OR report)</t>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Government report on racism in social care misses one important thing out - thecanary.co</t>
+          <t>Trump tariffs live updates: EU, India seal trade deal in rebuff to Trump as he threatens S. Korea tariff boost - Yahoo Finance UK</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Mon, 26 Jan 2026 19:05:17 GMT</t>
+          <t>Tue, 27 Jan 2026 16:42:00 GMT</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiekFVX3lxTFA1UFVsamhLS2plWXJOM2xWN2dncElHQnlfX0FQaUlEaTdfTHdKaUViMmZ2a2ZMZDhkZFgtUDBRbld6eVpONUJ6dDh1cXVPMGhpSnFtMnplaXVUN1AxeXVnOWd2U1JXZndhWTlTaDR3V2tNa0pQREdvU0RB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0gFBVV95cUxPRzdWMzRXR1F4eUlpNzNLeGw0QzdFTkRhOFVqLTlubG03MEFqaEtqcHI5U2Nudm9OSm5vUmt3emVGVGVwX3NzZndFUExDY3B6OTBuVE1rUVFsakhxLVZwUW5Gal9pWUZUc19KMnNSSVpocmhHMGo4T1k5SGczanc2WkFteV9hVTRLdUhoVFNNSHZDVERpS1RHejZPTXRFNGlkTUlzS0JHWWdva3FQRnZFQkFLZUVodWZFbVlpRW9ILTliRUwxdHJIcGZ2aFhFbzBtOXc?oc=5</t>
         </is>
       </c>
       <c r="F21" t="n">
@@ -1061,17 +1061,17 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Trump tariffs live updates: EU, India seal trade deal in rebuff to Trump as he threatens S. Korea tariff boost - Yahoo Finance UK</t>
+          <t>Official Website - AFC Wimbledon</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Tue, 27 Jan 2026 16:42:00 GMT</t>
+          <t>Tue, 27 Jan 2026 14:18:31 GMT</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0gFBVV95cUxPRzdWMzRXR1F4eUlpNzNLeGw0QzdFTkRhOFVqLTlubG03MEFqaEtqcHI5U2Nudm9OSm5vUmt3emVGVGVwX3NzZndFUExDY3B6OTBuVE1rUVFsakhxLVZwUW5Gal9pWUZUc19KMnNSSVpocmhHMGo4T1k5SGczanc2WkFteV9hVTRLdUhoVFNNSHZDVERpS1RHejZPTXRFNGlkTUlzS0JHWWdva3FQRnZFQkFLZUVodWZFbVlpRW9ILTliRUwxdHJIcGZ2aFhFbzBtOXc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijAFBVV95cUxQalpFT2t2S3NhYnVYcVhBX1dzbHJFaEJiV3VqZVZMZkI3U1VFNDUtWkJFSXRPMHdxV21YNGl5TjRaNlZtOWpsZHFiSllJenZjWTk3YW9WVHdoLTlRdEpnTlJXemFKVUhyU3hwZ3FLWWd6bXNIYmRxUHhITWczSS10bzZjMGFoa0FuUDlTbQ?oc=5</t>
         </is>
       </c>
       <c r="F22" t="n">
@@ -1091,17 +1091,17 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Official Website - AFC Wimbledon</t>
+          <t>Tariffs, trade and Trump - Institute for Government</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Tue, 27 Jan 2026 14:18:31 GMT</t>
+          <t>Fri, 23 Jan 2026 15:56:15 GMT</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijAFBVV95cUxQalpFT2t2S3NhYnVYcVhBX1dzbHJFaEJiV3VqZVZMZkI3U1VFNDUtWkJFSXRPMHdxV21YNGl5TjRaNlZtOWpsZHFiSllJenZjWTk3YW9WVHdoLTlRdEpnTlJXemFKVUhyU3hwZ3FLWWd6bXNIYmRxUHhITWczSS10bzZjMGFoa0FuUDlTbQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMic0FVX3lxTE9aMER4a2VpcHYtMHJabVdaZ2E0a1puR0dMaDRBU1EzZE9jS0ZxTTFabUNYdWxNaFJidlhOZjc3RmFEVENZbk1yYU1hZlp5bmlHM0dqME45Y0tqTE5tRFFJYU1nTDN5QVBaLVBKZHE5MGE3ek0?oc=5</t>
         </is>
       </c>
       <c r="F23" t="n">
@@ -1121,17 +1121,17 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Tariffs, trade and Trump - Institute for Government</t>
+          <t>EU-India trade deal to lower food, drinks tariffs - Just Drinks</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Fri, 23 Jan 2026 15:56:15 GMT</t>
+          <t>Tue, 27 Jan 2026 12:10:09 GMT</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMic0FVX3lxTE9aMER4a2VpcHYtMHJabVdaZ2E0a1puR0dMaDRBU1EzZE9jS0ZxTTFabUNYdWxNaFJidlhOZjc3RmFEVENZbk1yYU1hZlp5bmlHM0dqME45Y0tqTE5tRFFJYU1nTDN5QVBaLVBKZHE5MGE3ek0?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiigFBVV95cUxQNy1kWXkxd2RYR3ZSS18wMVhyNlNONEVjb19Ba3BBXzNIbFNTcTJUUmEzSzU3ci1DMjNlMTNqemFFekNUM0pQMzRuQzBjQ3VaZ0l1OHQzdmpSbEV3aUVEaWNIQ3R5NWJMakVqa2VzUE5sQXplM093YU1tcTg5NjQ2NmU5NkV5ODZjZlE?oc=5</t>
         </is>
       </c>
       <c r="F24" t="n">
@@ -1151,17 +1151,17 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>EU-India trade deal to lower food, drinks tariffs - Just Drinks</t>
+          <t>How Prepared are Leaders for Supply Chain Risk in 2026? - Supply Chain Digital Magazine</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Tue, 27 Jan 2026 12:10:09 GMT</t>
+          <t>Tue, 27 Jan 2026 15:19:06 GMT</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiigFBVV95cUxQNy1kWXkxd2RYR3ZSS18wMVhyNlNONEVjb19Ba3BBXzNIbFNTcTJUUmEzSzU3ci1DMjNlMTNqemFFekNUM0pQMzRuQzBjQ3VaZ0l1OHQzdmpSbEV3aUVEaWNIQ3R5NWJMakVqa2VzUE5sQXplM093YU1tcTg5NjQ2NmU5NkV5ODZjZlE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMihgFBVV95cUxPekc1a3FMb3hvZ0NmQWI5bERoeUpIdE5UVl9acHZZaFh1WGdWaVU3MEVUZFNGdndWektXQ3hrQ014VWxURWZ3VlZULUNCb19qY2tWQWhWcVJDWFV6X1JFMElVcGZxRFl5NVljVnRSbTkyNmdPdmhYTUp0N20zV3RtcW4xY3h2Zw?oc=5</t>
         </is>
       </c>
       <c r="F25" t="n">
@@ -1181,17 +1181,17 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>How Prepared are Leaders for Supply Chain Risk in 2026? - Supply Chain Digital Magazine</t>
+          <t>Galvanised Steel for Longspan Shelf Picking - Logistics Business</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Tue, 27 Jan 2026 15:19:06 GMT</t>
+          <t>Tue, 27 Jan 2026 23:03:17 GMT</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihgFBVV95cUxPekc1a3FMb3hvZ0NmQWI5bERoeUpIdE5UVl9acHZZaFh1WGdWaVU3MEVUZFNGdndWektXQ3hrQ014VWxURWZ3VlZULUNCb19qY2tWQWhWcVJDWFV6X1JFMElVcGZxRFl5NVljVnRSbTkyNmdPdmhYTUp0N20zV3RtcW4xY3h2Zw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxPRGI4a29qMXlBVFZSemdfWm8zTm1qRWdSSzU4RnZ3b3NJTE1acERpUXpkNXNqN2tLSldsQVVZenpXQjBXYk9ZYVJRNXY3NnRXY2ZSNVdfMFpVZjY5ak8ya0dubmtQUmxRbDlSbk9vTGtqU21kOF94Si1HZlBvTjJhWnE1VHQyaks1eHQwa3RDYmNNZ1diYzNGVTkyVmctaHlhYnpYSQ?oc=5</t>
         </is>
       </c>
       <c r="F26" t="n">
@@ -1211,17 +1211,17 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Galvanised Steel for Longspan Shelf Picking - Logistics Business</t>
+          <t>Exclusive: US to issue general license lifting some sanctions on Venezuelan oil industry, sources say - Reuters</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Tue, 27 Jan 2026 23:03:17 GMT</t>
+          <t>Tue, 27 Jan 2026 22:59:33 GMT</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxPRGI4a29qMXlBVFZSemdfWm8zTm1qRWdSSzU4RnZ3b3NJTE1acERpUXpkNXNqN2tLSldsQVVZenpXQjBXYk9ZYVJRNXY3NnRXY2ZSNVdfMFpVZjY5ak8ya0dubmtQUmxRbDlSbk9vTGtqU21kOF94Si1HZlBvTjJhWnE1VHQyaks1eHQwa3RDYmNNZ1diYzNGVTkyVmctaHlhYnpYSQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixwFBVV95cUxNQWl5N1JydFB0MW8wSW1CME4wRTI0cUxZRmU4TXVfN1ZlaFJXSGljcThWWHBtNTY2MEFjcEZiOUdWSUdFbUhFSHFyQVRob0ZtNEgxZmpkMVNKbmxpekZzdGdMRU1tWmxMUThDUHZsVF9PSWdLZmtQNHAxR1dVRnh5aFhmb2hYVnBPZ3BXMTZ3dUwyUk1ZYlZJRFQwbXNObkoxaFZIaGlUWkhKbER2NGhNai1FQ2M0WENlVThIVEJCU2cwaHVlM3Zz?oc=5</t>
         </is>
       </c>
       <c r="F27" t="n">
@@ -1241,17 +1241,17 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Exclusive: US to issue general license lifting some sanctions on Venezuelan oil industry, sources say - Reuters</t>
+          <t>US administration withdraws announcement of 10% additional tariffs on several EU countries and the UK over Greenland - Deloitte</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Tue, 27 Jan 2026 22:59:33 GMT</t>
+          <t>Wed, 28 Jan 2026 00:29:27 GMT</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixwFBVV95cUxNQWl5N1JydFB0MW8wSW1CME4wRTI0cUxZRmU4TXVfN1ZlaFJXSGljcThWWHBtNTY2MEFjcEZiOUdWSUdFbUhFSHFyQVRob0ZtNEgxZmpkMVNKbmxpekZzdGdMRU1tWmxMUThDUHZsVF9PSWdLZmtQNHAxR1dVRnh5aFhmb2hYVnBPZ3BXMTZ3dUwyUk1ZYlZJRFQwbXNObkoxaFZIaGlUWkhKbER2NGhNai1FQ2M0WENlVThIVEJCU2cwaHVlM3Zz?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi4wFBVV95cUxPYlpYbkJrTmwtbDVkSmY4S3BRcC1kSzFHQ1h2WXVmdzE4VV9QUmNZU0hqVkk1b3U0ZTZBNG9LVUFmOXZtSmp1SkM4ZUJfc3dHZmdKWWtaWmhmUk9GQ1RBaEdTaUVoakxmWndWOTQ5VWtaaVREUEVmbmZVM21oTVAtNXFhdzNWek5RSVVhaS10WHV3dFRweFhCaF9lYkFxYl9Qc3ptdzd2ZGNjM0ZvV2xvWnd0Qzc0cURPcGhrbW1hWm5sWldrckxPTHFCSHp2SkVLdG5VMldIQnpSdFF4NGR2WlNyaw?oc=5</t>
         </is>
       </c>
       <c r="F28" t="n">
@@ -1271,17 +1271,17 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>US administration withdraws announcement of 10% additional tariffs on several EU countries and the UK over Greenland - Deloitte</t>
+          <t>Portsmouth International Port: a £195m boost for the city - portsmouth.co.uk</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Wed, 28 Jan 2026 00:29:27 GMT</t>
+          <t>Wed, 28 Jan 2026 00:01:00 GMT</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi4wFBVV95cUxPYlpYbkJrTmwtbDVkSmY4S3BRcC1kSzFHQ1h2WXVmdzE4VV9QUmNZU0hqVkk1b3U0ZTZBNG9LVUFmOXZtSmp1SkM4ZUJfc3dHZmdKWWtaWmhmUk9GQ1RBaEdTaUVoakxmWndWOTQ5VWtaaVREUEVmbmZVM21oTVAtNXFhdzNWek5RSVVhaS10WHV3dFRweFhCaF9lYkFxYl9Qc3ptdzd2ZGNjM0ZvV2xvWnd0Qzc0cURPcGhrbW1hWm5sWldrckxPTHFCSHp2SkVLdG5VMldIQnpSdFF4NGR2WlNyaw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxQS0V1cUxLSHRSb2JGSkFKOE41cFBCU05KMHZJWVpqZFlieXVnZ0E5V3ZqaW5zQmZTc0h5NkdRYndsSG9SUVE5MEFWQXFlMmFkaU5BXzh1a2NzNi1sZ21RZHVLdjRqUlM2NXBVOUVlRlR4eHJONUNtbUZQVjZrR1lLbWdPR2hFX0JQZ1NsNmZnREp2LXdhUldCbnVVYk5xb292MkhlVUNFdmt6RDlt?oc=5</t>
         </is>
       </c>
       <c r="F29" t="n">
@@ -1301,17 +1301,17 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Portsmouth International Port: a £195m boost for the city - portsmouth.co.uk</t>
+          <t>Elliptic's 2026 regulatory and policy outlook: Sanctions enforcement will intensify - Elliptic</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Wed, 28 Jan 2026 00:01:00 GMT</t>
+          <t>Tue, 27 Jan 2026 15:34:09 GMT</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxQS0V1cUxLSHRSb2JGSkFKOE41cFBCU05KMHZJWVpqZFlieXVnZ0E5V3ZqaW5zQmZTc0h5NkdRYndsSG9SUVE5MEFWQXFlMmFkaU5BXzh1a2NzNi1sZ21RZHVLdjRqUlM2NXBVOUVlRlR4eHJONUNtbUZQVjZrR1lLbWdPR2hFX0JQZ1NsNmZnREp2LXdhUldCbnVVYk5xb292MkhlVUNFdmt6RDlt?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxNRGFtbjd5aEY2aV80MFRaV0JQbzNnY0FPVkhkR0hrcWFSMzhXMzZEbG9qMUQ0Y1A1c3ZhYTQyVjU5dkRLRGNvZWhfYUJDZDlvUkxoaDJqTmxIbFJZZElqY3RWZ0IxWkFHVFdObE9ZbHJ4NndrcVVjbEdOVnpaZTljV0lnVDBZMy12VElRTDhHLVhvZFd3Tkprd3BweFFwdXdkY2w5LUY4VVZzX3oxVWlN?oc=5</t>
         </is>
       </c>
       <c r="F30" t="n">
@@ -1331,17 +1331,17 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Elliptic's 2026 regulatory and policy outlook: Sanctions enforcement will intensify - Elliptic</t>
+          <t>US ports may see muted spring after 2025 surge - Supply Chain Dive</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Tue, 27 Jan 2026 15:34:09 GMT</t>
+          <t>Tue, 27 Jan 2026 20:21:17 GMT</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxNRGFtbjd5aEY2aV80MFRaV0JQbzNnY0FPVkhkR0hrcWFSMzhXMzZEbG9qMUQ0Y1A1c3ZhYTQyVjU5dkRLRGNvZWhfYUJDZDlvUkxoaDJqTmxIbFJZZElqY3RWZ0IxWkFHVFdObE9ZbHJ4NndrcVVjbEdOVnpaZTljV0lnVDBZMy12VElRTDhHLVhvZFd3Tkprd3BweFFwdXdkY2w5LUY4VVZzX3oxVWlN?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxPVFhyVUJDWW5Zb2VuSFBtT1hBMERBbFJMZ3RfcUVyVGY5RDF2YmxjeW01OTdkVUpQVWRfbm5NTzktcWtIUE5TcFNjYkVpYzJEZTFPeXIwOFNGX3E3UWRRLVdTMDlyRC1qYWF1YXYzbllfM3RCbTBRVFR3NXBLSnVPUDVQZmhTZFhheEt0SHZYUUM4NjFXWG1YdVg0aVpueTQ?oc=5</t>
         </is>
       </c>
       <c r="F31" t="n">
@@ -1361,17 +1361,17 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>US ports may see muted spring after 2025 surge - Supply Chain Dive</t>
+          <t>Polish Developer Reserves Port Site for New Offshore Wind Project - Offshore Wind</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Tue, 27 Jan 2026 20:21:17 GMT</t>
+          <t>Tue, 27 Jan 2026 15:04:01 GMT</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxPVFhyVUJDWW5Zb2VuSFBtT1hBMERBbFJMZ3RfcUVyVGY5RDF2YmxjeW01OTdkVUpQVWRfbm5NTzktcWtIUE5TcFNjYkVpYzJEZTFPeXIwOFNGX3E3UWRRLVdTMDlyRC1qYWF1YXYzbllfM3RCbTBRVFR3NXBLSnVPUDVQZmhTZFhheEt0SHZYUUM4NjFXWG1YdVg0aVpueTQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxQMmprbWM3MFVPYjBkVEtBdWNXbmMxQzd5S0szTUIzNVliLVVjSzdmQ2hCT3lFQVFlUHRRTVNNUWgyRjlVeGg3U0c3em5PX0VEWU1jczZQOWtGQVBRLWF2UzVZTHkzNXVWeFJOUFJaU2VEclI3TlpPZVRXNHRFSW9YdnhWckRjYUw3VWRQQjlxcWVhblhpT2ZKeDU2SkxtRkhSSXZ1NVdaUkhQUQ?oc=5</t>
         </is>
       </c>
       <c r="F32" t="n">
@@ -1391,17 +1391,17 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Polish Developer Reserves Port Site for New Offshore Wind Project - Offshore Wind</t>
+          <t>Construction supply chain braces itself after slowdown in growth - Construction Wave</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Tue, 27 Jan 2026 15:04:01 GMT</t>
+          <t>Tue, 27 Jan 2026 16:46:26 GMT</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxQMmprbWM3MFVPYjBkVEtBdWNXbmMxQzd5S0szTUIzNVliLVVjSzdmQ2hCT3lFQVFlUHRRTVNNUWgyRjlVeGg3U0c3em5PX0VEWU1jczZQOWtGQVBRLWF2UzVZTHkzNXVWeFJOUFJaU2VEclI3TlpPZVRXNHRFSW9YdnhWckRjYUw3VWRQQjlxcWVhblhpT2ZKeDU2SkxtRkhSSXZ1NVdaUkhQUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxNeFBYYU1ybFg5YVN0UTYwaDMzNXg0bGhhSEttRHNjQlRhTEI1dUFKVVZiemVWR24zU2pkNFNTaXFqRXhsc0k5Mm9FQUhaUVlPOWptM0t3cHFrTzdoNnI4RVNyQklQN0xWZHlyOGMtdVVRU1cxUkkxeVpyVFR6dmVBRklLVEJJeGJXVkFwZGN1SXU5ajk2M2liTzR5UVRaUFR0N1hpOWxMd1k0YWM?oc=5</t>
         </is>
       </c>
       <c r="F33" t="n">
@@ -1421,17 +1421,17 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Construction supply chain braces itself after slowdown in growth - Construction Wave</t>
+          <t>Storm Chandra: EFL games at Port Vale, Cheltenham and Barrow postponed - BBC</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Tue, 27 Jan 2026 16:46:26 GMT</t>
+          <t>Tue, 27 Jan 2026 12:36:24 GMT</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxNeFBYYU1ybFg5YVN0UTYwaDMzNXg0bGhhSEttRHNjQlRhTEI1dUFKVVZiemVWR24zU2pkNFNTaXFqRXhsc0k5Mm9FQUhaUVlPOWptM0t3cHFrTzdoNnI4RVNyQklQN0xWZHlyOGMtdVVRU1cxUkkxeVpyVFR6dmVBRklLVEJJeGJXVkFwZGN1SXU5ajk2M2liTzR5UVRaUFR0N1hpOWxMd1k0YWM?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiZ0FVX3lxTE0zSXFpSVhYVEpmUVhQdklHUWV2NFpOdnFlbmJncGNzSktVM08yWkxDZ1AwM1RFNFhCeGJ2M3J1T2NmMDBZT2xMYWptNXNxOVV2Szh3LXJBbHU1cklkRUwxeGdsbnBSeHM?oc=5</t>
         </is>
       </c>
       <c r="F34" t="n">
@@ -1451,17 +1451,17 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Storm Chandra: EFL games at Port Vale, Cheltenham and Barrow postponed - BBC</t>
+          <t>EU expected to approve new Iran sanctions in response to crackdown - Reuters</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Tue, 27 Jan 2026 12:36:24 GMT</t>
+          <t>Tue, 27 Jan 2026 19:03:12 GMT</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiZ0FVX3lxTE0zSXFpSVhYVEpmUVhQdklHUWV2NFpOdnFlbmJncGNzSktVM08yWkxDZ1AwM1RFNFhCeGJ2M3J1T2NmMDBZT2xMYWptNXNxOVV2Szh3LXJBbHU1cklkRUwxeGdsbnBSeHM?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxNQTI0aVQ4VEswVHdQdndrTHYyejZPaE40TE1tb2FyRWdULU4tcUZ4UVEza2kxeTl6a1Q4SEdzaGRZNmhOVEk5anhTQ2o4TExGdzhGOHBFSEM1aG9TRUJEODJ3eE84Y3pnc2lRMHZKaGJqRjZNRjVjVnVIQndsWmljR2l6UFlsZFJKS29rMDBOUFU3VTdsSEt4dkxoZUJwdG1pUDdSdFpzVmM3aUZfcXpKNA?oc=5</t>
         </is>
       </c>
       <c r="F35" t="n">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>EU expected to approve new Iran sanctions in response to crackdown - Reuters</t>
+          <t>Trump threatens Canada with 100% tariffs if it 'makes a deal with China' - BBC</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Tue, 27 Jan 2026 19:03:12 GMT</t>
+          <t>Sat, 24 Jan 2026 22:10:33 GMT</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxNQTI0aVQ4VEswVHdQdndrTHYyejZPaE40TE1tb2FyRWdULU4tcUZ4UVEza2kxeTl6a1Q4SEdzaGRZNmhOVEk5anhTQ2o4TExGdzhGOHBFSEM1aG9TRUJEODJ3eE84Y3pnc2lRMHZKaGJqRjZNRjVjVnVIQndsWmljR2l6UFlsZFJKS29rMDBOUFU3VTdsSEt4dkxoZUJwdG1pUDdSdFpzVmM3aUZfcXpKNA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTE1PaGloV0lKT3NjQTF3dUZIWGVPNmZTSW8yN3g1OWtfanlsWjlUTDItQWVuZkp6WC1RNTJPRDdya0lKTzdGcjNQc0hLOGtCWmhRaEJCRlNRc3A1UQ?oc=5</t>
         </is>
       </c>
       <c r="F36" t="n">
@@ -1511,17 +1511,17 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Trump threatens Canada with 100% tariffs if it 'makes a deal with China' - BBC</t>
+          <t>Logistics Automation Industry Research Report 2026 - Global Market Size, Share, Trends, Opportunities, and Forecasts, 2021-2025 &amp; 2026-2031 - Yahoo Finance UK</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Sat, 24 Jan 2026 22:10:33 GMT</t>
+          <t>Tue, 27 Jan 2026 16:11:00 GMT</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTE1PaGloV0lKT3NjQTF3dUZIWGVPNmZTSW8yN3g1OWtfanlsWjlUTDItQWVuZkp6WC1RNTJPRDdya0lKTzdGcjNQc0hLOGtCWmhRaEJCRlNRc3A1UQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxOZDd2R3NHb2NBTmpZcTQwUWgzYUZyQ2NWVmtBWUszbmdMenI4Y09vQjNkUmZJTlRnRjFTYXRyRjBUT3FwR2JUYkRGZXh3LWkxR1JDTzJieUJraktmYWx3VGRuV185aXl5bmJicXN3UGpCSmVQVjI3Z2FSYjNYTFJLb184d0x1VnJKUm5SWHc2TGxfbGZhRjlLaUdB?oc=5</t>
         </is>
       </c>
       <c r="F37" t="n">
@@ -1541,17 +1541,17 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Logistics Automation Industry Research Report 2026 - Global Market Size, Share, Trends, Opportunities, and Forecasts, 2021-2025 &amp; 2026-2031 - Yahoo Finance UK</t>
+          <t>Can Avetta and Graphite Fix Supplier Onboarding? - Supply Chain Digital Magazine</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Tue, 27 Jan 2026 16:11:00 GMT</t>
+          <t>Tue, 27 Jan 2026 16:46:09 GMT</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxOZDd2R3NHb2NBTmpZcTQwUWgzYUZyQ2NWVmtBWUszbmdMenI4Y09vQjNkUmZJTlRnRjFTYXRyRjBUT3FwR2JUYkRGZXh3LWkxR1JDTzJieUJraktmYWx3VGRuV185aXl5bmJicXN3UGpCSmVQVjI3Z2FSYjNYTFJLb184d0x1VnJKUm5SWHc2TGxfbGZhRjlLaUdB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiiwFBVV95cUxOdWpUY1hnZmdYRmZqV2xJaDdVZ2U1Ni1zNlk5cjF6d1hNZ2xCR3luVWFJMHB1OFRVSGZ5M0pQUEJVM05pNDFFMVMtZGc3MFVGclA2OHF5OXlwZHNNazdwU1hDYmZvRDZEbFBQcDVQVHRKcEJMU0NhcEdJTk5FSXFOdzZLYjRWRXdGcTFv?oc=5</t>
         </is>
       </c>
       <c r="F38" t="n">
@@ -1571,17 +1571,17 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Can Avetta and Graphite Fix Supplier Onboarding? - Supply Chain Digital Magazine</t>
+          <t>China: Compliance Required for Layoff due to AI Replacement - Taylor Wessing</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Tue, 27 Jan 2026 16:46:09 GMT</t>
+          <t>Tue, 27 Jan 2026 16:06:43 GMT</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiiwFBVV95cUxOdWpUY1hnZmdYRmZqV2xJaDdVZ2U1Ni1zNlk5cjF6d1hNZ2xCR3luVWFJMHB1OFRVSGZ5M0pQUEJVM05pNDFFMVMtZGc3MFVGclA2OHF5OXlwZHNNazdwU1hDYmZvRDZEbFBQcDVQVHRKcEJMU0NhcEdJTk5FSXFOdzZLYjRWRXdGcTFv?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizgFBVV95cUxQNFl0c09CNHhiV09aZXIwOW9QbVg2ZWNiVnFVcmVSQmUydW0wdll6MFotazlzYzZ5djRfT1JzdjFhdnB0dnVFSE0wRjRRYTZldllWMHZxNWZRckhZMEwxQ0pDVGNPUXBTdnctYWZ1c2NLN25qVmVGajgyZ09yRFlLV21DZm9wN0U2UURLeFFqTTJ0cVlCY3pyWk1LT3c4SVRFSmp3U2JRTUUzMV9feGMtZ240WlE0VmV2VlNfcUdRNUdJRDhfbFgxRlU3eUotdw?oc=5</t>
         </is>
       </c>
       <c r="F39" t="n">
@@ -1601,17 +1601,17 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>China: Compliance Required for Layoff due to AI Replacement - Taylor Wessing</t>
+          <t>UK wants to use oil from shadow fleet to fund Ukraine war effort - BBC</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Tue, 27 Jan 2026 16:06:43 GMT</t>
+          <t>Tue, 27 Jan 2026 18:15:05 GMT</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizgFBVV95cUxQNFl0c09CNHhiV09aZXIwOW9QbVg2ZWNiVnFVcmVSQmUydW0wdll6MFotazlzYzZ5djRfT1JzdjFhdnB0dnVFSE0wRjRRYTZldllWMHZxNWZRckhZMEwxQ0pDVGNPUXBTdnctYWZ1c2NLN25qVmVGajgyZ09yRFlLV21DZm9wN0U2UURLeFFqTTJ0cVlCY3pyWk1LT3c4SVRFSmp3U2JRTUUzMV9feGMtZ240WlE0VmV2VlNfcUdRNUdJRDhfbFgxRlU3eUotdw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTE1udFNydU14TnlEcFNoNWlPSjhFZEJuSG5INlYxazJWLVVoQndSbmdpdmZ0NEtNVGJfc1diN3JKOU9VV1N2Q2JKOUVodTJKbEV5RldVbWp0SkN1dw?oc=5</t>
         </is>
       </c>
       <c r="F40" t="n">
@@ -1631,17 +1631,17 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>UK wants to use oil from shadow fleet to fund Ukraine war effort - BBC</t>
+          <t>This Ugreen 4-port plug is the last charger you’ll ever need (40% off) - Macworld</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Tue, 27 Jan 2026 18:15:05 GMT</t>
+          <t>Tue, 27 Jan 2026 16:26:00 GMT</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTE1udFNydU14TnlEcFNoNWlPSjhFZEJuSG5INlYxazJWLVVoQndSbmdpdmZ0NEtNVGJfc1diN3JKOU9VV1N2Q2JKOUVodTJKbEV5RldVbWp0SkN1dw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxQdjRDamxVWXNZT3ZiUlJxZjdlNjJMUi1qRWRldHQzSjUwejJTQ0ZDYlJfQnNWNDdmbko5MWJYam5NT1laSFIzVE1jZ2pPaWtkcVA2eloyMFYwejE4OUpQOWVPalRCV0dieFJ1WlFMVVlxRVZ3Q2xCR2UxSnhHNVJUN1N6dW40Mzc1MkNBZmJpQWlkN1IzbFlvWWlXT3dXODZZVmhsZVVJMFJPemNLV2JPMk5R?oc=5</t>
         </is>
       </c>
       <c r="F41" t="n">
@@ -1661,17 +1661,17 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>This Ugreen 4-port plug is the last charger you’ll ever need (40% off) - Macworld</t>
+          <t>Bayer's New Variety: Transforming Strawberry Supply Chains - Supply Chain Digital Magazine</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Tue, 27 Jan 2026 16:26:00 GMT</t>
+          <t>Tue, 27 Jan 2026 15:38:58 GMT</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxQdjRDamxVWXNZT3ZiUlJxZjdlNjJMUi1qRWRldHQzSjUwejJTQ0ZDYlJfQnNWNDdmbko5MWJYam5NT1laSFIzVE1jZ2pPaWtkcVA2eloyMFYwejE4OUpQOWVPalRCV0dieFJ1WlFMVVlxRVZ3Q2xCR2UxSnhHNVJUN1N6dW40Mzc1MkNBZmJpQWlkN1IzbFlvWWlXT3dXODZZVmhsZVVJMFJPemNLV2JPMk5R?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxQQjd2RjdJcVdGUExFbjJzcXlvOEFTMi1PWUI0a3o1WGhxSHpnUE9TMTJXYUltV0dXNUtOYjRQQ09NMzhpSnVrcEtZWUFBaG1ZVE5kOTZ6QUJaTVBfRVlsTFdLUkZXYlRMSXRfYlVPVmZvYmhSZXEzdEFPLVdNMThUYThKWXloYWhBemFZMEVWOS1vZTFxeUNB?oc=5</t>
         </is>
       </c>
       <c r="F42" t="n">
@@ -1691,17 +1691,17 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Bayer's New Variety: Transforming Strawberry Supply Chains - Supply Chain Digital Magazine</t>
+          <t>Tariffs, demand boost US steel outlook: Nucor - Argus Media</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Tue, 27 Jan 2026 15:38:58 GMT</t>
+          <t>Tue, 27 Jan 2026 21:14:56 GMT</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxQQjd2RjdJcVdGUExFbjJzcXlvOEFTMi1PWUI0a3o1WGhxSHpnUE9TMTJXYUltV0dXNUtOYjRQQ09NMzhpSnVrcEtZWUFBaG1ZVE5kOTZ6QUJaTVBfRVlsTFdLUkZXYlRMSXRfYlVPVmZvYmhSZXEzdEFPLVdNMThUYThKWXloYWhBemFZMEVWOS1vZTFxeUNB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxPdGpsREs1bmswcHJXcUtBQWRuamg3SjlFV1k5TDE1VnRKT2lkMUYtVUZBQS1nOFY3c3Rnb1UxYjRSRXMtSldqSjdpVnpfemtWWmNHU2NiY1lTQmFwVnRsVV83VVdUek5lRk9tOXowMHVhV0dscGZkUExfZVFBanljWDBLb1hVNkhNRDN6RDhTbmJpSjlCaWNMRUVQQ3VwY3ZBRnhybkpkNF9zWDFPVkJFN2xNWUdsaEdydUE?oc=5</t>
         </is>
       </c>
       <c r="F43" t="n">
@@ -1721,17 +1721,17 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Tariffs, demand boost US steel outlook: Nucor - Argus Media</t>
+          <t>KuCoin EU Completes MiCAR Compliance Milestone, Appoints Sabina Liu as Managing Director to Lead Next Phase of Europe Expansion - PA Media</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Tue, 27 Jan 2026 21:14:56 GMT</t>
+          <t>Tue, 27 Jan 2026 19:49:46 GMT</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxPdGpsREs1bmswcHJXcUtBQWRuamg3SjlFV1k5TDE1VnRKT2lkMUYtVUZBQS1nOFY3c3Rnb1UxYjRSRXMtSldqSjdpVnpfemtWWmNHU2NiY1lTQmFwVnRsVV83VVdUek5lRk9tOXowMHVhV0dscGZkUExfZVFBanljWDBLb1hVNkhNRDN6RDhTbmJpSjlCaWNMRUVQQ3VwY3ZBRnhybkpkNF9zWDFPVkJFN2xNWUdsaEdydUE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiigJBVV95cUxNaHByYlF4VE5VSnZYdFUxa3gxcUdNeHZVaWlDUmhlX1pza3FCWnhEUnZ4RFRSMnBaWGlfUEtDbldQNnM2cTROSnJ0OGJYU2FwbC15NGo3UGc0MG5DQUdnSHZCZS02QXNDc1puSWwxOXpITlZRR1ZaaDFUSC1IWEFsX3R3VEt3dTVaR1BlUjlOSmtoaTRJazVzVG90Z2lsYngzN29EbFdwRHdNMi1CRmRHSXU1MWFURkVMM3p2dl9MYldBUXktenZkTUdWTzIxT2xFQ25sNm5XaWoxZHM2VDRRdzd3eFZQSWVqNWRuVDRlWEg2dE1wMjFCa2RScTF3QUtoZndIakMtcVd2UQ?oc=5</t>
         </is>
       </c>
       <c r="F44" t="n">
@@ -1751,17 +1751,17 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>KuCoin EU Completes MiCAR Compliance Milestone, Appoints Sabina Liu as Managing Director to Lead Next Phase of Europe Expansion - PA Media</t>
+          <t>BPI teams up with NMT International Shipping UK to boost overseas machinery buyers - Project Plant</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Tue, 27 Jan 2026 19:49:46 GMT</t>
+          <t>Tue, 27 Jan 2026 13:53:09 GMT</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiigJBVV95cUxNaHByYlF4VE5VSnZYdFUxa3gxcUdNeHZVaWlDUmhlX1pza3FCWnhEUnZ4RFRSMnBaWGlfUEtDbldQNnM2cTROSnJ0OGJYU2FwbC15NGo3UGc0MG5DQUdnSHZCZS02QXNDc1puSWwxOXpITlZRR1ZaaDFUSC1IWEFsX3R3VEt3dTVaR1BlUjlOSmtoaTRJazVzVG90Z2lsYngzN29EbFdwRHdNMi1CRmRHSXU1MWFURkVMM3p2dl9MYldBUXktenZkTUdWTzIxT2xFQ25sNm5XaWoxZHM2VDRRdzd3eFZQSWVqNWRuVDRlWEg2dE1wMjFCa2RScTF3QUtoZndIakMtcVd2UQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxNZV9yRUx5d3pOSnZJeWs5M1VDelBPMFVyV2dsYWRRYUpkZlp3NUY1dUpzWWtJUVVmS0ZEQ1AweC12RlN2UERmSlpHdGY4RDR1RUlwek5SOXE5b25QamhFZ011REFkbXNWbEY0blZFSXVqWF9RQ2k1cHI0T1gydm9pZ0JDMjJ0dUVtTDVGQmxNMEdZU05KZElITXl4ZG9iT0xwNjBhUmJ6cWNyeWd5aXI3NnVUbW9heDJ4bGc?oc=5</t>
         </is>
       </c>
       <c r="F45" t="n">
@@ -1781,17 +1781,17 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>BPI teams up with NMT International Shipping UK to boost overseas machinery buyers - Project Plant</t>
+          <t>Gelatinous horde of red stinging jellyfish washes into Melbourne beaches - The Guardian</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Tue, 27 Jan 2026 13:53:09 GMT</t>
+          <t>Wed, 28 Jan 2026 00:10:00 GMT</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxNZV9yRUx5d3pOSnZJeWs5M1VDelBPMFVyV2dsYWRRYUpkZlp3NUY1dUpzWWtJUVVmS0ZEQ1AweC12RlN2UERmSlpHdGY4RDR1RUlwek5SOXE5b25QamhFZ011REFkbXNWbEY0blZFSXVqWF9RQ2k1cHI0T1gydm9pZ0JDMjJ0dUVtTDVGQmxNMEdZU05KZElITXl4ZG9iT0xwNjBhUmJ6cWNyeWd5aXI3NnVUbW9heDJ4bGc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxQZGk5ZnNRRnNjcjRNbHBVOFBKOFpQQ1oyYjB2amUyRlZtcjJKUHFsLWcwRmNkd0toUWpQSm5RYW9oeVdZZ3cwYjVzb2RXMVAydFVaSU1IQ2FFOEdHTjhFc3MzMnNLT1o2WDh1clE0a3FBNS1jOUVpT3kzNExhamJIajVxNm16WmNOQTNpTzhqZElUdU55bGJhYzRhdzl6cVZMUXhDaF8zSFc4NU0?oc=5</t>
         </is>
       </c>
       <c r="F46" t="n">
@@ -1811,17 +1811,17 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Gelatinous horde of red stinging jellyfish washes into Melbourne beaches - The Guardian</t>
+          <t>Supply chain tech and land wins bode well as agency Agent prepares for 20th birthday - Prolific North</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Wed, 28 Jan 2026 00:10:00 GMT</t>
+          <t>Tue, 27 Jan 2026 16:29:04 GMT</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxQZGk5ZnNRRnNjcjRNbHBVOFBKOFpQQ1oyYjB2amUyRlZtcjJKUHFsLWcwRmNkd0toUWpQSm5RYW9oeVdZZ3cwYjVzb2RXMVAydFVaSU1IQ2FFOEdHTjhFc3MzMnNLT1o2WDh1clE0a3FBNS1jOUVpT3kzNExhamJIajVxNm16WmNOQTNpTzhqZElUdU55bGJhYzRhdzl6cVZMUXhDaF8zSFc4NU0?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxOMkNDUkl6Q0pMSXU2Y2VxeUpQRVRiS01lcTlSeTE2ei05Qkc4Rm8tSURqVTlDbUhtYzV2cGpJMkZHME9mbThpRE5iOWdLYWtueVAwemNpYkw3b3ZPa2ppZF9EVDdZZjBQSThqNElaOGw4c1Q4dlFrdXB4NkUwYW91TnRFYVVoU2xOMkp0dnNzanRMUG9tWk53RkNMaEwtUkdrYXZpcVlfdlN5dlNoS0liemhJOTBHelpJMEwwWExKUQ?oc=5</t>
         </is>
       </c>
       <c r="F47" t="n">
@@ -1841,17 +1841,17 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Supply chain tech and land wins bode well as agency Agent prepares for 20th birthday - Prolific North</t>
+          <t>Concerns seal and porpoise deaths could be result of fallen shipping containers | ITV News - ITVX</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Tue, 27 Jan 2026 16:29:04 GMT</t>
+          <t>Tue, 27 Jan 2026 16:32:03 GMT</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxOMkNDUkl6Q0pMSXU2Y2VxeUpQRVRiS01lcTlSeTE2ei05Qkc4Rm8tSURqVTlDbUhtYzV2cGpJMkZHME9mbThpRE5iOWdLYWtueVAwemNpYkw3b3ZPa2ppZF9EVDdZZjBQSThqNElaOGw4c1Q4dlFrdXB4NkUwYW91TnRFYVVoU2xOMkp0dnNzanRMUG9tWk53RkNMaEwtUkdrYXZpcVlfdlN5dlNoS0liemhJOTBHelpJMEwwWExKUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxPTUZkQXZ2QTlwZTZlaUN0RUhsT01vR2pRTFdYMGFQYkNEVXhaVVdJWVlfYjgyZHdiVmFzQ2d6ZkVXSXpBclJjZWhqdUJJUlMtREo4N3AybDdnVy1sLTdJbUhyU3phWU1LeXo3ZTVIUF80amZXQmFMZkNvd2pLRHNUcXMzR2E3d2NtdnZDWnd0RjBRX2NnUE05TDdnUHFhTVpxbU5ORnlDR0Etd0pOcEQ3QWYtaHR1bGlGWS01dDdFZUxXZw?oc=5</t>
         </is>
       </c>
       <c r="F48" t="n">
@@ -1871,17 +1871,17 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Concerns seal and porpoise deaths could be result of fallen shipping containers | ITV News - ITVX</t>
+          <t>US Withdrawal From WHO Creates New Pharma Logistics Vulnerabilities - PharmTech.com</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Tue, 27 Jan 2026 16:32:03 GMT</t>
+          <t>Tue, 27 Jan 2026 17:02:01 GMT</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxPTUZkQXZ2QTlwZTZlaUN0RUhsT01vR2pRTFdYMGFQYkNEVXhaVVdJWVlfYjgyZHdiVmFzQ2d6ZkVXSXpBclJjZWhqdUJJUlMtREo4N3AybDdnVy1sLTdJbUhyU3phWU1LeXo3ZTVIUF80amZXQmFMZkNvd2pLRHNUcXMzR2E3d2NtdnZDWnd0RjBRX2NnUE05TDdnUHFhTVpxbU5ORnlDR0Etd0pOcEQ3QWYtaHR1bGlGWS01dDdFZUxXZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxPZ3pFNVJlb21YOHNXVDlSNWFNcUVqd3hudW0xRkZkUkxIbHo0ejg3YWRPRl9lUDNMRHduRDkxMVU2dmF1ZGhMeDM3aGpha3A1TndQNWtSMVBSUFcwTDNyQUE3S21sQi0wZ0w0ZmVVOURJZVJJWklqaWNicFozemloTlBOX2htTUVKelJxVG9nQThWRTJDN2ozdFhMZFhQQUk?oc=5</t>
         </is>
       </c>
       <c r="F49" t="n">
@@ -1901,17 +1901,17 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>US Withdrawal From WHO Creates New Pharma Logistics Vulnerabilities - PharmTech.com</t>
+          <t>Caspian Less Safe for Shipping as Russia and Iran Increase Military Use of Sea - The Jamestown Foundation</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Tue, 27 Jan 2026 17:02:01 GMT</t>
+          <t>Tue, 27 Jan 2026 22:18:38 GMT</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxPZ3pFNVJlb21YOHNXVDlSNWFNcUVqd3hudW0xRkZkUkxIbHo0ejg3YWRPRl9lUDNMRHduRDkxMVU2dmF1ZGhMeDM3aGpha3A1TndQNWtSMVBSUFcwTDNyQUE3S21sQi0wZ0w0ZmVVOURJZVJJWklqaWNicFozemloTlBOX2htTUVKelJxVG9nQThWRTJDN2ozdFhMZFhQQUk?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxQQ3VYT0FNLWs0djlMZXY3SFJKMVNBY29OMHdJSG5mMWtuWld6MlhkblN0eUUzd3Z0R3hnYTRaX0E5bmZyeG4xenRtTWlCM1dJcGlrRnVCT19uWHBMLXNGZE5BOUpsTHp6a3lHRS1QUzBuMHBGejhpSmVuTk5maEpVR2Q4a3ZDZk8zci1uMDN5SHItVEpERlNYVzMtX3BSbHNNSjdv?oc=5</t>
         </is>
       </c>
       <c r="F50" t="n">
@@ -1931,17 +1931,17 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Caspian Less Safe for Shipping as Russia and Iran Increase Military Use of Sea - The Jamestown Foundation</t>
+          <t>Rethinking Tail Spend: Transforming Procurement Before Compliance Risks Escalate - Pharmaceutical Executive</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Tue, 27 Jan 2026 22:18:38 GMT</t>
+          <t>Tue, 27 Jan 2026 18:30:21 GMT</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxQQ3VYT0FNLWs0djlMZXY3SFJKMVNBY29OMHdJSG5mMWtuWld6MlhkblN0eUUzd3Z0R3hnYTRaX0E5bmZyeG4xenRtTWlCM1dJcGlrRnVCT19uWHBMLXNGZE5BOUpsTHp6a3lHRS1QUzBuMHBGejhpSmVuTk5maEpVR2Q4a3ZDZk8zci1uMDN5SHItVEpERlNYVzMtX3BSbHNNSjdv?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiekFVX3lxTE1ndmVhRGtYR1E5ZlBPaGV6b1VVemVOTFg2VU04MFhWMXQwek9kbWRYRWxreWRQQjFVVy1aLXh1NXJZTjI5LXV1WWQ4NFE1UVgzaGpGc0FUb21qbnoyR0J0WmdoT2hYM19ac2ZvdWFfSXkwNkpMQ2VmUE5n?oc=5</t>
         </is>
       </c>
       <c r="F51" t="n">
@@ -1961,17 +1961,17 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Rethinking Tail Spend: Transforming Procurement Before Compliance Risks Escalate - Pharmaceutical Executive</t>
+          <t>Green shipping row sinks EU unity as camps split east and west - Euractiv</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Tue, 27 Jan 2026 18:30:21 GMT</t>
+          <t>Tue, 27 Jan 2026 05:01:06 GMT</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiekFVX3lxTE1ndmVhRGtYR1E5ZlBPaGV6b1VVemVOTFg2VU04MFhWMXQwek9kbWRYRWxreWRQQjFVVy1aLXh1NXJZTjI5LXV1WWQ4NFE1UVgzaGpGc0FUb21qbnoyR0J0WmdoT2hYM19ac2ZvdWFfSXkwNkpMQ2VmUE5n?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxOS0ZrM3VicG0wS0xkTWt6bUV2TGNaaVhUSTFXZlVfaDRFNUVjbDBkd05POW14MUpLWGlNRXhSUlljOUVxeHM2T2xfQXF4amhTdTJ1aVpncGdYUDZaYkxXeHpFUnVoZV9PX1hQMkhrbGNKLUxGX3NDTmFkelBBVDVpWWlPQTJxb003MlVQcW9jS1lDMzNtTXUzLQ?oc=5</t>
         </is>
       </c>
       <c r="F52" t="n">
@@ -1991,17 +1991,17 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Green shipping row sinks EU unity as camps split east and west - Euractiv</t>
+          <t>Gold soars past $5,100 an ounce, silver hits new record on tariff and US shutdown fears – as it happened - The Guardian</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Tue, 27 Jan 2026 05:01:06 GMT</t>
+          <t>Mon, 26 Jan 2026 07:53:00 GMT</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxOS0ZrM3VicG0wS0xkTWt6bUV2TGNaaVhUSTFXZlVfaDRFNUVjbDBkd05POW14MUpLWGlNRXhSUlljOUVxeHM2T2xfQXF4amhTdTJ1aVpncGdYUDZaYkxXeHpFUnVoZV9PX1hQMkhrbGNKLUxGX3NDTmFkelBBVDVpWWlPQTJxb003MlVQcW9jS1lDMzNtTXUzLQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxNVnJhMFZvVzZTU05lQlRmLWV0RDR2aEpSbnAtNHpOOUFyekEyTXcwT1NidVRnX2RLTW5nVURWZlh6VTRJcW5zS3VfdG1nVDBjOFRuaGIyc3BVeUhPVjc2dFdLVUMtS0JVVGZ1TzQ4X2FsbGxsdF81X1E1c3p6cU5jTThDdUJScWtFR1BBUDlHVV9CQk81SWV4WkhTYkFoZWw2SE5sR0Y3Si1lMk9jRjVZLUZlQndyZzdnM1FMWXc4WFNvVnhmbFE?oc=5</t>
         </is>
       </c>
       <c r="F53" t="n">
@@ -2011,27 +2011,27 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Supply_Chain</t>
+          <t>Protest</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally)</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Gold soars past $5,100 an ounce, silver hits new record on tariff and US shutdown fears – as it happened - The Guardian</t>
+          <t>Thousands protest in Paris over death of immigrant worker in police custody - France 24</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Mon, 26 Jan 2026 07:53:00 GMT</t>
+          <t>Sun, 25 Jan 2026 19:41:42 GMT</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxNVnJhMFZvVzZTU05lQlRmLWV0RDR2aEpSbnAtNHpOOUFyekEyTXcwT1NidVRnX2RLTW5nVURWZlh6VTRJcW5zS3VfdG1nVDBjOFRuaGIyc3BVeUhPVjc2dFdLVUMtS0JVVGZ1TzQ4X2FsbGxsdF81X1E1c3p6cU5jTThDdUJScWtFR1BBUDlHVV9CQk81SWV4WkhTYkFoZWw2SE5sR0Y3Si1lMk9jRjVZLUZlQndyZzdnM1FMWXc4WFNvVnhmbFE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxPYlU5TUFUS2RwUWU4T1pmRlhjWGgyVXpmTmphRUZ5eVlTTWFnNTdBQlRvMnNReXpFa0dFeGtGc2xaZEFBWFJkeE1LLUtNXy1wNDlYVWZQaGU4VEpyZ0hocEpyYU1zalhZLXJtQkxRTW9mT1haREZEU1ROTl9SbXpsbHY0LWhoSVBCSWFiRjF0ajdQOUtlRUlubTZ5NExrY09sX3RnOFl4UW5KVHpFb1pZNGxvMnQ4TzAzTF9wZDJMWmJNUQ?oc=5</t>
         </is>
       </c>
       <c r="F54" t="n">
@@ -2051,17 +2051,17 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Thousands protest in Paris over death of immigrant worker in police custody - France 24</t>
+          <t>Locals back police decision to stop controversial UKIP march through Whitechapel - Islam Channel</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Sun, 25 Jan 2026 19:41:42 GMT</t>
+          <t>Sun, 25 Jan 2026 12:20:56 GMT</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxPYlU5TUFUS2RwUWU4T1pmRlhjWGgyVXpmTmphRUZ5eVlTTWFnNTdBQlRvMnNReXpFa0dFeGtGc2xaZEFBWFJkeE1LLUtNXy1wNDlYVWZQaGU4VEpyZ0hocEpyYU1zalhZLXJtQkxRTW9mT1haREZEU1ROTl9SbXpsbHY0LWhoSVBCSWFiRjF0ajdQOUtlRUlubTZ5NExrY09sX3RnOFl4UW5KVHpFb1pZNGxvMnQ4TzAzTF9wZDJMWmJNUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxOaGYzdXFOVGhMdGdaSFgwd0VuUWlTeUwxUldyLUI3RGhKdG01bG1qWm5XWmFvU2RrV19ZdU9nTnZKbm5lNUFYRmw1Rk15N1ozSnZfZk95M2x2aUNaX3dsLTJzM2ZMbFBsSl8wbUYyeTQ2SFJvUnZIRjhHcFM5eXVDZWJWOXk5b2VDX3ZuU3hSMDFEUDhFaWgteXk2NEl1NTh5UGNuejlpQkk?oc=5</t>
         </is>
       </c>
       <c r="F55" t="n">
@@ -2081,17 +2081,17 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Locals back police decision to stop controversial UKIP march through Whitechapel - Islam Channel</t>
+          <t>Clashes erupt at antigovernment protest in Albanian capital Tirana - Al Jazeera</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Sun, 25 Jan 2026 12:20:56 GMT</t>
+          <t>Sun, 25 Jan 2026 13:07:30 GMT</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxOaGYzdXFOVGhMdGdaSFgwd0VuUWlTeUwxUldyLUI3RGhKdG01bG1qWm5XWmFvU2RrV19ZdU9nTnZKbm5lNUFYRmw1Rk15N1ozSnZfZk95M2x2aUNaX3dsLTJzM2ZMbFBsSl8wbUYyeTQ2SFJvUnZIRjhHcFM5eXVDZWJWOXk5b2VDX3ZuU3hSMDFEUDhFaWgteXk2NEl1NTh5UGNuejlpQkk?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxPN1NfVUJRMXlIUWdtcmc4TW1NR2NCeE82SC1Cdy1VSnIyWFFjSE1INHItZEQ1U2ZqemE4UmVGaFd4Z0RYRHVUSm1Pc2pXX01TVlpwbWlPNWw4TmZkVHM3ZGZwNHp0TGZJUDlMWklmVTk3ZWhfbnh6b2JyQk4tcXBweFFtVHlNUW5Gd2NhS1JtemVhRFp4X1l2V1dhdkFKWXJXZ1ZlcmRtTmctZ2gxempZ0gG0AUFVX3lxTE43amVva3dPTnlVS2I0dy1oYXFFdkdySmZGVkF6dWV5V2RQeGFGdFM5bHcwLWNQd1J5bkJQTTdzc1ByYU0xc2ZHTGpWX1ZacGs4dmNWWndRc2lnelRKSVJYVlo3YWFoUWhuXzFWYWxvZl8zX0cyOUMxWTZ6Nlk2MnhTajFhZUNENzdaMzBrTkxFWGQ3ZEZ4S1U5Sk1iLUpmUXNvdi1hRW1IRHVQcXFZTFY1YXNwWA?oc=5</t>
         </is>
       </c>
       <c r="F56" t="n">
@@ -2111,17 +2111,17 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Clashes erupt at antigovernment protest in Albanian capital Tirana - Al Jazeera</t>
+          <t>Arrests after protesters breach London prison grounds - BBC</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Sun, 25 Jan 2026 13:07:30 GMT</t>
+          <t>Sun, 25 Jan 2026 13:33:07 GMT</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxPN1NfVUJRMXlIUWdtcmc4TW1NR2NCeE82SC1Cdy1VSnIyWFFjSE1INHItZEQ1U2ZqemE4UmVGaFd4Z0RYRHVUSm1Pc2pXX01TVlpwbWlPNWw4TmZkVHM3ZGZwNHp0TGZJUDlMWklmVTk3ZWhfbnh6b2JyQk4tcXBweFFtVHlNUW5Gd2NhS1JtemVhRFp4X1l2V1dhdkFKWXJXZ1ZlcmRtTmctZ2gxempZ0gG0AUFVX3lxTE43amVva3dPTnlVS2I0dy1oYXFFdkdySmZGVkF6dWV5V2RQeGFGdFM5bHcwLWNQd1J5bkJQTTdzc1ByYU0xc2ZHTGpWX1ZacGs4dmNWWndRc2lnelRKSVJYVlo3YWFoUWhuXzFWYWxvZl8zX0cyOUMxWTZ6Nlk2MnhTajFhZUNENzdaMzBrTkxFWGQ3ZEZ4S1U5Sk1iLUpmUXNvdi1hRW1IRHVQcXFZTFY1YXNwWA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTE9oT2V2cHBpRDhqRE50M2lwajdjVlNnZEJtUjZTNmk2WXgwZmc4UGJHVFdhX2NzZXp0MmZjZE5saFpmX20xV2xDSXFROTNnWUJTMkhYbER2clhNQdIBX0FVX3lxTE43OFRBeUlPXzNBZkw1YTlGQURlVnZSbzlIdnN1UkI4RU9GSGZRdjd6ZnJxakdpTjAwRlEtbk14M0U0OFl1QU40SW9hVDRxRDNvX2x4alhDejIwMEo3X0J3?oc=5</t>
         </is>
       </c>
       <c r="F57" t="n">
@@ -2141,17 +2141,17 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Arrests after protesters breach London prison grounds - BBC</t>
+          <t>CVC strikes $1.6bn deal for US private credit group Marathon - Financial Times</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Sun, 25 Jan 2026 13:33:07 GMT</t>
+          <t>Mon, 26 Jan 2026 08:07:17 GMT</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTE9oT2V2cHBpRDhqRE50M2lwajdjVlNnZEJtUjZTNmk2WXgwZmc4UGJHVFdhX2NzZXp0MmZjZE5saFpmX20xV2xDSXFROTNnWUJTMkhYbER2clhNQdIBX0FVX3lxTE43OFRBeUlPXzNBZkw1YTlGQURlVnZSbzlIdnN1UkI4RU9GSGZRdjd6ZnJxakdpTjAwRlEtbk14M0U0OFl1QU40SW9hVDRxRDNvX2x4alhDejIwMEo3X0J3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMicEFVX3lxTE5HcmJmMzV3ckVtem5LS3dpSzI3UGNKbW1Ma3VkWjE2S1BJUFNjZkVFczV6RHAzTUF6QTNpS18tQW9oOEVTZ0trR29ZV3ZMTm53TDhTVnZROFNGNXdQX1ptdXFTdVBGQnc0Rl95UjVJOXk?oc=5</t>
         </is>
       </c>
       <c r="F58" t="n">
@@ -2171,17 +2171,17 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>CVC strikes $1.6bn deal for US private credit group Marathon - Financial Times</t>
+          <t>Police charge three pro-Palestine protesters with racial hatred for chanting ‘intifada’ - 5Pillars</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Mon, 26 Jan 2026 08:07:17 GMT</t>
+          <t>Tue, 27 Jan 2026 10:29:23 GMT</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMicEFVX3lxTE5HcmJmMzV3ckVtem5LS3dpSzI3UGNKbW1Ma3VkWjE2S1BJUFNjZkVFczV6RHAzTUF6QTNpS18tQW9oOEVTZ0trR29ZV3ZMTm53TDhTVnZROFNGNXdQX1ptdXFTdVBGQnc0Rl95UjVJOXk?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxQRWtHXzIxTlJXcjVzUnFnMThuclNRYUo4VVVWdkhMZ2ZVMEFLQXJnSVlRdXZTcWpBTXpTNUp3akh0clNKeUQxQnZaZEhxaGIwVmw4aFplME92cnhxYmp2NHFOQm5FU3Vad1g1QnNJTjJsaE1mLVZUaDFFV282QWMwWkd2Y0Jwd21zeVVFVENKQ2dRMGNIdFBkbng5WUhNR0NFN3ZUTmJldUJVNGpzUlUxc3RBQzBXNGpEVDlJXw?oc=5</t>
         </is>
       </c>
       <c r="F59" t="n">
@@ -2201,17 +2201,17 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Police charge three pro-Palestine protesters with racial hatred for chanting ‘intifada’ - 5Pillars</t>
+          <t>March 2026 Civil Service Police Exam - cambridgema.gov</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Tue, 27 Jan 2026 10:29:23 GMT</t>
+          <t>Tue, 27 Jan 2026 17:03:16 GMT</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxQRWtHXzIxTlJXcjVzUnFnMThuclNRYUo4VVVWdkhMZ2ZVMEFLQXJnSVlRdXZTcWpBTXpTNUp3akh0clNKeUQxQnZaZEhxaGIwVmw4aFplME92cnhxYmp2NHFOQm5FU3Vad1g1QnNJTjJsaE1mLVZUaDFFV282QWMwWkd2Y0Jwd21zeVVFVENKQ2dRMGNIdFBkbng5WUhNR0NFN3ZUTmJldUJVNGpzUlUxc3RBQzBXNGpEVDlJXw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi7wFBVV95cUxNUEdOcGJLaUtCLWRlbHdzMzJ2Zzg1Y3JGRkNmNHFhMGFFYWtXUWR5RFVQM1lTTkJkNk43N1Q3cFJieEl1VUE2amRSUXBkOFQwM2FZYXdUckJ5SDB1V25WUi1FbXgtU1pLV1VyMEtFUnZ1Y19hTFU2a2tnM1ZfeGhQdVV5dGxOR2RyTk1sWVJFbG1JanVTZ2tOaExMSWdTeWhpN2RxMjFnTkVIU3JQU2poYmxNcmE3S2RpLUxzOTlhUlIyT1QwTnF3TTE1YlpkRDhiZG5EMGgxdDRzcmF0M2JxZVhNb1pXbURrSUszM2M5Zw?oc=5</t>
         </is>
       </c>
       <c r="F60" t="n">
@@ -2231,17 +2231,17 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>March 2026 Civil Service Police Exam - cambridgema.gov</t>
+          <t>Rally organiser's claim of 'bashing' by Middle Eastern men comes unstuck - Australian Broadcasting Corporation</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Tue, 27 Jan 2026 17:03:16 GMT</t>
+          <t>Tue, 27 Jan 2026 19:00:00 GMT</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi7wFBVV95cUxNUEdOcGJLaUtCLWRlbHdzMzJ2Zzg1Y3JGRkNmNHFhMGFFYWtXUWR5RFVQM1lTTkJkNk43N1Q3cFJieEl1VUE2amRSUXBkOFQwM2FZYXdUckJ5SDB1V25WUi1FbXgtU1pLV1VyMEtFUnZ1Y19hTFU2a2tnM1ZfeGhQdVV5dGxOR2RyTk1sWVJFbG1JanVTZ2tOaExMSWdTeWhpN2RxMjFnTkVIU3JQU2poYmxNcmE3S2RpLUxzOTlhUlIyT1QwTnF3TTE1YlpkRDhiZG5EMGgxdDRzcmF0M2JxZVhNb1pXbURrSUszM2M5Zw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxPZjBRcFIxT1FCWlZuUC1ZUzh1YmJxM0pFeTF6NXF1SDVwV3I2ZDdEa00tN25yLV9NZlg3N2hObVB6MkJkNDNVcDhsaEVUSXJSU3o4ckJGbmFrQUNxQUhKOEstSXFoakVYVGdXRU9Zcm5zY1VHdy00cThVTk1XSUpzN3E2YThHZkUzUHJVd3UzVmtxenowck5FRm9RbGU1dw?oc=5</t>
         </is>
       </c>
       <c r="F61" t="n">
@@ -2261,17 +2261,17 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Rally organiser's claim of 'bashing' by Middle Eastern men comes unstuck - Australian Broadcasting Corporation</t>
+          <t>WATCH: Shocking moment car mounts pavement during police chase - cambstimes.co.uk</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Tue, 27 Jan 2026 19:00:00 GMT</t>
+          <t>Mon, 26 Jan 2026 17:10:00 GMT</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxPZjBRcFIxT1FCWlZuUC1ZUzh1YmJxM0pFeTF6NXF1SDVwV3I2ZDdEa00tN25yLV9NZlg3N2hObVB6MkJkNDNVcDhsaEVUSXJSU3o4ckJGbmFrQUNxQUhKOEstSXFoakVYVGdXRU9Zcm5zY1VHdy00cThVTk1XSUpzN3E2YThHZkUzUHJVd3UzVmtxenowck5FRm9RbGU1dw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxNWUZQZFEyMXBJcFlOYjhRN2lxeW8yQzFDdkZYQ0tZcmNRRmVSc29QQU1OR2oxUkl4Q3dNQlZlV3JJYUYwVHdXeXdpTU5nRGxmQmxKc0pfNXc1cExiSnd4Zjg0UUpwS1dHb2ltZjZnYUhYdk0zR2FKcVM4X2t0Wm5HdGptWWZFc0dpeG5lOHBSMHktWEU?oc=5</t>
         </is>
       </c>
       <c r="F62" t="n">
@@ -2291,17 +2291,17 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>WATCH: Shocking moment car mounts pavement during police chase - cambstimes.co.uk</t>
+          <t>Dozens arrested at anti-ICE protest - CNN</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Mon, 26 Jan 2026 17:10:00 GMT</t>
+          <t>Tue, 27 Jan 2026 12:21:00 GMT</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxNWUZQZFEyMXBJcFlOYjhRN2lxeW8yQzFDdkZYQ0tZcmNRRmVSc29QQU1OR2oxUkl4Q3dNQlZlV3JJYUYwVHdXeXdpTU5nRGxmQmxKc0pfNXc1cExiSnd4Zjg0UUpwS1dHb2ltZjZnYUhYdk0zR2FKcVM4X2t0Wm5HdGptWWZFc0dpeG5lOHBSMHktWEU?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMihwFBVV95cUxNNi1KRVYzd0kxZ3RFYjREY3JDWUQ3ODUxVkpDaFh4YkZfZjdjT2lmaFYwc1BBVjBJWnNQU0g2MUpnT1F4ZXhpZmhYUldYSmJFcVROUERnTnRhSjFKSmVqQlFqTjU0SzBfOTUyODFpTE1seGd0NlFrM1pjblVUXy1oZTJvQlpkbW8?oc=5</t>
         </is>
       </c>
       <c r="F63" t="n">
@@ -2321,17 +2321,17 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Dozens arrested at anti-ICE protest - CNN</t>
+          <t>Police allege man charged with hate speech at Sydney protest has links to disbanded neo-Nazi group - The Guardian</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Tue, 27 Jan 2026 12:21:00 GMT</t>
+          <t>Tue, 27 Jan 2026 02:08:00 GMT</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihwFBVV95cUxNNi1KRVYzd0kxZ3RFYjREY3JDWUQ3ODUxVkpDaFh4YkZfZjdjT2lmaFYwc1BBVjBJWnNQU0g2MUpnT1F4ZXhpZmhYUldYSmJFcVROUERnTnRhSjFKSmVqQlFqTjU0SzBfOTUyODFpTE1seGd0NlFrM1pjblVUXy1oZTJvQlpkbW8?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi8gFBVV95cUxPbWNpQW1BekVUNF9aa19XbDlZYmVubWZYbzZMZFNfclBEcExYbU90cTl4S2R5UEFaeXRGOXJvY3B2Zi0tZnlOcnp4WUJxMzNwdVNzNTVhd0pLY2E1NG85LWRLNXVwamwyUHhuZk40RHpRaENhZGU5Q3o5R2NwYVowSDRVMkJmaW55UGprYk96U0ZVUlVlQy1tRWRwZXVOOWlyQS1hZ0hUNnlFNlBlZjlpcklZNGF4UmZKU1hSR3Q2VmtqeVNoSHVvR2NadWpVQUtEelVpRFAwQUJFWkZyYnI4Y1N3Rm9BRTRvbzhlTGxhOWZidw?oc=5</t>
         </is>
       </c>
       <c r="F64" t="n">
@@ -2351,17 +2351,17 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Police allege man charged with hate speech at Sydney protest has links to disbanded neo-Nazi group - The Guardian</t>
+          <t>BHG Group to Outline Growth Strategy at March 2026 Capital Markets Day - TipRanks</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Tue, 27 Jan 2026 02:08:00 GMT</t>
+          <t>Tue, 27 Jan 2026 06:37:24 GMT</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi8gFBVV95cUxPbWNpQW1BekVUNF9aa19XbDlZYmVubWZYbzZMZFNfclBEcExYbU90cTl4S2R5UEFaeXRGOXJvY3B2Zi0tZnlOcnp4WUJxMzNwdVNzNTVhd0pLY2E1NG85LWRLNXVwamwyUHhuZk40RHpRaENhZGU5Q3o5R2NwYVowSDRVMkJmaW55UGprYk96U0ZVUlVlQy1tRWRwZXVOOWlyQS1hZ0hUNnlFNlBlZjlpcklZNGF4UmZKU1hSR3Q2VmtqeVNoSHVvR2NadWpVQUtEelVpRFAwQUJFWkZyYnI4Y1N3Rm9BRTRvbzhlTGxhOWZidw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxOcjF5dUlJdzFxTDNJNGF1dnpKRXJ3RHBfZ1ExUDFVVUJHOFctTnZaZk9LQTZDR0NfMEw3SWt5MVJOaXVkV3diZkpNakJXUEtSdUxLMFBOcTZ6Tzc4MnBYUU9NMklKM3BKbXlKYzNwX0JvMVNLc25EWmtBMC1lUUdiVUlRYzl2RENFYWxaVXZfekJaY2dienloUGxyQ0NVS2RXbGtQdFZqQWY3bXo0ZDE1Smg5ZEZ3UG1IUllDZmJ6VQ?oc=5</t>
         </is>
       </c>
       <c r="F65" t="n">
@@ -2381,17 +2381,17 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>BHG Group to Outline Growth Strategy at March 2026 Capital Markets Day - TipRanks</t>
+          <t>Killings in Minneapolis Invert Usual Dynamic Over Policing the Police - The New York Times</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Tue, 27 Jan 2026 06:37:24 GMT</t>
+          <t>Tue, 27 Jan 2026 16:25:00 GMT</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxOcjF5dUlJdzFxTDNJNGF1dnpKRXJ3RHBfZ1ExUDFVVUJHOFctTnZaZk9LQTZDR0NfMEw3SWt5MVJOaXVkV3diZkpNakJXUEtSdUxLMFBOcTZ6Tzc4MnBYUU9NMklKM3BKbXlKYzNwX0JvMVNLc25EWmtBMC1lUUdiVUlRYzl2RENFYWxaVXZfekJaY2dienloUGxyQ0NVS2RXbGtQdFZqQWY3bXo0ZDE1Smg5ZEZ3UG1IUllDZmJ6VQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxQSzY5bGtOTHZaSGJpcGU4bHJpUHNHYmptOE15clRaVi0tZ2xvTENnRzhsbTlUcWFhZmFnRUpFbGV5NDZmbk14dlJjUzFNTVhsbnEwb09zcjNZVm56X0JPdEQwVVJMWTZNTHJoR1d4VFlfYUt5bnp6Uk1OaWNKcXJaT3lCUE9CQ2NCdHZPRFpjajhfU2pTbDBWZg?oc=5</t>
         </is>
       </c>
       <c r="F66" t="n">
@@ -2411,17 +2411,17 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Killings in Minneapolis Invert Usual Dynamic Over Policing the Police - The New York Times</t>
+          <t>Police release shock footage of moment man allegedly threw bomb into Invasion Day protest - Sky News Australia</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Tue, 27 Jan 2026 16:25:00 GMT</t>
+          <t>Tue, 27 Jan 2026 21:32:18 GMT</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxQSzY5bGtOTHZaSGJpcGU4bHJpUHNHYmptOE15clRaVi0tZ2xvTENnRzhsbTlUcWFhZmFnRUpFbGV5NDZmbk14dlJjUzFNTVhsbnEwb09zcjNZVm56X0JPdEQwVVJMWTZNTHJoR1d4VFlfYUt5bnp6Uk1OaWNKcXJaT3lCUE9CQ2NCdHZPRFpjajhfU2pTbDBWZg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMisAJBVV95cUxQdTBhOHdlS2ZqU1VQRzhvRm95UkhhVGI3WFh6dDgzRUV2YXp6MnpRNzdxdXBDODhrZ1dicE9QcU1sRWFWWVloUkpYQklJZ2UxdUFVMGxXaFIzOGZQM3NETURNQXpqVmZub1N4a0s3OGozUDFkay03ZjdldG5TQU84c2N6dkNYWDEtT1pXUE14RjFZcFpsSXFTR05MSEVuWkRueUFud0ZLbENucERTY1NZR2NQWlNKNnAyUDJqSGpMQ2tMcmVsLWhZNWZMOGJwcHYxV0dRVWNqNGx0SFhOMDBpcWt3VzFFRmxNUEpxQmlBZ0MxZm1mdVdzMnk1T01TeUY5RmpJOXN1RTBuRnVZc08tbEI3T3c1dGlkYnZlWGl3cWo2aWVDWlRZN3JZQ2xSZ2lH0gG2AkFVX3lxTE11RTdSdlJyOHJhenNTOXpvTjItek12V1NrMUVGaHpMZGdPdlItWDcydmVYSl9zNjB3WDFLdmUycm1MMjNucFotSEU5NnBOXzNkYWxzLVNhVk5qQmZOUEc1YTE4UDQ4UTJ0emtldnBva3RqeEwwWjFFdm1raEFIdmo5V2ZGcHNyTm41bC1RcVBVUjU0aGphS2ptdlBwZUdzMzR1ZXhSaEtCdXRyQm9YQmlfZkl6Rm9rSXlPZ3ZKU2VzM0lva1ZuZ0pTbWc0V2otVjZ0eWJnNEUxdFpWa2hsX2dZR3czdTRLdzA1QmNUYjBSbmRnN0dZRXc5R0pXS3FsN3FaejlDd0hLTjVQRlNSanhsb1VDRldUNnRUYW9EU3NaUGtsM0JSYjRPbExuaXdjZXJxdkhrWWc?oc=5</t>
         </is>
       </c>
       <c r="F67" t="n">
@@ -2441,17 +2441,17 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Police release shock footage of moment man allegedly threw bomb into Invasion Day protest - Sky News Australia</t>
+          <t>Video shows Alhambra police helping Border Patrol, activists say - abc7.com</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Tue, 27 Jan 2026 21:32:18 GMT</t>
+          <t>Tue, 27 Jan 2026 06:55:27 GMT</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisAJBVV95cUxQdTBhOHdlS2ZqU1VQRzhvRm95UkhhVGI3WFh6dDgzRUV2YXp6MnpRNzdxdXBDODhrZ1dicE9QcU1sRWFWWVloUkpYQklJZ2UxdUFVMGxXaFIzOGZQM3NETURNQXpqVmZub1N4a0s3OGozUDFkay03ZjdldG5TQU84c2N6dkNYWDEtT1pXUE14RjFZcFpsSXFTR05MSEVuWkRueUFud0ZLbENucERTY1NZR2NQWlNKNnAyUDJqSGpMQ2tMcmVsLWhZNWZMOGJwcHYxV0dRVWNqNGx0SFhOMDBpcWt3VzFFRmxNUEpxQmlBZ0MxZm1mdVdzMnk1T01TeUY5RmpJOXN1RTBuRnVZc08tbEI3T3c1dGlkYnZlWGl3cWo2aWVDWlRZN3JZQ2xSZ2lH0gG2AkFVX3lxTE11RTdSdlJyOHJhenNTOXpvTjItek12V1NrMUVGaHpMZGdPdlItWDcydmVYSl9zNjB3WDFLdmUycm1MMjNucFotSEU5NnBOXzNkYWxzLVNhVk5qQmZOUEc1YTE4UDQ4UTJ0emtldnBva3RqeEwwWjFFdm1raEFIdmo5V2ZGcHNyTm41bC1RcVBVUjU0aGphS2ptdlBwZUdzMzR1ZXhSaEtCdXRyQm9YQmlfZkl6Rm9rSXlPZ3ZKU2VzM0lva1ZuZ0pTbWc0V2otVjZ0eWJnNEUxdFpWa2hsX2dZR3czdTRLdzA1QmNUYjBSbmRnN0dZRXc5R0pXS3FsN3FaejlDd0hLTjVQRlNSanhsb1VDRldUNnRUYW9EU3NaUGtsM0JSYjRPbExuaXdjZXJxdkhrWWc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxNMnNxVUMtR3d4QXJNa1hJcVdabE9YdGt3VlctdmxlOGJPNklzdUo5OTRXNlVOQm54a3R5Y09uNmdTX3ZUdFZDel8wRElsdWhvRUcxY0stY2Q5UTk3bHlYZTFnYWpmVWxTZnZRdzQ3aGJLdjd5WkpuTGU4R0hQY3R3dEtCU0lGb3g2TEtQMzNqMjg3c2NPb0xSZVJ5RXXSAaIBQVVfeXFMTnUtN3M2N1lLQWgtelBYZmJSNGhrUzJPQ2xQOFRackthT3Ric1U2cFJyNHdrcTVRZXFLY2RnNk9KWDN0eUZZYTdFU0JySnJBNU9xbzhrcWZXdnR5cFBVOG45VUVNdjVoMWZTWVJOcTl1WnZ0bTVjbTZWc0FrVUtDNFJzQ29lS3o1bHIwQ25Jd3NqR3NjRmFETDZnWUFhNUUxbG1B?oc=5</t>
         </is>
       </c>
       <c r="F68" t="n">
@@ -2471,17 +2471,17 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Video shows Alhambra police helping Border Patrol, activists say - abc7.com</t>
+          <t>PPB Monitors Protest Activity in South Waterfront; Four Arrests Made - portland.gov</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Tue, 27 Jan 2026 06:55:27 GMT</t>
+          <t>Sun, 25 Jan 2026 10:21:17 GMT</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxNMnNxVUMtR3d4QXJNa1hJcVdabE9YdGt3VlctdmxlOGJPNklzdUo5OTRXNlVOQm54a3R5Y09uNmdTX3ZUdFZDel8wRElsdWhvRUcxY0stY2Q5UTk3bHlYZTFnYWpmVWxTZnZRdzQ3aGJLdjd5WkpuTGU4R0hQY3R3dEtCU0lGb3g2TEtQMzNqMjg3c2NPb0xSZVJ5RXXSAaIBQVVfeXFMTnUtN3M2N1lLQWgtelBYZmJSNGhrUzJPQ2xQOFRackthT3Ric1U2cFJyNHdrcTVRZXFLY2RnNk9KWDN0eUZZYTdFU0JySnJBNU9xbzhrcWZXdnR5cFBVOG45VUVNdjVoMWZTWVJOcTl1WnZ0bTVjbTZWc0FrVUtDNFJzQ29lS3o1bHIwQ25Jd3NqR3NjRmFETDZnWUFhNUUxbG1B?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxQZ0xmVkpILXRXUlZfczJhRmxaTEZpaVFTanpodkVsWTQzMHlhY0hoWWlmVnZ2S2JpTTNZcGNjSl9zaHFrRnpxeXNjNk5LZGpQOFg3NU1yWnBGVnBZLWgtOGhLUXdpbjJuWll6ZTh5TDllT1VfS0lBRkV6aXJHVl8yNWJiTW9jSS1mSk1JXzRLS2JINWVjRXBURWRmWGhGSWZYTHVxNFMxbFhmV3UtZ2ZWZg?oc=5</t>
         </is>
       </c>
       <c r="F69" t="n">
@@ -2491,27 +2491,27 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Protest</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally)</t>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>PPB Monitors Protest Activity in South Waterfront; Four Arrests Made - portland.gov</t>
+          <t>Free AI training for all, as government and industry programme expands to provide 10 million workers with key AI skills by 2030 - GOV.UK</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Sun, 25 Jan 2026 10:21:17 GMT</t>
+          <t>Wed, 28 Jan 2026 00:02:21 GMT</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxQZ0xmVkpILXRXUlZfczJhRmxaTEZpaVFTanpodkVsWTQzMHlhY0hoWWlmVnZ2S2JpTTNZcGNjSl9zaHFrRnpxeXNjNk5LZGpQOFg3NU1yWnBGVnBZLWgtOGhLUXdpbjJuWll6ZTh5TDllT1VfS0lBRkV6aXJHVl8yNWJiTW9jSS1mSk1JXzRLS2JINWVjRXBURWRmWGhGSWZYTHVxNFMxbFhmV3UtZ2ZWZg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi8wFBVV95cUxPRFUxYjB1cTFReVkxRmRzYkV5WVdfWnVtNVBkUE1QWGNkczBmOFItcUZVYW1FRm9XSFBpWmRsTk01N2dxNzJsdUFRWjJKZnpUeUZPY3J2V2lwN19WeVVUOHFWTm0yNUZGVG4zX3VZM0FOZTRleU5HNFQzYkE0QmN6WFh3bUVhdnJ2UWRHSTJ4RjZpTFJ1bVh6VHJ1dFdHRzhCT2pjeWJCWi11VTZ2bUtIM20yYlNZQ3ppUUNxSHZCMW9rSmtYUmhJRktmSHB3UkpfVzN6dFhEVUNuM2ZndmE0Wk9NdEZDLTVKOGRNUllZTmNjYUU?oc=5</t>
         </is>
       </c>
       <c r="F70" t="n">
@@ -2531,17 +2531,17 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Free AI training for all, as government and industry programme expands to provide 10 million workers with key AI skills by 2030 - GOV.UK</t>
+          <t>NHS AI and robot pilot to help detect lung cancer sooner - Home | Digital Health</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Wed, 28 Jan 2026 00:02:21 GMT</t>
+          <t>Tue, 27 Jan 2026 13:40:28 GMT</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi8wFBVV95cUxPRFUxYjB1cTFReVkxRmRzYkV5WVdfWnVtNVBkUE1QWGNkczBmOFItcUZVYW1FRm9XSFBpWmRsTk01N2dxNzJsdUFRWjJKZnpUeUZPY3J2V2lwN19WeVVUOHFWTm0yNUZGVG4zX3VZM0FOZTRleU5HNFQzYkE0QmN6WFh3bUVhdnJ2UWRHSTJ4RjZpTFJ1bVh6VHJ1dFdHRzhCT2pjeWJCWi11VTZ2bUtIM20yYlNZQ3ppUUNxSHZCMW9rSmtYUmhJRktmSHB3UkpfVzN6dFhEVUNuM2ZndmE0Wk9NdEZDLTVKOGRNUllZTmNjYUU?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxOYklzVWtjWUhnZHNNcldpcHd0LVN1THdGU1ktNWZkZEFpb0NIQ2xPdXdqZXhuWTdoVkhaOV9LUEFZUnJHOGtNWDNpaHpvanNNdVNmWFZOa25iV25nTEEwa25CNnJOM09EREp4bXZQRENEU2pHaF9iRGZNSjRydEhhWHUyWWtsTU1hc0EzNlpSSzhYZmptLTZqQklSZw?oc=5</t>
         </is>
       </c>
       <c r="F71" t="n">
@@ -2561,17 +2561,17 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>NHS AI and robot pilot to help detect lung cancer sooner - Home | Digital Health</t>
+          <t>AI and investigations taking the opportunities and meeting the challenges - A&amp;O Shearman</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Tue, 27 Jan 2026 13:40:28 GMT</t>
+          <t>Tue, 27 Jan 2026 10:02:02 GMT</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxOYklzVWtjWUhnZHNNcldpcHd0LVN1THdGU1ktNWZkZEFpb0NIQ2xPdXdqZXhuWTdoVkhaOV9LUEFZUnJHOGtNWDNpaHpvanNNdVNmWFZOa25iV25nTEEwa25CNnJOM09EREp4bXZQRENEU2pHaF9iRGZNSjRydEhhWHUyWWtsTU1hc0EzNlpSSzhYZmptLTZqQklSZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi-wFBVV95cUxQV01mMkFKdzJSb0wwaHFTQXgtTDkzQ2ZjSm5xX2pXZDlVbk1hMG5maXFlMnpuWVRsRHNjSVppZFUxLUl5ZGFQcHJYdXJHZHdqR1VFTzRQNG9Sd1UwNTc4QjB3d0ppay1fU1NtM3hUVE84d0IyM2VzZ1NlMWVBY0s3eWpvbHVmQU1aV3RSbi1uNG5ITXZ5VGtfS2UtNU05QTFfV2pwaEFOZ0pfem9FWWxuaGZScWhicldNZFNkQmFOWVAxWGtVdV9fYVNadzBuRkR1bzZmanNDUXhRcVl5QUVTWklzenRQa00wMnVvalF5dmJMYzU4V3ZFNS11bw?oc=5</t>
         </is>
       </c>
       <c r="F72" t="n">
@@ -2591,17 +2591,17 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>AI and investigations taking the opportunities and meeting the challenges - A&amp;O Shearman</t>
+          <t>AI centre for policing will help catch more criminals quicker - National Police Chiefs' Council (NPCC)</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Tue, 27 Jan 2026 10:02:02 GMT</t>
+          <t>Tue, 27 Jan 2026 14:55:14 GMT</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi-wFBVV95cUxQV01mMkFKdzJSb0wwaHFTQXgtTDkzQ2ZjSm5xX2pXZDlVbk1hMG5maXFlMnpuWVRsRHNjSVppZFUxLUl5ZGFQcHJYdXJHZHdqR1VFTzRQNG9Sd1UwNTc4QjB3d0ppay1fU1NtM3hUVE84d0IyM2VzZ1NlMWVBY0s3eWpvbHVmQU1aV3RSbi1uNG5ITXZ5VGtfS2UtNU05QTFfV2pwaEFOZ0pfem9FWWxuaGZScWhicldNZFNkQmFOWVAxWGtVdV9fYVNadzBuRkR1bzZmanNDUXhRcVl5QUVTWklzenRQa00wMnVvalF5dmJMYzU4V3ZFNS11bw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxOLVJqMGFTck41UW00U3YwbjFucTA5bUlKUHFFZzBUOHlPOHlvYzI0VmhwRkxXUFlHcU9CSUh5U2FRcXNyVjRrcUxod3U3M2RxZ2prQkt2ZEdsSjNaZ0xacm9WXy1BLXptbGFFejg0NzVqeElMMklyRUJZSmphU2RtTlA3WHNiWFVXREdCbHRUdFlRMkRBcmg0T0dPSm9sN3h3ZERjUF8zbGRvTkV6X01ZOQ?oc=5</t>
         </is>
       </c>
       <c r="F73" t="n">
@@ -2621,17 +2621,17 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>AI centre for policing will help catch more criminals quicker - National Police Chiefs' Council (NPCC)</t>
+          <t>AI and the media revolution: A look ahead to 2026 - IBC.org</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Tue, 27 Jan 2026 14:55:14 GMT</t>
+          <t>Tue, 27 Jan 2026 14:50:52 GMT</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxOLVJqMGFTck41UW00U3YwbjFucTA5bUlKUHFFZzBUOHlPOHlvYzI0VmhwRkxXUFlHcU9CSUh5U2FRcXNyVjRrcUxod3U3M2RxZ2prQkt2ZEdsSjNaZ0xacm9WXy1BLXptbGFFejg0NzVqeElMMklyRUJZSmphU2RtTlA3WHNiWFVXREdCbHRUdFlRMkRBcmg0T0dPSm9sN3h3ZERjUF8zbGRvTkV6X01ZOQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxQcXRkWnItcGtfT0I0aVBLcjVYQWQ4OWJtcThfb3VQQUhIZm5Dbi1nNFBTWEZCemx1ejBnM3p5b3JsbEJYcndWZ3Vib2ZWNkRKdUc5X0plWjQyU1hrZkF3eUEyc2RySWdBMlpDMFcwUmc5MmI5eHpMdlIycjFOZnVEX1oyOEhsYkM0MnU2UXVEUmIxZVBhV2taYnY0MExOZGNOOVh0RGRhSFhUME0?oc=5</t>
         </is>
       </c>
       <c r="F74" t="n">
@@ -2651,17 +2651,17 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>AI and the media revolution: A look ahead to 2026 - IBC.org</t>
+          <t>UK Insurers Prioritise AI and Third-Party Risk in 2026 - Claims Media</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Tue, 27 Jan 2026 14:50:52 GMT</t>
+          <t>Tue, 27 Jan 2026 15:18:07 GMT</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxQcXRkWnItcGtfT0I0aVBLcjVYQWQ4OWJtcThfb3VQQUhIZm5Dbi1nNFBTWEZCemx1ejBnM3p5b3JsbEJYcndWZ3Vib2ZWNkRKdUc5X0plWjQyU1hrZkF3eUEyc2RySWdBMlpDMFcwUmc5MmI5eHpMdlIycjFOZnVEX1oyOEhsYkM0MnU2UXVEUmIxZVBhV2taYnY0MExOZGNOOVh0RGRhSFhUME0?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxOTnNBR1Y2eTNTdUxlSXFjdnp3eWEyZHo5dDdXaWN6LVdSNnUxUUdLOGJ3N2NCekc0TVJ4TmR1Y0VreHBiYlpDM2lxRWQtNW9ER3Y4RVhNTUlvUWp3NUxySFN3Y2FBVWJSOEFKaU1kTnF4MEFOOE9MampLOGlhRU0yWU41aWxuS2I3TmY3a1dCN3A?oc=5</t>
         </is>
       </c>
       <c r="F75" t="n">
@@ -2681,17 +2681,17 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>UK Insurers Prioritise AI and Third-Party Risk in 2026 - Claims Media</t>
+          <t>Aon targets faster placement decisions with AI and analytics as renewal pace accelerates - theinsurer.com</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Tue, 27 Jan 2026 15:18:07 GMT</t>
+          <t>Tue, 27 Jan 2026 21:06:07 GMT</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxOTnNBR1Y2eTNTdUxlSXFjdnp3eWEyZHo5dDdXaWN6LVdSNnUxUUdLOGJ3N2NCekc0TVJ4TmR1Y0VreHBiYlpDM2lxRWQtNW9ER3Y4RVhNTUlvUWp3NUxySFN3Y2FBVWJSOEFKaU1kTnF4MEFOOE9MampLOGlhRU0yWU41aWxuS2I3TmY3a1dCN3A?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixwFBVV95cUxNSTdHZnZseDZvSWxRNHBLeW5kUjJKN1BmLVRmTTRJQl9yancyZWVuYVE5eFhoV2JDLWs4OFJ1ZlRPRDBJQzJHRHByMEgwWUhKbWpKUFh2OGFIVEY5QU9PeFVTczZ5WFpLd01XUzNaaVROR3F2U1cyclBBWm41clJfemloSUdSLWhhN2RsQlFOLTZRTXlMVDI2aHkxVGk4STNkY3VyeDZPcWV5M3pCM3dja2dYMGlZRTBMaDVLZ2RBc0lRNFJCQ2Z3?oc=5</t>
         </is>
       </c>
       <c r="F76" t="n">
@@ -2711,17 +2711,17 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Aon targets faster placement decisions with AI and analytics as renewal pace accelerates - theinsurer.com</t>
+          <t>How China Caught Up on AI—and May Now Win the Future - Time Magazine</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Tue, 27 Jan 2026 21:06:07 GMT</t>
+          <t>Tue, 27 Jan 2026 16:16:05 GMT</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixwFBVV95cUxNSTdHZnZseDZvSWxRNHBLeW5kUjJKN1BmLVRmTTRJQl9yancyZWVuYVE5eFhoV2JDLWs4OFJ1ZlRPRDBJQzJHRHByMEgwWUhKbWpKUFh2OGFIVEY5QU9PeFVTczZ5WFpLd01XUzNaaVROR3F2U1cyclBBWm41clJfemloSUdSLWhhN2RsQlFOLTZRTXlMVDI2aHkxVGk4STNkY3VyeDZPcWV5M3pCM3dja2dYMGlZRTBMaDVLZ2RBc0lRNFJCQ2Z3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiVEFVX3lxTFB4WVZSc1oxYS1zbjNEal9pNmlqTE9Bb3dlelU5bHI2Z1JQdlZUS1h4My1nemdvR0NpY3dpdHE0ZndTRll3WXNHVFh6UFZ5eW9TRHlXRA?oc=5</t>
         </is>
       </c>
       <c r="F77" t="n">
@@ -2741,17 +2741,17 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>How China Caught Up on AI—and May Now Win the Future - Time Magazine</t>
+          <t>For €170 million: Vienna gives AI and life sciences a new home - European Biotechnology Magazine</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Tue, 27 Jan 2026 16:16:05 GMT</t>
+          <t>Tue, 27 Jan 2026 14:10:22 GMT</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiVEFVX3lxTFB4WVZSc1oxYS1zbjNEal9pNmlqTE9Bb3dlelU5bHI2Z1JQdlZUS1h4My1nemdvR0NpY3dpdHE0ZndTRll3WXNHVFh6UFZ5eW9TRHlXRA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxQR0Y4RlBmVGtCaHFtYkE1NUdjSi1MSDFRcXcxZ1FWZmdWcGxJYzlNczZLUDEtZU9IY2xva0RJUXdnVlA5RVdyRDBJa2pteWk5NGRQa2xxX2tYYnFycHVxLWZYUEhWdmZidHRMTlRJVmpHSTF2aGcySHhqWW5JTjhiampQSFBTaGVVY1Uwdlh1NndHVDIzelRFTUt0VnE5RG83aFAtYmVTVjdwNk9rdkE?oc=5</t>
         </is>
       </c>
       <c r="F78" t="n">
@@ -2771,17 +2771,17 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>For €170 million: Vienna gives AI and life sciences a new home - European Biotechnology Magazine</t>
+          <t>Industry reacts to FCA’s AI review into retail financial services - Money Marketing</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Tue, 27 Jan 2026 14:10:22 GMT</t>
+          <t>Tue, 27 Jan 2026 16:46:23 GMT</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxQR0Y4RlBmVGtCaHFtYkE1NUdjSi1MSDFRcXcxZ1FWZmdWcGxJYzlNczZLUDEtZU9IY2xva0RJUXdnVlA5RVdyRDBJa2pteWk5NGRQa2xxX2tYYnFycHVxLWZYUEhWdmZidHRMTlRJVmpHSTF2aGcySHhqWW5JTjhiampQSFBTaGVVY1Uwdlh1NndHVDIzelRFTUt0VnE5RG83aFAtYmVTVjdwNk9rdkE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxQWmV0aWJFcUw3OWREd3BHU1RLNkVNWkZrTjhKWHNKN2Z2R2pUd3J6TVg4d1hFMjVuaUM2dTVzUE9CbjAtenJHNE1uOTlHcDEtZ1E4MFE4ZklJazJ1cWNseTdIN2l6NnJ6VnVORHhESURqV3VkbkRKS0pVUjFtS3JBZG8zeENVYUhMdFVFaWlISUpQRUUzYTNoeFdQUGIxT1BrQVlSQjVB?oc=5</t>
         </is>
       </c>
       <c r="F79" t="n">
@@ -2801,17 +2801,17 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Industry reacts to FCA’s AI review into retail financial services - Money Marketing</t>
+          <t>Microsoft Pledged to Save Water. In the A.I. Era, It Expects Water Use to Soar. - The New York Times</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Tue, 27 Jan 2026 16:46:23 GMT</t>
+          <t>Tue, 27 Jan 2026 23:30:19 GMT</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxQWmV0aWJFcUw3OWREd3BHU1RLNkVNWkZrTjhKWHNKN2Z2R2pUd3J6TVg4d1hFMjVuaUM2dTVzUE9CbjAtenJHNE1uOTlHcDEtZ1E4MFE4ZklJazJ1cWNseTdIN2l6NnJ6VnVORHhESURqV3VkbkRKS0pVUjFtS3JBZG8zeENVYUhMdFVFaWlISUpQRUUzYTNoeFdQUGIxT1BrQVlSQjVB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiigFBVV95cUxPa0ItMU1VNTFqUUhlSHJMd3FFR01wVGsxdVEySm55WEN1djJDUTgyMnVDNEhTRG1RbXhJOExuWm45SFpieDcxUVBzZC1TallVWjhyajFCeFYxT3QxN3FOYUxJdk1KRHJYcTZ4UU5kcWNNcUtjMHdVS0pwQVUzbF9XWWZvNTlPV3RfMVE?oc=5</t>
         </is>
       </c>
       <c r="F80" t="n">
@@ -2831,17 +2831,17 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Microsoft Pledged to Save Water. In the A.I. Era, It Expects Water Use to Soar. - The New York Times</t>
+          <t>Study suggests AI is having a greater impact on UK jobs than in other major economies - New Electronics</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Tue, 27 Jan 2026 23:30:19 GMT</t>
+          <t>Tue, 27 Jan 2026 22:15:54 GMT</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiigFBVV95cUxPa0ItMU1VNTFqUUhlSHJMd3FFR01wVGsxdVEySm55WEN1djJDUTgyMnVDNEhTRG1RbXhJOExuWm45SFpieDcxUVBzZC1TallVWjhyajFCeFYxT3QxN3FOYUxJdk1KRHJYcTZ4UU5kcWNNcUtjMHdVS0pwQVUzbF9XWWZvNTlPV3RfMVE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizAFBVV95cUxOWDk1Znp3Mk0wTVBOaGMyTzdBSHZWTDBLSXJ5U19VVHVsUFFxaUcyeXUyRjFqS29XR3RuVUdMQ3JiUy1jc292THVMenVsaDVaZ3JRd1V2enJmcVYzXzJCbnpxbFdmYlpUd0ZaMVM2bm0xQm9haVQxbWxscUxUd0dYNjNBLXk1MlBIdmhUR09rZnBidnZZc2MwV3JxTG56MjBDS0tGd0hXQ29fdUw2MzBkQjJJUkZUdTZzZ0FPbjJJY1hOX2Rncm00UVFUOHg?oc=5</t>
         </is>
       </c>
       <c r="F81" t="n">
@@ -2861,17 +2861,17 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Study suggests AI is having a greater impact on UK jobs than in other major economies - New Electronics</t>
+          <t>Crew Studies Robotics and Virtual Reality Advancing Space Tech - NASA (.gov)</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Tue, 27 Jan 2026 22:15:54 GMT</t>
+          <t>Tue, 27 Jan 2026 19:20:59 GMT</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizAFBVV95cUxOWDk1Znp3Mk0wTVBOaGMyTzdBSHZWTDBLSXJ5U19VVHVsUFFxaUcyeXUyRjFqS29XR3RuVUdMQ3JiUy1jc292THVMenVsaDVaZ3JRd1V2enJmcVYzXzJCbnpxbFdmYlpUd0ZaMVM2bm0xQm9haVQxbWxscUxUd0dYNjNBLXk1MlBIdmhUR09rZnBidnZZc2MwV3JxTG56MjBDS0tGd0hXQ29fdUw2MzBkQjJJUkZUdTZzZ0FPbjJJY1hOX2Rncm00UVFUOHg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxNUGxKN3VXZU5ualpMLUVWU1FzRjE5TVlaV3VjUnlYVFZib1JVeXhVY2ttNnFkdkhfWUpINW15enR6M1BlRFpCSk1BX183VFJ5VFlHQVV5R3RvZTA2cjl1ZVI0dTFIZzAydW1rRFA0WUh3M1ZsQW90RkFmTGlmWTN5T1BTOXlMZ21OaVI1NmgtUnVPWDhiYVFSMXZRVTlleEpRbHZxTklCZXJQMWFpQnNTVlJqQmI?oc=5</t>
         </is>
       </c>
       <c r="F82" t="n">
@@ -2891,17 +2891,17 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Crew Studies Robotics and Virtual Reality Advancing Space Tech - NASA (.gov)</t>
+          <t>Technology for policing: the BlueprintCo ACE supplier story - GOV.UK</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Tue, 27 Jan 2026 19:20:59 GMT</t>
+          <t>Tue, 27 Jan 2026 12:11:15 GMT</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxNUGxKN3VXZU5ualpMLUVWU1FzRjE5TVlaV3VjUnlYVFZib1JVeXhVY2ttNnFkdkhfWUpINW15enR6M1BlRFpCSk1BX183VFJ5VFlHQVV5R3RvZTA2cjl1ZVI0dTFIZzAydW1rRFA0WUh3M1ZsQW90RkFmTGlmWTN5T1BTOXlMZ21OaVI1NmgtUnVPWDhiYVFSMXZRVTlleEpRbHZxTklCZXJQMWFpQnNTVlJqQmI?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxQNngwdS11ZEItcHBVYWFXNzF6SUJxdDdBbi13em10RUJrQjNnYzNoQWpkNTNKVEhsdXFqN2NxT1h6UHZncFY2STZWbkxwNjBJU3hoVGhWelQ3ZTI1cGpNZHM2RUYtVHRHZlB1YVk4bXRpMjRxLWRXSF9EaUt0TTJOWUw0aVc3TG0wZ2cwZFhIWDNFUHdRQWdUbmJMMFZKaFlscWJr?oc=5</t>
         </is>
       </c>
       <c r="F83" t="n">
@@ -2921,17 +2921,17 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Technology for policing: the BlueprintCo ACE supplier story - GOV.UK</t>
+          <t>SEALSQ Explores Post-Quantum Cryptography for Physical AI Systems and Robotics at Davos - The Quantum Insider</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Tue, 27 Jan 2026 12:11:15 GMT</t>
+          <t>Tue, 27 Jan 2026 13:33:09 GMT</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxQNngwdS11ZEItcHBVYWFXNzF6SUJxdDdBbi13em10RUJrQjNnYzNoQWpkNTNKVEhsdXFqN2NxT1h6UHZncFY2STZWbkxwNjBJU3hoVGhWelQ3ZTI1cGpNZHM2RUYtVHRHZlB1YVk4bXRpMjRxLWRXSF9EaUt0TTJOWUw0aVc3TG0wZ2cwZFhIWDNFUHdRQWdUbmJMMFZKaFlscWJr?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxPWHVuSjk3WTBnbjVQVkVJM2tfUEl6OGxyREJ0eTI4WF9YNTdjeF8xRDAzaWk0a3VEbk8zaXJPVldqUTQ1dGZGUlVEWEg4YzZhYjl3eERtTVFwMExkNUNYSFpqN1FjcjVBTWljNDZYRlo1N3dtcEhVTTFXTG0yZHFkUll0V0RVRExITGVfZ3RjT0FaN1VULV9yN3NjYw?oc=5</t>
         </is>
       </c>
       <c r="F84" t="n">
@@ -2951,17 +2951,17 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>SEALSQ Explores Post-Quantum Cryptography for Physical AI Systems and Robotics at Davos - The Quantum Insider</t>
+          <t>Urban Health Research Conference focuses on how AI and big data shape health care - today.wayne.edu</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Tue, 27 Jan 2026 13:33:09 GMT</t>
+          <t>Tue, 27 Jan 2026 15:48:42 GMT</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxPWHVuSjk3WTBnbjVQVkVJM2tfUEl6OGxyREJ0eTI4WF9YNTdjeF8xRDAzaWk0a3VEbk8zaXJPVldqUTQ1dGZGUlVEWEg4YzZhYjl3eERtTVFwMExkNUNYSFpqN1FjcjVBTWljNDZYRlo1N3dtcEhVTTFXTG0yZHFkUll0V0RVRExITGVfZ3RjT0FaN1VULV9yN3NjYw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0gFBVV95cUxPY2cyZDhmdkI5b05qUDMwT3pjeGNpT0JDOFlKR0FWalVnaXpuTmFTNzBsVlFBSFVTblRXRUpRbjBVeFUwbkU2eGNVbGhtb3ZiVzFQR25DWWdLTnpScThOZU41NzhzdlhraWlHVTE3cVlFU1ZjaG93MkcycjlaVmJLSFBnNU9XSy1HdkFHVmljMHJLT2xqYmVhU2RNWU56am81YmxIOUIyUHVFSkNaWC0tYUYyYW1uWHF6WExxMUtSci1RTURNcDB3VjkyY2VMZUVnTEE?oc=5</t>
         </is>
       </c>
       <c r="F85" t="n">
@@ -2981,17 +2981,17 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Urban Health Research Conference focuses on how AI and big data shape health care - today.wayne.edu</t>
+          <t>AI and digital finance raise financial stability implications - BIS - Finextra Research</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Tue, 27 Jan 2026 15:48:42 GMT</t>
+          <t>Tue, 27 Jan 2026 00:01:00 GMT</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0gFBVV95cUxPY2cyZDhmdkI5b05qUDMwT3pjeGNpT0JDOFlKR0FWalVnaXpuTmFTNzBsVlFBSFVTblRXRUpRbjBVeFUwbkU2eGNVbGhtb3ZiVzFQR25DWWdLTnpScThOZU41NzhzdlhraWlHVTE3cVlFU1ZjaG93MkcycjlaVmJLSFBnNU9XSy1HdkFHVmljMHJLT2xqYmVhU2RNWU56am81YmxIOUIyUHVFSkNaWC0tYUYyYW1uWHF6WExxMUtSci1RTURNcDB3VjkyY2VMZUVnTEE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxQOW9lT0h5a3FJR1k1V0ZDZlk0OGkwR3VJbi1zWmRlMjJFLVNVS3ZuNXRCY3FRUWFwUUh1a0g3aWhmMmRTaTgyX3E0bmhjUjRXQzVnZEE5cjRwUFNvNEtqQ1NjYkRrcF9tcFJTMWxZR0hHMjlvMUR3OTVjb0dmc2hHYWdpQ0ZxNXBQVE1JdF9qdVZNNjhQUS1sMEwtVFpEenBhY01Wb0JYQnhyUTJqMzhz?oc=5</t>
         </is>
       </c>
       <c r="F86" t="n">
@@ -3011,17 +3011,17 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>AI and digital finance raise financial stability implications - BIS - Finextra Research</t>
+          <t>AI and experimental convergence: a synergistic pathway to JAK2 inhibitor discovery - Nature</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Tue, 27 Jan 2026 00:01:00 GMT</t>
+          <t>Tue, 27 Jan 2026 12:31:25 GMT</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxQOW9lT0h5a3FJR1k1V0ZDZlk0OGkwR3VJbi1zWmRlMjJFLVNVS3ZuNXRCY3FRUWFwUUh1a0g3aWhmMmRTaTgyX3E0bmhjUjRXQzVnZEE5cjRwUFNvNEtqQ1NjYkRrcF9tcFJTMWxZR0hHMjlvMUR3OTVjb0dmc2hHYWdpQ0ZxNXBQVE1JdF9qdVZNNjhQUS1sMEwtVFpEenBhY01Wb0JYQnhyUTJqMzhz?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiX0FVX3lxTE00MlJDdEZQRzlxWTBZbEx4VFV4UVdLNk53Q1pseGJORmhiR0RHajh6WUt6WElNQUdQNDlnUGIwME9STnZyWndFTmNQM0pPbUZNLW4xYnJmSEpjQVZaODZV?oc=5</t>
         </is>
       </c>
       <c r="F87" t="n">
@@ -3041,17 +3041,17 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>AI and experimental convergence: a synergistic pathway to JAK2 inhibitor discovery - Nature</t>
+          <t>Google Cloud brings more AI tech to Formula E in major expansion - SportsPro</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Tue, 27 Jan 2026 12:31:25 GMT</t>
+          <t>Tue, 27 Jan 2026 11:27:13 GMT</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiX0FVX3lxTE00MlJDdEZQRzlxWTBZbEx4VFV4UVdLNk53Q1pseGJORmhiR0RHajh6WUt6WElNQUdQNDlnUGIwME9STnZyWndFTmNQM0pPbUZNLW4xYnJmSEpjQVZaODZV?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxQby1KVG9PTVVCeHJ5SFllRThBMlcxQWpCbEdIdFdSOVJKYlVZQ09rX0MxZU9tRWVlUHJ2NjB2VlMxTG92YXQ0SDZ4TXFMV3BwRV85TTYtMzlMcS1jRFZuWFNzZkMteDRWMmFCSUZvWXlLNmRGVVpUZ2Z3Zzc1cEo4TGNocTM5S1h5bGlBSXc2cDlnRHluR1FzU1NmUGNnOWtZMHc2LTRlSQ?oc=5</t>
         </is>
       </c>
       <c r="F88" t="n">
@@ -3071,17 +3071,17 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Google Cloud brings more AI tech to Formula E in major expansion - SportsPro</t>
+          <t>AI will not replace human business relationships, says recruiter - The Times</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Tue, 27 Jan 2026 11:27:13 GMT</t>
+          <t>Tue, 27 Jan 2026 17:39:07 GMT</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxQby1KVG9PTVVCeHJ5SFllRThBMlcxQWpCbEdIdFdSOVJKYlVZQ09rX0MxZU9tRWVlUHJ2NjB2VlMxTG92YXQ0SDZ4TXFMV3BwRV85TTYtMzlMcS1jRFZuWFNzZkMteDRWMmFCSUZvWXlLNmRGVVpUZ2Z3Zzc1cEo4TGNocTM5S1h5bGlBSXc2cDlnRHluR1FzU1NmUGNnOWtZMHc2LTRlSQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi1gNBVV95cUxPdXpGcDhrNFdYdjE1VjlGRUpLbXFVSkZhclBBMzRxTVJ6R0lQLTNfekFmNkhPRDYtSXFqV29pcmloVVBZUVQxb0ZvMGduaWdRd0lHYzRrakFEbzBKeTBkb0dYMFRILUc3LWd2Y0N6UmhzMFNuOWk0VU8zMzRmWEFwS0k5UTBOMWFtWXFCelZtUEF3LUFKUFktSWhfSUVmOW5qOVd6S2NmeFpuSmNRUEZBdlF3am03LU1WNndVcm8wcmxsVGhsSlhVQWFIWndWWUxBWUZDMnptRGNmUHBRVnpvTWVYRExFenVscmlLbUpLb01oa2tnYkdDalhUalh1OFZlTUF1LTFpVU1UVUNNeDJZQUNleWt2WWttNHJuanNhTkdwT1JXX1RmV2s2Yl9nSTZiQTN5WmlqSXZEQ3NmM1Z4V2pQbHp1RS1KbGtIVVkwWlFvb0RaVVJGbzVrcnFNZ05ucW1oUlRkb0pyX1dGbVFHeVJSSUx4Uk1zbTZ1aWlWLW80MVlpVUU4eVZReF9OY05ET2VZUE1LMGxqX0VQY1VDX1NhRXdvaFV4amQxRTVtTUprdnFmSWpmMDkzOFdFVlFBNjctNFhGa2s4NVZYV1lMNDJfbktQUQ?oc=5</t>
         </is>
       </c>
       <c r="F89" t="n">
@@ -3101,17 +3101,17 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>AI will not replace human business relationships, says recruiter - The Times</t>
+          <t>AfricAI-Micropolis Deal Paves Way for Sovereign AI and Robotics in Africa - TechAfrica News</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Tue, 27 Jan 2026 17:39:07 GMT</t>
+          <t>Tue, 27 Jan 2026 11:47:14 GMT</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi1gNBVV95cUxPdXpGcDhrNFdYdjE1VjlGRUpLbXFVSkZhclBBMzRxTVJ6R0lQLTNfekFmNkhPRDYtSXFqV29pcmloVVBZUVQxb0ZvMGduaWdRd0lHYzRrakFEbzBKeTBkb0dYMFRILUc3LWd2Y0N6UmhzMFNuOWk0VU8zMzRmWEFwS0k5UTBOMWFtWXFCelZtUEF3LUFKUFktSWhfSUVmOW5qOVd6S2NmeFpuSmNRUEZBdlF3am03LU1WNndVcm8wcmxsVGhsSlhVQWFIWndWWUxBWUZDMnptRGNmUHBRVnpvTWVYRExFenVscmlLbUpLb01oa2tnYkdDalhUalh1OFZlTUF1LTFpVU1UVUNNeDJZQUNleWt2WWttNHJuanNhTkdwT1JXX1RmV2s2Yl9nSTZiQTN5WmlqSXZEQ3NmM1Z4V2pQbHp1RS1KbGtIVVkwWlFvb0RaVVJGbzVrcnFNZ05ucW1oUlRkb0pyX1dGbVFHeVJSSUx4Uk1zbTZ1aWlWLW80MVlpVUU4eVZReF9OY05ET2VZUE1LMGxqX0VQY1VDX1NhRXdvaFV4amQxRTVtTUprdnFmSWpmMDkzOFdFVlFBNjctNFhGa2s4NVZYV1lMNDJfbktQUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxPZ29OdnZhNkRDU1NJeERrNE4zQUN0dXFxTzJDZFZZTWN2LTVzMENsdUtpdGk0SU80UkwzXzRfVWZXYS1adUpma1ZleHhONnV4b1VvUDRmcmM2WkVjLVp1dG1teTMtcGZydnp0YmNOTHotMnBLZDhmbnZoNFZKMGhvbjZ1WHRQVzZyQWh4YlNaaTFSS0Q3N1RLb0JzTmlmS1ZPTDBLWGtpalZWU19WQ0tnM0h3?oc=5</t>
         </is>
       </c>
       <c r="F90" t="n">
@@ -3131,17 +3131,17 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>AfricAI-Micropolis Deal Paves Way for Sovereign AI and Robotics in Africa - TechAfrica News</t>
+          <t>KPMG Global tech report 2026 - KPMG</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Tue, 27 Jan 2026 11:47:14 GMT</t>
+          <t>Tue, 27 Jan 2026 13:25:05 GMT</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxPZ29OdnZhNkRDU1NJeERrNE4zQUN0dXFxTzJDZFZZTWN2LTVzMENsdUtpdGk0SU80UkwzXzRfVWZXYS1adUpma1ZleHhONnV4b1VvUDRmcmM2WkVjLVp1dG1teTMtcGZydnp0YmNOTHotMnBLZDhmbnZoNFZKMGhvbjZ1WHRQVzZyQWh4YlNaaTFSS0Q3N1RLb0JzTmlmS1ZPTDBLWGtpalZWU19WQ0tnM0h3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMie0FVX3lxTE9STXN3YTRkVnNhc1VQdWhrLUl6SHVkSFZUSWtJTDR2Wlp0bzVONUpzY2lGQlFTRkdFQy1EbXpJZUpNazJCelVnNktzeE9oRlFJaHlRTEVUb1QxaDRsTWx5UXFIbjRoNVBtSGt0cTFGcnF4ekNjY3B5ZGJkZw?oc=5</t>
         </is>
       </c>
       <c r="F91" t="n">
@@ -3161,17 +3161,17 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>KPMG Global tech report 2026 - KPMG</t>
+          <t>Beyond Formatting: How Technology and AI Are Transforming Legal Word Processing - JD Supra</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Tue, 27 Jan 2026 13:25:05 GMT</t>
+          <t>Tue, 27 Jan 2026 20:28:04 GMT</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMie0FVX3lxTE9STXN3YTRkVnNhc1VQdWhrLUl6SHVkSFZUSWtJTDR2Wlp0bzVONUpzY2lGQlFTRkdFQy1EbXpJZUpNazJCelVnNktzeE9oRlFJaHlRTEVUb1QxaDRsTWx5UXFIbjRoNVBtSGt0cTFGcnF4ekNjY3B5ZGJkZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiigFBVV95cUxPLUZWX29CY1lpYXlNMTZvbTdnRklUOEZuYzNlMXgxdi1wckU5RnZYRUxFRWR3Q2Z6TjZLTXB3N2hLUERiSC15R0E3eEZzMkdlb3RXMzNvYUhsZWoyU1NkOVlsN01FekN1WVN6WjlUTmNNTTBZdUtDakRZb3JtT3VwQXVOUzZZU29PTHc?oc=5</t>
         </is>
       </c>
       <c r="F92" t="n">
@@ -3191,17 +3191,17 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Beyond Formatting: How Technology and AI Are Transforming Legal Word Processing - JD Supra</t>
+          <t>SALUS Controls launches intelligent AI-driven energy saving feature SALUS Sense - Installer Online</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Tue, 27 Jan 2026 20:28:04 GMT</t>
+          <t>Tue, 27 Jan 2026 16:45:19 GMT</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiigFBVV95cUxPLUZWX29CY1lpYXlNMTZvbTdnRklUOEZuYzNlMXgxdi1wckU5RnZYRUxFRWR3Q2Z6TjZLTXB3N2hLUERiSC15R0E3eEZzMkdlb3RXMzNvYUhsZWoyU1NkOVlsN01FekN1WVN6WjlUTmNNTTBZdUtDakRZb3JtT3VwQXVOUzZZU29PTHc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxPVUdSMnB0LVFKaW96RDM5OGd0NWFMNUFuOUk0eTU5c0NQSEJiVW1hWGJsSzJDbkNBX3h5VmlPdUtCQWJNeVc1NjU4Qm9ROWZGZS1jUFJHWGFBRWdBeXhDVFVhRmF4Z3NiODR2aHV5djJ3ZDVzNXp6bENYM3VJeDlyMkhwbmpyb1VMNEhQeTlLb3hWdDk0cFdoMW9Eb1cwdzREZ2dHeXFQMkY3TEgtQU1iWDgzbjBrTzRRVDlOb3R4OA?oc=5</t>
         </is>
       </c>
       <c r="F93" t="n">
@@ -3221,17 +3221,17 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>SALUS Controls launches intelligent AI-driven energy saving feature SALUS Sense - Installer Online</t>
+          <t>Blending Scientific Writing, AI, and the ‘Creative Act’ of Research - CU Anschutz newsroom</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Tue, 27 Jan 2026 16:45:19 GMT</t>
+          <t>Tue, 27 Jan 2026 13:17:38 GMT</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxPVUdSMnB0LVFKaW96RDM5OGd0NWFMNUFuOUk0eTU5c0NQSEJiVW1hWGJsSzJDbkNBX3h5VmlPdUtCQWJNeVc1NjU4Qm9ROWZGZS1jUFJHWGFBRWdBeXhDVFVhRmF4Z3NiODR2aHV5djJ3ZDVzNXp6bENYM3VJeDlyMkhwbmpyb1VMNEhQeTlLb3hWdDk0cFdoMW9Eb1cwdzREZ2dHeXFQMkY3TEgtQU1iWDgzbjBrTzRRVDlOb3R4OA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMic0FVX3lxTE9vbFc1WHlnYWstUU9mVTZXSkRWQ01vSVdXMWlXNGlGNnMtUkNWcVlEVU9Md2wyWnZyWVdHV2gyN25yR1NvbFNRWE9yZWxiRE9Wb3ZiLWtRVHpLVEZLYXRYYXlBMUdwT1VmYTRENTFlQVRMU3M?oc=5</t>
         </is>
       </c>
       <c r="F94" t="n">
@@ -3251,17 +3251,17 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Blending Scientific Writing, AI, and the ‘Creative Act’ of Research - CU Anschutz newsroom</t>
+          <t>AI and facial recognition to be rolled out as Britain’s ‘broken’ policing system faces sweeping reforms - The Independent</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Tue, 27 Jan 2026 13:17:38 GMT</t>
+          <t>Mon, 26 Jan 2026 19:32:00 GMT</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMic0FVX3lxTE9vbFc1WHlnYWstUU9mVTZXSkRWQ01vSVdXMWlXNGlGNnMtUkNWcVlEVU9Md2wyWnZyWVdHV2gyN25yR1NvbFNRWE9yZWxiRE9Wb3ZiLWtRVHpLVEZLYXRYYXlBMUdwT1VmYTRENTFlQVRMU3M?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxNbU1PRmNVSGU5N0ZEVXUyVUxPUFpRdF9BUVctRDZLSENwbFJMTFVTR2FXWGxLTTlpcG5KeFBPQlc2VGIzX0NnNWRYWnhXcXFyWVZIUUVDS3ByTkRBalZ1alNpMHh0ZlVrMExqSEtpYlJRNDFhenZqanZRb0FrZEtRTzJqZ1dJQWVqbmE5OGF5UHNLdGpnRHk0SGdISnpMWnV3WmIwUF8yaw?oc=5</t>
         </is>
       </c>
       <c r="F95" t="n">
@@ -3281,17 +3281,17 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>AI and facial recognition to be rolled out as Britain’s ‘broken’ policing system faces sweeping reforms - The Independent</t>
+          <t>To power AI energy needs, nuclear is going to have a comeback - Devex</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Mon, 26 Jan 2026 19:32:00 GMT</t>
+          <t>Tue, 27 Jan 2026 17:25:45 GMT</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxNbU1PRmNVSGU5N0ZEVXUyVUxPUFpRdF9BUVctRDZLSENwbFJMTFVTR2FXWGxLTTlpcG5KeFBPQlc2VGIzX0NnNWRYWnhXcXFyWVZIUUVDS3ByTkRBalZ1alNpMHh0ZlVrMExqSEtpYlJRNDFhenZqanZRb0FrZEtRTzJqZ1dJQWVqbmE5OGF5UHNLdGpnRHk0SGdISnpMWnV3WmIwUF8yaw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxQVFBmcTVleXJyS1dEWGdHTUxlVTZvbmhaMDhPczNvSTk5NU5mSWJXcE1YT3RDX1J0MzhTWEVoQWpIT1hCRllPVnRRcHVoYTlZNTh1R2JmRG1UNUtzYXZpWGM3Tjg1NlRiSkFFUmJWQ2Z3RGNsSnlYblRNTEZBODg4Y2tYczFSbVYxcWg2TkZKRk1BNEw0aWtUMUxB?oc=5</t>
         </is>
       </c>
       <c r="F96" t="n">
@@ -3311,17 +3311,17 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>To power AI energy needs, nuclear is going to have a comeback - Devex</t>
+          <t>Mozilla is building an AI ‘rebel alliance’ to take on industry heavyweights OpenAI, Anthropic - CNBC</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Tue, 27 Jan 2026 17:25:45 GMT</t>
+          <t>Tue, 27 Jan 2026 17:00:35 GMT</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxQVFBmcTVleXJyS1dEWGdHTUxlVTZvbmhaMDhPczNvSTk5NU5mSWJXcE1YT3RDX1J0MzhTWEVoQWpIT1hCRllPVnRRcHVoYTlZNTh1R2JmRG1UNUtzYXZpWGM3Tjg1NlRiSkFFUmJWQ2Z3RGNsSnlYblRNTEZBODg4Y2tYczFSbVYxcWg2TkZKRk1BNEw0aWtUMUxB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxOd0dwWnB6ZTBzZ1JicWZTaEUxaVRhdFlTUHY1NWp6SmtrNXBkNTVGcGtucHhvOURxSks4NUowT1Q2bFl2bVRWUnpPSUNrVVBUYS01TVI0VlhmT19Kdk1MNU5MaS1VZ1RaVDR3MGh4dXpjN29JSkpuMmRjU3FnWTZ3YkhyQlR5N2ZmTXhZN0lPOHQ1MTRTMUZPRW15S1hZUFg5cFhTaEZB0gGrAUFVX3lxTFBVY1BFV0hkaS10ZGx1QmFHRDRZemFGcDg1LU9LMnRjVEFzcUNkd09uWmJJb2Q5NjRQNkwtSDFSRTZibFdvU3p3MXJiTTU3a3lkdzBVX0VRenJDYVJ3QmNYb0NuRVQ0TFp0RHg4TnA1ZEI3U2xON3dLbzJmd00wcWdZMVQzaDhHcGN0dzJpSXJkNkpQWnpmeUFueVZDZ1FtcWxhYmQ0UjRfUkZfSQ?oc=5</t>
         </is>
       </c>
       <c r="F97" t="n">
@@ -3341,17 +3341,17 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Mozilla is building an AI ‘rebel alliance’ to take on industry heavyweights OpenAI, Anthropic - CNBC</t>
+          <t>Flow Meter Market to Hit $9.99 Billion by 2026 Driven by Automation and Infrastructure Expansion - Yahoo Finance UK</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Tue, 27 Jan 2026 17:00:35 GMT</t>
+          <t>Tue, 27 Jan 2026 18:00:00 GMT</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxOd0dwWnB6ZTBzZ1JicWZTaEUxaVRhdFlTUHY1NWp6SmtrNXBkNTVGcGtucHhvOURxSks4NUowT1Q2bFl2bVRWUnpPSUNrVVBUYS01TVI0VlhmT19Kdk1MNU5MaS1VZ1RaVDR3MGh4dXpjN29JSkpuMmRjU3FnWTZ3YkhyQlR5N2ZmTXhZN0lPOHQ1MTRTMUZPRW15S1hZUFg5cFhTaEZB0gGrAUFVX3lxTFBVY1BFV0hkaS10ZGx1QmFHRDRZemFGcDg1LU9LMnRjVEFzcUNkd09uWmJJb2Q5NjRQNkwtSDFSRTZibFdvU3p3MXJiTTU3a3lkdzBVX0VRenJDYVJ3QmNYb0NuRVQ0TFp0RHg4TnA1ZEI3U2xON3dLbzJmd00wcWdZMVQzaDhHcGN0dzJpSXJkNkpQWnpmeUFueVZDZ1FtcWxhYmQ0UjRfUkZfSQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMifEFVX3lxTE1fUGQzcGQxV0lVRWhPVTZtcDVydTFVbDhLZXNjdnVSdVZmRGlxYU1XOVNpY2J2Yzh1Tk1IMzhoTHZGWkNacFl4Q0RUaTdqemxYS3AyOEwwSWxkMFhEdVpZMGdTYm1NOU5FamhiWEhBQ1lQR1VjWkIwUGdQNm0?oc=5</t>
         </is>
       </c>
       <c r="F98" t="n">
@@ -3371,17 +3371,17 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Flow Meter Market to Hit $9.99 Billion by 2026 Driven by Automation and Infrastructure Expansion - Yahoo Finance UK</t>
+          <t>Preparing Your Brand for Agentic AI - Harvard Business Review</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Tue, 27 Jan 2026 18:00:00 GMT</t>
+          <t>Tue, 27 Jan 2026 15:35:17 GMT</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMifEFVX3lxTE1fUGQzcGQxV0lVRWhPVTZtcDVydTFVbDhLZXNjdnVSdVZmRGlxYU1XOVNpY2J2Yzh1Tk1IMzhoTHZGWkNacFl4Q0RUaTdqemxYS3AyOEwwSWxkMFhEdVpZMGdTYm1NOU5FamhiWEhBQ1lQR1VjWkIwUGdQNm0?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMia0FVX3lxTE9naUNGRzY4UjJLOE4ySkYtQmpDdExIUnh0ZUFtTVJYbzBMZWFmVWt0U1RWNlp4TngtS0NYNzY2UlB1bjEyVHZSa1U0eTlsVnJwMG8wejhhLUw1VjFucmpVLXJfT1RYMWpOMTkw?oc=5</t>
         </is>
       </c>
       <c r="F99" t="n">
@@ -3401,17 +3401,17 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Preparing Your Brand for Agentic AI - Harvard Business Review</t>
+          <t>New Dataflow features to enable streaming and ML workloads - Google Cloud</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Tue, 27 Jan 2026 15:35:17 GMT</t>
+          <t>Tue, 27 Jan 2026 17:13:53 GMT</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMia0FVX3lxTE9naUNGRzY4UjJLOE4ySkYtQmpDdExIUnh0ZUFtTVJYbzBMZWFmVWt0U1RWNlp4TngtS0NYNzY2UlB1bjEyVHZSa1U0eTlsVnJwMG8wejhhLUw1VjFucmpVLXJfT1RYMWpOMTkw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxPNjVrblNqeURfcVdSZnBYQUNlSGZ2N290azRwcGZ2UDM5NGl2V0xhOXBFbmNDTFk2c0F2MTNYa09xRkp2a0FDZUMzQVhEQ29yVDVJUDF1eTRzMW1abUIwU2xzMVZwVFFFR1RDOTM1eERWTkhOd05xcG1LR0JSemxMaFFiTDRLRmFleXQ2THQ0dFlBaE5DU0xhUXptLXZvRm9kX3I3cW5qMUt6WjZnMmlfUHhVVQ?oc=5</t>
         </is>
       </c>
       <c r="F100" t="n">
@@ -3431,17 +3431,17 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>New Dataflow features to enable streaming and ML workloads - Google Cloud</t>
+          <t>Reflections on the World Economic Forum: AI, Geopolitics, and Biothreats - Center for Global Development</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Tue, 27 Jan 2026 17:13:53 GMT</t>
+          <t>Mon, 26 Jan 2026 20:52:13 GMT</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxPNjVrblNqeURfcVdSZnBYQUNlSGZ2N290azRwcGZ2UDM5NGl2V0xhOXBFbmNDTFk2c0F2MTNYa09xRkp2a0FDZUMzQVhEQ29yVDVJUDF1eTRzMW1abUIwU2xzMVZwVFFFR1RDOTM1eERWTkhOd05xcG1LR0JSemxMaFFiTDRLRmFleXQ2THQ0dFlBaE5DU0xhUXptLXZvRm9kX3I3cW5qMUt6WjZnMmlfUHhVVQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilAFBVV95cUxQMFFvOHFfeFVPZFU2UXlHbzl1STBrYXVhZFdwc1dKcjZvT25IZ3FGbEEtdHpNclhFMVJRZ25rVzFvanl4WXJJZVZieWpMSUpfek9VSHA0WS02eGJGU241cGc1bUpHdXZBdWREeHpERS0wNUFGWUZZYVNmZDUxV1Fpb1lSWUJRR1oyNUhrUlVUZ1VLOVE4?oc=5</t>
         </is>
       </c>
       <c r="F101" t="n">
@@ -3461,17 +3461,17 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Reflections on the World Economic Forum: AI, Geopolitics, and Biothreats - Center for Global Development</t>
+          <t>C3.AI in talks to merge with startup Automation Anywhere, The Information reports - Reuters</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Mon, 26 Jan 2026 20:52:13 GMT</t>
+          <t>Wed, 28 Jan 2026 02:14:00 GMT</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilAFBVV95cUxQMFFvOHFfeFVPZFU2UXlHbzl1STBrYXVhZFdwc1dKcjZvT25IZ3FGbEEtdHpNclhFMVJRZ25rVzFvanl4WXJJZVZieWpMSUpfek9VSHA0WS02eGJGU241cGc1bUpHdXZBdWREeHpERS0wNUFGWUZZYVNmZDUxV1Fpb1lSWUJRR1oyNUhrUlVUZ1VLOVE4?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxPOUlydFFnLVlCeE5TYWQwZUl1SGpFckx6QWlKeTNrZVpreDhNZVpPY0M4U0xDYjlCay1ibFRRb3ZHOHdMX3NMOWE3RFNIcHR2a0FqNkhLNVlXQUprUG5yNldBTVk4eTE5UDd0ZXUxWkt5RkFYWFdWaExtQ1U2VDBmZXA3VHhYVm04TmVudElBeTRpX3QyemxZdjd5dHdUc0ZDVXhZWnRpczY0cl9HaHdoX3BHM28?oc=5</t>
         </is>
       </c>
       <c r="F102" t="n">
@@ -3481,27 +3481,27 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Insider_Risk</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+          <t>("insider risk" OR "insider threat" OR "internal threat" OR "employee misconduct" OR "data exfiltration" OR "privileged access abuse" OR "malicious insider" OR "negligent insider" OR "insider attack" OR "corporate espionage" OR "information leakage" OR "unauthorised access" OR "policy violation" OR "security breach" OR "insider vulnerability")</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>C3.AI in talks to merge with startup Automation Anywhere, The Information reports - Reuters</t>
+          <t>The evolution of insider threat (UK) - Kennedys Law LLP</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Wed, 28 Jan 2026 02:14:00 GMT</t>
+          <t>Tue, 27 Jan 2026 10:14:44 GMT</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxPOUlydFFnLVlCeE5TYWQwZUl1SGpFckx6QWlKeTNrZVpreDhNZVpPY0M4U0xDYjlCay1ibFRRb3ZHOHdMX3NMOWE3RFNIcHR2a0FqNkhLNVlXQUprUG5yNldBTVk4eTE5UDd0ZXUxWkt5RkFYWFdWaExtQ1U2VDBmZXA3VHhYVm04TmVudElBeTRpX3QyemxZdjd5dHdUc0ZDVXhZWnRpczY0cl9HaHdoX3BHM28?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxPQXZJVmUxck5Cb0RSUHVfeVdVVlFlaUJvQ1JiRkV1cVlWOFVrSWJEU0J6UW5yeHRVajVBb3l1dmRsRXg5ZjNsaDVHZWJZc05SX0Rhd2pQcWFrXy1VM3ZYNW9FVDVrc0RtRXdxM2FDWXVnQi1BdmJYQzRRaFEwRnEwWldZSlNiUDhiVEJfSTNyU0lldElCR0pQTmlVZw?oc=5</t>
         </is>
       </c>
       <c r="F103" t="n">
@@ -3521,17 +3521,17 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>The evolution of insider threat (UK) - Kennedys Law LLP</t>
+          <t>Current geopolitical tensions are putting pressure on the internal security of European organisations - TradingView</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Tue, 27 Jan 2026 10:14:44 GMT</t>
+          <t>Tue, 27 Jan 2026 09:05:23 GMT</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxPQXZJVmUxck5Cb0RSUHVfeVdVVlFlaUJvQ1JiRkV1cVlWOFVrSWJEU0J6UW5yeHRVajVBb3l1dmRsRXg5ZjNsaDVHZWJZc05SX0Rhd2pQcWFrXy1VM3ZYNW9FVDVrc0RtRXdxM2FDWXVnQi1BdmJYQzRRaFEwRnEwWldZSlNiUDhiVEJfSTNyU0lldElCR0pQTmlVZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi6wFBVV95cUxOdXBuRnhOamJ5eEpFNS15RjM3VmVwWlREUHpBdlpCSEdEU1hsbE4wSzBudkVsZllieVhqYkJ6RDRQQXl6bnhxWHdybnVIZmJfTEZ0RUNjejRfc3VTcnQ4WWVLVHMtZjdUV3pxOWdCVHo4dUVEZXFjMF9HQnhPUlNOSTN2RFd1RmJaMUR1M1lLWDlZM3ZXSlFMRzlqOG9CRnZEMnFQQUJFVDJZWGlrSTF1eTdXMDhEUzRncy1tamRFRlhrNGpMak1PdjRDN1Y0Xzg4aFdHcm5sOVd6VXR0bW9qZFM3ODBfYnVDdTBn?oc=5</t>
         </is>
       </c>
       <c r="F104" t="n">
@@ -3551,17 +3551,17 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Current geopolitical tensions are putting pressure on the internal security of European organisations - TradingView</t>
+          <t>AI Colleague Risks: The New Insider Threat in UC and Collaboration - UC Today</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>Tue, 27 Jan 2026 09:05:23 GMT</t>
+          <t>Sun, 25 Jan 2026 13:19:01 GMT</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi6wFBVV95cUxOdXBuRnhOamJ5eEpFNS15RjM3VmVwWlREUHpBdlpCSEdEU1hsbE4wSzBudkVsZllieVhqYkJ6RDRQQXl6bnhxWHdybnVIZmJfTEZ0RUNjejRfc3VTcnQ4WWVLVHMtZjdUV3pxOWdCVHo4dUVEZXFjMF9HQnhPUlNOSTN2RFd1RmJaMUR1M1lLWDlZM3ZXSlFMRzlqOG9CRnZEMnFQQUJFVDJZWGlrSTF1eTdXMDhEUzRncy1tamRFRlhrNGpMak1PdjRDN1Y0Xzg4aFdHcm5sOVd6VXR0bW9qZFM3ODBfYnVDdTBn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiSEFVX3lxTE12TDdZanZ3eWpsSjhacm9ZS3lMUmtMZUpXU3ZNWFdMa2xhM1VGUk5fMGNfSUxfeDJFb1k2Nnk1V1RUR1hxMklpWQ?oc=5</t>
         </is>
       </c>
       <c r="F105" t="n">
@@ -3581,17 +3581,17 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>AI Colleague Risks: The New Insider Threat in UC and Collaboration - UC Today</t>
+          <t>When trust turns toxic: Mars exec jailed in $28m fraud case that exposed insider risk - BakeryAndSnacks.com</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>Sun, 25 Jan 2026 13:19:01 GMT</t>
+          <t>Fri, 23 Jan 2026 11:59:00 GMT</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiSEFVX3lxTE12TDdZanZ3eWpsSjhacm9ZS3lMUmtMZUpXU3ZNWFdMa2xhM1VGUk5fMGNfSUxfeDJFb1k2Nnk1V1RUR1hxMklpWQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxQbF9hVkI3MEk0MzNFektLYnB5d29BZ0tzMWRuVnNRWjE1ajdIM0xnSHE4YTk5N2RGS1lMMldqdXNkNjlpaUNCQWtmU3JLU2FuSWZLbTRBNHYzZnFwRmRscU52RDN6RDZPd3dCaDZLVUpQdlNQWi1HSEtGbE9ZOGhpV3ZsRHEwYlQ5NEQ5YmVFTFpsVlpWckFmVTNKTFJPQUFBaEVrLV9lZU4?oc=5</t>
         </is>
       </c>
       <c r="F106" t="n">
@@ -3611,17 +3611,17 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Nightfall shines light on AI browser data exfiltration - Computer Weekly</t>
+          <t>New solution helps prevent data exfiltration in real time - BetaNews</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Wed, 21 Jan 2026 14:26:15 GMT</t>
+          <t>Wed, 21 Jan 2026 15:08:58 GMT</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxONTRLQU9XaGdZaDhGdkdfVkRyNWFLQ2FZRDdoNzFOSFZUcEdvc1Y0ejRlQTNlengtNG1ZTGltaV9yRXc2VzNsR2FibGhsRG9ISFlwOE01aGpyZU92SGNocVFrNHRXZERPNVpybnpoM0JwaGFqLXQ2aHMyR0s2UXVCamRlTUJIQlo2NEpWTGQwb1k5OTdJRzZDSTU5R25mczQ1WVdmdk9ZVkVYcXkxaWlycg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxQLUc0TjVWRGtyTDRtM0RzVWJBMGRad2RLUGZubkpKZVF6SGZHc2ZEUm90U0UycXlMQUthd3BRMzR4WDltQlhZWG4wam1ER3Rfb1ozNDhMdzlQSjVXM2hYVTVUdGthTlpxb2dKQ1JJbzA2cHVaU0lRSGJyN3JLSkd3UmVqR3pVR0YtTldjRThBelk?oc=5</t>
         </is>
       </c>
       <c r="F107" t="n">
@@ -3641,17 +3641,17 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>When trust turns toxic: Mars exec jailed in $28m fraud case that exposed insider risk - BakeryAndSnacks.com</t>
+          <t>Davos panel warns AI agents could run amok - theregister.com</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Fri, 23 Jan 2026 11:59:00 GMT</t>
+          <t>Wed, 21 Jan 2026 23:04:00 GMT</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxQbF9hVkI3MEk0MzNFektLYnB5d29BZ0tzMWRuVnNRWjE1ajdIM0xnSHE4YTk5N2RGS1lMMldqdXNkNjlpaUNCQWtmU3JLU2FuSWZLbTRBNHYzZnFwRmRscU52RDN6RDZPd3dCaDZLVUpQdlNQWi1HSEtGbE9ZOGhpV3ZsRHEwYlQ5NEQ5YmVFTFpsVlpWckFmVTNKTFJPQUFBaEVrLV9lZU4?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMickFVX3lxTFBCNUFJN3BRRzA2WjVvdVRNblFtR0VnWGNDd1B2dXNDVmhFS0ozTnVVNmdtdEtLY2IwZGJZX2hpcHVoZFdrOVgzTWlZTFBVSnEwUnJpaXNGWjNuLVpzUXo2ay14UTF6ZDZiTTY3TzFpUXFlZw?oc=5</t>
         </is>
       </c>
       <c r="F108" t="n">
@@ -3671,17 +3671,17 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>The Email Insider Threat Has Evolved in the Era of Generative AI - Security Magazine</t>
+          <t>$40M US Crypto Heist Linked to Contractor’s Son Raises Insider Risk Alarm - FXLeaders</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Wed, 21 Jan 2026 05:00:00 GMT</t>
+          <t>Mon, 26 Jan 2026 08:00:27 GMT</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxNZDlHSnIxUVNnNU9aSVJlYzRIZko2WFBJUktaSXA0NWZ0SlRKRHNoTjRSdE1PRmNDZjJReENpOXRLbjZjVmxJTFNmNUFTWE5HdlVUT1NubGRCZElYY2pyUFRTaUdzV0M2Y1o3TGRWZ09BUVFpWHZxYWdobFp4UHNDWmtkRUJBOF9XSDhIRVg4LUJ4Q1VFRTdidlJ1RmxFUGZzYmNYVkxKbFJZM1ZrenBaQXB1dw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxPT2VKaXZjSXNkQ0dJMEFyRlh1YkRBZ0pKNU5BR0Q3VjRsM1JnSXRyUGxUUVBYNVlJOGVJZmIxSXp1Tk44LXRhc3hKbXVkOW5hQUg5V2pQaWRTczR2OE9zMU5zNktzT1pFTlNaV1pFQmlNWEVDcFFYYkFEb3JJZDNLVFB4UmExWTczZTNtdy1wWm9PWFFmT2pIYTJoLWdrVE4wR0xaVVlXQ0RiNnZ1Q0M0bS1Ia1Q?oc=5</t>
         </is>
       </c>
       <c r="F109" t="n">
@@ -3691,27 +3691,27 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Insider_Risk</t>
+          <t>Fraud_Scam</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>("insider risk" OR "insider threat" OR "internal threat" OR "employee misconduct" OR "data exfiltration" OR "privileged access abuse" OR "malicious insider" OR "negligent insider" OR "insider attack" OR "corporate espionage" OR "information leakage" OR "unauthorised access" OR "policy violation" OR "security breach" OR "insider vulnerability")</t>
+          <t>("fraud" OR "scam" OR "phishing" OR "identity theft" OR "account takeover" OR "payment fraud" OR "credit card fraud" OR "wire fraud" OR "business email compromise" OR "fake invoice" OR "social engineering" OR "advance fee fraud")</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>New solution helps prevent data exfiltration in real time - BetaNews</t>
+          <t>How McAfee’s Scam Detector Checks QR Codes and Flags Suspicious Social Messages - McAfee</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Wed, 21 Jan 2026 15:08:58 GMT</t>
+          <t>Tue, 27 Jan 2026 14:16:29 GMT</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxQLUc0TjVWRGtyTDRtM0RzVWJBMGRad2RLUGZubkpKZVF6SGZHc2ZEUm90U0UycXlMQUthd3BRMzR4WDltQlhZWG4wam1ER3Rfb1ozNDhMdzlQSjVXM2hYVTVUdGthTlpxb2dKQ1JJbzA2cHVaU0lRSGJyN3JLSkd3UmVqR3pVR0YtTldjRThBelk?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikgFBVV95cUxNbmVmUklKS2hzZzJyU3BQcld4T2JvTVFWaHRhdnNGWXhHYmtBT0Z3THIwd2phNEFrcXpPaVlSOHdvOGMzU3VUdFlMb2RoTUVMcW11cG56NkRCTnFCRFRub3ozbXgtOXBtLWpudlNzOEo2SDlVQllpbWwwcHktdThyWm54TEhEcl8zMjRFOUx2VjMzdw?oc=5</t>
         </is>
       </c>
       <c r="F110" t="n">
@@ -3721,27 +3721,27 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Insider_Risk</t>
+          <t>Fraud_Scam</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>("insider risk" OR "insider threat" OR "internal threat" OR "employee misconduct" OR "data exfiltration" OR "privileged access abuse" OR "malicious insider" OR "negligent insider" OR "insider attack" OR "corporate espionage" OR "information leakage" OR "unauthorised access" OR "policy violation" OR "security breach" OR "insider vulnerability")</t>
+          <t>("fraud" OR "scam" OR "phishing" OR "identity theft" OR "account takeover" OR "payment fraud" OR "credit card fraud" OR "wire fraud" OR "business email compromise" OR "fake invoice" OR "social engineering" OR "advance fee fraud")</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Davos panel warns AI agents could run amok - theregister.com</t>
+          <t>Top Impersonation Tactics Used in Social Engineering and Phishing - SOCRadar® Cyber Intelligence Inc.</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Wed, 21 Jan 2026 23:04:00 GMT</t>
+          <t>Tue, 27 Jan 2026 12:53:55 GMT</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMickFVX3lxTFBCNUFJN3BRRzA2WjVvdVRNblFtR0VnWGNDd1B2dXNDVmhFS0ozTnVVNmdtdEtLY2IwZGJZX2hpcHVoZFdrOVgzTWlZTFBVSnEwUnJpaXNGWjNuLVpzUXo2ay14UTF6ZDZiTTY3TzFpUXFlZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxPa0k0Z3UyVWwyYVBtMmtESUtsSkZpTWd6ZHBOUEJLYmVvRWFyR1g5bmNvbWRJb3VaR2ZLbl9IRDRUOFp4RFY0RmVZaEVvUFBYZWdCZjZjaUVobTJPNTZteXJoOGxpRTgtMkl3YXVENFYxT0N0MzdiTDlMb0FEVTZzQQ?oc=5</t>
         </is>
       </c>
       <c r="F111" t="n">
@@ -3751,27 +3751,27 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Insider_Risk</t>
+          <t>Fraud_Scam</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>("insider risk" OR "insider threat" OR "internal threat" OR "employee misconduct" OR "data exfiltration" OR "privileged access abuse" OR "malicious insider" OR "negligent insider" OR "insider attack" OR "corporate espionage" OR "information leakage" OR "unauthorised access" OR "policy violation" OR "security breach" OR "insider vulnerability")</t>
+          <t>("fraud" OR "scam" OR "phishing" OR "identity theft" OR "account takeover" OR "payment fraud" OR "credit card fraud" OR "wire fraud" OR "business email compromise" OR "fake invoice" OR "social engineering" OR "advance fee fraud")</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>$40M US Crypto Heist Linked to Contractor’s Son Raises Insider Risk Alarm - FXLeaders</t>
+          <t>Islanders warned about scam JEP social media account - bailiwickexpress.com</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Mon, 26 Jan 2026 08:00:27 GMT</t>
+          <t>Sat, 24 Jan 2026 15:37:53 GMT</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxPT2VKaXZjSXNkQ0dJMEFyRlh1YkRBZ0pKNU5BR0Q3VjRsM1JnSXRyUGxUUVBYNVlJOGVJZmIxSXp1Tk44LXRhc3hKbXVkOW5hQUg5V2pQaWRTczR2OE9zMU5zNktzT1pFTlNaV1pFQmlNWEVDcFFYYkFEb3JJZDNLVFB4UmExWTczZTNtdy1wWm9PWFFmT2pIYTJoLWdrVE4wR0xaVVlXQ0RiNnZ1Q0M0bS1Ia1Q?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilgFBVV95cUxNVGYzbHo3QTl2ZDc4dTlmd2tKUW40WFZvRzlXZ2NBd241SDJWZnpJa2h1bmdkNGVDaWc5MkRGdUphOGpZSUkwbk1oVko1OHN3Y2ptaXhqZXBlT1kxODFGMjJKOS1KSXRTN2dkdENqWVdzVjhFNzJsQzhtUnhDQjhlNFIybWVTYW8tTGdKMzBZN2ZhdWQ5cnc?oc=5</t>
         </is>
       </c>
       <c r="F112" t="n">
@@ -3791,17 +3791,17 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>How McAfee’s Scam Detector Checks QR Codes and Flags Suspicious Social Messages - McAfee</t>
+          <t>SCAM ALERT: South African mining company not offering training programme through social media – ignore dodgy link and follow verified portals - Africa Check</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>Tue, 27 Jan 2026 14:16:29 GMT</t>
+          <t>Fri, 23 Jan 2026 11:34:29 GMT</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikgFBVV95cUxNbmVmUklKS2hzZzJyU3BQcld4T2JvTVFWaHRhdnNGWXhHYmtBT0Z3THIwd2phNEFrcXpPaVlSOHdvOGMzU3VUdFlMb2RoTUVMcW11cG56NkRCTnFCRFRub3ozbXgtOXBtLWpudlNzOEo2SDlVQllpbWwwcHktdThyWm54TEhEcl8zMjRFOUx2VjMzdw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxPZ2NlM19wRTFPUzQ3ckdaQUVjWEg0TnJobE54ZHQ1WThsYk45TnJ2S1hzdlV1TWV3MUc0YTQ5TTR4QjZIbWJqS2p5dlBBc0dPSjVGRkl0d2g4MUVWdE55WU9pTTBEdExGQTZSY0ZRYzZldHlTUmtfcVA5SURpdC12dUhmNXFTcHo5TTIwX3FLdXc3clpQQTVDSjNETWZjcGIwZXBQRHBxUnY3R0hrbUJCQmg1NEx0dw?oc=5</t>
         </is>
       </c>
       <c r="F113" t="n">
@@ -3821,17 +3821,17 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Top Impersonation Tactics Used in Social Engineering and Phishing - SOCRadar® Cyber Intelligence Inc.</t>
+          <t>Police warning: Beware of social media scam stealing bank access - RTL Today</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>Tue, 27 Jan 2026 12:53:55 GMT</t>
+          <t>Mon, 26 Jan 2026 16:30:50 GMT</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxPa0k0Z3UyVWwyYVBtMmtESUtsSkZpTWd6ZHBOUEJLYmVvRWFyR1g5bmNvbWRJb3VaR2ZLbl9IRDRUOFp4RFY0RmVZaEVvUFBYZWdCZjZjaUVobTJPNTZteXJoOGxpRTgtMkl3YXVENFYxT0N0MzdiTDlMb0FEVTZzQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxOYkF6X2FsdEN6ME5PX25oUF8zTVVPLWYzd1pMRkE4ZnFac1Jubjg5Tk42ZlczU29FMXhLZENqc3VsZG1DUnJFaTVtOW1WcVp4bzYySUItalE0LWQ5OGpHZGd4SFRUU0x4S2ZlNEVMLWl5WDAzaEhUdUZkcmEtak9NWkFvV3Z6S1V0Z0VoeFZpX0pEa0lZWWFzQWhrcw?oc=5</t>
         </is>
       </c>
       <c r="F114" t="n">
@@ -3841,27 +3841,27 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Fraud_Scam</t>
+          <t>Current_Affairs</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>("fraud" OR "scam" OR "phishing" OR "identity theft" OR "account takeover" OR "payment fraud" OR "credit card fraud" OR "wire fraud" OR "business email compromise" OR "fake invoice" OR "social engineering" OR "advance fee fraud")</t>
+          <t>(geopolitics OR migration OR economy OR conflict OR legislation OR terrorism OR disinformation OR misinformation OR government OR policy OR regulation) AND (briefing OR analysis OR update OR report)</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Islanders warned about scam JEP social media account - bailiwickexpress.com</t>
+          <t>Persistent threats, low sophistication: Pool Re maps ‘substantial’ UK terrorism risk landscape - Global Reinsurance</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>Sat, 24 Jan 2026 15:37:53 GMT</t>
+          <t>Wed, 28 Jan 2026 14:02:17 GMT</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilgFBVV95cUxNVGYzbHo3QTl2ZDc4dTlmd2tKUW40WFZvRzlXZ2NBd241SDJWZnpJa2h1bmdkNGVDaWc5MkRGdUphOGpZSUkwbk1oVko1OHN3Y2ptaXhqZXBlT1kxODFGMjJKOS1KSXRTN2dkdENqWVdzVjhFNzJsQzhtUnhDQjhlNFIybWVTYW8tTGdKMzBZN2ZhdWQ5cnc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi3gFBVV95cUxQTFMySFVCY0JyTW1NcUhvNWdvSlFnaVpLZG1udkd2U1h0MWFHRnB2ZVk4RUtHR25TM3BmalRWYlZ4UVgtVmd3Mk1ESjdBZ01VamFVbFRUbzZ6ZzZSMGxvQlp2dVU1cjhNM3ZnWmJacG1uM0d2dTMtZmd6aTNmb0tSVFVZNERxYzB5bUFyQTc0clZmeDhSTkhWWnZwRVprQ1JLNG1UNjFZbWdIUlBfTkttTFlsWnhVV1ZwVzdRQ3E5UDFlWC12MWZfOVZpdEhuaHdjbFc1UDc3Y1JYc3lpQUE?oc=5</t>
         </is>
       </c>
       <c r="F115" t="n">
@@ -3871,27 +3871,27 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Fraud_Scam</t>
+          <t>Current_Affairs</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>("fraud" OR "scam" OR "phishing" OR "identity theft" OR "account takeover" OR "payment fraud" OR "credit card fraud" OR "wire fraud" OR "business email compromise" OR "fake invoice" OR "social engineering" OR "advance fee fraud")</t>
+          <t>(geopolitics OR migration OR economy OR conflict OR legislation OR terrorism OR disinformation OR misinformation OR government OR policy OR regulation) AND (briefing OR analysis OR update OR report)</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>SCAM ALERT: South African mining company not offering training programme through social media – ignore dodgy link and follow verified portals - Africa Check</t>
+          <t>Government responds to the sixth Commissioners’ report into Thurrock Council’s progress under intervention - yourthurrock.com</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>Fri, 23 Jan 2026 11:34:29 GMT</t>
+          <t>Wed, 28 Jan 2026 13:49:29 GMT</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxPZ2NlM19wRTFPUzQ3ckdaQUVjWEg0TnJobE54ZHQ1WThsYk45TnJ2S1hzdlV1TWV3MUc0YTQ5TTR4QjZIbWJqS2p5dlBBc0dPSjVGRkl0d2g4MUVWdE55WU9pTTBEdExGQTZSY0ZRYzZldHlTUmtfcVA5SURpdC12dUhmNXFTcHo5TTIwX3FLdXc3clpQQTVDSjNETWZjcGIwZXBQRHBxUnY3R0hrbUJCQmg1NEx0dw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi3gFBVV95cUxNX3RwOW55Z1BmS0ZNSzJKaWdKMDM3cWpJRllaenZSXzdObnpZVmljUDNuSldWMGUwU21sX1Z6MzFnc1BlYXlCOGozMkpad1hNNXhYbFdjMEF2ZGdfV1U3b2xza2prbWhkSHNxWTRTNEtvNXVYY1U1Y2pxa0VuWXpLYTRFdlh3ZFRuZG9NT2t3cFdpT1RGcjktYVg5T3JNbVUxWmQ1NDBPbzNjNVdHSnFQdmdDcE51SWZkYmFEbWlxc0JzM2FVSDlWLU9fd3d3NzQ5RUo4UWdVcjZtS3Q0Rmc?oc=5</t>
         </is>
       </c>
       <c r="F116" t="n">
@@ -3901,30 +3901,2610 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
+          <t>Current_Affairs</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>(geopolitics OR migration OR economy OR conflict OR legislation OR terrorism OR disinformation OR misinformation OR government OR policy OR regulation) AND (briefing OR analysis OR update OR report)</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Kingston mayor highlights government work in annual report - Spectrum News</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>Wed, 28 Jan 2026 13:22:00 GMT</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxNMDBTR243VWR2ampuLVBrR1MzTWlUbWMySTBMZzFHalhiZ0NhSklWaGVqNGR3ZlNXWHVVR2FaUUVfemZ5MHhyRTJCOTNUOVJnX181VW9kaVVfSE9kQVh2LTJQZWFaQlNuU0J3V2FncW9raTFITXJmUHJMdXJKOUVVdEJjVnJWUWQxNS1JMFlYSGlYd2xsZmhnX3ZBYlEyQzhFRnlVZEJB?oc=5</t>
+        </is>
+      </c>
+      <c r="F117" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>Current_Affairs</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>(geopolitics OR migration OR economy OR conflict OR legislation OR terrorism OR disinformation OR misinformation OR government OR policy OR regulation) AND (briefing OR analysis OR update OR report)</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>DSM Foundation Reacts to Government Report on Ketamine Use and Risks - BusinessMole</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>Wed, 28 Jan 2026 13:18:19 GMT</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxQS2pyREFjcExEamNEQURrUjRETE5MRzUtOHJHb3R3d0cxM1E0X2FpM1B3MnhjVnNvaFFDVld1b3MwbVFhSDlpX2phUkN4WW5YUnIxZDd5R1RJWW9aaGw2U0tkXzJza0szWnlHUDc2MFl3UXFXeVlLMHMyZGI4OVlpV01JalBJemVEUG00WmhRclo4anZIbEJWS1dkX2plMjA?oc=5</t>
+        </is>
+      </c>
+      <c r="F118" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>Current_Affairs</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>(geopolitics OR migration OR economy OR conflict OR legislation OR terrorism OR disinformation OR misinformation OR government OR policy OR regulation) AND (briefing OR analysis OR update OR report)</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Press Conference: Monetary Policy Report – January 2026 - Bank of Canada</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>Wed, 28 Jan 2026 02:36:35 GMT</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxPZWlvMExpSV9saFJ2bGFtcVVuMXdQTnhvcHdnaG1VOEZiMHo2S2lpQ3JfYVg5WC1OMmdCMUp0d2hSR0txc05ORFdaTUlUcTZhbTd1dExYMEowMnVIZGtHQ0tXNXVrb1pwcW9VXzdGTzZtZGRnbVVQT0Q4SXNjSEdKYnE5RkhvanBvdEpDSXl0NEdmQm5MejlB?oc=5</t>
+        </is>
+      </c>
+      <c r="F119" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>Supply_Chain</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>Focus on privacy compliance - White &amp; Case LLP</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>Wed, 28 Jan 2026 12:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMickFVX3lxTE44VDYxWHFycVVwRExpUE9INGw2RVhlWUk0VlV3cUNwX0o1T3BxcmVHYzdBX0FQSDlpNWdJTmdyaC1FdUpGSzBqbldGQzMxYlNOclJkbDJ4aUJZaVM0aExWZF9NOFhqRGhBaWNoSFhnNWl3QQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F120" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>Supply_Chain</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>‘Helvellyn’ takes to the waters: new pilot boat comes on board at Cumbrian port - cumberland.gov.uk</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>Wed, 28 Jan 2026 10:58:11 GMT</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxNcHRvOXJkY2t0RlNNbFRGbDlpOUhBaUhRMDFPT2ZEMDBoTVZYMFFJdWFRbTJsM2NTQTZ0elJ2ZFlxOVlFN1BMUUlkTmtnbVZsY2pwRWlTczBKUHFxWEtHWld3NHNqOGQyd1RadmdZM1hYb3I5b0g4VFJvTnV5dEs1X00tNFpZNHl2aVVPYV9xWmpib0xQS05sS1dFLXhSaEVlcEx2VW9R?oc=5</t>
+        </is>
+      </c>
+      <c r="F121" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>Supply_Chain</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>Sanctions are not a humane alternative to bombs. They are economic warfare with civilians as collateral damage - The Guardian</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>Wed, 28 Jan 2026 12:53:00 GMT</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi3gFBVV95cUxNZkNXdHVJY1dLSHV3ZXRUM1Y4cWM5MGRZWEh0SWRfOHM4NkdoRk1qNzVxNGpFalJmVzRkRzVBS3ZEWXIwYWxqQXpMcHhPa2t0R0RTNU85MXpXZFFjblRCamo3ZlI4b3hPZl9CTGVnMjgySlNUZnRfUWNjMFBvaDl2MGcwbVdjdURESEdyNG1xc3lyM0V0cEJ5Uy1sUEFZR1NKU2lSeHNZNnd5LTZnMWI1Q2UwWGMyeFFIUkh6bTlsbG9rVTBqRmJBNkw1TVFLVGVxWllCVkM4TExrMXZxc3c?oc=5</t>
+        </is>
+      </c>
+      <c r="F122" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>Supply_Chain</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>CMA issues significant new guidance on supply chain responsibility for environmental claims - Fieldfisher</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>Wed, 28 Jan 2026 09:49:15 GMT</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMilAFBVV95cUxOcnJwTDBOSEhBbWxObUt4bzdXdkJvZWxzYjdCazNRUUpyTHNQVzhLbzNDMnhNRWhJOG1JUTZoVXphcWxKQmtDYmpWaUxGVG1NbFQySjRES3Q5YXUwTVdlVmd6M3d3a3pDZ0FMbDhHMkNVa3RYRDRVMDZKYUpUbjFCVFcwVkhmUTFuYlVhSTA0aE5yU2ZD?oc=5</t>
+        </is>
+      </c>
+      <c r="F123" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>Supply_Chain</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>Polish port picked for offshore wind operations base - 4C Offshore</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>Wed, 28 Jan 2026 12:47:32 GMT</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxOYWtJM1gyQmQ1Um9kMTJfclV1dTI5WUdVdmtQMEZ3RDV3dnpkZFdHWFZqSGwxUy1yZWZvdWQzVUY5dXRrZDh4VDhDRjlJYkttcWZMNjFEU3pzMFJFNWx4Q0pZYlVfY3FjZUNpVkEwaFBlUzVvNUwwSmtGNUNKQkRjbHBNYmhlLWdJV3Y1SmRENUMybEt4ZUdJelhSam1IVFU?oc=5</t>
+        </is>
+      </c>
+      <c r="F124" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>Supply_Chain</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>Historic building on the up after £3.2m restoration - inverclyde.gov.uk</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>Wed, 28 Jan 2026 11:14:00 GMT</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxQUG5FZ1BZeGJCN2dPZ3FOOS1WOGxHQnJWZ2QtOG9MejRYMER1YjhMVVUwZFRQX3BEWk9Xb3dqWWt1WjdSZnl5M3ZMckgybEdkQ3RpWnBBSjZ5d1lzdTNSbUktYnIzQnhmaDRnZHlEbnFnaV9sTjMwT1ZvQjFLQ2puWXJRMzUtU0pYcng1QzhaVTVUSHRibjBTekRn?oc=5</t>
+        </is>
+      </c>
+      <c r="F125" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>Supply_Chain</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>What is the Supply Chain Risk of the Rising Price of Gold? - Supply Chain Digital Magazine</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>Wed, 28 Jan 2026 13:14:51 GMT</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMie0FVX3lxTE4zc3pQV2E2RWZWckNscURzX0F4TThUY3MzejZJWWhiN2hYSWdxb3hNYzV3TV9VTmdJd0RGeExBMmVqT1M4MEV3c3puby1fVTRyTk10amcyYlJ4YnN1YU5SUDJyX1lqbEV0Sk1HbmMxSEVScC1TNFRadzVvQQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F126" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>Supply_Chain</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>Sussex: Coach Paul Farbrace expects side to face sanctions over finances - BBC</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>Wed, 28 Jan 2026 10:47:06 GMT</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiZkFVX3lxTFBoZ2JHNmNxQ01JdlZPQWFna1U5RUpYSU5kOVJyWWxROTV3cV9FaUd6eFlmLWdLTmRZMFYxRWRFNmprSXdSM2owQ29OS3NlX0FWTkgtbkpLTUNHT2RWMkVYMnV1UjZ3QQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F127" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>Supply_Chain</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>Sanctions without shock? United Nations snapback and Iran's oil exports - Clingendael</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>Wed, 28 Jan 2026 12:21:06 GMT</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxQNEthalRKZ3ZROEFDc0FrMmg0SjJiVERYNjg2dkN5SjU4N3BxOTRQR0xjNEJVMXE5T1JUYlNwNjFjMjlYMUl2ZGlKckRTb2U2SlhTNXp6YWpXVmVQRXJVWndPUG9ueGpnUlVoTEZRZGthNzl5ODdYd1o5d2wwSEJHX3daVlhybk52T244T0pSa2hKVUlaanoxb3dsOTZZQ1dfNDFzWUpfWHNmaGY5Y1E?oc=5</t>
+        </is>
+      </c>
+      <c r="F128" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>Supply_Chain</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>News Content Hub - Portside ballast water partnership targets discharge compliance - rivieramm.com</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>Wed, 28 Jan 2026 11:11:03 GMT</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxPbUZjNG0yS1BmOEdXSE5TbVJuSVRNdXBxTFFfQ2NURXRYWkhTcEFvX2N5Uk9NQ1VfOXZSM3N1RmI0VXhubWFmV1RmZ1p5bXFxcDBxNnFZdE9BamVNQVZBU0JKOXdRZk9tajBaYkFxTXFWbUF1RWRrZHY3bW05eEFVN1pDbTh3MmduN1RNaUtDVzBoUnlUc1NmTkhsNlNzMmx2ajh0NGtXaTlPb2hfVWtYWk8xcw?oc=5</t>
+        </is>
+      </c>
+      <c r="F129" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>Supply_Chain</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>Will the Volatile Ocean Freight Rates of the 2020s Give Way to a More Sedate Environment This Year? - International Banker</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>Wed, 28 Jan 2026 11:23:42 GMT</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi1gFBVV95cUxPeXVoQk1qRFhKQXdzdWtkejRfalV2cDBhRTd6YTllQ3UzdURFb0s2cEljS0t3ckxPR1dDOXFBaWxNQmU3U0pOanFqeHZnN1lPVGZCVHRPZTM4aHhLdWh6SndaVkdBUVlhMmRmTHgzNGdIR2RCRFN1ajBpSHM2MGdNbHFDYl9pbHJJU1RJQ0dLa3dBOGlYU3RHb25fQ0hFbWMzNFRTVFpSMVZTVXFKRmp2azJpY1VYNmRsczZNYmFmNWx5X05pU3BSdndpbjFBbzZLWTdSUEh3?oc=5</t>
+        </is>
+      </c>
+      <c r="F130" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>Supply_Chain</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>China’s ambassador warns Albanese reclaiming Port of Darwin will force Beijing to intervene - The Guardian</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>Wed, 28 Jan 2026 05:40:00 GMT</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxQMmNPREs3S0RvS3RMbFd2SUlDcVloZXU4b1dtTVZHZmdkNy1VcEEteHFpMTNGcFdzak1hNXNHUHdzU3VSVHVnSENsU3k0WGhDa3EydkVlOFZxZmlrRjJqYl9SNG1XZ0FHNW1Cel9sQ2hfbVRDa1AzaUh5aW9vY3I0bklGUC1nNEZRTW0yckI4bFlDSzJNZUs5YnNyMXdncmZsenJZ?oc=5</t>
+        </is>
+      </c>
+      <c r="F131" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>Supply_Chain</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>NHS announces next phase of supply chain engagement - Wired-Gov</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>Wed, 28 Jan 2026 11:26:05 GMT</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxQWnRaVkFDTy11NEtmMkZZRXVocHBLU2U5MGZ2MkVsVFRuaEpVYzNRNTVWOW9SY1ZOY2dHWnZoV184MS12dVZ3SXZVUTR4aWFOOFlOS1hTa0FDaUZtZDZFQWY0bjVIdWRPMEQweFNyZ3dkOUNzYzBrQV9pbzdPdTVMQ1Q3NGpqUUFCMG9RbHFqMmhJOUgtVmVzNGl1bzRKNExDdEYyLWdZYmE0d2xVV055dUNlSk1pSGVwdnc?oc=5</t>
+        </is>
+      </c>
+      <c r="F132" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>Supply_Chain</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>Here's how China's response to Trump tariffs silently rocks bitcoin - Yahoo Finance UK</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>Wed, 28 Jan 2026 06:19:00 GMT</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMijAFBVV95cUxPQjZ2T0pvS3FHbGlPN0NqTEdtOTBCMm1YaXplSEZLVUVMdkhuYlNkNVd0eU1PMXhXeGp2ZmlYbW9Ya3F1VHRKSW5qRzd0TmRHeDZYUUlxUzZUd2lfdU9kWF9XdXhvRFpiYUREd0lRRGtDNlBobFJ6cE1PdDVQcW1vanRoV19RdGd1VnBJeQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F133" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>Supply_Chain</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>Investec provides £11m Croydon logistics loan - Green Street News</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>Wed, 28 Jan 2026 12:38:10 GMT</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiiAFBVV95cUxPdWZGbjczXzJRTThhSkZmUHRBTFJ4R01QN2dlRXBsZmlmaVJaa2NmaVpjZmJtNnN0dXU5eW9BTy1CbTRNY0lxZDRUcU80Qm05UGVGa1FiQ201azZxNW95RXhFdmlWeEYyZzZNaDM2V2NxMEwyZ2xaYnZtUVljb1FiUlNoaHZSYkZK?oc=5</t>
+        </is>
+      </c>
+      <c r="F134" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>Supply_Chain</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>Prysmian: Managing Material Shortages in APAC Data Centres - Supply Chain Digital Magazine</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>Wed, 28 Jan 2026 10:51:35 GMT</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMilAFBVV95cUxPR19ocm5GZl96OEpaN3R0NjNiM2xMTURNVmNzZGRGNUY0cWwwbDNVN0FpMWUzMm50cTJSSlhYMzdzU3JqZjBPTC1obHN2cE4tNXRYd0NZS2hoMmNjeThiOXNUSWstQ1ZscDVMS2p3RE1ha2c3U1dxZDFvRURHS3hNYXNXUXV6UFl3dy1TVkRhTnIyeEJj?oc=5</t>
+        </is>
+      </c>
+      <c r="F135" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>Supply_Chain</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>Scotland-France ferry could relaunch amid £35bn Dunkirk regeneration plan - The Guardian</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>Wed, 28 Jan 2026 02:30:00 GMT</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxOZmw1YUY3M3JPcENyVTEteUZqd254R3R3aFlxTTFTTXRNdDZfekF0NlNWbXI4dVVWdVFFd0V0WlUtQ3pNM0pvOTNsMDQ0c0V0RHpNcVFLUWxTLU4wcDNyb2VsWmxRNDdJOHowSU5KWUZUSmhpNVUxVURfRVpvU2Q2dlB4ejZGQ212TjVYWTJyR0QwMEY2aHgwYXlQSEw?oc=5</t>
+        </is>
+      </c>
+      <c r="F136" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>Supply_Chain</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>Strong cruise performance and stable ferry traffic at the Port of Tallinn in 2025 - Shippax</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>Wed, 28 Jan 2026 07:24:40 GMT</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxQR19Sb2ZRMDZ1Qm80Q0dwUmFZUHJ5Sm5qRUZmWG9IeGNCVHRKTHIyWlN1UjJNY29obGtlQjVXM2pUbTVrQXA1OFNGYU9tVTdFX1Z3VWQ0TlktcnJkenRuS0gxdE9oc2VfQXFWbnRUeV9YeGZBVXRzMm53Wm92QVNvRmpNTGlEZDdwMlZYVEx0TzhNOUVOSksybkNjZTlXOW5KN2F6SjhvSDQ2TmZqYjh0c0lwZjZick9YUXc?oc=5</t>
+        </is>
+      </c>
+      <c r="F137" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>Supply_Chain</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>MGA expands freight liability appetite with new vehicle transporter policy - Insurance Times</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>Wed, 28 Jan 2026 14:32:56 GMT</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMixwFBVV95cUxOdlR6VDFJeE9lSTdxb0lLZjFmOWNZSHNZQ2JPbjNTYk43amF4N1F2RGc5QzZRd0ZkT1J5QWVwM1REQzZURTJoaG1LWXFybFZDMGU5MkdoRVN4emw2cTN3VlU3Ui10dFp6VWNCUFJyckRCd1M3TXBZb09VZF9wNEp5Z19LZjVSUGNCLWd2YXpsZE5uczYwWUhIZjRUUGhlNnlyVjQwRjl3c1hmd2RQaTlUWkg0dTYzZmRPeC1tVF9nb3hJb0l0XzZv?oc=5</t>
+        </is>
+      </c>
+      <c r="F138" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>Supply_Chain</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>Edeka Turns to Voice Tech - Logistics Business</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>Wed, 28 Jan 2026 12:28:40 GMT</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxPN043YnVMN3VYRlhQVUR4WExxTm9MNHhlRXlIZ0hreS15Q2x5c2FmcE40alRNT0o4NEZZMEVtYmRXTW1kcFJQemRnVXdUWTlHTDJneTJSS0FEdTFfNHNLQmpkN1c4ZEZQZTVTMXVWTHRmVWxDVXlncWRLT29mcWxPNjdRTHliWURBYlVSSmYzaWU4VERLUlpmaTNkRQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F139" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>Supply_Chain</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>EC initiates steps for Google’s compliance with Digital Markets Act - verdict.co.uk</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>Wed, 28 Jan 2026 09:17:55 GMT</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMifEFVX3lxTFBRZllVX2RIU2prbmJwUkVwRExYb0tBcHlQOUFFeWcwcWhMS0FQaVJ6TzZsSnlIVHFuUzEwSWlrZjZ2U2NDdUh4dUNNbGszWThLc2l0elgxYmowLXZsalFydWFfWlVtLWhhd0lPV0dkc2xOUVRkeVBuMzU0TXc?oc=5</t>
+        </is>
+      </c>
+      <c r="F140" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>Supply_Chain</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>Technology ‘Business Case’ isn’t a Strategy - Logistics Business</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>Wed, 28 Jan 2026 11:58:51 GMT</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxPSXVfYnlRSXcyZ2JFamlYdENCMGFVUVZFY3F3M2xUNEl5WWpiVmJlVnpFd2RiRVNHQ3VzTFNLSm02RFc3YjZRM01CSmJYVy1KTWVNR0VaTTgtVFBYRTRYVnIyV090UEZaTGFGbXJrR2poVkFkWW5pd0tseDJ3SWVHT0p2WjZUaEtHb196cWNCaTc?oc=5</t>
+        </is>
+      </c>
+      <c r="F141" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>Supply_Chain</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>Top 10: Supplier Collaboration Platforms - Supply Chain Digital Magazine</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>Wed, 28 Jan 2026 11:39:46 GMT</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiggFBVV95cUxNS0JrZ3pWNk9LeUoweUVNdkdacHo2UFY3ZTUyaHNJLUhhRDhGSWRoQWN4UXdaeHdnYUhJZ3Jqc1RKaHpxdkJLX2VJZU5WRFl0Yktid0NlTU1jcjREMzJtN200MmVzd0t6UVQ3NzNlVWJRUVNLT3ZsQ0oyYWFBVDdQQ1Zn?oc=5</t>
+        </is>
+      </c>
+      <c r="F142" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>Supply_Chain</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>Exiger teams up with Snowflake to bring AI-driven supply chain and risk intelligence to the energy sector - Industrial Cyber</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>Wed, 28 Jan 2026 08:18:35 GMT</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi1AFBVV95cUxOWGs0RkpTcklGc3lmWUNka3BJSmx4WTUtLTFBY29UMUg4SE9PcmhVdEdNUU5oeTdwSlVlRURPNGh1S1AxQzVUOFRPbDVmaWRLaUJnY1dGRjBqcjM3ZlNlNFZ6YkNja28ya25fd1RRaGVKVUhPVzNmNHV1Z0pEaEliRUw2bFpLenpzMEwxcGVnYmZzaWVDSEd2VmFtdkhndGFNUjkzQ3U3TkJUM3pySnZkY0kzUzdxNVZHNmh5S21uaWkzN0FuQjJHVzllWW5faHJRUzczdg?oc=5</t>
+        </is>
+      </c>
+      <c r="F143" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>Supply_Chain</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>IEA examines warehousing needs for stockpiling critical minerals - Logistics Manager</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>Wed, 28 Jan 2026 12:04:05 GMT</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxOcTV2RmlLUkpyRzAybmVJNzYyN09aVENGX3VXcWRLbjdXYjdFcTRacURWTzctTnc1RkM3VkowQUoxUlJXcHF0STlQd2FsRExHemNWNFRIWlpqV0R0Q0k3VkJZWlZ2ZDZ6ZDA2a0loV19KaEFUZmlHYVo1eUVqQTlXdDVsYkdmWWZISWdnN3dldmViZkhSRE1UTDFwenRtSTg?oc=5</t>
+        </is>
+      </c>
+      <c r="F144" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>Supply_Chain</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>Stuart reports 97% compliance with age-restricted deliveries - conveniencestore.co.uk</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>Wed, 28 Jan 2026 14:36:49 GMT</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxPZVg1X21GYmlkSExmUXBhYksxbFhfaTM1TTFwZENtdndidHFnRFB4U1lLTjRockt0VHY0d2hMZDU4eG10RzhRTXNYb2lxN3JPcnJhTmxJSVZzUTRpcU5zVExTcXpiY1FPVDZKMGZBdmo0WUE2MGR4Wkd5UUF2QnY4bE96U0xkb19EcnlnM1JhUUZlTnVfeHYtRElaeG03QWl4T05qbURfc1hIdnNBOUxhb2k3cHhERW5Samc?oc=5</t>
+        </is>
+      </c>
+      <c r="F145" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>Supply_Chain</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>Software provider announced for new cargo terminal in Vietnam - Logistics Manager</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>Wed, 28 Jan 2026 09:00:40 GMT</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxPaUJkOFNIVDVGVkkyZlNjY1BwZjlXZWo0bk1NeE5PUEx2dkNGMjRGTFJnbjFESk5pazJZcElySFdSYXFERkNmQkRiRWlTRVpUbndVWWhlUUNCZExTOTVqbTV0Wm5YdG5RZVg2Qkp2X0phelQ0amNiWU82b2hHLXc1Zm1IQVM0YlZvcktUSC1ZVURIUVdlQUdxZGVTdw?oc=5</t>
+        </is>
+      </c>
+      <c r="F146" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>Supply_Chain</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>Credit, compliance and cargo - Air Cargo Week</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>Wed, 28 Jan 2026 08:36:28 GMT</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiY0FVX3lxTE1zTmpncVJhVEdmWU5XTEs0eFR1ejFSMW9mV3djRVdGUUotSHdTamhBaWJibGhNeFNUTGlPMFk3bDIwSl9uRmRhUVM3c1FuNTA2M3ZzRW5ULTBHVFRkVHZDMjNDUQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F147" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>Supply_Chain</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>Port of Tyne Director to lead Harwich Haven Authority - Port Technology</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>Wed, 28 Jan 2026 11:05:49 GMT</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMilAFBVV95cUxPQTd3SkFXdlZERzlkcjFGWUJMaHhfNEhMTVl4VHVCMUFYUkJSN1pLei1Ecng4TnFIUG9lVmQxYkkwNU15LUFEckpPUVBRVmlsZE82eXF2QjA3bm5zcHJKaTViMVB3N3FyY1Y0UHN5SHE2MnBpanRhZWJkclZLcHAzVkxCQ2ZOVHcwamxfX1JFVTZ6aFlH?oc=5</t>
+        </is>
+      </c>
+      <c r="F148" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>Supply_Chain</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>New freight vessel begins sea trials - businesscornwall.co.uk</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>Wed, 28 Jan 2026 12:25:08 GMT</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxNeE52SlFOYUNtMTQzZTlvMHQ1YmJaTEZZV3JuRVhjb1BVdXhhcjhqelFJeEVxT003MWJ0R3FoMVVZTGJsQVJjOGRMOE1QNVNuMDRmeENlaTRlcFRuUm9ncU5CMVE5MTdZazhxR3NsQW9XYjI4a05NY1pjajlXV2Y4clVaZng1VDUtdnZWYV8tdjZRcGJkQ1FlYlkyb0ZIZFdYSGhNTHdhV2lEWkY3SlVJRGxwWmxrSXM?oc=5</t>
+        </is>
+      </c>
+      <c r="F149" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>Supply_Chain</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>Sustainability award recognizes value across the full supply chain - NutraIngredients.com</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>Wed, 28 Jan 2026 12:11:01 GMT</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxPSGJpT3RUSlZIc2dwSU5jZmlUSnN1SkhFd0RfX201elIybmZ3eUFscUVUdl9ZSGhkd2Q0d2dFcHU2Ti1mX01TeWhVcDRnbjFrNkRCd0tqRkM5bXJ1TTdicDhIS2stWE82Ykw2cEFzWEFXZWZRekVZRGxMSjNmYjBEd09iZTZjNXdGUC01UDhNVzJET3ZRMTBhdTBfdHEwRW5QbEpRTG5RV045M2NNVWdYQWRhcU9scUFLZWxV?oc=5</t>
+        </is>
+      </c>
+      <c r="F150" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>Supply_Chain</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>EU steel defence: Tougher tariffs in, Russian steel out - ALDE Party</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>Wed, 28 Jan 2026 09:43:52 GMT</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxQU2g5VDlTRmJXMFlHSjFjcUlEOEVDdk9Cb0NRNUhrZ3UyS1lHSkhLdDVYc3hlcXNoVDFVUHgwdDZzMU12bkJzdFZzRXpLOHJzbWNQX1ZpaEJEam5zTktlYzlrc2ZzMWRCdm4tOU1nXzZrN1dNaFZtbHJuV1hldjRVaWU0cEEyNHlyUkI4OURkbEVfeDNGY1FyZU5lUQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F151" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>Supply_Chain</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>Tax Disputes: HMRC compliance, key risks, and upcoming changes - KPMG</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>Wed, 28 Jan 2026 04:09:39 GMT</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiY0FVX3lxTFBkQURtRVZKMi1HdFA5bDk3eEZxWGNKdk51YU9QclpIYzF3cG5LWmFLUjdpcWpGcndHNWxrSEIwSHBXbGJ6WV81YURsU19IMUtMQ0NoS04tVnVGWFJPdTZ4Zk84VQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F152" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>Supply_Chain</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>Weak EV battery supply chain puts British businesses at risk - Environment Journal</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>Wed, 28 Jan 2026 08:03:56 GMT</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxPVE50X2VlMHluNkVHUGFtVU5hQXNWaUpDQmd6X2dkX1VLRmlyb2hJc2gzd2xDYmQ5UDRjZXNzVnZZV3VHUk9STE9CVXdxVTRUU19aaHJXaEctOGJ2N3BPV2w3U09KalVka0lXUmFwTlNScDFfUllWdEprQ29uRHI4aTl1QnZrSGVueUFQVnNicW05dW80UlhkSkFleTVtTk5Ub09reg?oc=5</t>
+        </is>
+      </c>
+      <c r="F153" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>Supply_Chain</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>b-next and Behavox join forces to advance capital markets compliance - FinTech Global</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>Wed, 28 Jan 2026 11:16:17 GMT</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxQOGlLdEUtNjBUTW4yRTNUdjVVdEFJTWhQZC1VTHpQVERRQTR4ZHFDeG1CX1VIZDZoRnNWcFVxSTJzUE1WTXN4eTM4RThQbHZsZU1MWDhxTXl0aGxQRldfVmx3WGw1QTJ0YktwaVgyWVNBVUdnTUxHTHo2S1VIMWZySXlwaXEzR19TT0tKS29IR0x5dm8zdG9nQTZXZWd1VUpFbm1DYXFB?oc=5</t>
+        </is>
+      </c>
+      <c r="F154" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>Supply_Chain</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>What is the Cause of the Supply Chain Confidence Gap? - Procurement Magazine</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>Wed, 28 Jan 2026 12:29:31 GMT</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMic0FVX3lxTE1TcjNlVmZ1M19zcDVQcGZ5bFZFNDA4R2ZxNWxUaGNneGVYTkRSTVVac2JMUXlWeHJmZEZyNkQzOHN1cGFpWG9LQ2NycmRSb2hjTjBIVnp3ZFZlWTZLX1lfNUJCOUp0MnlXc2o1LVlvWmlQNDQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F155" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>Supply_Chain</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>European road operator launches U.S. coast-to-coast freight - Trans.INFO</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>Wed, 28 Jan 2026 13:27:13 GMT</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiY0FVX3lxTE5STFVxZFIyamZETU1TNVVfRXNQSExvMUFvTUxaUzJIdTRET3ZfOHRjNGVjQVgyMnRNaDhQVGk3am1ESUhyVU8tdDctenE3dEkzMUlrbjFiTjZ1enRycVJzMV9hbw?oc=5</t>
+        </is>
+      </c>
+      <c r="F156" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>Supply_Chain</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>US to Ease Venezuela Oil Sanctions to Speed Exports - Offshore Engineer Magazine</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>Wed, 28 Jan 2026 08:57:59 GMT</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxOYzB0WWJEQ01EQzlxVlZZZzgwbEJpS3lwOE1aRVotY05mSTJHVTN5RW5GMEtJVEMyWHdVMFBiMUozU3E0ZXNaYTVHZDI4Y3JLUzU4RDQ5TXN1M3VlTDN3d1BscVlPbG9BZVRiUGlEUWc3amYzaF9wNkRXTDdYZXRrcV9jQ193dlBwd3hRNjJMZnlVdGM?oc=5</t>
+        </is>
+      </c>
+      <c r="F157" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>Supply_Chain</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>Moving sustainability compliance beyond box-ticking - Fruitnet</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>Wed, 28 Jan 2026 09:25:12 GMT</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxQRS1hVDRZbFlYb2VXeEd5a3NhUlpLOTduTVJaaEJwQ0Z1ZlVZY2tDUlI2NURPMHJTMWRtWVMxRy1pZmFLTm85ODRrdzNqNU1BRVlEMDl2WExEaC12R05aQnhvZ3RWWWJQdFlacXNuV0ZPYzBuYlF3el9DdTNnLVprXzZmbW1oNnFFMEIxdGJHZlkyTXNLRFR4dEtZb3g4elNoQnBj?oc=5</t>
+        </is>
+      </c>
+      <c r="F158" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>Supply_Chain</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>2050 Port Vision officially launched - portofrotterdam.com</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>Wed, 28 Jan 2026 08:02:32 GMT</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxOVm1maWMyM2FpVmlTWTNCclg1UWM4aGI0blNHNVdqV0dxdVhkZVQzSDY3UDZnN3dFMGJ2VjNvVDJQenFCZHpxbDhaeGR5eHNIZF9SM2JicnV1eHRnbjZMSjhBa21ybXBKOWVuRnJWTWE0N0h5UnNRWnJjMkN4dXFUY3gzRTVNOUFjay1kbDc2SEt4VE5nNTBMMGdiUQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F159" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>Protest</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally OR tactics OR targets OR groups)</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>More 'No Kings' protests planned for March 28 as outrage spreads over Minneapolis deaths - ABC News</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>Wed, 28 Jan 2026 11:09:27 GMT</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxNWGlGcy1ub0RtU2REQzJreEE0ZlN2OWhxbUEyamxJenVIcmtFZVhZcDV3cE1LR0drUUN3amRrMFJ1c24wQjkxQlpGTmpqRmFqTUhwcTRzZ1dkNDBoVnVxcXA0X0ZNaGtHZzcyS0d5MEpZeEtIY3lTYkFRQm9ma2QyRXBmS2dEVDc3UUhBaWlEZldqZzQ5bHBrQ3NLLXRrUlk1MVA3eldORUTSAa4BQVVfeXFMT190cXhqdE9NOWlJZmdFSk5IQzhtUWNwYU5nWHpnVmlfaGlJUFF2aUptY2E3S0s4anNWYVEyVWpNckpOaXh3MXVCc09IekpTUTJvTmRJTHVwVkRoU2QtTzVtRUxTMlcwVkxVUU1wV2tPLWtHQ0xxeU1vUF9hTk56dW4wbWJPZU9FTUpFSXFxUGx5cWV3S2c4X0haUGZneG9uX2ozTzdqSXpLeFQxSDZn?oc=5</t>
+        </is>
+      </c>
+      <c r="F160" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>Protest</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally OR tactics OR targets OR groups)</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>Police throw child to the ground during Rojava protest in Mardin - Bianet</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>Wed, 28 Jan 2026 11:18:00 GMT</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxNeThwdHAtbjg0eFprWG5vX1BVS184RW5vck91SG9ISWJrRHNackVJMU4ycDBYZWNxV0hKYXExdWRsUzFLZm9YUzNhZEE2V0NVMFM1b2RtRHI1ZEhwY1lJMko0YlNXckhicXFBdWRhREtHSTVILXFONy1lQzdGeENXX05QZ1FlZHlUZ2pHTXNQU291LWdYM1k3WUtSa3M?oc=5</t>
+        </is>
+      </c>
+      <c r="F161" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>Protest</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally OR tactics OR targets OR groups)</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>Thousands rally in Serbia's capital against crackdown on student-led protests - Yahoo News Canada</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>Wed, 28 Jan 2026 08:14:59 GMT</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMihwFBVV95cUxPWHczMlJJZUwyNWJGekxGSzlvODZCM24wWkwyNUhpTmp5SlFBZUhpNEctM3ctS2NZNF9FS1NWZmczdmpsQXR1ZlRjM2YtRExHenRGbWx5NkEwaEcyNVMxV0VJclNpOVZpTk9MRXEyMnFhT1h0UnpiajVtSTJTYWtmbFRPLXEtX3c?oc=5</t>
+        </is>
+      </c>
+      <c r="F162" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>Protest</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally OR tactics OR targets OR groups)</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>Heavy police presence as educational protests escalate at Addington Primary School - dailynews.co.za</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>Wed, 28 Jan 2026 11:08:57 GMT</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxPaGszeWdzNklTWUdrNkdmMkJRaEE2aVpuUTMwdlNRTUNmM1FZMHpKR0JpdlZQMXYxRFlKOEJxT0RvTmw0NTJ6YWpUUVlOVVNRZ3ZvZlVHaVJuNTBGQm5uS2xidllmVkd1cUJKYnIxLVhSRlZPRTVhSXZEOGFiUVJMNmRXck54d0gxWlYyeHhDV3RFeVZPWlpha2dReXZSSFVPYkVFR0h1MDNlOXNNdDZVUWF1ZnJDNzQ2YXlWRHF2TXM?oc=5</t>
+        </is>
+      </c>
+      <c r="F163" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>Protest</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally OR tactics OR targets OR groups)</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>Car driver fleeing police strikes SFPD officer in Oakland - sfchronicle.com</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>Wed, 28 Jan 2026 05:05:03 GMT</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxObVgxOUlTeUFUOGNnem55SVRCMzBhSWE3VFhpMjBWYkRKQWdKVThCTTRvM1k3blFoOEE4UHk3VXRPR1prbEx0VnBvVW03QWJEMWxhQzRvV3R2NnZHNlNDMGdhVlY4RnB6N1NfZkZUZVI3UUkyQ1B0ejlwS0NJbmxKQkE0YnF3TW1hN01oV3FYcGVnVFZ5UnplcVZMaDJkMVU?oc=5</t>
+        </is>
+      </c>
+      <c r="F164" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>UK businesses and academia eligible for new EU funding on AI and related technologies - EEAS</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>Wed, 28 Jan 2026 12:13:30 GMT</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi0AFBVV95cUxNMnVMcmlCSlltUlYxb1V0ZDhFQjlWSzJrdnBHcXEyMEFYYnFaUjBRcHdsem5UM0lXNGo1TmZCRTZwb1hXMDBGVDFsOTVsLWRmVjk4QWRmdEpwYjFjR2JKcG9hbGtoNVNudjNhZno4OTRfQ3hETkNMTC0xczQ5S3U2TGU4b0EzZ3ZqODVNbERTRE5KTVRPSDVCY25jUGg5NjdzQUJxRzR6bWtrNllabHN6cnA0dGtDbm9VUWFXRXlETjROa1ZXaVJQLThoWTVlYjBa?oc=5</t>
+        </is>
+      </c>
+      <c r="F165" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>Briefing: AI and immigration law – what guidance is there for lawyers? - Free Movement</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>Wed, 28 Jan 2026 08:34:09 GMT</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxPRGl2SnJyN3lNbUlVdDE1eW1Pa2l5bHUyNjFJRTVWZnM5TUVtRDhyWnFkN012c2R0VE1kZlFucEI4WmlfUTNpT3FQdDdPOTRNZVhnNkpvYzRuTUhTa0YwT0R6TnJIYVpTclgxUlE0VGVpVktMb1d3Nms4c0dpYXN0alhZU3FsVlgzWEZib05EMFhEUDBTbzlDanVTaw?oc=5</t>
+        </is>
+      </c>
+      <c r="F166" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>Government appoints Mike Clancy to new AI and future of work panel - Bectu</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>Wed, 28 Jan 2026 10:13:22 GMT</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxQVzQ2alQzakhUbGNscHd1YzlFUUpYQjZabzFldG5nT0tnVXVLQ1hfZTFoY0JJWHpSRGs1d2RKSGUyaDY4UkxCMlpJQUEwamljSlBaN1FuUkRZWTExcEJSVm1MNl9QMVhIY3I4dHllbUJRS0pKS0lia1g3VDViNUtKd1ZkSF95SENqOTJJYmpjT1RQeDdSRnRV?oc=5</t>
+        </is>
+      </c>
+      <c r="F167" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>West Midlands AI and coding trainer to open new Dubai base - BBC</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>Wed, 28 Jan 2026 06:05:45 GMT</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTE1XN1BWU1ZLb24yclpFYnFDdmJwcHVXclBCb3EzLW1TZnRVUUE4OHpldEFPTFlobUpjdjBHM0NuakdnMEJyR2oxMjBHZFJPekFNU0tpVXNuMm9QUQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F168" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>Omdia: AI and Micro-LED innovation to shape professional AV at ISE Barcelona 2026 - Omdia</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>Wed, 28 Jan 2026 09:26:44 GMT</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxPaTlnbEdKWnJJZldMWmpPUjNuUUstcTQtODRIVXNzNVBhYVdPNVNuYkN6NXVwT2YzRkJDMTBPdmRqM01seV93RFQ4dXFleHFvcmZVbGNjcjk0RURja09iR1lNRk42T2hvOGFSVVRITExIUGQ1WVprN3JDR25ocnpfUEF4NWh6M1BKNEdNUTBsN2VlbklMSnlScmZmYmNKektFNDZXSzk0RTBobk5SekVsdUtZT1lnWTBx?oc=5</t>
+        </is>
+      </c>
+      <c r="F169" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>Privacy, AI and the need for a coherent global baseline - IAPP</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>Wed, 28 Jan 2026 14:36:24 GMT</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMihAFBVV95cUxQWEF1TWN6Y3c0a1VfRUIyck5rRU85M25GR0xVZHVFZkJIbmhQbDVRQjdaRDZwVkh3Zi1IaWhEYW02QzR6dC1hYUFPeHhTNnBfV3VDZHhqMWwwUEE0dUVwTm9PSXZlV3VlcWozU0hrSkE0UkRCbGRId1FuaEt5LUhwb3BpRHU?oc=5</t>
+        </is>
+      </c>
+      <c r="F170" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>January: New government-funded AI scholarships launch at the University of Bristol | News and features - bristol.ac.uk</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>Wed, 28 Jan 2026 10:20:09 GMT</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxQSTZDMTMxaWxwS1BvN0x5R251RkpuZ3RCNjA5RENKZ2pEWjZFQmJjZEo1RzRxbkNOQzNXS3Q0czBIcThveExNb2NWdmlZb1Z1X3prRFNISk4zdEVqMnJKelhLZG1fWjZUZnIyZnZGRkFlOHA5Z0xtUS15Y3FsWjdEQWxEcmN3M1dvdVE1Y1NvU0Z1TEE0ak5zaXdLalpqZ1RFZFR3UEZnVERma2lIZkFFYmpQdXZKMmNHcF9LcEdWSQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F171" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>Almost two-thirds of charity job candidates using AI when applying for roles - Civil Society Media</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>Wed, 28 Jan 2026 12:51:25 GMT</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxQNnN1cWNOWWlvQnhmbkxPTWFKS3Q4N3YtUkxBQjBlTzI1OFlQYjdJQ0FXZmhoMWJPME45WXpfQ2JyaFVoNmR6RTVqbUVHTzV4OWlIRThVUkdlVlJobFRZV0FNTV9wUnBEMVQ4U3hFZ2hzNE9NZ2RDOG9pRFlWN2h3c1NEMTVzVUhyc3hMejFveGpEanhienE1Vk56OVlEU1lYT1ljRUQxZ2VzUEFleHZnNHFxaklxZEUy?oc=5</t>
+        </is>
+      </c>
+      <c r="F172" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>AI and robots join forces in NHS trial to improve cancer diagnosis - Digital Watch Observatory</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>Wed, 28 Jan 2026 11:41:38 GMT</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxOZFpvLWEyVzhCSHdXck8zQzd2MGpXU0d2cFlDelhMbTJNanFnWi1BblE5VzdSUHM5bExHRG05MzB1RF84czEyNEpDemhldEVzZ2MxcWdQQmQyWkVObWJuU3JXVUc5YWlZVUl2THRPVzZ2NlQtN3Bqb2pCaktDY3JGcU9CcndVSm1hSnRsc3FnUjNwYXZ2el9r?oc=5</t>
+        </is>
+      </c>
+      <c r="F173" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>Webinar: A guide to creating ethical AI-generated imagery - Charity Digital</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>Wed, 28 Jan 2026 11:41:03 GMT</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxQOGZMMjhzUDdUZU1NZU4weDd5NGJWbzdwaUhaVXpmTjJvMkx5S0lHSFJzVmloZzBiSWxUb3c4T29lZkZZSFZXSE9TOFhNLWJjRG5aVmVheENOd0I0UG1ETUVjSC1uSzloWW5tNHNlNnR4dXFrbGdnS0h1VGJpNm1HQjhSZGlmSWJsNjhiMzlzRElSUEVlZjRZQllNQQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F174" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>AI, London shorts and artist filmmaking at LSFF - Film London</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>Wed, 28 Jan 2026 13:03:30 GMT</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMihgFBVV95cUxNQmczcUpHSmlVcWViVU8wRFpmSDVYRzZOVzBzc2djYkdnQjFKdHZMLTB0bkUyU2tPY3FEVUVLLVFVR21HS1dfRW9GN0ZidmxEazBSNVpaNlg0WUo2VzF5ZHoySy04Z0NZYzhpT0lPSjc1cTlaZG5COGVGd3JBbDNUaUoxZHZSQQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F175" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>Data resilience &amp; trust seen as key to safe AI use - IT Brief UK</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>Wed, 28 Jan 2026 08:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiggFBVV95cUxNR01zNzlaTEJiTlp4VndjQkNUWXI1Rlh6Vi12SG1Sa2NMNUtEM1diNmZoVmdCSF8xN2Q3V2xwREtZZXUtNjduU296ZklqdDBRNUFQakRieThxdW9WTHo2WmF2ZUFHVkVKUWxmM3FGZk5zVjkydnFOWERnWG1mclJaMzBn?oc=5</t>
+        </is>
+      </c>
+      <c r="F176" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>The Typewriter Repair Class, AI, And The Next Stage Of Jobs - Forbes</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>Wed, 28 Jan 2026 14:37:38 GMT</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxNMGp5WWo0MzBjQVdfd19WLVB2NjQwcDhOa0lYM2ttS09ENzBQM2hEWC1EZ09RYVAzSTdUcEdfdjZRSTZ3eXFCemJJYzlTQTl2SEszNk4zODJnZVdTMzA2eHdrSHFnYm9RMXZmYTdwOFJEWlVHOURYZmVWNlM0ZkpiR1hTMGtzRktVZ1dfNlNBa0s4Nm1HRUVzWlpsd2RFT1V6aFV2RFFkNkVUb1p0dWFJOGt1bw?oc=5</t>
+        </is>
+      </c>
+      <c r="F177" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>Security Orchestration Automation and Response Industry Research 2026 - Global Market Size, Share, Trends, Opportunities, and Forecasts, 2021-2025 &amp; 2026-2031 - Yahoo Finance UK</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>Wed, 28 Jan 2026 09:16:00 GMT</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxPelgxV21jdnpONVBsVkRMQ3c2c1QwRWRpQjlla0pyYnhqa2hqaldFUVhZMmlDRGdoMzZ6OHBiZ0VvNnplOHVGMEJUb2RSN3ZnbVZNT211RnoweEI3Qms1ODNWX1hWYUY0RGN3VzBSYnp3Nnk5VjI4UFR2dDc0QWFtRk8yT1U1emJEaGdyM3pnZkhnVjVIcUZ1Yk1YWXEwblpreFE?oc=5</t>
+        </is>
+      </c>
+      <c r="F178" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>My daughter deleted AI - and so did all her friends: the TikTok trend convincing Gen Alpha to push back - Prolific North</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>Wed, 28 Jan 2026 07:26:00 GMT</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi1AFBVV95cUxPMVJoQ2RjNjk4dDAyMFpmVXVuYXpzaUFuU1hnbDlTakxaVHdHQXg2TlRuck82ekoxYk9HNHhiLVFjOFpoMWdIRFUxQVVfSWZhamFTMGV2NnZxa2k0bV9maTFCWGZweG55dS1CaHlUM3hWWC1EY1FTTThHQ1B5cjBHd0xQcDBPZFlvRFZuYU11b1YzQkhiRUVnREI4LTdoZ3pVMUVWaEE5ZGJzTXJ3MFNwM1pUT2RiNnlJQW9iXzNwTkFrWUMwaE1ic1dMTDQ1OHgxb3ZSZQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F179" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>Microsoft Preview: Azure, AI, and a Test of Growth Quality - XTB.com</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>Wed, 28 Jan 2026 11:35:34 GMT</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxNZmFpRGhJWFJEWFNxUUV4WTZWYkdST0dNaG93clFxLWwtUHNhNHJUMHdXakRjUWZ3TTl3dUdsSGZOM0tDNmQ2d0xVcHlnV0NMZEFfRnhabGxRbHNPSHFERGMwWUNxS2pMbFRXQjF6ekw2X1k3SjJfZ3BwMENQMmh6XzFxZzhObnI2MDhaT2RvRHg2UlBHYTh4UmM2Mzk5U3UxQl96alFhR2NwZlhNbkNrVVN3?oc=5</t>
+        </is>
+      </c>
+      <c r="F180" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>How Gen Z Uses Gen AI—and Why It Worries Them - Harvard Business Review</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>Wed, 28 Jan 2026 13:12:03 GMT</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMieEFVX3lxTFBDR1F5UVlBUjg4LWx6T0pUNXBMWkdLMzdQeTEteWkxcDZoLWtqVjRaNWxIQTBQUnVobnFuVFpER25KNVF5a2hlMTRKeHBZUzNWWnU3NVpjeU9sbHlldVNTUVBBQUlyTHluTW1DVUFTXzRrMnlMN3YwYg?oc=5</t>
+        </is>
+      </c>
+      <c r="F181" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>The AI Impact Report 2026: Avature Finds Gap Between AI Investment and HR Execution - PR Newswire UK</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>Wed, 28 Jan 2026 14:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi1wFBVV95cUxQZDd1N3lNVTM1bkFKYlhPVEZJLUZnYVZjVllsa25fanl6T0tzZGRfUjVieTZIa2xGS1hMTkF6cFRtLThVcExmVGlmb1NObFY3TzhJYjNiMUR4NkdYWXlLMkRGeVJmV0pYUmZrdmFmb2FYbXF2MEk5b1pzMVMyb0QwWHNodGRkMGtHdGVNUjNfM1JiSng4M3N5TEFJalF0ME8tMUZnSERWNjU3c0JZakFrU1RIOHVmbGkwekw2RG15UUlkbEd5alNNM1RKVEhJcHpPWkZRTDdsVQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F182" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>AI as a Supporting Role, Not The Headline Act. - UKSPA</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>Wed, 28 Jan 2026 13:18:44 GMT</t>
+        </is>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiekFVX3lxTE92WFFSSHJrLVF5Ti1PVl8zTUNkbm1hOEJETHlSWFh0dE1heWRZZEs3NEJmSUxLMlVZU2owZTdzX08xZHdOWDh3VkRuQ0JYbk9HdEk4dGdQTjY4OExzTllLb25KdVFPT0JGZm14VFk4TnhvV3hWbHBSUGdB?oc=5</t>
+        </is>
+      </c>
+      <c r="F183" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>C-suite leaders lack AI competency, survey suggests - HR Magazine</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>Wed, 28 Jan 2026 11:00:53 GMT</t>
+        </is>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxQZmI5dEctTmJJS3VkRmFURF9wXzFvN2tqbk1GVzFnb1J4dWJld0ROLXFFbE5SZFhjaXgzeHJNSWJ2RDdBaHZkOHU5UmZtb1pXUHpVZmdUOVpYUVo4dFlDclFsTWhmV1ktd1NfVVNiSkgwalZKcW5SWFVsemlnVjIxdEt6U1RUUXphSGR6RW9SOXl4Vm5PaGpv?oc=5</t>
+        </is>
+      </c>
+      <c r="F184" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>ASML shares hit record high as AI demand fuels orders - Financial Times</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>Wed, 28 Jan 2026 10:05:37 GMT</t>
+        </is>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMicEFVX3lxTFBsTkdNaGppTlc3Y1g1aXFCMi0xb0dhY1E5OGdWc0tWNVlrVmdXTE9CTE9uRUF0WnU1VHBSRVdYaVRjV1lZU0tHenBDMmRncUctVzV2QzhNaVNtSEFTaTN6alhnX1FXbmk5d1RfTk9wenQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F185" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>Doomsday Clock ticks closer to midnight amid rising global risks - Engineering and Technology Magazine</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>Wed, 28 Jan 2026 11:59:21 GMT</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxQRWZmd3JZckV6VHVCR2stWXNhZDBEc052NC1KWW5va09DSl9LYXhYTmNCRVRDYkV3a1dVaFVrakJTWWdSbkM3QThwZzZYbjlIenBaSU05ZmVNVXAtVFJaME9HNG1nX0RFWExiVFEwRXQzTmczMmlfai1uMlQzWWJ0TGtsMkNVLTdTUUoxVXpUWXY5QWJPRFZtbnJkSU43QTdfOEdGdFJkUjlTOWhRUV9PYzNGYno5THJaNXN0a1FUaXE?oc=5</t>
+        </is>
+      </c>
+      <c r="F186" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>Amazon axes 16,000 jobs amid push to replace office workers with AI - The Telegraph</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>Wed, 28 Jan 2026 12:09:00 GMT</t>
+        </is>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiiwFBVV95cUxQcmxjMnVwc0Q2UndlREZzTlBESy1JVFphaldZQXdFRmRMZHNOUnM4bm9WSWZoRkxnSkRPRWsydEE3VzM2VVNERldSYjhLckwzNHNHWHk4ZHl6REhkVTNXamg2NEc1cmpCV1RieDlXcG5EVUlnaXNPTzRUUnBLcjF6eDZtN2U0S1ZlR1NZ?oc=5</t>
+        </is>
+      </c>
+      <c r="F187" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>How to Communicate About Quantum Technology — Science-Backed Tips For Talking Quantum - The Quantum Insider</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>Wed, 28 Jan 2026 12:54:30 GMT</t>
+        </is>
+      </c>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxQb3doYzF4ZDdMb2o5ZGtvSmpuQ2QtSmw0T3REQzk5RjRoMk9uRElpVzFmanBUdVl5VzVPa2otSG1fYWM5cG1KZ20tUGo0OUE4N1RrcXZCRFlpMlExeTJaUjhLOHRIaDVXY0h6SGtBV19GT2VPSWVNY0FpRGhqclFHZUdqNE1CZHJrMVRPNExOc1hnNVZSSHdQZjZVS0xrQU55SVZvdXNGTkFJdlgtSmkwYXg5LVNrUUZETFQ5M0UtYzc2YUk?oc=5</t>
+        </is>
+      </c>
+      <c r="F188" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>Claroty Team82 reveals critical RCE vulnerability in IDIS Cloud Manager Viewer tied to spear-phishing risk - Industrial Cyber</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>Wed, 28 Jan 2026 14:36:06 GMT</t>
+        </is>
+      </c>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi8AFBVV95cUxNaVp0MGF1SVNCekRvZk53VTJWeHB5bjUxRkpDTWlVTGFqVGpWaVNkNWJGbzhQR252MEJONTNMaURBenBuVVN3dE5FR3Z6OVZCV0Q5UFhSTmtMUkFZY1dkN0d6X3ZUZGVSTzQ0eHEtUW56SnNBblZ2aGJpSTk0RXVjblQ3MGFXZDBYa1VXZmhURkZ6OFF0NEhFOXVBSzFMcGRmLTZTUzQ1WGdFazlFZ1lCbC1pWkFhR25WUElCYkJITnlId3ppal92UWxNLU1QQTZhSkYyRkk0OTZuNzc1Q3QyQ0JybUl4YjREV1Z0VTRhWS0?oc=5</t>
+        </is>
+      </c>
+      <c r="F189" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>Made Smarter prepares Yorkshire manufacturers for AI future - Machinery Market</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>Wed, 28 Jan 2026 09:18:05 GMT</t>
+        </is>
+      </c>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxPY2xfU0VPMDRmVldSYWdfVnhCanBpVzZHQXdoS2NlQmotUnFkMDBQWGhuZVZGbFdVSlV2MkMxQ3RsMGhiYjQ1WXBzY2FJSDlLYTNCWHBiZXN6ZnVvS1dtelJiMXVZT3RsZERseTVtaV85UWMtMGRPMmZOeVFMYWNOS2RWaFNSSFI2OW5vbnZYOTR4YXBDWEFmVGY2X2FfLW1fZmdmbkxROVY?oc=5</t>
+        </is>
+      </c>
+      <c r="F190" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>Digital careers report - software firms tackle talent crunch through collaborative resource sharing - Diginomica</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>Wed, 28 Jan 2026 09:43:54 GMT</t>
+        </is>
+      </c>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxObUFxd0s3QnZTdktiT1pEeHBSdVFpSXdjb2xnM3BlMUViSkFzUE9Fel9seDBvclJ3U2ZZc192VXd2a1l1cWh5OGdtMThfMXQyd3VBeFZCVGQyUUFDbWZHQndQZE5HVzVqTkZkZXZReXh1UV9aUG5jRUpOZ1hfaW5nTExBeEtWQzU3VjExYzdqN3Q3czZHQ0JZMmw3Qk1mc1h1TWxPdkxyZFZRLXYya3VLZ3ZISEd1dk9OODVVUtIBwgFBVV95cUxPRWV3dmphS1ZPNjJZM2hhRjhxdXllcVdYTW1GZENDZkRtMFQ4YTRSdTFMMjJBZ1BuVEJWR0FRSkhBT3J5S2Z4TkFBOUZ4ZTg3ME4tQnRvVEhlOUtORnhZb2MzUWpWQXB3b3JQOUFDZFdub084SHBnR00xbExwaUFJSHIwb2cxdGR4OE1aQ2dITTFMM24tTXpGS096bFE5Xy1NbmlUd0xvT0JzV0JIU0M1LXJ0Rk1WVHU1MXhRdGpOSjB5Zw?oc=5</t>
+        </is>
+      </c>
+      <c r="F191" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>Confectionery market trends: AI and plant-based innovation redefine guilt-free treats - Food Ingredients First</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>Wed, 28 Jan 2026 09:28:36 GMT</t>
+        </is>
+      </c>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMihAFBVV95cUxPOVFiVkRYZVlmLVkxUjZHTkRkRlBHTnVyYXZuTWpMYzRFTW11dG5yNFlVZ2tkWWlVUVZRMTk0Q0stT1VBQUR0dUMxdFd3THNfMUJnR3AwS293S3NrMi1ndUEwTDlGOHBMYjB0OC1lTmlPZkg2aHJiYm40NHpSOGdSd3lpVzE?oc=5</t>
+        </is>
+      </c>
+      <c r="F192" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>BigBear.ai and AD Ports Group Announce Strategic Partnership Exploring Development of Next-Generation AI Customs Management Systems for Ports and Borders - Morningstar</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>Wed, 28 Jan 2026 14:15:00 GMT</t>
+        </is>
+      </c>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiugJBVV95cUxPaGdCZEtEdXFIc25aN245U0N0eG5FbENyN2lWMUM0ZUdieDJhZE5GT0NVOUVzWDFiWVVmTUExX0ZkcGxvWmJlQkR4a2FSaV9sdGNya3hCYUpiYWtIUTQwVkFCanhYWTRreTBqUTFmSk4xbVZnSlNrUnB3T0Q0cHhyWEhjNjFNelBqRzd1dURBZkNublRaRzFKWmJ6alZ6Mmt3TThTc3d3em9mNEg3dERfd2NVMEtVUjBxWGZ0UlVXaENyc20xRnF2ZFc5b3JZaUFXd3Y3a3Y2QUhndkE1UDNtYVFMQXhYUVVGRTIyUTM3b2dmUmc3cld0U1ROWDEzbk9ZaEdqX1lWdEpPajZaZDJ1S0hUU1NJdl9yWjA4dW93U3VCTUVxc2JoRjJ4S2Faa09rNHhFWkFDcEtxdw?oc=5</t>
+        </is>
+      </c>
+      <c r="F193" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>At Davos, tech CEOs laid out their vision for AI’s world domination - The Guardian</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>Tue, 27 Jan 2026 19:05:00 GMT</t>
+        </is>
+      </c>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMijwFBVV95cUxQanZQR3Zqa3MwanRfajQwallkejFMRVNBd3llWm5YUTU1UDVSVDR3N19IaGFzSFZGVHJaR2J1MmY3bm9TMzVEd0hWd2cydTdaYUJXa05RXzIza0hRaE9JNFNrc2k4b2xGT2FHNGhwaGNRVEphdnpkanowa05ZN29teXhCYzBfdWhuajdmd0w5NA?oc=5</t>
+        </is>
+      </c>
+      <c r="F194" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>Arabic.AI partners with Stanford to launch the first holistic benchmark for Arabic AI models - Wamda</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>Wed, 28 Jan 2026 09:57:10 GMT</t>
+        </is>
+      </c>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxNMUVWd2hwdjlQQXgxVXhmdnI4eUlQTkRHQzh1UVZwRUozNnduUG5yUHZZX0llWnl3S25CWVo2SGhhNUM1Zl81OFNNcFJyNWlrSlBiV0VuaW81UTAzVkl6WGUzcmdkUlhhLTVTem1EVHJEeDU3YTczUTJxNFpsRG1KcHVqcWtZcWhtLVVVY3RLX2VjOW9SQTdOT1NR?oc=5</t>
+        </is>
+      </c>
+      <c r="F195" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>AI reshapes university language classrooms - Digital Watch Observatory</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>Wed, 28 Jan 2026 11:24:26 GMT</t>
+        </is>
+      </c>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMid0FVX3lxTFB6RXMyQXRNTmNRa2ZaWDFiVm05cjVEVHB4RnhIdVdjOVRJUnpwYjg5MjJhY3pKMFBtRmlKS1JKN29xSi1La0VtZDJCZ2xQVHlnWURBb0tyXy1ZQmxweWhsOGVLd05WXzVkckZod1VxUmxBMEt0UjRR?oc=5</t>
+        </is>
+      </c>
+      <c r="F196" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>AfricAI positions Africa for large-scale adoption of intelligent machines - Digital Watch Observatory</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>Wed, 28 Jan 2026 11:09:57 GMT</t>
+        </is>
+      </c>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMie0FVX3lxTFAwVTN3aUZSMl9pYzBfWTRaR05wU3ROUHowNk5GNVRWTVhPWWMzUng1bjFwSFdSWS10c25UQTd3clFYQlVZczU0eVF3SXB3ZklsTENjUWVqc09pWV9hZ1k5bFpXQXpYVXdKSVhvcXQxY3h2YmdLSFo5T1ZsYw?oc=5</t>
+        </is>
+      </c>
+      <c r="F197" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
           <t>Fraud_Scam</t>
         </is>
       </c>
-      <c r="B117" t="inlineStr">
-        <is>
-          <t>("fraud" OR "scam" OR "phishing" OR "identity theft" OR "account takeover" OR "payment fraud" OR "credit card fraud" OR "wire fraud" OR "business email compromise" OR "fake invoice" OR "social engineering" OR "advance fee fraud")</t>
-        </is>
-      </c>
-      <c r="C117" t="inlineStr">
-        <is>
-          <t>Police warning: Beware of social media scam stealing bank access - RTL Today</t>
-        </is>
-      </c>
-      <c r="D117" t="inlineStr">
-        <is>
-          <t>Mon, 26 Jan 2026 16:30:50 GMT</t>
-        </is>
-      </c>
-      <c r="E117" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxOYkF6X2FsdEN6ME5PX25oUF8zTVVPLWYzd1pMRkE4ZnFac1Jubjg5Tk42ZlczU29FMXhLZENqc3VsZG1DUnJFaTVtOW1WcVp4bzYySUItalE0LWQ5OGpHZGd4SFRUU0x4S2ZlNEVMLWl5WDAzaEhUdUZkcmEtak9NWkFvV3Z6S1V0Z0VoeFZpX0pEa0lZWWFzQWhrcw?oc=5</t>
-        </is>
-      </c>
-      <c r="F117" t="n">
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>(fraud OR scam OR phishing OR smishing OR vishing OR "identity theft" OR impersonation OR spoofing OR "account takeover" OR "payment fraud" OR "invoice fraud" OR "wire fraud" OR "business email compromise" OR BEC OR "fake invoice" OR "supplier fraud" OR "procurement fraud" OR "social engineering" OR extortion OR blackmail)AND (company OR business OR enterprise OR customer OR client OR employee OR bank OR financial OR payment OR transaction)</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>Jersey businesses urged to beware of scam financial emails - BBC</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>Tue, 27 Jan 2026 16:43:45 GMT</t>
+        </is>
+      </c>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTE1pWER4ajJRcUk3NHRXN0pMZkxGbWd4WjYzbnRzQUd2ZkwxNllfMXlFRElwSGpBSEJweHA1eXU0YnRlQldLcWFYdWU5NEFnNGNBcFF4X3RFOERzZ9IBX0FVX3lxTE1QckxlMlhjejd6enltLUl5ZzkyZ1VjeUlwcTJydUNqLUpGRVdVTTZXSkI0d1h0eUVNbS1KR3JHa3dVaVdyby0xWGVaWFJWVWwzRjFXYWwyMWxCTUlwSUxB?oc=5</t>
+        </is>
+      </c>
+      <c r="F198" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>Fraud_Scam</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>(fraud OR scam OR phishing OR smishing OR vishing OR "identity theft" OR impersonation OR spoofing OR "account takeover" OR "payment fraud" OR "invoice fraud" OR "wire fraud" OR "business email compromise" OR BEC OR "fake invoice" OR "supplier fraud" OR "procurement fraud" OR "social engineering" OR extortion OR blackmail)AND (company OR business OR enterprise OR customer OR client OR employee OR bank OR financial OR payment OR transaction)</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>Interpol Takes Down Online Scammers - Africa Defense Forum</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>Tue, 27 Jan 2026 18:54:12 GMT</t>
+        </is>
+      </c>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMieEFVX3lxTE9EeWNQellWeGdrM2NBNk5GOWV6ZHlxWGtZblBJS1JTbElWQTdISFlPUndyTnY5SC1KTS1tTmRxbnRQaTZ4eG9DU041bVFGcDgwb1pEUFphRjZkSTF2Y0RBdFNTVUNjbE1HbnB3aWllajg2UUl1Z0pGYg?oc=5</t>
+        </is>
+      </c>
+      <c r="F199" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>Fraud_Scam</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>(fraud OR scam OR phishing OR smishing OR vishing OR "identity theft" OR impersonation OR spoofing OR "account takeover" OR "payment fraud" OR "invoice fraud" OR "wire fraud" OR "business email compromise" OR BEC OR "fake invoice" OR "supplier fraud" OR "procurement fraud" OR "social engineering" OR extortion OR blackmail)AND (company OR business OR enterprise OR customer OR client OR employee OR bank OR financial OR payment OR transaction)</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>Nicosia based company defrauded of more than €120,000 via email scam - Cyprus Mail</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>Tue, 27 Jan 2026 18:05:58 GMT</t>
+        </is>
+      </c>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxPMjRpT0tWVTd2X1lvRXVYMFlkZExpbWQ5MVIxX0FNVWR0MHZzN3lwMkMwTFBIeHRpZG1vd29ocjJEYlY4Y0VyQkx2bXp2ZFZCWkY4TFB2WGVibEVMRERCNHF3MFNEMGF2ZDMyXzJJZWV6ZUZ3bmdGallVMThfcnJTc2lPWVlsNmlIZEltY0pQRndXazRJdkVDSG9ONFdFckI2akxqSQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F200" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>Fraud_Scam</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>(fraud OR scam OR phishing OR smishing OR vishing OR "identity theft" OR impersonation OR spoofing OR "account takeover" OR "payment fraud" OR "invoice fraud" OR "wire fraud" OR "business email compromise" OR BEC OR "fake invoice" OR "supplier fraud" OR "procurement fraud" OR "social engineering" OR extortion OR blackmail)AND (company OR business OR enterprise OR customer OR client OR employee OR bank OR financial OR payment OR transaction)</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>City of Enterprise Warns of Scam Emails Targeting Businesses - wiregrassdailynews.com</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>Tue, 27 Jan 2026 17:22:58 GMT</t>
+        </is>
+      </c>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxPckNiSGNTSDJXYklmajZ2alZLTkRSZnhrSUprWks5ZUJhdkJJU0pWYm9Hdy05a2hOVHZOU0doWVBJU0hEU3RvUU1NX0VOSHFrYmdoeDFFcEpDRFJoWURzck5IX0FlYlRFNnZGYTNaR2k4YUN5YmFQenI0WlhPM3cxN1BZZmNJclp2T19HMm1aSUdtclpVOEtqVWlYanBQUHhkc3F2dHZrZzJ6OEpOaHgzd2VMaWdMQUZh?oc=5</t>
+        </is>
+      </c>
+      <c r="F201" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>Fraud_Scam</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>(fraud OR scam OR phishing OR smishing OR vishing OR "identity theft" OR impersonation OR spoofing OR "account takeover" OR "payment fraud" OR "invoice fraud" OR "wire fraud" OR "business email compromise" OR BEC OR "fake invoice" OR "supplier fraud" OR "procurement fraud" OR "social engineering" OR extortion OR blackmail)AND (company OR business OR enterprise OR customer OR client OR employee OR bank OR financial OR payment OR transaction)</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>Scam Emails - edson.ca</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>Tue, 27 Jan 2026 18:45:47 GMT</t>
+        </is>
+      </c>
+      <c r="E202" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMia0FVX3lxTE1RWlk3eHc5SmtLSE9WU1NWYVp2MUIzT1JjeVB0Ni1LUGJKaGg2bXNGVkQyeEVxaEs2QXZsc0c3X3dBbi1PcXI2LWcyQ2d4MERobFdSOVc2RzdfR0ZYUFpNSzJ3dDFtVnlCN1hF?oc=5</t>
+        </is>
+      </c>
+      <c r="F202" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>Fraud_Scam</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>(fraud OR scam OR phishing OR smishing OR vishing OR "identity theft" OR impersonation OR spoofing OR "account takeover" OR "payment fraud" OR "invoice fraud" OR "wire fraud" OR "business email compromise" OR BEC OR "fake invoice" OR "supplier fraud" OR "procurement fraud" OR "social engineering" OR extortion OR blackmail)AND (company OR business OR enterprise OR customer OR client OR employee OR bank OR financial OR payment OR transaction)</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>On Your Side: Marshfield, Mo. business owner could have lost $1,000 in Venmo scam - ky3.com</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>Tue, 27 Jan 2026 23:59:00 GMT</t>
+        </is>
+      </c>
+      <c r="E203" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxNd0NSSkJ3cTdrTmZFYUo0LXhWdVQ0ajJMekRUdkNHYWdKLXBqWkNyQ1BZV1BRdms5bnlVRnBwcDYyajdwUTJkSmozY1VBYjJVX3E3bXN1MXgzRElnMHNCYThSSWZQd0RYc05QSDBPZGdVT291U215c0c3bF9Pd1lpS0VPc01KeTR6cE80SWtHeEVFM09vemxPNWlndmtCaU94dEJSWNIBuAFBVV95cUxOckIxSE9SNjlYdXQzZnVfZXJiVEZpZ2lYQVlEc2JHME1FYUx3V2tCQUk3Yjc4MDU5bHdZMnVWQld1a19nYXp3ZWhGWmZKellMdmRKcWZVd2Y0Qlp4d1MtZlI3aXU0bi0zbExwbElfa1Jqb25vTGs1MTVna1cxZGNLMXZhdERVRmExQzFUTHR0YmNRQ3VDZGoxclhiUVdtelVpRG02Y21LWnJBQUNLX2FEeHFCSnhVWFpW?oc=5</t>
+        </is>
+      </c>
+      <c r="F203" t="n">
         <v>7</v>
       </c>
     </row>

--- a/data/topic_feeds.xlsx
+++ b/data/topic_feeds.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F203"/>
+  <dimension ref="A1:F278"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3611,17 +3611,17 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>New solution helps prevent data exfiltration in real time - BetaNews</t>
+          <t>$40M US Crypto Heist Linked to Contractor’s Son Raises Insider Risk Alarm - FXLeaders</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Wed, 21 Jan 2026 15:08:58 GMT</t>
+          <t>Mon, 26 Jan 2026 08:00:27 GMT</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxQLUc0TjVWRGtyTDRtM0RzVWJBMGRad2RLUGZubkpKZVF6SGZHc2ZEUm90U0UycXlMQUthd3BRMzR4WDltQlhZWG4wam1ER3Rfb1ozNDhMdzlQSjVXM2hYVTVUdGthTlpxb2dKQ1JJbzA2cHVaU0lRSGJyN3JLSkd3UmVqR3pVR0YtTldjRThBelk?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxPT2VKaXZjSXNkQ0dJMEFyRlh1YkRBZ0pKNU5BR0Q3VjRsM1JnSXRyUGxUUVBYNVlJOGVJZmIxSXp1Tk44LXRhc3hKbXVkOW5hQUg5V2pQaWRTczR2OE9zMU5zNktzT1pFTlNaV1pFQmlNWEVDcFFYYkFEb3JJZDNLVFB4UmExWTczZTNtdy1wWm9PWFFmT2pIYTJoLWdrVE4wR0xaVVlXQ0RiNnZ1Q0M0bS1Ia1Q?oc=5</t>
         </is>
       </c>
       <c r="F107" t="n">
@@ -3631,27 +3631,27 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Insider_Risk</t>
+          <t>Fraud_Scam</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>("insider risk" OR "insider threat" OR "internal threat" OR "employee misconduct" OR "data exfiltration" OR "privileged access abuse" OR "malicious insider" OR "negligent insider" OR "insider attack" OR "corporate espionage" OR "information leakage" OR "unauthorised access" OR "policy violation" OR "security breach" OR "insider vulnerability")</t>
+          <t>("fraud" OR "scam" OR "phishing" OR "identity theft" OR "account takeover" OR "payment fraud" OR "credit card fraud" OR "wire fraud" OR "business email compromise" OR "fake invoice" OR "social engineering" OR "advance fee fraud")</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Davos panel warns AI agents could run amok - theregister.com</t>
+          <t>How McAfee’s Scam Detector Checks QR Codes and Flags Suspicious Social Messages - McAfee</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Wed, 21 Jan 2026 23:04:00 GMT</t>
+          <t>Tue, 27 Jan 2026 14:16:29 GMT</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMickFVX3lxTFBCNUFJN3BRRzA2WjVvdVRNblFtR0VnWGNDd1B2dXNDVmhFS0ozTnVVNmdtdEtLY2IwZGJZX2hpcHVoZFdrOVgzTWlZTFBVSnEwUnJpaXNGWjNuLVpzUXo2ay14UTF6ZDZiTTY3TzFpUXFlZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikgFBVV95cUxNbmVmUklKS2hzZzJyU3BQcld4T2JvTVFWaHRhdnNGWXhHYmtBT0Z3THIwd2phNEFrcXpPaVlSOHdvOGMzU3VUdFlMb2RoTUVMcW11cG56NkRCTnFCRFRub3ozbXgtOXBtLWpudlNzOEo2SDlVQllpbWwwcHktdThyWm54TEhEcl8zMjRFOUx2VjMzdw?oc=5</t>
         </is>
       </c>
       <c r="F108" t="n">
@@ -3661,27 +3661,27 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Insider_Risk</t>
+          <t>Fraud_Scam</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>("insider risk" OR "insider threat" OR "internal threat" OR "employee misconduct" OR "data exfiltration" OR "privileged access abuse" OR "malicious insider" OR "negligent insider" OR "insider attack" OR "corporate espionage" OR "information leakage" OR "unauthorised access" OR "policy violation" OR "security breach" OR "insider vulnerability")</t>
+          <t>("fraud" OR "scam" OR "phishing" OR "identity theft" OR "account takeover" OR "payment fraud" OR "credit card fraud" OR "wire fraud" OR "business email compromise" OR "fake invoice" OR "social engineering" OR "advance fee fraud")</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>$40M US Crypto Heist Linked to Contractor’s Son Raises Insider Risk Alarm - FXLeaders</t>
+          <t>Top Impersonation Tactics Used in Social Engineering and Phishing - SOCRadar® Cyber Intelligence Inc.</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Mon, 26 Jan 2026 08:00:27 GMT</t>
+          <t>Tue, 27 Jan 2026 12:53:55 GMT</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxPT2VKaXZjSXNkQ0dJMEFyRlh1YkRBZ0pKNU5BR0Q3VjRsM1JnSXRyUGxUUVBYNVlJOGVJZmIxSXp1Tk44LXRhc3hKbXVkOW5hQUg5V2pQaWRTczR2OE9zMU5zNktzT1pFTlNaV1pFQmlNWEVDcFFYYkFEb3JJZDNLVFB4UmExWTczZTNtdy1wWm9PWFFmT2pIYTJoLWdrVE4wR0xaVVlXQ0RiNnZ1Q0M0bS1Ia1Q?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxPa0k0Z3UyVWwyYVBtMmtESUtsSkZpTWd6ZHBOUEJLYmVvRWFyR1g5bmNvbWRJb3VaR2ZLbl9IRDRUOFp4RFY0RmVZaEVvUFBYZWdCZjZjaUVobTJPNTZteXJoOGxpRTgtMkl3YXVENFYxT0N0MzdiTDlMb0FEVTZzQQ?oc=5</t>
         </is>
       </c>
       <c r="F109" t="n">
@@ -3701,17 +3701,17 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>How McAfee’s Scam Detector Checks QR Codes and Flags Suspicious Social Messages - McAfee</t>
+          <t>Islanders warned about scam JEP social media account - bailiwickexpress.com</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Tue, 27 Jan 2026 14:16:29 GMT</t>
+          <t>Sat, 24 Jan 2026 15:37:53 GMT</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikgFBVV95cUxNbmVmUklKS2hzZzJyU3BQcld4T2JvTVFWaHRhdnNGWXhHYmtBT0Z3THIwd2phNEFrcXpPaVlSOHdvOGMzU3VUdFlMb2RoTUVMcW11cG56NkRCTnFCRFRub3ozbXgtOXBtLWpudlNzOEo2SDlVQllpbWwwcHktdThyWm54TEhEcl8zMjRFOUx2VjMzdw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilgFBVV95cUxNVGYzbHo3QTl2ZDc4dTlmd2tKUW40WFZvRzlXZ2NBd241SDJWZnpJa2h1bmdkNGVDaWc5MkRGdUphOGpZSUkwbk1oVko1OHN3Y2ptaXhqZXBlT1kxODFGMjJKOS1KSXRTN2dkdENqWVdzVjhFNzJsQzhtUnhDQjhlNFIybWVTYW8tTGdKMzBZN2ZhdWQ5cnc?oc=5</t>
         </is>
       </c>
       <c r="F110" t="n">
@@ -3731,17 +3731,17 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Top Impersonation Tactics Used in Social Engineering and Phishing - SOCRadar® Cyber Intelligence Inc.</t>
+          <t>SCAM ALERT: South African mining company not offering training programme through social media – ignore dodgy link and follow verified portals - Africa Check</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Tue, 27 Jan 2026 12:53:55 GMT</t>
+          <t>Fri, 23 Jan 2026 11:34:29 GMT</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxPa0k0Z3UyVWwyYVBtMmtESUtsSkZpTWd6ZHBOUEJLYmVvRWFyR1g5bmNvbWRJb3VaR2ZLbl9IRDRUOFp4RFY0RmVZaEVvUFBYZWdCZjZjaUVobTJPNTZteXJoOGxpRTgtMkl3YXVENFYxT0N0MzdiTDlMb0FEVTZzQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxPZ2NlM19wRTFPUzQ3ckdaQUVjWEg0TnJobE54ZHQ1WThsYk45TnJ2S1hzdlV1TWV3MUc0YTQ5TTR4QjZIbWJqS2p5dlBBc0dPSjVGRkl0d2g4MUVWdE55WU9pTTBEdExGQTZSY0ZRYzZldHlTUmtfcVA5SURpdC12dUhmNXFTcHo5TTIwX3FLdXc3clpQQTVDSjNETWZjcGIwZXBQRHBxUnY3R0hrbUJCQmg1NEx0dw?oc=5</t>
         </is>
       </c>
       <c r="F111" t="n">
@@ -3761,17 +3761,17 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Islanders warned about scam JEP social media account - bailiwickexpress.com</t>
+          <t>Police warning: Beware of social media scam stealing bank access - RTL Today</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Sat, 24 Jan 2026 15:37:53 GMT</t>
+          <t>Mon, 26 Jan 2026 16:30:50 GMT</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilgFBVV95cUxNVGYzbHo3QTl2ZDc4dTlmd2tKUW40WFZvRzlXZ2NBd241SDJWZnpJa2h1bmdkNGVDaWc5MkRGdUphOGpZSUkwbk1oVko1OHN3Y2ptaXhqZXBlT1kxODFGMjJKOS1KSXRTN2dkdENqWVdzVjhFNzJsQzhtUnhDQjhlNFIybWVTYW8tTGdKMzBZN2ZhdWQ5cnc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxOYkF6X2FsdEN6ME5PX25oUF8zTVVPLWYzd1pMRkE4ZnFac1Jubjg5Tk42ZlczU29FMXhLZENqc3VsZG1DUnJFaTVtOW1WcVp4bzYySUItalE0LWQ5OGpHZGd4SFRUU0x4S2ZlNEVMLWl5WDAzaEhUdUZkcmEtak9NWkFvV3Z6S1V0Z0VoeFZpX0pEa0lZWWFzQWhrcw?oc=5</t>
         </is>
       </c>
       <c r="F112" t="n">
@@ -3781,27 +3781,27 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Fraud_Scam</t>
+          <t>Current_Affairs</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>("fraud" OR "scam" OR "phishing" OR "identity theft" OR "account takeover" OR "payment fraud" OR "credit card fraud" OR "wire fraud" OR "business email compromise" OR "fake invoice" OR "social engineering" OR "advance fee fraud")</t>
+          <t>(geopolitics OR migration OR economy OR conflict OR legislation OR terrorism OR disinformation OR misinformation OR government OR policy OR regulation) AND (briefing OR analysis OR update OR report)</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>SCAM ALERT: South African mining company not offering training programme through social media – ignore dodgy link and follow verified portals - Africa Check</t>
+          <t>Persistent threats, low sophistication: Pool Re maps ‘substantial’ UK terrorism risk landscape - Global Reinsurance</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>Fri, 23 Jan 2026 11:34:29 GMT</t>
+          <t>Wed, 28 Jan 2026 14:02:17 GMT</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxPZ2NlM19wRTFPUzQ3ckdaQUVjWEg0TnJobE54ZHQ1WThsYk45TnJ2S1hzdlV1TWV3MUc0YTQ5TTR4QjZIbWJqS2p5dlBBc0dPSjVGRkl0d2g4MUVWdE55WU9pTTBEdExGQTZSY0ZRYzZldHlTUmtfcVA5SURpdC12dUhmNXFTcHo5TTIwX3FLdXc3clpQQTVDSjNETWZjcGIwZXBQRHBxUnY3R0hrbUJCQmg1NEx0dw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi3gFBVV95cUxQTFMySFVCY0JyTW1NcUhvNWdvSlFnaVpLZG1udkd2U1h0MWFHRnB2ZVk4RUtHR25TM3BmalRWYlZ4UVgtVmd3Mk1ESjdBZ01VamFVbFRUbzZ6ZzZSMGxvQlp2dVU1cjhNM3ZnWmJacG1uM0d2dTMtZmd6aTNmb0tSVFVZNERxYzB5bUFyQTc0clZmeDhSTkhWWnZwRVprQ1JLNG1UNjFZbWdIUlBfTkttTFlsWnhVV1ZwVzdRQ3E5UDFlWC12MWZfOVZpdEhuaHdjbFc1UDc3Y1JYc3lpQUE?oc=5</t>
         </is>
       </c>
       <c r="F113" t="n">
@@ -3811,27 +3811,27 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Fraud_Scam</t>
+          <t>Current_Affairs</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>("fraud" OR "scam" OR "phishing" OR "identity theft" OR "account takeover" OR "payment fraud" OR "credit card fraud" OR "wire fraud" OR "business email compromise" OR "fake invoice" OR "social engineering" OR "advance fee fraud")</t>
+          <t>(geopolitics OR migration OR economy OR conflict OR legislation OR terrorism OR disinformation OR misinformation OR government OR policy OR regulation) AND (briefing OR analysis OR update OR report)</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Police warning: Beware of social media scam stealing bank access - RTL Today</t>
+          <t>Government responds to the sixth Commissioners’ report into Thurrock Council’s progress under intervention - yourthurrock.com</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>Mon, 26 Jan 2026 16:30:50 GMT</t>
+          <t>Wed, 28 Jan 2026 13:49:29 GMT</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxOYkF6X2FsdEN6ME5PX25oUF8zTVVPLWYzd1pMRkE4ZnFac1Jubjg5Tk42ZlczU29FMXhLZENqc3VsZG1DUnJFaTVtOW1WcVp4bzYySUItalE0LWQ5OGpHZGd4SFRUU0x4S2ZlNEVMLWl5WDAzaEhUdUZkcmEtak9NWkFvV3Z6S1V0Z0VoeFZpX0pEa0lZWWFzQWhrcw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi3gFBVV95cUxNX3RwOW55Z1BmS0ZNSzJKaWdKMDM3cWpJRllaenZSXzdObnpZVmljUDNuSldWMGUwU21sX1Z6MzFnc1BlYXlCOGozMkpad1hNNXhYbFdjMEF2ZGdfV1U3b2xza2prbWhkSHNxWTRTNEtvNXVYY1U1Y2pxa0VuWXpLYTRFdlh3ZFRuZG9NT2t3cFdpT1RGcjktYVg5T3JNbVUxWmQ1NDBPbzNjNVdHSnFQdmdDcE51SWZkYmFEbWlxc0JzM2FVSDlWLU9fd3d3NzQ5RUo4UWdVcjZtS3Q0Rmc?oc=5</t>
         </is>
       </c>
       <c r="F114" t="n">
@@ -3851,17 +3851,17 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Persistent threats, low sophistication: Pool Re maps ‘substantial’ UK terrorism risk landscape - Global Reinsurance</t>
+          <t>Kingston mayor highlights government work in annual report - Spectrum News</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>Wed, 28 Jan 2026 14:02:17 GMT</t>
+          <t>Wed, 28 Jan 2026 13:22:00 GMT</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi3gFBVV95cUxQTFMySFVCY0JyTW1NcUhvNWdvSlFnaVpLZG1udkd2U1h0MWFHRnB2ZVk4RUtHR25TM3BmalRWYlZ4UVgtVmd3Mk1ESjdBZ01VamFVbFRUbzZ6ZzZSMGxvQlp2dVU1cjhNM3ZnWmJacG1uM0d2dTMtZmd6aTNmb0tSVFVZNERxYzB5bUFyQTc0clZmeDhSTkhWWnZwRVprQ1JLNG1UNjFZbWdIUlBfTkttTFlsWnhVV1ZwVzdRQ3E5UDFlWC12MWZfOVZpdEhuaHdjbFc1UDc3Y1JYc3lpQUE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxNMDBTR243VWR2ampuLVBrR1MzTWlUbWMySTBMZzFHalhiZ0NhSklWaGVqNGR3ZlNXWHVVR2FaUUVfemZ5MHhyRTJCOTNUOVJnX181VW9kaVVfSE9kQVh2LTJQZWFaQlNuU0J3V2FncW9raTFITXJmUHJMdXJKOUVVdEJjVnJWUWQxNS1JMFlYSGlYd2xsZmhnX3ZBYlEyQzhFRnlVZEJB?oc=5</t>
         </is>
       </c>
       <c r="F115" t="n">
@@ -3881,17 +3881,17 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Government responds to the sixth Commissioners’ report into Thurrock Council’s progress under intervention - yourthurrock.com</t>
+          <t>DSM Foundation Reacts to Government Report on Ketamine Use and Risks - BusinessMole</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>Wed, 28 Jan 2026 13:49:29 GMT</t>
+          <t>Wed, 28 Jan 2026 13:18:19 GMT</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi3gFBVV95cUxNX3RwOW55Z1BmS0ZNSzJKaWdKMDM3cWpJRllaenZSXzdObnpZVmljUDNuSldWMGUwU21sX1Z6MzFnc1BlYXlCOGozMkpad1hNNXhYbFdjMEF2ZGdfV1U3b2xza2prbWhkSHNxWTRTNEtvNXVYY1U1Y2pxa0VuWXpLYTRFdlh3ZFRuZG9NT2t3cFdpT1RGcjktYVg5T3JNbVUxWmQ1NDBPbzNjNVdHSnFQdmdDcE51SWZkYmFEbWlxc0JzM2FVSDlWLU9fd3d3NzQ5RUo4UWdVcjZtS3Q0Rmc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxQS2pyREFjcExEamNEQURrUjRETE5MRzUtOHJHb3R3d0cxM1E0X2FpM1B3MnhjVnNvaFFDVld1b3MwbVFhSDlpX2phUkN4WW5YUnIxZDd5R1RJWW9aaGw2U0tkXzJza0szWnlHUDc2MFl3UXFXeVlLMHMyZGI4OVlpV01JalBJemVEUG00WmhRclo4anZIbEJWS1dkX2plMjA?oc=5</t>
         </is>
       </c>
       <c r="F116" t="n">
@@ -3911,17 +3911,17 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Kingston mayor highlights government work in annual report - Spectrum News</t>
+          <t>Press Conference: Monetary Policy Report – January 2026 - Bank of Canada</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>Wed, 28 Jan 2026 13:22:00 GMT</t>
+          <t>Wed, 28 Jan 2026 02:36:35 GMT</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxNMDBTR243VWR2ampuLVBrR1MzTWlUbWMySTBMZzFHalhiZ0NhSklWaGVqNGR3ZlNXWHVVR2FaUUVfemZ5MHhyRTJCOTNUOVJnX181VW9kaVVfSE9kQVh2LTJQZWFaQlNuU0J3V2FncW9raTFITXJmUHJMdXJKOUVVdEJjVnJWUWQxNS1JMFlYSGlYd2xsZmhnX3ZBYlEyQzhFRnlVZEJB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxPZWlvMExpSV9saFJ2bGFtcVVuMXdQTnhvcHdnaG1VOEZiMHo2S2lpQ3JfYVg5WC1OMmdCMUp0d2hSR0txc05ORFdaTUlUcTZhbTd1dExYMEowMnVIZGtHQ0tXNXVrb1pwcW9VXzdGTzZtZGRnbVVQT0Q4SXNjSEdKYnE5RkhvanBvdEpDSXl0NEdmQm5MejlB?oc=5</t>
         </is>
       </c>
       <c r="F117" t="n">
@@ -3931,27 +3931,27 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Current_Affairs</t>
+          <t>Supply_Chain</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>(geopolitics OR migration OR economy OR conflict OR legislation OR terrorism OR disinformation OR misinformation OR government OR policy OR regulation) AND (briefing OR analysis OR update OR report)</t>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>DSM Foundation Reacts to Government Report on Ketamine Use and Risks - BusinessMole</t>
+          <t>Focus on privacy compliance - White &amp; Case LLP</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>Wed, 28 Jan 2026 13:18:19 GMT</t>
+          <t>Wed, 28 Jan 2026 12:00:00 GMT</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxQS2pyREFjcExEamNEQURrUjRETE5MRzUtOHJHb3R3d0cxM1E0X2FpM1B3MnhjVnNvaFFDVld1b3MwbVFhSDlpX2phUkN4WW5YUnIxZDd5R1RJWW9aaGw2U0tkXzJza0szWnlHUDc2MFl3UXFXeVlLMHMyZGI4OVlpV01JalBJemVEUG00WmhRclo4anZIbEJWS1dkX2plMjA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMickFVX3lxTE44VDYxWHFycVVwRExpUE9INGw2RVhlWUk0VlV3cUNwX0o1T3BxcmVHYzdBX0FQSDlpNWdJTmdyaC1FdUpGSzBqbldGQzMxYlNOclJkbDJ4aUJZaVM0aExWZF9NOFhqRGhBaWNoSFhnNWl3QQ?oc=5</t>
         </is>
       </c>
       <c r="F118" t="n">
@@ -3961,27 +3961,27 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Current_Affairs</t>
+          <t>Supply_Chain</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>(geopolitics OR migration OR economy OR conflict OR legislation OR terrorism OR disinformation OR misinformation OR government OR policy OR regulation) AND (briefing OR analysis OR update OR report)</t>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Press Conference: Monetary Policy Report – January 2026 - Bank of Canada</t>
+          <t>‘Helvellyn’ takes to the waters: new pilot boat comes on board at Cumbrian port - cumberland.gov.uk</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>Wed, 28 Jan 2026 02:36:35 GMT</t>
+          <t>Wed, 28 Jan 2026 10:58:11 GMT</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxPZWlvMExpSV9saFJ2bGFtcVVuMXdQTnhvcHdnaG1VOEZiMHo2S2lpQ3JfYVg5WC1OMmdCMUp0d2hSR0txc05ORFdaTUlUcTZhbTd1dExYMEowMnVIZGtHQ0tXNXVrb1pwcW9VXzdGTzZtZGRnbVVQT0Q4SXNjSEdKYnE5RkhvanBvdEpDSXl0NEdmQm5MejlB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxNcHRvOXJkY2t0RlNNbFRGbDlpOUhBaUhRMDFPT2ZEMDBoTVZYMFFJdWFRbTJsM2NTQTZ0elJ2ZFlxOVlFN1BMUUlkTmtnbVZsY2pwRWlTczBKUHFxWEtHWld3NHNqOGQyd1RadmdZM1hYb3I5b0g4VFJvTnV5dEs1X00tNFpZNHl2aVVPYV9xWmpib0xQS05sS1dFLXhSaEVlcEx2VW9R?oc=5</t>
         </is>
       </c>
       <c r="F119" t="n">
@@ -4001,17 +4001,17 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Focus on privacy compliance - White &amp; Case LLP</t>
+          <t>Sanctions are not a humane alternative to bombs. They are economic warfare with civilians as collateral damage - The Guardian</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>Wed, 28 Jan 2026 12:00:00 GMT</t>
+          <t>Wed, 28 Jan 2026 12:53:00 GMT</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMickFVX3lxTE44VDYxWHFycVVwRExpUE9INGw2RVhlWUk0VlV3cUNwX0o1T3BxcmVHYzdBX0FQSDlpNWdJTmdyaC1FdUpGSzBqbldGQzMxYlNOclJkbDJ4aUJZaVM0aExWZF9NOFhqRGhBaWNoSFhnNWl3QQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi3gFBVV95cUxNZkNXdHVJY1dLSHV3ZXRUM1Y4cWM5MGRZWEh0SWRfOHM4NkdoRk1qNzVxNGpFalJmVzRkRzVBS3ZEWXIwYWxqQXpMcHhPa2t0R0RTNU85MXpXZFFjblRCamo3ZlI4b3hPZl9CTGVnMjgySlNUZnRfUWNjMFBvaDl2MGcwbVdjdURESEdyNG1xc3lyM0V0cEJ5Uy1sUEFZR1NKU2lSeHNZNnd5LTZnMWI1Q2UwWGMyeFFIUkh6bTlsbG9rVTBqRmJBNkw1TVFLVGVxWllCVkM4TExrMXZxc3c?oc=5</t>
         </is>
       </c>
       <c r="F120" t="n">
@@ -4031,17 +4031,17 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>‘Helvellyn’ takes to the waters: new pilot boat comes on board at Cumbrian port - cumberland.gov.uk</t>
+          <t>CMA issues significant new guidance on supply chain responsibility for environmental claims - Fieldfisher</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>Wed, 28 Jan 2026 10:58:11 GMT</t>
+          <t>Wed, 28 Jan 2026 09:49:15 GMT</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxNcHRvOXJkY2t0RlNNbFRGbDlpOUhBaUhRMDFPT2ZEMDBoTVZYMFFJdWFRbTJsM2NTQTZ0elJ2ZFlxOVlFN1BMUUlkTmtnbVZsY2pwRWlTczBKUHFxWEtHWld3NHNqOGQyd1RadmdZM1hYb3I5b0g4VFJvTnV5dEs1X00tNFpZNHl2aVVPYV9xWmpib0xQS05sS1dFLXhSaEVlcEx2VW9R?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilAFBVV95cUxOcnJwTDBOSEhBbWxObUt4bzdXdkJvZWxzYjdCazNRUUpyTHNQVzhLbzNDMnhNRWhJOG1JUTZoVXphcWxKQmtDYmpWaUxGVG1NbFQySjRES3Q5YXUwTVdlVmd6M3d3a3pDZ0FMbDhHMkNVa3RYRDRVMDZKYUpUbjFCVFcwVkhmUTFuYlVhSTA0aE5yU2ZD?oc=5</t>
         </is>
       </c>
       <c r="F121" t="n">
@@ -4061,17 +4061,17 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Sanctions are not a humane alternative to bombs. They are economic warfare with civilians as collateral damage - The Guardian</t>
+          <t>Polish port picked for offshore wind operations base - 4C Offshore</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>Wed, 28 Jan 2026 12:53:00 GMT</t>
+          <t>Wed, 28 Jan 2026 12:47:32 GMT</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi3gFBVV95cUxNZkNXdHVJY1dLSHV3ZXRUM1Y4cWM5MGRZWEh0SWRfOHM4NkdoRk1qNzVxNGpFalJmVzRkRzVBS3ZEWXIwYWxqQXpMcHhPa2t0R0RTNU85MXpXZFFjblRCamo3ZlI4b3hPZl9CTGVnMjgySlNUZnRfUWNjMFBvaDl2MGcwbVdjdURESEdyNG1xc3lyM0V0cEJ5Uy1sUEFZR1NKU2lSeHNZNnd5LTZnMWI1Q2UwWGMyeFFIUkh6bTlsbG9rVTBqRmJBNkw1TVFLVGVxWllCVkM4TExrMXZxc3c?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxOYWtJM1gyQmQ1Um9kMTJfclV1dTI5WUdVdmtQMEZ3RDV3dnpkZFdHWFZqSGwxUy1yZWZvdWQzVUY5dXRrZDh4VDhDRjlJYkttcWZMNjFEU3pzMFJFNWx4Q0pZYlVfY3FjZUNpVkEwaFBlUzVvNUwwSmtGNUNKQkRjbHBNYmhlLWdJV3Y1SmRENUMybEt4ZUdJelhSam1IVFU?oc=5</t>
         </is>
       </c>
       <c r="F122" t="n">
@@ -4091,17 +4091,17 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>CMA issues significant new guidance on supply chain responsibility for environmental claims - Fieldfisher</t>
+          <t>Historic building on the up after £3.2m restoration - inverclyde.gov.uk</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>Wed, 28 Jan 2026 09:49:15 GMT</t>
+          <t>Wed, 28 Jan 2026 11:14:00 GMT</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilAFBVV95cUxOcnJwTDBOSEhBbWxObUt4bzdXdkJvZWxzYjdCazNRUUpyTHNQVzhLbzNDMnhNRWhJOG1JUTZoVXphcWxKQmtDYmpWaUxGVG1NbFQySjRES3Q5YXUwTVdlVmd6M3d3a3pDZ0FMbDhHMkNVa3RYRDRVMDZKYUpUbjFCVFcwVkhmUTFuYlVhSTA0aE5yU2ZD?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxQUG5FZ1BZeGJCN2dPZ3FOOS1WOGxHQnJWZ2QtOG9MejRYMER1YjhMVVUwZFRQX3BEWk9Xb3dqWWt1WjdSZnl5M3ZMckgybEdkQ3RpWnBBSjZ5d1lzdTNSbUktYnIzQnhmaDRnZHlEbnFnaV9sTjMwT1ZvQjFLQ2puWXJRMzUtU0pYcng1QzhaVTVUSHRibjBTekRn?oc=5</t>
         </is>
       </c>
       <c r="F123" t="n">
@@ -4121,17 +4121,17 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Polish port picked for offshore wind operations base - 4C Offshore</t>
+          <t>What is the Supply Chain Risk of the Rising Price of Gold? - Supply Chain Digital Magazine</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>Wed, 28 Jan 2026 12:47:32 GMT</t>
+          <t>Wed, 28 Jan 2026 13:14:51 GMT</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxOYWtJM1gyQmQ1Um9kMTJfclV1dTI5WUdVdmtQMEZ3RDV3dnpkZFdHWFZqSGwxUy1yZWZvdWQzVUY5dXRrZDh4VDhDRjlJYkttcWZMNjFEU3pzMFJFNWx4Q0pZYlVfY3FjZUNpVkEwaFBlUzVvNUwwSmtGNUNKQkRjbHBNYmhlLWdJV3Y1SmRENUMybEt4ZUdJelhSam1IVFU?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMie0FVX3lxTE4zc3pQV2E2RWZWckNscURzX0F4TThUY3MzejZJWWhiN2hYSWdxb3hNYzV3TV9VTmdJd0RGeExBMmVqT1M4MEV3c3puby1fVTRyTk10amcyYlJ4YnN1YU5SUDJyX1lqbEV0Sk1HbmMxSEVScC1TNFRadzVvQQ?oc=5</t>
         </is>
       </c>
       <c r="F124" t="n">
@@ -4151,17 +4151,17 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Historic building on the up after £3.2m restoration - inverclyde.gov.uk</t>
+          <t>Sussex: Coach Paul Farbrace expects side to face sanctions over finances - BBC</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>Wed, 28 Jan 2026 11:14:00 GMT</t>
+          <t>Wed, 28 Jan 2026 10:47:06 GMT</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxQUG5FZ1BZeGJCN2dPZ3FOOS1WOGxHQnJWZ2QtOG9MejRYMER1YjhMVVUwZFRQX3BEWk9Xb3dqWWt1WjdSZnl5M3ZMckgybEdkQ3RpWnBBSjZ5d1lzdTNSbUktYnIzQnhmaDRnZHlEbnFnaV9sTjMwT1ZvQjFLQ2puWXJRMzUtU0pYcng1QzhaVTVUSHRibjBTekRn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiZkFVX3lxTFBoZ2JHNmNxQ01JdlZPQWFna1U5RUpYSU5kOVJyWWxROTV3cV9FaUd6eFlmLWdLTmRZMFYxRWRFNmprSXdSM2owQ29OS3NlX0FWTkgtbkpLTUNHT2RWMkVYMnV1UjZ3QQ?oc=5</t>
         </is>
       </c>
       <c r="F125" t="n">
@@ -4181,17 +4181,17 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>What is the Supply Chain Risk of the Rising Price of Gold? - Supply Chain Digital Magazine</t>
+          <t>Sanctions without shock? United Nations snapback and Iran's oil exports - Clingendael</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>Wed, 28 Jan 2026 13:14:51 GMT</t>
+          <t>Wed, 28 Jan 2026 12:21:06 GMT</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMie0FVX3lxTE4zc3pQV2E2RWZWckNscURzX0F4TThUY3MzejZJWWhiN2hYSWdxb3hNYzV3TV9VTmdJd0RGeExBMmVqT1M4MEV3c3puby1fVTRyTk10amcyYlJ4YnN1YU5SUDJyX1lqbEV0Sk1HbmMxSEVScC1TNFRadzVvQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxQNEthalRKZ3ZROEFDc0FrMmg0SjJiVERYNjg2dkN5SjU4N3BxOTRQR0xjNEJVMXE5T1JUYlNwNjFjMjlYMUl2ZGlKckRTb2U2SlhTNXp6YWpXVmVQRXJVWndPUG9ueGpnUlVoTEZRZGthNzl5ODdYd1o5d2wwSEJHX3daVlhybk52T244T0pSa2hKVUlaanoxb3dsOTZZQ1dfNDFzWUpfWHNmaGY5Y1E?oc=5</t>
         </is>
       </c>
       <c r="F126" t="n">
@@ -4211,17 +4211,17 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Sussex: Coach Paul Farbrace expects side to face sanctions over finances - BBC</t>
+          <t>News Content Hub - Portside ballast water partnership targets discharge compliance - rivieramm.com</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>Wed, 28 Jan 2026 10:47:06 GMT</t>
+          <t>Wed, 28 Jan 2026 11:11:03 GMT</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiZkFVX3lxTFBoZ2JHNmNxQ01JdlZPQWFna1U5RUpYSU5kOVJyWWxROTV3cV9FaUd6eFlmLWdLTmRZMFYxRWRFNmprSXdSM2owQ29OS3NlX0FWTkgtbkpLTUNHT2RWMkVYMnV1UjZ3QQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxPbUZjNG0yS1BmOEdXSE5TbVJuSVRNdXBxTFFfQ2NURXRYWkhTcEFvX2N5Uk9NQ1VfOXZSM3N1RmI0VXhubWFmV1RmZ1p5bXFxcDBxNnFZdE9BamVNQVZBU0JKOXdRZk9tajBaYkFxTXFWbUF1RWRrZHY3bW05eEFVN1pDbTh3MmduN1RNaUtDVzBoUnlUc1NmTkhsNlNzMmx2ajh0NGtXaTlPb2hfVWtYWk8xcw?oc=5</t>
         </is>
       </c>
       <c r="F127" t="n">
@@ -4241,17 +4241,17 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Sanctions without shock? United Nations snapback and Iran's oil exports - Clingendael</t>
+          <t>Will the Volatile Ocean Freight Rates of the 2020s Give Way to a More Sedate Environment This Year? - International Banker</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>Wed, 28 Jan 2026 12:21:06 GMT</t>
+          <t>Wed, 28 Jan 2026 11:23:42 GMT</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxQNEthalRKZ3ZROEFDc0FrMmg0SjJiVERYNjg2dkN5SjU4N3BxOTRQR0xjNEJVMXE5T1JUYlNwNjFjMjlYMUl2ZGlKckRTb2U2SlhTNXp6YWpXVmVQRXJVWndPUG9ueGpnUlVoTEZRZGthNzl5ODdYd1o5d2wwSEJHX3daVlhybk52T244T0pSa2hKVUlaanoxb3dsOTZZQ1dfNDFzWUpfWHNmaGY5Y1E?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi1gFBVV95cUxPeXVoQk1qRFhKQXdzdWtkejRfalV2cDBhRTd6YTllQ3UzdURFb0s2cEljS0t3ckxPR1dDOXFBaWxNQmU3U0pOanFqeHZnN1lPVGZCVHRPZTM4aHhLdWh6SndaVkdBUVlhMmRmTHgzNGdIR2RCRFN1ajBpSHM2MGdNbHFDYl9pbHJJU1RJQ0dLa3dBOGlYU3RHb25fQ0hFbWMzNFRTVFpSMVZTVXFKRmp2azJpY1VYNmRsczZNYmFmNWx5X05pU3BSdndpbjFBbzZLWTdSUEh3?oc=5</t>
         </is>
       </c>
       <c r="F128" t="n">
@@ -4271,17 +4271,17 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>News Content Hub - Portside ballast water partnership targets discharge compliance - rivieramm.com</t>
+          <t>China’s ambassador warns Albanese reclaiming Port of Darwin will force Beijing to intervene - The Guardian</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>Wed, 28 Jan 2026 11:11:03 GMT</t>
+          <t>Wed, 28 Jan 2026 05:40:00 GMT</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxPbUZjNG0yS1BmOEdXSE5TbVJuSVRNdXBxTFFfQ2NURXRYWkhTcEFvX2N5Uk9NQ1VfOXZSM3N1RmI0VXhubWFmV1RmZ1p5bXFxcDBxNnFZdE9BamVNQVZBU0JKOXdRZk9tajBaYkFxTXFWbUF1RWRrZHY3bW05eEFVN1pDbTh3MmduN1RNaUtDVzBoUnlUc1NmTkhsNlNzMmx2ajh0NGtXaTlPb2hfVWtYWk8xcw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxQMmNPREs3S0RvS3RMbFd2SUlDcVloZXU4b1dtTVZHZmdkNy1VcEEteHFpMTNGcFdzak1hNXNHUHdzU3VSVHVnSENsU3k0WGhDa3EydkVlOFZxZmlrRjJqYl9SNG1XZ0FHNW1Cel9sQ2hfbVRDa1AzaUh5aW9vY3I0bklGUC1nNEZRTW0yckI4bFlDSzJNZUs5YnNyMXdncmZsenJZ?oc=5</t>
         </is>
       </c>
       <c r="F129" t="n">
@@ -4301,17 +4301,17 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Will the Volatile Ocean Freight Rates of the 2020s Give Way to a More Sedate Environment This Year? - International Banker</t>
+          <t>NHS announces next phase of supply chain engagement - Wired-Gov</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>Wed, 28 Jan 2026 11:23:42 GMT</t>
+          <t>Wed, 28 Jan 2026 11:26:05 GMT</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi1gFBVV95cUxPeXVoQk1qRFhKQXdzdWtkejRfalV2cDBhRTd6YTllQ3UzdURFb0s2cEljS0t3ckxPR1dDOXFBaWxNQmU3U0pOanFqeHZnN1lPVGZCVHRPZTM4aHhLdWh6SndaVkdBUVlhMmRmTHgzNGdIR2RCRFN1ajBpSHM2MGdNbHFDYl9pbHJJU1RJQ0dLa3dBOGlYU3RHb25fQ0hFbWMzNFRTVFpSMVZTVXFKRmp2azJpY1VYNmRsczZNYmFmNWx5X05pU3BSdndpbjFBbzZLWTdSUEh3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxQWnRaVkFDTy11NEtmMkZZRXVocHBLU2U5MGZ2MkVsVFRuaEpVYzNRNTVWOW9SY1ZOY2dHWnZoV184MS12dVZ3SXZVUTR4aWFOOFlOS1hTa0FDaUZtZDZFQWY0bjVIdWRPMEQweFNyZ3dkOUNzYzBrQV9pbzdPdTVMQ1Q3NGpqUUFCMG9RbHFqMmhJOUgtVmVzNGl1bzRKNExDdEYyLWdZYmE0d2xVV055dUNlSk1pSGVwdnc?oc=5</t>
         </is>
       </c>
       <c r="F130" t="n">
@@ -4331,17 +4331,17 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>China’s ambassador warns Albanese reclaiming Port of Darwin will force Beijing to intervene - The Guardian</t>
+          <t>Here's how China's response to Trump tariffs silently rocks bitcoin - Yahoo Finance UK</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>Wed, 28 Jan 2026 05:40:00 GMT</t>
+          <t>Wed, 28 Jan 2026 06:19:00 GMT</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxQMmNPREs3S0RvS3RMbFd2SUlDcVloZXU4b1dtTVZHZmdkNy1VcEEteHFpMTNGcFdzak1hNXNHUHdzU3VSVHVnSENsU3k0WGhDa3EydkVlOFZxZmlrRjJqYl9SNG1XZ0FHNW1Cel9sQ2hfbVRDa1AzaUh5aW9vY3I0bklGUC1nNEZRTW0yckI4bFlDSzJNZUs5YnNyMXdncmZsenJZ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijAFBVV95cUxPQjZ2T0pvS3FHbGlPN0NqTEdtOTBCMm1YaXplSEZLVUVMdkhuYlNkNVd0eU1PMXhXeGp2ZmlYbW9Ya3F1VHRKSW5qRzd0TmRHeDZYUUlxUzZUd2lfdU9kWF9XdXhvRFpiYUREd0lRRGtDNlBobFJ6cE1PdDVQcW1vanRoV19RdGd1VnBJeQ?oc=5</t>
         </is>
       </c>
       <c r="F131" t="n">
@@ -4361,17 +4361,17 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>NHS announces next phase of supply chain engagement - Wired-Gov</t>
+          <t>Investec provides £11m Croydon logistics loan - Green Street News</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>Wed, 28 Jan 2026 11:26:05 GMT</t>
+          <t>Wed, 28 Jan 2026 12:38:10 GMT</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxQWnRaVkFDTy11NEtmMkZZRXVocHBLU2U5MGZ2MkVsVFRuaEpVYzNRNTVWOW9SY1ZOY2dHWnZoV184MS12dVZ3SXZVUTR4aWFOOFlOS1hTa0FDaUZtZDZFQWY0bjVIdWRPMEQweFNyZ3dkOUNzYzBrQV9pbzdPdTVMQ1Q3NGpqUUFCMG9RbHFqMmhJOUgtVmVzNGl1bzRKNExDdEYyLWdZYmE0d2xVV055dUNlSk1pSGVwdnc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiiAFBVV95cUxPdWZGbjczXzJRTThhSkZmUHRBTFJ4R01QN2dlRXBsZmlmaVJaa2NmaVpjZmJtNnN0dXU5eW9BTy1CbTRNY0lxZDRUcU80Qm05UGVGa1FiQ201azZxNW95RXhFdmlWeEYyZzZNaDM2V2NxMEwyZ2xaYnZtUVljb1FiUlNoaHZSYkZK?oc=5</t>
         </is>
       </c>
       <c r="F132" t="n">
@@ -4391,17 +4391,17 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Here's how China's response to Trump tariffs silently rocks bitcoin - Yahoo Finance UK</t>
+          <t>Prysmian: Managing Material Shortages in APAC Data Centres - Supply Chain Digital Magazine</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>Wed, 28 Jan 2026 06:19:00 GMT</t>
+          <t>Wed, 28 Jan 2026 10:51:35 GMT</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijAFBVV95cUxPQjZ2T0pvS3FHbGlPN0NqTEdtOTBCMm1YaXplSEZLVUVMdkhuYlNkNVd0eU1PMXhXeGp2ZmlYbW9Ya3F1VHRKSW5qRzd0TmRHeDZYUUlxUzZUd2lfdU9kWF9XdXhvRFpiYUREd0lRRGtDNlBobFJ6cE1PdDVQcW1vanRoV19RdGd1VnBJeQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilAFBVV95cUxPR19ocm5GZl96OEpaN3R0NjNiM2xMTURNVmNzZGRGNUY0cWwwbDNVN0FpMWUzMm50cTJSSlhYMzdzU3JqZjBPTC1obHN2cE4tNXRYd0NZS2hoMmNjeThiOXNUSWstQ1ZscDVMS2p3RE1ha2c3U1dxZDFvRURHS3hNYXNXUXV6UFl3dy1TVkRhTnIyeEJj?oc=5</t>
         </is>
       </c>
       <c r="F133" t="n">
@@ -4421,17 +4421,17 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Investec provides £11m Croydon logistics loan - Green Street News</t>
+          <t>Scotland-France ferry could relaunch amid £35bn Dunkirk regeneration plan - The Guardian</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>Wed, 28 Jan 2026 12:38:10 GMT</t>
+          <t>Wed, 28 Jan 2026 02:30:00 GMT</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiiAFBVV95cUxPdWZGbjczXzJRTThhSkZmUHRBTFJ4R01QN2dlRXBsZmlmaVJaa2NmaVpjZmJtNnN0dXU5eW9BTy1CbTRNY0lxZDRUcU80Qm05UGVGa1FiQ201azZxNW95RXhFdmlWeEYyZzZNaDM2V2NxMEwyZ2xaYnZtUVljb1FiUlNoaHZSYkZK?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxOZmw1YUY3M3JPcENyVTEteUZqd254R3R3aFlxTTFTTXRNdDZfekF0NlNWbXI4dVVWdVFFd0V0WlUtQ3pNM0pvOTNsMDQ0c0V0RHpNcVFLUWxTLU4wcDNyb2VsWmxRNDdJOHowSU5KWUZUSmhpNVUxVURfRVpvU2Q2dlB4ejZGQ212TjVYWTJyR0QwMEY2aHgwYXlQSEw?oc=5</t>
         </is>
       </c>
       <c r="F134" t="n">
@@ -4451,17 +4451,17 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Prysmian: Managing Material Shortages in APAC Data Centres - Supply Chain Digital Magazine</t>
+          <t>Strong cruise performance and stable ferry traffic at the Port of Tallinn in 2025 - Shippax</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>Wed, 28 Jan 2026 10:51:35 GMT</t>
+          <t>Wed, 28 Jan 2026 07:24:40 GMT</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilAFBVV95cUxPR19ocm5GZl96OEpaN3R0NjNiM2xMTURNVmNzZGRGNUY0cWwwbDNVN0FpMWUzMm50cTJSSlhYMzdzU3JqZjBPTC1obHN2cE4tNXRYd0NZS2hoMmNjeThiOXNUSWstQ1ZscDVMS2p3RE1ha2c3U1dxZDFvRURHS3hNYXNXUXV6UFl3dy1TVkRhTnIyeEJj?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxQR19Sb2ZRMDZ1Qm80Q0dwUmFZUHJ5Sm5qRUZmWG9IeGNCVHRKTHIyWlN1UjJNY29obGtlQjVXM2pUbTVrQXA1OFNGYU9tVTdFX1Z3VWQ0TlktcnJkenRuS0gxdE9oc2VfQXFWbnRUeV9YeGZBVXRzMm53Wm92QVNvRmpNTGlEZDdwMlZYVEx0TzhNOUVOSksybkNjZTlXOW5KN2F6SjhvSDQ2TmZqYjh0c0lwZjZick9YUXc?oc=5</t>
         </is>
       </c>
       <c r="F135" t="n">
@@ -4481,17 +4481,17 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Scotland-France ferry could relaunch amid £35bn Dunkirk regeneration plan - The Guardian</t>
+          <t>MGA expands freight liability appetite with new vehicle transporter policy - Insurance Times</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>Wed, 28 Jan 2026 02:30:00 GMT</t>
+          <t>Wed, 28 Jan 2026 14:32:56 GMT</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxOZmw1YUY3M3JPcENyVTEteUZqd254R3R3aFlxTTFTTXRNdDZfekF0NlNWbXI4dVVWdVFFd0V0WlUtQ3pNM0pvOTNsMDQ0c0V0RHpNcVFLUWxTLU4wcDNyb2VsWmxRNDdJOHowSU5KWUZUSmhpNVUxVURfRVpvU2Q2dlB4ejZGQ212TjVYWTJyR0QwMEY2aHgwYXlQSEw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixwFBVV95cUxOdlR6VDFJeE9lSTdxb0lLZjFmOWNZSHNZQ2JPbjNTYk43amF4N1F2RGc5QzZRd0ZkT1J5QWVwM1REQzZURTJoaG1LWXFybFZDMGU5MkdoRVN4emw2cTN3VlU3Ui10dFp6VWNCUFJyckRCd1M3TXBZb09VZF9wNEp5Z19LZjVSUGNCLWd2YXpsZE5uczYwWUhIZjRUUGhlNnlyVjQwRjl3c1hmd2RQaTlUWkg0dTYzZmRPeC1tVF9nb3hJb0l0XzZv?oc=5</t>
         </is>
       </c>
       <c r="F136" t="n">
@@ -4511,17 +4511,17 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Strong cruise performance and stable ferry traffic at the Port of Tallinn in 2025 - Shippax</t>
+          <t>Edeka Turns to Voice Tech - Logistics Business</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>Wed, 28 Jan 2026 07:24:40 GMT</t>
+          <t>Wed, 28 Jan 2026 12:28:40 GMT</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxQR19Sb2ZRMDZ1Qm80Q0dwUmFZUHJ5Sm5qRUZmWG9IeGNCVHRKTHIyWlN1UjJNY29obGtlQjVXM2pUbTVrQXA1OFNGYU9tVTdFX1Z3VWQ0TlktcnJkenRuS0gxdE9oc2VfQXFWbnRUeV9YeGZBVXRzMm53Wm92QVNvRmpNTGlEZDdwMlZYVEx0TzhNOUVOSksybkNjZTlXOW5KN2F6SjhvSDQ2TmZqYjh0c0lwZjZick9YUXc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxPN043YnVMN3VYRlhQVUR4WExxTm9MNHhlRXlIZ0hreS15Q2x5c2FmcE40alRNT0o4NEZZMEVtYmRXTW1kcFJQemRnVXdUWTlHTDJneTJSS0FEdTFfNHNLQmpkN1c4ZEZQZTVTMXVWTHRmVWxDVXlncWRLT29mcWxPNjdRTHliWURBYlVSSmYzaWU4VERLUlpmaTNkRQ?oc=5</t>
         </is>
       </c>
       <c r="F137" t="n">
@@ -4541,17 +4541,17 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>MGA expands freight liability appetite with new vehicle transporter policy - Insurance Times</t>
+          <t>EC initiates steps for Google’s compliance with Digital Markets Act - verdict.co.uk</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>Wed, 28 Jan 2026 14:32:56 GMT</t>
+          <t>Wed, 28 Jan 2026 09:17:55 GMT</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixwFBVV95cUxOdlR6VDFJeE9lSTdxb0lLZjFmOWNZSHNZQ2JPbjNTYk43amF4N1F2RGc5QzZRd0ZkT1J5QWVwM1REQzZURTJoaG1LWXFybFZDMGU5MkdoRVN4emw2cTN3VlU3Ui10dFp6VWNCUFJyckRCd1M3TXBZb09VZF9wNEp5Z19LZjVSUGNCLWd2YXpsZE5uczYwWUhIZjRUUGhlNnlyVjQwRjl3c1hmd2RQaTlUWkg0dTYzZmRPeC1tVF9nb3hJb0l0XzZv?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMifEFVX3lxTFBRZllVX2RIU2prbmJwUkVwRExYb0tBcHlQOUFFeWcwcWhMS0FQaVJ6TzZsSnlIVHFuUzEwSWlrZjZ2U2NDdUh4dUNNbGszWThLc2l0elgxYmowLXZsalFydWFfWlVtLWhhd0lPV0dkc2xOUVRkeVBuMzU0TXc?oc=5</t>
         </is>
       </c>
       <c r="F138" t="n">
@@ -4571,17 +4571,17 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Edeka Turns to Voice Tech - Logistics Business</t>
+          <t>Technology ‘Business Case’ isn’t a Strategy - Logistics Business</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>Wed, 28 Jan 2026 12:28:40 GMT</t>
+          <t>Wed, 28 Jan 2026 11:58:51 GMT</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxPN043YnVMN3VYRlhQVUR4WExxTm9MNHhlRXlIZ0hreS15Q2x5c2FmcE40alRNT0o4NEZZMEVtYmRXTW1kcFJQemRnVXdUWTlHTDJneTJSS0FEdTFfNHNLQmpkN1c4ZEZQZTVTMXVWTHRmVWxDVXlncWRLT29mcWxPNjdRTHliWURBYlVSSmYzaWU4VERLUlpmaTNkRQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxPSXVfYnlRSXcyZ2JFamlYdENCMGFVUVZFY3F3M2xUNEl5WWpiVmJlVnpFd2RiRVNHQ3VzTFNLSm02RFc3YjZRM01CSmJYVy1KTWVNR0VaTTgtVFBYRTRYVnIyV090UEZaTGFGbXJrR2poVkFkWW5pd0tseDJ3SWVHT0p2WjZUaEtHb196cWNCaTc?oc=5</t>
         </is>
       </c>
       <c r="F139" t="n">
@@ -4601,17 +4601,17 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>EC initiates steps for Google’s compliance with Digital Markets Act - verdict.co.uk</t>
+          <t>Top 10: Supplier Collaboration Platforms - Supply Chain Digital Magazine</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>Wed, 28 Jan 2026 09:17:55 GMT</t>
+          <t>Wed, 28 Jan 2026 11:39:46 GMT</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMifEFVX3lxTFBRZllVX2RIU2prbmJwUkVwRExYb0tBcHlQOUFFeWcwcWhMS0FQaVJ6TzZsSnlIVHFuUzEwSWlrZjZ2U2NDdUh4dUNNbGszWThLc2l0elgxYmowLXZsalFydWFfWlVtLWhhd0lPV0dkc2xOUVRkeVBuMzU0TXc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiggFBVV95cUxNS0JrZ3pWNk9LeUoweUVNdkdacHo2UFY3ZTUyaHNJLUhhRDhGSWRoQWN4UXdaeHdnYUhJZ3Jqc1RKaHpxdkJLX2VJZU5WRFl0Yktid0NlTU1jcjREMzJtN200MmVzd0t6UVQ3NzNlVWJRUVNLT3ZsQ0oyYWFBVDdQQ1Zn?oc=5</t>
         </is>
       </c>
       <c r="F140" t="n">
@@ -4631,17 +4631,17 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Technology ‘Business Case’ isn’t a Strategy - Logistics Business</t>
+          <t>Exiger teams up with Snowflake to bring AI-driven supply chain and risk intelligence to the energy sector - Industrial Cyber</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>Wed, 28 Jan 2026 11:58:51 GMT</t>
+          <t>Wed, 28 Jan 2026 08:18:35 GMT</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxPSXVfYnlRSXcyZ2JFamlYdENCMGFVUVZFY3F3M2xUNEl5WWpiVmJlVnpFd2RiRVNHQ3VzTFNLSm02RFc3YjZRM01CSmJYVy1KTWVNR0VaTTgtVFBYRTRYVnIyV090UEZaTGFGbXJrR2poVkFkWW5pd0tseDJ3SWVHT0p2WjZUaEtHb196cWNCaTc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi1AFBVV95cUxOWGs0RkpTcklGc3lmWUNka3BJSmx4WTUtLTFBY29UMUg4SE9PcmhVdEdNUU5oeTdwSlVlRURPNGh1S1AxQzVUOFRPbDVmaWRLaUJnY1dGRjBqcjM3ZlNlNFZ6YkNja28ya25fd1RRaGVKVUhPVzNmNHV1Z0pEaEliRUw2bFpLenpzMEwxcGVnYmZzaWVDSEd2VmFtdkhndGFNUjkzQ3U3TkJUM3pySnZkY0kzUzdxNVZHNmh5S21uaWkzN0FuQjJHVzllWW5faHJRUzczdg?oc=5</t>
         </is>
       </c>
       <c r="F141" t="n">
@@ -4661,17 +4661,17 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Top 10: Supplier Collaboration Platforms - Supply Chain Digital Magazine</t>
+          <t>IEA examines warehousing needs for stockpiling critical minerals - Logistics Manager</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>Wed, 28 Jan 2026 11:39:46 GMT</t>
+          <t>Wed, 28 Jan 2026 12:04:05 GMT</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiggFBVV95cUxNS0JrZ3pWNk9LeUoweUVNdkdacHo2UFY3ZTUyaHNJLUhhRDhGSWRoQWN4UXdaeHdnYUhJZ3Jqc1RKaHpxdkJLX2VJZU5WRFl0Yktid0NlTU1jcjREMzJtN200MmVzd0t6UVQ3NzNlVWJRUVNLT3ZsQ0oyYWFBVDdQQ1Zn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxOcTV2RmlLUkpyRzAybmVJNzYyN09aVENGX3VXcWRLbjdXYjdFcTRacURWTzctTnc1RkM3VkowQUoxUlJXcHF0STlQd2FsRExHemNWNFRIWlpqV0R0Q0k3VkJZWlZ2ZDZ6ZDA2a0loV19KaEFUZmlHYVo1eUVqQTlXdDVsYkdmWWZISWdnN3dldmViZkhSRE1UTDFwenRtSTg?oc=5</t>
         </is>
       </c>
       <c r="F142" t="n">
@@ -4691,17 +4691,17 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Exiger teams up with Snowflake to bring AI-driven supply chain and risk intelligence to the energy sector - Industrial Cyber</t>
+          <t>Stuart reports 97% compliance with age-restricted deliveries - conveniencestore.co.uk</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>Wed, 28 Jan 2026 08:18:35 GMT</t>
+          <t>Wed, 28 Jan 2026 14:36:49 GMT</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi1AFBVV95cUxOWGs0RkpTcklGc3lmWUNka3BJSmx4WTUtLTFBY29UMUg4SE9PcmhVdEdNUU5oeTdwSlVlRURPNGh1S1AxQzVUOFRPbDVmaWRLaUJnY1dGRjBqcjM3ZlNlNFZ6YkNja28ya25fd1RRaGVKVUhPVzNmNHV1Z0pEaEliRUw2bFpLenpzMEwxcGVnYmZzaWVDSEd2VmFtdkhndGFNUjkzQ3U3TkJUM3pySnZkY0kzUzdxNVZHNmh5S21uaWkzN0FuQjJHVzllWW5faHJRUzczdg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxPZVg1X21GYmlkSExmUXBhYksxbFhfaTM1TTFwZENtdndidHFnRFB4U1lLTjRockt0VHY0d2hMZDU4eG10RzhRTXNYb2lxN3JPcnJhTmxJSVZzUTRpcU5zVExTcXpiY1FPVDZKMGZBdmo0WUE2MGR4Wkd5UUF2QnY4bE96U0xkb19EcnlnM1JhUUZlTnVfeHYtRElaeG03QWl4T05qbURfc1hIdnNBOUxhb2k3cHhERW5Samc?oc=5</t>
         </is>
       </c>
       <c r="F143" t="n">
@@ -4721,17 +4721,17 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>IEA examines warehousing needs for stockpiling critical minerals - Logistics Manager</t>
+          <t>Software provider announced for new cargo terminal in Vietnam - Logistics Manager</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>Wed, 28 Jan 2026 12:04:05 GMT</t>
+          <t>Wed, 28 Jan 2026 09:00:40 GMT</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxOcTV2RmlLUkpyRzAybmVJNzYyN09aVENGX3VXcWRLbjdXYjdFcTRacURWTzctTnc1RkM3VkowQUoxUlJXcHF0STlQd2FsRExHemNWNFRIWlpqV0R0Q0k3VkJZWlZ2ZDZ6ZDA2a0loV19KaEFUZmlHYVo1eUVqQTlXdDVsYkdmWWZISWdnN3dldmViZkhSRE1UTDFwenRtSTg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxPaUJkOFNIVDVGVkkyZlNjY1BwZjlXZWo0bk1NeE5PUEx2dkNGMjRGTFJnbjFESk5pazJZcElySFdSYXFERkNmQkRiRWlTRVpUbndVWWhlUUNCZExTOTVqbTV0Wm5YdG5RZVg2Qkp2X0phelQ0amNiWU82b2hHLXc1Zm1IQVM0YlZvcktUSC1ZVURIUVdlQUdxZGVTdw?oc=5</t>
         </is>
       </c>
       <c r="F144" t="n">
@@ -4751,17 +4751,17 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Stuart reports 97% compliance with age-restricted deliveries - conveniencestore.co.uk</t>
+          <t>Credit, compliance and cargo - Air Cargo Week</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>Wed, 28 Jan 2026 14:36:49 GMT</t>
+          <t>Wed, 28 Jan 2026 08:36:28 GMT</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxPZVg1X21GYmlkSExmUXBhYksxbFhfaTM1TTFwZENtdndidHFnRFB4U1lLTjRockt0VHY0d2hMZDU4eG10RzhRTXNYb2lxN3JPcnJhTmxJSVZzUTRpcU5zVExTcXpiY1FPVDZKMGZBdmo0WUE2MGR4Wkd5UUF2QnY4bE96U0xkb19EcnlnM1JhUUZlTnVfeHYtRElaeG03QWl4T05qbURfc1hIdnNBOUxhb2k3cHhERW5Samc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiY0FVX3lxTE1zTmpncVJhVEdmWU5XTEs0eFR1ejFSMW9mV3djRVdGUUotSHdTamhBaWJibGhNeFNUTGlPMFk3bDIwSl9uRmRhUVM3c1FuNTA2M3ZzRW5ULTBHVFRkVHZDMjNDUQ?oc=5</t>
         </is>
       </c>
       <c r="F145" t="n">
@@ -4781,17 +4781,17 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Software provider announced for new cargo terminal in Vietnam - Logistics Manager</t>
+          <t>Port of Tyne Director to lead Harwich Haven Authority - Port Technology</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>Wed, 28 Jan 2026 09:00:40 GMT</t>
+          <t>Wed, 28 Jan 2026 11:05:49 GMT</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxPaUJkOFNIVDVGVkkyZlNjY1BwZjlXZWo0bk1NeE5PUEx2dkNGMjRGTFJnbjFESk5pazJZcElySFdSYXFERkNmQkRiRWlTRVpUbndVWWhlUUNCZExTOTVqbTV0Wm5YdG5RZVg2Qkp2X0phelQ0amNiWU82b2hHLXc1Zm1IQVM0YlZvcktUSC1ZVURIUVdlQUdxZGVTdw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilAFBVV95cUxPQTd3SkFXdlZERzlkcjFGWUJMaHhfNEhMTVl4VHVCMUFYUkJSN1pLei1Ecng4TnFIUG9lVmQxYkkwNU15LUFEckpPUVBRVmlsZE82eXF2QjA3bm5zcHJKaTViMVB3N3FyY1Y0UHN5SHE2MnBpanRhZWJkclZLcHAzVkxCQ2ZOVHcwamxfX1JFVTZ6aFlH?oc=5</t>
         </is>
       </c>
       <c r="F146" t="n">
@@ -4811,17 +4811,17 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Credit, compliance and cargo - Air Cargo Week</t>
+          <t>New freight vessel begins sea trials - businesscornwall.co.uk</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>Wed, 28 Jan 2026 08:36:28 GMT</t>
+          <t>Wed, 28 Jan 2026 12:25:08 GMT</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiY0FVX3lxTE1zTmpncVJhVEdmWU5XTEs0eFR1ejFSMW9mV3djRVdGUUotSHdTamhBaWJibGhNeFNUTGlPMFk3bDIwSl9uRmRhUVM3c1FuNTA2M3ZzRW5ULTBHVFRkVHZDMjNDUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxNeE52SlFOYUNtMTQzZTlvMHQ1YmJaTEZZV3JuRVhjb1BVdXhhcjhqelFJeEVxT003MWJ0R3FoMVVZTGJsQVJjOGRMOE1QNVNuMDRmeENlaTRlcFRuUm9ncU5CMVE5MTdZazhxR3NsQW9XYjI4a05NY1pjajlXV2Y4clVaZng1VDUtdnZWYV8tdjZRcGJkQ1FlYlkyb0ZIZFdYSGhNTHdhV2lEWkY3SlVJRGxwWmxrSXM?oc=5</t>
         </is>
       </c>
       <c r="F147" t="n">
@@ -4841,17 +4841,17 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Port of Tyne Director to lead Harwich Haven Authority - Port Technology</t>
+          <t>Sustainability award recognizes value across the full supply chain - NutraIngredients.com</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>Wed, 28 Jan 2026 11:05:49 GMT</t>
+          <t>Wed, 28 Jan 2026 12:11:01 GMT</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilAFBVV95cUxPQTd3SkFXdlZERzlkcjFGWUJMaHhfNEhMTVl4VHVCMUFYUkJSN1pLei1Ecng4TnFIUG9lVmQxYkkwNU15LUFEckpPUVBRVmlsZE82eXF2QjA3bm5zcHJKaTViMVB3N3FyY1Y0UHN5SHE2MnBpanRhZWJkclZLcHAzVkxCQ2ZOVHcwamxfX1JFVTZ6aFlH?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxPSGJpT3RUSlZIc2dwSU5jZmlUSnN1SkhFd0RfX201elIybmZ3eUFscUVUdl9ZSGhkd2Q0d2dFcHU2Ti1mX01TeWhVcDRnbjFrNkRCd0tqRkM5bXJ1TTdicDhIS2stWE82Ykw2cEFzWEFXZWZRekVZRGxMSjNmYjBEd09iZTZjNXdGUC01UDhNVzJET3ZRMTBhdTBfdHEwRW5QbEpRTG5RV045M2NNVWdYQWRhcU9scUFLZWxV?oc=5</t>
         </is>
       </c>
       <c r="F148" t="n">
@@ -4871,17 +4871,17 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>New freight vessel begins sea trials - businesscornwall.co.uk</t>
+          <t>EU steel defence: Tougher tariffs in, Russian steel out - ALDE Party</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>Wed, 28 Jan 2026 12:25:08 GMT</t>
+          <t>Wed, 28 Jan 2026 09:43:52 GMT</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxNeE52SlFOYUNtMTQzZTlvMHQ1YmJaTEZZV3JuRVhjb1BVdXhhcjhqelFJeEVxT003MWJ0R3FoMVVZTGJsQVJjOGRMOE1QNVNuMDRmeENlaTRlcFRuUm9ncU5CMVE5MTdZazhxR3NsQW9XYjI4a05NY1pjajlXV2Y4clVaZng1VDUtdnZWYV8tdjZRcGJkQ1FlYlkyb0ZIZFdYSGhNTHdhV2lEWkY3SlVJRGxwWmxrSXM?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxQU2g5VDlTRmJXMFlHSjFjcUlEOEVDdk9Cb0NRNUhrZ3UyS1lHSkhLdDVYc3hlcXNoVDFVUHgwdDZzMU12bkJzdFZzRXpLOHJzbWNQX1ZpaEJEam5zTktlYzlrc2ZzMWRCdm4tOU1nXzZrN1dNaFZtbHJuV1hldjRVaWU0cEEyNHlyUkI4OURkbEVfeDNGY1FyZU5lUQ?oc=5</t>
         </is>
       </c>
       <c r="F149" t="n">
@@ -4901,17 +4901,17 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Sustainability award recognizes value across the full supply chain - NutraIngredients.com</t>
+          <t>Tax Disputes: HMRC compliance, key risks, and upcoming changes - KPMG</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>Wed, 28 Jan 2026 12:11:01 GMT</t>
+          <t>Wed, 28 Jan 2026 04:09:39 GMT</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxPSGJpT3RUSlZIc2dwSU5jZmlUSnN1SkhFd0RfX201elIybmZ3eUFscUVUdl9ZSGhkd2Q0d2dFcHU2Ti1mX01TeWhVcDRnbjFrNkRCd0tqRkM5bXJ1TTdicDhIS2stWE82Ykw2cEFzWEFXZWZRekVZRGxMSjNmYjBEd09iZTZjNXdGUC01UDhNVzJET3ZRMTBhdTBfdHEwRW5QbEpRTG5RV045M2NNVWdYQWRhcU9scUFLZWxV?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiY0FVX3lxTFBkQURtRVZKMi1HdFA5bDk3eEZxWGNKdk51YU9QclpIYzF3cG5LWmFLUjdpcWpGcndHNWxrSEIwSHBXbGJ6WV81YURsU19IMUtMQ0NoS04tVnVGWFJPdTZ4Zk84VQ?oc=5</t>
         </is>
       </c>
       <c r="F150" t="n">
@@ -4931,17 +4931,17 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>EU steel defence: Tougher tariffs in, Russian steel out - ALDE Party</t>
+          <t>Weak EV battery supply chain puts British businesses at risk - Environment Journal</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>Wed, 28 Jan 2026 09:43:52 GMT</t>
+          <t>Wed, 28 Jan 2026 08:03:56 GMT</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxQU2g5VDlTRmJXMFlHSjFjcUlEOEVDdk9Cb0NRNUhrZ3UyS1lHSkhLdDVYc3hlcXNoVDFVUHgwdDZzMU12bkJzdFZzRXpLOHJzbWNQX1ZpaEJEam5zTktlYzlrc2ZzMWRCdm4tOU1nXzZrN1dNaFZtbHJuV1hldjRVaWU0cEEyNHlyUkI4OURkbEVfeDNGY1FyZU5lUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxPVE50X2VlMHluNkVHUGFtVU5hQXNWaUpDQmd6X2dkX1VLRmlyb2hJc2gzd2xDYmQ5UDRjZXNzVnZZV3VHUk9STE9CVXdxVTRUU19aaHJXaEctOGJ2N3BPV2w3U09KalVka0lXUmFwTlNScDFfUllWdEprQ29uRHI4aTl1QnZrSGVueUFQVnNicW05dW80UlhkSkFleTVtTk5Ub09reg?oc=5</t>
         </is>
       </c>
       <c r="F151" t="n">
@@ -4961,17 +4961,17 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Tax Disputes: HMRC compliance, key risks, and upcoming changes - KPMG</t>
+          <t>b-next and Behavox join forces to advance capital markets compliance - FinTech Global</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>Wed, 28 Jan 2026 04:09:39 GMT</t>
+          <t>Wed, 28 Jan 2026 11:16:17 GMT</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiY0FVX3lxTFBkQURtRVZKMi1HdFA5bDk3eEZxWGNKdk51YU9QclpIYzF3cG5LWmFLUjdpcWpGcndHNWxrSEIwSHBXbGJ6WV81YURsU19IMUtMQ0NoS04tVnVGWFJPdTZ4Zk84VQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxQOGlLdEUtNjBUTW4yRTNUdjVVdEFJTWhQZC1VTHpQVERRQTR4ZHFDeG1CX1VIZDZoRnNWcFVxSTJzUE1WTXN4eTM4RThQbHZsZU1MWDhxTXl0aGxQRldfVmx3WGw1QTJ0YktwaVgyWVNBVUdnTUxHTHo2S1VIMWZySXlwaXEzR19TT0tKS29IR0x5dm8zdG9nQTZXZWd1VUpFbm1DYXFB?oc=5</t>
         </is>
       </c>
       <c r="F152" t="n">
@@ -4991,17 +4991,17 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Weak EV battery supply chain puts British businesses at risk - Environment Journal</t>
+          <t>What is the Cause of the Supply Chain Confidence Gap? - Procurement Magazine</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>Wed, 28 Jan 2026 08:03:56 GMT</t>
+          <t>Wed, 28 Jan 2026 12:29:31 GMT</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxPVE50X2VlMHluNkVHUGFtVU5hQXNWaUpDQmd6X2dkX1VLRmlyb2hJc2gzd2xDYmQ5UDRjZXNzVnZZV3VHUk9STE9CVXdxVTRUU19aaHJXaEctOGJ2N3BPV2w3U09KalVka0lXUmFwTlNScDFfUllWdEprQ29uRHI4aTl1QnZrSGVueUFQVnNicW05dW80UlhkSkFleTVtTk5Ub09reg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMic0FVX3lxTE1TcjNlVmZ1M19zcDVQcGZ5bFZFNDA4R2ZxNWxUaGNneGVYTkRSTVVac2JMUXlWeHJmZEZyNkQzOHN1cGFpWG9LQ2NycmRSb2hjTjBIVnp3ZFZlWTZLX1lfNUJCOUp0MnlXc2o1LVlvWmlQNDQ?oc=5</t>
         </is>
       </c>
       <c r="F153" t="n">
@@ -5021,17 +5021,17 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>b-next and Behavox join forces to advance capital markets compliance - FinTech Global</t>
+          <t>European road operator launches U.S. coast-to-coast freight - Trans.INFO</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>Wed, 28 Jan 2026 11:16:17 GMT</t>
+          <t>Wed, 28 Jan 2026 13:27:13 GMT</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxQOGlLdEUtNjBUTW4yRTNUdjVVdEFJTWhQZC1VTHpQVERRQTR4ZHFDeG1CX1VIZDZoRnNWcFVxSTJzUE1WTXN4eTM4RThQbHZsZU1MWDhxTXl0aGxQRldfVmx3WGw1QTJ0YktwaVgyWVNBVUdnTUxHTHo2S1VIMWZySXlwaXEzR19TT0tKS29IR0x5dm8zdG9nQTZXZWd1VUpFbm1DYXFB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiY0FVX3lxTE5STFVxZFIyamZETU1TNVVfRXNQSExvMUFvTUxaUzJIdTRET3ZfOHRjNGVjQVgyMnRNaDhQVGk3am1ESUhyVU8tdDctenE3dEkzMUlrbjFiTjZ1enRycVJzMV9hbw?oc=5</t>
         </is>
       </c>
       <c r="F154" t="n">
@@ -5051,17 +5051,17 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>What is the Cause of the Supply Chain Confidence Gap? - Procurement Magazine</t>
+          <t>US to Ease Venezuela Oil Sanctions to Speed Exports - Offshore Engineer Magazine</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>Wed, 28 Jan 2026 12:29:31 GMT</t>
+          <t>Wed, 28 Jan 2026 08:57:59 GMT</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMic0FVX3lxTE1TcjNlVmZ1M19zcDVQcGZ5bFZFNDA4R2ZxNWxUaGNneGVYTkRSTVVac2JMUXlWeHJmZEZyNkQzOHN1cGFpWG9LQ2NycmRSb2hjTjBIVnp3ZFZlWTZLX1lfNUJCOUp0MnlXc2o1LVlvWmlQNDQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxOYzB0WWJEQ01EQzlxVlZZZzgwbEJpS3lwOE1aRVotY05mSTJHVTN5RW5GMEtJVEMyWHdVMFBiMUozU3E0ZXNaYTVHZDI4Y3JLUzU4RDQ5TXN1M3VlTDN3d1BscVlPbG9BZVRiUGlEUWc3amYzaF9wNkRXTDdYZXRrcV9jQ193dlBwd3hRNjJMZnlVdGM?oc=5</t>
         </is>
       </c>
       <c r="F155" t="n">
@@ -5081,17 +5081,17 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>European road operator launches U.S. coast-to-coast freight - Trans.INFO</t>
+          <t>Moving sustainability compliance beyond box-ticking - Fruitnet</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>Wed, 28 Jan 2026 13:27:13 GMT</t>
+          <t>Wed, 28 Jan 2026 09:25:12 GMT</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiY0FVX3lxTE5STFVxZFIyamZETU1TNVVfRXNQSExvMUFvTUxaUzJIdTRET3ZfOHRjNGVjQVgyMnRNaDhQVGk3am1ESUhyVU8tdDctenE3dEkzMUlrbjFiTjZ1enRycVJzMV9hbw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxQRS1hVDRZbFlYb2VXeEd5a3NhUlpLOTduTVJaaEJwQ0Z1ZlVZY2tDUlI2NURPMHJTMWRtWVMxRy1pZmFLTm85ODRrdzNqNU1BRVlEMDl2WExEaC12R05aQnhvZ3RWWWJQdFlacXNuV0ZPYzBuYlF3el9DdTNnLVprXzZmbW1oNnFFMEIxdGJHZlkyTXNLRFR4dEtZb3g4elNoQnBj?oc=5</t>
         </is>
       </c>
       <c r="F156" t="n">
@@ -5111,17 +5111,17 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>US to Ease Venezuela Oil Sanctions to Speed Exports - Offshore Engineer Magazine</t>
+          <t>2050 Port Vision officially launched - portofrotterdam.com</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>Wed, 28 Jan 2026 08:57:59 GMT</t>
+          <t>Wed, 28 Jan 2026 08:02:32 GMT</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxOYzB0WWJEQ01EQzlxVlZZZzgwbEJpS3lwOE1aRVotY05mSTJHVTN5RW5GMEtJVEMyWHdVMFBiMUozU3E0ZXNaYTVHZDI4Y3JLUzU4RDQ5TXN1M3VlTDN3d1BscVlPbG9BZVRiUGlEUWc3amYzaF9wNkRXTDdYZXRrcV9jQ193dlBwd3hRNjJMZnlVdGM?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxOVm1maWMyM2FpVmlTWTNCclg1UWM4aGI0blNHNVdqV0dxdVhkZVQzSDY3UDZnN3dFMGJ2VjNvVDJQenFCZHpxbDhaeGR5eHNIZF9SM2JicnV1eHRnbjZMSjhBa21ybXBKOWVuRnJWTWE0N0h5UnNRWnJjMkN4dXFUY3gzRTVNOUFjay1kbDc2SEt4VE5nNTBMMGdiUQ?oc=5</t>
         </is>
       </c>
       <c r="F157" t="n">
@@ -5131,27 +5131,27 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>Supply_Chain</t>
+          <t>Protest</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally OR tactics OR targets OR groups)</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Moving sustainability compliance beyond box-ticking - Fruitnet</t>
+          <t>More 'No Kings' protests planned for March 28 as outrage spreads over Minneapolis deaths - ABC News</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>Wed, 28 Jan 2026 09:25:12 GMT</t>
+          <t>Wed, 28 Jan 2026 11:09:27 GMT</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxQRS1hVDRZbFlYb2VXeEd5a3NhUlpLOTduTVJaaEJwQ0Z1ZlVZY2tDUlI2NURPMHJTMWRtWVMxRy1pZmFLTm85ODRrdzNqNU1BRVlEMDl2WExEaC12R05aQnhvZ3RWWWJQdFlacXNuV0ZPYzBuYlF3el9DdTNnLVprXzZmbW1oNnFFMEIxdGJHZlkyTXNLRFR4dEtZb3g4elNoQnBj?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxNWGlGcy1ub0RtU2REQzJreEE0ZlN2OWhxbUEyamxJenVIcmtFZVhZcDV3cE1LR0drUUN3amRrMFJ1c24wQjkxQlpGTmpqRmFqTUhwcTRzZ1dkNDBoVnVxcXA0X0ZNaGtHZzcyS0d5MEpZeEtIY3lTYkFRQm9ma2QyRXBmS2dEVDc3UUhBaWlEZldqZzQ5bHBrQ3NLLXRrUlk1MVA3eldORUTSAa4BQVVfeXFMT190cXhqdE9NOWlJZmdFSk5IQzhtUWNwYU5nWHpnVmlfaGlJUFF2aUptY2E3S0s4anNWYVEyVWpNckpOaXh3MXVCc09IekpTUTJvTmRJTHVwVkRoU2QtTzVtRUxTMlcwVkxVUU1wV2tPLWtHQ0xxeU1vUF9hTk56dW4wbWJPZU9FTUpFSXFxUGx5cWV3S2c4X0haUGZneG9uX2ozTzdqSXpLeFQxSDZn?oc=5</t>
         </is>
       </c>
       <c r="F158" t="n">
@@ -5161,27 +5161,27 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>Supply_Chain</t>
+          <t>Protest</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally OR tactics OR targets OR groups)</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>2050 Port Vision officially launched - portofrotterdam.com</t>
+          <t>Police throw child to the ground during Rojava protest in Mardin - Bianet</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>Wed, 28 Jan 2026 08:02:32 GMT</t>
+          <t>Wed, 28 Jan 2026 11:18:00 GMT</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxOVm1maWMyM2FpVmlTWTNCclg1UWM4aGI0blNHNVdqV0dxdVhkZVQzSDY3UDZnN3dFMGJ2VjNvVDJQenFCZHpxbDhaeGR5eHNIZF9SM2JicnV1eHRnbjZMSjhBa21ybXBKOWVuRnJWTWE0N0h5UnNRWnJjMkN4dXFUY3gzRTVNOUFjay1kbDc2SEt4VE5nNTBMMGdiUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxNeThwdHAtbjg0eFprWG5vX1BVS184RW5vck91SG9ISWJrRHNackVJMU4ycDBYZWNxV0hKYXExdWRsUzFLZm9YUzNhZEE2V0NVMFM1b2RtRHI1ZEhwY1lJMko0YlNXckhicXFBdWRhREtHSTVILXFONy1lQzdGeENXX05QZ1FlZHlUZ2pHTXNQU291LWdYM1k3WUtSa3M?oc=5</t>
         </is>
       </c>
       <c r="F159" t="n">
@@ -5201,17 +5201,17 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>More 'No Kings' protests planned for March 28 as outrage spreads over Minneapolis deaths - ABC News</t>
+          <t>Thousands rally in Serbia's capital against crackdown on student-led protests - Yahoo News Canada</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>Wed, 28 Jan 2026 11:09:27 GMT</t>
+          <t>Wed, 28 Jan 2026 08:14:59 GMT</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxNWGlGcy1ub0RtU2REQzJreEE0ZlN2OWhxbUEyamxJenVIcmtFZVhZcDV3cE1LR0drUUN3amRrMFJ1c24wQjkxQlpGTmpqRmFqTUhwcTRzZ1dkNDBoVnVxcXA0X0ZNaGtHZzcyS0d5MEpZeEtIY3lTYkFRQm9ma2QyRXBmS2dEVDc3UUhBaWlEZldqZzQ5bHBrQ3NLLXRrUlk1MVA3eldORUTSAa4BQVVfeXFMT190cXhqdE9NOWlJZmdFSk5IQzhtUWNwYU5nWHpnVmlfaGlJUFF2aUptY2E3S0s4anNWYVEyVWpNckpOaXh3MXVCc09IekpTUTJvTmRJTHVwVkRoU2QtTzVtRUxTMlcwVkxVUU1wV2tPLWtHQ0xxeU1vUF9hTk56dW4wbWJPZU9FTUpFSXFxUGx5cWV3S2c4X0haUGZneG9uX2ozTzdqSXpLeFQxSDZn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMihwFBVV95cUxPWHczMlJJZUwyNWJGekxGSzlvODZCM24wWkwyNUhpTmp5SlFBZUhpNEctM3ctS2NZNF9FS1NWZmczdmpsQXR1ZlRjM2YtRExHenRGbWx5NkEwaEcyNVMxV0VJclNpOVZpTk9MRXEyMnFhT1h0UnpiajVtSTJTYWtmbFRPLXEtX3c?oc=5</t>
         </is>
       </c>
       <c r="F160" t="n">
@@ -5231,17 +5231,17 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Police throw child to the ground during Rojava protest in Mardin - Bianet</t>
+          <t>Heavy police presence as educational protests escalate at Addington Primary School - dailynews.co.za</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>Wed, 28 Jan 2026 11:18:00 GMT</t>
+          <t>Wed, 28 Jan 2026 11:08:57 GMT</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxNeThwdHAtbjg0eFprWG5vX1BVS184RW5vck91SG9ISWJrRHNackVJMU4ycDBYZWNxV0hKYXExdWRsUzFLZm9YUzNhZEE2V0NVMFM1b2RtRHI1ZEhwY1lJMko0YlNXckhicXFBdWRhREtHSTVILXFONy1lQzdGeENXX05QZ1FlZHlUZ2pHTXNQU291LWdYM1k3WUtSa3M?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxPaGszeWdzNklTWUdrNkdmMkJRaEE2aVpuUTMwdlNRTUNmM1FZMHpKR0JpdlZQMXYxRFlKOEJxT0RvTmw0NTJ6YWpUUVlOVVNRZ3ZvZlVHaVJuNTBGQm5uS2xidllmVkd1cUJKYnIxLVhSRlZPRTVhSXZEOGFiUVJMNmRXck54d0gxWlYyeHhDV3RFeVZPWlpha2dReXZSSFVPYkVFR0h1MDNlOXNNdDZVUWF1ZnJDNzQ2YXlWRHF2TXM?oc=5</t>
         </is>
       </c>
       <c r="F161" t="n">
@@ -5261,17 +5261,17 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Thousands rally in Serbia's capital against crackdown on student-led protests - Yahoo News Canada</t>
+          <t>Car driver fleeing police strikes SFPD officer in Oakland - sfchronicle.com</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>Wed, 28 Jan 2026 08:14:59 GMT</t>
+          <t>Wed, 28 Jan 2026 05:05:03 GMT</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihwFBVV95cUxPWHczMlJJZUwyNWJGekxGSzlvODZCM24wWkwyNUhpTmp5SlFBZUhpNEctM3ctS2NZNF9FS1NWZmczdmpsQXR1ZlRjM2YtRExHenRGbWx5NkEwaEcyNVMxV0VJclNpOVZpTk9MRXEyMnFhT1h0UnpiajVtSTJTYWtmbFRPLXEtX3c?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxObVgxOUlTeUFUOGNnem55SVRCMzBhSWE3VFhpMjBWYkRKQWdKVThCTTRvM1k3blFoOEE4UHk3VXRPR1prbEx0VnBvVW03QWJEMWxhQzRvV3R2NnZHNlNDMGdhVlY4RnB6N1NfZkZUZVI3UUkyQ1B0ejlwS0NJbmxKQkE0YnF3TW1hN01oV3FYcGVnVFZ5UnplcVZMaDJkMVU?oc=5</t>
         </is>
       </c>
       <c r="F162" t="n">
@@ -5281,27 +5281,27 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>Protest</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally OR tactics OR targets OR groups)</t>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Heavy police presence as educational protests escalate at Addington Primary School - dailynews.co.za</t>
+          <t>UK businesses and academia eligible for new EU funding on AI and related technologies - EEAS</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>Wed, 28 Jan 2026 11:08:57 GMT</t>
+          <t>Wed, 28 Jan 2026 12:13:30 GMT</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxPaGszeWdzNklTWUdrNkdmMkJRaEE2aVpuUTMwdlNRTUNmM1FZMHpKR0JpdlZQMXYxRFlKOEJxT0RvTmw0NTJ6YWpUUVlOVVNRZ3ZvZlVHaVJuNTBGQm5uS2xidllmVkd1cUJKYnIxLVhSRlZPRTVhSXZEOGFiUVJMNmRXck54d0gxWlYyeHhDV3RFeVZPWlpha2dReXZSSFVPYkVFR0h1MDNlOXNNdDZVUWF1ZnJDNzQ2YXlWRHF2TXM?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0AFBVV95cUxNMnVMcmlCSlltUlYxb1V0ZDhFQjlWSzJrdnBHcXEyMEFYYnFaUjBRcHdsem5UM0lXNGo1TmZCRTZwb1hXMDBGVDFsOTVsLWRmVjk4QWRmdEpwYjFjR2JKcG9hbGtoNVNudjNhZno4OTRfQ3hETkNMTC0xczQ5S3U2TGU4b0EzZ3ZqODVNbERTRE5KTVRPSDVCY25jUGg5NjdzQUJxRzR6bWtrNllabHN6cnA0dGtDbm9VUWFXRXlETjROa1ZXaVJQLThoWTVlYjBa?oc=5</t>
         </is>
       </c>
       <c r="F163" t="n">
@@ -5311,27 +5311,27 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>Protest</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally OR tactics OR targets OR groups)</t>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Car driver fleeing police strikes SFPD officer in Oakland - sfchronicle.com</t>
+          <t>Briefing: AI and immigration law – what guidance is there for lawyers? - Free Movement</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>Wed, 28 Jan 2026 05:05:03 GMT</t>
+          <t>Wed, 28 Jan 2026 08:34:09 GMT</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxObVgxOUlTeUFUOGNnem55SVRCMzBhSWE3VFhpMjBWYkRKQWdKVThCTTRvM1k3blFoOEE4UHk3VXRPR1prbEx0VnBvVW03QWJEMWxhQzRvV3R2NnZHNlNDMGdhVlY4RnB6N1NfZkZUZVI3UUkyQ1B0ejlwS0NJbmxKQkE0YnF3TW1hN01oV3FYcGVnVFZ5UnplcVZMaDJkMVU?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxPRGl2SnJyN3lNbUlVdDE1eW1Pa2l5bHUyNjFJRTVWZnM5TUVtRDhyWnFkN012c2R0VE1kZlFucEI4WmlfUTNpT3FQdDdPOTRNZVhnNkpvYzRuTUhTa0YwT0R6TnJIYVpTclgxUlE0VGVpVktMb1d3Nms4c0dpYXN0alhZU3FsVlgzWEZib05EMFhEUDBTbzlDanVTaw?oc=5</t>
         </is>
       </c>
       <c r="F164" t="n">
@@ -5351,17 +5351,17 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>UK businesses and academia eligible for new EU funding on AI and related technologies - EEAS</t>
+          <t>Government appoints Mike Clancy to new AI and future of work panel - Bectu</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>Wed, 28 Jan 2026 12:13:30 GMT</t>
+          <t>Wed, 28 Jan 2026 10:13:22 GMT</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0AFBVV95cUxNMnVMcmlCSlltUlYxb1V0ZDhFQjlWSzJrdnBHcXEyMEFYYnFaUjBRcHdsem5UM0lXNGo1TmZCRTZwb1hXMDBGVDFsOTVsLWRmVjk4QWRmdEpwYjFjR2JKcG9hbGtoNVNudjNhZno4OTRfQ3hETkNMTC0xczQ5S3U2TGU4b0EzZ3ZqODVNbERTRE5KTVRPSDVCY25jUGg5NjdzQUJxRzR6bWtrNllabHN6cnA0dGtDbm9VUWFXRXlETjROa1ZXaVJQLThoWTVlYjBa?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxQVzQ2alQzakhUbGNscHd1YzlFUUpYQjZabzFldG5nT0tnVXVLQ1hfZTFoY0JJWHpSRGs1d2RKSGUyaDY4UkxCMlpJQUEwamljSlBaN1FuUkRZWTExcEJSVm1MNl9QMVhIY3I4dHllbUJRS0pKS0lia1g3VDViNUtKd1ZkSF95SENqOTJJYmpjT1RQeDdSRnRV?oc=5</t>
         </is>
       </c>
       <c r="F165" t="n">
@@ -5381,17 +5381,17 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Briefing: AI and immigration law – what guidance is there for lawyers? - Free Movement</t>
+          <t>West Midlands AI and coding trainer to open new Dubai base - BBC</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>Wed, 28 Jan 2026 08:34:09 GMT</t>
+          <t>Wed, 28 Jan 2026 06:05:45 GMT</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxPRGl2SnJyN3lNbUlVdDE1eW1Pa2l5bHUyNjFJRTVWZnM5TUVtRDhyWnFkN012c2R0VE1kZlFucEI4WmlfUTNpT3FQdDdPOTRNZVhnNkpvYzRuTUhTa0YwT0R6TnJIYVpTclgxUlE0VGVpVktMb1d3Nms4c0dpYXN0alhZU3FsVlgzWEZib05EMFhEUDBTbzlDanVTaw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTE1XN1BWU1ZLb24yclpFYnFDdmJwcHVXclBCb3EzLW1TZnRVUUE4OHpldEFPTFlobUpjdjBHM0NuakdnMEJyR2oxMjBHZFJPekFNU0tpVXNuMm9QUQ?oc=5</t>
         </is>
       </c>
       <c r="F166" t="n">
@@ -5411,17 +5411,17 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Government appoints Mike Clancy to new AI and future of work panel - Bectu</t>
+          <t>Omdia: AI and Micro-LED innovation to shape professional AV at ISE Barcelona 2026 - Omdia</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>Wed, 28 Jan 2026 10:13:22 GMT</t>
+          <t>Wed, 28 Jan 2026 09:26:44 GMT</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxQVzQ2alQzakhUbGNscHd1YzlFUUpYQjZabzFldG5nT0tnVXVLQ1hfZTFoY0JJWHpSRGs1d2RKSGUyaDY4UkxCMlpJQUEwamljSlBaN1FuUkRZWTExcEJSVm1MNl9QMVhIY3I4dHllbUJRS0pKS0lia1g3VDViNUtKd1ZkSF95SENqOTJJYmpjT1RQeDdSRnRV?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxPaTlnbEdKWnJJZldMWmpPUjNuUUstcTQtODRIVXNzNVBhYVdPNVNuYkN6NXVwT2YzRkJDMTBPdmRqM01seV93RFQ4dXFleHFvcmZVbGNjcjk0RURja09iR1lNRk42T2hvOGFSVVRITExIUGQ1WVprN3JDR25ocnpfUEF4NWh6M1BKNEdNUTBsN2VlbklMSnlScmZmYmNKektFNDZXSzk0RTBobk5SekVsdUtZT1lnWTBx?oc=5</t>
         </is>
       </c>
       <c r="F167" t="n">
@@ -5441,17 +5441,17 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>West Midlands AI and coding trainer to open new Dubai base - BBC</t>
+          <t>Privacy, AI and the need for a coherent global baseline - IAPP</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>Wed, 28 Jan 2026 06:05:45 GMT</t>
+          <t>Wed, 28 Jan 2026 14:36:24 GMT</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTE1XN1BWU1ZLb24yclpFYnFDdmJwcHVXclBCb3EzLW1TZnRVUUE4OHpldEFPTFlobUpjdjBHM0NuakdnMEJyR2oxMjBHZFJPekFNU0tpVXNuMm9QUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMihAFBVV95cUxQWEF1TWN6Y3c0a1VfRUIyck5rRU85M25GR0xVZHVFZkJIbmhQbDVRQjdaRDZwVkh3Zi1IaWhEYW02QzR6dC1hYUFPeHhTNnBfV3VDZHhqMWwwUEE0dUVwTm9PSXZlV3VlcWozU0hrSkE0UkRCbGRId1FuaEt5LUhwb3BpRHU?oc=5</t>
         </is>
       </c>
       <c r="F168" t="n">
@@ -5471,17 +5471,17 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Omdia: AI and Micro-LED innovation to shape professional AV at ISE Barcelona 2026 - Omdia</t>
+          <t>January: New government-funded AI scholarships launch at the University of Bristol | News and features - bristol.ac.uk</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>Wed, 28 Jan 2026 09:26:44 GMT</t>
+          <t>Wed, 28 Jan 2026 10:20:09 GMT</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxPaTlnbEdKWnJJZldMWmpPUjNuUUstcTQtODRIVXNzNVBhYVdPNVNuYkN6NXVwT2YzRkJDMTBPdmRqM01seV93RFQ4dXFleHFvcmZVbGNjcjk0RURja09iR1lNRk42T2hvOGFSVVRITExIUGQ1WVprN3JDR25ocnpfUEF4NWh6M1BKNEdNUTBsN2VlbklMSnlScmZmYmNKektFNDZXSzk0RTBobk5SekVsdUtZT1lnWTBx?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxQSTZDMTMxaWxwS1BvN0x5R251RkpuZ3RCNjA5RENKZ2pEWjZFQmJjZEo1RzRxbkNOQzNXS3Q0czBIcThveExNb2NWdmlZb1Z1X3prRFNISk4zdEVqMnJKelhLZG1fWjZUZnIyZnZGRkFlOHA5Z0xtUS15Y3FsWjdEQWxEcmN3M1dvdVE1Y1NvU0Z1TEE0ak5zaXdLalpqZ1RFZFR3UEZnVERma2lIZkFFYmpQdXZKMmNHcF9LcEdWSQ?oc=5</t>
         </is>
       </c>
       <c r="F169" t="n">
@@ -5501,17 +5501,17 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Privacy, AI and the need for a coherent global baseline - IAPP</t>
+          <t>Almost two-thirds of charity job candidates using AI when applying for roles - Civil Society Media</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>Wed, 28 Jan 2026 14:36:24 GMT</t>
+          <t>Wed, 28 Jan 2026 12:51:25 GMT</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihAFBVV95cUxQWEF1TWN6Y3c0a1VfRUIyck5rRU85M25GR0xVZHVFZkJIbmhQbDVRQjdaRDZwVkh3Zi1IaWhEYW02QzR6dC1hYUFPeHhTNnBfV3VDZHhqMWwwUEE0dUVwTm9PSXZlV3VlcWozU0hrSkE0UkRCbGRId1FuaEt5LUhwb3BpRHU?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxQNnN1cWNOWWlvQnhmbkxPTWFKS3Q4N3YtUkxBQjBlTzI1OFlQYjdJQ0FXZmhoMWJPME45WXpfQ2JyaFVoNmR6RTVqbUVHTzV4OWlIRThVUkdlVlJobFRZV0FNTV9wUnBEMVQ4U3hFZ2hzNE9NZ2RDOG9pRFlWN2h3c1NEMTVzVUhyc3hMejFveGpEanhienE1Vk56OVlEU1lYT1ljRUQxZ2VzUEFleHZnNHFxaklxZEUy?oc=5</t>
         </is>
       </c>
       <c r="F170" t="n">
@@ -5531,17 +5531,17 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>January: New government-funded AI scholarships launch at the University of Bristol | News and features - bristol.ac.uk</t>
+          <t>AI and robots join forces in NHS trial to improve cancer diagnosis - Digital Watch Observatory</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>Wed, 28 Jan 2026 10:20:09 GMT</t>
+          <t>Wed, 28 Jan 2026 11:41:38 GMT</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxQSTZDMTMxaWxwS1BvN0x5R251RkpuZ3RCNjA5RENKZ2pEWjZFQmJjZEo1RzRxbkNOQzNXS3Q0czBIcThveExNb2NWdmlZb1Z1X3prRFNISk4zdEVqMnJKelhLZG1fWjZUZnIyZnZGRkFlOHA5Z0xtUS15Y3FsWjdEQWxEcmN3M1dvdVE1Y1NvU0Z1TEE0ak5zaXdLalpqZ1RFZFR3UEZnVERma2lIZkFFYmpQdXZKMmNHcF9LcEdWSQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxOZFpvLWEyVzhCSHdXck8zQzd2MGpXU0d2cFlDelhMbTJNanFnWi1BblE5VzdSUHM5bExHRG05MzB1RF84czEyNEpDemhldEVzZ2MxcWdQQmQyWkVObWJuU3JXVUc5YWlZVUl2THRPVzZ2NlQtN3Bqb2pCaktDY3JGcU9CcndVSm1hSnRsc3FnUjNwYXZ2el9r?oc=5</t>
         </is>
       </c>
       <c r="F171" t="n">
@@ -5561,17 +5561,17 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Almost two-thirds of charity job candidates using AI when applying for roles - Civil Society Media</t>
+          <t>Webinar: A guide to creating ethical AI-generated imagery - Charity Digital</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>Wed, 28 Jan 2026 12:51:25 GMT</t>
+          <t>Wed, 28 Jan 2026 11:41:03 GMT</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxQNnN1cWNOWWlvQnhmbkxPTWFKS3Q4N3YtUkxBQjBlTzI1OFlQYjdJQ0FXZmhoMWJPME45WXpfQ2JyaFVoNmR6RTVqbUVHTzV4OWlIRThVUkdlVlJobFRZV0FNTV9wUnBEMVQ4U3hFZ2hzNE9NZ2RDOG9pRFlWN2h3c1NEMTVzVUhyc3hMejFveGpEanhienE1Vk56OVlEU1lYT1ljRUQxZ2VzUEFleHZnNHFxaklxZEUy?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxQOGZMMjhzUDdUZU1NZU4weDd5NGJWbzdwaUhaVXpmTjJvMkx5S0lHSFJzVmloZzBiSWxUb3c4T29lZkZZSFZXSE9TOFhNLWJjRG5aVmVheENOd0I0UG1ETUVjSC1uSzloWW5tNHNlNnR4dXFrbGdnS0h1VGJpNm1HQjhSZGlmSWJsNjhiMzlzRElSUEVlZjRZQllNQQ?oc=5</t>
         </is>
       </c>
       <c r="F172" t="n">
@@ -5591,17 +5591,17 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>AI and robots join forces in NHS trial to improve cancer diagnosis - Digital Watch Observatory</t>
+          <t>AI, London shorts and artist filmmaking at LSFF - Film London</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>Wed, 28 Jan 2026 11:41:38 GMT</t>
+          <t>Wed, 28 Jan 2026 13:03:30 GMT</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxOZFpvLWEyVzhCSHdXck8zQzd2MGpXU0d2cFlDelhMbTJNanFnWi1BblE5VzdSUHM5bExHRG05MzB1RF84czEyNEpDemhldEVzZ2MxcWdQQmQyWkVObWJuU3JXVUc5YWlZVUl2THRPVzZ2NlQtN3Bqb2pCaktDY3JGcU9CcndVSm1hSnRsc3FnUjNwYXZ2el9r?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMihgFBVV95cUxNQmczcUpHSmlVcWViVU8wRFpmSDVYRzZOVzBzc2djYkdnQjFKdHZMLTB0bkUyU2tPY3FEVUVLLVFVR21HS1dfRW9GN0ZidmxEazBSNVpaNlg0WUo2VzF5ZHoySy04Z0NZYzhpT0lPSjc1cTlaZG5COGVGd3JBbDNUaUoxZHZSQQ?oc=5</t>
         </is>
       </c>
       <c r="F173" t="n">
@@ -5621,17 +5621,17 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Webinar: A guide to creating ethical AI-generated imagery - Charity Digital</t>
+          <t>Data resilience &amp; trust seen as key to safe AI use - IT Brief UK</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>Wed, 28 Jan 2026 11:41:03 GMT</t>
+          <t>Wed, 28 Jan 2026 08:00:00 GMT</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxQOGZMMjhzUDdUZU1NZU4weDd5NGJWbzdwaUhaVXpmTjJvMkx5S0lHSFJzVmloZzBiSWxUb3c4T29lZkZZSFZXSE9TOFhNLWJjRG5aVmVheENOd0I0UG1ETUVjSC1uSzloWW5tNHNlNnR4dXFrbGdnS0h1VGJpNm1HQjhSZGlmSWJsNjhiMzlzRElSUEVlZjRZQllNQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiggFBVV95cUxNR01zNzlaTEJiTlp4VndjQkNUWXI1Rlh6Vi12SG1Sa2NMNUtEM1diNmZoVmdCSF8xN2Q3V2xwREtZZXUtNjduU296ZklqdDBRNUFQakRieThxdW9WTHo2WmF2ZUFHVkVKUWxmM3FGZk5zVjkydnFOWERnWG1mclJaMzBn?oc=5</t>
         </is>
       </c>
       <c r="F174" t="n">
@@ -5651,17 +5651,17 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>AI, London shorts and artist filmmaking at LSFF - Film London</t>
+          <t>The Typewriter Repair Class, AI, And The Next Stage Of Jobs - Forbes</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>Wed, 28 Jan 2026 13:03:30 GMT</t>
+          <t>Wed, 28 Jan 2026 14:37:38 GMT</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihgFBVV95cUxNQmczcUpHSmlVcWViVU8wRFpmSDVYRzZOVzBzc2djYkdnQjFKdHZMLTB0bkUyU2tPY3FEVUVLLVFVR21HS1dfRW9GN0ZidmxEazBSNVpaNlg0WUo2VzF5ZHoySy04Z0NZYzhpT0lPSjc1cTlaZG5COGVGd3JBbDNUaUoxZHZSQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxNMGp5WWo0MzBjQVdfd19WLVB2NjQwcDhOa0lYM2ttS09ENzBQM2hEWC1EZ09RYVAzSTdUcEdfdjZRSTZ3eXFCemJJYzlTQTl2SEszNk4zODJnZVdTMzA2eHdrSHFnYm9RMXZmYTdwOFJEWlVHOURYZmVWNlM0ZkpiR1hTMGtzRktVZ1dfNlNBa0s4Nm1HRUVzWlpsd2RFT1V6aFV2RFFkNkVUb1p0dWFJOGt1bw?oc=5</t>
         </is>
       </c>
       <c r="F175" t="n">
@@ -5681,17 +5681,17 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Data resilience &amp; trust seen as key to safe AI use - IT Brief UK</t>
+          <t>Security Orchestration Automation and Response Industry Research 2026 - Global Market Size, Share, Trends, Opportunities, and Forecasts, 2021-2025 &amp; 2026-2031 - Yahoo Finance UK</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>Wed, 28 Jan 2026 08:00:00 GMT</t>
+          <t>Wed, 28 Jan 2026 09:16:00 GMT</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiggFBVV95cUxNR01zNzlaTEJiTlp4VndjQkNUWXI1Rlh6Vi12SG1Sa2NMNUtEM1diNmZoVmdCSF8xN2Q3V2xwREtZZXUtNjduU296ZklqdDBRNUFQakRieThxdW9WTHo2WmF2ZUFHVkVKUWxmM3FGZk5zVjkydnFOWERnWG1mclJaMzBn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxPelgxV21jdnpONVBsVkRMQ3c2c1QwRWRpQjlla0pyYnhqa2hqaldFUVhZMmlDRGdoMzZ6OHBiZ0VvNnplOHVGMEJUb2RSN3ZnbVZNT211RnoweEI3Qms1ODNWX1hWYUY0RGN3VzBSYnp3Nnk5VjI4UFR2dDc0QWFtRk8yT1U1emJEaGdyM3pnZkhnVjVIcUZ1Yk1YWXEwblpreFE?oc=5</t>
         </is>
       </c>
       <c r="F176" t="n">
@@ -5711,17 +5711,17 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>The Typewriter Repair Class, AI, And The Next Stage Of Jobs - Forbes</t>
+          <t>My daughter deleted AI - and so did all her friends: the TikTok trend convincing Gen Alpha to push back - Prolific North</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>Wed, 28 Jan 2026 14:37:38 GMT</t>
+          <t>Wed, 28 Jan 2026 07:26:00 GMT</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxNMGp5WWo0MzBjQVdfd19WLVB2NjQwcDhOa0lYM2ttS09ENzBQM2hEWC1EZ09RYVAzSTdUcEdfdjZRSTZ3eXFCemJJYzlTQTl2SEszNk4zODJnZVdTMzA2eHdrSHFnYm9RMXZmYTdwOFJEWlVHOURYZmVWNlM0ZkpiR1hTMGtzRktVZ1dfNlNBa0s4Nm1HRUVzWlpsd2RFT1V6aFV2RFFkNkVUb1p0dWFJOGt1bw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi1AFBVV95cUxPMVJoQ2RjNjk4dDAyMFpmVXVuYXpzaUFuU1hnbDlTakxaVHdHQXg2TlRuck82ekoxYk9HNHhiLVFjOFpoMWdIRFUxQVVfSWZhamFTMGV2NnZxa2k0bV9maTFCWGZweG55dS1CaHlUM3hWWC1EY1FTTThHQ1B5cjBHd0xQcDBPZFlvRFZuYU11b1YzQkhiRUVnREI4LTdoZ3pVMUVWaEE5ZGJzTXJ3MFNwM1pUT2RiNnlJQW9iXzNwTkFrWUMwaE1ic1dMTDQ1OHgxb3ZSZQ?oc=5</t>
         </is>
       </c>
       <c r="F177" t="n">
@@ -5741,17 +5741,17 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Security Orchestration Automation and Response Industry Research 2026 - Global Market Size, Share, Trends, Opportunities, and Forecasts, 2021-2025 &amp; 2026-2031 - Yahoo Finance UK</t>
+          <t>Microsoft Preview: Azure, AI, and a Test of Growth Quality - XTB.com</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>Wed, 28 Jan 2026 09:16:00 GMT</t>
+          <t>Wed, 28 Jan 2026 11:35:34 GMT</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxPelgxV21jdnpONVBsVkRMQ3c2c1QwRWRpQjlla0pyYnhqa2hqaldFUVhZMmlDRGdoMzZ6OHBiZ0VvNnplOHVGMEJUb2RSN3ZnbVZNT211RnoweEI3Qms1ODNWX1hWYUY0RGN3VzBSYnp3Nnk5VjI4UFR2dDc0QWFtRk8yT1U1emJEaGdyM3pnZkhnVjVIcUZ1Yk1YWXEwblpreFE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxNZmFpRGhJWFJEWFNxUUV4WTZWYkdST0dNaG93clFxLWwtUHNhNHJUMHdXakRjUWZ3TTl3dUdsSGZOM0tDNmQ2d0xVcHlnV0NMZEFfRnhabGxRbHNPSHFERGMwWUNxS2pMbFRXQjF6ekw2X1k3SjJfZ3BwMENQMmh6XzFxZzhObnI2MDhaT2RvRHg2UlBHYTh4UmM2Mzk5U3UxQl96alFhR2NwZlhNbkNrVVN3?oc=5</t>
         </is>
       </c>
       <c r="F178" t="n">
@@ -5771,17 +5771,17 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>My daughter deleted AI - and so did all her friends: the TikTok trend convincing Gen Alpha to push back - Prolific North</t>
+          <t>How Gen Z Uses Gen AI—and Why It Worries Them - Harvard Business Review</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>Wed, 28 Jan 2026 07:26:00 GMT</t>
+          <t>Wed, 28 Jan 2026 13:12:03 GMT</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi1AFBVV95cUxPMVJoQ2RjNjk4dDAyMFpmVXVuYXpzaUFuU1hnbDlTakxaVHdHQXg2TlRuck82ekoxYk9HNHhiLVFjOFpoMWdIRFUxQVVfSWZhamFTMGV2NnZxa2k0bV9maTFCWGZweG55dS1CaHlUM3hWWC1EY1FTTThHQ1B5cjBHd0xQcDBPZFlvRFZuYU11b1YzQkhiRUVnREI4LTdoZ3pVMUVWaEE5ZGJzTXJ3MFNwM1pUT2RiNnlJQW9iXzNwTkFrWUMwaE1ic1dMTDQ1OHgxb3ZSZQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMieEFVX3lxTFBDR1F5UVlBUjg4LWx6T0pUNXBMWkdLMzdQeTEteWkxcDZoLWtqVjRaNWxIQTBQUnVobnFuVFpER25KNVF5a2hlMTRKeHBZUzNWWnU3NVpjeU9sbHlldVNTUVBBQUlyTHluTW1DVUFTXzRrMnlMN3YwYg?oc=5</t>
         </is>
       </c>
       <c r="F179" t="n">
@@ -5801,17 +5801,17 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Microsoft Preview: Azure, AI, and a Test of Growth Quality - XTB.com</t>
+          <t>The AI Impact Report 2026: Avature Finds Gap Between AI Investment and HR Execution - PR Newswire UK</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>Wed, 28 Jan 2026 11:35:34 GMT</t>
+          <t>Wed, 28 Jan 2026 14:00:00 GMT</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxNZmFpRGhJWFJEWFNxUUV4WTZWYkdST0dNaG93clFxLWwtUHNhNHJUMHdXakRjUWZ3TTl3dUdsSGZOM0tDNmQ2d0xVcHlnV0NMZEFfRnhabGxRbHNPSHFERGMwWUNxS2pMbFRXQjF6ekw2X1k3SjJfZ3BwMENQMmh6XzFxZzhObnI2MDhaT2RvRHg2UlBHYTh4UmM2Mzk5U3UxQl96alFhR2NwZlhNbkNrVVN3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi1wFBVV95cUxQZDd1N3lNVTM1bkFKYlhPVEZJLUZnYVZjVllsa25fanl6T0tzZGRfUjVieTZIa2xGS1hMTkF6cFRtLThVcExmVGlmb1NObFY3TzhJYjNiMUR4NkdYWXlLMkRGeVJmV0pYUmZrdmFmb2FYbXF2MEk5b1pzMVMyb0QwWHNodGRkMGtHdGVNUjNfM1JiSng4M3N5TEFJalF0ME8tMUZnSERWNjU3c0JZakFrU1RIOHVmbGkwekw2RG15UUlkbEd5alNNM1RKVEhJcHpPWkZRTDdsVQ?oc=5</t>
         </is>
       </c>
       <c r="F180" t="n">
@@ -5831,17 +5831,17 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>How Gen Z Uses Gen AI—and Why It Worries Them - Harvard Business Review</t>
+          <t>AI as a Supporting Role, Not The Headline Act. - UKSPA</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>Wed, 28 Jan 2026 13:12:03 GMT</t>
+          <t>Wed, 28 Jan 2026 13:18:44 GMT</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMieEFVX3lxTFBDR1F5UVlBUjg4LWx6T0pUNXBMWkdLMzdQeTEteWkxcDZoLWtqVjRaNWxIQTBQUnVobnFuVFpER25KNVF5a2hlMTRKeHBZUzNWWnU3NVpjeU9sbHlldVNTUVBBQUlyTHluTW1DVUFTXzRrMnlMN3YwYg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiekFVX3lxTE92WFFSSHJrLVF5Ti1PVl8zTUNkbm1hOEJETHlSWFh0dE1heWRZZEs3NEJmSUxLMlVZU2owZTdzX08xZHdOWDh3VkRuQ0JYbk9HdEk4dGdQTjY4OExzTllLb25KdVFPT0JGZm14VFk4TnhvV3hWbHBSUGdB?oc=5</t>
         </is>
       </c>
       <c r="F181" t="n">
@@ -5861,17 +5861,17 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>The AI Impact Report 2026: Avature Finds Gap Between AI Investment and HR Execution - PR Newswire UK</t>
+          <t>C-suite leaders lack AI competency, survey suggests - HR Magazine</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>Wed, 28 Jan 2026 14:00:00 GMT</t>
+          <t>Wed, 28 Jan 2026 11:00:53 GMT</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi1wFBVV95cUxQZDd1N3lNVTM1bkFKYlhPVEZJLUZnYVZjVllsa25fanl6T0tzZGRfUjVieTZIa2xGS1hMTkF6cFRtLThVcExmVGlmb1NObFY3TzhJYjNiMUR4NkdYWXlLMkRGeVJmV0pYUmZrdmFmb2FYbXF2MEk5b1pzMVMyb0QwWHNodGRkMGtHdGVNUjNfM1JiSng4M3N5TEFJalF0ME8tMUZnSERWNjU3c0JZakFrU1RIOHVmbGkwekw2RG15UUlkbEd5alNNM1RKVEhJcHpPWkZRTDdsVQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxQZmI5dEctTmJJS3VkRmFURF9wXzFvN2tqbk1GVzFnb1J4dWJld0ROLXFFbE5SZFhjaXgzeHJNSWJ2RDdBaHZkOHU5UmZtb1pXUHpVZmdUOVpYUVo4dFlDclFsTWhmV1ktd1NfVVNiSkgwalZKcW5SWFVsemlnVjIxdEt6U1RUUXphSGR6RW9SOXl4Vm5PaGpv?oc=5</t>
         </is>
       </c>
       <c r="F182" t="n">
@@ -5891,17 +5891,17 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>AI as a Supporting Role, Not The Headline Act. - UKSPA</t>
+          <t>ASML shares hit record high as AI demand fuels orders - Financial Times</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>Wed, 28 Jan 2026 13:18:44 GMT</t>
+          <t>Wed, 28 Jan 2026 10:05:37 GMT</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiekFVX3lxTE92WFFSSHJrLVF5Ti1PVl8zTUNkbm1hOEJETHlSWFh0dE1heWRZZEs3NEJmSUxLMlVZU2owZTdzX08xZHdOWDh3VkRuQ0JYbk9HdEk4dGdQTjY4OExzTllLb25KdVFPT0JGZm14VFk4TnhvV3hWbHBSUGdB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMicEFVX3lxTFBsTkdNaGppTlc3Y1g1aXFCMi0xb0dhY1E5OGdWc0tWNVlrVmdXTE9CTE9uRUF0WnU1VHBSRVdYaVRjV1lZU0tHenBDMmRncUctVzV2QzhNaVNtSEFTaTN6alhnX1FXbmk5d1RfTk9wenQ?oc=5</t>
         </is>
       </c>
       <c r="F183" t="n">
@@ -5921,17 +5921,17 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>C-suite leaders lack AI competency, survey suggests - HR Magazine</t>
+          <t>Doomsday Clock ticks closer to midnight amid rising global risks - Engineering and Technology Magazine</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>Wed, 28 Jan 2026 11:00:53 GMT</t>
+          <t>Wed, 28 Jan 2026 11:59:21 GMT</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxQZmI5dEctTmJJS3VkRmFURF9wXzFvN2tqbk1GVzFnb1J4dWJld0ROLXFFbE5SZFhjaXgzeHJNSWJ2RDdBaHZkOHU5UmZtb1pXUHpVZmdUOVpYUVo4dFlDclFsTWhmV1ktd1NfVVNiSkgwalZKcW5SWFVsemlnVjIxdEt6U1RUUXphSGR6RW9SOXl4Vm5PaGpv?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxQRWZmd3JZckV6VHVCR2stWXNhZDBEc052NC1KWW5va09DSl9LYXhYTmNCRVRDYkV3a1dVaFVrakJTWWdSbkM3QThwZzZYbjlIenBaSU05ZmVNVXAtVFJaME9HNG1nX0RFWExiVFEwRXQzTmczMmlfai1uMlQzWWJ0TGtsMkNVLTdTUUoxVXpUWXY5QWJPRFZtbnJkSU43QTdfOEdGdFJkUjlTOWhRUV9PYzNGYno5THJaNXN0a1FUaXE?oc=5</t>
         </is>
       </c>
       <c r="F184" t="n">
@@ -5951,17 +5951,17 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>ASML shares hit record high as AI demand fuels orders - Financial Times</t>
+          <t>Amazon axes 16,000 jobs amid push to replace office workers with AI - The Telegraph</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>Wed, 28 Jan 2026 10:05:37 GMT</t>
+          <t>Wed, 28 Jan 2026 12:09:00 GMT</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMicEFVX3lxTFBsTkdNaGppTlc3Y1g1aXFCMi0xb0dhY1E5OGdWc0tWNVlrVmdXTE9CTE9uRUF0WnU1VHBSRVdYaVRjV1lZU0tHenBDMmRncUctVzV2QzhNaVNtSEFTaTN6alhnX1FXbmk5d1RfTk9wenQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiiwFBVV95cUxQcmxjMnVwc0Q2UndlREZzTlBESy1JVFphaldZQXdFRmRMZHNOUnM4bm9WSWZoRkxnSkRPRWsydEE3VzM2VVNERldSYjhLckwzNHNHWHk4ZHl6REhkVTNXamg2NEc1cmpCV1RieDlXcG5EVUlnaXNPTzRUUnBLcjF6eDZtN2U0S1ZlR1NZ?oc=5</t>
         </is>
       </c>
       <c r="F185" t="n">
@@ -5981,17 +5981,17 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Doomsday Clock ticks closer to midnight amid rising global risks - Engineering and Technology Magazine</t>
+          <t>How to Communicate About Quantum Technology — Science-Backed Tips For Talking Quantum - The Quantum Insider</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>Wed, 28 Jan 2026 11:59:21 GMT</t>
+          <t>Wed, 28 Jan 2026 12:54:30 GMT</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxQRWZmd3JZckV6VHVCR2stWXNhZDBEc052NC1KWW5va09DSl9LYXhYTmNCRVRDYkV3a1dVaFVrakJTWWdSbkM3QThwZzZYbjlIenBaSU05ZmVNVXAtVFJaME9HNG1nX0RFWExiVFEwRXQzTmczMmlfai1uMlQzWWJ0TGtsMkNVLTdTUUoxVXpUWXY5QWJPRFZtbnJkSU43QTdfOEdGdFJkUjlTOWhRUV9PYzNGYno5THJaNXN0a1FUaXE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxQb3doYzF4ZDdMb2o5ZGtvSmpuQ2QtSmw0T3REQzk5RjRoMk9uRElpVzFmanBUdVl5VzVPa2otSG1fYWM5cG1KZ20tUGo0OUE4N1RrcXZCRFlpMlExeTJaUjhLOHRIaDVXY0h6SGtBV19GT2VPSWVNY0FpRGhqclFHZUdqNE1CZHJrMVRPNExOc1hnNVZSSHdQZjZVS0xrQU55SVZvdXNGTkFJdlgtSmkwYXg5LVNrUUZETFQ5M0UtYzc2YUk?oc=5</t>
         </is>
       </c>
       <c r="F186" t="n">
@@ -6011,17 +6011,17 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Amazon axes 16,000 jobs amid push to replace office workers with AI - The Telegraph</t>
+          <t>Claroty Team82 reveals critical RCE vulnerability in IDIS Cloud Manager Viewer tied to spear-phishing risk - Industrial Cyber</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>Wed, 28 Jan 2026 12:09:00 GMT</t>
+          <t>Wed, 28 Jan 2026 14:36:06 GMT</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiiwFBVV95cUxQcmxjMnVwc0Q2UndlREZzTlBESy1JVFphaldZQXdFRmRMZHNOUnM4bm9WSWZoRkxnSkRPRWsydEE3VzM2VVNERldSYjhLckwzNHNHWHk4ZHl6REhkVTNXamg2NEc1cmpCV1RieDlXcG5EVUlnaXNPTzRUUnBLcjF6eDZtN2U0S1ZlR1NZ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi8AFBVV95cUxNaVp0MGF1SVNCekRvZk53VTJWeHB5bjUxRkpDTWlVTGFqVGpWaVNkNWJGbzhQR252MEJONTNMaURBenBuVVN3dE5FR3Z6OVZCV0Q5UFhSTmtMUkFZY1dkN0d6X3ZUZGVSTzQ0eHEtUW56SnNBblZ2aGJpSTk0RXVjblQ3MGFXZDBYa1VXZmhURkZ6OFF0NEhFOXVBSzFMcGRmLTZTUzQ1WGdFazlFZ1lCbC1pWkFhR25WUElCYkJITnlId3ppal92UWxNLU1QQTZhSkYyRkk0OTZuNzc1Q3QyQ0JybUl4YjREV1Z0VTRhWS0?oc=5</t>
         </is>
       </c>
       <c r="F187" t="n">
@@ -6041,17 +6041,17 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>How to Communicate About Quantum Technology — Science-Backed Tips For Talking Quantum - The Quantum Insider</t>
+          <t>Made Smarter prepares Yorkshire manufacturers for AI future - Machinery Market</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>Wed, 28 Jan 2026 12:54:30 GMT</t>
+          <t>Wed, 28 Jan 2026 09:18:05 GMT</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxQb3doYzF4ZDdMb2o5ZGtvSmpuQ2QtSmw0T3REQzk5RjRoMk9uRElpVzFmanBUdVl5VzVPa2otSG1fYWM5cG1KZ20tUGo0OUE4N1RrcXZCRFlpMlExeTJaUjhLOHRIaDVXY0h6SGtBV19GT2VPSWVNY0FpRGhqclFHZUdqNE1CZHJrMVRPNExOc1hnNVZSSHdQZjZVS0xrQU55SVZvdXNGTkFJdlgtSmkwYXg5LVNrUUZETFQ5M0UtYzc2YUk?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxPY2xfU0VPMDRmVldSYWdfVnhCanBpVzZHQXdoS2NlQmotUnFkMDBQWGhuZVZGbFdVSlV2MkMxQ3RsMGhiYjQ1WXBzY2FJSDlLYTNCWHBiZXN6ZnVvS1dtelJiMXVZT3RsZERseTVtaV85UWMtMGRPMmZOeVFMYWNOS2RWaFNSSFI2OW5vbnZYOTR4YXBDWEFmVGY2X2FfLW1fZmdmbkxROVY?oc=5</t>
         </is>
       </c>
       <c r="F188" t="n">
@@ -6071,17 +6071,17 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Claroty Team82 reveals critical RCE vulnerability in IDIS Cloud Manager Viewer tied to spear-phishing risk - Industrial Cyber</t>
+          <t>Digital careers report - software firms tackle talent crunch through collaborative resource sharing - Diginomica</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>Wed, 28 Jan 2026 14:36:06 GMT</t>
+          <t>Wed, 28 Jan 2026 09:43:54 GMT</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi8AFBVV95cUxNaVp0MGF1SVNCekRvZk53VTJWeHB5bjUxRkpDTWlVTGFqVGpWaVNkNWJGbzhQR252MEJONTNMaURBenBuVVN3dE5FR3Z6OVZCV0Q5UFhSTmtMUkFZY1dkN0d6X3ZUZGVSTzQ0eHEtUW56SnNBblZ2aGJpSTk0RXVjblQ3MGFXZDBYa1VXZmhURkZ6OFF0NEhFOXVBSzFMcGRmLTZTUzQ1WGdFazlFZ1lCbC1pWkFhR25WUElCYkJITnlId3ppal92UWxNLU1QQTZhSkYyRkk0OTZuNzc1Q3QyQ0JybUl4YjREV1Z0VTRhWS0?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxObUFxd0s3QnZTdktiT1pEeHBSdVFpSXdjb2xnM3BlMUViSkFzUE9Fel9seDBvclJ3U2ZZc192VXd2a1l1cWh5OGdtMThfMXQyd3VBeFZCVGQyUUFDbWZHQndQZE5HVzVqTkZkZXZReXh1UV9aUG5jRUpOZ1hfaW5nTExBeEtWQzU3VjExYzdqN3Q3czZHQ0JZMmw3Qk1mc1h1TWxPdkxyZFZRLXYya3VLZ3ZISEd1dk9OODVVUtIBwgFBVV95cUxPRWV3dmphS1ZPNjJZM2hhRjhxdXllcVdYTW1GZENDZkRtMFQ4YTRSdTFMMjJBZ1BuVEJWR0FRSkhBT3J5S2Z4TkFBOUZ4ZTg3ME4tQnRvVEhlOUtORnhZb2MzUWpWQXB3b3JQOUFDZFdub084SHBnR00xbExwaUFJSHIwb2cxdGR4OE1aQ2dITTFMM24tTXpGS096bFE5Xy1NbmlUd0xvT0JzV0JIU0M1LXJ0Rk1WVHU1MXhRdGpOSjB5Zw?oc=5</t>
         </is>
       </c>
       <c r="F189" t="n">
@@ -6101,17 +6101,17 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Made Smarter prepares Yorkshire manufacturers for AI future - Machinery Market</t>
+          <t>Confectionery market trends: AI and plant-based innovation redefine guilt-free treats - Food Ingredients First</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>Wed, 28 Jan 2026 09:18:05 GMT</t>
+          <t>Wed, 28 Jan 2026 09:28:36 GMT</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxPY2xfU0VPMDRmVldSYWdfVnhCanBpVzZHQXdoS2NlQmotUnFkMDBQWGhuZVZGbFdVSlV2MkMxQ3RsMGhiYjQ1WXBzY2FJSDlLYTNCWHBiZXN6ZnVvS1dtelJiMXVZT3RsZERseTVtaV85UWMtMGRPMmZOeVFMYWNOS2RWaFNSSFI2OW5vbnZYOTR4YXBDWEFmVGY2X2FfLW1fZmdmbkxROVY?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMihAFBVV95cUxPOVFiVkRYZVlmLVkxUjZHTkRkRlBHTnVyYXZuTWpMYzRFTW11dG5yNFlVZ2tkWWlVUVZRMTk0Q0stT1VBQUR0dUMxdFd3THNfMUJnR3AwS293S3NrMi1ndUEwTDlGOHBMYjB0OC1lTmlPZkg2aHJiYm40NHpSOGdSd3lpVzE?oc=5</t>
         </is>
       </c>
       <c r="F190" t="n">
@@ -6131,17 +6131,17 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Digital careers report - software firms tackle talent crunch through collaborative resource sharing - Diginomica</t>
+          <t>BigBear.ai and AD Ports Group Announce Strategic Partnership Exploring Development of Next-Generation AI Customs Management Systems for Ports and Borders - Morningstar</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>Wed, 28 Jan 2026 09:43:54 GMT</t>
+          <t>Wed, 28 Jan 2026 14:15:00 GMT</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxObUFxd0s3QnZTdktiT1pEeHBSdVFpSXdjb2xnM3BlMUViSkFzUE9Fel9seDBvclJ3U2ZZc192VXd2a1l1cWh5OGdtMThfMXQyd3VBeFZCVGQyUUFDbWZHQndQZE5HVzVqTkZkZXZReXh1UV9aUG5jRUpOZ1hfaW5nTExBeEtWQzU3VjExYzdqN3Q3czZHQ0JZMmw3Qk1mc1h1TWxPdkxyZFZRLXYya3VLZ3ZISEd1dk9OODVVUtIBwgFBVV95cUxPRWV3dmphS1ZPNjJZM2hhRjhxdXllcVdYTW1GZENDZkRtMFQ4YTRSdTFMMjJBZ1BuVEJWR0FRSkhBT3J5S2Z4TkFBOUZ4ZTg3ME4tQnRvVEhlOUtORnhZb2MzUWpWQXB3b3JQOUFDZFdub084SHBnR00xbExwaUFJSHIwb2cxdGR4OE1aQ2dITTFMM24tTXpGS096bFE5Xy1NbmlUd0xvT0JzV0JIU0M1LXJ0Rk1WVHU1MXhRdGpOSjB5Zw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiugJBVV95cUxPaGdCZEtEdXFIc25aN245U0N0eG5FbENyN2lWMUM0ZUdieDJhZE5GT0NVOUVzWDFiWVVmTUExX0ZkcGxvWmJlQkR4a2FSaV9sdGNya3hCYUpiYWtIUTQwVkFCanhYWTRreTBqUTFmSk4xbVZnSlNrUnB3T0Q0cHhyWEhjNjFNelBqRzd1dURBZkNublRaRzFKWmJ6alZ6Mmt3TThTc3d3em9mNEg3dERfd2NVMEtVUjBxWGZ0UlVXaENyc20xRnF2ZFc5b3JZaUFXd3Y3a3Y2QUhndkE1UDNtYVFMQXhYUVVGRTIyUTM3b2dmUmc3cld0U1ROWDEzbk9ZaEdqX1lWdEpPajZaZDJ1S0hUU1NJdl9yWjA4dW93U3VCTUVxc2JoRjJ4S2Faa09rNHhFWkFDcEtxdw?oc=5</t>
         </is>
       </c>
       <c r="F191" t="n">
@@ -6161,17 +6161,17 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Confectionery market trends: AI and plant-based innovation redefine guilt-free treats - Food Ingredients First</t>
+          <t>At Davos, tech CEOs laid out their vision for AI’s world domination - The Guardian</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>Wed, 28 Jan 2026 09:28:36 GMT</t>
+          <t>Tue, 27 Jan 2026 19:05:00 GMT</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihAFBVV95cUxPOVFiVkRYZVlmLVkxUjZHTkRkRlBHTnVyYXZuTWpMYzRFTW11dG5yNFlVZ2tkWWlVUVZRMTk0Q0stT1VBQUR0dUMxdFd3THNfMUJnR3AwS293S3NrMi1ndUEwTDlGOHBMYjB0OC1lTmlPZkg2aHJiYm40NHpSOGdSd3lpVzE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijwFBVV95cUxQanZQR3Zqa3MwanRfajQwallkejFMRVNBd3llWm5YUTU1UDVSVDR3N19IaGFzSFZGVHJaR2J1MmY3bm9TMzVEd0hWd2cydTdaYUJXa05RXzIza0hRaE9JNFNrc2k4b2xGT2FHNGhwaGNRVEphdnpkanowa05ZN29teXhCYzBfdWhuajdmd0w5NA?oc=5</t>
         </is>
       </c>
       <c r="F192" t="n">
@@ -6191,17 +6191,17 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>BigBear.ai and AD Ports Group Announce Strategic Partnership Exploring Development of Next-Generation AI Customs Management Systems for Ports and Borders - Morningstar</t>
+          <t>Arabic.AI partners with Stanford to launch the first holistic benchmark for Arabic AI models - Wamda</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>Wed, 28 Jan 2026 14:15:00 GMT</t>
+          <t>Wed, 28 Jan 2026 09:57:10 GMT</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiugJBVV95cUxPaGdCZEtEdXFIc25aN245U0N0eG5FbENyN2lWMUM0ZUdieDJhZE5GT0NVOUVzWDFiWVVmTUExX0ZkcGxvWmJlQkR4a2FSaV9sdGNya3hCYUpiYWtIUTQwVkFCanhYWTRreTBqUTFmSk4xbVZnSlNrUnB3T0Q0cHhyWEhjNjFNelBqRzd1dURBZkNublRaRzFKWmJ6alZ6Mmt3TThTc3d3em9mNEg3dERfd2NVMEtVUjBxWGZ0UlVXaENyc20xRnF2ZFc5b3JZaUFXd3Y3a3Y2QUhndkE1UDNtYVFMQXhYUVVGRTIyUTM3b2dmUmc3cld0U1ROWDEzbk9ZaEdqX1lWdEpPajZaZDJ1S0hUU1NJdl9yWjA4dW93U3VCTUVxc2JoRjJ4S2Faa09rNHhFWkFDcEtxdw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxNMUVWd2hwdjlQQXgxVXhmdnI4eUlQTkRHQzh1UVZwRUozNnduUG5yUHZZX0llWnl3S25CWVo2SGhhNUM1Zl81OFNNcFJyNWlrSlBiV0VuaW81UTAzVkl6WGUzcmdkUlhhLTVTem1EVHJEeDU3YTczUTJxNFpsRG1KcHVqcWtZcWhtLVVVY3RLX2VjOW9SQTdOT1NR?oc=5</t>
         </is>
       </c>
       <c r="F193" t="n">
@@ -6221,17 +6221,17 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>At Davos, tech CEOs laid out their vision for AI’s world domination - The Guardian</t>
+          <t>AI reshapes university language classrooms - Digital Watch Observatory</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>Tue, 27 Jan 2026 19:05:00 GMT</t>
+          <t>Wed, 28 Jan 2026 11:24:26 GMT</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijwFBVV95cUxQanZQR3Zqa3MwanRfajQwallkejFMRVNBd3llWm5YUTU1UDVSVDR3N19IaGFzSFZGVHJaR2J1MmY3bm9TMzVEd0hWd2cydTdaYUJXa05RXzIza0hRaE9JNFNrc2k4b2xGT2FHNGhwaGNRVEphdnpkanowa05ZN29teXhCYzBfdWhuajdmd0w5NA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMid0FVX3lxTFB6RXMyQXRNTmNRa2ZaWDFiVm05cjVEVHB4RnhIdVdjOVRJUnpwYjg5MjJhY3pKMFBtRmlKS1JKN29xSi1La0VtZDJCZ2xQVHlnWURBb0tyXy1ZQmxweWhsOGVLd05WXzVkckZod1VxUmxBMEt0UjRR?oc=5</t>
         </is>
       </c>
       <c r="F194" t="n">
@@ -6251,17 +6251,17 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Arabic.AI partners with Stanford to launch the first holistic benchmark for Arabic AI models - Wamda</t>
+          <t>AfricAI positions Africa for large-scale adoption of intelligent machines - Digital Watch Observatory</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>Wed, 28 Jan 2026 09:57:10 GMT</t>
+          <t>Wed, 28 Jan 2026 11:09:57 GMT</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxNMUVWd2hwdjlQQXgxVXhmdnI4eUlQTkRHQzh1UVZwRUozNnduUG5yUHZZX0llWnl3S25CWVo2SGhhNUM1Zl81OFNNcFJyNWlrSlBiV0VuaW81UTAzVkl6WGUzcmdkUlhhLTVTem1EVHJEeDU3YTczUTJxNFpsRG1KcHVqcWtZcWhtLVVVY3RLX2VjOW9SQTdOT1NR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMie0FVX3lxTFAwVTN3aUZSMl9pYzBfWTRaR05wU3ROUHowNk5GNVRWTVhPWWMzUng1bjFwSFdSWS10c25UQTd3clFYQlVZczU0eVF3SXB3ZklsTENjUWVqc09pWV9hZ1k5bFpXQXpYVXdKSVhvcXQxY3h2YmdLSFo5T1ZsYw?oc=5</t>
         </is>
       </c>
       <c r="F195" t="n">
@@ -6271,27 +6271,27 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Fraud_Scam</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+          <t>(fraud OR scam OR phishing OR smishing OR vishing OR "identity theft" OR impersonation OR spoofing OR "account takeover" OR "payment fraud" OR "invoice fraud" OR "wire fraud" OR "business email compromise" OR BEC OR "fake invoice" OR "supplier fraud" OR "procurement fraud" OR "social engineering" OR extortion OR blackmail)AND (company OR business OR enterprise OR customer OR client OR employee OR bank OR financial OR payment OR transaction)</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>AI reshapes university language classrooms - Digital Watch Observatory</t>
+          <t>Jersey businesses urged to beware of scam financial emails - BBC</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>Wed, 28 Jan 2026 11:24:26 GMT</t>
+          <t>Tue, 27 Jan 2026 16:43:45 GMT</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMid0FVX3lxTFB6RXMyQXRNTmNRa2ZaWDFiVm05cjVEVHB4RnhIdVdjOVRJUnpwYjg5MjJhY3pKMFBtRmlKS1JKN29xSi1La0VtZDJCZ2xQVHlnWURBb0tyXy1ZQmxweWhsOGVLd05WXzVkckZod1VxUmxBMEt0UjRR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTE1pWER4ajJRcUk3NHRXN0pMZkxGbWd4WjYzbnRzQUd2ZkwxNllfMXlFRElwSGpBSEJweHA1eXU0YnRlQldLcWFYdWU5NEFnNGNBcFF4X3RFOERzZ9IBX0FVX3lxTE1QckxlMlhjejd6enltLUl5ZzkyZ1VjeUlwcTJydUNqLUpGRVdVTTZXSkI0d1h0eUVNbS1KR3JHa3dVaVdyby0xWGVaWFJWVWwzRjFXYWwyMWxCTUlwSUxB?oc=5</t>
         </is>
       </c>
       <c r="F196" t="n">
@@ -6301,27 +6301,27 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Fraud_Scam</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+          <t>(fraud OR scam OR phishing OR smishing OR vishing OR "identity theft" OR impersonation OR spoofing OR "account takeover" OR "payment fraud" OR "invoice fraud" OR "wire fraud" OR "business email compromise" OR BEC OR "fake invoice" OR "supplier fraud" OR "procurement fraud" OR "social engineering" OR extortion OR blackmail)AND (company OR business OR enterprise OR customer OR client OR employee OR bank OR financial OR payment OR transaction)</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>AfricAI positions Africa for large-scale adoption of intelligent machines - Digital Watch Observatory</t>
+          <t>Interpol Takes Down Online Scammers - Africa Defense Forum</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>Wed, 28 Jan 2026 11:09:57 GMT</t>
+          <t>Tue, 27 Jan 2026 18:54:12 GMT</t>
         </is>
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMie0FVX3lxTFAwVTN3aUZSMl9pYzBfWTRaR05wU3ROUHowNk5GNVRWTVhPWWMzUng1bjFwSFdSWS10c25UQTd3clFYQlVZczU0eVF3SXB3ZklsTENjUWVqc09pWV9hZ1k5bFpXQXpYVXdKSVhvcXQxY3h2YmdLSFo5T1ZsYw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMieEFVX3lxTE9EeWNQellWeGdrM2NBNk5GOWV6ZHlxWGtZblBJS1JTbElWQTdISFlPUndyTnY5SC1KTS1tTmRxbnRQaTZ4eG9DU041bVFGcDgwb1pEUFphRjZkSTF2Y0RBdFNTVUNjbE1HbnB3aWllajg2UUl1Z0pGYg?oc=5</t>
         </is>
       </c>
       <c r="F197" t="n">
@@ -6341,17 +6341,17 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Jersey businesses urged to beware of scam financial emails - BBC</t>
+          <t>Nicosia based company defrauded of more than €120,000 via email scam - Cyprus Mail</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>Tue, 27 Jan 2026 16:43:45 GMT</t>
+          <t>Tue, 27 Jan 2026 18:05:58 GMT</t>
         </is>
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTE1pWER4ajJRcUk3NHRXN0pMZkxGbWd4WjYzbnRzQUd2ZkwxNllfMXlFRElwSGpBSEJweHA1eXU0YnRlQldLcWFYdWU5NEFnNGNBcFF4X3RFOERzZ9IBX0FVX3lxTE1QckxlMlhjejd6enltLUl5ZzkyZ1VjeUlwcTJydUNqLUpGRVdVTTZXSkI0d1h0eUVNbS1KR3JHa3dVaVdyby0xWGVaWFJWVWwzRjFXYWwyMWxCTUlwSUxB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxPMjRpT0tWVTd2X1lvRXVYMFlkZExpbWQ5MVIxX0FNVWR0MHZzN3lwMkMwTFBIeHRpZG1vd29ocjJEYlY4Y0VyQkx2bXp2ZFZCWkY4TFB2WGVibEVMRERCNHF3MFNEMGF2ZDMyXzJJZWV6ZUZ3bmdGallVMThfcnJTc2lPWVlsNmlIZEltY0pQRndXazRJdkVDSG9ONFdFckI2akxqSQ?oc=5</t>
         </is>
       </c>
       <c r="F198" t="n">
@@ -6371,17 +6371,17 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Interpol Takes Down Online Scammers - Africa Defense Forum</t>
+          <t>City of Enterprise Warns of Scam Emails Targeting Businesses - wiregrassdailynews.com</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>Tue, 27 Jan 2026 18:54:12 GMT</t>
+          <t>Tue, 27 Jan 2026 17:22:58 GMT</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMieEFVX3lxTE9EeWNQellWeGdrM2NBNk5GOWV6ZHlxWGtZblBJS1JTbElWQTdISFlPUndyTnY5SC1KTS1tTmRxbnRQaTZ4eG9DU041bVFGcDgwb1pEUFphRjZkSTF2Y0RBdFNTVUNjbE1HbnB3aWllajg2UUl1Z0pGYg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxPckNiSGNTSDJXYklmajZ2alZLTkRSZnhrSUprWks5ZUJhdkJJU0pWYm9Hdy05a2hOVHZOU0doWVBJU0hEU3RvUU1NX0VOSHFrYmdoeDFFcEpDRFJoWURzck5IX0FlYlRFNnZGYTNaR2k4YUN5YmFQenI0WlhPM3cxN1BZZmNJclp2T19HMm1aSUdtclpVOEtqVWlYanBQUHhkc3F2dHZrZzJ6OEpOaHgzd2VMaWdMQUZh?oc=5</t>
         </is>
       </c>
       <c r="F199" t="n">
@@ -6401,17 +6401,17 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Nicosia based company defrauded of more than €120,000 via email scam - Cyprus Mail</t>
+          <t>Scam Emails - edson.ca</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>Tue, 27 Jan 2026 18:05:58 GMT</t>
+          <t>Tue, 27 Jan 2026 18:45:47 GMT</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxPMjRpT0tWVTd2X1lvRXVYMFlkZExpbWQ5MVIxX0FNVWR0MHZzN3lwMkMwTFBIeHRpZG1vd29ocjJEYlY4Y0VyQkx2bXp2ZFZCWkY4TFB2WGVibEVMRERCNHF3MFNEMGF2ZDMyXzJJZWV6ZUZ3bmdGallVMThfcnJTc2lPWVlsNmlIZEltY0pQRndXazRJdkVDSG9ONFdFckI2akxqSQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMia0FVX3lxTE1RWlk3eHc5SmtLSE9WU1NWYVp2MUIzT1JjeVB0Ni1LUGJKaGg2bXNGVkQyeEVxaEs2QXZsc0c3X3dBbi1PcXI2LWcyQ2d4MERobFdSOVc2RzdfR0ZYUFpNSzJ3dDFtVnlCN1hF?oc=5</t>
         </is>
       </c>
       <c r="F200" t="n">
@@ -6431,17 +6431,17 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>City of Enterprise Warns of Scam Emails Targeting Businesses - wiregrassdailynews.com</t>
+          <t>On Your Side: Marshfield, Mo. business owner could have lost $1,000 in Venmo scam - ky3.com</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>Tue, 27 Jan 2026 17:22:58 GMT</t>
+          <t>Tue, 27 Jan 2026 23:59:00 GMT</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxPckNiSGNTSDJXYklmajZ2alZLTkRSZnhrSUprWks5ZUJhdkJJU0pWYm9Hdy05a2hOVHZOU0doWVBJU0hEU3RvUU1NX0VOSHFrYmdoeDFFcEpDRFJoWURzck5IX0FlYlRFNnZGYTNaR2k4YUN5YmFQenI0WlhPM3cxN1BZZmNJclp2T19HMm1aSUdtclpVOEtqVWlYanBQUHhkc3F2dHZrZzJ6OEpOaHgzd2VMaWdMQUZh?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxNd0NSSkJ3cTdrTmZFYUo0LXhWdVQ0ajJMekRUdkNHYWdKLXBqWkNyQ1BZV1BRdms5bnlVRnBwcDYyajdwUTJkSmozY1VBYjJVX3E3bXN1MXgzRElnMHNCYThSSWZQd0RYc05QSDBPZGdVT291U215c0c3bF9Pd1lpS0VPc01KeTR6cE80SWtHeEVFM09vemxPNWlndmtCaU94dEJSWNIBuAFBVV95cUxOckIxSE9SNjlYdXQzZnVfZXJiVEZpZ2lYQVlEc2JHME1FYUx3V2tCQUk3Yjc4MDU5bHdZMnVWQld1a19nYXp3ZWhGWmZKellMdmRKcWZVd2Y0Qlp4d1MtZlI3aXU0bi0zbExwbElfa1Jqb25vTGs1MTVna1cxZGNLMXZhdERVRmExQzFUTHR0YmNRQ3VDZGoxclhiUVdtelVpRG02Y21LWnJBQUNLX2FEeHFCSnhVWFpW?oc=5</t>
         </is>
       </c>
       <c r="F201" t="n">
@@ -6451,27 +6451,27 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>Fraud_Scam</t>
+          <t>Current_Affairs</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>(fraud OR scam OR phishing OR smishing OR vishing OR "identity theft" OR impersonation OR spoofing OR "account takeover" OR "payment fraud" OR "invoice fraud" OR "wire fraud" OR "business email compromise" OR BEC OR "fake invoice" OR "supplier fraud" OR "procurement fraud" OR "social engineering" OR extortion OR blackmail)AND (company OR business OR enterprise OR customer OR client OR employee OR bank OR financial OR payment OR transaction)</t>
+          <t>(geopolitics OR migration OR economy OR conflict OR legislation OR terrorism OR disinformation OR misinformation OR government OR policy OR regulation) AND (briefing OR analysis OR update OR report)</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Scam Emails - edson.ca</t>
+          <t>Policy &amp; Public Affairs Update – January 2025 - British Psychological Society</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>Tue, 27 Jan 2026 18:45:47 GMT</t>
+          <t>Wed, 28 Jan 2026 15:54:48 GMT</t>
         </is>
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMia0FVX3lxTE1RWlk3eHc5SmtLSE9WU1NWYVp2MUIzT1JjeVB0Ni1LUGJKaGg2bXNGVkQyeEVxaEs2QXZsc0c3X3dBbi1PcXI2LWcyQ2d4MERobFdSOVc2RzdfR0ZYUFpNSzJ3dDFtVnlCN1hF?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMieEFVX3lxTE42Ujh4OVlRRGlwY0IyNUo4aERBOFJJaDk1YzBnRVBsRHlyaUpPTzRneGdJN19TQnJmeDNWRlJjRkpjNnYtaHRzMzdjbDl4Wm93RFNDZDA2YzZNdTcxYU1DWFAxUUgtdkl2NEJtcWtKUG1SaE1CLXVKNA?oc=5</t>
         </is>
       </c>
       <c r="F202" t="n">
@@ -6481,30 +6481,2280 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
+          <t>Current_Affairs</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>(geopolitics OR migration OR economy OR conflict OR legislation OR terrorism OR disinformation OR misinformation OR government OR policy OR regulation) AND (briefing OR analysis OR update OR report)</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>Campaigners accuse government of 'dereliction of duty' as report says 22,000 patient deaths avoidable under Swiss-style model - Morning Star | The People’s Daily</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>Wed, 28 Jan 2026 17:11:35 GMT</t>
+        </is>
+      </c>
+      <c r="E203" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiyAFBVV95cUxPQWpUY0JtSW8ySFU2Qk82R2ZTRHVGRHJrLVMyQWtQajF5cXZhREg5VjJoa2ZCV1lrTEh6QWQ3UEdFNjc5V3pxektDdGhoWWVOS3NfOHpKNzExSkNvWU1hQy1malllbVJTSzhYMVFrRWtZdEJ5QjN3alJvR1FGdFlGWTJpT1pDNXdtSFBTTmt2Uk91eGNQeXBwMlgwWXJSZWFjSzZvQkFWRDFlRFJ5V3NBQTNKeXBITHFkX2VVQk5adVlleFZsTEtidA?oc=5</t>
+        </is>
+      </c>
+      <c r="F203" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>Current_Affairs</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>(geopolitics OR migration OR economy OR conflict OR legislation OR terrorism OR disinformation OR misinformation OR government OR policy OR regulation) AND (briefing OR analysis OR update OR report)</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>Welsh Government issues update after major England pub announcement - walesonline.co.uk</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>Wed, 28 Jan 2026 16:14:00 GMT</t>
+        </is>
+      </c>
+      <c r="E204" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxOclZXd0owaGhyLUhCVkZjMXVZNDBrWkJZWHJqMUNaQTQ4aUJQdU03aHNHUktuSk9hWTlJQzhlREdteVZpZ3l4M2FCeTRDeDF2RkJ6UDFhakZyT0tFb0RjUEFMdXpVOWM2cnRkWlBhLUtCX2wyS25jbHBjODFfTTRNcUFGWHUzb3NCSzduTkdsQ09RcVgzbGRab3Rn0gGfAUFVX3lxTE0wUGhqU0Y1U09mMEFwRkNFX0V5S2VmdmV1V2k4dmdOYm9xSlRXMDltVlNCcm91OGtrNXBZMzF2WGIwdGI3OEVXbnM0eGw2WHR1elRteHhoZGZDMUVHa3RFM2VoX2tFemxpSDdqazFGOXVESUpYUjJTZXFSazItcVJSTFRuV2I3bTZFYUp3UWFOTU50N05qQ0xoVE55UDhWZw?oc=5</t>
+        </is>
+      </c>
+      <c r="F204" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>Current_Affairs</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>(geopolitics OR migration OR economy OR conflict OR legislation OR terrorism OR disinformation OR misinformation OR government OR policy OR regulation) AND (briefing OR analysis OR update OR report)</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>Exclusive: White House set to meet with banks, crypto companies to broker legislation compromise - Reuters</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>Wed, 28 Jan 2026 21:07:46 GMT</t>
+        </is>
+      </c>
+      <c r="E205" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi2gFBVV95cUxNZTdyeXJlNk1XYXJEXzVIM0trWW1XXzhwLTJMbXM4NmJUX2s0UWZMRnppblVVVmZCUHN1Q1NMUmpjTE1odV9sbjE5R0JlU2k3S0Joclc1UG5pVWNpTXFSYWJ4V1VGX0ljcWlPenA0R0Y5U2gyMGNYZHpBYlJPWTFhc0hVdGdfU3lwalBBNjFlM2ZNR3huN01TaWxlOHF4bWVrMjR5MFM2b1VHMTh4TDg0V1pZekE4WWNQVVEwTGhaVDhKcnBsREtrcUtpOVB5OFpKQkVBd05QcUFudw?oc=5</t>
+        </is>
+      </c>
+      <c r="F205" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>Current_Affairs</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>(geopolitics OR migration OR economy OR conflict OR legislation OR terrorism OR disinformation OR misinformation OR government OR policy OR regulation) AND (briefing OR analysis OR update OR report)</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>The Trump Administration’s Latest Expansion of the Mexico City Policy: A Funding Analysis - KFF</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>Wed, 28 Jan 2026 22:15:24 GMT</t>
+        </is>
+      </c>
+      <c r="E206" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiyAFBVV95cUxPNkN1SklpNE83V1hWb0JCLWUxTWhDQ0p5S1Q3UmNTVDJUWnR6RXpTX08tZmJUbWZUaVVjMkY4TjBGNE9WSUdnQW5weHlmbXY5YmdWdktZSWRNSnY2Q2dvWEE5Wl90MkRVMk9nWHJQVjQ3MFN4RS1aU0FwNFE0MkJjQ0l5UjFTWEllTXRrcUZlZ2JCQm0yakFOb25jbGQxTGxZNHNjcFNIdGZvNkk2T2VNRjdCazc5NFV0c0NIelExSkhVZFptamRoeQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F206" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>Current_Affairs</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>(geopolitics OR migration OR economy OR conflict OR legislation OR terrorism OR disinformation OR misinformation OR government OR policy OR regulation) AND (briefing OR analysis OR update OR report)</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>How Human Ecology Education Defuses The Roots Of Terrorism – Analysis - Eurasia Review</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>Thu, 29 Jan 2026 02:01:39 GMT</t>
+        </is>
+      </c>
+      <c r="E207" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxPMm5aSlRZWTYwOGR5LUlqVkhRU3ZvdzRacFFEeS1nV0Z3N1BzaWxTWlpiN2dVdGpqZWQ3Y3VRSDBfenlFcXJRSmZvWmZDbWNtYndQTkZWeHBwWUZja1FKQWgtV2JSVndrQWJoampzbl9RYWh1Wm9OdUxlTUNqQm11VDFFZktXaDNadUdpT3ZiZUJ1SnU4bDM2eGN6SWRPbmhMYmd5T1g0Snl6TWs?oc=5</t>
+        </is>
+      </c>
+      <c r="F207" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>Current_Affairs</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>(geopolitics OR migration OR economy OR conflict OR legislation OR terrorism OR disinformation OR misinformation OR government OR policy OR regulation) AND (briefing OR analysis OR update OR report)</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>FFRA’s Impact Report Highlights Progress in Film Recycling - PlasticsToday</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>Wed, 28 Jan 2026 20:28:15 GMT</t>
+        </is>
+      </c>
+      <c r="E208" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxNUGs4eDVQWWlHa1dsazJ0c0I1UEpQZ2tleGJOM19xMS1hR0hySVh2OFNWQkRscWdfbWpHQlJiY0JCWmw2S1Y5RDhmYlROMHU4bDh5bXl6RnJXZlpQVzNEX1Z1UnZyVk93UFZGdW1SaGwxcUxaSlVBTVMwSDdQTzAtZTJ4VllZMUdDNTVfazUzUnpGUXJRSlMzNjZ5Q1JhWDV1cnFFNEhn?oc=5</t>
+        </is>
+      </c>
+      <c r="F208" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>Current_Affairs</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>(geopolitics OR migration OR economy OR conflict OR legislation OR terrorism OR disinformation OR misinformation OR government OR policy OR regulation) AND (briefing OR analysis OR update OR report)</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>Economy update: S&amp;P 500 hits 7,000 mark ahead of major interest rate decision - GB News</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>Wed, 28 Jan 2026 16:36:36 GMT</t>
+        </is>
+      </c>
+      <c r="E209" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiaEFVX3lxTE9GbGEzMzlJSXUtMGFBRUhmZjAtUWJZaHE5eE9QN0d5NklmWFI1anFBWVFVNklKanlsRjdvQ2p0RG1reWRVR1R0aEVUTUN2WGc4Y2MtenRrdXJjM3pmbHpFcWFLSHhsV2lO?oc=5</t>
+        </is>
+      </c>
+      <c r="F209" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>Current_Affairs</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>(geopolitics OR migration OR economy OR conflict OR legislation OR terrorism OR disinformation OR misinformation OR government OR policy OR regulation) AND (briefing OR analysis OR update OR report)</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>Trump Meeting Complicates Slovak PM’s ‘Sovereign’ Foreign Policy – Analysis - Eurasia Review</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>Thu, 29 Jan 2026 01:31:27 GMT</t>
+        </is>
+      </c>
+      <c r="E210" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxOV2ZBcGNsYU1sWDJJNGk0TEkxUE1aeTQzWThLT2ZQbzlLRWJLRGZSNG9qTnVYREhmMk5NenpqdUpEVjNUTUstMUl3bmJaX3czSUVKS2pOcTc5UVdDeDgwQjRnUWlVdk1qU3RtTFA1dWxiLW9pUFgyV05rNjRhZ0RrRUZmbG1FWWJEVjdZMTlLT1dOS21SMmNDQnFYTHpZU2pLYm82MEZVZWVNZ2hCWVJn?oc=5</t>
+        </is>
+      </c>
+      <c r="F210" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>Current_Affairs</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>(geopolitics OR migration OR economy OR conflict OR legislation OR terrorism OR disinformation OR misinformation OR government OR policy OR regulation) AND (briefing OR analysis OR update OR report)</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>New report: EU installs 27.1 GWh of new batteries in 2025 as utility-scale storage drives record growth - Sonnenseite</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>Thu, 29 Jan 2026 01:55:00 GMT</t>
+        </is>
+      </c>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi2gFBVV95cUxPZnAxVkJkZW5NUW83UENDcUk0ekFZQVR2MXM1bVk0a2VERVpiZVBqQVJCWjNNWmdwWjlsWmV4SW91NXcwcDF3RHlUcGM5VF9PRW9JY3pVOTNVVk15MVFZYUxNSVZPOTlndVZfUXhXbHdrbTU1NHdaN3UxQXFvRjNXamVYSlAzWjBPMjNaRUJVdENydFNka0RQaVlFbXRNQnhWMWx0MTFITFE0TmpjUGVlUGxtSGE0dV9hSlVDUTVHZmRERXJFa3kyTlIwdnZaUkFrSkZEWlc1bUZRZw?oc=5</t>
+        </is>
+      </c>
+      <c r="F211" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>Supply_Chain</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>CMA CGM and Stonepeak Announce Groundbreaking Terminal Joint Venture, UNITED PORTS LLC - Stonepeak</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>Wed, 28 Jan 2026 18:01:34 GMT</t>
+        </is>
+      </c>
+      <c r="E212" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxNdkMzeVdvb2JURWE0T2E2SzB1c21WNjdHVUEyT2F0c0h6SWl4RExIX2xHbklETTlzSS1VMW02Nm5WSkozb3hJMTBFUlB4Nkt6YTMzQWhsR0paZUpoSlgzTXR0cW1IenlwQWhFQUY1ZE45akFETXE2MF9iYlg4NE84SGRCVGN5UE82RFNKY3V4aUVSeHoyOU51ekZsWHdkWXFCZ282SFpVYXVNTTZWNWh2dU53?oc=5</t>
+        </is>
+      </c>
+      <c r="F212" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>Supply_Chain</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>Russian oil income drops sharply as sanctions bite - Financial Times</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>Thu, 29 Jan 2026 05:00:38 GMT</t>
+        </is>
+      </c>
+      <c r="E213" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMicEFVX3lxTFBHRTkwS0h1Vk43djd6VF9kX1JUeTdsYWM4RElsSDJjZDYwVGhFQS1ZWWVRRHV5WTJGNjNoNEJBX01DaUlLRWkyWVZhMy00V015bDBIRU81eFZCbWU5d2EwQkc4ZVUzT3lmWUp4NnQ0X1E?oc=5</t>
+        </is>
+      </c>
+      <c r="F213" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>Supply_Chain</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>Are you one of the 800,000 households on the Feed-in Tariff paid to generate and export electricity? From 1 April it'll get worse - Money Saving Expert</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>Wed, 28 Jan 2026 19:14:33 GMT</t>
+        </is>
+      </c>
+      <c r="E214" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMilAFBVV95cUxQMG5KcEVTMFB2Vkh1V1BvaUNqSnBKSzE4V3I2YUExLW9vSk5sbkxQSGFXeGRuNVN3d3c4dEU2VF9UaEg3MExKeGlLTE9taVZBTTI5VDdjZVJlazlwVjBSNWhicGRSNnpBX0NjcER6RTh4d1Y2RDdnNFhYNUZGd3ZpWkNfOXFzcmUtT1MxZHJpUGxmUTRE?oc=5</t>
+        </is>
+      </c>
+      <c r="F214" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>Supply_Chain</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>CAF Disciplinary Board imposes sanctions on the Fédération Sénégalaise de Football (FSF), the Fédération Royale Marocaine de Football (FRMF) - Confédération Africaine de Football</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>Thu, 29 Jan 2026 00:11:32 GMT</t>
+        </is>
+      </c>
+      <c r="E215" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi-wFBVV95cUxQQVphMktMeGtocUJpa0N5ZWo5YUc5T0xncW5WQU5kRTBCZmltdXZJLUk5SUlQT3ZaMnJaajdsQmtMZ0hwb3ZKZHlFM250Qkh2R1BuS0NGUHl3WDQ4UnhJVEd2cTN2LVpBVG15U3ptZ25WbU15b0Z0ZnBGUHNNQkx5Z2I3c1RaN3NHb2pDdG56ck90QTg5Wnh5OVVsNkdvbUVDdkZrXzVFbDI2UmtXb3FUdGxNNzd0ZFJlX3NCVTRnRVc4Zmc1YlI4MmhBSk1wWkJKX0dOenZlc29uWmE3UFpjMk9GZFlJWll1NmZhc1pGSXlTNHpreUg5b25TSQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F215" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>Supply_Chain</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>Reshoring in action: Three mobility manufacturers betting on homegrown production - Monocle</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>Thu, 29 Jan 2026 00:08:57 GMT</t>
+        </is>
+      </c>
+      <c r="E216" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxOR2pWVHQtQ3JaODNBdXNUaXVHdzNVckc2LUYxV3lScVdHdlRSWVk0d3ZFQWpscnQ0NXRCNW1vbzU2SDl5MnBSamRPTVk2cG9PLThpTVBya3l1VVp5V25rNjJqSkhaN0JSUlBkRTlrOUFya0VCbGFETm1wYWN6RmYzSVVWdFRwYUpsTnhPN3hUZFg?oc=5</t>
+        </is>
+      </c>
+      <c r="F216" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>Supply_Chain</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>How Tariffs Accelerated Brazil’s Export Diversification - FTI Consulting</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>Thu, 29 Jan 2026 04:23:40 GMT</t>
+        </is>
+      </c>
+      <c r="E217" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxOYTVBLWVrTmJBbExsRkJlMWVpRWdMcTZfRUhjS3p6cGlVeDcxRHJ3TlphS25qdnRoeFBXXzVBY05tb2xfYmlFSUhJQ0ZJTGFscW9CdnBVYnpiMGRKNVNaWVd5ZkJaOW1UOE0tNGZFRERLbmtHRFNJTVBsbFlTVFBWOVZDZzdlLVVWeFpHNnBlc3VncFlHT1VlUDlFa09WQQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F217" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>Supply_Chain</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>China warns Australia against taking back control of key port in Darwin - Al Jazeera</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>Thu, 29 Jan 2026 05:28:14 GMT</t>
+        </is>
+      </c>
+      <c r="E218" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxPZmJONHZ2d2R3eW9MWF9MNVhuLXV3anBzaW1VZVRlVUZmR3JNb3dSUHlwWkhJdVNzZ1hvUnpHdjJVbjRvU0F0TVdGR1duX2Fid0laXzdEUHJXWDJzNGcyR1psVi11NE9ZYW16R2I3aHpzQkZIUXBBNE5pQ2lTOXdsdm9oUWhuUTRyc3hqOV9kTjZnVXA0V19wMlQ0OER0TVJKSnNKV1pxRXRwckVXMXlYRW9R0gG3AUFVX3lxTFB2TXdzRF8yTXVhRXlPUEphTWxOZFRFamZkTzI2YTZyUHZhU2p0R2RsZWE2TzJsR0xLRU9KdFlSVDJzOUowaXNWZ0hjc0N6OXIyUzRtZ0VYaWRjQ0prWEQxYmZCaGc2NlF3b0UzRWRFNUtteGc2NUotTnVwT3h3S0o4UHdjWHVUYjNOYXpjWWMwM3FyUmJwV3lES2JTb3BDMmNJeGhyMzFFYlBOYU5VbVB2Q1JuM193MA?oc=5</t>
+        </is>
+      </c>
+      <c r="F218" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>Supply_Chain</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>Fresh investment in Stornoway's deep-water port - BBC</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>Wed, 28 Jan 2026 14:21:46 GMT</t>
+        </is>
+      </c>
+      <c r="E219" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiXEFVX3lxTE5va3VJWlRFMkZYLUR6ZnIxOHdfSkZoQmRUOUM2UXpZQkZEX1J1UUJiY1llWE1OcE0ycjhUdXpUY2FubmV3cnhydDVMSEhuX1oxbzQwbV95ZzVXYXJi?oc=5</t>
+        </is>
+      </c>
+      <c r="F219" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>Supply_Chain</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>Will Ryder to leave Vale's Academy set-up - Port Vale Football Club</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>Wed, 28 Jan 2026 11:33:30 GMT</t>
+        </is>
+      </c>
+      <c r="E220" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMidkFVX3lxTE1KZVRaTGxXMzZyRjUwSHhqQnhBTUVmbTllV29saURTeG13MWpUQldMN3puQmFfeWtqLUJ0NWM2clN2Z0pLWlBlMFpBamlMWlR3bVZkcmpWLU90TWRkRnJCWF9oYTF5N2owQTV0TXQ2UHRaUHowVnc?oc=5</t>
+        </is>
+      </c>
+      <c r="F220" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>Supply_Chain</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>ECOWAS lifts all sanctions against Guinea - Anadolu Ajansı</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>Thu, 29 Jan 2026 05:27:10 GMT</t>
+        </is>
+      </c>
+      <c r="E221" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiiAFBVV95cUxQaUMwU1BQUXM1XzhnN3l5VHpWb2F2aXM3Y3NKMU8yemhYbHNTWWUzNXZIaTY3T0syOS1SNXp1VFpHVGdHNERHQ0d2MlFfMlBVT01qRkEybWNsU1hLZkNxMEx6OEhXZ05hYVhPQlROWXcwWkdITkxORmIyT1lfc2JRaXZac0xORG5P?oc=5</t>
+        </is>
+      </c>
+      <c r="F221" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>Supply_Chain</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>EU to impose new sanctions on Iran as France backs IRGC terror listing - Financial Times</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>Thu, 29 Jan 2026 06:03:37 GMT</t>
+        </is>
+      </c>
+      <c r="E222" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMicEFVX3lxTE9ub2x1aWE2VGVLaXQ4WmJZbzE2QzQ2M1V2VE9hbnJ0dDE0bml0dXpmeE1iSG01dXl6cVBCWWdaMGZzZmRwbDVGMnB4cXFhM0JnRjl4N3BaLUtwTkdZVHU2OU9qSkJ4Qmdrd1pKQWVuV00?oc=5</t>
+        </is>
+      </c>
+      <c r="F222" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>Supply_Chain</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>Introducing Auberge Port-Gitana, Lake Geneva’s newest bolthole - Monocle</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>Thu, 29 Jan 2026 01:19:37 GMT</t>
+        </is>
+      </c>
+      <c r="E223" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMikgFBVV95cUxNZHRtM25HeWNWT0Z2a2ttTGFDcHBJeENGbGZ3UXF0RzhsYVUxaWI0WDJoVVBncGVtWHlZMVh4TkRvV0lSSkd0TFE4Z04walJUT3BENEttRWxpS0N4OUZ5VlN3dnRJRTdJSlh4RUJURjJINjh2WUdqZG9nWFpodnhidW5WUEJmZ0JpTGRQS3QwSTRUQQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F223" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>Supply_Chain</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>Carlyle agrees deal to buy Lukoil’s international assets after sanctions - Financial Times</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>Thu, 29 Jan 2026 07:29:07 GMT</t>
+        </is>
+      </c>
+      <c r="E224" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMicEFVX3lxTE10cy1LRG5VeExnZ3B1d3RUS0xCRENscDVOQzd4MG5vS2MyaC1vd3BSYXJIeHpndjhVQjlQREEtYUdELU55Zlh4bTJ5OC1rTGtibHhhMDd4djROZ2R0YjVHaFdaYldGMFE4d3JRLUV5N0I?oc=5</t>
+        </is>
+      </c>
+      <c r="F224" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>Supply_Chain</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>James Plant: Tranmere Rovers sign Port Vale midfielder on 18-month deal - BBC</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>Wed, 28 Jan 2026 17:24:11 GMT</t>
+        </is>
+      </c>
+      <c r="E225" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiZ0FVX3lxTE1PS000U2JzX3NIUTFSdTlGTThpX1lrZ0R4UDhwcHE5bUJOUkV5QjAyV2JDTmYzSlE4SlAtVXI4YTgzYlFGYUlFUHhraXVDcW5Wdm42MWNkMVh6YzZnWUMwcHFMTFhCYTA?oc=5</t>
+        </is>
+      </c>
+      <c r="F225" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>Supply_Chain</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>Banaszkiewicz touts Freight Investor Services as the right horse to back in 2026 - Tradewinds News</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>Thu, 29 Jan 2026 01:27:50 GMT</t>
+        </is>
+      </c>
+      <c r="E226" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi0AFBVV95cUxOalIyMU8wSVBIYzVvcHM4dHhMZ3lTN09aQnhFRlBPd0xjNDFBTU9JdzA1REtCdExFSWRtSklzdmlBSWpNXzFtVHFIWmpMdjNVclV5UVEyaGpGbDM0RVV3WF9mRUo3dnplM3ZZbmd0STliQmVsYUpPRE5rX3F4aWZzQ2Nlb0YzYS1kNzBCZVNKdVV0N3hNRFZrX1dxNGY3UTNsU3JsQjJXOTl5U3dhREdoSGdTNzVhTW5PcWItTVlpU3RWaXNxNzdiNmlmbFVoa0ZT?oc=5</t>
+        </is>
+      </c>
+      <c r="F226" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>Supply_Chain</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>FuriosaAI starts shipping - Electronics Weekly</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>Thu, 29 Jan 2026 07:00:13 GMT</t>
+        </is>
+      </c>
+      <c r="E227" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiigFBVV95cUxQdG1qSmVLQlo0UGgxb2pWWUJENmo3Z0lNdHZDYm9kNDUzUVBwc2NZWlRnNUJKejlyc0Z2MV8zcGg4b082amZJTkdYd2pGbVpkTVJFTkk4NVdQeXpWanJJUWxsMkI3Q1ZCV0R0Nk93UWpDaVhGbXNBa1JVM1VJTzhDMGRQM3ZBM3VuUWc?oc=5</t>
+        </is>
+      </c>
+      <c r="F227" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>Supply_Chain</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>ICS' latest flag state performance table shows strong compliance with global standards - Baird Maritime</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>Thu, 29 Jan 2026 04:47:12 GMT</t>
+        </is>
+      </c>
+      <c r="E228" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxOM0lKb3JJOWR6UjNTMHdEbmwyaklhMVQwZTdSOUs4ajhfczRxUVBFR3Jha1BBVVdYd1A0bzJfd0VPczJpY19HRWoxNUIzODdwdkhQbndseHdGbkQ4QWpkdGVTNGI3MkdqRmNKTjJGNlQ1My11WTM2amtENzN1MGY5bGp0RGdocmR5Q0k2X0M4aHN3MWdoelp6NW9GNnZjM3RJbWxidjZjYXJYOVFXcUZIYmk1VUtuQ0djTVF6X3U4OE80UdIBzwFBVV95cUxOQngtYnhfdTBoZXF5R3NvVjNNdTc0NVNoYXVSZFYza3U2b1ZmbU1vekJydHFwUVJzNVIxSmlMS1lhMVFhb212N09iOEpVVGpsVlJPcjdrZ2MyaWhqY1hhTVZBSjA3eHBGSXVmekREZV9ORGF5RnROVllGY0laLXhfX2MyYmpUNTZHNkZsdjF0MUVndEhZZ1B1Z2txN2FkRkRXUlFJeGFYWjRscTRJOGRMX0VZM0dkUW9NUWFmbjlSMUVUcFhNZUJKWEI0UlVBSVU?oc=5</t>
+        </is>
+      </c>
+      <c r="F228" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>Supply_Chain</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>At World’s Busiest Port, China’s Unbalanced Economy Comes Into View - The New York Times</t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>Thu, 29 Jan 2026 05:00:15 GMT</t>
+        </is>
+      </c>
+      <c r="E229" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiekFVX3lxTE9tMV9aOUFOTE5mNTd3OVpiMWtwbjd1bmdmTmlfamtnSGpqdDZrLXhKR0EzeDdkX21YZ21yTERJOU5jZXJsajFNVHp3ci1FR2U1ZWRLSDFVNmlOaXhMYXhzQ1QxQ09rcERJMjV2b3VqMU9GVzBQX2V4UW5n?oc=5</t>
+        </is>
+      </c>
+      <c r="F229" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>Supply_Chain</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>Priceless But Free: The Software Supply Chain Disconnect - Forbes</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>Wed, 28 Jan 2026 23:54:13 GMT</t>
+        </is>
+      </c>
+      <c r="E230" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxQU21MMjBzOWtZU1Q4Mk1vOEVoQ25Pd1g4dW1jQnhuQm1uS3BUdW95MVV1bkZlejBXcGRTWHZ0ckt2dDlaU0tyWU9jU0lfalFoS3lNZmJ3UXhBSFJ6RldPRzNhbnBfRDd5OWJtN0RGSHJMeG92T0Fqc3NJZnE5VWJQOU9wWm1RaHRCMHc2TXRmSXpWZ0F3UUwzaGJBU29jUGFkQnhEcEU0TWwtNklO?oc=5</t>
+        </is>
+      </c>
+      <c r="F230" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>Supply_Chain</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>Rolls-Royce Buyback Weighed Against Airbus Supply-Chain Risks And Valuation - simplywall.st</t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>Thu, 29 Jan 2026 05:25:16 GMT</t>
+        </is>
+      </c>
+      <c r="E231" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi4AFBVV95cUxQZ2R1OTVtN2k5OUs1M1d3UWttaGtQN183a2k3Zzg4anFlMUdBbjBxcnhmZlo3R3ZWYTRBNzJxWDhPbWRXQ1NFNlZfY2l1dDkyMzROV3dRcHY5YzNsWlJhMXBHbjVraVN4b2FJUHNQMjJHNmpzWWFaQS1ILXMweHoxc0lfYmwxZnk1Z0x6ODNOem9KSS1vOS1SNm1hVmpiUGh1cGwwQzVkR0d6VGpwOFlLRi1pTE9TUmNuak1oY01rTllWQU80UW5obDNlVm90bTQ0ekZuZEdxNkZTQlJ6dDZ0etIB5gFBVV95cUxQUWduZkwxOEFuUnlIZU1QVjZKdnBmV1lPYnlTb1hNSms0YUpRUms0TlVoX3ZEalFVRThsdXhSQlZFU2Q4clg5bVNLX25kM1ZhQ29vVVc0eGdldVB0eVZBNi1KUEhNVXJKQldhaTRIeUYyR3ZnLW50cFZfdm5aY01wSVpENW9PZ1c3dXUzbUFQYk5wb05wZThLYlV3RmJTQkxudzhwaGJSRWhaWTdVZDc3aExCdWtuQkU2aXd5VUQwazN4X1BGRUlFNzE3MWdjOFh4eXRxcUVHeWtPSjcwdEpZb0ZDRGZwUQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F231" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>Supply_Chain</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>Firms Strike Deal for $10 Billion Shipping-Ports Venture - The Wall Street Journal</t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>Wed, 28 Jan 2026 18:50:00 GMT</t>
+        </is>
+      </c>
+      <c r="E232" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiqwNBVV95cUxPYmZVNHVodzFYeDNjZnFDQXpBZUpBU2dwd0ZvVnRlWXdDVUJMQUV3ZjhPalF0bzU3Zm5zTmlHUFZLdkx2YVA5NHhTMWtaRjVMaUYwWUZyUW5zTm81eFNjR254UWlwNnBNRGl1cXBWSGxIWEZOTVlacUFCX1lKUkwzSTZSUlVqY2hPUE5nRjBXaEJIMXE5U0JnRTdhT3o2a2c5VzJMZjBiLUZxNF81QjdueTVhRXlFVWIwdVhCVVJ6bkxOSmxDTEVneFJsRnhlbmc1M3F4cnFzSVlyYzRKeTZGZTNIa2RMYzJUeTdXRlJ5ZWt5dUl5cU9JMU1hblN6MnoxdzZCallpd1VqaFFGY25maldXTmJiU1pZbTRDVFlkNXR6R3lfcUlzWlVYVWdrLTFVT2ZYNXp2R1FDQmp2eFh1clM4RWdReDJYMElYWlFIcTZiMy1SenROQlFWUmJlTDZjc2FuRXBDTGFUSWZqSVRqRGZZZmswaF90cWFsQTIxS1dfbHdFZ0RMNkdtYnY4Vkh0ZXBGNUJPNml6YnhfS0RDM0h2ZThRaHVnS1ZN?oc=5</t>
+        </is>
+      </c>
+      <c r="F232" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>Supply_Chain</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>Freight Island serves up Leeds expansion - Bdaily</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>Thu, 29 Jan 2026 00:21:33 GMT</t>
+        </is>
+      </c>
+      <c r="E233" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiiAFBVV95cUxPeVJ3ZlZRUzJtUUJmMlZBQUFkUEI0ZDE1ZzhkOVN0d2RVWE12SjAwaWNPR0FNUjY4LWV2bVBGOUhZNGJqQW9JbW5kMHdaTXo4MG10VDZDb2RQalY2akpKNTdxRkQ0cVZYSkVjZ2NLOEJGajdEejhkWDFOQTlLbHVod3MxajlJX2pI?oc=5</t>
+        </is>
+      </c>
+      <c r="F233" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>Supply_Chain</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>The New Frontier of Operations and Supply Chain: AI, Resilience, and Intelligence - ARC Advisory Group</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>Thu, 29 Jan 2026 05:41:50 GMT</t>
+        </is>
+      </c>
+      <c r="E234" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMilgFBVV95cUxQb2FMUHI4WmJpNFQzOGpiRGxZRUxnNUtPcnZibzBpOWstTFpxeDlja0pCWEJfNGZGODNmREt4NVdBSm5yQ1NSQVF2bFQ4eGJUVnktSXI0cUJVUk5wcTdjT2M2c1lvVi1WcWY1elBfRjZIbGd2S0tnSzlhZWhPdUY5NjltNUdCaDlNcjh6SlVZQ1VnRTdCRUE?oc=5</t>
+        </is>
+      </c>
+      <c r="F234" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>Supply_Chain</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>Vietnam and the EU upgrade ties as US tariffs reshape global trade - The Independent</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>Thu, 29 Jan 2026 06:21:00 GMT</t>
+        </is>
+      </c>
+      <c r="E235" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxObzF4bmFoYXowU0VsX0xPbE5kYmlMT3diQkJRV1dlaUlCcENTWGMtTHRyNnlDTHE3QkRaanRCYlhfV1VsR1N6NEFrUVREY092MHNza2RVYTR1d01wZDJPMGJzWHJjWmdvMFFvd0R0N3BWTVpORERxUTlLdVNUcUYySXhyTzZQTGt4NzRZSlBHY1pzaTQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F235" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>Supply_Chain</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>Starmer and Xi Discuss Tariffs and Migration Strategies - Global Banking &amp; Finance Review</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>Thu, 29 Jan 2026 07:37:08 GMT</t>
+        </is>
+      </c>
+      <c r="E236" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMijwFBVV95cUxPM0hOTTdvbTFvNERHcVZMWncwWTR0QlQ1WVJrcUlHcEtiVXFUaHRaY1cwTjVwU3dHV2FPb010YlhqTTlhbmQzRDRhTE5hS1NPT1dmdWtHOVU5NFlYRlF6ZFY5aVFCREk5UDRncXBJSHJCR1VHVm5rYVNnUzZIc3pSUEZpNHF6X0NzYV9kMWR2UQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F236" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>Supply_Chain</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>Robust cytoplasmic partitioning by solving a cytoskeletal instability - Nature</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>Wed, 28 Jan 2026 17:25:11 GMT</t>
+        </is>
+      </c>
+      <c r="E237" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiX0FVX3lxTE5Rall1alZIVmw5YUZpRGlmMUpuSEZLMWdwT3VKOHdPVVMwMnR5TzV4UFk1TTYtanBrdEdmZ002QnNnVkJNX1hTRDZEd0J5QkZGNldNWEV0bHhUa0lCcnRF?oc=5</t>
+        </is>
+      </c>
+      <c r="F237" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>Supply_Chain</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>India to slash tariffs on high-end EU cars to 30% in boost for luxury carmakers - Reuters</t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>Wed, 28 Jan 2026 23:30:00 GMT</t>
+        </is>
+      </c>
+      <c r="E238" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxPYWhwY3d4cERpSUxvRDVzU3RfMVFZaUpuendqVTNGSGVHMUVoNWhjNlltc1FHZTlpY2Y5eGxMbnVHbURBSVI3VEw1RDA4XzYwcjJqX0ZFenZqMEtmWnJJNHJoaVNRMkhicWVhSDBhN2N5bWtFSHVzSGFRSFc2bzJfbUpEWEFQdGVQNjlUdm1ud1pfd0N2czRld3NrVjB4c2Q2eDFaSU1JU3FXaWlYOW9J?oc=5</t>
+        </is>
+      </c>
+      <c r="F238" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>Supply_Chain</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>UK's largest 'living seawall' unveiled at Sussex beach in pioneering project - theargus.co.uk</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>Thu, 29 Jan 2026 05:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="E239" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxOeWpWRlJ4TmhxcUh1Rjc1M0xkU0xmTlZOM1ZCWGhqUzJBSXFJdDlxdk9vMUhKX1JPOFFzYmcwUDZkRkpTWndHdE43SlpfOVI0UU8wMkp0eE16RE12Z0prYm1JU0tuUml4bVpoQkN0bnlxSzJHR3NhM3ZSNzhkSDNWdzRMcVpzUzRNTEVudTFaX3BxQUdadlppbEZB?oc=5</t>
+        </is>
+      </c>
+      <c r="F239" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>Supply_Chain</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>Orlen Neptun books Kołobrzeg Port space for offshore wind project - Splash247</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>Thu, 29 Jan 2026 07:22:28 GMT</t>
+        </is>
+      </c>
+      <c r="E240" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMikgFBVV95cUxPaUhBMU9ULUJCWHZBajF5ODBzVENsemZhSXZza0ZwcURRXzZyMEZVcWh6Z29pY2JEZlZzYl9QczZHaHVGR2xRaWY0d2JJMkFZRDc2OUVybThtZWpCZHh5T0pzZWIyOXhjZGcxdWt1WmdNVlNHSzRIeGlkMkt3QUZQeWN1VktPNnRFcko2enpLejZwdw?oc=5</t>
+        </is>
+      </c>
+      <c r="F240" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>Supply_Chain</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>Port Glasgow woman caught with £67k of cannabis warned she 'could face jail' - greenocktelegraph.co.uk</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>Thu, 29 Jan 2026 06:30:00 GMT</t>
+        </is>
+      </c>
+      <c r="E241" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxQWTN2NlhLMGo4YzlJZjItWGV3Yk9aY210QUFuSE1LUXFDYmNhZXk1RkRrMVFuRzJtUmY5aUl4WmZJa1RDVDRuLVNkUEJPeVAyOWNINjI5MzhNT3IzcHpkdmlXczA1N2E5Ynd4dWFZWWw2YUZwd3NwNkRhR0s2aFBtdEttWjBKNnQ5SGo3VWNUa3JJNVMwWVF3ZnI0Zw?oc=5</t>
+        </is>
+      </c>
+      <c r="F241" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>Supply_Chain</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>Hatters boss responds to transfer speculation over Port Vale striker - lutontoday.co.uk</t>
+        </is>
+      </c>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>Wed, 28 Jan 2026 11:32:00 GMT</t>
+        </is>
+      </c>
+      <c r="E242" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxQak1WMlR6dFVpUi1MVW1odjRDcWJWTFBlYzh3dmtFLXFxZmM4YlNWNEdES2F3ZUhNQUxYakgtek1sV0hhenlYcWpxdmxheW9BSW9jaE0zYWR0QVFMU0RFVUtzbnB0N2ttRlAwVmI4UnRxMmRZbEZpUWlINW5EVVN6aVNYYkl1ZE1OY2UzNnRoRzhPUWU0VllqQzNYbUZ6X0k4WnUxTmRoRVc1RS00YjRSZUFZbWVnZGsyckwweHhEQURpYjdydTJJc2RKYw?oc=5</t>
+        </is>
+      </c>
+      <c r="F242" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>Supply_Chain</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>Palau revamps shipping register - Splash247</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>Thu, 29 Jan 2026 07:12:15 GMT</t>
+        </is>
+      </c>
+      <c r="E243" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiZEFVX3lxTFBTaUtZbkV4bEVRUjlKN1cyamFLMXNRaWZPa2tuSkllV0JjMFE1UlkyMV9Eak5hTUJHdU1QOTZBQTZoWFRSVXcwUTlPZnVNRUpkZmdfNkVZVVRSeFNiREhKTjd2RmM?oc=5</t>
+        </is>
+      </c>
+      <c r="F243" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>Supply_Chain</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>Russian Strike Damages Port of Pivdennyi - The Maritime Executive</t>
+        </is>
+      </c>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>Wed, 28 Jan 2026 23:28:00 GMT</t>
+        </is>
+      </c>
+      <c r="E244" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMihgFBVV95cUxNZG5lRTJwSUNsSEJOMkt2QktDY2wyTmdtRU9oSHY4QThYU19jWE91UXo1ZHA0MlZhNVpPZWpqN29lMWNka2h6TWdNQWpucElrV2I2N0RZT1I3djZhWjF2MTJ3UXJ6NGVNSWFnRk5sajRhcUpSdlZDeFlsakJ5X1VxbG1yeTBUQQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F244" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>Supply_Chain</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>Beibu Gulf Port invests $2.24 billion in terminal construction - Seatrade Maritime News</t>
+        </is>
+      </c>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>Thu, 29 Jan 2026 02:36:08 GMT</t>
+        </is>
+      </c>
+      <c r="E245" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxQazA2TUZuTUZwUjRiZ1FpQm9VRFRfN3pJckgxWnM0dktsUDhZcGd6TGl6QkhMemtNU1IyNjJYSFdFTllWYVdNdDc2TXE3ZHE3Q1FIM2Z3bnpBaVpic0E5NUpCQk8zbUJlelE4UllzeUdLNGRCeXBqREJ6bklDM1N5OEY4ZnFjMVlvenEwZXMwMXJCSzVoTlk0TkwwMHB3RjFUVEIxN0FwalBNb3lkYjdyVw?oc=5</t>
+        </is>
+      </c>
+      <c r="F245" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>Protest</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally OR tactics OR targets OR groups)</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>The Met Police spent £12m in just three months to police Palestine Action protests - thecanary.co</t>
+        </is>
+      </c>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t>Wed, 28 Jan 2026 16:52:58 GMT</t>
+        </is>
+      </c>
+      <c r="E246" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMif0FVX3lxTFBxcmdvaHM5RnZOTmdVdUJmRDUtNTRlcVlFVUhUYUhwQUFiR1BldzMwOWNUUm5ReE1XbEgwSmFiV3VKc0VKTXpVeGpuNjdsQ0wzcVZ2ankwb0lXM09YYkFRREZSVi11ejIxQkloWjE2LXptUkNHVXAzNkxyTWEtLXM?oc=5</t>
+        </is>
+      </c>
+      <c r="F246" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>Protest</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally OR tactics OR targets OR groups)</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>Police probe explosive device thrown at Indigenous protest in Australia - Al Jazeera</t>
+        </is>
+      </c>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>Thu, 29 Jan 2026 07:21:43 GMT</t>
+        </is>
+      </c>
+      <c r="E247" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxOcV9sWlZ3Mm9GZW5Nby1mbVpiTE9JOGVJcDUtcjEycHpIblJhNHVWTGdVWGZiUTd6dGM5aXUtbUxYRC1mNW1FTEpXS0FSbnFVSHluclZBdko3UEplM2RlSUNwdlJsdEU2bWhnT01wY3dEQTVIc2dvVHdtT19oeTg0WjY4c1h6Q2N2WDVOZERWS2Raa25mUUY4clBLVGZzZGpRRnJHU01FOWR6T3dNbjZKbTln0gG3AUFVX3lxTE82MkFseGtjUW1HUUowTU9vMmRzNzRfaE5hc1p2QjlaRlpNdmVJQXBJY1hMOHdDLVdtaENJZmg0TGdWOEZublF1OVE1Vl9VTW9zeGlKMjVEVEVaQ1o4OXhjbm1iLW5EbDd5cFJaVmlTbkZ2TWNEMDBwR2FFQUxqWU1hdm9tbkpjcmM4VEc0d3lhdDdtdUNVb0ljT1hlOHpydjhkbElDMXZhcmlicUJKM3AyN19xYU9PSQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F247" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>Protest</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally OR tactics OR targets OR groups)</t>
+        </is>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>Suros Capital raises introducer commission to 3% until the end of March - Bridging &amp; Commercial</t>
+        </is>
+      </c>
+      <c r="D248" t="inlineStr">
+        <is>
+          <t>Wed, 28 Jan 2026 12:28:00 GMT</t>
+        </is>
+      </c>
+      <c r="E248" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiyAFBVV95cUxQMkt0SlNNM2VKRkRaZ2FaMnlpTFFVaG9vbUNvcm9wMmJTQXd3ZWVsZzh6LXl4eTZBcmpyTkhHVVVHaTlNWThuV1Q3SmsxUWQ5cDBfLXA3ZWRYZWROOTVuOGFmVC1YNzJyeFZ0Z3pGYnJIVXVSVzNUTkhvMk9mX1JkaW5lMTM2SzE4Z1lzQTVVR0I3dVIzUzRXNXVhRWxWYWdqQ3ZDTDdIT25hMkRTaUpLRlJRN2llOWhvSVlhRFhuUXBaamJWTWczTQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F248" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>Protest</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally OR tactics OR targets OR groups)</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>Police to oversee asylum seekers march in North Wales with protesters warned not to 'kick off' - dailypost.co.uk</t>
+        </is>
+      </c>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>Wed, 28 Jan 2026 15:24:00 GMT</t>
+        </is>
+      </c>
+      <c r="E249" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxNLUFHbHJsZEdhTEE5ck1aZTF5M2Y2WDNfeXR5YzVIUUpVbHFXWGJYS0ZpS0pNQzNya2lhT2VkNkdKOHVuUUczb2s5VzMwWGJRTlYteHgzV2ZZR3MwWmp0bzJHcE9uOEJMX1BacWtydFFHZlJJeURxNHh0R3hOd3Y2YmNMMUVmb0NrMFZHQ2VkalBxMk9FVlN30gGcAUFVX3lxTE9OWkpCYno2WXNYYnNDSVV3STE5SFBoakswNXB3Rnd5dHloaWtZd0laem5NVHBwMFg4Z0pfSVprMjRuS0F3REdvcFJMOW10cHBfTnpqV2xWMlU1bl9DWFhRU25Ya3dhWVFMbHpMdTVqUTVrRzgyNUVheHB6Q1RNN2pBUm9DVnNucTB3TVZ5Y1RTTlQ2WjNnNEk0ZDRJbg?oc=5</t>
+        </is>
+      </c>
+      <c r="F249" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>Protest</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally OR tactics OR targets OR groups)</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>Eye on Africa - Nigerian police fire tear gas, protester injured in Lagos floating slum protests - France 24</t>
+        </is>
+      </c>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>Wed, 28 Jan 2026 21:23:49 GMT</t>
+        </is>
+      </c>
+      <c r="E250" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxQTkFBV0VVT3M4MGZoRFZPNFJxNGo4aTVKRjllMXBrV3UyUS1uNDRmckFmUW9scVFOemQ2MXFrMk1VN1VueEtyOVNIc2l5cU9za25qdC1qRHVqTzVJdE9xUzdCNl9WRUpILWJGUENIYm14SVV1eTBJYWl2R2JwS0dIZFl0SHNrdnZOY1hEM2phN2lubGFkcnRibGFzSjBqRnlvNU82Nkk3NmgtdGM?oc=5</t>
+        </is>
+      </c>
+      <c r="F250" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>Protest</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally OR tactics OR targets OR groups)</t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>UN human rights rapporteur applies to join legal case against protest laws – as it happened - The Guardian</t>
+        </is>
+      </c>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>Thu, 29 Jan 2026 06:30:35 GMT</t>
+        </is>
+      </c>
+      <c r="E251" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi6wFBVV95cUxQNFBFVFdDNGt6cGFYSUp3TU5HalRaY3R3YXRFdkMwT1d6NC1IWDh6dXdxTGJaemFnQnFONGVOb1c5eW5uV0pmWHlDcmNlTGFIZEhqNVQyenBianJIbklOazFTenpUNVR5X2tMWmNISFNWelNwSFV4aXpXNUl2MHVXYmJ2WmotMHhPdkNDcV9mYTJXcGNQTm5TR19HUnpvSTkzYjVsLUl5NFA2OUlnUWlabE5mLXJsVnQ0UFlUZEdPam0xQVh6VHp4dFRlUnkzcmJWTTJzaDV4VVo4aUM4dndXSno2Vk1XY2l5dE9R?oc=5</t>
+        </is>
+      </c>
+      <c r="F251" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>Protest</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally OR tactics OR targets OR groups)</t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>Eugene protests prompt review of DHS and local police use of force policies - kpic.com</t>
+        </is>
+      </c>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t>Thu, 29 Jan 2026 03:14:21 GMT</t>
+        </is>
+      </c>
+      <c r="E252" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxQd0l5dkt0RnVIdHZtbkZlblJSUGFhNXJLT0p6NWVqa0dfYTlqbkJSZWRzenJQa3J4dHpKUGRTMjFvRkozbzRoZHBtWnRCRTlycmN3eWZfM2xBTkg1MkRZdHhGY3ZjM1FTaDkyY3JpS2ZOWlVfY3JiMXpYNVZteUNnVkZKMXVGZGtXTHhnV2VMOGkzUlVzSzJfMnlMZFlBVU4zSTdKLVV3?oc=5</t>
+        </is>
+      </c>
+      <c r="F252" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>Protest</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally OR tactics OR targets OR groups)</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>Demolitions: Lagos police to charge protest leaders in court - Premium Times Nigeria</t>
+        </is>
+      </c>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t>Thu, 29 Jan 2026 03:40:07 GMT</t>
+        </is>
+      </c>
+      <c r="E253" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxPYUtxa1BHbEw4V3VTeXppbzQ1LWFjV0NNREFHSWVJa1czM2s5VEVtNFlwUDBIZl9UYVE2NU5FQlJJR1RvZFI0dTI3X3c5d05JcVViNHpwcW5CcFFlRW9SR2FLVVJXclBOMDZ1bk9LX1dGaUZaaVFoRDBmQThBQmhIR3VwR0tiQzlzcTRPV3YzVWNEck5HU0JBaGVrRHVwd2NPN0RkSkFrb1NJLXlYMFNubEN1WkFjbEE?oc=5</t>
+        </is>
+      </c>
+      <c r="F253" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>Protest</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally OR tactics OR targets OR groups)</t>
+        </is>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>Why it took nearly 30 minutes for police to evacuate Perth Invasion Day rally - Australian Broadcasting Corporation</t>
+        </is>
+      </c>
+      <c r="D254" t="inlineStr">
+        <is>
+          <t>Thu, 29 Jan 2026 02:56:45 GMT</t>
+        </is>
+      </c>
+      <c r="E254" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxNazN5ek9BVEFYdzdBNjNWa09LNVJTaFVDRFROSXlCRERsVzBqX2x4MDNJRjVHT2wxOWRsM2c0bTMwdkQ1TjNuNkdwaGRqVC1qdGtpb29yNEYwbmU3SDUtYUtRY0pIN1hTbHItVnR5SVhrNFV6V0lOejNBN196aHhkOUdaamtpeGtmTW1CdWhSMmcwcWxDQzV5NksxcDd5MUQ5?oc=5</t>
+        </is>
+      </c>
+      <c r="F254" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>Protest</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally OR tactics OR targets OR groups)</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>Bystander videos have long shaped public opinion of police violence - NPR</t>
+        </is>
+      </c>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>Wed, 28 Jan 2026 10:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="E255" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxPa05KM2gwV0E4bmJpUW81eXZ4VE9xOS12Vm92OTV5d3l1N3ZfaV9MZ2hWQTV6RU9YUDhseGdvNmNhUU8tTkVTMWsyRFVTNUhhYU1QVUNqWVhtSHFRbHFmRzdaTTdVUVFQNUYwSzlzaWVlbnFsWTZPRHFRSi10NUhDR0EzQW4tVFZZU1RYNnF6VUU1eGRsenpLMkpYSWc?oc=5</t>
+        </is>
+      </c>
+      <c r="F255" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+        </is>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>New year, new laws? Data, AI and cybersecurity in 2026 - Fox Williams</t>
+        </is>
+      </c>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t>Wed, 28 Jan 2026 10:31:56 GMT</t>
+        </is>
+      </c>
+      <c r="E256" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMilgFBVV95cUxPR1ZNbXlVS2loVWxUZy1fTm94c2RiaVM1aGcwOWd3UDVRVHRfOFRtbDcza3I2VDVpTWpYQWhrLURYblo1UEtFM2V5blhrY0Jjdkl6Z1JpTWdBZXdDYjVuTl9MSHAyaXRoUDhoUk5PS0ZyM2pubUxEeEZQV3VKR2ZWX2FwYkhEaDd5XzVLUjZMLUtDclVValE?oc=5</t>
+        </is>
+      </c>
+      <c r="F256" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+        </is>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>Tesla cuts car models in shift to robots and AI - BBC</t>
+        </is>
+      </c>
+      <c r="D257" t="inlineStr">
+        <is>
+          <t>Thu, 29 Jan 2026 02:35:07 GMT</t>
+        </is>
+      </c>
+      <c r="E257" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiXEFVX3lxTE5IbGk3VlhfUmJ0LWhHTDVnaUR6cUtfdkdGTXFWTUc4U2J2a2tpeWpTakM2NTZIWW9TS2dVcF9kT1VVVm5IMWVSWmJYV09PNGJDTF9kZ0ZWaFlhSkZ3?oc=5</t>
+        </is>
+      </c>
+      <c r="F257" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+        </is>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>AI in NHS care: what’s the impact, and what do people think? - Healthwatch</t>
+        </is>
+      </c>
+      <c r="D258" t="inlineStr">
+        <is>
+          <t>Thu, 29 Jan 2026 00:09:34 GMT</t>
+        </is>
+      </c>
+      <c r="E258" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxNVHZxUDNiYTZ6eWJtV2pOQ2xjb19kdGNUTVJBUGNVM2FLMVlrVy10VTMzYTZpRHlfX2F2SVFvTkU1bDlZYUtTTEt4cjFQdkNFRFR6THFQN2JjQXFWa3c1TzNWclM5d29mbDBsZS0teVNxUURaRTJYNF9Wb21xOVlqNi04MDdlOEpxZzd3WDZKUWg5U3Q4NkVMeG5Yaw?oc=5</t>
+        </is>
+      </c>
+      <c r="F258" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+        </is>
+      </c>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t>Cybersecurity considerations 2025: Healthcare - KPMG</t>
+        </is>
+      </c>
+      <c r="D259" t="inlineStr">
+        <is>
+          <t>Thu, 29 Jan 2026 01:38:29 GMT</t>
+        </is>
+      </c>
+      <c r="E259" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxQV1dRYmlzZkNsR01Hb2h5NXpPQmZuUEFTOTYtNjlwSFlhVDZLQ29oOTJhZmhMRUxBLVU1eW5wYU55bDk0THAyRXRiX243QkNxeEZIODVoN0hmWEVOaTNrbWo0cHNoTWtpWmYzM0MybEdGMGRsZVJyMkhFRUQ0enNuT2RqSnlyWm8tYk9iSlR2TG5vaTRRSU9rR0pWaG45dHQt?oc=5</t>
+        </is>
+      </c>
+      <c r="F259" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+        </is>
+      </c>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t>Meta wows Wall Street despite spending billions on AI and facing social media addiction trial - The Guardian</t>
+        </is>
+      </c>
+      <c r="D260" t="inlineStr">
+        <is>
+          <t>Thu, 29 Jan 2026 00:10:00 GMT</t>
+        </is>
+      </c>
+      <c r="E260" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMihgFBVV95cUxNUmdoaDMyZU8wMC1jckVCamVURjlmRmtWc251d1FyYVBlZzNoM3hyVkgzTnktVnVYSTBKWWpvYTZjLVN5R3FqQ0h6SXFvNWlCSTZUVlJOWFp3dHVHem0xYXh3R19GSGNOSGxkWk94OHFtcExsLXlzUXduNVZ1dkh5U2pNWDVIdw?oc=5</t>
+        </is>
+      </c>
+      <c r="F260" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+        </is>
+      </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>KONE elevates its automation and AI strategies with Microsoft Power Platform - Microsoft</t>
+        </is>
+      </c>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t>Wed, 28 Jan 2026 19:48:53 GMT</t>
+        </is>
+      </c>
+      <c r="E261" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMidEFVX3lxTE1wTjRXSEc1MFpsandiX05yQ21VUG0tS1pna191d1doRDdFdnVwYkl5YUtHZXRKZENNOTBucjlmY0hkbVA5a3UySVk4SXdGTS0zVFJTY2FsbDFtSXJwVWQyWko4MEZKUzktOFZ6TnByeDNLSC16?oc=5</t>
+        </is>
+      </c>
+      <c r="F261" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+        </is>
+      </c>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t>AI x Dispute Resolution webinar series 2026 - Simmons &amp; Simmons</t>
+        </is>
+      </c>
+      <c r="D262" t="inlineStr">
+        <is>
+          <t>Wed, 28 Jan 2026 17:00:35 GMT</t>
+        </is>
+      </c>
+      <c r="E262" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxQRkdGTzM0NG1vS1lYVmg1Ry1hX0xPdURTQzNUZm5aWnRtVU45WFotT3pMdUhXUWMwbk9jSlVxdTFOOEZJSkNDSERRTi1lQnVIcW1LcTY4b3ZvRkZrUkJMRmk2SWhCd2dkc0hBcDhUazRjcDdwNHVOZVQ4bXJJYXRYWmpUX3RxR2ZOdGhPVHVDclRUVlNvUEw4Vjgzd1VTTGRVWENteXNYSktGRGk1NXYzeQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F262" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+        </is>
+      </c>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t>Nokia Reports Jump In Sales From AI And Cloud Customers - The Wall Street Journal</t>
+        </is>
+      </c>
+      <c r="D263" t="inlineStr">
+        <is>
+          <t>Thu, 29 Jan 2026 06:48:00 GMT</t>
+        </is>
+      </c>
+      <c r="E263" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiqgNBVV95cUxOTXFwbndJaHl1NGlaWFNWc093NmdDRTRLb3h6eUE4VjZaWkFucmpCNkRLMG1JSXk4SlBONmgwcUpBX09XbGU2RlFMVENyRWx6enlMY2lEUWk4Yk9BVFBvWFZnOEFVMkpoeEp2VFdGdlNBaFp6RVRiQW5XaXppblNIZTFXRjgtOExfTXFGbnh3SzRjSVgzZmpOc2EzbzBLSFNtaTQ5ak9DZElMOU1wMTN5Tk1QeHJqZ2xDRDduSmdWYUhxM0pwRnhWLUZQbm0wMnd0RDdrbEVCYTBmZGhVcDRUMzRVTXdVZzdReVplemRIZlZiTU9hbm5ZZmx4Z3Awc29TUGt1YzFRV1ZmYk9PQ3FSdkVPTDE4ajFxU0laZHNaWml4UVBuRG1JYi1RZTQxTGhMZExCNHZpTEZrR0ZIVFBvLW1ESkJmNlZwX2JmSWNySVAtYjZ5bmFhMVJocVlpMFlfTmpYVHpyNFpNNDNZajdEejgxekV0MDQtRi10UW8zWGw4dlF5cWpXQUVHYXFISU56ZGZQZU1Dc3JoTEpkTzJra3NzVkQ1Qm1McUE?oc=5</t>
+        </is>
+      </c>
+      <c r="F263" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+        </is>
+      </c>
+      <c r="C264" t="inlineStr">
+        <is>
+          <t>AI for beginners — what you really need to know to keep up - The Times</t>
+        </is>
+      </c>
+      <c r="D264" t="inlineStr">
+        <is>
+          <t>Wed, 28 Jan 2026 23:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="E264" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMizwNBVV95cUxPamtHVjlKUlhaSTQ5NjlMZ2Y5RGEwQVkyb3RYdGV5RmRjbVR3RkdIZU9EdFZ1ZFBOeXZwclc3cVNReEFXQlFtQXcxNDlkNzJHSGNESXFiTXhMWWF3T1A0WnNBZ0dnbDRxcVY2bV8xVnZFcmlsT0kxb0FJUm1QY2s5OGV4WVpDWnpSSzNMWF8wYmRlUzFYRTMtWHNzajFCenZScVVEcXRhSnJtYjFNUTdCYm5pN0d0cE1TVTFsRjllSzM5cDN3bkhCcGctUGFHMGFkZWZNaU1UMnYxZnBGR2ZRLWcyM3lXY3ZEREtnNHFDcUVMSUhJbzZLcmxFNVZSMEtyeWl0TndMQmJ6WFZTLWlKaWJWeHNxeUE0QnRGRWhlM2oxQi16bjhtNlVrQjBFbmhZWlR3OXZiQThmb1B5SjNoY0tidkdudmQ5QTFFeTFJajNaV19IWm5fR0VhSWp0VXRrZHlFUjRpdnJ0c001bXgyd0hROU1YMlNfdkt5a0pJV0YwWG5Xc2lFYTNkdGh0azhJNUd1RWxGQldVVTJqOWoxb3kyUTZTZGRkM0p3Y3UyTkxyRmRkb1ZCRzdnX25xcVp2UEpBcUh5VzdPRlFGenJJ?oc=5</t>
+        </is>
+      </c>
+      <c r="F264" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+        </is>
+      </c>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t>Liz Kendall’s speech at Bloomberg - GOV.UK</t>
+        </is>
+      </c>
+      <c r="D265" t="inlineStr">
+        <is>
+          <t>Wed, 28 Jan 2026 15:33:11 GMT</t>
+        </is>
+      </c>
+      <c r="E265" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMie0FVX3lxTFBXdmxuQ2JKTzJEb3lKVVAzWFdETVRacHpBdWwyZ19uQndwU2tuRGVzZmVJTXBxRWk3MlRGZVZFUHd5ZGdGNFoyRmQxc0NOdjNEeVc4MU1BRjF0Q0RXdmhkNWJLU25YQTltMGFSMi1JeGZabzlPUGQwTzIxVQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F265" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+        </is>
+      </c>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t>IonQ Acquires Seed Innovations to Scale AI-Driven Quantum Software - IonQ Quantum Computing</t>
+        </is>
+      </c>
+      <c r="D266" t="inlineStr">
+        <is>
+          <t>Wed, 28 Jan 2026 17:03:14 GMT</t>
+        </is>
+      </c>
+      <c r="E266" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxPd3NlbVZGeWdXdUhvcFc4czJZeGg3Z1Q0SWtoSTQzRzRuNHpGRF9MS2luNWI5VmZYeWJXUGhxR3ZBOVFrOUtVbzRYeXpvOUtXOTZhYlp4TWFHM1JTS2MtMWlsS2NWMnBxbjFvYzlsVVFvdFA0ZUEzdVVaeU5EOVBENE85RTRqM0NhaHFfNnhPRmI4eC1FSl9KTFN5Wl9VVlh2SjRuYQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F266" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+        </is>
+      </c>
+      <c r="C267" t="inlineStr">
+        <is>
+          <t>Amazon axes 16,000 jobs as it pushes AI and efficiency - Reuters</t>
+        </is>
+      </c>
+      <c r="D267" t="inlineStr">
+        <is>
+          <t>Wed, 28 Jan 2026 18:17:10 GMT</t>
+        </is>
+      </c>
+      <c r="E267" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxQYzNEb1ZIQjc2dUkxU1VwZFlLNG5TVEROWmxORFU5M0Q0RTNieUc0aU9JZUhsUEtnTXdnTW1mZWlhUjlVaXJPdEVPcEE5X3FaeTJNVzYwakx4N1hlZ2hXN0Zwc1NDaE9sV01HbDZGNXBVYXBxQnh6RGRTUkY5N3pyaFV1YllsanllY3ktRU05YW9vUG9ad05teTROYUFmR3JjRFNWVEh2RUtlUQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F267" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+        </is>
+      </c>
+      <c r="C268" t="inlineStr">
+        <is>
+          <t>International Publishers and Booksellers Discuss "Artificial Intelligence and Publishing Intelligence" - Publishing Perspectives</t>
+        </is>
+      </c>
+      <c r="D268" t="inlineStr">
+        <is>
+          <t>Wed, 28 Jan 2026 14:53:29 GMT</t>
+        </is>
+      </c>
+      <c r="E268" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi3AFBVV95cUxPSUtXTkd3d1dNc0NYc2hHNllScXNnRVRZTEZYWDFpWW1uQ1lXeEUwVDF0bnVLSXBHSXYxNjE1RnRadzlnNGRIV2pNMUZZVl9GRUdOcHFpQl90V3NxYnV5Ry1yZndDSV8yU0lwVTBSRFhwMlZrSm1TNVkwdzVQYXJXWFVSRVBiUWZSZWluVDFMYVZkeWtXRkJacUoyc1p2M0o1b21KX3JqQ05NbmVjZ0U2d0Q2UUVJZHlhSWw2NFd0YTVIVjVtbW5fWXpLOGZ0N2VOZU45NkF2SlZwUEFt?oc=5</t>
+        </is>
+      </c>
+      <c r="F268" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+        </is>
+      </c>
+      <c r="C269" t="inlineStr">
+        <is>
+          <t>What can we expect from Meta's Q4 2025 results? Advertising, AI, and the price of aggressive growth - XTB.com</t>
+        </is>
+      </c>
+      <c r="D269" t="inlineStr">
+        <is>
+          <t>Wed, 28 Jan 2026 16:38:11 GMT</t>
+        </is>
+      </c>
+      <c r="E269" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi0AFBVV95cUxNRXFKR2VTQUtSdWtHRDN0RG5vbDdscmpzdmJ3RjZvYWdxRUN2dFh1ZERaZUJGX3U0NjFPc3VCVXF0aVVtcUpDckgxbkV2d3l0dlpXVXdXdVBNSk14azVKRHRqR3Ffd2k0TW9VX0hvRWtJV0gyMVhSQWdRcTBzMVpzNzlNc205VGt3bnJWMHRDMExwMGs0czh3S3pnUnFQVVgzX2xNbDZGZEpuWU9rQm41OFF6dDlXd2tKc2xIMWk3ZlZ5OTdpdHpacHRGOG1EanVn?oc=5</t>
+        </is>
+      </c>
+      <c r="F269" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+        </is>
+      </c>
+      <c r="C270" t="inlineStr">
+        <is>
+          <t>AI and Tokenized Finance Are Reshaping the Foundations of Financial Trust - ASEAN+3 Macroeconomic Research Office</t>
+        </is>
+      </c>
+      <c r="D270" t="inlineStr">
+        <is>
+          <t>Thu, 29 Jan 2026 02:39:14 GMT</t>
+        </is>
+      </c>
+      <c r="E270" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxQekJQMzZFSmFQaUtuSVM2YVdfa1hiZWtuLTFHcURpZnNnN25vVTl5MHlVUHBWSVpTMnRDZHNtSHhQVkp4R2ZCUU9MSG5tUFZmVVkxbEZCZ0EzaVV5YkEzenFJdmZRV0FFVm1jOUlOX0t1dTQyb2cwcFluemVPU1ZOVjV4elBORU9hN0dzYUdaLTBvQ2x5bkRnU2ctRQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F270" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+        </is>
+      </c>
+      <c r="C271" t="inlineStr">
+        <is>
+          <t>AI use by individuals surges across the OECD as adoption by firms continues to expand - OECD</t>
+        </is>
+      </c>
+      <c r="D271" t="inlineStr">
+        <is>
+          <t>Wed, 28 Jan 2026 15:40:27 GMT</t>
+        </is>
+      </c>
+      <c r="E271" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi4AFBVV95cUxPWXdPSDIzaWVUQmhoZlRaWjlnbllJSkljVWRLMVhFNmpxYVgzZERmN2JWMkZhamhnQUk1SmlqY2dSMXRUVDQ1QXgtMHc1NmVrX2JoVElhLWd0Uk1lbUZqejhGX1d0TkN1YjZ0OHMwQTFEZDhzcWZtbklueXQ4cHBUa1VkMVhlclhFU0VzbEtNQXlNUGc2OU42RDFyN3BmNWplNUFzWXNvZGM5aHpNbFV3dVdnczQtTmVvMFR0RTY4TDlrUzJtUGVvcFdweXQyVlJTZFBFLTBCdUVOdEtpenQ0eQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F271" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+        </is>
+      </c>
+      <c r="C272" t="inlineStr">
+        <is>
+          <t>Expedia's Ariane Gorin on AI visibility, traveler experience and activities growth - PhocusWire</t>
+        </is>
+      </c>
+      <c r="D272" t="inlineStr">
+        <is>
+          <t>Thu, 29 Jan 2026 06:02:25 GMT</t>
+        </is>
+      </c>
+      <c r="E272" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMihgFBVV95cUxNVDZYWklHTnVuZnRqVFNJekprQXNkeVo3VjFRQ3hyZDZGNzRYSm5tSE9rSTJrYXBmQlF2RU9ZV0pwOEUwb2dtWl9rcmhfNEV3OUVLOGxJc1F6RFdvYVkwZUJkbWM3Q2pmNVlIR3RpRzBjVHFYOXNTY3Y3S2M3LWNmRjhLN3c3dw?oc=5</t>
+        </is>
+      </c>
+      <c r="F272" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+        </is>
+      </c>
+      <c r="C273" t="inlineStr">
+        <is>
+          <t>AI drives 70% surge in weekly cyber attacks in 2025 - SecurityBrief Australia</t>
+        </is>
+      </c>
+      <c r="D273" t="inlineStr">
+        <is>
+          <t>Wed, 28 Jan 2026 23:27:00 GMT</t>
+        </is>
+      </c>
+      <c r="E273" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMijgFBVV95cUxNcnFmRVhRby13UnVSZkdJYnNEYVlNNEhnX1FhSkpNUVZ2bXNSR3FXbWRkbUVvLUFpVWFaNVZhblRqU09xUy1pMjNDQVVKaTBlcEtpbzFMUHMzdFJ0YzJnQ3FvZ0JORUhrYWstajdfSUdDNmZpdEpvaV9ITVF6dWVpODFVWndTZTc2MF9qZHR3?oc=5</t>
+        </is>
+      </c>
+      <c r="F273" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+        </is>
+      </c>
+      <c r="C274" t="inlineStr">
+        <is>
+          <t>AI and the Liberal Arts - wellesley.edu</t>
+        </is>
+      </c>
+      <c r="D274" t="inlineStr">
+        <is>
+          <t>Wed, 28 Jan 2026 21:28:25 GMT</t>
+        </is>
+      </c>
+      <c r="E274" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMia0FVX3lxTE1VSEU5VlJ0UWp0WC1xQWI4NUl6TDVreVBJeGN6dnhROTJsMnNPdUcxb216a3BTakFnUDd4ZmJ0bG43V0p2ek1PRGxvd2RzYlZRcUhMZkRGcmlBeVBMMTVOU3VOcXRWTjh6ZERR?oc=5</t>
+        </is>
+      </c>
+      <c r="F274" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+        </is>
+      </c>
+      <c r="C275" t="inlineStr">
+        <is>
+          <t>Lanarkshire chosen for new UK AI growth zone - UK Defence Journal</t>
+        </is>
+      </c>
+      <c r="D275" t="inlineStr">
+        <is>
+          <t>Thu, 29 Jan 2026 00:01:19 GMT</t>
+        </is>
+      </c>
+      <c r="E275" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMigwFBVV95cUxPWmxQUFV5VlR4Mjh4S3AxUEtraDZkOTBtUkczUk9qQVdlQ1o3M1UwWkNJTFYzdjF0N2tabHVLdEdobWRUWFRxYURta3NJc0FrWG5DaVhxdERpVC0yRmc0RnhXcG9BZnR0cGlEU2lfamlRUXFyS25tUG5zaVJ2UGsweGZpUQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F275" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+        </is>
+      </c>
+      <c r="C276" t="inlineStr">
+        <is>
+          <t>Afternoon Update: protests planned for Isaac Herzog’s visit; Tesla pivots to robotics; and Paul Dano breaks silence on Tarantino - The Guardian</t>
+        </is>
+      </c>
+      <c r="D276" t="inlineStr">
+        <is>
+          <t>Thu, 29 Jan 2026 05:46:00 GMT</t>
+        </is>
+      </c>
+      <c r="E276" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxPY3lPVjA1bkxBMEJaUUVwZHNwczkwQ3doVGFERzNZa2FfRWI2Z1p2S1NvREpGSGFpNzcyOF9ma3Nic0JRbFc4M01FWUVGWWVGWm0yWjdCdFVrYm9JaDZLWGNvWjBwM08tVjlFTG9fVkJQbTdoSmFZel9hZGxVamg0Z2xFTHliSC1kN2gtQWphaGs?oc=5</t>
+        </is>
+      </c>
+      <c r="F276" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
           <t>Fraud_Scam</t>
         </is>
       </c>
-      <c r="B203" t="inlineStr">
+      <c r="B277" t="inlineStr">
         <is>
           <t>(fraud OR scam OR phishing OR smishing OR vishing OR "identity theft" OR impersonation OR spoofing OR "account takeover" OR "payment fraud" OR "invoice fraud" OR "wire fraud" OR "business email compromise" OR BEC OR "fake invoice" OR "supplier fraud" OR "procurement fraud" OR "social engineering" OR extortion OR blackmail)AND (company OR business OR enterprise OR customer OR client OR employee OR bank OR financial OR payment OR transaction)</t>
         </is>
       </c>
-      <c r="C203" t="inlineStr">
-        <is>
-          <t>On Your Side: Marshfield, Mo. business owner could have lost $1,000 in Venmo scam - ky3.com</t>
-        </is>
-      </c>
-      <c r="D203" t="inlineStr">
-        <is>
-          <t>Tue, 27 Jan 2026 23:59:00 GMT</t>
-        </is>
-      </c>
-      <c r="E203" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxNd0NSSkJ3cTdrTmZFYUo0LXhWdVQ0ajJMekRUdkNHYWdKLXBqWkNyQ1BZV1BRdms5bnlVRnBwcDYyajdwUTJkSmozY1VBYjJVX3E3bXN1MXgzRElnMHNCYThSSWZQd0RYc05QSDBPZGdVT291U215c0c3bF9Pd1lpS0VPc01KeTR6cE80SWtHeEVFM09vemxPNWlndmtCaU94dEJSWNIBuAFBVV95cUxOckIxSE9SNjlYdXQzZnVfZXJiVEZpZ2lYQVlEc2JHME1FYUx3V2tCQUk3Yjc4MDU5bHdZMnVWQld1a19nYXp3ZWhGWmZKellMdmRKcWZVd2Y0Qlp4d1MtZlI3aXU0bi0zbExwbElfa1Jqb25vTGs1MTVna1cxZGNLMXZhdERVRmExQzFUTHR0YmNRQ3VDZGoxclhiUVdtelVpRG02Y21LWnJBQUNLX2FEeHFCSnhVWFpW?oc=5</t>
-        </is>
-      </c>
-      <c r="F203" t="n">
+      <c r="C277" t="inlineStr">
+        <is>
+          <t>Email fraud using AI dramatically accelerates cyberattacks on companies - igor´sLAB</t>
+        </is>
+      </c>
+      <c r="D277" t="inlineStr">
+        <is>
+          <t>Thu, 29 Jan 2026 05:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="E277" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxPa255NTBXWWE1cEdKelp4aVh3akF6VmVLNXFram5SZXkxdEtlcHFCS3Yxc05yMUpncHllQWpOb2NiSWdZQ2ZTd1hmeEZXSk00ZDNIOFdOQU16VlF1Y0ZXRG96T21hY3RxRjI4aFZmaWZYNFJWcUtRZk1rZ0k2NlRrZEhpMlViZjJiWHBMRUFUR2c1dTRvUzl3Q0JHV2ZnR00?oc=5</t>
+        </is>
+      </c>
+      <c r="F277" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>Fraud_Scam</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>(fraud OR scam OR phishing OR smishing OR vishing OR "identity theft" OR impersonation OR spoofing OR "account takeover" OR "payment fraud" OR "invoice fraud" OR "wire fraud" OR "business email compromise" OR BEC OR "fake invoice" OR "supplier fraud" OR "procurement fraud" OR "social engineering" OR extortion OR blackmail)AND (company OR business OR enterprise OR customer OR client OR employee OR bank OR financial OR payment OR transaction)</t>
+        </is>
+      </c>
+      <c r="C278" t="inlineStr">
+        <is>
+          <t>Threat Actors Leverage Real Enterprise Email Threads to Deliver Phishing Links - CybersecurityNews</t>
+        </is>
+      </c>
+      <c r="D278" t="inlineStr">
+        <is>
+          <t>Wed, 28 Jan 2026 16:37:11 GMT</t>
+        </is>
+      </c>
+      <c r="E278" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMic0FVX3lxTE11RXltbC1yQnlhbDZ6R1FFU0tnRTJrZXNNTURvZGJCNDlhNmNTclBRM2JrREppdzR2UVd2WFAyNnh3a0ZGR3A3U0h4anVTYy1DdEw4VjVlZDZHM201RHZKRWNhZndOV0VnRkVMU0FkaUVTdm_SAXhBVV95cUxPSEpKWTVfelBjeVJMcDdkNHdSMFZ1UFhqT1pST3VYNEJJWlhLOHFQSVQ5UEFyeFBGcmpRMHNLci1OQzl2NTRmSnM5SE0xZG5ZYnEzZHQzWTg1dmhBUVA2cWZMSGxBY2Z1VmVfcnF1NDh2MzI4bzZjODg?oc=5</t>
+        </is>
+      </c>
+      <c r="F278" t="n">
         <v>7</v>
       </c>
     </row>

--- a/data/topic_feeds.xlsx
+++ b/data/topic_feeds.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F278"/>
+  <dimension ref="A1:F361"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8758,6 +8758,2496 @@
         <v>7</v>
       </c>
     </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>Current_Affairs</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>(geopolitics OR migration OR economy OR conflict OR legislation OR terrorism OR disinformation OR misinformation OR government OR policy OR regulation) AND (briefing OR analysis OR update OR report)</t>
+        </is>
+      </c>
+      <c r="C279" t="inlineStr">
+        <is>
+          <t>First Annual Report published by the Immigration Advice Authority - GOV.UK</t>
+        </is>
+      </c>
+      <c r="D279" t="inlineStr">
+        <is>
+          <t>Thu, 29 Jan 2026 13:17:12 GMT</t>
+        </is>
+      </c>
+      <c r="E279" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxNd2daM1B1NkM0bzAwSE5wWWFSRzRiYWtyQjZ6d0NoRlpaVnIzR0tNcDctQXRqMHgycmRVTjZCY0QzcVhxS2hvVHlQSmQ0eks5Tjl4NGx3aGpZOENBR1hTV0JpLVNXejloYUMwMWpENDhMemdqc0hRMS05SlFVNG15ZXRQdHhzRGx6TWV1Ui0xTU5TaXFUQTZobVdBaG02bk5UaUE?oc=5</t>
+        </is>
+      </c>
+      <c r="F279" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>Current_Affairs</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>(geopolitics OR migration OR economy OR conflict OR legislation OR terrorism OR disinformation OR misinformation OR government OR policy OR regulation) AND (briefing OR analysis OR update OR report)</t>
+        </is>
+      </c>
+      <c r="C280" t="inlineStr">
+        <is>
+          <t>Europe’s health and competitiveness suffering due to slow pollution laws implementation, says new report - European Commission</t>
+        </is>
+      </c>
+      <c r="D280" t="inlineStr">
+        <is>
+          <t>Thu, 29 Jan 2026 09:12:48 GMT</t>
+        </is>
+      </c>
+      <c r="E280" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxQYzBBYUNldDlRdEsxcHhqV3BGRE1LNDdkaUtlNEpjc19VY0w0U0ZvVTkyQzNyTjkxd1ZmSFNBX1RjSndNN3JTSDlBa1Jac0dOSE9Fb3FsTmxJZWRmMFJmcnFTNm80Q18xcEp4M1U0dGItY0FwcFh0bTc0UGRlUllIQk9oZVllVHZodnpsUVRzdVA0OGlOZWF0R1JIQWZYTWNIOEc1Wk1idHdMQXpGZF9Kajd3?oc=5</t>
+        </is>
+      </c>
+      <c r="F280" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>Current_Affairs</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>(geopolitics OR migration OR economy OR conflict OR legislation OR terrorism OR disinformation OR misinformation OR government OR policy OR regulation) AND (briefing OR analysis OR update OR report)</t>
+        </is>
+      </c>
+      <c r="C281" t="inlineStr">
+        <is>
+          <t>Cost of clinical negligence to be revealed in government report - Dentistry UK</t>
+        </is>
+      </c>
+      <c r="D281" t="inlineStr">
+        <is>
+          <t>Fri, 30 Jan 2026 00:09:14 GMT</t>
+        </is>
+      </c>
+      <c r="E281" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxPYjVwaTN1UkZsRS1raGh3cVF5b1ZSRy1sYnZFM3ZxVDgzYmFUckRQYkpTMlhEbFZmM3c5N0xvbUtETHlIVFZDYVN1M3QtZjBYc00tQmZjbHd1eVRFRFJGZGIybGhzM0x3Z1R3ZUxsX05Mc1NnTHJqT3YydWszZGZQdzg5UkVIVEZvRmpOMDhQSE9QdXEzSzlrYTlIYUpWZ3Iz?oc=5</t>
+        </is>
+      </c>
+      <c r="F281" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>Current_Affairs</t>
+        </is>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>(geopolitics OR migration OR economy OR conflict OR legislation OR terrorism OR disinformation OR misinformation OR government OR policy OR regulation) AND (briefing OR analysis OR update OR report)</t>
+        </is>
+      </c>
+      <c r="C282" t="inlineStr">
+        <is>
+          <t>AI report card update! - Lewis Silkin LLP</t>
+        </is>
+      </c>
+      <c r="D282" t="inlineStr">
+        <is>
+          <t>Thu, 29 Jan 2026 13:24:53 GMT</t>
+        </is>
+      </c>
+      <c r="E282" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMigwFBVV95cUxPcmhjYXpPRXYzREZaRjF0WE8xdEdDREZTdDdVUUxJYUd6SVN6OU1qanI3dHEtb0VZekpxTHhSdTdNWTNGSmFBZ1dGOG1rbEgwZ093aGk2Q1BmNTFqeW1hNlBrVVZEYVk3d29oOS1fdWFMd2tJZjlxMy1pUUxUcEZJMDhRQQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F282" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>Current_Affairs</t>
+        </is>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>(geopolitics OR migration OR economy OR conflict OR legislation OR terrorism OR disinformation OR misinformation OR government OR policy OR regulation) AND (briefing OR analysis OR update OR report)</t>
+        </is>
+      </c>
+      <c r="C283" t="inlineStr">
+        <is>
+          <t>Collins Demands Government Update on Follow-Up to Quota Loss - The Fishing Daily</t>
+        </is>
+      </c>
+      <c r="D283" t="inlineStr">
+        <is>
+          <t>Thu, 29 Jan 2026 13:32:25 GMT</t>
+        </is>
+      </c>
+      <c r="E283" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxQbC13bTd6ZXJCWlRXRXIzYlJCb0VJaUMxNHU0SHQ2by1neXV6Q2ZpUzBQNVFGOENzV0FqcEwtWHh3b3c1V1lFMVhGYkdGZDBiNXFfTC1FclNDdUFnYUZSanN4RERjN21faFBXS3hCNXlTV0dGdE9NRE4zNVUzSmQ1OGczYkFtZWlNc0pUYTZNVTllREdHT3dUSzZ2dTRtdy1tbktDTTZ2U21rZTBiQ1RScHdENlhzM3M1?oc=5</t>
+        </is>
+      </c>
+      <c r="F283" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>Current_Affairs</t>
+        </is>
+      </c>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>(geopolitics OR migration OR economy OR conflict OR legislation OR terrorism OR disinformation OR misinformation OR government OR policy OR regulation) AND (briefing OR analysis OR update OR report)</t>
+        </is>
+      </c>
+      <c r="C284" t="inlineStr">
+        <is>
+          <t>Government report highlights artificial intelligence gains in Kazakhstan - eurasianet.org</t>
+        </is>
+      </c>
+      <c r="D284" t="inlineStr">
+        <is>
+          <t>Thu, 29 Jan 2026 16:30:37 GMT</t>
+        </is>
+      </c>
+      <c r="E284" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxOOGdaTjIxaHlzWDdjNXA3VnhTbzJIMkgyd3BMLUdNTk8yYjQ1eHp5Tkx5dDJmOWlUY0ludHpuTk1IWDhXdDdjMDVLNURfU0o4QzVHbWpJQ3BVenl2eWhhdmQ3WVpYYVBwYldLMktGSktmOS1QTEdHeWZhenpxcTc2aHNaRWRUTjM0bzdWby1HLWZIUzhZbjRmTkt5aw?oc=5</t>
+        </is>
+      </c>
+      <c r="F284" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>Current_Affairs</t>
+        </is>
+      </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>(geopolitics OR migration OR economy OR conflict OR legislation OR terrorism OR disinformation OR misinformation OR government OR policy OR regulation) AND (briefing OR analysis OR update OR report)</t>
+        </is>
+      </c>
+      <c r="C285" t="inlineStr">
+        <is>
+          <t>CEO Innovation Policy Update 01.29.26 - massbio.org</t>
+        </is>
+      </c>
+      <c r="D285" t="inlineStr">
+        <is>
+          <t>Thu, 29 Jan 2026 21:26:45 GMT</t>
+        </is>
+      </c>
+      <c r="E285" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMihgFBVV95cUxOdzdQZ095T0VOb09PcVQ0WTVITlFVWTVwMklpelZfaDdUdzFiVjQ4TmRRanoyZ1lGc1ZLSXlpUjAyZGJBVU1uZkpSNzJuZm1NOVpEOWdWWVFaaVM4TDVuNU93NHpVdkstTkpiWURTVVpLWnlOLXJWT1JfVlNPNFB2TWJSUzRxZw?oc=5</t>
+        </is>
+      </c>
+      <c r="F285" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>Current_Affairs</t>
+        </is>
+      </c>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>(geopolitics OR migration OR economy OR conflict OR legislation OR terrorism OR disinformation OR misinformation OR government OR policy OR regulation) AND (briefing OR analysis OR update OR report)</t>
+        </is>
+      </c>
+      <c r="C286" t="inlineStr">
+        <is>
+          <t>Joint Committee on Housing, Local Government and Heritage publishes Report on PLS of General Scheme of the Apartment and Duplex Defects Remediation Bill 2024 - Houses of the Oireachtas</t>
+        </is>
+      </c>
+      <c r="D286" t="inlineStr">
+        <is>
+          <t>Thu, 29 Jan 2026 12:52:58 GMT</t>
+        </is>
+      </c>
+      <c r="E286" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMixgJBVV95cUxNdUNrOWhTbUlJOHkyOGpVc1FOVmZreXZ0NnA0Q3A0bG9iUXVQMThLX0ZGcl82ZWsyUlNpdEJsamRpNGRETEdQd2Z4ZUpwckExaWVWRzNQcEJHX09vc29ISl93NFg5R1FrcG53eDNVWE1JWTItV0pvLTYyekJJbGE3OERtWUhabGFlSWJ4ekM5T3Z2bmIzN2VNc1pxU01PZjFwaV9lN20xdXlJSll6NXQxdWsxdUQ2OGQtSnRiTjVLNzN6bk5DYVRybERicnY4YWJPZ0hxNERfcHdpT0NpWF95aGRHWnJXSEJBS0xwN2h1T0pOUk1UV3pTczJXdFlOQVZPOTMtR0lwcTFwNFpMeXgxZUFIc2JCNkFRbEYzR3MwUGRHQk9qV2dNcWJueXY5LXZ0YVViTGp5UkUySVJOOElqbHhVd0w5dw?oc=5</t>
+        </is>
+      </c>
+      <c r="F286" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>Current_Affairs</t>
+        </is>
+      </c>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>(geopolitics OR migration OR economy OR conflict OR legislation OR terrorism OR disinformation OR misinformation OR government OR policy OR regulation) AND (briefing OR analysis OR update OR report)</t>
+        </is>
+      </c>
+      <c r="C287" t="inlineStr">
+        <is>
+          <t>Six Senators Accuse Deputy Attorney General of “Glaring” Crypto Conflict, Cite ProPublica Investigation - ProPublica</t>
+        </is>
+      </c>
+      <c r="D287" t="inlineStr">
+        <is>
+          <t>Thu, 29 Jan 2026 21:30:00 GMT</t>
+        </is>
+      </c>
+      <c r="E287" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMihAFBVV95cUxQemppblFtQ0VkUXpta2VqQWV0azdKT2tvV2o2VllsMDRuMjdtaEU2SnRISW9DdE9hck5fRnBkMTE4TTdLMmJCRllqWEdwVm5hLXlvdy1QSVF6bXpKeV9mWGRVYW0zLXdjcC1wWHh1bkFPM0dzNEtEUjZsaTdXU3ZIRUdTWFo?oc=5</t>
+        </is>
+      </c>
+      <c r="F287" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>Current_Affairs</t>
+        </is>
+      </c>
+      <c r="B288" t="inlineStr">
+        <is>
+          <t>(geopolitics OR migration OR economy OR conflict OR legislation OR terrorism OR disinformation OR misinformation OR government OR policy OR regulation) AND (briefing OR analysis OR update OR report)</t>
+        </is>
+      </c>
+      <c r="C288" t="inlineStr">
+        <is>
+          <t>Memphis Grizzlies Announce Ticket Policy Update for January 28 Game - NBA</t>
+        </is>
+      </c>
+      <c r="D288" t="inlineStr">
+        <is>
+          <t>Thu, 29 Jan 2026 17:32:52 GMT</t>
+        </is>
+      </c>
+      <c r="E288" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxPN3UyUUx1RFZwRE9KWW5zbjZvY3hqRmpPODZpRGJ6Z2ZnRm56THRtVmdncl9hUnk5QUtRaUtRZy14MkJUbzFzb0YtaGQ1M0ZWZU9NdWh0QkR2THhILUwwRWhZb1plbjE3c0xzR2s5WTFaQWFnWjdtWnltWlA4bFFEc1NUbjdFUUdMcXhmTV9tLWZXR3J2RTNHV2J3?oc=5</t>
+        </is>
+      </c>
+      <c r="F288" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>Current_Affairs</t>
+        </is>
+      </c>
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>(geopolitics OR migration OR economy OR conflict OR legislation OR terrorism OR disinformation OR misinformation OR government OR policy OR regulation) AND (briefing OR analysis OR update OR report)</t>
+        </is>
+      </c>
+      <c r="C289" t="inlineStr">
+        <is>
+          <t>The Africa Creator Economy Report 2.0 is live - readcommunique.com</t>
+        </is>
+      </c>
+      <c r="D289" t="inlineStr">
+        <is>
+          <t>Thu, 29 Jan 2026 11:02:03 GMT</t>
+        </is>
+      </c>
+      <c r="E289" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMidkFVX3lxTE5TTk1rYzR2Y2E1V2ZlV0R5VVgxR09zV2dCSGJxQzFFX2JWVTV4UEQ1Q2tMX3ltREdFYzVtcXhZT3pYdzkyajBYcnpyd1dDVjdSak5rTnA4VklEOXhacDZaX2NrbURENWc3c05DOU1qRFU1QUVsY1E?oc=5</t>
+        </is>
+      </c>
+      <c r="F289" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>Supply_Chain</t>
+        </is>
+      </c>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+        </is>
+      </c>
+      <c r="C290" t="inlineStr">
+        <is>
+          <t>Trump threatens tariffs on Canada planes and nations selling oil to Cuba - BBC</t>
+        </is>
+      </c>
+      <c r="D290" t="inlineStr">
+        <is>
+          <t>Fri, 30 Jan 2026 06:12:07 GMT</t>
+        </is>
+      </c>
+      <c r="E290" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTFB1WkVQc0puSWViS1UwYU43WVk1Wi1fcXZVa3hldVc5NE9kV1FZSjdjc0RfUUlieTZnVmJqWGxfcV8xR0pmWHU1dHR4UVRUV0hObkIxSkJQejIzUQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F290" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>Supply_Chain</t>
+        </is>
+      </c>
+      <c r="B291" t="inlineStr">
+        <is>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+        </is>
+      </c>
+      <c r="C291" t="inlineStr">
+        <is>
+          <t>Prime Minister secures Scotch whisky tariff cut in China worth £250 million - GOV.UK</t>
+        </is>
+      </c>
+      <c r="D291" t="inlineStr">
+        <is>
+          <t>Thu, 29 Jan 2026 18:42:43 GMT</t>
+        </is>
+      </c>
+      <c r="E291" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxPWWkwSVRjMzJ4cGpFd3Q4cUNnaXMtcVFHZ0dXeW16SlhfSW1vakhmbXltVDJNT3N6YWZkVEltX05vZGpKRDlhZWU5Z1lDelo1WHV3clU2SHJ0M3VQZlRFV3lEbUMtYkROUzVheFVLR1NBOFp6djg1WG94UW9rc2R3RE9USnZYMnA1TC12WXBxT3FJTTN0QmVLYzBCRV9nQmkyWTZTMXNFY1JNUW5jQ1E?oc=5</t>
+        </is>
+      </c>
+      <c r="F291" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>Supply_Chain</t>
+        </is>
+      </c>
+      <c r="B292" t="inlineStr">
+        <is>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+        </is>
+      </c>
+      <c r="C292" t="inlineStr">
+        <is>
+          <t>Iran: Council adopts new sanctions over serious human rights violations and Iran’s continued support to Russia’s war of aggression against Ukraine - consilium.europa.eu</t>
+        </is>
+      </c>
+      <c r="D292" t="inlineStr">
+        <is>
+          <t>Thu, 29 Jan 2026 13:47:25 GMT</t>
+        </is>
+      </c>
+      <c r="E292" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiuAJBVV95cUxNUlJDN05Ga0tES3FpZnI0eXkzZlUwTTMyRXNkbDJ6TXVzeEQyNGtlWWNHSWo3RktDajF3cEZHengxVjdUcmg5Z0VhTm1QcWM3aTZIcGFma2lNQVdHRnRsZy1FQmdlYWhVLVZoOG1MeVZ4Y0Z2WXpSY2hoX3RZc1JyYmRuWWV2OHhNRjFJdVhxWDBlT29TX3kteWdnZklad2ttTFpsYVdQa2FpRkFCV29VTDlLcnZnQ1piZXZjVnVFdU5UcWRPQ3MyamVVNXR5T3hmTW05RmdjWWNSd1NndFBfRDIzQ2lQdWhJamxNYjVvYVdJZmdVTnZRSUdHVkw5ZGhBTWV2MGpKVmhtdVQ0UW9iMk5MS0E0enNOR2NxakdKckdtOXFJWDVnUVNVMzlZQVlHVjc5NjBGdlQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F292" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>Supply_Chain</t>
+        </is>
+      </c>
+      <c r="B293" t="inlineStr">
+        <is>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+        </is>
+      </c>
+      <c r="C293" t="inlineStr">
+        <is>
+          <t>Panama court kicks Hong Kong’s CK Hutchison out of canal ports - Financial Times</t>
+        </is>
+      </c>
+      <c r="D293" t="inlineStr">
+        <is>
+          <t>Fri, 30 Jan 2026 05:03:45 GMT</t>
+        </is>
+      </c>
+      <c r="E293" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMicEFVX3lxTFB6RGZwSW84bWh1Nm05RUI2OFh0c2VHeEtYQU5LamFIaV84dHY0V0tBNlA5VGVCWVNOdFRpMkRmWG1Xczg3X3FkajQwbElEanF0QnNPb0dGQzdkcmVjaWRuSnpqOUZyMXl4eUNyZHU1QUk?oc=5</t>
+        </is>
+      </c>
+      <c r="F293" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>Supply_Chain</t>
+        </is>
+      </c>
+      <c r="B294" t="inlineStr">
+        <is>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+        </is>
+      </c>
+      <c r="C294" t="inlineStr">
+        <is>
+          <t>Cyber disruption, tariffs and restructuring drive 15.5% fall in UK vehicle production - The Manufacturer</t>
+        </is>
+      </c>
+      <c r="D294" t="inlineStr">
+        <is>
+          <t>Thu, 29 Jan 2026 23:31:32 GMT</t>
+        </is>
+      </c>
+      <c r="E294" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxQeTRDeEt3SlVvTnJmM1R1NW1VbGRseVp2WnIxTXFtd3c3X2lqSmYzZUxKTkhOc0JqeTgzTHRtT1hkV2sxdVJJLXFWREhoM0RwdVdXTE92OTZ3S3IwTVk2ZDNCVXJJcFc5ZjlNTWZmR1JUMWp1bFd5VlduT2pySWo3RkIyenlmanNiTHlkajQxZHFsNlBHTm0xa0ZybUd3RFBJWXUxbzU0RlBGRDN3RHVJanRVTkZMUThKTXJzNl9Gek82Xzg?oc=5</t>
+        </is>
+      </c>
+      <c r="F294" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>Supply_Chain</t>
+        </is>
+      </c>
+      <c r="B295" t="inlineStr">
+        <is>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+        </is>
+      </c>
+      <c r="C295" t="inlineStr">
+        <is>
+          <t>Logistics UK and Loughborough College form training partnership - SMMT</t>
+        </is>
+      </c>
+      <c r="D295" t="inlineStr">
+        <is>
+          <t>Thu, 29 Jan 2026 18:43:39 GMT</t>
+        </is>
+      </c>
+      <c r="E295" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxPaWE2Sm9hZVdNUTBfSjFXWGFSTUI2R1IzdTFqSkpsX0x6c1YxOHhtZ1pvR3FsZUxuaEVlLVZ0cUJzbDRnaS1STEo0aWx6aGlheGxZVFZ5SmlDck9pVFlrdi1mQldIX285UlpNQVluNmZRUHA0TndtT0lGTFJZdE5BU3BjdlIzUTdMeGJyVXZzV0E?oc=5</t>
+        </is>
+      </c>
+      <c r="F295" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>Supply_Chain</t>
+        </is>
+      </c>
+      <c r="B296" t="inlineStr">
+        <is>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+        </is>
+      </c>
+      <c r="C296" t="inlineStr">
+        <is>
+          <t>Beyond tariffs: A better approach to green industrial policy - CEPR</t>
+        </is>
+      </c>
+      <c r="D296" t="inlineStr">
+        <is>
+          <t>Fri, 30 Jan 2026 00:02:21 GMT</t>
+        </is>
+      </c>
+      <c r="E296" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMijgFBVV95cUxOMUQxZkZlY2F5VUNPTTFCeE9VMlhHQnZCMC00U3owUlkwcmpPOU9sWlBVOFNjR0FJX2gyNF9reEw0Zk5NQ21GZlczb3BybE9EdnBiN3lQdWJvd2xuWGR1S1l6cWljYXVmckx4SGoyd0V2cUZwUHpCOFZvcVdyUGU0bUhPSWlmbzY0d2NNWkhn?oc=5</t>
+        </is>
+      </c>
+      <c r="F296" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>Supply_Chain</t>
+        </is>
+      </c>
+      <c r="B297" t="inlineStr">
+        <is>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+        </is>
+      </c>
+      <c r="C297" t="inlineStr">
+        <is>
+          <t>Wiltshire's small businesses brace for impact as US tariffs loom - Rayo</t>
+        </is>
+      </c>
+      <c r="D297" t="inlineStr">
+        <is>
+          <t>Fri, 30 Jan 2026 05:31:18 GMT</t>
+        </is>
+      </c>
+      <c r="E297" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxOLWliNW1qcTk2aWdxb1MwZU85TzNldjJwX2Fvb2g3Z3J0OXF4aUFBRVRFTklIaW5wSUt3RFVGV3l2OXh0S2pkME5zaHEtemljRXVQZW0tUUFyc3VlTVF0Sm5PdjRYQU56VVRrdmN0T2JWQjdCQWtCUGZTa2lUUldfdlVxT0h3Q0ZYcXp4VUxQQ2ZnbHc?oc=5</t>
+        </is>
+      </c>
+      <c r="F297" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>Supply_Chain</t>
+        </is>
+      </c>
+      <c r="B298" t="inlineStr">
+        <is>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+        </is>
+      </c>
+      <c r="C298" t="inlineStr">
+        <is>
+          <t>Airbus Renews Logistics Flows Contract - Logistics Business</t>
+        </is>
+      </c>
+      <c r="D298" t="inlineStr">
+        <is>
+          <t>Thu, 29 Jan 2026 23:43:07 GMT</t>
+        </is>
+      </c>
+      <c r="E298" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxPOEx0NTh1ckNtUWR6dUhwS05nX1h0YnhHMEJrMUdqbmFsN2pyMnFsdWYxRktqcTRGMVVZb3pvY0Jhbl9DVzQ2NW1pdFlCTEV0OGVGOEQ2dmlaQTNZTXBwandMMDZPenRGcnNwQ0pLbTRscUFVaWFYREZUWnlVeVdlekxCUGZMN2Z6dEhBeEt1cXpvTXpyVjAwLTY3dmNINlo3UmlDcw?oc=5</t>
+        </is>
+      </c>
+      <c r="F298" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>Supply_Chain</t>
+        </is>
+      </c>
+      <c r="B299" t="inlineStr">
+        <is>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+        </is>
+      </c>
+      <c r="C299" t="inlineStr">
+        <is>
+          <t>Senator asks Trump for details on Rolex he accepted before Swiss tariff deal - The Independent</t>
+        </is>
+      </c>
+      <c r="D299" t="inlineStr">
+        <is>
+          <t>Thu, 29 Jan 2026 18:07:00 GMT</t>
+        </is>
+      </c>
+      <c r="E299" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxOTW9LQllQN2ZMZzk0MTBURHNnOS1jZGdFYWRMWGxMM1JxQS04cXQ5c3p4RnpERkVMdVgtQVgxejhEanM2RnRITHJwS2pWV0lrLWJIeGJkQzUwOHNIMy1IakZTWVQzMm9nbllSMGN4R3Ita25HMGoxVVdaSkNCTlF0VEZwWEZlZGEzbVFIRDB5RVBhUEVHTTR3UXFsZ3lxVjZwREthaHZ2RDFtZ2M0WXJWMA?oc=5</t>
+        </is>
+      </c>
+      <c r="F299" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>Supply_Chain</t>
+        </is>
+      </c>
+      <c r="B300" t="inlineStr">
+        <is>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+        </is>
+      </c>
+      <c r="C300" t="inlineStr">
+        <is>
+          <t>New Isles of Scilly freight ship begins sea trials - BBC</t>
+        </is>
+      </c>
+      <c r="D300" t="inlineStr">
+        <is>
+          <t>Thu, 29 Jan 2026 14:34:23 GMT</t>
+        </is>
+      </c>
+      <c r="E300" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTE5sdUFaOFFBTlB6dGk1NGhEaE8xaWdLSWRvWHBMRWdWZVpRd2xfWUs0UjZYWW8tTzlEUThoOTMtdnhvckI5ekJ4SkdyRTF0ZUFfRUxlWUJYbjR4dw?oc=5</t>
+        </is>
+      </c>
+      <c r="F300" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>Supply_Chain</t>
+        </is>
+      </c>
+      <c r="B301" t="inlineStr">
+        <is>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+        </is>
+      </c>
+      <c r="C301" t="inlineStr">
+        <is>
+          <t>Top 10 Cloud Compliance Tools for Enterprise Security and Audit Readiness in 2026 - Qualys</t>
+        </is>
+      </c>
+      <c r="D301" t="inlineStr">
+        <is>
+          <t>Fri, 30 Jan 2026 04:42:31 GMT</t>
+        </is>
+      </c>
+      <c r="E301" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiyAFBVV95cUxOd2N6SkJkbzZ0WE5sSzJsUnpJSjhNUVR3dWdfWUVYNXNhTjBiVVhERlA2bWlXYkRnLUlPcFFVQkVKdjFpNmxUSW9ZNk5sRHNyVzVlRFRJVThQamV4M1VUc25mYkE0NllaQ1diQ3hhc2JIT3lUT2p2MVNkNXk4cWx5X2lOaTdXcHFOdkFqZE9WNDY1YWw2bFJxb2dJSTRXckhqbDFFQlhKbC0wN3Jwc3FPQ1VQRURqRGlLWVNHNDcwMkFzSjkyN2tBQQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F301" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>Supply_Chain</t>
+        </is>
+      </c>
+      <c r="B302" t="inlineStr">
+        <is>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+        </is>
+      </c>
+      <c r="C302" t="inlineStr">
+        <is>
+          <t>VolkerFitzpatrick completes landmark Rockingham Gateway Logistics Facility - VolkerFitzpatrick</t>
+        </is>
+      </c>
+      <c r="D302" t="inlineStr">
+        <is>
+          <t>Thu, 29 Jan 2026 19:33:12 GMT</t>
+        </is>
+      </c>
+      <c r="E302" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxOZlM4SFA4ck5TdUlZdnhMMG03NW5mWXlfazMyX1lUUEdrR0lrMDA3VThJVjktcDdSUE1zaG1wRVoyLXdZLU5pTTB1ZVVGeWFzSFZNMGVxMVkwS1hsRUpDWmtmeC1pcksxcmJ6TlZkand0R1JubXUycGJLalVoZUVNbDJicHZBdWxrRFFlcURuZE9aTmI4Y1BOM25UYnFNd3FrRWVZNEhLOU9wWDNLSHFkWUFCTkl4NTZodVE?oc=5</t>
+        </is>
+      </c>
+      <c r="F302" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>Supply_Chain</t>
+        </is>
+      </c>
+      <c r="B303" t="inlineStr">
+        <is>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+        </is>
+      </c>
+      <c r="C303" t="inlineStr">
+        <is>
+          <t>5 strategies to protect against food supply chain shocks - FoodNavigator.com</t>
+        </is>
+      </c>
+      <c r="D303" t="inlineStr">
+        <is>
+          <t>Thu, 29 Jan 2026 15:55:42 GMT</t>
+        </is>
+      </c>
+      <c r="E303" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxONWg3RENmalN5Nk9jRENabzVPajduOVNZdFFqbkVOSmpIdERWWnhieE5zRnFHcTg4SXlXejZQaVRpVmhEeUxvNUlmeEw5a25zX0RhMExvZk9hRDQ4cVRrUmYycU1UajVpRnJLejZmY1dScEYzOFlMdEgtU0VHY0FiTEkwSkhIay1nLUdUTzBlYW1teFlhTGtrbmdBX0VhX1p1N0k5TUdzWUNBU2p4Smc?oc=5</t>
+        </is>
+      </c>
+      <c r="F303" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>Supply_Chain</t>
+        </is>
+      </c>
+      <c r="B304" t="inlineStr">
+        <is>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+        </is>
+      </c>
+      <c r="C304" t="inlineStr">
+        <is>
+          <t>US curbs oil sanctions on Venezuela after Maduro ouster - Upstream Online</t>
+        </is>
+      </c>
+      <c r="D304" t="inlineStr">
+        <is>
+          <t>Thu, 29 Jan 2026 22:55:31 GMT</t>
+        </is>
+      </c>
+      <c r="E304" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxONlpST2lsXzZuV19BdXdFbUhDVThkRF9qTk9GakNDcEFRRzNHa2lRMFFEd2FGU29xSHNMVWtQYWU5aUVnMDVudEJOWnBGaGdOVHd2aTMtU2xLUzltTG1UaFQ3a2JFbHVvbmROTXFoMkZGckE3ajZkVmxkdnQtMEpuZ3VSYzNJN1YwcHRYdVNKRGV6MW1pY002b2hTbVp3OVdPY3lKVklDWjI2TVE?oc=5</t>
+        </is>
+      </c>
+      <c r="F304" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="inlineStr">
+        <is>
+          <t>Supply_Chain</t>
+        </is>
+      </c>
+      <c r="B305" t="inlineStr">
+        <is>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+        </is>
+      </c>
+      <c r="C305" t="inlineStr">
+        <is>
+          <t>Dynamic Pricing Is Changing the Parcel Shipping Industry - Harvard Business Review</t>
+        </is>
+      </c>
+      <c r="D305" t="inlineStr">
+        <is>
+          <t>Thu, 29 Jan 2026 20:51:47 GMT</t>
+        </is>
+      </c>
+      <c r="E305" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMihwFBVV95cUxNZTBaNWNFbEZYZFFZQTl6LWllbW1EYVpmZzBSaXpSdDZLRDl0LURVSkIzUzJ0R1lQQ2JURXo4d2NKbDFrRzlsc0pCd1JnVmh2TlluSDBQcm5hRWUzREVEdGZqQ2VVbVlNVTBEVnc5Mmd4cGwwSVZoVGk0SWVlamJSNFRWUlJ2TmM?oc=5</t>
+        </is>
+      </c>
+      <c r="F305" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
+          <t>Supply_Chain</t>
+        </is>
+      </c>
+      <c r="B306" t="inlineStr">
+        <is>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+        </is>
+      </c>
+      <c r="C306" t="inlineStr">
+        <is>
+          <t>Splash Wrap: The week in shipping in 450 words - Splash247</t>
+        </is>
+      </c>
+      <c r="D306" t="inlineStr">
+        <is>
+          <t>Fri, 30 Jan 2026 06:28:37 GMT</t>
+        </is>
+      </c>
+      <c r="E306" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMid0FVX3lxTE11TU5vLUpIaFNaYkw1a0NfbnZ0eHluNm8xb0JUNVdqMVhjaTM1aEtiQjRLWllubW1NaF95NGEyZlRVckZ5d0F0dWlyTnlxWWktOGJ5QkpHNHB2SXRIZFJLLXlTQ1N0TVgxNlMxUmx1N1dFRnpvR2JZ?oc=5</t>
+        </is>
+      </c>
+      <c r="F306" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="inlineStr">
+        <is>
+          <t>Supply_Chain</t>
+        </is>
+      </c>
+      <c r="B307" t="inlineStr">
+        <is>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+        </is>
+      </c>
+      <c r="C307" t="inlineStr">
+        <is>
+          <t>Private equity firm HitecVision open to a shipping comeback - Tradewinds News</t>
+        </is>
+      </c>
+      <c r="D307" t="inlineStr">
+        <is>
+          <t>Fri, 30 Jan 2026 07:14:38 GMT</t>
+        </is>
+      </c>
+      <c r="E307" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxOSF8tVmRUTU8wcVpiMUtJc0hGWmxKOFdudGk5ZGlpdkxYQ25OTU5jeDJEa0F5ZlhQWnV2QTd4RmhmUllQN0lmaU1XMWpHaEZDbV9SX1dsVXBsWnFaQjBZZnhlYkk3MEFjVC00MEtyRnlTdWVtc0VOTkJaTGo1NVNKS3RFbk9MU2lreUVyWDVzZmc5SVJ3TldPcml6cGk2ZDBmbWNiV1BrZTktM0t2eExJ?oc=5</t>
+        </is>
+      </c>
+      <c r="F307" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="inlineStr">
+        <is>
+          <t>Supply_Chain</t>
+        </is>
+      </c>
+      <c r="B308" t="inlineStr">
+        <is>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+        </is>
+      </c>
+      <c r="C308" t="inlineStr">
+        <is>
+          <t>GB Railfreight signs ten-year wagon maintenance deal with Wabtec - Rail Magazine</t>
+        </is>
+      </c>
+      <c r="D308" t="inlineStr">
+        <is>
+          <t>Fri, 30 Jan 2026 06:03:52 GMT</t>
+        </is>
+      </c>
+      <c r="E308" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxPajRkQy16S1NlbjM4ald3RFA5emhVVGg2STlMYUlsSFhKMmhITFlEbGp1dldBekVLaFNoeVVoWFVqQlg4OFZyZjQ5OWNIVEVHVllEblBORlJCYlRQUlk0cW5fb052cWF6X21RMWNxYW40cldyeTJyZnFxeXlVd3BTRk9GdjFqTXFHWDdTeTl2c2tPajNNNkNBaHFVVGZsVDA?oc=5</t>
+        </is>
+      </c>
+      <c r="F308" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="inlineStr">
+        <is>
+          <t>Supply_Chain</t>
+        </is>
+      </c>
+      <c r="B309" t="inlineStr">
+        <is>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+        </is>
+      </c>
+      <c r="C309" t="inlineStr">
+        <is>
+          <t>How Cloud ERP Helps Manufacturers Improve Productivity and Logistics - ERP Today</t>
+        </is>
+      </c>
+      <c r="D309" t="inlineStr">
+        <is>
+          <t>Fri, 30 Jan 2026 06:03:37 GMT</t>
+        </is>
+      </c>
+      <c r="E309" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxPZkd3SzdUaWpUeUxZbW9pbWk0QTRIaUx0eVFvV3ZNTG5GZ1NqYWZxbDdqVW5DTEE2enBtTkY4WEhPOHowdl92R2NTV0tfUGE1WmdldWVGclRTYm53MEFSN0FDTW1OUFBMRE9ZcWdQRzlSX19tNzlnQ2tQaURrZHhWYWhkbU5ZZ2Q0MzFvMG80NmM?oc=5</t>
+        </is>
+      </c>
+      <c r="F309" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="inlineStr">
+        <is>
+          <t>Supply_Chain</t>
+        </is>
+      </c>
+      <c r="B310" t="inlineStr">
+        <is>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+        </is>
+      </c>
+      <c r="C310" t="inlineStr">
+        <is>
+          <t>WEBINAR: Supply Chain Resilience: Adapting for the Future of A&amp;D - Aviation Week Network</t>
+        </is>
+      </c>
+      <c r="D310" t="inlineStr">
+        <is>
+          <t>Thu, 29 Jan 2026 23:37:09 GMT</t>
+        </is>
+      </c>
+      <c r="E310" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxPMG1oNXNiVXliQmp5LXpZT21QUzF0cXQ2eGdRU0ZvaTV4NmowdVpIend0WnhlT0xLbFRKVEJCaHVYaWJfY013UmlNTzJJd2hscFdMdjktNGx6YTRhYWhUbVp4WXVRNnJoRV9pSTFrQ3RfeS1TM2Z0MGM0c3J4QmxfYUJMMnZ1c2txQ0RzRXZVbG5kQ1c4SWJz?oc=5</t>
+        </is>
+      </c>
+      <c r="F310" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="inlineStr">
+        <is>
+          <t>Supply_Chain</t>
+        </is>
+      </c>
+      <c r="B311" t="inlineStr">
+        <is>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+        </is>
+      </c>
+      <c r="C311" t="inlineStr">
+        <is>
+          <t>Tariffs Won’t Fix American Manufacturing But Digital Factories Might - Forbes</t>
+        </is>
+      </c>
+      <c r="D311" t="inlineStr">
+        <is>
+          <t>Fri, 30 Jan 2026 02:56:44 GMT</t>
+        </is>
+      </c>
+      <c r="E311" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxQQXpnQU11VmdkYVlTTElHTm1uRFdGUjZab1M5eTkzWU1HZzBGWFdSa3JXUC1RejJiNlRKZkdGM3R6TFJwYVpRc0Q0bHRYYUd0VlJ1WHRmSW45SEFNVndPLTRBeWI1UU0ySVdKQlpBd2RmNDktVTlSdm9BLXZWR0Y0Q19nTkxkNjQwWXhxd1BiQWpFVzBkU05Rd2dvMUlpdkNtVWY2ZFgteTVNZkNLUkplLXJxOFRPVWk4bnJv?oc=5</t>
+        </is>
+      </c>
+      <c r="F311" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="inlineStr">
+        <is>
+          <t>Supply_Chain</t>
+        </is>
+      </c>
+      <c r="B312" t="inlineStr">
+        <is>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+        </is>
+      </c>
+      <c r="C312" t="inlineStr">
+        <is>
+          <t>ICS Publishes 2025-2026 Flag State Performance Table Highlighting Strong Compliance with Global Standards - Maritime Fairtrade</t>
+        </is>
+      </c>
+      <c r="D312" t="inlineStr">
+        <is>
+          <t>Fri, 30 Jan 2026 07:08:23 GMT</t>
+        </is>
+      </c>
+      <c r="E312" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi0gFBVV95cUxNRzF5OEluWktuTU9kMWFXT3lrY1lMVVA0ai0zelQ2MkRTblNyQ0hYUl80c0JtSzl1VW00eFR2a1BtTENONXh0T1pmUkVOTzNRb2ZWVTF4T0xfUFl5OVdUbVpZNHN4SDVSLUVNUlhRcFVDc3BaMTdJZll6bHRtdXVzNkNTYXpIb3FzZHFSS0E1U3BhdEVDRnFqTUhqbUJVd2hVZ0JuV3ZOaVo4anprb0tWdnVUX1ZFZUFmQkd6VmhXYWlYLWxVYzd5bUNndXlVX0Zubnc?oc=5</t>
+        </is>
+      </c>
+      <c r="F312" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="inlineStr">
+        <is>
+          <t>Supply_Chain</t>
+        </is>
+      </c>
+      <c r="B313" t="inlineStr">
+        <is>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+        </is>
+      </c>
+      <c r="C313" t="inlineStr">
+        <is>
+          <t>L3Harris Technologies secures $95.6 million contract for logistics support By Investing.com - Investing.com UK</t>
+        </is>
+      </c>
+      <c r="D313" t="inlineStr">
+        <is>
+          <t>Thu, 29 Jan 2026 22:28:00 GMT</t>
+        </is>
+      </c>
+      <c r="E313" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMizgFBVV95cUxPVXhJS1lQVDJoZEV4VmwtOFdfdXlnS0U1ck5ranljS1BnSGhoX093NUtaamViTkdVRFZ2YjJkUXF6OUV5STR3NS1aeXkzM2JPQ00wMmNBaGN4Q0pfUU1POTVERl9wZG5sY2lsSWhTSjFjMGRhXzRGMldvN0RHNFFIX3lraGxSelFJMUE2NVN6c1lCMS1QZHBFNFZ1TnFXcWx2VmxCMmxhV0JaMndQOWxvWG4yUVZDN2RoRkk3Uko5ZjVPc3dySGNMMEVSQ2wwQQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F313" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="inlineStr">
+        <is>
+          <t>Supply_Chain</t>
+        </is>
+      </c>
+      <c r="B314" t="inlineStr">
+        <is>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+        </is>
+      </c>
+      <c r="C314" t="inlineStr">
+        <is>
+          <t>Al Jazeera denounces YouTube’s compliance with Israel’s ban on network - Al Jazeera</t>
+        </is>
+      </c>
+      <c r="D314" t="inlineStr">
+        <is>
+          <t>Thu, 29 Jan 2026 16:48:09 GMT</t>
+        </is>
+      </c>
+      <c r="E314" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxObHJFaGhCOF9xeDFDdmphbC1NS3ozS28wNWxWV2RKenNORE85RlEwZWlZV3FlQ2NFbVhBX2hfMWRvMzc3UW1lNFpFY3duWHlzclZWbHI0bGM0dENBbTkxXzVzcXh1bWxOdlA2OUtvWmFYeXFOWjNoOHZTeUNrcDRORl9ERkgtTThzRnUwRWg3WThkME9DTmRTMVV5VTF4d0ZIMzlYUDREeExpd1JtaEHSAbMBQVVfeXFMT1RGRmZ5cXR5Rlp5MFFXbFUzWXNsUGtXREo4eEFUdWt6NUxwS0o4cjBFX19nS05CZGpKWHlwS3dsd0l6ak03VUNkeXJkcDVhMDdZU1EtMDFQYk9KaDdRc3pNT29hQXhWSkwzQXBzMTlRc2hqLTljejVVeGdMMk5pTmF4ZkZWSWlaYzA3bE96U1pCZm9WNURsaS02U1k1aU8wUUVKdFBBb1poY2x2REsxaVJSaWs?oc=5</t>
+        </is>
+      </c>
+      <c r="F314" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="inlineStr">
+        <is>
+          <t>Supply_Chain</t>
+        </is>
+      </c>
+      <c r="B315" t="inlineStr">
+        <is>
+          <t>("supply chain" OR logistics OR shipping OR freight OR port OR tariffs OR sanctions OR embargoes OR reshoring OR nearshoring OR compliance OR "supply chain disruption" OR fragmentation OR instability) AND (company OR manufacturer OR factory OR supplier OR export OR import OR production)</t>
+        </is>
+      </c>
+      <c r="C315" t="inlineStr">
+        <is>
+          <t>VACANCY | Logistics officer – Travel &amp; Operations - Soudal Quick-Step Pro Cycling Team</t>
+        </is>
+      </c>
+      <c r="D315" t="inlineStr">
+        <is>
+          <t>Thu, 29 Jan 2026 11:01:23 GMT</t>
+        </is>
+      </c>
+      <c r="E315" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxQamhjZmtSeWxJYXMzRzFEN2lpMTdVZENSWlMxUXdXVWxiTjJ3X0Y5d0phRDBOZll6aVRGZjdCQ0htcER1eUxjckFVVHVFNDBfMGpkMWdZSUdRNVBwYzVOQnI3T0QxVmVuSFVqZm1hS3lnYk52V3NqWEdqSVQ2QzRNZUROdGV0bmVFS2dWZGxMOVN2aVEtLTdyQw?oc=5</t>
+        </is>
+      </c>
+      <c r="F315" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="inlineStr">
+        <is>
+          <t>Protest</t>
+        </is>
+      </c>
+      <c r="B316" t="inlineStr">
+        <is>
+          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally OR tactics OR targets OR groups)</t>
+        </is>
+      </c>
+      <c r="C316" t="inlineStr">
+        <is>
+          <t>Metropolitan Police strikes called off as workers accept new pay offer - Unite the Union</t>
+        </is>
+      </c>
+      <c r="D316" t="inlineStr">
+        <is>
+          <t>Thu, 29 Jan 2026 09:40:32 GMT</t>
+        </is>
+      </c>
+      <c r="E316" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxPZGZLQ1JjVFFWRWJFa01lWUhfRkhfOGd5M3Z6SGRuQUxPcmkwR1N1M3ZYSmxUdjMwRnByb3ViOG1fdGJuS2Uycm1DUDJsNmpFVjJNZEMyU2pyZ1NnREI3dUxVaEIwMk1pSTM4ak5ULXpYZnRtVzFqNEVnSHpPbWpWeFNrOGxfVlAydE9wLWxBTmU0WkY5WEdDeUJ2LUF0MjVnRTc0VWpGZi1SOTVQZ0o0bzRWVW5Ua1FZbjhIM29Sa3p5Q1ZIRE5oOFJ3?oc=5</t>
+        </is>
+      </c>
+      <c r="F316" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="inlineStr">
+        <is>
+          <t>Protest</t>
+        </is>
+      </c>
+      <c r="B317" t="inlineStr">
+        <is>
+          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally OR tactics OR targets OR groups)</t>
+        </is>
+      </c>
+      <c r="C317" t="inlineStr">
+        <is>
+          <t>Protest held in the Netherlands over police violence against 2 Muslim women - Anadolu Ajansı</t>
+        </is>
+      </c>
+      <c r="D317" t="inlineStr">
+        <is>
+          <t>Fri, 30 Jan 2026 04:49:25 GMT</t>
+        </is>
+      </c>
+      <c r="E317" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxOTmJ2M3B1YzE5Y1RjZUJTRDA0ZV9zZ2JFR3l1N3I3TktlM3JXWU5kWXQ0NVRKNW1WVkFob3VfRjRHbWpybXVzUU92RkU0SVRMcmlMdEJBMEFDajVBcm12a2FwS3A0TFRNcXh3Wm9xQ0cxX1MzazUyQU1zNVJkeWpOZFRZdzZNMzBReHBYNlNJZm9pd2dmQ3dhV0NzbndDck1RSHNrSGE3Y2ROQjFIeTJmbHNsdHVUQQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F317" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="inlineStr">
+        <is>
+          <t>Protest</t>
+        </is>
+      </c>
+      <c r="B318" t="inlineStr">
+        <is>
+          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally OR tactics OR targets OR groups)</t>
+        </is>
+      </c>
+      <c r="C318" t="inlineStr">
+        <is>
+          <t>Police syndicates threaten action at Lisbon Airport over Easter - Portugal Resident</t>
+        </is>
+      </c>
+      <c r="D318" t="inlineStr">
+        <is>
+          <t>Thu, 29 Jan 2026 13:52:37 GMT</t>
+        </is>
+      </c>
+      <c r="E318" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxQUkx4VTdKeFU4V25EN0YwZzZoVTd6cFpSdzRaV09ud1VaMVBBY1M4dlZNMFJYV1hDQ3BqeExZNldfTjV3S3F6ZUdsWEhmQWZDLXhua2N3dnNHbFBSc2hLbGlBU1lCRC1BdzVDdGhZT1FDR2NJRGhpSmdfN292Q2NtR2VhQUtmazdQaWROQ0daV1B4dUQwVUF4RVgxbVc4QQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F318" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="inlineStr">
+        <is>
+          <t>Protest</t>
+        </is>
+      </c>
+      <c r="B319" t="inlineStr">
+        <is>
+          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally OR tactics OR targets OR groups)</t>
+        </is>
+      </c>
+      <c r="C319" t="inlineStr">
+        <is>
+          <t>3 dead, 17 injured as police crack down on protests in Nigeria - İlke Haber Ajansı</t>
+        </is>
+      </c>
+      <c r="D319" t="inlineStr">
+        <is>
+          <t>Thu, 29 Jan 2026 19:51:39 GMT</t>
+        </is>
+      </c>
+      <c r="E319" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxNUDVyamRxMzU5UlZCWjhiMkpxanFWeW1jYk5SYzRCSl96dXJlWGR2cU1DVEdnSTYxTHFjRjFaeHBTLVJHbHAzd01ESHNHQmpNRTFSTDlBbjltcnpOTFNOYnFfNjM2aC1yQUZaajJNM0NfRE9oVWRhamdWMmhhRW1OUDh6MEI1VVVhV19VeVdweFo3WDRqSVdoV0Q3eUdNeEJ1M1E?oc=5</t>
+        </is>
+      </c>
+      <c r="F319" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="inlineStr">
+        <is>
+          <t>Protest</t>
+        </is>
+      </c>
+      <c r="B320" t="inlineStr">
+        <is>
+          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally OR tactics OR targets OR groups)</t>
+        </is>
+      </c>
+      <c r="C320" t="inlineStr">
+        <is>
+          <t>Nasus Pharma Calls March 5 Special Meeting to Boost Share Capital and Approve New Equity Incentives - TipRanks</t>
+        </is>
+      </c>
+      <c r="D320" t="inlineStr">
+        <is>
+          <t>Thu, 29 Jan 2026 21:51:47 GMT</t>
+        </is>
+      </c>
+      <c r="E320" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi5gFBVV95cUxOWlk3dDVqdjNIb19fZXpWeVlKaUh6TGRDVkNvcGFmQ1NtdzFBZzlhWFVkaWs3NXczeDNUNmlQTXgyT0NtejZKbllIU1lLU0lpNlhVclJ6OFdjLU1QdEk3U1BLTTBNamk3SlBFdVVJdWVGUHZOWmJqalI5X1dpVFRKclduQ1ZYSEUyY3ZoU3Y5Vk9JSXFtc0JfSWVWTm9veTd0aDd4MFZ1V3BpTTNnNWViUDMyeFEtaDlWQmozNndORHNYUUJISUdDVUxGWHM0VTBCaVNmUUZ4QkZKUExudUhNNnVUTTN6QQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F320" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="inlineStr">
+        <is>
+          <t>Protest</t>
+        </is>
+      </c>
+      <c r="B321" t="inlineStr">
+        <is>
+          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally OR tactics OR targets OR groups)</t>
+        </is>
+      </c>
+      <c r="C321" t="inlineStr">
+        <is>
+          <t>Akron police say they’re unaware of any ICE activity in the area - beaconjournal.com</t>
+        </is>
+      </c>
+      <c r="D321" t="inlineStr">
+        <is>
+          <t>Thu, 29 Jan 2026 17:22:00 GMT</t>
+        </is>
+      </c>
+      <c r="E321" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxNb1otM2kwNkxrWXVybWRFX2dMS09Yb3dUNWRQZFQ2R1E5TWNaTWZqamFncEJwRk9Kd3JKbGtlMnpiNjVOb3NyNmJSLWY1bEo5QVZmSWgtazd4dUoteWc5b3R0WlNfT3NaM1JfSG5yYnJuVWJfUHlQaFYwMGpQLUk1Smw2N2hleTVfcktidTNma19lT0pWYXhxODY0ak1ybTJ4bHl2bldDQjlWZ3hNUXNndzRJNlNMN0txQ2NDQWN6RGl4blVHWFE?oc=5</t>
+        </is>
+      </c>
+      <c r="F321" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="inlineStr">
+        <is>
+          <t>Protest</t>
+        </is>
+      </c>
+      <c r="B322" t="inlineStr">
+        <is>
+          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally OR tactics OR targets OR groups)</t>
+        </is>
+      </c>
+      <c r="C322" t="inlineStr">
+        <is>
+          <t>Laser strike on Tucson Police aircraft leads to arrest - kold.com</t>
+        </is>
+      </c>
+      <c r="D322" t="inlineStr">
+        <is>
+          <t>Thu, 29 Jan 2026 14:03:00 GMT</t>
+        </is>
+      </c>
+      <c r="E322" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiiAFBVV95cUxOaVRIQlN2aWw0MWp2dWV6RmM4NlFHUkV4MDAxaTRDVHhqN1cwemVGR3BoUEtJSTI0aG9FbGNxSERNbWhHOHkzbjJ0NnR6M3NpNnRENUYzSWpPUFdDazgybHpPU0NDOEdjSjNxYjJwSGU4OWFFdjNGNTFJS3pSbHhJWkJrdGFMRFNz0gGcAUFVX3lxTE1mSl9rYUdmOGVHRm1pWnlXV2dPc2tKeGxOS2g0UllORDV4eEV6ZGp2ZlQyQ1BvdzlENExnY0lDQnpxelYzX1pDOWRFaXZpaXRlZndia0U2UFU0N3pqbVhSNmlTTk9NRkRtcUFFTnU5RGxhamxicEtOdkFHM1c1dWZkUFVvbFVHaGxIeEZRV1h1VFMxMDZZeXFNM19Wcg?oc=5</t>
+        </is>
+      </c>
+      <c r="F322" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="inlineStr">
+        <is>
+          <t>Protest</t>
+        </is>
+      </c>
+      <c r="B323" t="inlineStr">
+        <is>
+          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally OR tactics OR targets OR groups)</t>
+        </is>
+      </c>
+      <c r="C323" t="inlineStr">
+        <is>
+          <t>'Let police sweat it out': Defiant Tamaki slams moves to shut down harbour bridge protest march - NZ Herald</t>
+        </is>
+      </c>
+      <c r="D323" t="inlineStr">
+        <is>
+          <t>Fri, 30 Jan 2026 00:17:53 GMT</t>
+        </is>
+      </c>
+      <c r="E323" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi9wFBVV95cUxNeTg2OVQxVlpjTGhXTkNwMDVKbHFHbmVjcjl2QUVsUFZ2T0dQWG1kVlRYd25iUDNlQ21tangwck1DcjdCd09oMzZBcjJITU9oT1J5TkFjRGpfQnJmVDdpTGRuckU0aV9ZVXJPNHhGT2JMQzJsaVZjWVJXcTRhQUFhMGtjVHJRam5JZVZJUm9vcFhlMm5SbFlMRGRjZlhlLTJ4RU14UXAxVjZXd1NKenQxWnQtVURxbEZtby0yUGh4d2NvbzN6WXFhU3dZU2dGc1VYb1laTFdHR0xDNHJNWkw2RlBoT0VnTE1BQ2I2eXNsc0gyLUc3TGZz?oc=5</t>
+        </is>
+      </c>
+      <c r="F323" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="inlineStr">
+        <is>
+          <t>Protest</t>
+        </is>
+      </c>
+      <c r="B324" t="inlineStr">
+        <is>
+          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally OR tactics OR targets OR groups)</t>
+        </is>
+      </c>
+      <c r="C324" t="inlineStr">
+        <is>
+          <t>Billings protest urges local police to end ICE cooperation, seek policy change - kulr8.com</t>
+        </is>
+      </c>
+      <c r="D324" t="inlineStr">
+        <is>
+          <t>Fri, 30 Jan 2026 01:11:00 GMT</t>
+        </is>
+      </c>
+      <c r="E324" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi5wFBVV95cUxQQU1odzdrWTJDMlpUb3E3Y3A3MmpMWWJVaUhhSVB1UEp6d1AwRUFVVTB6cGo1RUNKNERwTE9WYTlCWk42d2h1aFN1cW13dHd5alNWMUhXSlhQcURybHZSQlp1UUdxY0VhU2NQM2MyenRuM2JZUGF0YmpSMlFGOEl2eV9ycUphUXFDS0w1RmVXUk5NZ3BnaUkyeHF0Mmh1OTNMcDZ6X3Uwb1g3VUV2WGhEM29DQ3ppbU4tTDFoTm0tOFVQTDY4QktNNHZRc3RZQWhEZFc4aFdlbU9LcXl0QWQ2SExSQTNpakk?oc=5</t>
+        </is>
+      </c>
+      <c r="F324" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="inlineStr">
+        <is>
+          <t>Protest</t>
+        </is>
+      </c>
+      <c r="B325" t="inlineStr">
+        <is>
+          <t>(protest OR protests OR demonstration OR demonstrations OR unrest OR "civil resistance" OR "civil disobedience" OR boycott OR boycotts OR march OR marches OR strike OR strikes) AND (police OR capital OR city OR arrests OR arrested OR union OR workers OR students OR rally OR tactics OR targets OR groups)</t>
+        </is>
+      </c>
+      <c r="C325" t="inlineStr">
+        <is>
+          <t>State police trooper injured in 6th vehicle strike since snowstorm - wrtv.com</t>
+        </is>
+      </c>
+      <c r="D325" t="inlineStr">
+        <is>
+          <t>Thu, 29 Jan 2026 16:04:25 GMT</t>
+        </is>
+      </c>
+      <c r="E325" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxNbGE1OGRhNURTWC1HQ3k5WXlZLUo4VFYwOHJzbHhuRDRrZDVrS3htWHBsZDVBOU9rSHJYS1NjTV9fblFFTm1jcG5kMUxzMENSOEVRSk5IYkhzZ1E3aEhhU18yUTJ0TFVLTTBTMWZNSDI2dkJ2dTZWeEFtNUJYeThLQU9YMjltamt1bHhlQmtEVk1pb0xFSWJOQURGd0JyUEJSbVdFaURB?oc=5</t>
+        </is>
+      </c>
+      <c r="F325" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B326" t="inlineStr">
+        <is>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+        </is>
+      </c>
+      <c r="C326" t="inlineStr">
+        <is>
+          <t>Abusers using AI and digital tech to attack and control women, charity warns - The Guardian</t>
+        </is>
+      </c>
+      <c r="D326" t="inlineStr">
+        <is>
+          <t>Fri, 30 Jan 2026 07:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="E326" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxNalRlb3UyM2w2eHBJQjRDYjNIMmN5Yl9sSDlRRmVDOUdpS0N5b3BHR0RXanJwM1FNd3pGWGw5T1RRYWZJQU9pOGluSUM2V2QxaDVyU3lJTVl1WS1OdzZlbGFQZG9YYzhENldpSy1lM2RrMFB4V01NVlRvUS1aLVpSY2QxTjk0YlN0M1ZuRGFwOURVQWoyQWo2MWdsRTVsY2xmZ0gtVUc4UzJTSXc2V3ZpV1o2YUVRUHc5Y1hSYkd3LWo?oc=5</t>
+        </is>
+      </c>
+      <c r="F326" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B327" t="inlineStr">
+        <is>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+        </is>
+      </c>
+      <c r="C327" t="inlineStr">
+        <is>
+          <t>AI's got news for you: Can AI improve our information environment? - IPPR</t>
+        </is>
+      </c>
+      <c r="D327" t="inlineStr">
+        <is>
+          <t>Fri, 30 Jan 2026 00:31:36 GMT</t>
+        </is>
+      </c>
+      <c r="E327" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiX0FVX3lxTE5RSkpmWEZDYnQ0OEFzdmR1T1p6b0dBa1pPZnlFNVhnclZJbGRBTlVLWEtZTUZ2ZkQxYkdSbmhXNkNlMlllS0ZUWm8taV9POTNqR3RaaWlJd2VNeU5iZXVz?oc=5</t>
+        </is>
+      </c>
+      <c r="F327" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B328" t="inlineStr">
+        <is>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+        </is>
+      </c>
+      <c r="C328" t="inlineStr">
+        <is>
+          <t>The problem with AI and Palantir - Stop the War</t>
+        </is>
+      </c>
+      <c r="D328" t="inlineStr">
+        <is>
+          <t>Thu, 29 Jan 2026 17:55:53 GMT</t>
+        </is>
+      </c>
+      <c r="E328" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMid0FVX3lxTE1lcUNSdEN2cXM1STJkbDZMclhORTkzSkl6dC1TNlJLVWp6eWJyeGpwUEFreDNwSnItZW9vQV94ZDNPZDkyRW9QelhINzMxTDZFYjFYcXRsY3BZS05ub19VTHdRcC1aWmhYZWR4V29SSFh2YlZvUnU4?oc=5</t>
+        </is>
+      </c>
+      <c r="F328" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B329" t="inlineStr">
+        <is>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+        </is>
+      </c>
+      <c r="C329" t="inlineStr">
+        <is>
+          <t>AI-fuelled cyber attacks surge 70%, Check Point warns - IT Brief UK</t>
+        </is>
+      </c>
+      <c r="D329" t="inlineStr">
+        <is>
+          <t>Thu, 29 Jan 2026 21:04:00 GMT</t>
+        </is>
+      </c>
+      <c r="E329" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMihgFBVV95cUxQbGtueEZtM0tPYzg5WjFSS1pfa3ZEX19FNXRYbHZRYk5yV19vT0dTb2R6bDEwNThrYmJiR0tWaHZXQldNMkdxS0JxNWtzUHNPX0Nkc3RuNGRUaTdKMFkzaHBVQkl4ZGdBU1dNRWxtRTVwenJUMC1yT3o3aXZfaGFQQnA0TFA4UQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F329" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B330" t="inlineStr">
+        <is>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+        </is>
+      </c>
+      <c r="C330" t="inlineStr">
+        <is>
+          <t>AI-generated ‘expert’ set to help the next generations of the workforce - Water Magazine</t>
+        </is>
+      </c>
+      <c r="D330" t="inlineStr">
+        <is>
+          <t>Fri, 30 Jan 2026 05:00:41 GMT</t>
+        </is>
+      </c>
+      <c r="E330" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxOZENOMW9OUVl1dEEzYmJ4eUZGVjlqdkRGQVFZWmQzVU1taXJCNTM1TmozcFdmUGdFdkhza0NZaVpqLWZrVWtDamNLVnJkbm80QlRIOGVVWW1KQ1kweHFQYkRmenlfWENfZGgzZVIwQkd6U21yV2NpdWRzakQwOUY2ZkV6ajViSG8zaUlsNzctMm9Jelc0dVJaZW54LVVRc2VGdGxzOHk3bXFNQS1iVF9ONEJ4SQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F330" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B331" t="inlineStr">
+        <is>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+        </is>
+      </c>
+      <c r="C331" t="inlineStr">
+        <is>
+          <t>AI and consumer creation The superfan factor - MIDiA Research</t>
+        </is>
+      </c>
+      <c r="D331" t="inlineStr">
+        <is>
+          <t>Thu, 29 Jan 2026 16:30:45 GMT</t>
+        </is>
+      </c>
+      <c r="E331" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiigFBVV95cUxQXzJPQzhkVlNsM21IeDh6d0R6RkJoZExhX0MzVXNnVTJvZ0gxUGFDQjZFMDRwb2Z4QWdiU2R3SmYweWlHaklzMlllTzRibXhvTVFLZFZFLTdmMDd5NGVhbU1pZEo2NzlmUHFNZ0xIRTM3a2lOOU9GRHozcUd6TFhWZkkzaVNPaFJacHc?oc=5</t>
+        </is>
+      </c>
+      <c r="F331" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B332" t="inlineStr">
+        <is>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+        </is>
+      </c>
+      <c r="C332" t="inlineStr">
+        <is>
+          <t>UK Launches Free AI Training Drive to Upskill 10 Million Workers by 2030 - BABL AI</t>
+        </is>
+      </c>
+      <c r="D332" t="inlineStr">
+        <is>
+          <t>Fri, 30 Jan 2026 00:52:39 GMT</t>
+        </is>
+      </c>
+      <c r="E332" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxOWkYzRXpMYmNmY09FZGo1aXQ5cUxuVEtOSkR3a3o0cmM2SjAtdTFIU1lJZ3Vybklqc3Vfd0ZmZmRQTzVQMkNRMGdOZC1fVVlFUzBWSGJGZDN6QkJGYTNBbEV2bVhfR3lFQ3FhS3pqWTk3X29YYWI0TzhxdkVjc2s4WG5CYWhDd3FwaUd1VlJodXBlbmM?oc=5</t>
+        </is>
+      </c>
+      <c r="F332" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B333" t="inlineStr">
+        <is>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+        </is>
+      </c>
+      <c r="C333" t="inlineStr">
+        <is>
+          <t>Automation and AI to drive the future of inspection - Machinery Market</t>
+        </is>
+      </c>
+      <c r="D333" t="inlineStr">
+        <is>
+          <t>Thu, 29 Jan 2026 15:17:38 GMT</t>
+        </is>
+      </c>
+      <c r="E333" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxOTjVJRVQ1dFRxTlhMeXV1ckc0eF9tUm5SSHBJckdZUWVURmdKRXptc1lVVlJLMmNPZDJldEtzdmtsRGplQ3c2WFVoVzZLTVVERzM4UkJPVzBMTnhRSW15dnhENXE5QnB0dHpnREJFY2ltYWJ3cUM5T0ZSOEg1Tlp5RzgwNGpTNGtuakZUS0ZvRDJqYU95dGhoRUQtV3pKdw?oc=5</t>
+        </is>
+      </c>
+      <c r="F333" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B334" t="inlineStr">
+        <is>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+        </is>
+      </c>
+      <c r="C334" t="inlineStr">
+        <is>
+          <t>Artificial Intelligence and Robotics in Aerospace and Defense Research Report 2026: $44.09 Bn Market Opportunities, Trends, Competitive Analysis, Strategies, Forecasts, 2020-2025, 2025-2030F, 2035F - Yahoo Finance UK</t>
+        </is>
+      </c>
+      <c r="D334" t="inlineStr">
+        <is>
+          <t>Thu, 29 Jan 2026 14:42:00 GMT</t>
+        </is>
+      </c>
+      <c r="E334" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxNY1VNLVhFODJseFNjUGdhM2ZvNHRvSnEzSHFuczFGbDkyd1RVZmlmZktxcDQtbFFfQlE3ZXJ3NDRCRzZITWRLNHQwdXluc1N1QjNTUmdHV1dWZGprS1lqelVvYVBnZUxlb1VnY3B4amdJOWRWV3d5d0Q3cEFxVHMtYllDaE94djYyVm1ETTF6dlA4S0o1YU4yRmZmRjBQZ0xK?oc=5</t>
+        </is>
+      </c>
+      <c r="F334" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B335" t="inlineStr">
+        <is>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+        </is>
+      </c>
+      <c r="C335" t="inlineStr">
+        <is>
+          <t>New cross-government AI and Future of Work Unit launched - Civil Service World</t>
+        </is>
+      </c>
+      <c r="D335" t="inlineStr">
+        <is>
+          <t>Thu, 29 Jan 2026 12:30:01 GMT</t>
+        </is>
+      </c>
+      <c r="E335" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxPV2czY1BKbEFTeS1rYzQwSXU2S3RHZHRpM3NSN3RaYlB0VU40cU1FVlEzNUN2MVJNN2N0S0VZVUw1bzhZWWw4NWNjc2EzLWtoVTFnYVIyNllrc1FVODh5TEh0Q25yRGxsemdrSWxxXzRfOGtvdUpnTmZ6UVVSeFp3TlBWUlRuS2ZuNTdLUzRtQ19nWUhSSTYtRXBuZVBmaU95T1Y0SnpxdkRiTWFvbmc?oc=5</t>
+        </is>
+      </c>
+      <c r="F335" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B336" t="inlineStr">
+        <is>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+        </is>
+      </c>
+      <c r="C336" t="inlineStr">
+        <is>
+          <t>Tesla axes Model S and X as revenues fall and focus shifts to AI and robotics - Business Matters</t>
+        </is>
+      </c>
+      <c r="D336" t="inlineStr">
+        <is>
+          <t>Fri, 30 Jan 2026 01:05:48 GMT</t>
+        </is>
+      </c>
+      <c r="E336" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMidkFVX3lxTFAtQjFhcmRlSXpOWHZ3YlFOMEdHckl0Rm1TanpBaGdqT3g4cXk3Y0toWUg5RkNPdjBXNjJrTHV2ZVNXeXJycVo0MjVoT3ZRWXpwMm8xWi1RVmt1N1l0YklqblRJdjVneV9tUUtReUtYNUtJU3M0WEE?oc=5</t>
+        </is>
+      </c>
+      <c r="F336" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B337" t="inlineStr">
+        <is>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+        </is>
+      </c>
+      <c r="C337" t="inlineStr">
+        <is>
+          <t>AI (artificial intelligence) - The Guardian</t>
+        </is>
+      </c>
+      <c r="D337" t="inlineStr">
+        <is>
+          <t>Fri, 30 Jan 2026 06:04:08 GMT</t>
+        </is>
+      </c>
+      <c r="E337" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMihgFBVV95cUxOOGRqWXFCYzZUV2VpOGxtLThsdE5zVGxoQ20tNk9VMnROMWxYcE5aTnhkNlF2MjlFbHY0VU1fckNDcXZoaFNVY0hWZkpUYkNRSGhST1BjZkVwSGR3bHNic0hxSzhDRTRsSmJ4ZF9QbkZSYnQ3TXVUUkxDMEhNek53eUhKeFV0UQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F337" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B338" t="inlineStr">
+        <is>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+        </is>
+      </c>
+      <c r="C338" t="inlineStr">
+        <is>
+          <t>FOMO.ai unveils Hello Gordon for AI-led interviews - IT Brief UK</t>
+        </is>
+      </c>
+      <c r="D338" t="inlineStr">
+        <is>
+          <t>Fri, 30 Jan 2026 03:38:00 GMT</t>
+        </is>
+      </c>
+      <c r="E338" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMihAFBVV95cUxQUGxLSjdxcHVEMUpYRGtudk0zTHF1U1U5a1NCU29ybVEzbHNMdmE5LXpUOXZMZS1hUFo2WURtckRKQjFoaEVQd1JHbXFldElxYUQtTXEtVEd6Y3dxTk5KclRCUFgzeTdkYjdWRWFid2RVM283NmxzV0tlZ2tlbFZoU2Z1ekc?oc=5</t>
+        </is>
+      </c>
+      <c r="F338" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B339" t="inlineStr">
+        <is>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+        </is>
+      </c>
+      <c r="C339" t="inlineStr">
+        <is>
+          <t>Spain Logs Nearly 2,800 Personal Data Breach Notifications in 2025 as Ransomware and Cyber Intrusions Dominate - BABL AI</t>
+        </is>
+      </c>
+      <c r="D339" t="inlineStr">
+        <is>
+          <t>Fri, 30 Jan 2026 00:02:39 GMT</t>
+        </is>
+      </c>
+      <c r="E339" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxQUEo3UzFQcmR2Q0dDTEgtazdmR25kSTdSZVJMSVFMbENTQkM3Rnh4QkFSaDA1cEtwRnJnWjVpdUV4WE16MWxtS0JUWGtGTWk0NFBiNU1ZQVFhdFdqMF8zWldkMHJ3R3RNSUdpc2dQcU1VZDhHTXFjNHR5TVBBRFluZFlNSUwyazJ0MHRGZ1J6Um0zckJHblpUU1VKSnV4blBudm1kQ1ctU2QyTWZjLXRkSEozT0lEdVJBRVlaQ1hGSm5jM1JO?oc=5</t>
+        </is>
+      </c>
+      <c r="F339" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B340" t="inlineStr">
+        <is>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+        </is>
+      </c>
+      <c r="C340" t="inlineStr">
+        <is>
+          <t>The Dash Between Us—On Dickinson, AI, and the Fear of Coherence - thebubble.org.uk</t>
+        </is>
+      </c>
+      <c r="D340" t="inlineStr">
+        <is>
+          <t>Thu, 29 Jan 2026 11:00:27 GMT</t>
+        </is>
+      </c>
+      <c r="E340" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxPQzRsT1djeFNTQktWMG5ZTjRkTGhDdlJTcDNBNm4zMW9xTnAzZUJvTmRxc0otNWFabE83bEh5SHByVDFJM0J4WVpaTk03NUZGNDFRc2l4emVUdFRwYlB5MzZpLWFaRnV6ZGtmVlU1U29RaVdwZWJoSWxFYUE2bk5iME9FREZxZDFEZXRqOVZTV3RvWDRsQUhtODFvY0JUYzFwWDJ5dVZTdXpPMmM?oc=5</t>
+        </is>
+      </c>
+      <c r="F340" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B341" t="inlineStr">
+        <is>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+        </is>
+      </c>
+      <c r="C341" t="inlineStr">
+        <is>
+          <t>Viewpoint: the EU’s ‘CERN for AI’ is nothing of the sort - Science|Business</t>
+        </is>
+      </c>
+      <c r="D341" t="inlineStr">
+        <is>
+          <t>Thu, 29 Jan 2026 14:44:53 GMT</t>
+        </is>
+      </c>
+      <c r="E341" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxQdlg3YUtTSlNTYkhBSnBHQ2ZVcFFBakRHRFBSMlRKMUhOc01KSGtCeXNNMWVBS1JRZ1VvUDg1VmVSYzBhbXZWNkxyWXd2UEo1R0Z5dzJ2RTA5eC1nYkVCd0ZRQlo3Vmhza1pZU0NFaS1CTjBLWktrTlNHQXQ0SmR2cA?oc=5</t>
+        </is>
+      </c>
+      <c r="F341" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B342" t="inlineStr">
+        <is>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+        </is>
+      </c>
+      <c r="C342" t="inlineStr">
+        <is>
+          <t>Smart Communications names Heidi Johnson AI leader - IT Brief UK</t>
+        </is>
+      </c>
+      <c r="D342" t="inlineStr">
+        <is>
+          <t>Fri, 30 Jan 2026 02:33:00 GMT</t>
+        </is>
+      </c>
+      <c r="E342" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMihAFBVV95cUxQZDZMR0t3SWhkbnJJSzUtQzYwRTNkQUhGSkRYQk03cFlSRGdYTHZYS1VfaWVwMjk1QnVYLS1DX0xITy1odUVfZk5WQnE0WjNQb1FhQ2dReHUtSG9SckZseG5UQTZtLWlmb0Rfbk1fT21VNTVzSk9fRTJqMk1JalRjcXdBdm8?oc=5</t>
+        </is>
+      </c>
+      <c r="F342" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B343" t="inlineStr">
+        <is>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+        </is>
+      </c>
+      <c r="C343" t="inlineStr">
+        <is>
+          <t>Law and AI: Shared terms, different meanings - Fieldfisher</t>
+        </is>
+      </c>
+      <c r="D343" t="inlineStr">
+        <is>
+          <t>Thu, 29 Jan 2026 12:50:16 GMT</t>
+        </is>
+      </c>
+      <c r="E343" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiiAFBVV95cUxQc0NlU0RPRkRrZ1dWMnBfclJ4bEhIZURyeThwQi13YUNRWmxFRUR5Q21HMENHNjhBdFVHd3RfN29YZFEweDN0TU9QUkxrUF9CaC1jY0VFZnUwWVlhb25sQmM0TExVUzVvaHJacjhwcXAyMmNQMEZPcHFPTXJuNGMxVzRhUHpvUDg2?oc=5</t>
+        </is>
+      </c>
+      <c r="F343" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B344" t="inlineStr">
+        <is>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+        </is>
+      </c>
+      <c r="C344" t="inlineStr">
+        <is>
+          <t>Companies Are Laying Off Workers Because of AI’s Potential—Not Its Performance - Harvard Business Review</t>
+        </is>
+      </c>
+      <c r="D344" t="inlineStr">
+        <is>
+          <t>Thu, 29 Jan 2026 13:44:48 GMT</t>
+        </is>
+      </c>
+      <c r="E344" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxQZk83TWNoZnJEeWF4M0pseHZlSmxTbC1JWjlPSTFHU3RobDJuZWZveWNXWUVQcUp3dzlSRzAzQnd2N19WR3N0ejV5cVUtbExPdktHVkdtNWtUVktER05EaUVadHJ1TU5ITTgyaThFLUlSLWhnbUk5QS1JQ1Y3NmdaalE3NUpseVdiVUYtbTFHZjNkX1l4WWZ3dFhYWU1LLWNEVmdZ?oc=5</t>
+        </is>
+      </c>
+      <c r="F344" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B345" t="inlineStr">
+        <is>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+        </is>
+      </c>
+      <c r="C345" t="inlineStr">
+        <is>
+          <t>EU-India deal highlights growing alignment on technology policy - Science|Business</t>
+        </is>
+      </c>
+      <c r="D345" t="inlineStr">
+        <is>
+          <t>Thu, 29 Jan 2026 15:30:16 GMT</t>
+        </is>
+      </c>
+      <c r="E345" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxORW1IRHBocDFfdkx1cndFc20waWtOVHpEaWRKT3dIX2J1THZWUkNLYzkzdzdfWm9KZUlTQTZtTXRQWktyMzJPejlGZktmck52Ti1DWkFhWllDTlgwTllNNHotSGlieF9HNFFLemt3eXFraldNdVhkcDl5X0xIMTBOZUs0NEE5ejA0V2gzRkxzUW85NTEtbHBfeFI3ckR3TkhTckZWdUgyMGppSC1jR0FjeWN3?oc=5</t>
+        </is>
+      </c>
+      <c r="F345" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B346" t="inlineStr">
+        <is>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+        </is>
+      </c>
+      <c r="C346" t="inlineStr">
+        <is>
+          <t>AI and efficiency drive Bank of Scotland-owner Lloyds to £6.7bn profit - Scottish Financial News</t>
+        </is>
+      </c>
+      <c r="D346" t="inlineStr">
+        <is>
+          <t>Thu, 29 Jan 2026 13:12:16 GMT</t>
+        </is>
+      </c>
+      <c r="E346" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxNTmxUZVhuNF90MmxKeDZaSmlzX3BvV19GcWVORWpOTXYzYWpVWkVvTGRhZDV6SUlKTWxaOFBRNkVQU1NhbnVRSXVoSlF0THF4UEg3VU5UcVVLWlJpbFJUek1XYnhSOWpubGxzWllEMkYyUjhZdlNteEJCby1WNlQxcDNGTkVFbTZFYzhCbDV4UVQyc0VZc1ExY0dwbVJ6OGFmVlNVZk1EZ0htLWhJVW5IMWVzOVNwdDN1?oc=5</t>
+        </is>
+      </c>
+      <c r="F346" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B347" t="inlineStr">
+        <is>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+        </is>
+      </c>
+      <c r="C347" t="inlineStr">
+        <is>
+          <t>NTT DATA Signs Strategic Collaboration Agreement with AWS to Accelerate Enterprise Cloud and Agentic AI Adoption - NTT, Inc.</t>
+        </is>
+      </c>
+      <c r="D347" t="inlineStr">
+        <is>
+          <t>Thu, 29 Jan 2026 12:54:19 GMT</t>
+        </is>
+      </c>
+      <c r="E347" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMivgFBVV95cUxPTWMwZGF5Z0FBYXBRNzQ5UE8zMXkwTkZ1V0VrNE1OTEtBWUxnbnF4dTlrZ01CV0kxeG5VQjRiVFJOclZONHNYV3hXc0hjV0NQTUE3OEZFVTJOTXpUeG1YdXZ5cTVMX0JwYm9nOXhocDhYMURVdXBiUjFLYTFaQnJhVG8xUDhVcWZLQVpJczJuSGZFc050Q0ttWFZIZ3BjY21PNmNDYzBUdWI1NV94VDh4amhVTlh3TW9hSHpOSERn?oc=5</t>
+        </is>
+      </c>
+      <c r="F347" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B348" t="inlineStr">
+        <is>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+        </is>
+      </c>
+      <c r="C348" t="inlineStr">
+        <is>
+          <t>Civil litigation: AI and the evolving role of solicitors - The Law Society Gazette</t>
+        </is>
+      </c>
+      <c r="D348" t="inlineStr">
+        <is>
+          <t>Thu, 29 Jan 2026 12:37:13 GMT</t>
+        </is>
+      </c>
+      <c r="E348" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxQeEd5cTBwOF90anNjUmFxRjhyT1dhcF9HcXZFOXRtVUY1SFJZOWdRaHdXaHRPb3VLX1FnLUNfenNRYTRmNkNVdW9jSnZzTGhUbW56S1dDUXlRQzQ3Q3pKTG53NVMxeVlKS1huUVU5elFfS1lveXd6Nk5WaERIcXpkTm9zeTJFSlJZSEV6S28zMElLdUVocUFKc3FwY0t1MjRw?oc=5</t>
+        </is>
+      </c>
+      <c r="F348" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B349" t="inlineStr">
+        <is>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+        </is>
+      </c>
+      <c r="C349" t="inlineStr">
+        <is>
+          <t>AI is improving performance across global mining operations - BHP</t>
+        </is>
+      </c>
+      <c r="D349" t="inlineStr">
+        <is>
+          <t>Fri, 30 Jan 2026 01:33:09 GMT</t>
+        </is>
+      </c>
+      <c r="E349" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxPUWdUa3NUYzZ3dGtCM1Z2NDhfN3Mtclp5SlVVRy1FTUc2LXRHbXcxSlhXTWpJWE5oYkx2elMtVzYxTkZSN3BpUDlzRHJ3WFBwSjctMWF1WGRSVUFnNGhEREt3SXlJU2UtcThzNGVFckZYZ0x1dWRrbGgxRHpoVjdNOFItVEhMX29SckJHS1BwR3FKZHh6OHV1Q0xqMzBQMWRKN2NF?oc=5</t>
+        </is>
+      </c>
+      <c r="F349" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B350" t="inlineStr">
+        <is>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+        </is>
+      </c>
+      <c r="C350" t="inlineStr">
+        <is>
+          <t>AI, Automation, and Biosensors Speed the Path to Synthetic Jet Fuel - newscenter.lbl.gov</t>
+        </is>
+      </c>
+      <c r="D350" t="inlineStr">
+        <is>
+          <t>Thu, 29 Jan 2026 17:07:02 GMT</t>
+        </is>
+      </c>
+      <c r="E350" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxPd2c2cEU2TDBzRWlqZ1FPSXVWMFdUVlpVaWs5QlRzRElqMkt5ZlVjZXVybnA5MnNfeDJoUGkwRWZIclhnZGRvMjFwVnoza2l5bFptT0h5QnNqeW9LRU9hYmlYVmgzd2dsRjBhUTlINDhjM21OWXo5UXFTNFBGWFVNajNUVlRqMUgwZUp2OUxxZE0xOHNPdDM4U0ttMmtMYXBmVDdqVHFxUQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F350" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B351" t="inlineStr">
+        <is>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+        </is>
+      </c>
+      <c r="C351" t="inlineStr">
+        <is>
+          <t>The AI Shift: Could AI make — rather than take — jobs? - Financial Times</t>
+        </is>
+      </c>
+      <c r="D351" t="inlineStr">
+        <is>
+          <t>Thu, 29 Jan 2026 12:39:05 GMT</t>
+        </is>
+      </c>
+      <c r="E351" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMicEFVX3lxTE93UDFWSDh5ME9XczVpc1FxR3h0LThuXzVpRG52U2lxd09EMGV6QWlqNDlPXzE0bXNRR01QQjQzck1Ld2JoVDRhRlU5RENieTAtMHp4V0ZGZGtMWjZKWlp0NjFwNlplQ1NKVUljZ2pIUHA?oc=5</t>
+        </is>
+      </c>
+      <c r="F351" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B352" t="inlineStr">
+        <is>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+        </is>
+      </c>
+      <c r="C352" t="inlineStr">
+        <is>
+          <t>Meta scales back VR ambitions and shifts focus to AI and smart glasses - New Electronics</t>
+        </is>
+      </c>
+      <c r="D352" t="inlineStr">
+        <is>
+          <t>Thu, 29 Jan 2026 09:43:44 GMT</t>
+        </is>
+      </c>
+      <c r="E352" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxNTFJ1RHh6bGxZNEQzWWUySkJqeXBMZGRaeGk0aVdPU2pvTEo3TW9hMnQ2SDFTMU1McGFqQWZBRy13eFYyeE9vMURBM1hCVTg4QXQzdXFaY3loRlNhYmloX09wdGI3RU9RVzFKZW5DdUM5UG1zLW45UGR3WW93MzJuZ0h2UTVLYjliSzdzQXdFaEZBSjdoalEyRGxpRTgtcmZWUU5fUGRIaEtRWkJaX1pOQUUwLVk4VDdu?oc=5</t>
+        </is>
+      </c>
+      <c r="F352" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B353" t="inlineStr">
+        <is>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+        </is>
+      </c>
+      <c r="C353" t="inlineStr">
+        <is>
+          <t>You have until Monday to help influence the NHS's use of AI - HSJ | Health Service Journal</t>
+        </is>
+      </c>
+      <c r="D353" t="inlineStr">
+        <is>
+          <t>Thu, 29 Jan 2026 09:15:39 GMT</t>
+        </is>
+      </c>
+      <c r="E353" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxPeGZSclZ0UjVFaDktQUdOS3k2NWpWNm05bjlPOThpbWllS0JFVGs2YXd6Z245b2dVcHFPOWxTb0k5Z01rQlZPVExGc2tvUkF5SmN2elQwREpmY01UZVdwVFI4QzFIVWlTdk1aUEVwS3FlcGU0RjkwbXkwQ2lVdDRGalZoajNiNl93ZW45bFBrQkYyRWZLcEEta2dwclRXc0pLWDNFLWlPY3hHRlBEaWYyY0xlS1ZkLVNHX04yRnY1bw?oc=5</t>
+        </is>
+      </c>
+      <c r="F353" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B354" t="inlineStr">
+        <is>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+        </is>
+      </c>
+      <c r="C354" t="inlineStr">
+        <is>
+          <t>New national AI centre ‘will drive innovation’ across forces - Police Professional</t>
+        </is>
+      </c>
+      <c r="D354" t="inlineStr">
+        <is>
+          <t>Thu, 29 Jan 2026 17:04:07 GMT</t>
+        </is>
+      </c>
+      <c r="E354" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxNMXVYQmhvZGJiOUhsSGN3am4yaGplYTJTZ2JNaDJtcGxrOVJDT3RkcHhsNzEzdjNOOEs5Qy1HdXBOSUgwU3pudTJHNUJ3OGFpQmpmR05zVGRsYkg2NEJwV0x1QVhrX3oxaDhvTkx1WnRYa2pOMU13S0NMUEZhQXZYM1pEN0liU2Q4RXNrbEJwbk92RkpRaUNZcG54cw?oc=5</t>
+        </is>
+      </c>
+      <c r="F354" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B355" t="inlineStr">
+        <is>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+        </is>
+      </c>
+      <c r="C355" t="inlineStr">
+        <is>
+          <t>War Department Boards Merge to Form New Science, Technology and Innovation Board (STIB) - U.S. Department of War (.gov)</t>
+        </is>
+      </c>
+      <c r="D355" t="inlineStr">
+        <is>
+          <t>Thu, 29 Jan 2026 16:06:10 GMT</t>
+        </is>
+      </c>
+      <c r="E355" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi1AFBVV95cUxQTEVhR2tTclVKUDk2N1Z6dV8yaElkVHE4bHRGOHFYTE0yWGstTXJwZS1LNkxwZnNBZ2lVd3J0MXVKT1pVR3pjUVRkbHJld2ZoZ0ZaLXhVb3VEZl9xVndXODlLZkpOV2NuZVA4VWZENlFReWVka21nV0NJSzZWVnZFbFg2M0pNT1NFMTRLLW1wSVZ3a2R6YjkweGpiSDRweGZ4QVBIMm9uOE1pbnRxUWR0T2o0S2tpNS16REFwWUt5bXZaR1dVRV83NW90SUxuWUZXZU9EQw?oc=5</t>
+        </is>
+      </c>
+      <c r="F355" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B356" t="inlineStr">
+        <is>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+        </is>
+      </c>
+      <c r="C356" t="inlineStr">
+        <is>
+          <t>Sponsor focus on AI, defence set to drive European tech buyouts in 2026 – Dealspeak EMEA - White &amp; Case LLP</t>
+        </is>
+      </c>
+      <c r="D356" t="inlineStr">
+        <is>
+          <t>Thu, 29 Jan 2026 12:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="E356" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxPN2NZTHVnMjgzcEZ2dDJHcVVwQVcwMjYtTy1VVlJ2bUFyN0lrNmhIdjh6WTVzTjNUYUF3UzFCNlJKZFZpcV9jN2FUeHVUa0dDTjlKMU9QbVd5eF9MRzdDd0pGajVYMVJwNVpWaFVZaGlQSGNETndGdDM3V1BUaW1CRFo2NVFFTlZZS2lvQ2ROZlBEQlhXOHdlYmFUZTAyRHNvR25fQ0Fpc1Z4NVAxamVQR2xHRQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F356" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B357" t="inlineStr">
+        <is>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+        </is>
+      </c>
+      <c r="C357" t="inlineStr">
+        <is>
+          <t>Mercedes-Benz leads with smart factory innovations - Automotive Manufacturing Solutions</t>
+        </is>
+      </c>
+      <c r="D357" t="inlineStr">
+        <is>
+          <t>Thu, 29 Jan 2026 17:53:36 GMT</t>
+        </is>
+      </c>
+      <c r="E357" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxPZTdRRzIybDVfRVpoTU13aGNTY25acUZuR2h0SERybDZTNmtOb0FmbEV4MXJSUW4tX0s1VnNEcmFJRXFuWmhTSnJtVnN2aWU4enR2M2t4dXN0S0JWc1NJaENxRUszU2h4QXpONnYzY01fQkhNRkN3TGlYdGdZOHgweFpmWVBzS19RSHd6T3IzZVZscU1kWFZVaGhZSjZnYmVlMW9zNG9pZ2R5MHoxc2NvNnlNTWFoRzQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F357" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B358" t="inlineStr">
+        <is>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+        </is>
+      </c>
+      <c r="C358" t="inlineStr">
+        <is>
+          <t>Universal basic income could be used to soften hit from AI job losses in UK, minister says - The Guardian</t>
+        </is>
+      </c>
+      <c r="D358" t="inlineStr">
+        <is>
+          <t>Thu, 29 Jan 2026 08:57:00 GMT</t>
+        </is>
+      </c>
+      <c r="E358" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxOdlNOXzBSUGFveVpPMEtEVklHdy01SllZNVVIX3dHRXNpM0tVYnlxM291QmZ4V2hnN2xidjFJNzl1QkRVTG0yTHUtRzlwUE45MGNJZlotNFFBQmE0cnRRZU9rSzRUSlRaMmU1dXJ5ODFhenQzXzhESnAxcmY1R1c3azl1QjlZTFMtMTh6WnBTdFNlWE0zdmpHRTVjdTRGdnk4cWlaZnpWcjMxaXFWRmExQkhB?oc=5</t>
+        </is>
+      </c>
+      <c r="F358" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="B359" t="inlineStr">
+        <is>
+          <t>(technology OR cybersecurity OR ransomware OR hacking OR AI OR "artificial intelligence" OR "machine learning" OR automation OR quantum OR semiconductor OR software OR cloud OR 5G OR robotics) AND (launch OR update OR vulnerability OR breach OR research OR earnings OR partnership OR regulation) -(rumor OR review OR gaming OR crypto OR podcast OR live OR blog)</t>
+        </is>
+      </c>
+      <c r="C359" t="inlineStr">
+        <is>
+          <t>SMEs step up AI adoption as US pulls ahead of the UK - IT Brief UK</t>
+        </is>
+      </c>
+      <c r="D359" t="inlineStr">
+        <is>
+          <t>Thu, 29 Jan 2026 13:15:07 GMT</t>
+        </is>
+      </c>
+      <c r="E359" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMihwFBVV95cUxPZ0F1VXBxTFZjM2lmMlhNUGxHT1NySTY0R2Fqb1pJN1h1bXVSbUlsU09XaTFuZVZmSF85WW9MdUtELVhpNlJodTdDSThFX3Zub19meGZrdnFhRzl4NFQ4MUxJblFoWXpsNDZ1V3V4S3ptMU5KVlkxcjFkWUZQWEpOMVRkSW1laTQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F359" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="inlineStr">
+        <is>
+          <t>Fraud_Scam</t>
+        </is>
+      </c>
+      <c r="B360" t="inlineStr">
+        <is>
+          <t>(fraud OR scam OR phishing OR smishing OR vishing OR "identity theft" OR impersonation OR spoofing OR "account takeover" OR "payment fraud" OR "invoice fraud" OR "wire fraud" OR "business email compromise" OR BEC OR "fake invoice" OR "supplier fraud" OR "procurement fraud" OR "social engineering" OR extortion OR blackmail)AND (company OR business OR enterprise OR customer OR client OR employee OR bank OR financial OR payment OR transaction)</t>
+        </is>
+      </c>
+      <c r="C360" t="inlineStr">
+        <is>
+          <t>Scam emails impersonating JFSC target island businesses - Digital Watch Observatory</t>
+        </is>
+      </c>
+      <c r="D360" t="inlineStr">
+        <is>
+          <t>Thu, 29 Jan 2026 08:14:33 GMT</t>
+        </is>
+      </c>
+      <c r="E360" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMif0FVX3lxTE52eFpFclhVamlVZC14LW5vcFBPYkVpQ2k0WkZvbmdVX3lvZ2ppZXJPeDdTRlJlSGR0OU9ISFhhOTRYbTF1eFpjdUhnYzUxX05sLWJzZUNHMEhFMFZmcFBKNnFsUllselg2NXVSeXlkUzlRX0Nua2VNNTlqSFdIVW8?oc=5</t>
+        </is>
+      </c>
+      <c r="F360" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" t="inlineStr">
+        <is>
+          <t>Fraud_Scam</t>
+        </is>
+      </c>
+      <c r="B361" t="inlineStr">
+        <is>
+          <t>(fraud OR scam OR phishing OR smishing OR vishing OR "identity theft" OR impersonation OR spoofing OR "account takeover" OR "payment fraud" OR "invoice fraud" OR "wire fraud" OR "business email compromise" OR BEC OR "fake invoice" OR "supplier fraud" OR "procurement fraud" OR "social engineering" OR extortion OR blackmail)AND (company OR business OR enterprise OR customer OR client OR employee OR bank OR financial OR payment OR transaction)</t>
+        </is>
+      </c>
+      <c r="C361" t="inlineStr">
+        <is>
+          <t>City of Norfolk warns public about email scam - norfolkdailynews.com</t>
+        </is>
+      </c>
+      <c r="D361" t="inlineStr">
+        <is>
+          <t>Thu, 29 Jan 2026 15:59:00 GMT</t>
+        </is>
+      </c>
+      <c r="E361" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiyAFBVV95cUxQRWFYVHh0Y2ZIRTh4c2tIcXFkUDA1V1NjZ1NlWTNIdzZjVC1fVFJOYzkzeGswWnpGOVBFMVNIN3VhVjdxTFhiSF9kNl9lWkZvdFZ2VkY2Mm5Oa2dVZlBqLUlFRUdjZjFPVmdNb2J6VzFYc0xNUmg4Y3BYNFR1Q1FhblptZzhQYlQ1RHJJaEFCS1g1ZjhSTmwwblZPQWdibkhGNjFKZDFYaWYzS2VxU3kyUkVLa2Roc09mTUJUaUhsY2pqSTZCQUxCVg?oc=5</t>
+        </is>
+      </c>
+      <c r="F361" t="n">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
